--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A8FA56-F499-4750-AE5D-A9FF82C44E2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E35A25-66AE-4828-976E-1A081AC593C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1786,10 +1786,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CNS_05</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Historical Average or D&amp;A</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2380,6 +2376,9 @@
   </si>
   <si>
     <t>N</t>
+  </si>
+  <si>
+    <t>CNS_03</t>
   </si>
 </sst>
 </file>
@@ -3754,29 +3753,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4089,7 +4088,7 @@
         <v>362</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4121,10 +4120,10 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4135,7 +4134,7 @@
         <v>57.77</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E6" s="48"/>
     </row>
@@ -4187,13 +4186,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
-        <v>370</v>
-      </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="B12" s="342" t="s">
+        <v>369</v>
+      </c>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4217,7 +4216,7 @@
         <v>356</v>
       </c>
       <c r="C16" s="48" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D16" s="32"/>
       <c r="E16" s="5"/>
@@ -4240,7 +4239,7 @@
         <v>56</v>
       </c>
       <c r="C18" s="48" t="s">
-        <v>363</v>
+        <v>430</v>
       </c>
       <c r="E18" s="5"/>
     </row>
@@ -4252,7 +4251,7 @@
         <v>0.3</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E19" s="339">
         <v>0.2</v>
@@ -4276,7 +4275,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="B21" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
@@ -4291,7 +4290,7 @@
     </row>
     <row r="23" spans="1:6" ht="13.9">
       <c r="A23" s="247" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B23" s="36"/>
       <c r="C23" s="36"/>
@@ -4300,22 +4299,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
-        <v>371</v>
-      </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="B25" s="342" t="s">
+        <v>370</v>
+      </c>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>348</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4327,13 +4326,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4353,13 +4352,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4388,13 +4387,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4410,13 +4409,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4480,13 +4479,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4502,7 +4501,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>347</v>
       </c>
       <c r="C50" s="344"/>
@@ -4524,22 +4523,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
-        <v>372</v>
-      </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="B54" s="342" t="s">
+        <v>371</v>
+      </c>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4569,7 +4568,7 @@
     </row>
     <row r="58" spans="1:6">
       <c r="B58" s="254" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
@@ -4587,7 +4586,7 @@
     </row>
     <row r="61" spans="1:6" ht="13.9">
       <c r="A61" s="247" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B61" s="36"/>
       <c r="C61" s="36"/>
@@ -4600,22 +4599,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
-        <v>373</v>
-      </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="B63" s="342" t="s">
+        <v>372</v>
+      </c>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4668,27 +4667,27 @@
     </row>
     <row r="72" spans="1:6">
       <c r="B72" s="332" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
+        <v>373</v>
+      </c>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B74" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
-        <v>375</v>
-      </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4713,7 +4712,7 @@
     </row>
     <row r="79" spans="1:6" ht="13.9">
       <c r="A79" s="247" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B79" s="36"/>
       <c r="C79" s="36"/>
@@ -4725,13 +4724,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
-        <v>376</v>
-      </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="B81" s="342" t="s">
+        <v>375</v>
+      </c>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4744,13 +4743,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>353</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4780,7 +4779,7 @@
     </row>
     <row r="88" spans="2:6">
       <c r="B88" s="336" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C88" s="337">
         <f>BS!G30/BS!G27</f>
@@ -4789,7 +4788,7 @@
     </row>
     <row r="89" spans="2:6">
       <c r="B89" s="336" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C89" s="337">
         <f>BS!G31/BS!G27</f>
@@ -4798,7 +4797,7 @@
     </row>
     <row r="90" spans="2:6">
       <c r="B90" s="336" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C90" s="338">
         <f>BS!C50</f>
@@ -4881,13 +4880,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
-        <v>377</v>
-      </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="B101" s="342" t="s">
+        <v>376</v>
+      </c>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4904,7 +4903,7 @@
     </row>
     <row r="104" spans="1:6">
       <c r="B104" s="336" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C104" s="248">
         <f>BS!D47</f>
@@ -4917,7 +4916,7 @@
     </row>
     <row r="106" spans="1:6" ht="13.9">
       <c r="A106" s="247" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B106" s="36"/>
       <c r="C106" s="36"/>
@@ -4926,13 +4925,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
-        <v>378</v>
-      </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="B108" s="343" t="s">
+        <v>377</v>
+      </c>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5075,17 +5074,17 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
-        <v>381</v>
-      </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="B119" s="346" t="s">
+        <v>380</v>
+      </c>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B121" s="36"/>
       <c r="C121" s="36"/>
@@ -5094,22 +5093,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
+        <v>378</v>
+      </c>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
+    </row>
+    <row r="124" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B124" s="342" t="s">
         <v>379</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
-    </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
-        <v>380</v>
-      </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5149,14 +5148,14 @@
     </row>
     <row r="130" spans="2:4">
       <c r="B130" s="234" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C130" s="337">
         <f>C19</f>
         <v>0.3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="131" spans="2:4">
@@ -5203,14 +5202,14 @@
     </row>
     <row r="136" spans="2:4">
       <c r="B136" s="234" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C136" s="337">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="137" spans="2:4">
@@ -5257,14 +5256,14 @@
     </row>
     <row r="142" spans="2:4">
       <c r="B142" s="234" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C142" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="143" spans="2:4">
@@ -5289,7 +5288,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="B145" s="80" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C145" s="239">
         <f>Scenarios!C99</f>
@@ -5311,7 +5310,7 @@
     </row>
     <row r="148" spans="1:6" ht="13.9">
       <c r="A148" s="247" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B148" s="36"/>
       <c r="C148" s="36"/>
@@ -5320,22 +5319,22 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
-        <v>387</v>
-      </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="B150" s="341" t="s">
+        <v>386</v>
+      </c>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="344" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C153" s="344"/>
       <c r="D153" s="344"/>
@@ -5344,89 +5343,78 @@
     </row>
     <row r="154" spans="1:6">
       <c r="B154" s="238" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="155" spans="1:6">
       <c r="B155" s="238" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="156" spans="1:6">
       <c r="B156" s="238" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="158" spans="1:6">
       <c r="B158" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
-        <v>392</v>
-      </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="B159" s="343" t="s">
+        <v>391</v>
+      </c>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
+        <v>392</v>
+      </c>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
+    </row>
+    <row r="163" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B163" s="340" t="s">
         <v>393</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
-    </row>
-    <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
-        <v>394</v>
-      </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="238" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="238" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="168" spans="2:6">
       <c r="B168" s="238" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5443,6 +5431,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -6000,7 +5999,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C22" s="181">
         <v>2542046725</v>
@@ -6036,7 +6035,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C23" s="181">
         <v>-633430356</v>
@@ -6072,7 +6071,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="C24" s="181">
         <v>-3527746522</v>
@@ -7436,7 +7435,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8814,7 +8813,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -12302,7 +12301,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -13675,7 +13674,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13727,7 +13726,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -14236,7 +14235,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -17190,7 +17189,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17405,12 +17404,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!E19</f>
@@ -17461,14 +17460,14 @@
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="316"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!C67</f>
@@ -17503,14 +17502,14 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>59.048136223898794</v>
       </c>
       <c r="D99" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E35A25-66AE-4828-976E-1A081AC593C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456BB8B1-204C-460A-8054-C958A68B5EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3753,29 +3753,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4131,7 +4131,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>57.77</v>
+        <v>57.52</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>427</v>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>27959.016108460004</v>
+        <v>27838.023308960004</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4186,13 +4186,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>8.8211113876756064E-2</v>
+        <v>8.984625754804787E-2</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4299,22 +4299,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>348</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4326,13 +4326,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4352,13 +4352,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4387,13 +4387,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4409,13 +4409,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4479,13 +4479,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4501,7 +4501,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>347</v>
       </c>
       <c r="C50" s="344"/>
@@ -4523,22 +4523,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.9541392420431456E-2</v>
+        <v>7.9887104313774771E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.1544054007270202E-2</v>
+        <v>4.1724617524339355E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4599,22 +4599,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4672,22 +4672,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4724,13 +4724,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>375</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4743,13 +4743,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>353</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4880,13 +4880,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>376</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4925,13 +4925,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>377</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5074,13 +5074,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>380</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5093,22 +5093,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>378</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>379</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5319,13 +5319,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B150" s="347" t="s">
         <v>386</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5362,13 +5362,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
+      <c r="B159" s="341" t="s">
         <v>391</v>
       </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5376,22 +5376,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
+      <c r="B162" s="346" t="s">
         <v>392</v>
       </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
+      <c r="B163" s="346" t="s">
         <v>393</v>
       </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5415,6 +5415,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5431,17 +5442,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -12984,12 +12984,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.1544054007270202E-2</v>
+        <v>4.1724617524339355E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.1544054007270202E-2</v>
+        <v>4.1724617524339355E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14183,50 +14183,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.9541392420431456E-2</v>
+        <v>7.9887104313774771E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.10367576704961093</v>
+        <v>0.10412637452114087</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.11379309515342934</v>
+        <v>0.11428767571303221</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.10890168055802604</v>
+        <v>0.10937500149230119</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10113196252517834</v>
+        <v>0.10157151382266259</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>6.238313437083072E-2</v>
+        <v>6.2654271081413263E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.2932634815763679E-2</v>
+        <v>2.3032307254983793E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.1526932651969387E-2</v>
+        <v>2.1620495467737682E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2331913028072258E-2</v>
+        <v>1.2385511398326396E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.2177554556255571E-2</v>
+        <v>1.2230482036072399E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>6.7419883542669725E-3</v>
+        <v>6.7712911548331537E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14240,43 +14240,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0452777139012749E-2</v>
+        <v>8.0802450196814438E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6983690144214971E-2</v>
+        <v>9.740521174602397E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2524702262939809E-2</v>
+        <v>9.2926843701843412E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5809750482387301E-2</v>
+        <v>8.6182706630172357E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2674490733233404E-2</v>
+        <v>6.2946893770147672E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6057316436809627E-2</v>
+        <v>2.617056972452177E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5067034882981195E-2</v>
+        <v>1.5132520952535181E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1664299406491632E-2</v>
+        <v>1.1714996118098429E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0052250929407986E-3</v>
+        <v>5.0269793744643588E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.4920395054079653E-3</v>
+        <v>-5.5159096353862682E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16545,7 +16545,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-57.77</v>
+        <v>-57.52</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16785,7 +16785,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>57.77</v>
+        <v>57.52</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>57.77</v>
+        <v>57.52</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17396,7 +17396,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>8.8211113876756064E-2</v>
+        <v>8.984625754804787E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456BB8B1-204C-460A-8054-C958A68B5EDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577612B6-D8A3-41E6-ACBD-6CA894EDF693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3753,29 +3753,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4131,7 +4131,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>57.52</v>
+        <v>57.4</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>427</v>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>27838.023308960004</v>
+        <v>27779.946765200002</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4186,13 +4186,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
+      <c r="B12" s="342" t="s">
         <v>369</v>
       </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
+      <c r="C12" s="342"/>
+      <c r="D12" s="342"/>
+      <c r="E12" s="342"/>
+      <c r="F12" s="342"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>8.984625754804787E-2</v>
+        <v>9.0634582120934004E-2</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4299,22 +4299,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
+      <c r="B25" s="342" t="s">
         <v>370</v>
       </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
+      <c r="C25" s="342"/>
+      <c r="D25" s="342"/>
+      <c r="E25" s="342"/>
+      <c r="F25" s="342"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
+      <c r="B26" s="345" t="s">
         <v>348</v>
       </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
+      <c r="C26" s="345"/>
+      <c r="D26" s="345"/>
+      <c r="E26" s="345"/>
+      <c r="F26" s="345"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4326,13 +4326,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+      <c r="B29" s="343" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
+      <c r="C29" s="343"/>
+      <c r="D29" s="343"/>
+      <c r="E29" s="343"/>
+      <c r="F29" s="343"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4352,13 +4352,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+      <c r="B32" s="343" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
+      <c r="C32" s="343"/>
+      <c r="D32" s="343"/>
+      <c r="E32" s="343"/>
+      <c r="F32" s="343"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4387,13 +4387,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+      <c r="B36" s="343" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
+      <c r="C36" s="343"/>
+      <c r="D36" s="343"/>
+      <c r="E36" s="343"/>
+      <c r="F36" s="343"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4409,13 +4409,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
+      <c r="B39" s="343" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
+      <c r="C39" s="343"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="343"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4479,13 +4479,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="343" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
+      <c r="C47" s="343"/>
+      <c r="D47" s="343"/>
+      <c r="E47" s="343"/>
+      <c r="F47" s="343"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4501,7 +4501,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
+      <c r="B50" s="343" t="s">
         <v>347</v>
       </c>
       <c r="C50" s="344"/>
@@ -4523,22 +4523,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
+      <c r="B53" s="342" t="s">
         <v>352</v>
       </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
+      <c r="C53" s="342"/>
+      <c r="D53" s="342"/>
+      <c r="E53" s="342"/>
+      <c r="F53" s="342"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
+      <c r="B54" s="342" t="s">
         <v>371</v>
       </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
+      <c r="C54" s="342"/>
+      <c r="D54" s="342"/>
+      <c r="E54" s="342"/>
+      <c r="F54" s="342"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.9887104313774771E-2</v>
+        <v>8.005411568167814E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.1724617524339355E-2</v>
+        <v>4.1811846689895467E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4599,22 +4599,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+      <c r="B63" s="342" t="s">
         <v>372</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
+      <c r="C63" s="342"/>
+      <c r="D63" s="342"/>
+      <c r="E63" s="342"/>
+      <c r="F63" s="342"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
+      <c r="B64" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
+      <c r="C64" s="345"/>
+      <c r="D64" s="345"/>
+      <c r="E64" s="345"/>
+      <c r="F64" s="345"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4672,22 +4672,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
+      <c r="B73" s="342" t="s">
         <v>373</v>
       </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
+      <c r="C73" s="342"/>
+      <c r="D73" s="342"/>
+      <c r="E73" s="342"/>
+      <c r="F73" s="342"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
+      <c r="B74" s="342" t="s">
         <v>374</v>
       </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
+      <c r="C74" s="342"/>
+      <c r="D74" s="342"/>
+      <c r="E74" s="342"/>
+      <c r="F74" s="342"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4724,13 +4724,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
+      <c r="B81" s="342" t="s">
         <v>375</v>
       </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
+      <c r="C81" s="342"/>
+      <c r="D81" s="342"/>
+      <c r="E81" s="342"/>
+      <c r="F81" s="342"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4743,13 +4743,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
+      <c r="B85" s="342" t="s">
         <v>353</v>
       </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
+      <c r="C85" s="342"/>
+      <c r="D85" s="342"/>
+      <c r="E85" s="342"/>
+      <c r="F85" s="342"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4880,13 +4880,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
+      <c r="B101" s="342" t="s">
         <v>376</v>
       </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+      <c r="C101" s="342"/>
+      <c r="D101" s="342"/>
+      <c r="E101" s="342"/>
+      <c r="F101" s="342"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4925,13 +4925,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
+      <c r="B108" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
+      <c r="C108" s="343"/>
+      <c r="D108" s="343"/>
+      <c r="E108" s="343"/>
+      <c r="F108" s="343"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5074,13 +5074,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
+      <c r="B119" s="346" t="s">
         <v>380</v>
       </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
+      <c r="C119" s="346"/>
+      <c r="D119" s="346"/>
+      <c r="E119" s="346"/>
+      <c r="F119" s="346"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5093,22 +5093,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+      <c r="B123" s="347" t="s">
         <v>378</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
+      <c r="C123" s="347"/>
+      <c r="D123" s="347"/>
+      <c r="E123" s="347"/>
+      <c r="F123" s="347"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
+      <c r="B124" s="342" t="s">
         <v>379</v>
       </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
+      <c r="C124" s="342"/>
+      <c r="D124" s="342"/>
+      <c r="E124" s="342"/>
+      <c r="F124" s="342"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5319,13 +5319,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
+      <c r="B150" s="341" t="s">
         <v>386</v>
       </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
+      <c r="C150" s="342"/>
+      <c r="D150" s="342"/>
+      <c r="E150" s="342"/>
+      <c r="F150" s="342"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5362,13 +5362,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
+      <c r="B159" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
+      <c r="C159" s="343"/>
+      <c r="D159" s="343"/>
+      <c r="E159" s="343"/>
+      <c r="F159" s="343"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5376,22 +5376,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
+      <c r="B162" s="340" t="s">
         <v>392</v>
       </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
+      <c r="C162" s="340"/>
+      <c r="D162" s="340"/>
+      <c r="E162" s="340"/>
+      <c r="F162" s="340"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
+      <c r="B163" s="340" t="s">
         <v>393</v>
       </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
+      <c r="C163" s="340"/>
+      <c r="D163" s="340"/>
+      <c r="E163" s="340"/>
+      <c r="F163" s="340"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5415,17 +5415,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5442,6 +5431,17 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -12984,12 +12984,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.1724617524339355E-2</v>
+        <v>4.1811846689895467E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.1724617524339355E-2</v>
+        <v>4.1811846689895467E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14183,50 +14183,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.9887104313774771E-2</v>
+        <v>8.005411568167814E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.10412637452114087</v>
+        <v>0.10434406032153351</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.11428767571303221</v>
+        <v>0.1145266046518051</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.10937500149230119</v>
+        <v>0.10960366003200636</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10157151382266259</v>
+        <v>0.1017838584508633</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>6.2654271081413263E-2</v>
+        <v>6.2785255620259425E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.3032307254983793E-2</v>
+        <v>2.3080458419976791E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.1620495467737682E-2</v>
+        <v>2.1665695109830515E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2385511398326396E-2</v>
+        <v>1.2411404453514536E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.2230482036072399E-2</v>
+        <v>1.2256050988064189E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>6.7712911548331537E-3</v>
+        <v>6.78544716421608E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14240,43 +14240,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0802450196814438E-2</v>
+        <v>8.0971375179804295E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.740521174602397E-2</v>
+        <v>9.7608846335040064E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2926843701843412E-2</v>
+        <v>9.3121115848955285E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6182706630172357E-2</v>
+        <v>8.6362879536019413E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2946893770147672E-2</v>
+        <v>6.3078490063743803E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.617056972452177E-2</v>
+        <v>2.6225281716977217E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5132520952535181E-2</v>
+        <v>1.5164156884840133E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1714996118098429E-2</v>
+        <v>1.1739487399181563E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0269793744643588E-3</v>
+        <v>5.037488739010278E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.5159096353862682E-3</v>
+        <v>-5.5274411537877726E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16545,7 +16545,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-57.52</v>
+        <v>-57.4</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16785,7 +16785,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>57.52</v>
+        <v>57.4</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>57.52</v>
+        <v>57.4</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17396,7 +17396,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>8.984625754804787E-2</v>
+        <v>9.0634582120934004E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{577612B6-D8A3-41E6-ACBD-6CA894EDF693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F16BEF1-5EC7-4551-BA34-A940B1091020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3753,29 +3753,29 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4131,7 +4131,7 @@
         <v>95</v>
       </c>
       <c r="C6" s="50">
-        <v>57.4</v>
+        <v>57.21</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>427</v>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="C10" s="35">
         <f>Thesis!C6*Thesis!C7/1000000</f>
-        <v>27779.946765200002</v>
+        <v>27687.992237580002</v>
       </c>
       <c r="D10" s="32"/>
       <c r="E10" s="5"/>
@@ -4186,13 +4186,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="342" t="s">
+      <c r="B12" s="340" t="s">
         <v>369</v>
       </c>
-      <c r="C12" s="342"/>
-      <c r="D12" s="342"/>
-      <c r="E12" s="342"/>
-      <c r="F12" s="342"/>
+      <c r="C12" s="340"/>
+      <c r="D12" s="340"/>
+      <c r="E12" s="340"/>
+      <c r="F12" s="340"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="45" t="s">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="C21" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>9.0634582120934004E-2</v>
+        <v>9.1887382418681218E-2</v>
       </c>
       <c r="D21" s="5"/>
       <c r="E21" s="5"/>
@@ -4299,22 +4299,22 @@
       <c r="F23" s="36"/>
     </row>
     <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="342" t="s">
+      <c r="B25" s="340" t="s">
         <v>370</v>
       </c>
-      <c r="C25" s="342"/>
-      <c r="D25" s="342"/>
-      <c r="E25" s="342"/>
-      <c r="F25" s="342"/>
+      <c r="C25" s="340"/>
+      <c r="D25" s="340"/>
+      <c r="E25" s="340"/>
+      <c r="F25" s="340"/>
     </row>
     <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="345" t="s">
+      <c r="B26" s="342" t="s">
         <v>348</v>
       </c>
-      <c r="C26" s="345"/>
-      <c r="D26" s="345"/>
-      <c r="E26" s="345"/>
-      <c r="F26" s="345"/>
+      <c r="C26" s="342"/>
+      <c r="D26" s="342"/>
+      <c r="E26" s="342"/>
+      <c r="F26" s="342"/>
     </row>
     <row r="28" spans="1:6">
       <c r="B28" s="234" t="s">
@@ -4326,13 +4326,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="343" t="s">
+      <c r="B29" s="341" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="343"/>
-      <c r="D29" s="343"/>
-      <c r="E29" s="343"/>
-      <c r="F29" s="343"/>
+      <c r="C29" s="341"/>
+      <c r="D29" s="341"/>
+      <c r="E29" s="341"/>
+      <c r="F29" s="341"/>
     </row>
     <row r="30" spans="1:6">
       <c r="B30" s="47" t="s">
@@ -4352,13 +4352,13 @@
       <c r="C31" s="76"/>
     </row>
     <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="343" t="s">
+      <c r="B32" s="341" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="343"/>
-      <c r="D32" s="343"/>
-      <c r="E32" s="343"/>
-      <c r="F32" s="343"/>
+      <c r="C32" s="341"/>
+      <c r="D32" s="341"/>
+      <c r="E32" s="341"/>
+      <c r="F32" s="341"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="47" t="s">
@@ -4387,13 +4387,13 @@
       </c>
     </row>
     <row r="36" spans="2:6">
-      <c r="B36" s="343" t="s">
+      <c r="B36" s="341" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="343"/>
-      <c r="D36" s="343"/>
-      <c r="E36" s="343"/>
-      <c r="F36" s="343"/>
+      <c r="C36" s="341"/>
+      <c r="D36" s="341"/>
+      <c r="E36" s="341"/>
+      <c r="F36" s="341"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="47" t="s">
@@ -4409,13 +4409,13 @@
       </c>
     </row>
     <row r="39" spans="2:6">
-      <c r="B39" s="343" t="s">
+      <c r="B39" s="341" t="s">
         <v>241</v>
       </c>
-      <c r="C39" s="343"/>
-      <c r="D39" s="343"/>
-      <c r="E39" s="343"/>
-      <c r="F39" s="343"/>
+      <c r="C39" s="341"/>
+      <c r="D39" s="341"/>
+      <c r="E39" s="341"/>
+      <c r="F39" s="341"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="47" t="s">
@@ -4479,13 +4479,13 @@
       </c>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="343" t="s">
+      <c r="B47" s="341" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="343"/>
-      <c r="D47" s="343"/>
-      <c r="E47" s="343"/>
-      <c r="F47" s="343"/>
+      <c r="C47" s="341"/>
+      <c r="D47" s="341"/>
+      <c r="E47" s="341"/>
+      <c r="F47" s="341"/>
     </row>
     <row r="48" spans="2:6">
       <c r="B48" s="47" t="s">
@@ -4501,7 +4501,7 @@
       </c>
     </row>
     <row r="50" spans="1:6">
-      <c r="B50" s="343" t="s">
+      <c r="B50" s="341" t="s">
         <v>347</v>
       </c>
       <c r="C50" s="344"/>
@@ -4523,22 +4523,22 @@
       </c>
     </row>
     <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="342" t="s">
+      <c r="B53" s="340" t="s">
         <v>352</v>
       </c>
-      <c r="C53" s="342"/>
-      <c r="D53" s="342"/>
-      <c r="E53" s="342"/>
-      <c r="F53" s="342"/>
+      <c r="C53" s="340"/>
+      <c r="D53" s="340"/>
+      <c r="E53" s="340"/>
+      <c r="F53" s="340"/>
     </row>
     <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="342" t="s">
+      <c r="B54" s="340" t="s">
         <v>371</v>
       </c>
-      <c r="C54" s="342"/>
-      <c r="D54" s="342"/>
-      <c r="E54" s="342"/>
-      <c r="F54" s="342"/>
+      <c r="C54" s="340"/>
+      <c r="D54" s="340"/>
+      <c r="E54" s="340"/>
+      <c r="F54" s="340"/>
     </row>
     <row r="56" spans="1:6">
       <c r="B56" s="47" t="s">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="C58" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.005411568167814E-2</v>
+        <v>8.0319983221959892E-2</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="C59" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.1811846689895467E-2</v>
+        <v>4.195070791819612E-2</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="13.9">
@@ -4599,22 +4599,22 @@
     </row>
     <row r="63" spans="1:6" ht="24.4" customHeight="1">
       <c r="A63" s="17"/>
-      <c r="B63" s="342" t="s">
+      <c r="B63" s="340" t="s">
         <v>372</v>
       </c>
-      <c r="C63" s="342"/>
-      <c r="D63" s="342"/>
-      <c r="E63" s="342"/>
-      <c r="F63" s="342"/>
+      <c r="C63" s="340"/>
+      <c r="D63" s="340"/>
+      <c r="E63" s="340"/>
+      <c r="F63" s="340"/>
     </row>
     <row r="64" spans="1:6">
-      <c r="B64" s="345" t="s">
+      <c r="B64" s="342" t="s">
         <v>253</v>
       </c>
-      <c r="C64" s="345"/>
-      <c r="D64" s="345"/>
-      <c r="E64" s="345"/>
-      <c r="F64" s="345"/>
+      <c r="C64" s="342"/>
+      <c r="D64" s="342"/>
+      <c r="E64" s="342"/>
+      <c r="F64" s="342"/>
     </row>
     <row r="66" spans="1:6">
       <c r="B66" s="234" t="s">
@@ -4672,22 +4672,22 @@
       <c r="C72" s="122"/>
     </row>
     <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="342" t="s">
+      <c r="B73" s="340" t="s">
         <v>373</v>
       </c>
-      <c r="C73" s="342"/>
-      <c r="D73" s="342"/>
-      <c r="E73" s="342"/>
-      <c r="F73" s="342"/>
+      <c r="C73" s="340"/>
+      <c r="D73" s="340"/>
+      <c r="E73" s="340"/>
+      <c r="F73" s="340"/>
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="342" t="s">
+      <c r="B74" s="340" t="s">
         <v>374</v>
       </c>
-      <c r="C74" s="342"/>
-      <c r="D74" s="342"/>
-      <c r="E74" s="342"/>
-      <c r="F74" s="342"/>
+      <c r="C74" s="340"/>
+      <c r="D74" s="340"/>
+      <c r="E74" s="340"/>
+      <c r="F74" s="340"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="47" t="s">
@@ -4724,13 +4724,13 @@
       <c r="A80" s="233"/>
     </row>
     <row r="81" spans="2:6">
-      <c r="B81" s="342" t="s">
+      <c r="B81" s="340" t="s">
         <v>375</v>
       </c>
-      <c r="C81" s="342"/>
-      <c r="D81" s="342"/>
-      <c r="E81" s="342"/>
-      <c r="F81" s="342"/>
+      <c r="C81" s="340"/>
+      <c r="D81" s="340"/>
+      <c r="E81" s="340"/>
+      <c r="F81" s="340"/>
     </row>
     <row r="82" spans="2:6">
       <c r="B82" s="1" t="s">
@@ -4743,13 +4743,13 @@
       </c>
     </row>
     <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="342" t="s">
+      <c r="B85" s="340" t="s">
         <v>353</v>
       </c>
-      <c r="C85" s="342"/>
-      <c r="D85" s="342"/>
-      <c r="E85" s="342"/>
-      <c r="F85" s="342"/>
+      <c r="C85" s="340"/>
+      <c r="D85" s="340"/>
+      <c r="E85" s="340"/>
+      <c r="F85" s="340"/>
     </row>
     <row r="86" spans="2:6">
       <c r="B86" s="47" t="s">
@@ -4880,13 +4880,13 @@
       </c>
     </row>
     <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="342" t="s">
+      <c r="B101" s="340" t="s">
         <v>376</v>
       </c>
-      <c r="C101" s="342"/>
-      <c r="D101" s="342"/>
-      <c r="E101" s="342"/>
-      <c r="F101" s="342"/>
+      <c r="C101" s="340"/>
+      <c r="D101" s="340"/>
+      <c r="E101" s="340"/>
+      <c r="F101" s="340"/>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
@@ -4925,13 +4925,13 @@
       <c r="F106" s="36"/>
     </row>
     <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="343" t="s">
+      <c r="B108" s="341" t="s">
         <v>377</v>
       </c>
-      <c r="C108" s="343"/>
-      <c r="D108" s="343"/>
-      <c r="E108" s="343"/>
-      <c r="F108" s="343"/>
+      <c r="C108" s="341"/>
+      <c r="D108" s="341"/>
+      <c r="E108" s="341"/>
+      <c r="F108" s="341"/>
     </row>
     <row r="110" spans="1:6" ht="12.4">
       <c r="B110" s="260" t="s">
@@ -5074,13 +5074,13 @@
       </c>
     </row>
     <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="346" t="s">
+      <c r="B119" s="345" t="s">
         <v>380</v>
       </c>
-      <c r="C119" s="346"/>
-      <c r="D119" s="346"/>
-      <c r="E119" s="346"/>
-      <c r="F119" s="346"/>
+      <c r="C119" s="345"/>
+      <c r="D119" s="345"/>
+      <c r="E119" s="345"/>
+      <c r="F119" s="345"/>
     </row>
     <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="247" t="s">
@@ -5093,22 +5093,22 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6">
-      <c r="B123" s="347" t="s">
+      <c r="B123" s="343" t="s">
         <v>378</v>
       </c>
-      <c r="C123" s="347"/>
-      <c r="D123" s="347"/>
-      <c r="E123" s="347"/>
-      <c r="F123" s="347"/>
+      <c r="C123" s="343"/>
+      <c r="D123" s="343"/>
+      <c r="E123" s="343"/>
+      <c r="F123" s="343"/>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="342" t="s">
+      <c r="B124" s="340" t="s">
         <v>379</v>
       </c>
-      <c r="C124" s="342"/>
-      <c r="D124" s="342"/>
-      <c r="E124" s="342"/>
-      <c r="F124" s="342"/>
+      <c r="C124" s="340"/>
+      <c r="D124" s="340"/>
+      <c r="E124" s="340"/>
+      <c r="F124" s="340"/>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="234" t="s">
@@ -5319,13 +5319,13 @@
       <c r="F148" s="36"/>
     </row>
     <row r="150" spans="1:6">
-      <c r="B150" s="341" t="s">
+      <c r="B150" s="347" t="s">
         <v>386</v>
       </c>
-      <c r="C150" s="342"/>
-      <c r="D150" s="342"/>
-      <c r="E150" s="342"/>
-      <c r="F150" s="342"/>
+      <c r="C150" s="340"/>
+      <c r="D150" s="340"/>
+      <c r="E150" s="340"/>
+      <c r="F150" s="340"/>
     </row>
     <row r="152" spans="1:6">
       <c r="B152" s="234" t="s">
@@ -5362,13 +5362,13 @@
       </c>
     </row>
     <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="343" t="s">
+      <c r="B159" s="341" t="s">
         <v>391</v>
       </c>
-      <c r="C159" s="343"/>
-      <c r="D159" s="343"/>
-      <c r="E159" s="343"/>
-      <c r="F159" s="343"/>
+      <c r="C159" s="341"/>
+      <c r="D159" s="341"/>
+      <c r="E159" s="341"/>
+      <c r="F159" s="341"/>
     </row>
     <row r="161" spans="2:6">
       <c r="B161" s="1" t="s">
@@ -5376,22 +5376,22 @@
       </c>
     </row>
     <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="340" t="s">
+      <c r="B162" s="346" t="s">
         <v>392</v>
       </c>
-      <c r="C162" s="340"/>
-      <c r="D162" s="340"/>
-      <c r="E162" s="340"/>
-      <c r="F162" s="340"/>
+      <c r="C162" s="346"/>
+      <c r="D162" s="346"/>
+      <c r="E162" s="346"/>
+      <c r="F162" s="346"/>
     </row>
     <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="340" t="s">
+      <c r="B163" s="346" t="s">
         <v>393</v>
       </c>
-      <c r="C163" s="340"/>
-      <c r="D163" s="340"/>
-      <c r="E163" s="340"/>
-      <c r="F163" s="340"/>
+      <c r="C163" s="346"/>
+      <c r="D163" s="346"/>
+      <c r="E163" s="346"/>
+      <c r="F163" s="346"/>
     </row>
     <row r="165" spans="2:6">
       <c r="B165" s="1" t="s">
@@ -5415,6 +5415,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B163:F163"/>
+    <mergeCell ref="B150:F150"/>
+    <mergeCell ref="B159:F159"/>
+    <mergeCell ref="B153:F153"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B119:F119"/>
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="B85:F85"/>
     <mergeCell ref="B124:F124"/>
     <mergeCell ref="B36:F36"/>
     <mergeCell ref="B12:F12"/>
@@ -5431,17 +5442,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="B54:F54"/>
     <mergeCell ref="B63:F63"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -12984,12 +12984,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.1811846689895467E-2</v>
+        <v>4.195070791819612E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.1811846689895467E-2</v>
+        <v>4.195070791819612E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14183,50 +14183,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.005411568167814E-2</v>
+        <v>8.0319983221959892E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.10434406032153351</v>
+        <v>0.10469059714133933</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.1145266046518051</v>
+        <v>0.1149069586962701</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.10960366003200636</v>
+        <v>0.10996766449636715</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.1017838584508633</v>
+        <v>0.10212189259009881</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>6.2785255620259425E-2</v>
+        <v>6.2993771588933586E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.3080458419976791E-2</v>
+        <v>2.3157110877585523E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.1665695109830515E-2</v>
+        <v>2.1737649000249458E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2411404453514536E-2</v>
+        <v>1.2452623940425352E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.2256050988064189E-2</v>
+        <v>1.2296754530936626E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>6.78544716421608E-3</v>
+        <v>6.807982297255777E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14240,43 +14240,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0971375179804295E-2</v>
+        <v>8.1240289028504914E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7608846335040064E-2</v>
+        <v>9.7933014851097691E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.3121115848955285E-2</v>
+        <v>9.3430380173571637E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6362879536019413E-2</v>
+        <v>8.6649699097491956E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.3078490063743803E-2</v>
+        <v>6.3287979892656776E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6225281716977217E-2</v>
+        <v>2.6312378440036571E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5164156884840133E-2</v>
+        <v>1.5214518531547346E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1739487399181563E-2</v>
+        <v>1.1778475383901794E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.037488739010278E-3</v>
+        <v>5.0542187313265151E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.5274411537877726E-3</v>
+        <v>-5.5457983259468296E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16545,7 +16545,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-57.4</v>
+        <v>-57.21</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16785,7 +16785,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>57.4</v>
+        <v>57.21</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>57.4</v>
+        <v>57.21</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17396,7 +17396,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.0634582120934004E-2</v>
+        <v>9.1887382418681218E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F16BEF1-5EC7-4551-BA34-A940B1091020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86934C2B-72B7-4ED8-B451-535ABFC66B20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -22,12 +22,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
-    <definedName name="Common_Shares">Thesis!$C$7</definedName>
+    <definedName name="Common_Shares">Thesis!$C$6</definedName>
     <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
-    <definedName name="Exchange_Rate">Thesis!$C$17</definedName>
-    <definedName name="Market_currency">Thesis!$D$6</definedName>
-    <definedName name="Market_Price">Thesis!$C$6</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$16</definedName>
+    <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
+    <definedName name="Market_currency">Thesis!$C$13</definedName>
+    <definedName name="Market_Price">Thesis!$C$12</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="439">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1578,10 +1578,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>N</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Operating Expenses Multiple (months)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1786,10 +1782,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Historical Average or D&amp;A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Step 1: Establishing the Company’s Sustainable Earning Power (Calculating Normalized FCFE)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2366,19 +2358,49 @@
     <t>@ Entry Yield</t>
   </si>
   <si>
+    <t>CNY</t>
+  </si>
+  <si>
+    <t>Company Information</t>
+  </si>
+  <si>
+    <t>Market Currency</t>
+  </si>
+  <si>
+    <t>Symbol:</t>
+  </si>
+  <si>
+    <t>Listing Information</t>
+  </si>
+  <si>
+    <t>Forex Symbol:</t>
+  </si>
+  <si>
+    <t>Capitalization:</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>重庆啤酒</t>
+  </si>
+  <si>
     <t>600132.SS</t>
   </si>
   <si>
-    <t>CNY</t>
-  </si>
-  <si>
-    <t>重庆啤酒</t>
-  </si>
-  <si>
-    <t>N</t>
+    <t/>
   </si>
   <si>
     <t>CNS_03</t>
+  </si>
+  <si>
+    <t>Latest Asset Value</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Historical Average or D&amp;A</t>
   </si>
 </sst>
 </file>
@@ -3052,7 +3074,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="352">
+  <cellXfs count="355">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3753,6 +3775,13 @@
     <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4065,13 +4094,12 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J168"/>
+  <dimension ref="A1:J179"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="25.59765625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.86328125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
@@ -4085,10 +4113,10 @@
       </c>
       <c r="D1" s="52"/>
       <c r="E1" s="331" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F1" s="284" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4106,9 +4134,8 @@
       <c r="J2" s="22"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="B4" s="45" t="str">
-        <f>D5&amp;" Stock Information"</f>
-        <v>600132.SS Stock Information</v>
+      <c r="B4" s="45" t="s">
+        <v>425</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4120,340 +4147,332 @@
         <v>323</v>
       </c>
       <c r="C5" s="333" t="s">
-        <v>428</v>
-      </c>
-      <c r="D5" s="49" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" s="51">
+        <v>483971198</v>
+      </c>
+      <c r="E6" s="48"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="C7" s="279">
+        <v>6</v>
+      </c>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="C8" s="33">
+        <f>EOMONTH(EDATE(BS!C1,C7+2),0)</f>
+        <v>45716</v>
+      </c>
+      <c r="E8" s="48"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="E9" s="34"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10" s="45" t="s">
+        <v>428</v>
+      </c>
+      <c r="C10" s="46"/>
+      <c r="E10" s="34"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>433</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>434</v>
+      </c>
+      <c r="E11" s="34"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="C6" s="50">
+      <c r="C12" s="50">
         <v>57.21</v>
       </c>
-      <c r="D6" s="48" t="s">
-        <v>427</v>
-      </c>
-      <c r="E6" s="48"/>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="B7" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C7" s="51">
-        <v>483971198</v>
-      </c>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="B8" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C8" s="279">
-        <v>6</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="48"/>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="B9" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C9" s="33">
-        <f>EOMONTH(EDATE(BS!C1,C8+2),0)</f>
-        <v>45716</v>
-      </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="B10" s="4" t="str">
-        <f>"Capitalization ("&amp;Market_currency&amp;"):"</f>
-        <v>Capitalization (CNY):</v>
-      </c>
-      <c r="C10" s="35">
-        <f>Thesis!C6*Thesis!C7/1000000</f>
+      <c r="D12" s="50"/>
+      <c r="E12" s="48"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="C13" s="48" t="s">
+        <v>424</v>
+      </c>
+      <c r="D13" s="48"/>
+      <c r="E13" s="5"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="C14" s="35">
+        <f>Thesis!C12*Common_Shares/1000000</f>
         <v>27687.992237580002</v>
       </c>
-      <c r="D10" s="32"/>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:10" ht="24.4" customHeight="1">
-      <c r="B12" s="340" t="s">
-        <v>369</v>
-      </c>
-      <c r="C12" s="340"/>
-      <c r="D12" s="340"/>
-      <c r="E12" s="340"/>
-      <c r="F12" s="340"/>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="B14" s="45" t="s">
+      <c r="D14" s="35" t="str">
+        <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
+        <v/>
+      </c>
+      <c r="E14" s="5"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="C15" s="32" t="str">
+        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <v>CNY</v>
+      </c>
+      <c r="D15" s="32" t="str">
+        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <v/>
+      </c>
+      <c r="E15" s="5"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="50">
+        <v>1</v>
+      </c>
+      <c r="D16" s="50"/>
+      <c r="E16" s="5"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+    </row>
+    <row r="18" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B18" s="343" t="s">
+        <v>367</v>
+      </c>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="B20" s="45" t="s">
         <v>313</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="B15" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="C15" s="32" t="str">
+      <c r="C20" s="46"/>
+      <c r="D20" s="5"/>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="B21" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="B16" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="C16" s="48" t="s">
-        <v>427</v>
-      </c>
-      <c r="D16" s="32"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="B17" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C17" s="50">
-        <v>1</v>
-      </c>
-      <c r="D17" s="32" t="str">
-        <f>IF(C16=D6,D6,C16&amp;"/"&amp;D6)</f>
-        <v>CNY</v>
-      </c>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="B18" s="2" t="s">
+      <c r="E21" s="5"/>
+    </row>
+    <row r="22" spans="1:6">
+      <c r="B22" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C22" s="48" t="s">
+        <v>424</v>
+      </c>
+      <c r="D22" s="32" t="str">
+        <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
+        <v/>
+      </c>
+      <c r="E22" s="341" t="str">
+        <f>IF(D11="","",1/Exchange_Rate*D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="B23" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C18" s="48" t="s">
-        <v>430</v>
-      </c>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="B19" s="2" t="s">
+      <c r="C23" s="48" t="s">
+        <v>435</v>
+      </c>
+      <c r="E23" s="5"/>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="B24" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="C19" s="249">
+      <c r="C24" s="249">
         <v>0.3</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="E19" s="339">
+      <c r="D24" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="E24" s="339">
         <v>0.2</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
-      <c r="B20" s="2" t="str">
+    <row r="25" spans="1:6">
+      <c r="B25" s="2" t="str">
         <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
         <v>Target Buy Price (CNY):</v>
       </c>
-      <c r="C20" s="252">
-        <f>C133</f>
+      <c r="C25" s="252">
+        <f>C139</f>
         <v>34.669224296258527</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="E20" s="330">
+      <c r="E25" s="330">
         <v>3</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
-      <c r="B21" s="1" t="s">
-        <v>409</v>
-      </c>
-      <c r="C21" s="280">
+    <row r="26" spans="1:6">
+      <c r="B26" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
         <v>9.1887382418681218E-2</v>
       </c>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23" spans="1:6" ht="13.9">
-      <c r="A23" s="247" t="s">
-        <v>364</v>
-      </c>
-      <c r="B23" s="36"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-    </row>
-    <row r="25" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B25" s="340" t="s">
-        <v>370</v>
-      </c>
-      <c r="C25" s="340"/>
-      <c r="D25" s="340"/>
-      <c r="E25" s="340"/>
-      <c r="F25" s="340"/>
-    </row>
-    <row r="26" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B26" s="342" t="s">
-        <v>348</v>
-      </c>
-      <c r="C26" s="342"/>
-      <c r="D26" s="342"/>
-      <c r="E26" s="342"/>
-      <c r="F26" s="342"/>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="B28" s="234" t="s">
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+    </row>
+    <row r="27" spans="1:6">
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="1:6" ht="13.9">
+      <c r="A28" s="247" t="s">
+        <v>362</v>
+      </c>
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+    </row>
+    <row r="30" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B30" s="343" t="s">
+        <v>368</v>
+      </c>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
+    </row>
+    <row r="31" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B31" s="345" t="s">
+        <v>347</v>
+      </c>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
+    </row>
+    <row r="33" spans="2:6">
+      <c r="B33" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C28" s="108">
+      <c r="C33" s="108">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B29" s="341" t="s">
+    <row r="34" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C29" s="341"/>
-      <c r="D29" s="341"/>
-      <c r="E29" s="341"/>
-      <c r="F29" s="341"/>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="B30" s="47" t="s">
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C30" s="188">
+      <c r="C35" s="188">
         <f>Normalized_FCF!C8</f>
         <v>3123489756.696907</v>
       </c>
-      <c r="D30" s="1" t="str">
+      <c r="D35" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
-      <c r="B31" s="47"/>
-      <c r="C31" s="76"/>
-    </row>
-    <row r="32" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B32" s="341" t="s">
+    <row r="36" spans="2:6">
+      <c r="B36" s="47"/>
+      <c r="C36" s="76"/>
+    </row>
+    <row r="37" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C32" s="341"/>
-      <c r="D32" s="341"/>
-      <c r="E32" s="341"/>
-      <c r="F32" s="341"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="47" t="s">
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C33" s="188">
+      <c r="C38" s="188">
         <f>Normalized_FCF!C9</f>
         <v>575917865</v>
       </c>
-      <c r="D33" s="1" t="str">
+      <c r="D38" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="34" spans="2:6">
-      <c r="B34" s="52" t="s">
+    <row r="39" spans="2:6">
+      <c r="B39" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C34" s="188">
+      <c r="C39" s="188">
         <f>Normalized_FCF!C10</f>
         <v>-575917865</v>
       </c>
-      <c r="D34" s="1" t="str">
+      <c r="D39" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="341" t="s">
+    <row r="41" spans="2:6">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C36" s="341"/>
-      <c r="D36" s="341"/>
-      <c r="E36" s="341"/>
-      <c r="F36" s="341"/>
-    </row>
-    <row r="37" spans="2:6">
-      <c r="B37" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C37" s="188">
-        <f>Normalized_FCF!C11</f>
-        <v>0</v>
-      </c>
-      <c r="D37" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="341" t="s">
-        <v>241</v>
-      </c>
-      <c r="C39" s="341"/>
-      <c r="D39" s="341"/>
-      <c r="E39" s="341"/>
-      <c r="F39" s="341"/>
-    </row>
-    <row r="40" spans="2:6">
-      <c r="B40" s="47" t="s">
-        <v>349</v>
-      </c>
-      <c r="C40" s="322">
-        <f>Normalized_FCF!C48</f>
-        <v>38554805.997018404</v>
-      </c>
-      <c r="D40" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-      <c r="E40" s="321"/>
-      <c r="F40" s="321"/>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="47" t="s">
-        <v>350</v>
-      </c>
-      <c r="C41" s="322">
-        <f>Normalized_FCF!C47</f>
-        <v>-7672861</v>
-      </c>
-      <c r="D41" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-      <c r="E41" s="321"/>
-      <c r="F41" s="321"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C42" s="188">
-        <f>Normalized_FCF!C12</f>
-        <v>30881944.997018404</v>
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
       </c>
       <c r="D42" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4461,405 +4480,413 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="1" t="s">
-        <v>247</v>
-      </c>
+      <c r="B44" s="344" t="s">
+        <v>241</v>
+      </c>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C45" s="188">
-        <f>Normalized_FCF!C15</f>
-        <v>-141879704.29826272</v>
+        <v>348</v>
+      </c>
+      <c r="C45" s="322">
+        <f>Normalized_FCF!C48</f>
+        <v>38554805.997018404</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
+      <c r="E45" s="321"/>
+      <c r="F45" s="321"/>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46" s="47" t="s">
+        <v>349</v>
+      </c>
+      <c r="C46" s="322">
+        <f>Normalized_FCF!C47</f>
+        <v>-7672861</v>
+      </c>
+      <c r="D46" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E46" s="321"/>
+      <c r="F46" s="321"/>
     </row>
     <row r="47" spans="2:6">
-      <c r="B47" s="341" t="s">
+      <c r="B47" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="C47" s="188">
+        <f>Normalized_FCF!C12</f>
+        <v>30881944.997018404</v>
+      </c>
+      <c r="D47" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="B49" s="1" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="47" t="s">
+        <v>266</v>
+      </c>
+      <c r="C50" s="188">
+        <f>Normalized_FCF!C15</f>
+        <v>-141879704.29826272</v>
+      </c>
+      <c r="D50" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="341"/>
-      <c r="D47" s="341"/>
-      <c r="E47" s="341"/>
-      <c r="F47" s="341"/>
-    </row>
-    <row r="48" spans="2:6">
-      <c r="B48" s="47" t="s">
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C48" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C14</f>
         <v>-788592925.42348135</v>
       </c>
-      <c r="D48" s="1" t="str">
+      <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
-      <c r="B50" s="341" t="s">
-        <v>347</v>
-      </c>
-      <c r="C50" s="344"/>
-      <c r="D50" s="344"/>
-      <c r="E50" s="344"/>
-      <c r="F50" s="344"/>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="B51" s="47" t="s">
+    <row r="55" spans="2:6">
+      <c r="B55" s="344" t="s">
+        <v>346</v>
+      </c>
+      <c r="C55" s="347"/>
+      <c r="D55" s="347"/>
+      <c r="E55" s="347"/>
+      <c r="F55" s="347"/>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C56" s="1">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
-      </c>
-      <c r="D51" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B53" s="340" t="s">
-        <v>352</v>
-      </c>
-      <c r="C53" s="340"/>
-      <c r="D53" s="340"/>
-      <c r="E53" s="340"/>
-      <c r="F53" s="340"/>
-    </row>
-    <row r="54" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B54" s="340" t="s">
-        <v>371</v>
-      </c>
-      <c r="C54" s="340"/>
-      <c r="D54" s="340"/>
-      <c r="E54" s="340"/>
-      <c r="F54" s="340"/>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="B56" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C56" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>2898672440.9970183</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="57" spans="1:6">
-      <c r="B57" s="47" t="s">
+    <row r="58" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B58" s="343" t="s">
+        <v>351</v>
+      </c>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
+    </row>
+    <row r="59" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B59" s="343" t="s">
+        <v>369</v>
+      </c>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C61" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>2898672440.9970183</v>
+      </c>
+      <c r="D61" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C57" s="188">
+      <c r="C62" s="188">
         <f>Normalized_FCF!C19</f>
         <v>2223899071.9721813</v>
       </c>
-      <c r="D57" s="1" t="str">
+      <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="1:6">
-      <c r="B58" s="254" t="s">
-        <v>400</v>
-      </c>
-      <c r="C58" s="92">
+    <row r="63" spans="2:6">
+      <c r="B63" s="254" t="s">
+        <v>398</v>
+      </c>
+      <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
         <v>8.0319983221959892E-2</v>
       </c>
     </row>
-    <row r="59" spans="1:6">
-      <c r="B59" s="254" t="s">
+    <row r="64" spans="2:6">
+      <c r="B64" s="254" t="s">
         <v>316</v>
       </c>
-      <c r="C59" s="92">
+      <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
         <v>4.195070791819612E-2</v>
       </c>
     </row>
-    <row r="61" spans="1:6" ht="13.9">
-      <c r="A61" s="247" t="s">
-        <v>365</v>
-      </c>
-      <c r="B61" s="36"/>
-      <c r="C61" s="36"/>
-      <c r="D61" s="36"/>
-      <c r="E61" s="36"/>
-      <c r="F61" s="36"/>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62" s="233"/>
-    </row>
-    <row r="63" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A63" s="17"/>
-      <c r="B63" s="340" t="s">
+    <row r="66" spans="1:6" ht="13.9">
+      <c r="A66" s="247" t="s">
+        <v>363</v>
+      </c>
+      <c r="B66" s="36"/>
+      <c r="C66" s="36"/>
+      <c r="D66" s="36"/>
+      <c r="E66" s="36"/>
+      <c r="F66" s="36"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="A67" s="233"/>
+    </row>
+    <row r="68" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A68" s="17"/>
+      <c r="B68" s="343" t="s">
+        <v>370</v>
+      </c>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="345" t="s">
+        <v>253</v>
+      </c>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
+    </row>
+    <row r="71" spans="1:6">
+      <c r="B71" s="234" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
+      <c r="B72" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="C72" s="311">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="B73" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="C73" s="263">
+        <f>IF(D73="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="286" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
+      <c r="B74" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C74" s="263">
+        <f>IF(D74="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="D74" s="286" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="80" t="s">
+        <v>248</v>
+      </c>
+      <c r="C75" s="263">
+        <f>SUM(C72:C74)</f>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
+      <c r="C76" s="122"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="332" t="s">
+        <v>364</v>
+      </c>
+      <c r="C77" s="122"/>
+    </row>
+    <row r="78" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B78" s="343" t="s">
+        <v>371</v>
+      </c>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
+    </row>
+    <row r="79" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C63" s="340"/>
-      <c r="D63" s="340"/>
-      <c r="E63" s="340"/>
-      <c r="F63" s="340"/>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="B64" s="342" t="s">
-        <v>253</v>
-      </c>
-      <c r="C64" s="342"/>
-      <c r="D64" s="342"/>
-      <c r="E64" s="342"/>
-      <c r="F64" s="342"/>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="B66" s="234" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="B67" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C67" s="311">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="B68" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C68" s="263">
-        <f>IF(D68="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D68" s="286" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C69" s="263">
-        <f>IF(D69="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D69" s="286" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="B70" s="80" t="s">
-        <v>248</v>
-      </c>
-      <c r="C70" s="263">
-        <f>SUM(C67:C69)</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="C71" s="122"/>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="332" t="s">
-        <v>366</v>
-      </c>
-      <c r="C72" s="122"/>
-    </row>
-    <row r="73" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B73" s="340" t="s">
-        <v>373</v>
-      </c>
-      <c r="C73" s="340"/>
-      <c r="D73" s="340"/>
-      <c r="E73" s="340"/>
-      <c r="F73" s="340"/>
-    </row>
-    <row r="74" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B74" s="340" t="s">
-        <v>374</v>
-      </c>
-      <c r="C74" s="340"/>
-      <c r="D74" s="340"/>
-      <c r="E74" s="340"/>
-      <c r="F74" s="340"/>
-    </row>
-    <row r="76" spans="1:6">
-      <c r="B76" s="47" t="s">
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C76" s="263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="47" t="s">
+      <c r="C81" s="263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="47" t="s">
         <v>284</v>
       </c>
-      <c r="C77" s="248">
+      <c r="C82" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>57.438828001604072</v>
       </c>
-      <c r="D77" s="1" t="str">
+      <c r="D82" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="13.9">
-      <c r="A79" s="247" t="s">
-        <v>367</v>
-      </c>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="36"/>
-      <c r="E79" s="36"/>
-      <c r="F79" s="36"/>
-    </row>
-    <row r="80" spans="1:6">
-      <c r="A80" s="233"/>
-    </row>
-    <row r="81" spans="2:6">
-      <c r="B81" s="340" t="s">
-        <v>375</v>
-      </c>
-      <c r="C81" s="340"/>
-      <c r="D81" s="340"/>
-      <c r="E81" s="340"/>
-      <c r="F81" s="340"/>
-    </row>
-    <row r="82" spans="2:6">
-      <c r="B82" s="1" t="s">
+    <row r="84" spans="1:6" ht="13.9">
+      <c r="A84" s="247" t="s">
+        <v>365</v>
+      </c>
+      <c r="B84" s="36"/>
+      <c r="C84" s="36"/>
+      <c r="D84" s="36"/>
+      <c r="E84" s="36"/>
+      <c r="F84" s="36"/>
+    </row>
+    <row r="85" spans="1:6">
+      <c r="A85" s="233"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="343" t="s">
+        <v>373</v>
+      </c>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="84" spans="2:6">
-      <c r="B84" s="234" t="s">
+    <row r="89" spans="1:6">
+      <c r="B89" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="85" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B85" s="340" t="s">
-        <v>353</v>
-      </c>
-      <c r="C85" s="340"/>
-      <c r="D85" s="340"/>
-      <c r="E85" s="340"/>
-      <c r="F85" s="340"/>
-    </row>
-    <row r="86" spans="2:6">
-      <c r="B86" s="47" t="s">
+    <row r="90" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B90" s="343" t="s">
+        <v>352</v>
+      </c>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C86" s="188">
+      <c r="C91" s="188">
         <f>Valuation_Model!C7</f>
         <v>123521704.27</v>
       </c>
-      <c r="D86" s="1" t="str">
+      <c r="D91" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:6">
-      <c r="B87" s="47" t="s">
+    <row r="92" spans="1:6">
+      <c r="B92" s="47" t="s">
         <v>285</v>
       </c>
-      <c r="C87" s="248">
-        <f>C86*scaling_factor*Exchange_Rate/Common_Shares</f>
+      <c r="C92" s="248">
+        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0.25522532080514426</v>
       </c>
-      <c r="D87" s="1" t="str">
+      <c r="D92" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:6">
-      <c r="B88" s="336" t="s">
-        <v>414</v>
-      </c>
-      <c r="C88" s="337">
+    <row r="93" spans="1:6">
+      <c r="B93" s="336" t="s">
+        <v>412</v>
+      </c>
+      <c r="C93" s="337">
         <f>BS!G30/BS!G27</f>
         <v>3.4701988818540461</v>
       </c>
     </row>
-    <row r="89" spans="2:6">
-      <c r="B89" s="336" t="s">
-        <v>415</v>
-      </c>
-      <c r="C89" s="337">
+    <row r="94" spans="1:6">
+      <c r="B94" s="336" t="s">
+        <v>413</v>
+      </c>
+      <c r="C94" s="337">
         <f>BS!G31/BS!G27</f>
         <v>5.0341856510546588E-2</v>
       </c>
     </row>
-    <row r="90" spans="2:6">
-      <c r="B90" s="336" t="s">
-        <v>417</v>
-      </c>
-      <c r="C90" s="338">
+    <row r="95" spans="1:6">
+      <c r="B95" s="336" t="s">
+        <v>415</v>
+      </c>
+      <c r="C95" s="338">
         <f>BS!C50</f>
         <v>3.9546057100127742E-2</v>
       </c>
     </row>
-    <row r="92" spans="2:6">
-      <c r="B92" s="1" t="s">
+    <row r="97" spans="1:6">
+      <c r="B97" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="93" spans="2:6">
-      <c r="B93" s="47" t="s">
+    <row r="98" spans="1:6">
+      <c r="B98" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C93" s="188">
+      <c r="C98" s="188">
         <f>BS!C66</f>
         <v>1081659074.0699999</v>
-      </c>
-      <c r="D93" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="94" spans="2:6">
-      <c r="B94" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C94" s="188">
-        <f>Valuation_Model!C8</f>
-        <v>65618450.04890883</v>
-      </c>
-      <c r="D94" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="95" spans="2:6">
-      <c r="B95" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C95" s="248">
-        <f>C94*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.13558337834994227</v>
-      </c>
-      <c r="D95" s="1" t="str">
-        <f>Market_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C98" s="188">
-        <f>Valuation_Model!C9</f>
-        <v>29558000.651999995</v>
       </c>
       <c r="D98" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4868,591 +4895,688 @@
     </row>
     <row r="99" spans="1:6">
       <c r="B99" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C99" s="248">
-        <f>C98*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.1073883681813636E-2</v>
+        <v>267</v>
+      </c>
+      <c r="C99" s="188">
+        <f>Valuation_Model!C8</f>
+        <v>65618450.04890883</v>
       </c>
       <c r="D99" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
+      <c r="B100" s="47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C100" s="248">
+        <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0.13558337834994227</v>
+      </c>
+      <c r="D100" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="101" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B101" s="340" t="s">
-        <v>376</v>
-      </c>
-      <c r="C101" s="340"/>
-      <c r="D101" s="340"/>
-      <c r="E101" s="340"/>
-      <c r="F101" s="340"/>
+    <row r="102" spans="1:6">
+      <c r="B102" s="1" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="103" spans="1:6">
       <c r="B103" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C103" s="248">
-        <f>Valuation_Model!C12</f>
-        <v>57.380259942830683</v>
+        <v>258</v>
+      </c>
+      <c r="C103" s="188">
+        <f>Valuation_Model!C9</f>
+        <v>29558000.651999995</v>
       </c>
       <c r="D103" s="1" t="str">
-        <f>Market_currency</f>
+        <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="104" spans="1:6">
-      <c r="B104" s="336" t="s">
-        <v>416</v>
+      <c r="B104" s="47" t="s">
+        <v>287</v>
       </c>
       <c r="C104" s="248">
-        <f>BS!D47</f>
-        <v>-13.312996389940134</v>
+        <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>6.1073883681813636E-2</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="13.9">
-      <c r="A106" s="247" t="s">
-        <v>368</v>
-      </c>
-      <c r="B106" s="36"/>
-      <c r="C106" s="36"/>
-      <c r="D106" s="36"/>
-      <c r="E106" s="36"/>
-      <c r="F106" s="36"/>
-    </row>
-    <row r="108" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B108" s="341" t="s">
-        <v>377</v>
-      </c>
-      <c r="C108" s="341"/>
-      <c r="D108" s="341"/>
-      <c r="E108" s="341"/>
-      <c r="F108" s="341"/>
-    </row>
-    <row r="110" spans="1:6" ht="12.4">
-      <c r="B110" s="260" t="s">
+    <row r="106" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B106" s="343" t="s">
+        <v>374</v>
+      </c>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
+    </row>
+    <row r="108" spans="1:6">
+      <c r="B108" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C108" s="248">
+        <f>Valuation_Model!C12</f>
+        <v>57.380259942830683</v>
+      </c>
+      <c r="D108" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
+      <c r="B109" s="336" t="s">
+        <v>414</v>
+      </c>
+      <c r="C109" s="248">
+        <f>BS!D47</f>
+        <v>-13.312996389940134</v>
+      </c>
+      <c r="D109" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" ht="13.9">
+      <c r="A111" s="247" t="s">
+        <v>366</v>
+      </c>
+      <c r="B111" s="36"/>
+      <c r="C111" s="36"/>
+      <c r="D111" s="36"/>
+      <c r="E111" s="36"/>
+      <c r="F111" s="36"/>
+    </row>
+    <row r="113" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B113" s="344" t="s">
+        <v>375</v>
+      </c>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
+    </row>
+    <row r="115" spans="1:6" ht="12.4">
+      <c r="B115" s="260" t="s">
         <v>118</v>
       </c>
-      <c r="C110" s="260" t="s">
+      <c r="C115" s="260" t="s">
         <v>133</v>
       </c>
-      <c r="D110" s="260" t="s">
+      <c r="D115" s="260" t="s">
         <v>113</v>
       </c>
-      <c r="E110" s="260" t="s">
+      <c r="E115" s="260" t="s">
         <v>260</v>
       </c>
-      <c r="F110" s="260" t="s">
+      <c r="F115" s="260" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="111" spans="1:6">
-      <c r="B111" s="255" t="str">
+    <row r="116" spans="1:6">
+      <c r="B116" s="255" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C111" s="256">
+      <c r="C116" s="256">
         <f>Valuation_Model!C74</f>
         <v>0.1</v>
       </c>
-      <c r="D111" s="257">
+      <c r="D116" s="257">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E111" s="258" t="str">
+      <c r="E116" s="258" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>99.94 CNY</v>
       </c>
-      <c r="F111" s="259">
+      <c r="F116" s="259">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="112" spans="1:6">
-      <c r="B112" s="242" t="str">
+    <row r="117" spans="1:6">
+      <c r="B117" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C112" s="243">
+      <c r="C117" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.06</v>
       </c>
-      <c r="D112" s="244">
+      <c r="D117" s="244">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E112" s="245" t="str">
+      <c r="E117" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>69.66 CNY</v>
       </c>
-      <c r="F112" s="246">
+      <c r="F117" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
-      <c r="B113" s="242" t="str">
+    <row r="118" spans="1:6">
+      <c r="B118" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C113" s="243">
+      <c r="C118" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.04</v>
       </c>
-      <c r="D113" s="244">
+      <c r="D118" s="244">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E113" s="245" t="str">
+      <c r="E118" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>65.17 CNY</v>
       </c>
-      <c r="F113" s="246">
+      <c r="F118" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
-      <c r="B114" s="242" t="str">
+    <row r="119" spans="1:6">
+      <c r="B119" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C114" s="243">
+      <c r="C119" s="243">
         <f>Valuation_Model!C77</f>
         <v>0.02</v>
       </c>
-      <c r="D114" s="244">
+      <c r="D119" s="244">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E114" s="245" t="str">
+      <c r="E119" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>61.09 CNY</v>
       </c>
-      <c r="F114" s="246">
+      <c r="F119" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="115" spans="1:6">
-      <c r="B115" s="242" t="str">
+    <row r="120" spans="1:6">
+      <c r="B120" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C115" s="243">
+      <c r="C120" s="243">
         <f>Valuation_Model!C78</f>
         <v>0</v>
       </c>
-      <c r="D115" s="244">
+      <c r="D120" s="244">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E115" s="245" t="str">
+      <c r="E120" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>57.38 CNY</v>
       </c>
-      <c r="F115" s="246">
+      <c r="F120" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" s="235" t="s">
+    <row r="122" spans="1:6">
+      <c r="B122" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C117" s="241">
+      <c r="C122" s="241">
         <f>Scenarios!C60</f>
         <v>66.592285778879997</v>
       </c>
-      <c r="D117" s="236" t="str">
+      <c r="D122" s="236" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="119" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B119" s="345" t="s">
-        <v>380</v>
-      </c>
-      <c r="C119" s="345"/>
-      <c r="D119" s="345"/>
-      <c r="E119" s="345"/>
-      <c r="F119" s="345"/>
-    </row>
-    <row r="121" spans="1:6" ht="13.9">
-      <c r="A121" s="247" t="s">
-        <v>412</v>
-      </c>
-      <c r="B121" s="36"/>
-      <c r="C121" s="36"/>
-      <c r="D121" s="36"/>
-      <c r="E121" s="36"/>
-      <c r="F121" s="36"/>
-    </row>
-    <row r="123" spans="1:6">
-      <c r="B123" s="343" t="s">
+    <row r="124" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C123" s="343"/>
-      <c r="D123" s="343"/>
-      <c r="E123" s="343"/>
-      <c r="F123" s="343"/>
-    </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="340" t="s">
-        <v>379</v>
-      </c>
-      <c r="C124" s="340"/>
-      <c r="D124" s="340"/>
-      <c r="E124" s="340"/>
-      <c r="F124" s="340"/>
-    </row>
-    <row r="125" spans="1:6">
-      <c r="B125" s="234" t="s">
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
+    </row>
+    <row r="126" spans="1:6" ht="13.9">
+      <c r="A126" s="247" t="s">
+        <v>410</v>
+      </c>
+      <c r="B126" s="36"/>
+      <c r="C126" s="36"/>
+      <c r="D126" s="36"/>
+      <c r="E126" s="36"/>
+      <c r="F126" s="36"/>
+    </row>
+    <row r="128" spans="1:6">
+      <c r="B128" s="346" t="s">
+        <v>376</v>
+      </c>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
+    </row>
+    <row r="129" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B129" s="343" t="s">
+        <v>377</v>
+      </c>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
+    </row>
+    <row r="130" spans="2:6">
+      <c r="B130" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
-      <c r="B126" s="1" t="s">
+    <row r="131" spans="2:6">
+      <c r="B131" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C126" s="251">
-        <f>E20</f>
+      <c r="C131" s="251">
+        <f>E25</f>
         <v>3</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
-      <c r="B127" s="1" t="s">
+    <row r="132" spans="2:6">
+      <c r="B132" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="C127" s="250">
-        <f>C19</f>
+      <c r="C132" s="250">
+        <f>C24</f>
         <v>0.3</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="236" t="s">
+    <row r="133" spans="2:6">
+      <c r="B133" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C128" s="237">
+      <c r="C133" s="237">
         <f>Scenarios!C77</f>
         <v>2.4</v>
       </c>
-      <c r="D128" s="236" t="str">
+      <c r="D133" s="236" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="130" spans="2:4">
-      <c r="B130" s="234" t="s">
-        <v>420</v>
-      </c>
-      <c r="C130" s="337">
-        <f>C19</f>
+    <row r="135" spans="2:6">
+      <c r="B135" s="234" t="s">
+        <v>418</v>
+      </c>
+      <c r="C135" s="270" t="str">
+        <f>C11</f>
+        <v>600132.SS</v>
+      </c>
+      <c r="D135" s="270" t="str">
+        <f>IF(D11="","",D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="2:6">
+      <c r="B136" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="C136" s="337">
+        <f>C24</f>
         <v>0.3</v>
       </c>
-      <c r="D130" s="1" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="131" spans="2:4">
-      <c r="B131" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="137" spans="2:6">
+      <c r="B137" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C131" s="240">
+      <c r="C137" s="240">
         <f>Scenarios!C81</f>
         <v>4.3586709148839331</v>
       </c>
     </row>
-    <row r="132" spans="2:4">
-      <c r="B132" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="138" spans="2:6">
+      <c r="B138" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C132" s="240">
+      <c r="C138" s="240">
         <f>Scenarios!C82</f>
         <v>30.310553381374593</v>
       </c>
     </row>
-    <row r="133" spans="2:4">
-      <c r="B133" s="80" t="s">
+    <row r="139" spans="2:6">
+      <c r="B139" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C133" s="239">
+      <c r="C139" s="239">
         <f>Scenarios!C83</f>
         <v>34.669224296258527</v>
       </c>
-      <c r="D133" s="47" t="str">
-        <f>Reporting_currency</f>
+      <c r="D139" s="342" t="str">
+        <f>IF($D$11="","",C139*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="2:6">
+      <c r="B140" s="290" t="s">
+        <v>426</v>
+      </c>
+      <c r="C140" s="340" t="str">
+        <f>Market_currency</f>
         <v>CNY</v>
       </c>
-    </row>
-    <row r="134" spans="2:4">
-      <c r="B134" s="238" t="s">
+      <c r="D140" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="2:6">
+      <c r="B141" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C134" s="92">
+      <c r="C141" s="92">
         <f>Scenarios!F83</f>
         <v>0.4793807737524155</v>
       </c>
     </row>
-    <row r="136" spans="2:4">
-      <c r="B136" s="234" t="s">
-        <v>423</v>
-      </c>
-      <c r="C136" s="337">
+    <row r="143" spans="2:6">
+      <c r="B143" s="234" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="144" spans="2:6">
+      <c r="B144" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="C144" s="337">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
-      <c r="D136" s="1" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="137" spans="2:4">
-      <c r="B137" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="145" spans="1:6">
+      <c r="B145" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C137" s="240">
+      <c r="C145" s="240">
         <f>Scenarios!C91</f>
         <v>5.0555555555555554</v>
       </c>
     </row>
-    <row r="138" spans="2:4">
-      <c r="B138" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="146" spans="1:6">
+      <c r="B146" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C138" s="240">
+      <c r="C146" s="240">
         <f>Scenarios!C92</f>
         <v>38.537202418333329</v>
       </c>
     </row>
-    <row r="139" spans="2:4">
-      <c r="B139" s="80" t="s">
+    <row r="147" spans="1:6">
+      <c r="B147" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C139" s="239">
+      <c r="C147" s="239">
         <f>Scenarios!C93</f>
         <v>43.592757973888887</v>
       </c>
-      <c r="D139" s="47" t="str">
-        <f>Reporting_currency</f>
+      <c r="D147" s="342" t="str">
+        <f>IF($D$11="","",C147*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
+      <c r="B148" s="290" t="s">
+        <v>426</v>
+      </c>
+      <c r="C148" s="340" t="str">
+        <f>Market_currency</f>
         <v>CNY</v>
       </c>
-    </row>
-    <row r="140" spans="2:4">
-      <c r="B140" s="238" t="s">
+      <c r="D148" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
+      <c r="B149" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C140" s="92">
+      <c r="C149" s="92">
         <f>Scenarios!F93</f>
         <v>0.345378260199104</v>
       </c>
     </row>
-    <row r="142" spans="2:4">
-      <c r="B142" s="234" t="s">
-        <v>410</v>
-      </c>
-      <c r="C142" s="92">
+    <row r="151" spans="1:6">
+      <c r="B151" s="234" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
+      <c r="B152" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="C152" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
-      <c r="D142" s="1" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="143" spans="2:4">
-      <c r="B143" s="236" t="str">
-        <f>"PV("&amp;C126&amp;" yrs of Dividends)"</f>
+    </row>
+    <row r="153" spans="1:6">
+      <c r="B153" s="236" t="str">
+        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C143" s="240">
+      <c r="C153" s="240">
         <f>Scenarios!C97</f>
         <v>6.1850327693949119</v>
       </c>
     </row>
-    <row r="144" spans="2:4">
-      <c r="B144" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C126&amp;")"</f>
+    <row r="154" spans="1:6">
+      <c r="B154" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C144" s="240">
+      <c r="C154" s="240">
         <f>Scenarios!C98</f>
         <v>52.863103454503879</v>
       </c>
     </row>
-    <row r="145" spans="1:6">
-      <c r="B145" s="80" t="s">
-        <v>411</v>
-      </c>
-      <c r="C145" s="239">
+    <row r="155" spans="1:6">
+      <c r="B155" s="80" t="s">
+        <v>409</v>
+      </c>
+      <c r="C155" s="239">
         <f>Scenarios!C99</f>
         <v>59.048136223898794</v>
       </c>
-      <c r="D145" s="101" t="str">
-        <f>Reporting_currency</f>
+      <c r="D155" s="342" t="str">
+        <f>IF($D$11="","",C155*$E$22)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
+      <c r="B156" s="290" t="s">
+        <v>426</v>
+      </c>
+      <c r="C156" s="340" t="str">
+        <f>Market_currency</f>
         <v>CNY</v>
       </c>
-    </row>
-    <row r="146" spans="1:6">
-      <c r="B146" s="238" t="s">
+      <c r="D156" s="340" t="str">
+        <f>IF($D$11="","",D$13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
+      <c r="B157" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C146" s="92">
+      <c r="C157" s="92">
         <f>Scenarios!F99</f>
         <v>0.1132886409700905</v>
       </c>
     </row>
-    <row r="148" spans="1:6" ht="13.9">
-      <c r="A148" s="247" t="s">
+    <row r="159" spans="1:6" ht="13.9">
+      <c r="A159" s="247" t="s">
+        <v>382</v>
+      </c>
+      <c r="B159" s="36"/>
+      <c r="C159" s="36"/>
+      <c r="D159" s="36"/>
+      <c r="E159" s="36"/>
+      <c r="F159" s="36"/>
+    </row>
+    <row r="161" spans="2:6">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="B148" s="36"/>
-      <c r="C148" s="36"/>
-      <c r="D148" s="36"/>
-      <c r="E148" s="36"/>
-      <c r="F148" s="36"/>
-    </row>
-    <row r="150" spans="1:6">
-      <c r="B150" s="347" t="s">
-        <v>386</v>
-      </c>
-      <c r="C150" s="340"/>
-      <c r="D150" s="340"/>
-      <c r="E150" s="340"/>
-      <c r="F150" s="340"/>
-    </row>
-    <row r="152" spans="1:6">
-      <c r="B152" s="234" t="s">
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
+    </row>
+    <row r="163" spans="2:6">
+      <c r="B163" s="234" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="164" spans="2:6">
+      <c r="B164" s="347" t="s">
+        <v>388</v>
+      </c>
+      <c r="C164" s="347"/>
+      <c r="D164" s="347"/>
+      <c r="E164" s="347"/>
+      <c r="F164" s="347"/>
+    </row>
+    <row r="165" spans="2:6">
+      <c r="B165" s="238" t="s">
         <v>385</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6">
-      <c r="B153" s="344" t="s">
-        <v>390</v>
-      </c>
-      <c r="C153" s="344"/>
-      <c r="D153" s="344"/>
-      <c r="E153" s="344"/>
-      <c r="F153" s="344"/>
-    </row>
-    <row r="154" spans="1:6">
-      <c r="B154" s="238" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6">
-      <c r="B155" s="238" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6">
-      <c r="B156" s="238" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6">
-      <c r="B158" s="1" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B159" s="341" t="s">
-        <v>391</v>
-      </c>
-      <c r="C159" s="341"/>
-      <c r="D159" s="341"/>
-      <c r="E159" s="341"/>
-      <c r="F159" s="341"/>
-    </row>
-    <row r="161" spans="2:6">
-      <c r="B161" s="1" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="162" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B162" s="346" t="s">
-        <v>392</v>
-      </c>
-      <c r="C162" s="346"/>
-      <c r="D162" s="346"/>
-      <c r="E162" s="346"/>
-      <c r="F162" s="346"/>
-    </row>
-    <row r="163" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B163" s="346" t="s">
-        <v>393</v>
-      </c>
-      <c r="C163" s="346"/>
-      <c r="D163" s="346"/>
-      <c r="E163" s="346"/>
-      <c r="F163" s="346"/>
-    </row>
-    <row r="165" spans="2:6">
-      <c r="B165" s="1" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="166" spans="2:6">
       <c r="B166" s="238" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
     </row>
     <row r="167" spans="2:6">
       <c r="B167" s="238" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="169" spans="2:6">
+      <c r="B169" s="1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="170" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B170" s="344" t="s">
+        <v>389</v>
+      </c>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
+    </row>
+    <row r="172" spans="2:6">
+      <c r="B172" s="1" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="173" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B173" s="349" t="s">
+        <v>390</v>
+      </c>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
+    </row>
+    <row r="174" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B174" s="349" t="s">
+        <v>391</v>
+      </c>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
+    </row>
+    <row r="176" spans="2:6">
+      <c r="B176" s="1" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="168" spans="2:6">
-      <c r="B168" s="238" t="s">
-        <v>398</v>
+    <row r="177" spans="2:2">
+      <c r="B177" s="238" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="178" spans="2:2">
+      <c r="B178" s="238" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="179" spans="2:2">
+      <c r="B179" s="238" t="s">
+        <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B163:F163"/>
-    <mergeCell ref="B150:F150"/>
-    <mergeCell ref="B159:F159"/>
-    <mergeCell ref="B153:F153"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B119:F119"/>
-    <mergeCell ref="B53:F53"/>
-    <mergeCell ref="B85:F85"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B25:F25"/>
-    <mergeCell ref="B26:F26"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B32:F32"/>
-    <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B39:F39"/>
-    <mergeCell ref="B47:F47"/>
-    <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B54:F54"/>
-    <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B31:F31"/>
+    <mergeCell ref="B34:F34"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B79:F79"/>
+    <mergeCell ref="B86:F86"/>
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="B128:F128"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B68:F68"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
-      <formula1>"HKD,USD,CNY,EUR"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D68:D69" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D73:D74" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C22:D22" xr:uid="{00000000-0002-0000-0000-000001000000}">
+      <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5476,7 +5600,7 @@
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
-        <f>Thesis!C16</f>
+        <f>Thesis!C22</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="104">
@@ -5999,7 +6123,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C22" s="181">
         <v>2542046725</v>
@@ -6035,7 +6159,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C23" s="181">
         <v>-633430356</v>
@@ -6071,7 +6195,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C24" s="181">
         <v>-3527746522</v>
@@ -6130,7 +6254,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>220</v>
+        <v>436</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7435,7 +7559,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8038,7 +8162,7 @@
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C1" xr:uid="{87139493-416E-4F03-A3A9-B1C3E5C019E4}"/>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8813,7 +8937,7 @@
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F45" s="287" t="s">
         <v>59</v>
@@ -9109,12 +9233,12 @@
         <v>-1016040624.0210911</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="288" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C74" s="289">
         <f>-$C$66/C73</f>
@@ -9138,12 +9262,12 @@
         <v>1016040624.0210911</v>
       </c>
       <c r="F75" s="283" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="290" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C76" s="291"/>
       <c r="D76" s="327">
@@ -9151,7 +9275,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="283" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
@@ -9341,7 +9465,7 @@
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
-        <f>Thesis!C16</f>
+        <f>Thesis!C22</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
@@ -10168,7 +10292,7 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="301" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10193,7 +10317,7 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="301" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10521,7 +10645,7 @@
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="300" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10581,7 +10705,7 @@
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="300" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10705,7 +10829,7 @@
         <v>-515765096.5</v>
       </c>
       <c r="E33" s="300" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10763,7 +10887,7 @@
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="300" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -11071,7 +11195,7 @@
       </c>
       <c r="D43" s="27"/>
       <c r="E43" s="299" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11210,7 +11334,7 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
@@ -11265,7 +11389,7 @@
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="323" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C49" s="324">
         <f>BS!$C$66*C53</f>
@@ -11398,7 +11522,7 @@
         <v>3.7946126449583846E-2</v>
       </c>
       <c r="E53" s="299" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11425,7 +11549,7 @@
         <v>6.2117512427032839E-2</v>
       </c>
       <c r="E54" s="299" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11740,7 +11864,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="300" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -11969,7 +12093,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>59</v>
+        <v>437</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12301,7 +12425,7 @@
       </c>
       <c r="D78" s="27"/>
       <c r="E78" s="300" t="s">
-        <v>363</v>
+        <v>438</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -13674,7 +13798,7 @@
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="302"/>
@@ -13726,7 +13850,7 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="302"/>
@@ -14235,7 +14359,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15036,7 +15160,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C76</f>
+        <f>Thesis!C81</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15046,7 +15170,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C70</f>
+        <f>Thesis!C75</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15064,10 +15188,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="348" t="s">
+      <c r="E6" s="351" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="348"/>
+      <c r="F6" s="351"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15082,8 +15206,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="348"/>
-      <c r="F7" s="348"/>
+      <c r="E7" s="351"/>
+      <c r="F7" s="351"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15098,8 +15222,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="348"/>
-      <c r="F8" s="348"/>
+      <c r="E8" s="351"/>
+      <c r="F8" s="351"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15114,8 +15238,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="348"/>
-      <c r="F9" s="348"/>
+      <c r="E9" s="351"/>
+      <c r="F9" s="351"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15141,7 +15265,7 @@
         <v>1</v>
       </c>
       <c r="D11" t="str">
-        <f>Thesis!D17</f>
+        <f>Thesis!C15</f>
         <v>CNY</v>
       </c>
       <c r="H11" s="121"/>
@@ -16609,11 +16733,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="350" t="str">
-        <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!D5&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
+      <c r="E7" s="353" t="str">
+        <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 重庆啤酒(600132.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="350"/>
+      <c r="F7" s="353"/>
       <c r="H7" s="276">
         <v>4</v>
       </c>
@@ -16634,8 +16758,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="350"/>
-      <c r="F8" s="350"/>
+      <c r="E8" s="353"/>
+      <c r="F8" s="353"/>
       <c r="H8" s="276">
         <v>5</v>
       </c>
@@ -16656,8 +16780,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="350"/>
-      <c r="F9" s="350"/>
+      <c r="E9" s="353"/>
+      <c r="F9" s="353"/>
       <c r="H9" s="276">
         <v>6</v>
       </c>
@@ -16667,8 +16791,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="350"/>
-      <c r="F10" s="350"/>
+      <c r="E10" s="353"/>
+      <c r="F10" s="353"/>
       <c r="H10" s="276">
         <v>7</v>
       </c>
@@ -16681,8 +16805,8 @@
       <c r="B11" s="160" t="s">
         <v>279</v>
       </c>
-      <c r="E11" s="350"/>
-      <c r="F11" s="350"/>
+      <c r="E11" s="353"/>
+      <c r="F11" s="353"/>
       <c r="H11" s="276">
         <v>8</v>
       </c>
@@ -16700,8 +16824,8 @@
         <v>3.7342435425912202E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="350"/>
-      <c r="F12" s="350"/>
+      <c r="E12" s="353"/>
+      <c r="F12" s="353"/>
       <c r="H12" s="276">
         <v>9</v>
       </c>
@@ -16718,8 +16842,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>2.3730241339145586E-2</v>
       </c>
-      <c r="E13" s="350"/>
-      <c r="F13" s="350"/>
+      <c r="E13" s="353"/>
+      <c r="F13" s="353"/>
       <c r="H13" s="276">
         <v>10</v>
       </c>
@@ -16736,8 +16860,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>8.315107055794968E-3</v>
       </c>
-      <c r="E14" s="350"/>
-      <c r="F14" s="350"/>
+      <c r="E14" s="353"/>
+      <c r="F14" s="353"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16753,7 +16877,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -16763,21 +16887,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="350" t="s">
-        <v>339</v>
-      </c>
-      <c r="F18" s="351"/>
+      <c r="E18" s="353" t="s">
+        <v>338</v>
+      </c>
+      <c r="F18" s="354"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="351"/>
-      <c r="F19" s="351"/>
+      <c r="E19" s="354"/>
+      <c r="F19" s="354"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>310</v>
       </c>
-      <c r="E20" s="351"/>
-      <c r="F20" s="351"/>
+      <c r="E20" s="354"/>
+      <c r="F20" s="354"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -16791,8 +16915,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="351"/>
-      <c r="F21" s="351"/>
+      <c r="E21" s="354"/>
+      <c r="F21" s="354"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -16806,8 +16930,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="351"/>
-      <c r="F22" s="351"/>
+      <c r="E22" s="354"/>
+      <c r="F22" s="354"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -16827,8 +16951,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="349"/>
-      <c r="F25" s="349"/>
+      <c r="E25" s="352"/>
+      <c r="F25" s="352"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -16838,8 +16962,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="349"/>
-      <c r="F26" s="349"/>
+      <c r="E26" s="352"/>
+      <c r="F26" s="352"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -16853,8 +16977,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="349"/>
-      <c r="F27" s="349"/>
+      <c r="E27" s="352"/>
+      <c r="F27" s="352"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -16864,8 +16988,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="349"/>
-      <c r="F28" s="349"/>
+      <c r="E28" s="352"/>
+      <c r="F28" s="352"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -16885,8 +17009,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="349"/>
-      <c r="F31" s="349"/>
+      <c r="E31" s="352"/>
+      <c r="F31" s="352"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -16896,8 +17020,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="349"/>
-      <c r="F32" s="349"/>
+      <c r="E32" s="352"/>
+      <c r="F32" s="352"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -16911,8 +17035,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="349"/>
-      <c r="F33" s="349"/>
+      <c r="E33" s="352"/>
+      <c r="F33" s="352"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -16922,8 +17046,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="349"/>
-      <c r="F34" s="349"/>
+      <c r="E34" s="352"/>
+      <c r="F34" s="352"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -16943,8 +17067,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -16954,8 +17078,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="349"/>
-      <c r="F38" s="349"/>
+      <c r="E38" s="352"/>
+      <c r="F38" s="352"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -16969,8 +17093,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="349"/>
-      <c r="F39" s="349"/>
+      <c r="E39" s="352"/>
+      <c r="F39" s="352"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -16981,8 +17105,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="E40" s="352"/>
+      <c r="F40" s="352"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17044,8 +17168,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="349"/>
-      <c r="F49" s="349"/>
+      <c r="E49" s="352"/>
+      <c r="F49" s="352"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17055,8 +17179,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="E50" s="352"/>
+      <c r="F50" s="352"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17070,8 +17194,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="349"/>
-      <c r="F51" s="349"/>
+      <c r="E51" s="352"/>
+      <c r="F51" s="352"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17081,8 +17205,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="349"/>
-      <c r="F52" s="349"/>
+      <c r="E52" s="352"/>
+      <c r="F52" s="352"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
@@ -17102,8 +17226,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="349"/>
-      <c r="F55" s="349"/>
+      <c r="E55" s="352"/>
+      <c r="F55" s="352"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17113,8 +17237,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="349"/>
-      <c r="F56" s="349"/>
+      <c r="E56" s="352"/>
+      <c r="F56" s="352"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17128,8 +17252,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="349"/>
-      <c r="F57" s="349"/>
+      <c r="E57" s="352"/>
+      <c r="F57" s="352"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17139,8 +17263,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="E58" s="352"/>
+      <c r="F58" s="352"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17158,13 +17282,13 @@
         <v>303</v>
       </c>
       <c r="F60" s="312">
-        <f>Thesis!E20</f>
+        <f>Thesis!E25</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17189,7 +17313,7 @@
       </c>
       <c r="D64" s="151"/>
       <c r="E64" s="281" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17222,7 +17346,7 @@
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E68" s="282" t="s">
         <v>322</v>
@@ -17269,7 +17393,7 @@
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F72" s="329">
         <f>BS!D89/C60</f>
@@ -17323,7 +17447,7 @@
         <v>306</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C127</f>
+        <f>Thesis!C132</f>
         <v>0.3</v>
       </c>
     </row>
@@ -17404,15 +17528,15 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C90" s="168">
-        <f>Thesis!E19</f>
+        <f>Thesis!E24</f>
         <v>0.2</v>
       </c>
     </row>
@@ -17460,17 +17584,17 @@
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="316"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C96" s="135">
-        <f>Thesis!C67</f>
+        <f>Thesis!C72</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
@@ -17502,14 +17626,14 @@
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>59.048136223898794</v>
       </c>
       <c r="D99" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
@@ -17524,32 +17648,32 @@
     </row>
     <row r="101" spans="2:8" ht="14.65">
       <c r="E101" s="320" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F101" s="317"/>
     </row>
     <row r="102" spans="2:8" ht="13.9">
       <c r="E102" s="313" t="s">
+        <v>333</v>
+      </c>
+      <c r="F102" s="318" t="s">
         <v>334</v>
-      </c>
-      <c r="F102" s="318" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="103" spans="2:8" ht="13.9">
       <c r="E103" s="314" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F103" s="318" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="104" spans="2:8" ht="13.9">
       <c r="E104" s="315" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F104" s="319" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86934C2B-72B7-4ED8-B451-535ABFC66B20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{729569F6-4F24-4946-8101-66334638C54F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4264,13 +4264,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4370,22 +4370,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4397,13 +4397,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4423,13 +4423,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4458,13 +4458,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4550,13 +4550,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4572,7 +4572,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4594,22 +4594,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4670,22 +4670,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4743,22 +4743,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4795,13 +4795,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4814,13 +4814,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4951,13 +4951,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4996,13 +4996,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5145,13 +5145,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5164,22 +5164,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5443,13 +5443,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5486,13 +5486,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5500,22 +5500,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5539,17 +5539,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5566,6 +5555,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -8672,7 +8672,7 @@
       <c r="F28" s="210" t="s">
         <v>245</v>
       </c>
-      <c r="G28" s="181">
+      <c r="G28" s="12">
         <v>1268437841.4300001</v>
       </c>
       <c r="H28" s="209"/>

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{729569F6-4F24-4946-8101-66334638C54F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02EABCEA-3E57-4B43-9EDC-69185C4AB90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4206,7 +4206,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>57.21</v>
+        <v>57.32</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4226,8 +4226,7 @@
         <v>430</v>
       </c>
       <c r="C14" s="35">
-        <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>27687.992237580002</v>
+        <v>1</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4264,13 +4263,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4319,7 +4318,7 @@
         <v>277</v>
       </c>
       <c r="C24" s="249">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>417</v>
@@ -4335,7 +4334,7 @@
       </c>
       <c r="C25" s="252">
         <f>C139</f>
-        <v>34.669224296258527</v>
+        <v>28.081736799883384</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>315</v>
@@ -4350,7 +4349,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>9.1887382418681218E-2</v>
+        <v>9.1161384857910033E-2</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4370,22 +4369,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4397,13 +4396,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4423,13 +4422,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4458,13 +4457,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4480,13 +4479,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4550,13 +4549,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4572,7 +4571,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4594,22 +4593,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4643,7 +4642,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.0319983221959892E-2</v>
+        <v>8.0165845082489973E-2</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4652,7 +4651,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.195070791819612E-2</v>
+        <v>4.1870202372644799E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -4670,22 +4669,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4743,22 +4742,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4795,13 +4794,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4814,13 +4813,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4951,13 +4950,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4996,13 +4995,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5145,13 +5144,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5164,22 +5163,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5201,7 +5200,7 @@
       </c>
       <c r="C132" s="250">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="133" spans="2:6">
@@ -5236,7 +5235,7 @@
       </c>
       <c r="C136" s="337">
         <f>C24</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="137" spans="2:6">
@@ -5246,7 +5245,7 @@
       </c>
       <c r="C137" s="240">
         <f>Scenarios!C81</f>
-        <v>4.3586709148839331</v>
+        <v>3.8134110787171998</v>
       </c>
     </row>
     <row r="138" spans="2:6">
@@ -5256,7 +5255,7 @@
       </c>
       <c r="C138" s="240">
         <f>Scenarios!C82</f>
-        <v>30.310553381374593</v>
+        <v>24.268325721166185</v>
       </c>
     </row>
     <row r="139" spans="2:6">
@@ -5265,7 +5264,7 @@
       </c>
       <c r="C139" s="239">
         <f>Scenarios!C83</f>
-        <v>34.669224296258527</v>
+        <v>28.081736799883384</v>
       </c>
       <c r="D139" s="342" t="str">
         <f>IF($D$11="","",C139*$E$22)</f>
@@ -5291,7 +5290,7 @@
       </c>
       <c r="C141" s="92">
         <f>Scenarios!F83</f>
-        <v>0.4793807737524155</v>
+        <v>0.57830345555145946</v>
       </c>
     </row>
     <row r="143" spans="2:6">
@@ -5443,13 +5442,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5486,13 +5485,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5500,22 +5499,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5539,6 +5538,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5555,17 +5565,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
@@ -13108,12 +13107,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.195070791819612E-2</v>
+        <v>4.1870202372644799E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.195070791819612E-2</v>
+        <v>4.1870202372644799E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14307,50 +14306,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.0319983221959892E-2</v>
+        <v>8.0165845082489973E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.10469059714133933</v>
+        <v>0.10448969055226838</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.1149069586962701</v>
+        <v>0.11468644638893254</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.10996766449636715</v>
+        <v>0.10975663094621711</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10212189259009881</v>
+        <v>0.10192591547591684</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>6.2993771588933586E-2</v>
+        <v>6.28728833322207E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.3157110877585523E-2</v>
+        <v>2.3112671202140053E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.1737649000249458E-2</v>
+        <v>2.1695933344456936E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2452623940425352E-2</v>
+        <v>1.2428726720721116E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.2296754530936626E-2</v>
+        <v>1.2273156432569512E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>6.807982297255777E-3</v>
+        <v>6.794917432414567E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14364,43 +14363,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1240289028504914E-2</v>
+        <v>8.1084384775309951E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7933014851097691E-2</v>
+        <v>9.7745076406687004E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.3430380173571637E-2</v>
+        <v>9.3251082514480693E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6649699097491956E-2</v>
+        <v>8.6483413910808007E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.3287979892656776E-2</v>
+        <v>6.3166527035221465E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6312378440036571E-2</v>
+        <v>2.6261883645402866E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5214518531547346E-2</v>
+        <v>1.5185321095426094E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1778475383901794E-2</v>
+        <v>1.1755871889620058E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0542187313265151E-3</v>
+        <v>5.0445194281086873E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.5457983259468296E-3</v>
+        <v>-5.5351556564448385E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16669,7 +16668,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-57.21</v>
+        <v>-57.32</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16909,7 +16908,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>57.21</v>
+        <v>57.32</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17448,7 +17447,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!C132</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -17457,7 +17456,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>4.3586709148839331</v>
+        <v>3.8134110787171998</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -17469,7 +17468,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>30.310553381374593</v>
+        <v>24.268325721166185</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -17479,7 +17478,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>34.669224296258527</v>
+        <v>28.081736799883384</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -17490,7 +17489,7 @@
       </c>
       <c r="F83" s="329">
         <f>(1-C83/C60)</f>
-        <v>0.4793807737524155</v>
+        <v>0.57830345555145946</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -17507,7 +17506,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>57.21</v>
+        <v>57.32</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17520,7 +17519,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.1887382418681218E-2</v>
+        <v>9.1161384857910033E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02EABCEA-3E57-4B43-9EDC-69185C4AB90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585B246B-22F4-4899-B039-92CCE7F332CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4226,7 +4226,8 @@
         <v>430</v>
       </c>
       <c r="C14" s="35">
-        <v>1</v>
+        <f>Thesis!C12*Common_Shares/1000000</f>
+        <v>27741.229069360001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4263,13 +4264,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
+      <c r="B18" s="345" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
+      <c r="C18" s="345"/>
+      <c r="D18" s="345"/>
+      <c r="E18" s="345"/>
+      <c r="F18" s="345"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4369,22 +4370,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
+      <c r="B30" s="345" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
+      <c r="C30" s="345"/>
+      <c r="D30" s="345"/>
+      <c r="E30" s="345"/>
+      <c r="F30" s="345"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
+      <c r="B31" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
+      <c r="C31" s="348"/>
+      <c r="D31" s="348"/>
+      <c r="E31" s="348"/>
+      <c r="F31" s="348"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4396,13 +4397,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+      <c r="B34" s="346" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
+      <c r="C34" s="346"/>
+      <c r="D34" s="346"/>
+      <c r="E34" s="346"/>
+      <c r="F34" s="346"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4422,13 +4423,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+      <c r="B37" s="346" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
+      <c r="C37" s="346"/>
+      <c r="D37" s="346"/>
+      <c r="E37" s="346"/>
+      <c r="F37" s="346"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4457,13 +4458,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
+      <c r="B41" s="346" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
+      <c r="C41" s="346"/>
+      <c r="D41" s="346"/>
+      <c r="E41" s="346"/>
+      <c r="F41" s="346"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4479,13 +4480,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
+      <c r="B44" s="346" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
+      <c r="C44" s="346"/>
+      <c r="D44" s="346"/>
+      <c r="E44" s="346"/>
+      <c r="F44" s="346"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4549,13 +4550,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
+      <c r="B52" s="346" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
+      <c r="C52" s="346"/>
+      <c r="D52" s="346"/>
+      <c r="E52" s="346"/>
+      <c r="F52" s="346"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4571,7 +4572,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
+      <c r="B55" s="346" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4593,22 +4594,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
+      <c r="B58" s="345" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
+      <c r="C58" s="345"/>
+      <c r="D58" s="345"/>
+      <c r="E58" s="345"/>
+      <c r="F58" s="345"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
+      <c r="B59" s="345" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
+      <c r="C59" s="345"/>
+      <c r="D59" s="345"/>
+      <c r="E59" s="345"/>
+      <c r="F59" s="345"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4669,22 +4670,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
+      <c r="B68" s="345" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
+      <c r="C68" s="345"/>
+      <c r="D68" s="345"/>
+      <c r="E68" s="345"/>
+      <c r="F68" s="345"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+      <c r="B69" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
+      <c r="C69" s="348"/>
+      <c r="D69" s="348"/>
+      <c r="E69" s="348"/>
+      <c r="F69" s="348"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4742,22 +4743,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
+      <c r="B78" s="345" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
+      <c r="C78" s="345"/>
+      <c r="D78" s="345"/>
+      <c r="E78" s="345"/>
+      <c r="F78" s="345"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
+      <c r="B79" s="345" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
+      <c r="C79" s="345"/>
+      <c r="D79" s="345"/>
+      <c r="E79" s="345"/>
+      <c r="F79" s="345"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4794,13 +4795,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
+      <c r="B86" s="345" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
+      <c r="C86" s="345"/>
+      <c r="D86" s="345"/>
+      <c r="E86" s="345"/>
+      <c r="F86" s="345"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4813,13 +4814,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
+      <c r="B90" s="345" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
+      <c r="C90" s="345"/>
+      <c r="D90" s="345"/>
+      <c r="E90" s="345"/>
+      <c r="F90" s="345"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4950,13 +4951,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
+      <c r="B106" s="345" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
+      <c r="C106" s="345"/>
+      <c r="D106" s="345"/>
+      <c r="E106" s="345"/>
+      <c r="F106" s="345"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4995,13 +4996,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
+      <c r="B113" s="346" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
+      <c r="C113" s="346"/>
+      <c r="D113" s="346"/>
+      <c r="E113" s="346"/>
+      <c r="F113" s="346"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5144,13 +5145,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
+      <c r="B124" s="349" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
+      <c r="C124" s="349"/>
+      <c r="D124" s="349"/>
+      <c r="E124" s="349"/>
+      <c r="F124" s="349"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5163,22 +5164,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
+      <c r="B128" s="350" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
+      <c r="C128" s="350"/>
+      <c r="D128" s="350"/>
+      <c r="E128" s="350"/>
+      <c r="F128" s="350"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
+      <c r="B129" s="345" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
+      <c r="C129" s="345"/>
+      <c r="D129" s="345"/>
+      <c r="E129" s="345"/>
+      <c r="F129" s="345"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5442,13 +5443,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="350" t="s">
+      <c r="B161" s="344" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="343"/>
-      <c r="D161" s="343"/>
-      <c r="E161" s="343"/>
-      <c r="F161" s="343"/>
+      <c r="C161" s="345"/>
+      <c r="D161" s="345"/>
+      <c r="E161" s="345"/>
+      <c r="F161" s="345"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5485,13 +5486,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="344" t="s">
+      <c r="B170" s="346" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="344"/>
-      <c r="D170" s="344"/>
-      <c r="E170" s="344"/>
-      <c r="F170" s="344"/>
+      <c r="C170" s="346"/>
+      <c r="D170" s="346"/>
+      <c r="E170" s="346"/>
+      <c r="F170" s="346"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5499,22 +5500,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="349" t="s">
+      <c r="B173" s="343" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="349"/>
-      <c r="D173" s="349"/>
-      <c r="E173" s="349"/>
-      <c r="F173" s="349"/>
+      <c r="C173" s="343"/>
+      <c r="D173" s="343"/>
+      <c r="E173" s="343"/>
+      <c r="F173" s="343"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="349" t="s">
+      <c r="B174" s="343" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="343"/>
+      <c r="D174" s="343"/>
+      <c r="E174" s="343"/>
+      <c r="F174" s="343"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5538,17 +5539,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5565,6 +5555,17 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{585B246B-22F4-4899-B039-92CCE7F332CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C2F1CE5-0F63-4031-BC68-905E2E5214BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -4206,7 +4206,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>57.32</v>
+        <v>57.12</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>27741.229069360001</v>
+        <v>27644.434829759997</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4350,7 +4350,7 @@
       </c>
       <c r="C26" s="280">
         <f ca="1">Scenarios!C87</f>
-        <v>9.1161384857910033E-2</v>
+        <v>9.2482801640861867E-2</v>
       </c>
       <c r="D26" s="5"/>
       <c r="E26" s="5"/>
@@ -4617,7 +4617,7 @@
       </c>
       <c r="C61" s="188">
         <f>Normalized_FCF!G19</f>
-        <v>2898672440.9970183</v>
+        <v>2322754575.9970183</v>
       </c>
       <c r="D61" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C63" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.0165845082489973E-2</v>
+        <v>8.0446537817372654E-2</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="C64" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.1870202372644799E-2</v>
+        <v>4.2016806722689079E-2</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="13.9">
@@ -7464,32 +7464,32 @@
         <v>53</v>
       </c>
       <c r="C62" s="183">
-        <f>IF(C$4="","",-C20)</f>
-        <v>0</v>
+        <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
+        <v>-575917865</v>
       </c>
       <c r="D62" s="183">
-        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",-D20)</f>
-        <v>0</v>
+        <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
+        <v>-514817738</v>
       </c>
       <c r="E62" s="183">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>-504410326</v>
       </c>
       <c r="F62" s="183">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>-451827434</v>
       </c>
       <c r="G62" s="183">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>-413794059</v>
       </c>
       <c r="H62" s="183">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>-174070610</v>
       </c>
       <c r="I62" s="183">
         <f t="shared" si="30"/>
-        <v>0</v>
+        <v>-173632673</v>
       </c>
       <c r="J62" s="183">
         <f t="shared" si="30"/>
@@ -9902,31 +9902,31 @@
       <c r="E10" s="302"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
-        <v>0</v>
+        <v>-575917865</v>
       </c>
       <c r="H10" s="191">
         <f>Data!D62</f>
-        <v>0</v>
+        <v>-514817738</v>
       </c>
       <c r="I10" s="191">
         <f>Data!E62</f>
-        <v>0</v>
+        <v>-504410326</v>
       </c>
       <c r="J10" s="191">
         <f>Data!F62</f>
-        <v>0</v>
+        <v>-451827434</v>
       </c>
       <c r="K10" s="191">
         <f>Data!G62</f>
-        <v>0</v>
+        <v>-413794059</v>
       </c>
       <c r="L10" s="191">
         <f>Data!H62</f>
-        <v>0</v>
+        <v>-174070610</v>
       </c>
       <c r="M10" s="191">
         <f>Data!I62</f>
-        <v>0</v>
+        <v>-173632673</v>
       </c>
       <c r="N10" s="191">
         <f>Data!J62</f>
@@ -10069,31 +10069,31 @@
       <c r="E13" s="302"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>3716012388.9970183</v>
+        <v>3140094523.9970183</v>
       </c>
       <c r="H13" s="184">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>3845664977.4262524</v>
+        <v>3330847239.4262524</v>
       </c>
       <c r="I13" s="184">
         <f t="shared" si="7"/>
-        <v>3756663019.9602156</v>
+        <v>3252252693.9602156</v>
       </c>
       <c r="J13" s="184">
         <f t="shared" si="7"/>
-        <v>3369473988.3216343</v>
+        <v>2917646554.3216343</v>
       </c>
       <c r="K13" s="184">
         <f t="shared" si="7"/>
-        <v>2122638774.7702808</v>
+        <v>1708844715.7702808</v>
       </c>
       <c r="L13" s="184">
         <f t="shared" si="7"/>
-        <v>739954593.22336733</v>
+        <v>565883983.22336733</v>
       </c>
       <c r="M13" s="184">
         <f t="shared" si="7"/>
-        <v>662889862.78214574</v>
+        <v>489257189.78214574</v>
       </c>
       <c r="N13" s="184">
         <f t="shared" si="7"/>
@@ -10238,31 +10238,31 @@
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>2898672440.9970183</v>
+        <v>2322754575.9970183</v>
       </c>
       <c r="H16" s="184">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>3181542980.4262524</v>
+        <v>2666725242.4262524</v>
       </c>
       <c r="I16" s="184">
         <f t="shared" si="8"/>
-        <v>3044783840.9602156</v>
+        <v>2540373514.9602156</v>
       </c>
       <c r="J16" s="184">
         <f t="shared" si="8"/>
-        <v>2827550169.3216343</v>
+        <v>2375722735.3216343</v>
       </c>
       <c r="K16" s="184">
         <f t="shared" si="8"/>
-        <v>1744171058.7702808</v>
+        <v>1330376999.7702808</v>
       </c>
       <c r="L16" s="184">
         <f t="shared" si="8"/>
-        <v>641173906.22336733</v>
+        <v>467103296.22336733</v>
       </c>
       <c r="M16" s="184">
         <f t="shared" si="8"/>
-        <v>601871856.78214574</v>
+        <v>428239183.78214574</v>
       </c>
       <c r="N16" s="184">
         <f t="shared" si="8"/>
@@ -10346,31 +10346,31 @@
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>2898672440.9970183</v>
+        <v>2322754575.9970183</v>
       </c>
       <c r="H19" s="186">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>3181542980.4262524</v>
+        <v>2666725242.4262524</v>
       </c>
       <c r="I19" s="186">
         <f t="shared" si="9"/>
-        <v>3044783840.9602156</v>
+        <v>2540373514.9602156</v>
       </c>
       <c r="J19" s="186">
         <f t="shared" si="9"/>
-        <v>2827550169.3216343</v>
+        <v>2375722735.3216343</v>
       </c>
       <c r="K19" s="186">
         <f t="shared" si="9"/>
-        <v>1744171058.7702808</v>
+        <v>1330376999.7702808</v>
       </c>
       <c r="L19" s="186">
         <f t="shared" si="9"/>
-        <v>641173906.22336733</v>
+        <v>467103296.22336733</v>
       </c>
       <c r="M19" s="186">
         <f t="shared" si="9"/>
-        <v>601871856.78214574</v>
+        <v>428239183.78214574</v>
       </c>
       <c r="N19" s="186">
         <f t="shared" si="9"/>
@@ -12430,31 +12430,31 @@
       <c r="F78" s="27"/>
       <c r="G78" s="6">
         <f t="shared" ref="G78:Q78" si="29">IF(G$4="","",-G10/G$4)</f>
-        <v>0</v>
+        <v>3.9326301153063785E-2</v>
       </c>
       <c r="H78" s="6">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>3.4750146660579968E-2</v>
       </c>
       <c r="I78" s="6">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>3.5929116708422096E-2</v>
       </c>
       <c r="J78" s="6">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>3.4439876053341624E-2</v>
       </c>
       <c r="K78" s="6">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>3.7818315462805736E-2</v>
       </c>
       <c r="L78" s="6">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>4.8596961543068702E-2</v>
       </c>
       <c r="M78" s="6">
         <f t="shared" si="29"/>
-        <v>0</v>
+        <v>5.0076680340574907E-2</v>
       </c>
       <c r="N78" s="6">
         <f t="shared" si="29"/>
@@ -12601,31 +12601,31 @@
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.25374629123236653</v>
+        <v>0.21441999007930274</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.25958200759006911</v>
+        <v>0.22483186092948915</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.26758687743114118</v>
+        <v>0.23165776072271912</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.25683315750755353</v>
+        <v>0.22239328145421189</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>0.19399655710824484</v>
+        <v>0.15617824164543909</v>
       </c>
       <c r="L81" s="65">
         <f t="shared" si="32"/>
-        <v>0.20658022000665721</v>
+        <v>0.15798325846358852</v>
       </c>
       <c r="M81" s="65">
         <f t="shared" si="32"/>
-        <v>0.19118132080791655</v>
+        <v>0.14110464046734167</v>
       </c>
       <c r="N81" s="65">
         <f t="shared" si="32"/>
@@ -12773,31 +12773,31 @@
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>0.19793458804882752</v>
+        <v>0.15860828689576373</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>0.21475383813747104</v>
+        <v>0.18000369147689105</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>0.21687976699703265</v>
+        <v>0.18095065028861054</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>0.21552581812914487</v>
+        <v>0.18108594207580322</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>0.15940685925041365</v>
+        <v>0.12158854378760792</v>
       </c>
       <c r="L84" s="65">
         <f t="shared" si="35"/>
-        <v>0.17900266830314501</v>
+        <v>0.13040570676007632</v>
       </c>
       <c r="M84" s="65">
         <f t="shared" si="35"/>
-        <v>0.17358337032608945</v>
+        <v>0.12350668998551453</v>
       </c>
       <c r="N84" s="65">
         <f t="shared" si="35"/>
@@ -12880,31 +12880,31 @@
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>0.19793458804882752</v>
+        <v>0.15860828689576373</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>0.21475383813747104</v>
+        <v>0.18000369147689105</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>0.21687976699703265</v>
+        <v>0.18095065028861054</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>0.21552581812914487</v>
+        <v>0.18108594207580322</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>0.15940685925041365</v>
+        <v>0.12158854378760792</v>
       </c>
       <c r="L87" s="65">
         <f t="shared" si="36"/>
-        <v>0.17900266830314501</v>
+        <v>0.13040570676007632</v>
       </c>
       <c r="M87" s="65">
         <f t="shared" si="36"/>
-        <v>0.17358337032608945</v>
+        <v>0.12350668998551453</v>
       </c>
       <c r="N87" s="65">
         <f t="shared" si="36"/>
@@ -13058,7 +13058,7 @@
       <c r="E92" s="302"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.40071132521634056</v>
+        <v>0.50006612287112806</v>
       </c>
       <c r="H92" s="171">
         <f t="shared" si="38"/>
@@ -13108,12 +13108,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.1870202372644799E-2</v>
+        <v>4.2016806722689079E-2</v>
       </c>
       <c r="E93" s="302"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.1870202372644799E-2</v>
+        <v>4.2016806722689079E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -13245,38 +13245,38 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>-0.15114069290137222</v>
+        <v>4.5467350067964762E-3</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="299"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-3.3713958233565489E-2</v>
+        <v>-5.726852710966468E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>2.3691759679573154E-2</v>
+        <v>2.4166186597983419E-2</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>0.11491082376078632</v>
+        <v>0.11468357575490451</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>0.58739867959224012</v>
+        <v>0.70737956901278332</v>
       </c>
       <c r="K97" s="6">
         <f t="shared" si="41"/>
-        <v>1.8686067958896064</v>
+        <v>2.0197792594100701</v>
       </c>
       <c r="L97" s="6">
         <f t="shared" si="41"/>
-        <v>0.11625570817719444</v>
+        <v>0.15661863543659238</v>
       </c>
       <c r="M97" s="6">
         <f t="shared" si="41"/>
-        <v>0.82281820292209007</v>
+        <v>0.3453621204922479</v>
       </c>
       <c r="N97" s="6">
         <f t="shared" si="41"/>
@@ -13856,31 +13856,31 @@
       <c r="E114" s="302"/>
       <c r="G114" s="334">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>0.87696929430413517</v>
+        <v>1.0944103829432141</v>
       </c>
       <c r="H114" s="334">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>0.97341096318776787</v>
+        <v>1.1613302966984029</v>
       </c>
       <c r="I114" s="334">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.2324842928148716</v>
+        <v>1.477203347027797</v>
       </c>
       <c r="J114" s="334">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.2607334616648864</v>
+        <v>1.5005063764384885</v>
       </c>
       <c r="K114" s="334">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>2.1154638803612684</v>
+        <v>2.773447584133756</v>
       </c>
       <c r="L114" s="334">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.1007619838386338</v>
+        <v>1.5109716987792317</v>
       </c>
       <c r="M114" s="334">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.2367746832021034</v>
+        <v>1.7382339197122179</v>
       </c>
       <c r="N114" s="334">
         <f>IF(N$4="","",Data!J$22/N19)</f>
@@ -13969,31 +13969,31 @@
       <c r="E117" s="302"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.25374629123236653</v>
+        <v>0.21441999007930274</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.25958200759006911</v>
+        <v>0.22483186092948915</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.26758687743114118</v>
+        <v>0.23165776072271912</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.25683315750755353</v>
+        <v>0.22239328145421189</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
-        <v>0.19399655710824484</v>
+        <v>0.15617824164543909</v>
       </c>
       <c r="L117" s="23">
         <f t="shared" si="45"/>
-        <v>0.20658022000665721</v>
+        <v>0.15798325846358852</v>
       </c>
       <c r="M117" s="23">
         <f t="shared" si="45"/>
-        <v>0.19118132080791655</v>
+        <v>0.14110464046734167</v>
       </c>
       <c r="N117" s="23">
         <f t="shared" si="45"/>
@@ -14257,31 +14257,31 @@
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>5.9893490624560233</v>
+        <v>4.7993653043729649</v>
       </c>
       <c r="H124" s="178">
         <f t="shared" si="49"/>
-        <v>6.5738271070136127</v>
+        <v>5.5100907935150563</v>
       </c>
       <c r="I124" s="178">
         <f t="shared" si="49"/>
-        <v>6.2912500858371647</v>
+        <v>5.2490179693714243</v>
       </c>
       <c r="J124" s="178">
         <f t="shared" si="49"/>
-        <v>5.842393475079553</v>
+        <v>4.9088101629585701</v>
       </c>
       <c r="K124" s="178">
         <f t="shared" si="49"/>
-        <v>3.6038736726028908</v>
+        <v>2.7488763903059388</v>
       </c>
       <c r="L124" s="178">
         <f t="shared" si="49"/>
-        <v>1.3248183133066678</v>
+        <v>0.96514688922328662</v>
       </c>
       <c r="M124" s="178">
         <f t="shared" si="49"/>
-        <v>1.2436108993042716</v>
+        <v>0.88484435758126612</v>
       </c>
       <c r="N124" s="178">
         <f t="shared" si="49"/>
@@ -14307,50 +14307,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.0165845082489973E-2</v>
+        <v>8.0446537817372654E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="299"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>0.10448969055226838</v>
+        <v>8.4022501827257789E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>0.11468644638893254</v>
+        <v>9.6465174956496091E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>0.10975663094621711</v>
+        <v>9.1894572292917101E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>0.10192591547591684</v>
+        <v>8.5938553273084209E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>6.28728833322207E-2</v>
+        <v>4.8124586665019939E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>2.3112671202140053E-2</v>
+        <v>1.6896829293124766E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>2.1695933344456936E-2</v>
+        <v>1.549097264673085E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2428726720721116E-2</v>
+        <v>1.2472244671423922E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.2273156432569512E-2</v>
+        <v>1.2316129669378229E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>6.794917432414567E-3</v>
+        <v>6.8187091601191003E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14364,43 +14364,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1084384775309951E-2</v>
+        <v>8.1368293685587664E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7745076406687004E-2</v>
+        <v>9.8087321071976541E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.3251082514480693E-2</v>
+        <v>9.3577591907038404E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6483413910808007E-2</v>
+        <v>8.6786226984725406E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.3166527035221465E-2</v>
+        <v>6.3387698348370006E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6261883645402866E-2</v>
+        <v>2.6353837019511422E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5185321095426094E-2</v>
+        <v>1.5238490987216803E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1755871889620058E-2</v>
+        <v>1.1797033906040297E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0445194281086873E-3</v>
+        <v>5.0621823112603284E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.5351556564448385E-3</v>
+        <v>-5.5545364535612429E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -16669,7 +16669,7 @@
       </c>
       <c r="I3" s="264">
         <f>-Market_Price</f>
-        <v>-57.32</v>
+        <v>-57.12</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -16752,7 +16752,7 @@
       </c>
       <c r="C8" s="115">
         <f>Normalized_FCF!G19</f>
-        <v>2898672440.9970183</v>
+        <v>2322754575.9970183</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -16858,7 +16858,7 @@
       </c>
       <c r="C14" s="159">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>8.315107055794968E-3</v>
+        <v>-7.4877931429291333E-3</v>
       </c>
       <c r="E14" s="353"/>
       <c r="F14" s="353"/>
@@ -16909,7 +16909,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>57.32</v>
+        <v>57.12</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -17507,7 +17507,7 @@
       </c>
       <c r="C86" s="266">
         <f>Market_Price</f>
-        <v>57.32</v>
+        <v>57.12</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -17520,7 +17520,7 @@
       </c>
       <c r="C87" s="265">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.1161384857910033E-2</v>
+        <v>9.2482801640861867E-2</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C2F1CE5-0F63-4031-BC68-905E2E5214BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FF4978F-7A32-4856-B1B5-C881C76DE9B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3782,29 +3782,29 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4264,13 +4264,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="345" t="s">
+      <c r="B18" s="343" t="s">
         <v>367</v>
       </c>
-      <c r="C18" s="345"/>
-      <c r="D18" s="345"/>
-      <c r="E18" s="345"/>
-      <c r="F18" s="345"/>
+      <c r="C18" s="343"/>
+      <c r="D18" s="343"/>
+      <c r="E18" s="343"/>
+      <c r="F18" s="343"/>
     </row>
     <row r="20" spans="1:6">
       <c r="B20" s="45" t="s">
@@ -4370,22 +4370,22 @@
       <c r="F28" s="36"/>
     </row>
     <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="345" t="s">
+      <c r="B30" s="343" t="s">
         <v>368</v>
       </c>
-      <c r="C30" s="345"/>
-      <c r="D30" s="345"/>
-      <c r="E30" s="345"/>
-      <c r="F30" s="345"/>
+      <c r="C30" s="343"/>
+      <c r="D30" s="343"/>
+      <c r="E30" s="343"/>
+      <c r="F30" s="343"/>
     </row>
     <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="348" t="s">
+      <c r="B31" s="345" t="s">
         <v>347</v>
       </c>
-      <c r="C31" s="348"/>
-      <c r="D31" s="348"/>
-      <c r="E31" s="348"/>
-      <c r="F31" s="348"/>
+      <c r="C31" s="345"/>
+      <c r="D31" s="345"/>
+      <c r="E31" s="345"/>
+      <c r="F31" s="345"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="234" t="s">
@@ -4397,13 +4397,13 @@
       </c>
     </row>
     <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="346" t="s">
+      <c r="B34" s="344" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="346"/>
-      <c r="D34" s="346"/>
-      <c r="E34" s="346"/>
-      <c r="F34" s="346"/>
+      <c r="C34" s="344"/>
+      <c r="D34" s="344"/>
+      <c r="E34" s="344"/>
+      <c r="F34" s="344"/>
     </row>
     <row r="35" spans="2:6">
       <c r="B35" s="47" t="s">
@@ -4423,13 +4423,13 @@
       <c r="C36" s="76"/>
     </row>
     <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="344" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="346"/>
-      <c r="D37" s="346"/>
-      <c r="E37" s="346"/>
-      <c r="F37" s="346"/>
+      <c r="C37" s="344"/>
+      <c r="D37" s="344"/>
+      <c r="E37" s="344"/>
+      <c r="F37" s="344"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="47" t="s">
@@ -4458,13 +4458,13 @@
       </c>
     </row>
     <row r="41" spans="2:6">
-      <c r="B41" s="346" t="s">
+      <c r="B41" s="344" t="s">
         <v>237</v>
       </c>
-      <c r="C41" s="346"/>
-      <c r="D41" s="346"/>
-      <c r="E41" s="346"/>
-      <c r="F41" s="346"/>
+      <c r="C41" s="344"/>
+      <c r="D41" s="344"/>
+      <c r="E41" s="344"/>
+      <c r="F41" s="344"/>
     </row>
     <row r="42" spans="2:6">
       <c r="B42" s="47" t="s">
@@ -4480,13 +4480,13 @@
       </c>
     </row>
     <row r="44" spans="2:6">
-      <c r="B44" s="346" t="s">
+      <c r="B44" s="344" t="s">
         <v>241</v>
       </c>
-      <c r="C44" s="346"/>
-      <c r="D44" s="346"/>
-      <c r="E44" s="346"/>
-      <c r="F44" s="346"/>
+      <c r="C44" s="344"/>
+      <c r="D44" s="344"/>
+      <c r="E44" s="344"/>
+      <c r="F44" s="344"/>
     </row>
     <row r="45" spans="2:6">
       <c r="B45" s="47" t="s">
@@ -4550,13 +4550,13 @@
       </c>
     </row>
     <row r="52" spans="2:6">
-      <c r="B52" s="346" t="s">
+      <c r="B52" s="344" t="s">
         <v>242</v>
       </c>
-      <c r="C52" s="346"/>
-      <c r="D52" s="346"/>
-      <c r="E52" s="346"/>
-      <c r="F52" s="346"/>
+      <c r="C52" s="344"/>
+      <c r="D52" s="344"/>
+      <c r="E52" s="344"/>
+      <c r="F52" s="344"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4572,7 +4572,7 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="346" t="s">
+      <c r="B55" s="344" t="s">
         <v>346</v>
       </c>
       <c r="C55" s="347"/>
@@ -4594,22 +4594,22 @@
       </c>
     </row>
     <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="345" t="s">
+      <c r="B58" s="343" t="s">
         <v>351</v>
       </c>
-      <c r="C58" s="345"/>
-      <c r="D58" s="345"/>
-      <c r="E58" s="345"/>
-      <c r="F58" s="345"/>
+      <c r="C58" s="343"/>
+      <c r="D58" s="343"/>
+      <c r="E58" s="343"/>
+      <c r="F58" s="343"/>
     </row>
     <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="345" t="s">
+      <c r="B59" s="343" t="s">
         <v>369</v>
       </c>
-      <c r="C59" s="345"/>
-      <c r="D59" s="345"/>
-      <c r="E59" s="345"/>
-      <c r="F59" s="345"/>
+      <c r="C59" s="343"/>
+      <c r="D59" s="343"/>
+      <c r="E59" s="343"/>
+      <c r="F59" s="343"/>
     </row>
     <row r="61" spans="2:6">
       <c r="B61" s="47" t="s">
@@ -4670,22 +4670,22 @@
     </row>
     <row r="68" spans="1:6" ht="24.4" customHeight="1">
       <c r="A68" s="17"/>
-      <c r="B68" s="345" t="s">
+      <c r="B68" s="343" t="s">
         <v>370</v>
       </c>
-      <c r="C68" s="345"/>
-      <c r="D68" s="345"/>
-      <c r="E68" s="345"/>
-      <c r="F68" s="345"/>
+      <c r="C68" s="343"/>
+      <c r="D68" s="343"/>
+      <c r="E68" s="343"/>
+      <c r="F68" s="343"/>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="348" t="s">
+      <c r="B69" s="345" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="348"/>
-      <c r="D69" s="348"/>
-      <c r="E69" s="348"/>
-      <c r="F69" s="348"/>
+      <c r="C69" s="345"/>
+      <c r="D69" s="345"/>
+      <c r="E69" s="345"/>
+      <c r="F69" s="345"/>
     </row>
     <row r="71" spans="1:6">
       <c r="B71" s="234" t="s">
@@ -4743,22 +4743,22 @@
       <c r="C77" s="122"/>
     </row>
     <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="345" t="s">
+      <c r="B78" s="343" t="s">
         <v>371</v>
       </c>
-      <c r="C78" s="345"/>
-      <c r="D78" s="345"/>
-      <c r="E78" s="345"/>
-      <c r="F78" s="345"/>
+      <c r="C78" s="343"/>
+      <c r="D78" s="343"/>
+      <c r="E78" s="343"/>
+      <c r="F78" s="343"/>
     </row>
     <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="345" t="s">
+      <c r="B79" s="343" t="s">
         <v>372</v>
       </c>
-      <c r="C79" s="345"/>
-      <c r="D79" s="345"/>
-      <c r="E79" s="345"/>
-      <c r="F79" s="345"/>
+      <c r="C79" s="343"/>
+      <c r="D79" s="343"/>
+      <c r="E79" s="343"/>
+      <c r="F79" s="343"/>
     </row>
     <row r="81" spans="1:6">
       <c r="B81" s="47" t="s">
@@ -4795,13 +4795,13 @@
       <c r="A85" s="233"/>
     </row>
     <row r="86" spans="1:6">
-      <c r="B86" s="345" t="s">
+      <c r="B86" s="343" t="s">
         <v>373</v>
       </c>
-      <c r="C86" s="345"/>
-      <c r="D86" s="345"/>
-      <c r="E86" s="345"/>
-      <c r="F86" s="345"/>
+      <c r="C86" s="343"/>
+      <c r="D86" s="343"/>
+      <c r="E86" s="343"/>
+      <c r="F86" s="343"/>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="1" t="s">
@@ -4814,13 +4814,13 @@
       </c>
     </row>
     <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="345" t="s">
+      <c r="B90" s="343" t="s">
         <v>352</v>
       </c>
-      <c r="C90" s="345"/>
-      <c r="D90" s="345"/>
-      <c r="E90" s="345"/>
-      <c r="F90" s="345"/>
+      <c r="C90" s="343"/>
+      <c r="D90" s="343"/>
+      <c r="E90" s="343"/>
+      <c r="F90" s="343"/>
     </row>
     <row r="91" spans="1:6">
       <c r="B91" s="47" t="s">
@@ -4951,13 +4951,13 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="345" t="s">
+      <c r="B106" s="343" t="s">
         <v>374</v>
       </c>
-      <c r="C106" s="345"/>
-      <c r="D106" s="345"/>
-      <c r="E106" s="345"/>
-      <c r="F106" s="345"/>
+      <c r="C106" s="343"/>
+      <c r="D106" s="343"/>
+      <c r="E106" s="343"/>
+      <c r="F106" s="343"/>
     </row>
     <row r="108" spans="1:6">
       <c r="B108" s="47" t="s">
@@ -4996,13 +4996,13 @@
       <c r="F111" s="36"/>
     </row>
     <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="346" t="s">
+      <c r="B113" s="344" t="s">
         <v>375</v>
       </c>
-      <c r="C113" s="346"/>
-      <c r="D113" s="346"/>
-      <c r="E113" s="346"/>
-      <c r="F113" s="346"/>
+      <c r="C113" s="344"/>
+      <c r="D113" s="344"/>
+      <c r="E113" s="344"/>
+      <c r="F113" s="344"/>
     </row>
     <row r="115" spans="1:6" ht="12.4">
       <c r="B115" s="260" t="s">
@@ -5145,13 +5145,13 @@
       </c>
     </row>
     <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="349" t="s">
+      <c r="B124" s="348" t="s">
         <v>378</v>
       </c>
-      <c r="C124" s="349"/>
-      <c r="D124" s="349"/>
-      <c r="E124" s="349"/>
-      <c r="F124" s="349"/>
+      <c r="C124" s="348"/>
+      <c r="D124" s="348"/>
+      <c r="E124" s="348"/>
+      <c r="F124" s="348"/>
     </row>
     <row r="126" spans="1:6" ht="13.9">
       <c r="A126" s="247" t="s">
@@ -5164,22 +5164,22 @@
       <c r="F126" s="36"/>
     </row>
     <row r="128" spans="1:6">
-      <c r="B128" s="350" t="s">
+      <c r="B128" s="346" t="s">
         <v>376</v>
       </c>
-      <c r="C128" s="350"/>
-      <c r="D128" s="350"/>
-      <c r="E128" s="350"/>
-      <c r="F128" s="350"/>
+      <c r="C128" s="346"/>
+      <c r="D128" s="346"/>
+      <c r="E128" s="346"/>
+      <c r="F128" s="346"/>
     </row>
     <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="345" t="s">
+      <c r="B129" s="343" t="s">
         <v>377</v>
       </c>
-      <c r="C129" s="345"/>
-      <c r="D129" s="345"/>
-      <c r="E129" s="345"/>
-      <c r="F129" s="345"/>
+      <c r="C129" s="343"/>
+      <c r="D129" s="343"/>
+      <c r="E129" s="343"/>
+      <c r="F129" s="343"/>
     </row>
     <row r="130" spans="2:6">
       <c r="B130" s="234" t="s">
@@ -5443,13 +5443,13 @@
       <c r="F159" s="36"/>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="344" t="s">
+      <c r="B161" s="350" t="s">
         <v>384</v>
       </c>
-      <c r="C161" s="345"/>
-      <c r="D161" s="345"/>
-      <c r="E161" s="345"/>
-      <c r="F161" s="345"/>
+      <c r="C161" s="343"/>
+      <c r="D161" s="343"/>
+      <c r="E161" s="343"/>
+      <c r="F161" s="343"/>
     </row>
     <row r="163" spans="2:6">
       <c r="B163" s="234" t="s">
@@ -5486,13 +5486,13 @@
       </c>
     </row>
     <row r="170" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B170" s="346" t="s">
+      <c r="B170" s="344" t="s">
         <v>389</v>
       </c>
-      <c r="C170" s="346"/>
-      <c r="D170" s="346"/>
-      <c r="E170" s="346"/>
-      <c r="F170" s="346"/>
+      <c r="C170" s="344"/>
+      <c r="D170" s="344"/>
+      <c r="E170" s="344"/>
+      <c r="F170" s="344"/>
     </row>
     <row r="172" spans="2:6">
       <c r="B172" s="1" t="s">
@@ -5500,22 +5500,22 @@
       </c>
     </row>
     <row r="173" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B173" s="343" t="s">
+      <c r="B173" s="349" t="s">
         <v>390</v>
       </c>
-      <c r="C173" s="343"/>
-      <c r="D173" s="343"/>
-      <c r="E173" s="343"/>
-      <c r="F173" s="343"/>
+      <c r="C173" s="349"/>
+      <c r="D173" s="349"/>
+      <c r="E173" s="349"/>
+      <c r="F173" s="349"/>
     </row>
     <row r="174" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B174" s="343" t="s">
+      <c r="B174" s="349" t="s">
         <v>391</v>
       </c>
-      <c r="C174" s="343"/>
-      <c r="D174" s="343"/>
-      <c r="E174" s="343"/>
-      <c r="F174" s="343"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="2:6">
       <c r="B176" s="1" t="s">
@@ -5539,6 +5539,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B173:F173"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B170:F170"/>
+    <mergeCell ref="B164:F164"/>
+    <mergeCell ref="B69:F69"/>
+    <mergeCell ref="B113:F113"/>
+    <mergeCell ref="B78:F78"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B90:F90"/>
     <mergeCell ref="B129:F129"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="B18:F18"/>
@@ -5555,17 +5566,6 @@
     <mergeCell ref="B55:F55"/>
     <mergeCell ref="B59:F59"/>
     <mergeCell ref="B68:F68"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B173:F173"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B170:F170"/>
-    <mergeCell ref="B164:F164"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62BF434F-99E4-46D2-A0A1-C9954A88D0C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5BB88E-4386-4200-8868-5BA3E78E159D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
-    <definedName name="Reporting_currency">Thesis!$C$22</definedName>
+    <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
     <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
   </definedNames>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="453">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1370,10 +1370,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Target Annual Return:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Target Annual Return =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1411,18 +1407,6 @@
   </si>
   <si>
     <t>Other Non-Operating Assets per share =</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Base Cost of Equity</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Management Risk Premium</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Business Model Risk Premium</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1519,10 +1503,6 @@
   </si>
   <si>
     <t>Report Interval:</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>assuming a holding period of</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2337,9 +2317,6 @@
     <t>Target Return</t>
   </si>
   <si>
-    <t>in contrast to a position yield of</t>
-  </si>
-  <si>
     <t>Result (Target)</t>
   </si>
   <si>
@@ -2382,13 +2359,61 @@
     <t>@Benchmark Yield</t>
   </si>
   <si>
-    <t>in contrast to a benchmark yield of</t>
-  </si>
-  <si>
     <t>Exit Price Output</t>
   </si>
   <si>
     <t>Benchmark Yield</t>
+  </si>
+  <si>
+    <t>Target return</t>
+  </si>
+  <si>
+    <t>Target Price</t>
+  </si>
+  <si>
+    <t>Entry Price</t>
+  </si>
+  <si>
+    <t>Sell Price</t>
+  </si>
+  <si>
+    <t>Exit Price</t>
+  </si>
+  <si>
+    <t>Holding Period</t>
+  </si>
+  <si>
+    <t>Risk Premium</t>
+  </si>
+  <si>
+    <t>Base Cost of Equity</t>
+  </si>
+  <si>
+    <t>Result (Exit)</t>
+  </si>
+  <si>
+    <t>Valuation Outputs</t>
+  </si>
+  <si>
+    <t>Business Model Risk Premium:</t>
+  </si>
+  <si>
+    <t>Management Risk Premium:</t>
+  </si>
+  <si>
+    <t>Base equity cost</t>
+  </si>
+  <si>
+    <t>Entry yield</t>
+  </si>
+  <si>
+    <t>Benchmark yield</t>
+  </si>
+  <si>
+    <t>DCF</t>
+  </si>
+  <si>
+    <t>Valuation Method</t>
   </si>
   <si>
     <t>N</t>
@@ -3086,7 +3111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="355">
+  <cellXfs count="358">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3600,14 +3625,8 @@
     </xf>
     <xf numFmtId="0" fontId="44" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="10" fontId="8" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3665,9 +3684,6 @@
     <xf numFmtId="179" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3675,7 +3691,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3767,9 +3782,6 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="175" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3784,9 +3796,6 @@
     </xf>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="180" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3794,6 +3803,33 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="4" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="40" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -4106,10 +4142,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J187"/>
+  <dimension ref="A1:J192"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.59765625" style="1" customWidth="1"/>
     <col min="3" max="4" width="25.59765625" style="1" customWidth="1"/>
     <col min="5" max="6" width="15.59765625" style="1" customWidth="1"/>
@@ -4124,11 +4160,11 @@
         <v>45780</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="331" t="s">
-        <v>361</v>
-      </c>
-      <c r="F1" s="284" t="s">
-        <v>435</v>
+      <c r="E1" s="326" t="s">
+        <v>356</v>
+      </c>
+      <c r="F1" s="281" t="s">
+        <v>445</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4147,7 +4183,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4156,10 +4192,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="C5" s="333" t="s">
-        <v>436</v>
+        <v>318</v>
+      </c>
+      <c r="C5" s="328" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4173,9 +4209,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C7" s="279">
+        <v>310</v>
+      </c>
+      <c r="C7" s="277">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4196,20 +4232,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>437</v>
+        <v>447</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>438</v>
+        <v>448</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4225,17 +4261,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4249,14 +4285,14 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="C15" s="32" t="str">
-        <f>IF(C22=C13,C13,C22&amp;"/"&amp;C13)</f>
+        <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
         <v>CNY</v>
       </c>
       <c r="D15" s="32" t="str">
-        <f>IF(D11="","",IF(C22=D13,D13,C22&amp;"/"&amp;D13))</f>
+        <f>IF(D11="","",IF(C25=D13,D13,C25&amp;"/"&amp;D13))</f>
         <v/>
       </c>
       <c r="E15" s="5"/>
@@ -4271,29 +4307,29 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B18" s="343" t="s">
-        <v>367</v>
-      </c>
-      <c r="C18" s="343"/>
-      <c r="D18" s="343"/>
-      <c r="E18" s="343"/>
-      <c r="F18" s="343"/>
-    </row>
-    <row r="20" spans="1:6">
+    <row r="18" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B18" s="346" t="s">
+        <v>362</v>
+      </c>
+      <c r="C18" s="346"/>
+      <c r="D18" s="346"/>
+      <c r="E18" s="346"/>
+      <c r="F18" s="346"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
@@ -4301,286 +4337,338 @@
       </c>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:6">
-      <c r="B22" s="4" t="s">
-        <v>355</v>
+    <row r="22" spans="2:6">
+      <c r="B22" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>424</v>
-      </c>
-      <c r="D22" s="32" t="str">
+        <v>449</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="E22" s="345" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="C23" s="291" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="C24" s="291" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="C25" s="48" t="s">
+        <v>418</v>
+      </c>
+      <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E22" s="341" t="str">
+      <c r="E25" s="335" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:6">
-      <c r="B23" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="48" t="s">
-        <v>439</v>
-      </c>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="B24" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="C24" s="249">
-        <v>0.4</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>417</v>
-      </c>
-      <c r="E24" s="339">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="B25" s="2" t="str">
-        <f>"Target Buy Price ("&amp;Market_currency&amp;"):"</f>
-        <v>Target Buy Price (CNY):</v>
-      </c>
-      <c r="C25" s="252">
-        <f>C139</f>
-        <v>28.081736799883384</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="E25" s="330">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="B26" s="1" t="s">
-        <v>407</v>
-      </c>
-      <c r="C26" s="280">
+    <row r="26" spans="2:6">
+      <c r="B26" s="1" t="str">
+        <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
+        <v>Expected Equity Value (CNY) :</v>
+      </c>
+      <c r="C26" s="341">
+        <f>C127</f>
+        <v>66.592285778879997</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E26" s="337">
         <f ca="1">Scenarios!C87</f>
         <v>9.4210132770872423E-2</v>
       </c>
-      <c r="D26" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="E26" s="339">
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:6" ht="13.9">
-      <c r="A28" s="247" t="s">
-        <v>362</v>
-      </c>
-      <c r="B28" s="36"/>
-      <c r="C28" s="36"/>
-      <c r="D28" s="36"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="36"/>
-    </row>
-    <row r="30" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B30" s="343" t="s">
-        <v>368</v>
-      </c>
-      <c r="C30" s="343"/>
-      <c r="D30" s="343"/>
-      <c r="E30" s="343"/>
-      <c r="F30" s="343"/>
-    </row>
-    <row r="31" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B31" s="345" t="s">
-        <v>347</v>
-      </c>
-      <c r="C31" s="345"/>
-      <c r="D31" s="345"/>
-      <c r="E31" s="345"/>
-      <c r="F31" s="345"/>
-    </row>
-    <row r="33" spans="2:6">
-      <c r="B33" s="234" t="s">
+    <row r="28" spans="2:6">
+      <c r="B28" s="45" t="s">
+        <v>437</v>
+      </c>
+      <c r="C28" s="268" t="str">
+        <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
+        <v>600132.SS (CNY)</v>
+      </c>
+      <c r="D28" s="268" t="str">
+        <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
+        <v/>
+      </c>
+      <c r="E28" s="342" t="s">
+        <v>433</v>
+      </c>
+      <c r="F28" s="340">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="C29" s="339">
+        <f>C144</f>
+        <v>28.081736799883384</v>
+      </c>
+      <c r="D29" s="339" t="str">
+        <f>D144</f>
+        <v/>
+      </c>
+      <c r="E29" s="343" t="s">
+        <v>428</v>
+      </c>
+      <c r="F29" s="338">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C30" s="148">
+        <f>C152</f>
+        <v>43.592757973888887</v>
+      </c>
+      <c r="D30" s="148" t="str">
+        <f>D152</f>
+        <v/>
+      </c>
+      <c r="E30" s="344" t="s">
+        <v>441</v>
+      </c>
+      <c r="F30" s="307">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="C31" s="148">
+        <f>C160</f>
+        <v>59.048136223898794</v>
+      </c>
+      <c r="D31" s="148" t="str">
+        <f>D160</f>
+        <v/>
+      </c>
+      <c r="E31" s="344" t="s">
+        <v>440</v>
+      </c>
+      <c r="F31" s="307">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
+      <c r="B32" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="C32" s="148">
+        <f>C168</f>
+        <v>53.520960428876833</v>
+      </c>
+      <c r="D32" s="148" t="str">
+        <f>D168</f>
+        <v/>
+      </c>
+      <c r="E32" s="344" t="s">
+        <v>442</v>
+      </c>
+      <c r="F32" s="307">
+        <v>0.1174</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+    </row>
+    <row r="34" spans="1:6" ht="13.9">
+      <c r="A34" s="247" t="s">
+        <v>357</v>
+      </c>
+      <c r="B34" s="36"/>
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+    </row>
+    <row r="36" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B36" s="346" t="s">
+        <v>363</v>
+      </c>
+      <c r="C36" s="346"/>
+      <c r="D36" s="346"/>
+      <c r="E36" s="346"/>
+      <c r="F36" s="346"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B37" s="348" t="s">
+        <v>342</v>
+      </c>
+      <c r="C37" s="348"/>
+      <c r="D37" s="348"/>
+      <c r="E37" s="348"/>
+      <c r="F37" s="348"/>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="B39" s="234" t="s">
         <v>231</v>
       </c>
-      <c r="C33" s="108">
+      <c r="C39" s="108">
         <f>scaling_factor</f>
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B34" s="344" t="s">
+    <row r="40" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B40" s="347" t="s">
         <v>232</v>
       </c>
-      <c r="C34" s="344"/>
-      <c r="D34" s="344"/>
-      <c r="E34" s="344"/>
-      <c r="F34" s="344"/>
-    </row>
-    <row r="35" spans="2:6">
-      <c r="B35" s="47" t="s">
+      <c r="C40" s="347"/>
+      <c r="D40" s="347"/>
+      <c r="E40" s="347"/>
+      <c r="F40" s="347"/>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C35" s="188">
+      <c r="C41" s="188">
         <f>Normalized_FCF!C8</f>
         <v>3123489756.696907</v>
       </c>
-      <c r="D35" s="1" t="str">
+      <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="36" spans="2:6">
-      <c r="B36" s="47"/>
-      <c r="C36" s="76"/>
-    </row>
-    <row r="37" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B37" s="344" t="s">
+    <row r="42" spans="1:6">
+      <c r="B42" s="47"/>
+      <c r="C42" s="76"/>
+    </row>
+    <row r="43" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B43" s="347" t="s">
         <v>234</v>
       </c>
-      <c r="C37" s="344"/>
-      <c r="D37" s="344"/>
-      <c r="E37" s="344"/>
-      <c r="F37" s="344"/>
-    </row>
-    <row r="38" spans="2:6">
-      <c r="B38" s="47" t="s">
+      <c r="C43" s="347"/>
+      <c r="D43" s="347"/>
+      <c r="E43" s="347"/>
+      <c r="F43" s="347"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C38" s="188">
+      <c r="C44" s="188">
         <f>Normalized_FCF!C9</f>
         <v>575917865</v>
       </c>
-      <c r="D38" s="1" t="str">
+      <c r="D44" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="39" spans="2:6">
-      <c r="B39" s="52" t="s">
+    <row r="45" spans="1:6">
+      <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C39" s="188">
+      <c r="C45" s="188">
         <f>Normalized_FCF!C10</f>
         <v>-575917865</v>
-      </c>
-      <c r="D39" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="41" spans="2:6">
-      <c r="B41" s="344" t="s">
-        <v>237</v>
-      </c>
-      <c r="C41" s="344"/>
-      <c r="D41" s="344"/>
-      <c r="E41" s="344"/>
-      <c r="F41" s="344"/>
-    </row>
-    <row r="42" spans="2:6">
-      <c r="B42" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="C42" s="188">
-        <f>Normalized_FCF!C11</f>
-        <v>0</v>
-      </c>
-      <c r="D42" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6">
-      <c r="B44" s="344" t="s">
-        <v>241</v>
-      </c>
-      <c r="C44" s="344"/>
-      <c r="D44" s="344"/>
-      <c r="E44" s="344"/>
-      <c r="F44" s="344"/>
-    </row>
-    <row r="45" spans="2:6">
-      <c r="B45" s="47" t="s">
-        <v>348</v>
-      </c>
-      <c r="C45" s="322">
-        <f>Normalized_FCF!C48</f>
-        <v>38554805.997018404</v>
       </c>
       <c r="D45" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E45" s="321"/>
-      <c r="F45" s="321"/>
-    </row>
-    <row r="46" spans="2:6">
-      <c r="B46" s="47" t="s">
-        <v>349</v>
-      </c>
-      <c r="C46" s="322">
+    </row>
+    <row r="47" spans="1:6">
+      <c r="B47" s="347" t="s">
+        <v>237</v>
+      </c>
+      <c r="C47" s="347"/>
+      <c r="D47" s="347"/>
+      <c r="E47" s="347"/>
+      <c r="F47" s="347"/>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="B48" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="C48" s="188">
+        <f>Normalized_FCF!C11</f>
+        <v>0</v>
+      </c>
+      <c r="D48" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="347" t="s">
+        <v>241</v>
+      </c>
+      <c r="C50" s="347"/>
+      <c r="D50" s="347"/>
+      <c r="E50" s="347"/>
+      <c r="F50" s="347"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="47" t="s">
+        <v>343</v>
+      </c>
+      <c r="C51" s="318">
+        <f>Normalized_FCF!C48</f>
+        <v>38554805.997018404</v>
+      </c>
+      <c r="D51" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E51" s="317"/>
+      <c r="F51" s="317"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="47" t="s">
+        <v>344</v>
+      </c>
+      <c r="C52" s="318">
         <f>Normalized_FCF!C47</f>
         <v>-7672861</v>
       </c>
-      <c r="D46" s="1" t="str">
+      <c r="D52" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E46" s="321"/>
-      <c r="F46" s="321"/>
-    </row>
-    <row r="47" spans="2:6">
-      <c r="B47" s="47" t="s">
+      <c r="E52" s="317"/>
+      <c r="F52" s="317"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C47" s="188">
+      <c r="C53" s="188">
         <f>Normalized_FCF!C12</f>
         <v>30881944.997018404</v>
-      </c>
-      <c r="D47" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="49" spans="2:6">
-      <c r="B49" s="1" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="47" t="s">
-        <v>266</v>
-      </c>
-      <c r="C50" s="188">
-        <f>Normalized_FCF!C15</f>
-        <v>-141879704.29826272</v>
-      </c>
-      <c r="D50" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="52" spans="2:6">
-      <c r="B52" s="344" t="s">
-        <v>242</v>
-      </c>
-      <c r="C52" s="344"/>
-      <c r="D52" s="344"/>
-      <c r="E52" s="344"/>
-      <c r="F52" s="344"/>
-    </row>
-    <row r="53" spans="2:6">
-      <c r="B53" s="47" t="s">
-        <v>240</v>
-      </c>
-      <c r="C53" s="188">
-        <f>Normalized_FCF!C14</f>
-        <v>-788592925.42348135</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4588,1080 +4676,1109 @@
       </c>
     </row>
     <row r="55" spans="2:6">
-      <c r="B55" s="344" t="s">
-        <v>346</v>
-      </c>
-      <c r="C55" s="347"/>
-      <c r="D55" s="347"/>
-      <c r="E55" s="347"/>
-      <c r="F55" s="347"/>
+      <c r="B55" s="1" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
-        <v>243</v>
-      </c>
-      <c r="C56" s="1">
-        <f>Normalized_FCF!C17</f>
-        <v>0</v>
+        <v>266</v>
+      </c>
+      <c r="C56" s="188">
+        <f>Normalized_FCF!C15</f>
+        <v>-141879704.29826272</v>
       </c>
       <c r="D56" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B58" s="343" t="s">
-        <v>351</v>
-      </c>
-      <c r="C58" s="343"/>
-      <c r="D58" s="343"/>
-      <c r="E58" s="343"/>
-      <c r="F58" s="343"/>
-    </row>
-    <row r="59" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B59" s="343" t="s">
-        <v>369</v>
-      </c>
-      <c r="C59" s="343"/>
-      <c r="D59" s="343"/>
-      <c r="E59" s="343"/>
-      <c r="F59" s="343"/>
-    </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="47" t="s">
-        <v>271</v>
-      </c>
-      <c r="C61" s="188">
-        <f>Normalized_FCF!G19</f>
-        <v>2322754575.9970183</v>
-      </c>
-      <c r="D61" s="1" t="str">
+    <row r="58" spans="2:6">
+      <c r="B58" s="347" t="s">
+        <v>242</v>
+      </c>
+      <c r="C58" s="347"/>
+      <c r="D58" s="347"/>
+      <c r="E58" s="347"/>
+      <c r="F58" s="347"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="47" t="s">
+        <v>240</v>
+      </c>
+      <c r="C59" s="188">
+        <f>Normalized_FCF!C14</f>
+        <v>-788592925.42348135</v>
+      </c>
+      <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="347" t="s">
+        <v>341</v>
+      </c>
+      <c r="C61" s="350"/>
+      <c r="D61" s="350"/>
+      <c r="E61" s="350"/>
+      <c r="F61" s="350"/>
+    </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
-        <v>249</v>
-      </c>
-      <c r="C62" s="188">
-        <f>Normalized_FCF!C19</f>
-        <v>2223899071.9721813</v>
+        <v>243</v>
+      </c>
+      <c r="C62" s="1">
+        <f>Normalized_FCF!C17</f>
+        <v>0</v>
       </c>
       <c r="D62" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="63" spans="2:6">
-      <c r="B63" s="254" t="s">
-        <v>398</v>
-      </c>
-      <c r="C63" s="92">
+    <row r="64" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B64" s="346" t="s">
+        <v>346</v>
+      </c>
+      <c r="C64" s="346"/>
+      <c r="D64" s="346"/>
+      <c r="E64" s="346"/>
+      <c r="F64" s="346"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B65" s="346" t="s">
+        <v>364</v>
+      </c>
+      <c r="C65" s="346"/>
+      <c r="D65" s="346"/>
+      <c r="E65" s="346"/>
+      <c r="F65" s="346"/>
+    </row>
+    <row r="67" spans="1:6">
+      <c r="B67" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C67" s="188">
+        <f>Normalized_FCF!G19</f>
+        <v>2322754575.9970183</v>
+      </c>
+      <c r="D67" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
+      <c r="B68" s="47" t="s">
+        <v>249</v>
+      </c>
+      <c r="C68" s="188">
+        <f>Normalized_FCF!C19</f>
+        <v>2223899071.9721813</v>
+      </c>
+      <c r="D68" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
+      <c r="B69" s="252" t="s">
+        <v>393</v>
+      </c>
+      <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
         <v>8.081439043489845E-2</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
-      <c r="B64" s="254" t="s">
-        <v>316</v>
-      </c>
-      <c r="C64" s="92">
+    <row r="70" spans="1:6">
+      <c r="B70" s="252" t="s">
+        <v>311</v>
+      </c>
+      <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
         <v>4.2208934224410834E-2</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="13.9">
-      <c r="A66" s="247" t="s">
-        <v>363</v>
-      </c>
-      <c r="B66" s="36"/>
-      <c r="C66" s="36"/>
-      <c r="D66" s="36"/>
-      <c r="E66" s="36"/>
-      <c r="F66" s="36"/>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67" s="233"/>
-    </row>
-    <row r="68" spans="1:6" ht="24.4" customHeight="1">
-      <c r="A68" s="17"/>
-      <c r="B68" s="343" t="s">
-        <v>370</v>
-      </c>
-      <c r="C68" s="343"/>
-      <c r="D68" s="343"/>
-      <c r="E68" s="343"/>
-      <c r="F68" s="343"/>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="B69" s="345" t="s">
+    <row r="72" spans="1:6" ht="13.9">
+      <c r="A72" s="247" t="s">
+        <v>358</v>
+      </c>
+      <c r="B72" s="36"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="36"/>
+    </row>
+    <row r="73" spans="1:6">
+      <c r="A73" s="233"/>
+    </row>
+    <row r="74" spans="1:6" ht="24.4" customHeight="1">
+      <c r="A74" s="17"/>
+      <c r="B74" s="346" t="s">
+        <v>365</v>
+      </c>
+      <c r="C74" s="346"/>
+      <c r="D74" s="346"/>
+      <c r="E74" s="346"/>
+      <c r="F74" s="346"/>
+    </row>
+    <row r="75" spans="1:6">
+      <c r="B75" s="348" t="s">
         <v>253</v>
       </c>
-      <c r="C69" s="345"/>
-      <c r="D69" s="345"/>
-      <c r="E69" s="345"/>
-      <c r="F69" s="345"/>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="B71" s="234" t="s">
+      <c r="C75" s="348"/>
+      <c r="D75" s="348"/>
+      <c r="E75" s="348"/>
+      <c r="F75" s="348"/>
+    </row>
+    <row r="77" spans="1:6">
+      <c r="B77" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
-      <c r="B72" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C72" s="311">
+    <row r="78" spans="1:6">
+      <c r="B78" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C78" s="92">
+        <f>F31</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
-      <c r="B73" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="C73" s="263">
-        <f>IF(D73="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D73" s="286" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="B74" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C74" s="263">
-        <f>IF(D74="Y",1%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="D74" s="286" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="B75" s="80" t="s">
+    <row r="79" spans="1:6">
+      <c r="B79" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="C79" s="92">
+        <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
+      <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C75" s="263">
-        <f>SUM(C72:C74)</f>
+      <c r="C80" s="261">
+        <f>F31+C79</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
-      <c r="C76" s="122"/>
-    </row>
-    <row r="77" spans="1:6">
-      <c r="B77" s="332" t="s">
-        <v>364</v>
-      </c>
-      <c r="C77" s="122"/>
-    </row>
-    <row r="78" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B78" s="343" t="s">
-        <v>371</v>
-      </c>
-      <c r="C78" s="343"/>
-      <c r="D78" s="343"/>
-      <c r="E78" s="343"/>
-      <c r="F78" s="343"/>
-    </row>
-    <row r="79" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B79" s="343" t="s">
-        <v>372</v>
-      </c>
-      <c r="C79" s="343"/>
-      <c r="D79" s="343"/>
-      <c r="E79" s="343"/>
-      <c r="F79" s="343"/>
-    </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="47" t="s">
+      <c r="C81" s="122"/>
+    </row>
+    <row r="82" spans="1:6">
+      <c r="B82" s="327" t="s">
+        <v>359</v>
+      </c>
+      <c r="C82" s="122"/>
+    </row>
+    <row r="83" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B83" s="346" t="s">
+        <v>366</v>
+      </c>
+      <c r="C83" s="346"/>
+      <c r="D83" s="346"/>
+      <c r="E83" s="346"/>
+      <c r="F83" s="346"/>
+    </row>
+    <row r="84" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B84" s="346" t="s">
+        <v>367</v>
+      </c>
+      <c r="C84" s="346"/>
+      <c r="D84" s="346"/>
+      <c r="E84" s="346"/>
+      <c r="F84" s="346"/>
+    </row>
+    <row r="86" spans="1:6">
+      <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="263">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6">
-      <c r="B82" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C82" s="248">
+      <c r="C86" s="261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
+      <c r="B87" s="47" t="s">
+        <v>283</v>
+      </c>
+      <c r="C87" s="248">
         <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>57.438828001604072</v>
       </c>
-      <c r="D82" s="1" t="str">
+      <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="84" spans="1:6" ht="13.9">
-      <c r="A84" s="247" t="s">
-        <v>365</v>
-      </c>
-      <c r="B84" s="36"/>
-      <c r="C84" s="36"/>
-      <c r="D84" s="36"/>
-      <c r="E84" s="36"/>
-      <c r="F84" s="36"/>
-    </row>
-    <row r="85" spans="1:6">
-      <c r="A85" s="233"/>
-    </row>
-    <row r="86" spans="1:6">
-      <c r="B86" s="343" t="s">
-        <v>373</v>
-      </c>
-      <c r="C86" s="343"/>
-      <c r="D86" s="343"/>
-      <c r="E86" s="343"/>
-      <c r="F86" s="343"/>
-    </row>
-    <row r="87" spans="1:6">
-      <c r="B87" s="1" t="s">
+    <row r="89" spans="1:6" ht="13.9">
+      <c r="A89" s="247" t="s">
+        <v>360</v>
+      </c>
+      <c r="B89" s="36"/>
+      <c r="C89" s="36"/>
+      <c r="D89" s="36"/>
+      <c r="E89" s="36"/>
+      <c r="F89" s="36"/>
+    </row>
+    <row r="90" spans="1:6">
+      <c r="A90" s="233"/>
+    </row>
+    <row r="91" spans="1:6">
+      <c r="B91" s="346" t="s">
+        <v>368</v>
+      </c>
+      <c r="C91" s="346"/>
+      <c r="D91" s="346"/>
+      <c r="E91" s="346"/>
+      <c r="F91" s="346"/>
+    </row>
+    <row r="92" spans="1:6">
+      <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="89" spans="1:6">
-      <c r="B89" s="234" t="s">
+    <row r="94" spans="1:6">
+      <c r="B94" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="90" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B90" s="343" t="s">
-        <v>352</v>
-      </c>
-      <c r="C90" s="343"/>
-      <c r="D90" s="343"/>
-      <c r="E90" s="343"/>
-      <c r="F90" s="343"/>
-    </row>
-    <row r="91" spans="1:6">
-      <c r="B91" s="47" t="s">
+    <row r="95" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B95" s="346" t="s">
+        <v>347</v>
+      </c>
+      <c r="C95" s="346"/>
+      <c r="D95" s="346"/>
+      <c r="E95" s="346"/>
+      <c r="F95" s="346"/>
+    </row>
+    <row r="96" spans="1:6">
+      <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C91" s="188">
+      <c r="C96" s="188">
         <f>Valuation_Model!C7</f>
         <v>123521704.27</v>
       </c>
-      <c r="D91" s="1" t="str">
+      <c r="D96" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="92" spans="1:6">
-      <c r="B92" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C92" s="248">
-        <f>C91*scaling_factor*Exchange_Rate/Common_Shares</f>
+    <row r="97" spans="2:6">
+      <c r="B97" s="47" t="s">
+        <v>284</v>
+      </c>
+      <c r="C97" s="248">
+        <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0.25522532080514426</v>
       </c>
-      <c r="D92" s="1" t="str">
+      <c r="D97" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
-      <c r="B93" s="336" t="s">
-        <v>412</v>
-      </c>
-      <c r="C93" s="337">
+    <row r="98" spans="2:6">
+      <c r="B98" s="331" t="s">
+        <v>407</v>
+      </c>
+      <c r="C98" s="332">
         <f>BS!G30/BS!G27</f>
         <v>3.4701988818540461</v>
       </c>
     </row>
-    <row r="94" spans="1:6">
-      <c r="B94" s="336" t="s">
-        <v>413</v>
-      </c>
-      <c r="C94" s="337">
+    <row r="99" spans="2:6">
+      <c r="B99" s="331" t="s">
+        <v>408</v>
+      </c>
+      <c r="C99" s="332">
         <f>BS!G31/BS!G27</f>
         <v>5.0341856510546588E-2</v>
       </c>
     </row>
-    <row r="95" spans="1:6">
-      <c r="B95" s="336" t="s">
-        <v>415</v>
-      </c>
-      <c r="C95" s="338">
+    <row r="100" spans="2:6">
+      <c r="B100" s="331" t="s">
+        <v>410</v>
+      </c>
+      <c r="C100" s="333">
         <f>BS!C50</f>
         <v>3.9546057100127742E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:6">
-      <c r="B97" s="1" t="s">
+    <row r="102" spans="2:6">
+      <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="98" spans="1:6">
-      <c r="B98" s="47" t="s">
+    <row r="103" spans="2:6">
+      <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C98" s="188">
+      <c r="C103" s="188">
         <f>BS!C66</f>
         <v>1081659074.0699999</v>
-      </c>
-      <c r="D98" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6">
-      <c r="B99" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="C99" s="188">
-        <f>Valuation_Model!C8</f>
-        <v>65618450.04890883</v>
-      </c>
-      <c r="D99" s="1" t="str">
-        <f>Reporting_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6">
-      <c r="B100" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C100" s="248">
-        <f>C99*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.13558337834994227</v>
-      </c>
-      <c r="D100" s="1" t="str">
-        <f>Market_currency</f>
-        <v>CNY</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6">
-      <c r="B102" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6">
-      <c r="B103" s="47" t="s">
-        <v>258</v>
-      </c>
-      <c r="C103" s="188">
-        <f>Valuation_Model!C9</f>
-        <v>29558000.651999995</v>
       </c>
       <c r="D103" s="1" t="str">
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="1:6">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
-        <v>287</v>
-      </c>
-      <c r="C104" s="248">
-        <f>C103*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>6.1073883681813636E-2</v>
+        <v>267</v>
+      </c>
+      <c r="C104" s="188">
+        <f>Valuation_Model!C8</f>
+        <v>65618450.04890883</v>
       </c>
       <c r="D104" s="1" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="105" spans="2:6">
+      <c r="B105" s="47" t="s">
+        <v>285</v>
+      </c>
+      <c r="C105" s="248">
+        <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>0.13558337834994227</v>
+      </c>
+      <c r="D105" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="106" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B106" s="343" t="s">
-        <v>374</v>
-      </c>
-      <c r="C106" s="343"/>
-      <c r="D106" s="343"/>
-      <c r="E106" s="343"/>
-      <c r="F106" s="343"/>
-    </row>
-    <row r="108" spans="1:6">
+    <row r="107" spans="2:6">
+      <c r="B107" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C108" s="248">
-        <f>Valuation_Model!C12</f>
-        <v>57.380259942830683</v>
+        <v>258</v>
+      </c>
+      <c r="C108" s="188">
+        <f>Valuation_Model!C9</f>
+        <v>29558000.651999995</v>
       </c>
       <c r="D108" s="1" t="str">
-        <f>Market_currency</f>
+        <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="1:6">
-      <c r="B109" s="336" t="s">
-        <v>414</v>
+    <row r="109" spans="2:6">
+      <c r="B109" s="47" t="s">
+        <v>286</v>
       </c>
       <c r="C109" s="248">
-        <f>BS!D47</f>
-        <v>-13.312996389940134</v>
+        <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <v>6.1073883681813636E-2</v>
       </c>
       <c r="D109" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="111" spans="1:6" ht="13.9">
-      <c r="A111" s="247" t="s">
-        <v>366</v>
-      </c>
-      <c r="B111" s="36"/>
-      <c r="C111" s="36"/>
-      <c r="D111" s="36"/>
-      <c r="E111" s="36"/>
-      <c r="F111" s="36"/>
-    </row>
-    <row r="113" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B113" s="344" t="s">
-        <v>375</v>
-      </c>
-      <c r="C113" s="344"/>
-      <c r="D113" s="344"/>
-      <c r="E113" s="344"/>
-      <c r="F113" s="344"/>
-    </row>
-    <row r="115" spans="1:6" ht="12.4">
-      <c r="B115" s="260" t="s">
+    <row r="111" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B111" s="346" t="s">
+        <v>369</v>
+      </c>
+      <c r="C111" s="346"/>
+      <c r="D111" s="346"/>
+      <c r="E111" s="346"/>
+      <c r="F111" s="346"/>
+    </row>
+    <row r="113" spans="1:6">
+      <c r="B113" s="47" t="s">
+        <v>282</v>
+      </c>
+      <c r="C113" s="248">
+        <f>Valuation_Model!C12</f>
+        <v>57.380259942830683</v>
+      </c>
+      <c r="D113" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
+      <c r="B114" s="331" t="s">
+        <v>409</v>
+      </c>
+      <c r="C114" s="248">
+        <f>BS!D47</f>
+        <v>-13.312996389940134</v>
+      </c>
+      <c r="D114" s="1" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" ht="13.9">
+      <c r="A116" s="247" t="s">
+        <v>361</v>
+      </c>
+      <c r="B116" s="36"/>
+      <c r="C116" s="36"/>
+      <c r="D116" s="36"/>
+      <c r="E116" s="36"/>
+      <c r="F116" s="36"/>
+    </row>
+    <row r="118" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B118" s="347" t="s">
+        <v>370</v>
+      </c>
+      <c r="C118" s="347"/>
+      <c r="D118" s="347"/>
+      <c r="E118" s="347"/>
+      <c r="F118" s="347"/>
+    </row>
+    <row r="120" spans="1:6" ht="12.4">
+      <c r="B120" s="258" t="s">
         <v>118</v>
       </c>
-      <c r="C115" s="260" t="s">
+      <c r="C120" s="258" t="s">
         <v>133</v>
       </c>
-      <c r="D115" s="260" t="s">
+      <c r="D120" s="258" t="s">
         <v>113</v>
       </c>
-      <c r="E115" s="260" t="s">
+      <c r="E120" s="258" t="s">
         <v>260</v>
       </c>
-      <c r="F115" s="260" t="s">
+      <c r="F120" s="258" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="116" spans="1:6">
-      <c r="B116" s="255" t="str">
+    <row r="121" spans="1:6">
+      <c r="B121" s="253" t="str">
         <f>Valuation_Model!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C116" s="256">
+      <c r="C121" s="254">
         <f>Valuation_Model!C74</f>
         <v>0.1</v>
       </c>
-      <c r="D116" s="257">
+      <c r="D121" s="255">
         <f>Valuation_Model!D74</f>
         <v>15</v>
       </c>
-      <c r="E116" s="258" t="str">
+      <c r="E121" s="256" t="str">
         <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
         <v>99.94 CNY</v>
       </c>
-      <c r="F116" s="259">
+      <c r="F121" s="257">
         <f>Valuation_Model!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="117" spans="1:6">
-      <c r="B117" s="242" t="str">
+    <row r="122" spans="1:6">
+      <c r="B122" s="242" t="str">
         <f>Valuation_Model!B75</f>
         <v>Optimistic</v>
       </c>
-      <c r="C117" s="243">
+      <c r="C122" s="243">
         <f>Valuation_Model!C75</f>
         <v>0.06</v>
       </c>
-      <c r="D117" s="244">
+      <c r="D122" s="244">
         <f>Valuation_Model!D75</f>
         <v>10</v>
       </c>
-      <c r="E117" s="245" t="str">
+      <c r="E122" s="245" t="str">
         <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
         <v>69.66 CNY</v>
       </c>
-      <c r="F117" s="246">
+      <c r="F122" s="246">
         <f>Valuation_Model!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="118" spans="1:6">
-      <c r="B118" s="242" t="str">
+    <row r="123" spans="1:6">
+      <c r="B123" s="242" t="str">
         <f>Valuation_Model!B76</f>
         <v>Base</v>
       </c>
-      <c r="C118" s="243">
+      <c r="C123" s="243">
         <f>Valuation_Model!C76</f>
         <v>0.04</v>
       </c>
-      <c r="D118" s="244">
+      <c r="D123" s="244">
         <f>Valuation_Model!D76</f>
         <v>10</v>
       </c>
-      <c r="E118" s="245" t="str">
+      <c r="E123" s="245" t="str">
         <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
         <v>65.17 CNY</v>
       </c>
-      <c r="F118" s="246">
+      <c r="F123" s="246">
         <f>Valuation_Model!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
-      <c r="B119" s="242" t="str">
+    <row r="124" spans="1:6">
+      <c r="B124" s="242" t="str">
         <f>Valuation_Model!B77</f>
         <v>Pessimistic</v>
       </c>
-      <c r="C119" s="243">
+      <c r="C124" s="243">
         <f>Valuation_Model!C77</f>
         <v>0.02</v>
       </c>
-      <c r="D119" s="244">
+      <c r="D124" s="244">
         <f>Valuation_Model!D77</f>
         <v>10</v>
       </c>
-      <c r="E119" s="245" t="str">
+      <c r="E124" s="245" t="str">
         <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
         <v>61.09 CNY</v>
       </c>
-      <c r="F119" s="246">
+      <c r="F124" s="246">
         <f>Valuation_Model!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="120" spans="1:6">
-      <c r="B120" s="242" t="str">
+    <row r="125" spans="1:6">
+      <c r="B125" s="242" t="str">
         <f>Valuation_Model!B78</f>
         <v>Devil's advocate</v>
       </c>
-      <c r="C120" s="243">
+      <c r="C125" s="243">
         <f>Valuation_Model!C78</f>
         <v>0</v>
       </c>
-      <c r="D120" s="244">
+      <c r="D125" s="244">
         <f>Valuation_Model!D78</f>
         <v>15</v>
       </c>
-      <c r="E120" s="245" t="str">
+      <c r="E125" s="245" t="str">
         <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
         <v>57.38 CNY</v>
       </c>
-      <c r="F120" s="246">
+      <c r="F125" s="246">
         <f>Valuation_Model!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="122" spans="1:6">
-      <c r="B122" s="235" t="s">
+    <row r="127" spans="1:6">
+      <c r="B127" s="235" t="s">
         <v>259</v>
       </c>
-      <c r="C122" s="241">
+      <c r="C127" s="241">
         <f>Scenarios!C60</f>
         <v>66.592285778879997</v>
       </c>
-      <c r="D122" s="236" t="str">
+      <c r="D127" s="236" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="124" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B124" s="348" t="s">
-        <v>378</v>
-      </c>
-      <c r="C124" s="348"/>
-      <c r="D124" s="348"/>
-      <c r="E124" s="348"/>
-      <c r="F124" s="348"/>
-    </row>
-    <row r="126" spans="1:6" ht="13.9">
-      <c r="A126" s="247" t="s">
-        <v>410</v>
-      </c>
-      <c r="B126" s="36"/>
-      <c r="C126" s="36"/>
-      <c r="D126" s="36"/>
-      <c r="E126" s="36"/>
-      <c r="F126" s="36"/>
-    </row>
-    <row r="128" spans="1:6">
-      <c r="B128" s="346" t="s">
-        <v>376</v>
-      </c>
-      <c r="C128" s="346"/>
-      <c r="D128" s="346"/>
-      <c r="E128" s="346"/>
-      <c r="F128" s="346"/>
-    </row>
-    <row r="129" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B129" s="343" t="s">
-        <v>377</v>
-      </c>
-      <c r="C129" s="343"/>
-      <c r="D129" s="343"/>
-      <c r="E129" s="343"/>
-      <c r="F129" s="343"/>
-    </row>
-    <row r="130" spans="2:6">
-      <c r="B130" s="234" t="s">
+    <row r="129" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B129" s="351" t="s">
+        <v>373</v>
+      </c>
+      <c r="C129" s="351"/>
+      <c r="D129" s="351"/>
+      <c r="E129" s="351"/>
+      <c r="F129" s="351"/>
+    </row>
+    <row r="131" spans="1:6" ht="13.9">
+      <c r="A131" s="247" t="s">
+        <v>405</v>
+      </c>
+      <c r="B131" s="36"/>
+      <c r="C131" s="36"/>
+      <c r="D131" s="36"/>
+      <c r="E131" s="36"/>
+      <c r="F131" s="36"/>
+    </row>
+    <row r="133" spans="1:6">
+      <c r="B133" s="349" t="s">
+        <v>371</v>
+      </c>
+      <c r="C133" s="349"/>
+      <c r="D133" s="349"/>
+      <c r="E133" s="349"/>
+      <c r="F133" s="349"/>
+    </row>
+    <row r="134" spans="1:6" ht="24.4" customHeight="1">
+      <c r="B134" s="346" t="s">
+        <v>372</v>
+      </c>
+      <c r="C134" s="346"/>
+      <c r="D134" s="346"/>
+      <c r="E134" s="346"/>
+      <c r="F134" s="346"/>
+    </row>
+    <row r="135" spans="1:6">
+      <c r="B135" s="234" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="131" spans="2:6">
-      <c r="B131" s="1" t="s">
+    <row r="136" spans="1:6">
+      <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C131" s="251">
-        <f>E25</f>
+      <c r="C136" s="250">
+        <f>F28</f>
         <v>3</v>
       </c>
     </row>
-    <row r="132" spans="2:6">
-      <c r="B132" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="C132" s="250">
-        <f>C24</f>
+    <row r="137" spans="1:6">
+      <c r="B137" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C137" s="249">
+        <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="133" spans="2:6">
-      <c r="B133" s="236" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="236" t="s">
         <v>262</v>
       </c>
-      <c r="C133" s="237">
+      <c r="C138" s="237">
         <f>Scenarios!C77</f>
         <v>2.4</v>
       </c>
-      <c r="D133" s="236" t="str">
+      <c r="D138" s="236" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="135" spans="2:6">
-      <c r="B135" s="234" t="s">
-        <v>418</v>
-      </c>
-      <c r="C135" s="270" t="str">
+    <row r="140" spans="1:6">
+      <c r="B140" s="234" t="s">
+        <v>412</v>
+      </c>
+      <c r="C140" s="268" t="str">
         <f>C11</f>
         <v>600132.SS</v>
       </c>
-      <c r="D135" s="270" t="str">
+      <c r="D140" s="268" t="str">
         <f>IF(D11="","",D11)</f>
         <v/>
       </c>
     </row>
-    <row r="136" spans="2:6">
-      <c r="B136" s="1" t="s">
-        <v>416</v>
-      </c>
-      <c r="C136" s="337">
-        <f>C24</f>
+    <row r="141" spans="1:6">
+      <c r="B141" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="C141" s="332">
+        <f>F29</f>
         <v>0.4</v>
       </c>
     </row>
-    <row r="137" spans="2:6">
-      <c r="B137" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="142" spans="1:6">
+      <c r="B142" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C137" s="240">
+      <c r="C142" s="240">
         <f>Scenarios!C81</f>
         <v>3.8134110787171998</v>
       </c>
     </row>
-    <row r="138" spans="2:6">
-      <c r="B138" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="143" spans="1:6">
+      <c r="B143" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C138" s="240">
+      <c r="C143" s="240">
         <f>Scenarios!C82</f>
         <v>24.268325721166185</v>
       </c>
     </row>
-    <row r="139" spans="2:6">
-      <c r="B139" s="80" t="s">
+    <row r="144" spans="1:6">
+      <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C139" s="239">
+      <c r="C144" s="239">
         <f>Scenarios!C83</f>
         <v>28.081736799883384</v>
       </c>
-      <c r="D139" s="342" t="str">
-        <f>IF($D$11="","",C139*$E$22)</f>
+      <c r="D144" s="336" t="str">
+        <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="140" spans="2:6">
-      <c r="B140" s="290" t="s">
-        <v>426</v>
-      </c>
-      <c r="C140" s="340" t="str">
+    <row r="145" spans="2:4">
+      <c r="B145" s="286" t="s">
+        <v>420</v>
+      </c>
+      <c r="C145" s="334" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D140" s="340" t="str">
+      <c r="D145" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="141" spans="2:6">
-      <c r="B141" s="238" t="s">
+    <row r="146" spans="2:4">
+      <c r="B146" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C141" s="92">
+      <c r="C146" s="92">
         <f>Scenarios!F83</f>
         <v>0.57830345555145946</v>
       </c>
     </row>
-    <row r="143" spans="2:6">
-      <c r="B143" s="234" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="144" spans="2:6">
-      <c r="B144" s="1" t="s">
-        <v>420</v>
-      </c>
-      <c r="C144" s="337">
+    <row r="148" spans="2:4">
+      <c r="B148" s="234" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4">
+      <c r="B149" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="C149" s="332">
         <f>Scenarios!C90</f>
         <v>0.2</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
-      <c r="B145" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="150" spans="2:4">
+      <c r="B150" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C145" s="240">
+      <c r="C150" s="240">
         <f>Scenarios!C91</f>
         <v>5.0555555555555554</v>
       </c>
     </row>
-    <row r="146" spans="2:4">
-      <c r="B146" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="151" spans="2:4">
+      <c r="B151" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C146" s="240">
+      <c r="C151" s="240">
         <f>Scenarios!C92</f>
         <v>38.537202418333329</v>
       </c>
     </row>
-    <row r="147" spans="2:4">
-      <c r="B147" s="80" t="s">
+    <row r="152" spans="2:4">
+      <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
-      <c r="C147" s="239">
+      <c r="C152" s="239">
         <f>Scenarios!C93</f>
         <v>43.592757973888887</v>
       </c>
-      <c r="D147" s="342" t="str">
-        <f>IF($D$11="","",C147*$E$22)</f>
+      <c r="D152" s="336" t="str">
+        <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="148" spans="2:4">
-      <c r="B148" s="290" t="s">
-        <v>426</v>
-      </c>
-      <c r="C148" s="340" t="str">
+    <row r="153" spans="2:4">
+      <c r="B153" s="286" t="s">
+        <v>420</v>
+      </c>
+      <c r="C153" s="334" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D148" s="340" t="str">
+      <c r="D153" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="149" spans="2:4">
-      <c r="B149" s="238" t="s">
+    <row r="154" spans="2:4">
+      <c r="B154" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C149" s="92">
+      <c r="C154" s="92">
         <f>Scenarios!F93</f>
         <v>0.345378260199104</v>
       </c>
     </row>
-    <row r="151" spans="2:4">
-      <c r="B151" s="234" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4">
-      <c r="B152" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="C152" s="92">
+    <row r="156" spans="2:4">
+      <c r="B156" s="234" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4">
+      <c r="B157" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="C157" s="92">
         <f>Scenarios!C96</f>
         <v>0.08</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
-      <c r="B153" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="158" spans="2:4">
+      <c r="B158" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C153" s="240">
+      <c r="C158" s="240">
         <f>Scenarios!C97</f>
         <v>6.1850327693949119</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
-      <c r="B154" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="159" spans="2:4">
+      <c r="B159" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C154" s="240">
+      <c r="C159" s="240">
         <f>Scenarios!C98</f>
         <v>52.863103454503879</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
-      <c r="B155" s="80" t="s">
-        <v>409</v>
-      </c>
-      <c r="C155" s="239">
+    <row r="160" spans="2:4">
+      <c r="B160" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="C160" s="239">
         <f>Scenarios!C99</f>
         <v>59.048136223898794</v>
       </c>
-      <c r="D155" s="342" t="str">
-        <f>IF($D$11="","",C155*$E$22)</f>
+      <c r="D160" s="336" t="str">
+        <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="156" spans="2:4">
-      <c r="B156" s="290" t="s">
-        <v>426</v>
-      </c>
-      <c r="C156" s="340" t="str">
+    <row r="161" spans="1:6">
+      <c r="B161" s="286" t="s">
+        <v>420</v>
+      </c>
+      <c r="C161" s="334" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D156" s="340" t="str">
+      <c r="D161" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="157" spans="2:4">
-      <c r="B157" s="238" t="s">
+    <row r="162" spans="1:6">
+      <c r="B162" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C157" s="92">
+      <c r="C162" s="92">
         <f>Scenarios!F99</f>
         <v>0.1132886409700905</v>
       </c>
     </row>
-    <row r="159" spans="2:4">
-      <c r="B159" s="234" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4">
-      <c r="B160" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="C160" s="92">
-        <f>E26</f>
+    <row r="164" spans="1:6">
+      <c r="B164" s="234" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
+      <c r="B165" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="C165" s="92">
+        <f>F32</f>
         <v>0.1174</v>
       </c>
     </row>
-    <row r="161" spans="1:6">
-      <c r="B161" s="236" t="str">
-        <f>"PV("&amp;C131&amp;" yrs of Dividends)"</f>
+    <row r="166" spans="1:6">
+      <c r="B166" s="236" t="str">
+        <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
-      <c r="C161" s="240">
+      <c r="C166" s="240">
         <f>Scenarios!C103</f>
         <v>5.7902475022527575</v>
       </c>
     </row>
-    <row r="162" spans="1:6">
-      <c r="B162" s="236" t="str">
-        <f>"+ PV(Equity Value realized at year "&amp;C131&amp;")"</f>
+    <row r="167" spans="1:6">
+      <c r="B167" s="236" t="str">
+        <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
-      <c r="C162" s="240">
+      <c r="C167" s="240">
         <f>Scenarios!C104</f>
         <v>47.730712926624079</v>
       </c>
     </row>
-    <row r="163" spans="1:6">
-      <c r="B163" s="80" t="s">
-        <v>409</v>
-      </c>
-      <c r="C163" s="239">
+    <row r="168" spans="1:6">
+      <c r="B168" s="80" t="s">
+        <v>404</v>
+      </c>
+      <c r="C168" s="239">
         <f>Scenarios!C105</f>
         <v>53.520960428876833</v>
       </c>
-      <c r="D163" s="342" t="str">
-        <f>IF($D$11="","",C163*$E$22)</f>
+      <c r="D168" s="336" t="str">
+        <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="164" spans="1:6">
-      <c r="B164" s="290" t="s">
-        <v>426</v>
-      </c>
-      <c r="C164" s="340" t="str">
+    <row r="169" spans="1:6">
+      <c r="B169" s="286" t="s">
+        <v>420</v>
+      </c>
+      <c r="C169" s="334" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D164" s="340" t="str">
+      <c r="D169" s="334" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
     </row>
-    <row r="165" spans="1:6">
-      <c r="B165" s="238" t="s">
+    <row r="170" spans="1:6">
+      <c r="B170" s="238" t="s">
         <v>263</v>
       </c>
-      <c r="C165" s="92">
+      <c r="C170" s="92">
         <f>Scenarios!F105</f>
         <v>0.19636122353473784</v>
       </c>
     </row>
-    <row r="167" spans="1:6" ht="13.9">
-      <c r="A167" s="247" t="s">
+    <row r="172" spans="1:6" ht="13.9">
+      <c r="A172" s="247" t="s">
+        <v>377</v>
+      </c>
+      <c r="B172" s="36"/>
+      <c r="C172" s="36"/>
+      <c r="D172" s="36"/>
+      <c r="E172" s="36"/>
+      <c r="F172" s="36"/>
+    </row>
+    <row r="174" spans="1:6">
+      <c r="B174" s="353" t="s">
+        <v>379</v>
+      </c>
+      <c r="C174" s="346"/>
+      <c r="D174" s="346"/>
+      <c r="E174" s="346"/>
+      <c r="F174" s="346"/>
+    </row>
+    <row r="176" spans="1:6">
+      <c r="B176" s="234" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="177" spans="2:6">
+      <c r="B177" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C177" s="350"/>
+      <c r="D177" s="350"/>
+      <c r="E177" s="350"/>
+      <c r="F177" s="350"/>
+    </row>
+    <row r="178" spans="2:6">
+      <c r="B178" s="238" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="179" spans="2:6">
+      <c r="B179" s="238" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="180" spans="2:6">
+      <c r="B180" s="238" t="s">
         <v>382</v>
       </c>
-      <c r="B167" s="36"/>
-      <c r="C167" s="36"/>
-      <c r="D167" s="36"/>
-      <c r="E167" s="36"/>
-      <c r="F167" s="36"/>
-    </row>
-    <row r="169" spans="1:6">
-      <c r="B169" s="350" t="s">
+    </row>
+    <row r="182" spans="2:6">
+      <c r="B182" s="1" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
+      <c r="B183" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C169" s="343"/>
-      <c r="D169" s="343"/>
-      <c r="E169" s="343"/>
-      <c r="F169" s="343"/>
-    </row>
-    <row r="171" spans="1:6">
-      <c r="B171" s="234" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6">
-      <c r="B172" s="347" t="s">
+      <c r="C183" s="347"/>
+      <c r="D183" s="347"/>
+      <c r="E183" s="347"/>
+      <c r="F183" s="347"/>
+    </row>
+    <row r="185" spans="2:6">
+      <c r="B185" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C172" s="347"/>
-      <c r="D172" s="347"/>
-      <c r="E172" s="347"/>
-      <c r="F172" s="347"/>
-    </row>
-    <row r="173" spans="1:6">
-      <c r="B173" s="238" t="s">
+    </row>
+    <row r="186" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B186" s="352" t="s">
         <v>385</v>
       </c>
-    </row>
-    <row r="174" spans="1:6">
-      <c r="B174" s="238" t="s">
+      <c r="C186" s="352"/>
+      <c r="D186" s="352"/>
+      <c r="E186" s="352"/>
+      <c r="F186" s="352"/>
+    </row>
+    <row r="187" spans="2:6" ht="24.4" customHeight="1">
+      <c r="B187" s="352" t="s">
         <v>386</v>
       </c>
-    </row>
-    <row r="175" spans="1:6">
-      <c r="B175" s="238" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="177" spans="2:6">
-      <c r="B177" s="1" t="s">
+      <c r="C187" s="352"/>
+      <c r="D187" s="352"/>
+      <c r="E187" s="352"/>
+      <c r="F187" s="352"/>
+    </row>
+    <row r="189" spans="2:6">
+      <c r="B189" s="1" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="178" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B178" s="344" t="s">
+    <row r="190" spans="2:6">
+      <c r="B190" s="238" t="s">
         <v>389</v>
       </c>
-      <c r="C178" s="344"/>
-      <c r="D178" s="344"/>
-      <c r="E178" s="344"/>
-      <c r="F178" s="344"/>
-    </row>
-    <row r="180" spans="2:6">
-      <c r="B180" s="1" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="181" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B181" s="349" t="s">
+    </row>
+    <row r="191" spans="2:6">
+      <c r="B191" s="238" t="s">
         <v>390</v>
       </c>
-      <c r="C181" s="349"/>
-      <c r="D181" s="349"/>
-      <c r="E181" s="349"/>
-      <c r="F181" s="349"/>
-    </row>
-    <row r="182" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B182" s="349" t="s">
+    </row>
+    <row r="192" spans="2:6">
+      <c r="B192" s="238" t="s">
         <v>391</v>
-      </c>
-      <c r="C182" s="349"/>
-      <c r="D182" s="349"/>
-      <c r="E182" s="349"/>
-      <c r="F182" s="349"/>
-    </row>
-    <row r="184" spans="2:6">
-      <c r="B184" s="1" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="185" spans="2:6">
-      <c r="B185" s="238" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="186" spans="2:6">
-      <c r="B186" s="238" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="187" spans="2:6">
-      <c r="B187" s="238" t="s">
-        <v>396</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B181:F181"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B169:F169"/>
-    <mergeCell ref="B178:F178"/>
-    <mergeCell ref="B172:F172"/>
-    <mergeCell ref="B69:F69"/>
-    <mergeCell ref="B113:F113"/>
-    <mergeCell ref="B78:F78"/>
-    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B84:F84"/>
+    <mergeCell ref="B91:F91"/>
+    <mergeCell ref="B111:F111"/>
+    <mergeCell ref="B133:F133"/>
+    <mergeCell ref="B50:F50"/>
     <mergeCell ref="B58:F58"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B41:F41"/>
-    <mergeCell ref="B18:F18"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B31:F31"/>
-    <mergeCell ref="B34:F34"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="B79:F79"/>
-    <mergeCell ref="B86:F86"/>
-    <mergeCell ref="B106:F106"/>
-    <mergeCell ref="B128:F128"/>
-    <mergeCell ref="B44:F44"/>
-    <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B55:F55"/>
-    <mergeCell ref="B59:F59"/>
-    <mergeCell ref="B68:F68"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="B74:F74"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1" xr:uid="{45F807FD-9E0F-415A-9BBD-D5FB6470B56D}">
       <formula1>"Y, N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D73:D74" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C23:C25" xr:uid="{342D2C68-3352-49DC-9D77-964DC8D8A160}">
       <formula1>"Y,N"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C22:D22" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+      <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5675,17 +5792,17 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.796875" style="1"/>
+    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.86328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
-        <f>Thesis!C22</f>
+        <f>Thesis!C25</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="104">
@@ -6208,7 +6325,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="C22" s="181">
         <v>2542046725</v>
@@ -6244,7 +6361,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C23" s="181">
         <v>-633430356</v>
@@ -6280,7 +6397,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="C24" s="181">
         <v>-3527746522</v>
@@ -6339,7 +6456,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>440</v>
+        <v>450</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7644,7 +7761,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8092,11 +8209,11 @@
         <f t="shared" si="40"/>
         <v>58261577</v>
       </c>
-      <c r="I77" s="335"/>
-      <c r="J77" s="335"/>
-      <c r="K77" s="335"/>
-      <c r="L77" s="335"/>
-      <c r="M77" s="335"/>
+      <c r="I77" s="330"/>
+      <c r="J77" s="330"/>
+      <c r="K77" s="330"/>
+      <c r="L77" s="330"/>
+      <c r="M77" s="330"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8126,11 +8243,11 @@
         <f t="shared" si="40"/>
         <v>364381375</v>
       </c>
-      <c r="I78" s="335"/>
-      <c r="J78" s="335"/>
-      <c r="K78" s="335"/>
-      <c r="L78" s="335"/>
-      <c r="M78" s="335"/>
+      <c r="I78" s="330"/>
+      <c r="J78" s="330"/>
+      <c r="K78" s="330"/>
+      <c r="L78" s="330"/>
+      <c r="M78" s="330"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -8262,15 +8379,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.33203125" style="1"/>
+    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.265625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="15" customHeight="1">
@@ -8328,7 +8445,7 @@
         <f>63423634.85+27585675</f>
         <v>91009309.849999994</v>
       </c>
-      <c r="D4" s="294">
+      <c r="D4" s="290">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -8338,7 +8455,7 @@
       <c r="G4" s="19">
         <v>1081659074.0699999</v>
       </c>
-      <c r="H4" s="294">
+      <c r="H4" s="290">
         <v>0.9</v>
       </c>
     </row>
@@ -8349,7 +8466,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="294">
+      <c r="D5" s="290">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -8359,7 +8476,7 @@
       <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="294">
+      <c r="H5" s="290">
         <v>0.7</v>
       </c>
     </row>
@@ -8370,7 +8487,7 @@
       <c r="C6" s="19">
         <v>2185835620.7199998</v>
       </c>
-      <c r="D6" s="294">
+      <c r="D6" s="290">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -8380,7 +8497,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="294">
+      <c r="H6" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8391,7 +8508,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="294">
+      <c r="D7" s="290">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -8401,7 +8518,7 @@
       <c r="G7" s="19">
         <v>22482125.719999999</v>
       </c>
-      <c r="H7" s="294">
+      <c r="H7" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8412,7 +8529,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="294">
+      <c r="D8" s="290">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -8422,7 +8539,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="294">
+      <c r="H8" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8433,7 +8550,7 @@
       <c r="C9" s="19">
         <v>28012999.57</v>
       </c>
-      <c r="D9" s="294">
+      <c r="D9" s="290">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -8443,7 +8560,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="294">
+      <c r="H9" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8454,10 +8571,10 @@
       <c r="C10" s="19">
         <v>0</v>
       </c>
-      <c r="D10" s="294">
+      <c r="D10" s="290">
         <v>0.9</v>
       </c>
-      <c r="H10" s="295"/>
+      <c r="H10" s="291"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
@@ -8466,10 +8583,10 @@
       <c r="C11" s="19">
         <v>270038356.50999999</v>
       </c>
-      <c r="D11" s="294">
+      <c r="D11" s="290">
         <v>0.05</v>
       </c>
-      <c r="H11" s="295"/>
+      <c r="H11" s="291"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
@@ -8527,7 +8644,7 @@
       <c r="C15" s="19">
         <v>0</v>
       </c>
-      <c r="D15" s="294">
+      <c r="D15" s="290">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -8536,7 +8653,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="294">
+      <c r="H15" s="290">
         <v>0.8</v>
       </c>
     </row>
@@ -8547,7 +8664,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="294">
+      <c r="D16" s="290">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -8556,7 +8673,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="294">
+      <c r="H16" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8567,7 +8684,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="294">
+      <c r="D17" s="290">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -8576,7 +8693,7 @@
       <c r="G17" s="19">
         <v>0</v>
       </c>
-      <c r="H17" s="294">
+      <c r="H17" s="290">
         <v>0.6</v>
       </c>
     </row>
@@ -8587,7 +8704,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="294">
+      <c r="D18" s="290">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -8596,7 +8713,7 @@
       <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="294">
+      <c r="H18" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8608,7 +8725,7 @@
         <f>4755026247.47+159772560.73+160044048.75</f>
         <v>5074842856.9499998</v>
       </c>
-      <c r="D19" s="294">
+      <c r="D19" s="290">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -8618,7 +8735,7 @@
         <f>142861296.29+17825955.91</f>
         <v>160687252.19999999</v>
       </c>
-      <c r="H19" s="294">
+      <c r="H19" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8629,7 +8746,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="294">
+      <c r="D20" s="290">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -8638,7 +8755,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="294">
+      <c r="H20" s="290">
         <v>0.2</v>
       </c>
     </row>
@@ -8649,7 +8766,7 @@
       <c r="C21" s="19">
         <v>650634797.63</v>
       </c>
-      <c r="D21" s="294">
+      <c r="D21" s="290">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -8658,7 +8775,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="294">
+      <c r="H21" s="290">
         <v>0.1</v>
       </c>
     </row>
@@ -8669,10 +8786,10 @@
       <c r="C22" s="19">
         <v>703465374.02999997</v>
       </c>
-      <c r="D22" s="294">
+      <c r="D22" s="290">
         <v>0.9</v>
       </c>
-      <c r="H22" s="295"/>
+      <c r="H22" s="291"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
@@ -8682,10 +8799,10 @@
         <f>699192456.06+479496.08</f>
         <v>699671952.13999999</v>
       </c>
-      <c r="D23" s="294">
-        <v>0</v>
-      </c>
-      <c r="H23" s="295"/>
+      <c r="D23" s="290">
+        <v>0</v>
+      </c>
+      <c r="H23" s="291"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
@@ -9018,13 +9135,13 @@
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="261" t="s">
+      <c r="C45" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>414</v>
-      </c>
-      <c r="F45" s="287" t="s">
+        <v>409</v>
+      </c>
+      <c r="F45" s="283" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9040,7 +9157,7 @@
         <f>H29</f>
         <v>-6443106811.8090019</v>
       </c>
-      <c r="F46" s="283"/>
+      <c r="F46" s="280"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
@@ -9055,23 +9172,23 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>-13.312996389940134</v>
       </c>
-      <c r="F47" s="283"/>
+      <c r="F47" s="280"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1">
-      <c r="F48" s="283"/>
+      <c r="F48" s="280"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="262" t="s">
+      <c r="C49" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
         <v>96</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="283"/>
+      <c r="F49" s="280"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
@@ -9085,7 +9202,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>3.9727648442014103E-2</v>
       </c>
-      <c r="F50" s="283"/>
+      <c r="F50" s="280"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
@@ -9096,22 +9213,22 @@
         <f>G29/G32</f>
         <v>0.10805831095063075</v>
       </c>
-      <c r="F51" s="283"/>
+      <c r="F51" s="280"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="F52" s="283"/>
+      <c r="F52" s="280"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="262" t="s">
+      <c r="C53" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="283"/>
+      <c r="F53" s="280"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
@@ -9125,7 +9242,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>0.32042139111496037</v>
       </c>
-      <c r="F54" s="283"/>
+      <c r="F54" s="280"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
@@ -9139,22 +9256,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>0</v>
       </c>
-      <c r="F55" s="283"/>
+      <c r="F55" s="280"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1">
-      <c r="F56" s="283"/>
+      <c r="F56" s="280"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
-      <c r="C57" s="262" t="s">
+      <c r="C57" s="260" t="s">
         <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="283"/>
+      <c r="F57" s="280"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
@@ -9176,22 +9293,22 @@
         <f>G39/G32</f>
         <v>0.46268104259923815</v>
       </c>
-      <c r="F59" s="283"/>
+      <c r="F59" s="280"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1">
-      <c r="F60" s="283"/>
+      <c r="F60" s="280"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="262" t="s">
+      <c r="C61" s="260" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="283"/>
+      <c r="F61" s="280"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
@@ -9205,7 +9322,7 @@
         <f>G28/G29</f>
         <v>1.0702127528080294</v>
       </c>
-      <c r="F62" s="283" t="s">
+      <c r="F62" s="280" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9224,13 +9341,13 @@
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="261" t="s">
+      <c r="C65" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>292</v>
-      </c>
-      <c r="F65" s="287" t="s">
+        <v>288</v>
+      </c>
+      <c r="F65" s="283" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9258,7 +9375,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="283"/>
+      <c r="F67" s="280"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
@@ -9268,7 +9385,7 @@
         <f>G18</f>
         <v>0</v>
       </c>
-      <c r="F68" s="283"/>
+      <c r="F68" s="280"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
@@ -9278,7 +9395,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="283"/>
+      <c r="F69" s="280"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
@@ -9288,26 +9405,26 @@
         <f>SUM(C66:C69)</f>
         <v>1081659074.0699999</v>
       </c>
-      <c r="F70" s="283"/>
+      <c r="F70" s="280"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1">
-      <c r="F71" s="283"/>
+      <c r="F71" s="280"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
-      <c r="B72" s="285" t="s">
-        <v>326</v>
-      </c>
-      <c r="C72" s="261" t="s">
+      <c r="B72" s="282" t="s">
+        <v>321</v>
+      </c>
+      <c r="C72" s="259" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="F72" s="283"/>
+      <c r="F72" s="280"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9318,65 +9435,65 @@
         <v>-1016040624.0210911</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
-      <c r="B74" s="288" t="s">
-        <v>329</v>
-      </c>
-      <c r="C74" s="289">
+      <c r="B74" s="284" t="s">
+        <v>324</v>
+      </c>
+      <c r="C74" s="285">
         <f>-$C$66/C73</f>
         <v>1.0222883058815033</v>
       </c>
-      <c r="D74" s="289">
+      <c r="D74" s="285">
         <f>-$C$66/D73</f>
         <v>1.0645825063462686</v>
       </c>
-      <c r="F74" s="283" t="s">
-        <v>327</v>
+      <c r="F74" s="280" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>328</v>
-      </c>
-      <c r="C75" s="293"/>
-      <c r="D75" s="292">
+        <v>323</v>
+      </c>
+      <c r="C75" s="289"/>
+      <c r="D75" s="288">
         <f>MAX(-D73*D76,G5)</f>
         <v>1016040624.0210911</v>
       </c>
-      <c r="F75" s="283" t="s">
-        <v>360</v>
+      <c r="F75" s="280" t="s">
+        <v>355</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
-      <c r="B76" s="290" t="s">
-        <v>330</v>
-      </c>
-      <c r="C76" s="291"/>
-      <c r="D76" s="327">
+      <c r="B76" s="286" t="s">
+        <v>325</v>
+      </c>
+      <c r="C76" s="287"/>
+      <c r="D76" s="323">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>1</v>
       </c>
-      <c r="F76" s="283" t="s">
-        <v>331</v>
+      <c r="F76" s="280" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
-      <c r="F77" s="283"/>
+      <c r="F77" s="280"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="261" t="s">
+      <c r="C78" s="259" t="s">
         <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="F78" s="283"/>
+      <c r="F78" s="280"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
@@ -9390,7 +9507,7 @@
         <f>G7*H7+G17*H17</f>
         <v>13489275.431999998</v>
       </c>
-      <c r="F79" s="283"/>
+      <c r="F79" s="280"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
@@ -9404,7 +9521,7 @@
         <f>G19*H19</f>
         <v>16068725.219999999</v>
       </c>
-      <c r="F80" s="283"/>
+      <c r="F80" s="280"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
@@ -9418,7 +9535,7 @@
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F81" s="283"/>
+      <c r="F81" s="280"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
@@ -9432,11 +9549,11 @@
         <f>SUM(D79:D81)</f>
         <v>29558000.651999995</v>
       </c>
-      <c r="F82" s="283"/>
+      <c r="F82" s="280"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9447,15 +9564,15 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>296</v>
-      </c>
-      <c r="D85" s="270" t="s">
-        <v>297</v>
+        <v>292</v>
+      </c>
+      <c r="D85" s="268" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="267" t="s">
-        <v>293</v>
+      <c r="B86" s="265" t="s">
+        <v>289</v>
       </c>
       <c r="C86" s="188">
         <f>-Valuation_Model!C7*Exchange_Rate</f>
@@ -9465,14 +9582,14 @@
         <f>C86*scaling_factor/Common_Shares</f>
         <v>-0.25522532080514426</v>
       </c>
-      <c r="E86" s="269" t="str">
+      <c r="E86" s="267" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="267" t="s">
-        <v>294</v>
+      <c r="B87" s="265" t="s">
+        <v>290</v>
       </c>
       <c r="C87" s="188">
         <f>Valuation_Model!C8*Exchange_Rate</f>
@@ -9482,13 +9599,13 @@
         <f>C87*scaling_factor/Common_Shares</f>
         <v>0.13558337834994227</v>
       </c>
-      <c r="E87" s="269" t="str">
+      <c r="E87" s="267" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="268" t="s">
+      <c r="B88" s="266" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="188">
@@ -9499,24 +9616,24 @@
         <f>C88*scaling_factor/Common_Shares</f>
         <v>6.1073883681813636E-2</v>
       </c>
-      <c r="E88" s="269" t="str">
+      <c r="E88" s="267" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
         <v>-28345253.569091171</v>
       </c>
-      <c r="D89" s="271">
+      <c r="D89" s="269">
         <f>SUM(D86:D88)</f>
         <v>-5.8568058773388353E-2</v>
       </c>
-      <c r="E89" s="269" t="str">
+      <c r="E89" s="267" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
@@ -9535,22 +9652,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
     <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.33203125" style="2"/>
+    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.265625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
-        <f>Thesis!C22</f>
+        <f>Thesis!C25</f>
         <v>CNY</v>
       </c>
       <c r="C1" s="53" t="s">
@@ -9637,7 +9754,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="302"/>
+      <c r="E3" s="298"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -9651,7 +9768,7 @@
         <v>14154446369.75</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="300"/>
+      <c r="E4" s="296"/>
       <c r="F4" s="57"/>
       <c r="G4" s="183">
         <f>Data!C36</f>
@@ -9707,7 +9824,7 @@
         <f>C25</f>
         <v>-10434492185.803093</v>
       </c>
-      <c r="E5" s="302"/>
+      <c r="E5" s="298"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-10995777063</v>
@@ -9762,7 +9879,7 @@
         <f>C4+C5</f>
         <v>3719954183.946907</v>
       </c>
-      <c r="E6" s="302"/>
+      <c r="E6" s="298"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
         <v>3648820779</v>
@@ -9817,7 +9934,7 @@
         <f>C35</f>
         <v>-596464427.25</v>
       </c>
-      <c r="E7" s="302"/>
+      <c r="E7" s="298"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-539608200</v>
@@ -9873,7 +9990,7 @@
         <v>3123489756.696907</v>
       </c>
       <c r="D8" s="59"/>
-      <c r="E8" s="308"/>
+      <c r="E8" s="304"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
@@ -9929,7 +10046,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>575917865</v>
       </c>
-      <c r="E9" s="302"/>
+      <c r="E9" s="298"/>
       <c r="G9" s="191">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>575917865</v>
@@ -9984,7 +10101,7 @@
         <f>-C4*C78</f>
         <v>-575917865</v>
       </c>
-      <c r="E10" s="302"/>
+      <c r="E10" s="298"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
         <v>-575917865</v>
@@ -10040,7 +10157,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="169"/>
-      <c r="E11" s="301"/>
+      <c r="E11" s="297"/>
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
@@ -10096,7 +10213,7 @@
         <f>C50</f>
         <v>30881944.997018404</v>
       </c>
-      <c r="E12" s="302"/>
+      <c r="E12" s="298"/>
       <c r="G12" s="191">
         <f>G50</f>
         <v>30881944.997018404</v>
@@ -10151,7 +10268,7 @@
         <f>SUM(C8:C12)</f>
         <v>3154371701.6939254</v>
       </c>
-      <c r="E13" s="302"/>
+      <c r="E13" s="298"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>3140094523.9970183</v>
@@ -10206,7 +10323,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-788592925.42348135</v>
       </c>
-      <c r="E14" s="302"/>
+      <c r="E14" s="298"/>
       <c r="G14" s="191">
         <f>Data!C46</f>
         <v>-670547120</v>
@@ -10262,7 +10379,7 @@
         <v>-141879704.29826272</v>
       </c>
       <c r="D15" s="60"/>
-      <c r="E15" s="309"/>
+      <c r="E15" s="305"/>
       <c r="F15" s="60"/>
       <c r="G15" s="183">
         <f>Data!C48</f>
@@ -10319,7 +10436,7 @@
         <v>2223899071.9721813</v>
       </c>
       <c r="D16" s="61"/>
-      <c r="E16" s="310"/>
+      <c r="E16" s="306"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -10376,8 +10493,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
-      <c r="E17" s="301" t="s">
-        <v>339</v>
+      <c r="E17" s="297" t="s">
+        <v>334</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10401,8 +10518,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
-      <c r="E18" s="301" t="s">
-        <v>340</v>
+      <c r="E18" s="297" t="s">
+        <v>335</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10427,7 +10544,7 @@
         <v>2223899071.9721813</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="299"/>
+      <c r="E19" s="295"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
@@ -10523,7 +10640,7 @@
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="299"/>
+      <c r="E22" s="295"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -10547,7 +10664,7 @@
         <v>-8039212664.4388895</v>
       </c>
       <c r="D23" s="58"/>
-      <c r="E23" s="301"/>
+      <c r="E23" s="297"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
@@ -10604,7 +10721,7 @@
         <v>-2395279521.3642035</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="299"/>
+      <c r="E24" s="295"/>
       <c r="F24" s="27"/>
       <c r="G24" s="183">
         <f>Data!C40</f>
@@ -10661,7 +10778,7 @@
         <v>-10434492185.803093</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="307"/>
+      <c r="E25" s="303"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -10710,14 +10827,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
-      <c r="E26" s="302"/>
+      <c r="E26" s="298"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="302"/>
+      <c r="E27" s="298"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -10729,8 +10846,8 @@
         <v>0.56796376590325659</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="300" t="s">
-        <v>341</v>
+      <c r="E28" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10789,8 +10906,8 @@
         <v>0.1692245290838959</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="300" t="s">
-        <v>341</v>
+      <c r="E29" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10847,7 +10964,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.73718829498715255</v>
       </c>
-      <c r="E30" s="302"/>
+      <c r="E30" s="298"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.75084185865894126</v>
@@ -10895,14 +11012,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
-      <c r="E31" s="302"/>
+      <c r="E31" s="298"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="302"/>
+      <c r="E32" s="298"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -10913,8 +11030,8 @@
         <f>AVERAGE(G33:J33)</f>
         <v>-515765096.5</v>
       </c>
-      <c r="E33" s="300" t="s">
-        <v>341</v>
+      <c r="E33" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -10971,8 +11088,8 @@
         <v>-80699330.75</v>
       </c>
       <c r="D34" s="58"/>
-      <c r="E34" s="300" t="s">
-        <v>341</v>
+      <c r="E34" s="296" t="s">
+        <v>336</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -11030,7 +11147,7 @@
         <v>-596464427.25</v>
       </c>
       <c r="D35" s="58"/>
-      <c r="E35" s="301"/>
+      <c r="E35" s="297"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -11079,14 +11196,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="E36" s="302"/>
+      <c r="E36" s="298"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="302"/>
+      <c r="E37" s="298"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -11099,7 +11216,7 @@
         <v>3.6438380069902347E-2</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="299"/>
+      <c r="E38" s="295"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -11157,7 +11274,7 @@
         <v>5.701341376549038E-3</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="299"/>
+      <c r="E39" s="295"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -11213,7 +11330,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>4.2139721446451381E-2</v>
       </c>
-      <c r="E40" s="302"/>
+      <c r="E40" s="298"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>3.6846911456484638E-2</v>
@@ -11261,26 +11378,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="E41" s="302"/>
+      <c r="E41" s="298"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="302"/>
+      <c r="E42" s="298"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="296">
+      <c r="C43" s="292">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="299" t="s">
-        <v>342</v>
+      <c r="E43" s="295" t="s">
+        <v>337</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11359,7 +11476,7 @@
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="302"/>
+      <c r="E46" s="298"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
@@ -11370,7 +11487,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-7672861</v>
       </c>
-      <c r="E47" s="302"/>
+      <c r="E47" s="298"/>
       <c r="G47" s="191">
         <f>Data!C51</f>
         <v>-7672861</v>
@@ -11419,111 +11536,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
         <v>38554805.997018404</v>
       </c>
-      <c r="E48" s="302"/>
-      <c r="G48" s="328">
+      <c r="E48" s="298"/>
+      <c r="G48" s="324">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>38554805.997018404</v>
       </c>
-      <c r="H48" s="328">
+      <c r="H48" s="324">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>66982141.426252395</v>
       </c>
-      <c r="I48" s="328">
+      <c r="I48" s="324">
         <f t="shared" si="19"/>
         <v>61731794.960215338</v>
       </c>
-      <c r="J48" s="328">
+      <c r="J48" s="324">
         <f t="shared" si="19"/>
         <v>33863778.321634412</v>
       </c>
-      <c r="K48" s="328">
+      <c r="K48" s="324">
         <f t="shared" si="19"/>
         <v>41746958.77028092</v>
       </c>
-      <c r="L48" s="328">
+      <c r="L48" s="324">
         <f t="shared" si="19"/>
         <v>8061746.2233673697</v>
       </c>
-      <c r="M48" s="328">
+      <c r="M48" s="324">
         <f t="shared" si="19"/>
         <v>6208975.7821457442</v>
       </c>
-      <c r="N48" s="328">
+      <c r="N48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="328">
+      <c r="O48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="328">
+      <c r="P48" s="324">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="328" t="str">
+      <c r="Q48" s="324" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="323" t="s">
-        <v>350</v>
-      </c>
-      <c r="C49" s="324">
+      <c r="B49" s="319" t="s">
+        <v>345</v>
+      </c>
+      <c r="C49" s="320">
         <f>BS!$C$66*C53</f>
         <v>41044772</v>
       </c>
-      <c r="D49" s="325"/>
-      <c r="E49" s="326"/>
-      <c r="F49" s="325"/>
-      <c r="G49" s="324">
+      <c r="D49" s="321"/>
+      <c r="E49" s="322"/>
+      <c r="F49" s="321"/>
+      <c r="G49" s="320">
         <f>Data!C52</f>
         <v>41044772</v>
       </c>
-      <c r="H49" s="324">
+      <c r="H49" s="320">
         <f>Data!D52</f>
         <v>71308016</v>
       </c>
-      <c r="I49" s="324">
+      <c r="I49" s="320">
         <f>Data!E52</f>
         <v>65718589</v>
       </c>
-      <c r="J49" s="324">
+      <c r="J49" s="320">
         <f>Data!F52</f>
         <v>36050786</v>
       </c>
-      <c r="K49" s="324">
+      <c r="K49" s="320">
         <f>Data!G52</f>
         <v>44443082</v>
       </c>
-      <c r="L49" s="324">
+      <c r="L49" s="320">
         <f>Data!H52</f>
         <v>8582394</v>
       </c>
-      <c r="M49" s="324">
+      <c r="M49" s="320">
         <f>Data!I52</f>
         <v>6609967</v>
       </c>
-      <c r="N49" s="324">
+      <c r="N49" s="320">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="324">
+      <c r="O49" s="320">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="324">
+      <c r="P49" s="320">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="324" t="str">
+      <c r="Q49" s="320" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11537,7 +11654,7 @@
         <f>C47+C48</f>
         <v>30881944.997018404</v>
       </c>
-      <c r="E50" s="302"/>
+      <c r="E50" s="298"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>30881944.997018404</v>
@@ -11585,14 +11702,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="E51" s="302"/>
+      <c r="E51" s="298"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="302"/>
+      <c r="E52" s="298"/>
       <c r="G52" s="97" t="s">
         <v>220</v>
       </c>
@@ -11606,8 +11723,8 @@
         <f>G53</f>
         <v>3.7946126449583846E-2</v>
       </c>
-      <c r="E53" s="299" t="s">
-        <v>343</v>
+      <c r="E53" s="295" t="s">
+        <v>338</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11633,8 +11750,8 @@
         <f>G54</f>
         <v>6.2117512427032839E-2</v>
       </c>
-      <c r="E54" s="299" t="s">
-        <v>344</v>
+      <c r="E54" s="295" t="s">
+        <v>339</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11660,7 +11777,7 @@
         <f>-C8/C47</f>
         <v>407.08280219033122</v>
       </c>
-      <c r="E55" s="302"/>
+      <c r="E55" s="298"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>405.22206501590478</v>
@@ -11708,14 +11825,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="E56" s="302"/>
+      <c r="E56" s="298"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="302"/>
+      <c r="E57" s="298"/>
       <c r="G57" s="97" t="s">
         <v>220</v>
       </c>
@@ -11729,7 +11846,7 @@
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="302"/>
+      <c r="E58" s="298"/>
       <c r="G58" s="191">
         <f>Data!C56</f>
         <v>0</v>
@@ -11784,7 +11901,7 @@
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="302"/>
+      <c r="E59" s="298"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
         <v>0</v>
@@ -11839,7 +11956,7 @@
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="302"/>
+      <c r="E60" s="298"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
         <v>0</v>
@@ -11894,7 +12011,7 @@
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="302"/>
+      <c r="E61" s="298"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
@@ -11945,11 +12062,11 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="297">
-        <v>0</v>
-      </c>
-      <c r="E62" s="300" t="s">
-        <v>345</v>
+      <c r="C62" s="293">
+        <v>0</v>
+      </c>
+      <c r="E62" s="296" t="s">
+        <v>340</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12005,7 +12122,7 @@
         <f>C61+C62</f>
         <v>0</v>
       </c>
-      <c r="E63" s="302"/>
+      <c r="E63" s="298"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>-222656878</v>
@@ -12053,14 +12170,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="E64" s="302"/>
+      <c r="E64" s="298"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="302"/>
+      <c r="E65" s="298"/>
       <c r="G65" s="97" t="s">
         <v>220</v>
       </c>
@@ -12074,7 +12191,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="302"/>
+      <c r="E66" s="298"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -12099,7 +12216,7 @@
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="302"/>
+      <c r="E67" s="298"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>0</v>
@@ -12124,7 +12241,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="302"/>
+      <c r="E68" s="298"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
@@ -12150,7 +12267,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="307"/>
+      <c r="E69" s="303"/>
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
@@ -12178,7 +12295,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12200,7 +12317,7 @@
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="299"/>
+      <c r="E72" s="295"/>
       <c r="F72" s="27"/>
       <c r="G72" s="97"/>
       <c r="H72" s="12"/>
@@ -12224,7 +12341,7 @@
         <v>0.73718829498715255</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="299"/>
+      <c r="E73" s="295"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -12281,7 +12398,7 @@
         <v>0.26281170501284751</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="299"/>
+      <c r="E74" s="295"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -12338,7 +12455,7 @@
         <v>4.2139721446451381E-2</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="299"/>
+      <c r="E75" s="295"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -12395,7 +12512,7 @@
         <v>0.22067198356639611</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="299"/>
+      <c r="E76" s="295"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -12452,7 +12569,7 @@
         <v>4.0688123714313247E-2</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="299"/>
+      <c r="E77" s="295"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -12509,8 +12626,8 @@
         <v>4.0688123714313247E-2</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="300" t="s">
-        <v>442</v>
+      <c r="E78" s="296" t="s">
+        <v>452</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12568,7 +12685,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="299"/>
+      <c r="E79" s="295"/>
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -12625,7 +12742,7 @@
         <v>2.1817840267505887E-3</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="299"/>
+      <c r="E80" s="295"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -12682,7 +12799,7 @@
         <v>0.22285376759314668</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="299"/>
+      <c r="E81" s="295"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -12739,7 +12856,7 @@
         <v>5.571344189828667E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="299"/>
+      <c r="E82" s="295"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -12792,12 +12909,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="298">
+      <c r="C83" s="294">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>1.0023684472850819E-2</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="299"/>
+      <c r="E83" s="295"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -12854,7 +12971,7 @@
         <v>0.15711664122200919</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="299"/>
+      <c r="E84" s="295"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -12906,26 +13023,26 @@
       <c r="B85" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="298">
+      <c r="C85" s="294">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="301" t="str">
+      <c r="E85" s="297" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="253"/>
-      <c r="H85" s="253"/>
-      <c r="I85" s="253"/>
-      <c r="J85" s="253"/>
-      <c r="K85" s="253"/>
-      <c r="L85" s="253"/>
-      <c r="M85" s="253"/>
-      <c r="N85" s="253"/>
-      <c r="O85" s="253"/>
-      <c r="P85" s="253"/>
-      <c r="Q85" s="253"/>
+      <c r="G85" s="251"/>
+      <c r="H85" s="251"/>
+      <c r="I85" s="251"/>
+      <c r="J85" s="251"/>
+      <c r="K85" s="251"/>
+      <c r="L85" s="251"/>
+      <c r="M85" s="251"/>
+      <c r="N85" s="251"/>
+      <c r="O85" s="251"/>
+      <c r="P85" s="251"/>
+      <c r="Q85" s="251"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
@@ -12935,7 +13052,7 @@
       <c r="C86" s="77">
         <v>0</v>
       </c>
-      <c r="E86" s="301" t="str">
+      <c r="E86" s="297" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -12961,7 +13078,7 @@
         <v>0.15711664122200919</v>
       </c>
       <c r="D87" s="75"/>
-      <c r="E87" s="299"/>
+      <c r="E87" s="295"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -13010,14 +13127,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
-      <c r="E88" s="302"/>
+      <c r="E88" s="298"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="302"/>
+      <c r="E89" s="298"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
@@ -13029,7 +13146,7 @@
         <f>G90</f>
         <v>2.4</v>
       </c>
-      <c r="E90" s="302"/>
+      <c r="E90" s="298"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
         <v>2.4</v>
@@ -13085,7 +13202,7 @@
         <f>C90*Common_Shares/scaling_factor</f>
         <v>1161530875.2</v>
       </c>
-      <c r="E91" s="302"/>
+      <c r="E91" s="298"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>1161530875.2</v>
@@ -13140,7 +13257,7 @@
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>0.52229477939839231</v>
       </c>
-      <c r="E92" s="302"/>
+      <c r="E92" s="298"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>0.50006612287112806</v>
@@ -13189,13 +13306,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>4.2208934224410834E-2</v>
       </c>
-      <c r="E93" s="302"/>
+      <c r="E93" s="298"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>4.2208934224410834E-2</v>
@@ -13243,7 +13360,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
-      <c r="E94" s="302"/>
+      <c r="E94" s="298"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
@@ -13252,7 +13369,7 @@
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="299"/>
+      <c r="E95" s="295"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -13276,7 +13393,7 @@
         <v>-3.3469780292926132E-2</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="299"/>
+      <c r="E96" s="295"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -13333,7 +13450,7 @@
         <v>4.5467350067964762E-3</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="299"/>
+      <c r="E97" s="295"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -13411,7 +13528,7 @@
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="302"/>
+      <c r="E100" s="298"/>
       <c r="G100" s="97" t="s">
         <v>220</v>
       </c>
@@ -13426,7 +13543,7 @@
         <v>10968339719.389999</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="303"/>
+      <c r="E101" s="299"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -13483,7 +13600,7 @@
         <v>91009309.849999994</v>
       </c>
       <c r="D102" s="89"/>
-      <c r="E102" s="304"/>
+      <c r="E102" s="300"/>
       <c r="F102" s="89"/>
       <c r="G102" s="185">
         <f>IF(G$4="","",Data!D77)</f>
@@ -13540,7 +13657,7 @@
         <v>2185835620.7199998</v>
       </c>
       <c r="D103" s="89"/>
-      <c r="E103" s="304"/>
+      <c r="E103" s="300"/>
       <c r="F103" s="89"/>
       <c r="G103" s="185">
         <f>IF(G$4="","",Data!D78)</f>
@@ -13597,7 +13714,7 @@
         <v>8514681613.9500008</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="303"/>
+      <c r="E104" s="299"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
@@ -13654,7 +13771,7 @@
         <v>2453658105.4399986</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="303"/>
+      <c r="E105" s="299"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
@@ -13703,7 +13820,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
-      <c r="E106" s="302"/>
+      <c r="E106" s="298"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
@@ -13712,7 +13829,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="303"/>
+      <c r="E107" s="299"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
         <v>220</v>
@@ -13738,7 +13855,7 @@
         <v>6.4297329243833525E-3</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="303"/>
+      <c r="E108" s="299"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -13795,7 +13912,7 @@
         <v>0.15442748968207132</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="303"/>
+      <c r="E109" s="299"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -13852,7 +13969,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="303"/>
+      <c r="E110" s="299"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
         <f>BS!$G$38/G$4</f>
@@ -13871,63 +13988,63 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="302"/>
+      <c r="E111" s="298"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E112" s="302"/>
+      <c r="E112" s="298"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C113" s="170"/>
-      <c r="E113" s="302"/>
-      <c r="G113" s="334">
+      <c r="E113" s="298"/>
+      <c r="G113" s="329">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>1.1301097053348144</v>
       </c>
-      <c r="H113" s="334">
+      <c r="H113" s="329">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>1.1421244767311443</v>
       </c>
-      <c r="I113" s="334">
+      <c r="I113" s="329">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>1.4506354245537583</v>
       </c>
-      <c r="J113" s="334">
+      <c r="J113" s="329">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>1.4858503664510887</v>
       </c>
-      <c r="K113" s="334">
+      <c r="K113" s="329">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>2.1056296742310616</v>
       </c>
-      <c r="L113" s="334">
+      <c r="L113" s="329">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>0.96876332816786648</v>
       </c>
-      <c r="M113" s="334">
+      <c r="M113" s="329">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>1.767034158859303</v>
       </c>
-      <c r="N113" s="334">
+      <c r="N113" s="329">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>2.5144917688633623</v>
       </c>
-      <c r="O113" s="334">
+      <c r="O113" s="329">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>4.0690767846879998</v>
       </c>
-      <c r="P113" s="334">
+      <c r="P113" s="329">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v>-2.9196128327089879</v>
       </c>
-      <c r="Q113" s="334" t="str">
+      <c r="Q113" s="329" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -13935,58 +14052,58 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="C114" s="170"/>
-      <c r="E114" s="302"/>
-      <c r="G114" s="334">
+      <c r="E114" s="298"/>
+      <c r="G114" s="329">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.0944103829432141</v>
       </c>
-      <c r="H114" s="334">
+      <c r="H114" s="329">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.1613302966984029</v>
       </c>
-      <c r="I114" s="334">
+      <c r="I114" s="329">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>1.477203347027797</v>
       </c>
-      <c r="J114" s="334">
+      <c r="J114" s="329">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>1.5005063764384885</v>
       </c>
-      <c r="K114" s="334">
+      <c r="K114" s="329">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>2.773447584133756</v>
       </c>
-      <c r="L114" s="334">
+      <c r="L114" s="329">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>1.5109716987792317</v>
       </c>
-      <c r="M114" s="334">
+      <c r="M114" s="329">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>1.7382339197122179</v>
       </c>
-      <c r="N114" s="334">
+      <c r="N114" s="329">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>2.378364555476101</v>
       </c>
-      <c r="O114" s="334">
+      <c r="O114" s="329">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>1.6724741518288628</v>
       </c>
-      <c r="P114" s="334">
+      <c r="P114" s="329">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>2.3783234522476708</v>
       </c>
-      <c r="Q114" s="334" t="str">
+      <c r="Q114" s="329" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
-      <c r="E115" s="302"/>
+      <c r="E115" s="298"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
@@ -13995,7 +14112,7 @@
       </c>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="305"/>
+      <c r="E116" s="301"/>
       <c r="F116" s="55"/>
       <c r="G116" s="23" t="str">
         <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
@@ -14051,7 +14168,7 @@
         <f>C81</f>
         <v>0.22285376759314668</v>
       </c>
-      <c r="E117" s="302"/>
+      <c r="E117" s="298"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>0.21441999007930274</v>
@@ -14105,7 +14222,7 @@
         <f>C4/C101</f>
         <v>1.2904821269100146</v>
       </c>
-      <c r="E118" s="302"/>
+      <c r="E118" s="298"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>1.3351699725448014</v>
@@ -14160,7 +14277,7 @@
         <v>4.4701988818540466</v>
       </c>
       <c r="D119" s="11"/>
-      <c r="E119" s="306"/>
+      <c r="E119" s="302"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
@@ -14217,7 +14334,7 @@
         <v>1.2729930668709819</v>
       </c>
       <c r="D120" s="103"/>
-      <c r="E120" s="305"/>
+      <c r="E120" s="301"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
@@ -14313,7 +14430,7 @@
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
-      <c r="E123" s="299"/>
+      <c r="E123" s="295"/>
       <c r="F123" s="27"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -14338,7 +14455,7 @@
         <v>4.5951062401283256</v>
       </c>
       <c r="D124" s="27"/>
-      <c r="E124" s="299"/>
+      <c r="E124" s="295"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
@@ -14395,7 +14512,7 @@
         <v>8.081439043489845E-2</v>
       </c>
       <c r="D125" s="27"/>
-      <c r="E125" s="299"/>
+      <c r="E125" s="295"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
@@ -14444,7 +14561,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15195,13 +15312,13 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.6640625" customWidth="1"/>
-    <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="13.9">
@@ -15245,7 +15362,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C81</f>
+        <f>Thesis!C86</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15255,7 +15372,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C75</f>
+        <f>Thesis!C80</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15273,10 +15390,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="351" t="s">
+      <c r="E6" s="354" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="351"/>
+      <c r="F6" s="354"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15291,8 +15408,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="351"/>
-      <c r="F7" s="351"/>
+      <c r="E7" s="354"/>
+      <c r="F7" s="354"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15307,8 +15424,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="351"/>
-      <c r="F8" s="351"/>
+      <c r="E8" s="354"/>
+      <c r="F8" s="354"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15323,8 +15440,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="351"/>
-      <c r="F9" s="351"/>
+      <c r="E9" s="354"/>
+      <c r="F9" s="354"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -15388,7 +15505,7 @@
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1">
+    <row r="16" spans="2:8" ht="13.35" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15398,7 +15515,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:8" ht="13.35" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15408,7 +15525,7 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:8" ht="13.35" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
@@ -16669,7 +16786,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16722,12 +16839,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="2.6640625" customWidth="1"/>
-    <col min="2" max="2" width="22.6640625" customWidth="1"/>
-    <col min="3" max="3" width="13.9296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="2.73046875" customWidth="1"/>
+    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.73046875" customWidth="1"/>
     <col min="5" max="6" width="42.59765625" customWidth="1"/>
     <col min="8" max="9" width="15.59765625" customWidth="1"/>
   </cols>
@@ -16740,19 +16857,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="277" t="s">
-        <v>302</v>
-      </c>
-      <c r="I2" s="278"/>
+      <c r="H2" s="275" t="s">
+        <v>298</v>
+      </c>
+      <c r="I2" s="276"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="276">
-        <v>0</v>
-      </c>
-      <c r="I3" s="264">
+      <c r="H3" s="274">
+        <v>0</v>
+      </c>
+      <c r="I3" s="262">
         <f>-Market_Price</f>
         <v>-56.86</v>
       </c>
@@ -16769,19 +16886,19 @@
         <v>151</v>
       </c>
       <c r="F4" s="156"/>
-      <c r="H4" s="276">
+      <c r="H4" s="274">
         <v>1</v>
       </c>
-      <c r="I4" s="264">
+      <c r="I4" s="262">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>2.4</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="H5" s="276">
+      <c r="H5" s="274">
         <v>2</v>
       </c>
-      <c r="I5" s="264">
+      <c r="I5" s="262">
         <f t="shared" si="0"/>
         <v>2.4</v>
       </c>
@@ -16795,13 +16912,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F6" s="100"/>
-      <c r="H6" s="276">
+      <c r="H6" s="274">
         <v>3</v>
       </c>
-      <c r="I6" s="264">
+      <c r="I6" s="262">
         <f t="shared" si="0"/>
         <v>68.992285778880003</v>
       </c>
@@ -16818,15 +16935,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="353" t="str">
+      <c r="E7" s="356" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 重庆啤酒(600132.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="353"/>
-      <c r="H7" s="276">
+      <c r="F7" s="356"/>
+      <c r="H7" s="274">
         <v>4</v>
       </c>
-      <c r="I7" s="264" t="str">
+      <c r="I7" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16843,12 +16960,12 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="353"/>
-      <c r="F8" s="353"/>
-      <c r="H8" s="276">
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
+      <c r="H8" s="274">
         <v>5</v>
       </c>
-      <c r="I8" s="264" t="str">
+      <c r="I8" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16865,37 +16982,37 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="353"/>
-      <c r="F9" s="353"/>
-      <c r="H9" s="276">
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
+      <c r="H9" s="274">
         <v>6</v>
       </c>
-      <c r="I9" s="264" t="str">
+      <c r="I9" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="353"/>
-      <c r="F10" s="353"/>
-      <c r="H10" s="276">
+      <c r="E10" s="356"/>
+      <c r="F10" s="356"/>
+      <c r="H10" s="274">
         <v>7</v>
       </c>
-      <c r="I10" s="264" t="str">
+      <c r="I10" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>279</v>
-      </c>
-      <c r="E11" s="353"/>
-      <c r="F11" s="353"/>
-      <c r="H11" s="276">
+        <v>278</v>
+      </c>
+      <c r="E11" s="356"/>
+      <c r="F11" s="356"/>
+      <c r="H11" s="274">
         <v>8</v>
       </c>
-      <c r="I11" s="264" t="str">
+      <c r="I11" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16909,12 +17026,12 @@
         <v>3.7342435425912202E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="353"/>
-      <c r="F12" s="353"/>
-      <c r="H12" s="276">
+      <c r="E12" s="356"/>
+      <c r="F12" s="356"/>
+      <c r="H12" s="274">
         <v>9</v>
       </c>
-      <c r="I12" s="264" t="str">
+      <c r="I12" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16927,12 +17044,12 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>2.3730241339145586E-2</v>
       </c>
-      <c r="E13" s="353"/>
-      <c r="F13" s="353"/>
-      <c r="H13" s="276">
+      <c r="E13" s="356"/>
+      <c r="F13" s="356"/>
+      <c r="H13" s="274">
         <v>10</v>
       </c>
-      <c r="I13" s="264" t="str">
+      <c r="I13" s="262" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16945,8 +17062,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-7.4877931429291333E-3</v>
       </c>
-      <c r="E14" s="353"/>
-      <c r="F14" s="353"/>
+      <c r="E14" s="356"/>
+      <c r="F14" s="356"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -16962,7 +17079,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -16972,25 +17089,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="353" t="s">
-        <v>338</v>
-      </c>
-      <c r="F18" s="354"/>
+      <c r="E18" s="356" t="s">
+        <v>333</v>
+      </c>
+      <c r="F18" s="357"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="354"/>
-      <c r="F19" s="354"/>
+      <c r="E19" s="357"/>
+      <c r="F19" s="357"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>310</v>
-      </c>
-      <c r="E20" s="354"/>
-      <c r="F20" s="354"/>
+        <v>306</v>
+      </c>
+      <c r="E20" s="357"/>
+      <c r="F20" s="357"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -17000,12 +17117,12 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="354"/>
-      <c r="F21" s="354"/>
+      <c r="E21" s="357"/>
+      <c r="F21" s="357"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C22" s="161">
         <f>Valuation_Model!C12</f>
@@ -17015,8 +17132,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="354"/>
-      <c r="F22" s="354"/>
+      <c r="E22" s="357"/>
+      <c r="F22" s="357"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17036,8 +17153,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="352"/>
-      <c r="F25" s="352"/>
+      <c r="E25" s="355"/>
+      <c r="F25" s="355"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17047,8 +17164,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="352"/>
-      <c r="F26" s="352"/>
+      <c r="E26" s="355"/>
+      <c r="F26" s="355"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -17062,8 +17179,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="352"/>
-      <c r="F27" s="352"/>
+      <c r="E27" s="355"/>
+      <c r="F27" s="355"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17073,8 +17190,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="352"/>
-      <c r="F28" s="352"/>
+      <c r="E28" s="355"/>
+      <c r="F28" s="355"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17094,8 +17211,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="352"/>
-      <c r="F31" s="352"/>
+      <c r="E31" s="355"/>
+      <c r="F31" s="355"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17105,8 +17222,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="352"/>
-      <c r="F32" s="352"/>
+      <c r="E32" s="355"/>
+      <c r="F32" s="355"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -17120,8 +17237,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="352"/>
-      <c r="F33" s="352"/>
+      <c r="E33" s="355"/>
+      <c r="F33" s="355"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17131,8 +17248,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="352"/>
-      <c r="F34" s="352"/>
+      <c r="E34" s="355"/>
+      <c r="F34" s="355"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17152,8 +17269,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="E37" s="355"/>
+      <c r="F37" s="355"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17163,8 +17280,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="352"/>
-      <c r="F38" s="352"/>
+      <c r="E38" s="355"/>
+      <c r="F38" s="355"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -17178,8 +17295,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="352"/>
-      <c r="F39" s="352"/>
+      <c r="E39" s="355"/>
+      <c r="F39" s="355"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17190,8 +17307,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="352"/>
-      <c r="F40" s="352"/>
+      <c r="E40" s="355"/>
+      <c r="F40" s="355"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17253,8 +17370,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="352"/>
-      <c r="F49" s="352"/>
+      <c r="E49" s="355"/>
+      <c r="F49" s="355"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17264,8 +17381,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="352"/>
-      <c r="F50" s="352"/>
+      <c r="E50" s="355"/>
+      <c r="F50" s="355"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17279,8 +17396,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="352"/>
-      <c r="F51" s="352"/>
+      <c r="E51" s="355"/>
+      <c r="F51" s="355"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17290,12 +17407,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="352"/>
-      <c r="F52" s="352"/>
+      <c r="E52" s="355"/>
+      <c r="F52" s="355"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17311,8 +17428,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="352"/>
-      <c r="F55" s="352"/>
+      <c r="E55" s="355"/>
+      <c r="F55" s="355"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17322,8 +17439,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="352"/>
-      <c r="F56" s="352"/>
+      <c r="E56" s="355"/>
+      <c r="F56" s="355"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17337,8 +17454,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="352"/>
-      <c r="F57" s="352"/>
+      <c r="E57" s="355"/>
+      <c r="F57" s="355"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17348,8 +17465,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="352"/>
-      <c r="F58" s="352"/>
+      <c r="E58" s="355"/>
+      <c r="F58" s="355"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17364,16 +17481,16 @@
         <v>CNY</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>303</v>
-      </c>
-      <c r="F60" s="312">
-        <f>Thesis!E25</f>
+        <v>299</v>
+      </c>
+      <c r="F60" s="308">
+        <f>Thesis!F28</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17382,10 +17499,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>311</v>
-      </c>
-      <c r="E63" s="282" t="s">
-        <v>319</v>
+        <v>307</v>
+      </c>
+      <c r="E63" s="279" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17397,8 +17514,8 @@
         <v>10</v>
       </c>
       <c r="D64" s="151"/>
-      <c r="E64" s="281" t="s">
-        <v>403</v>
+      <c r="E64" s="278" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17409,8 +17526,8 @@
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="D65" s="152"/>
-      <c r="E65" s="281" t="s">
-        <v>320</v>
+      <c r="E65" s="278" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17425,23 +17542,23 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E66" s="281" t="s">
-        <v>321</v>
+      <c r="E66" s="278" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>358</v>
-      </c>
-      <c r="E68" s="282" t="s">
-        <v>322</v>
+        <v>353</v>
+      </c>
+      <c r="E68" s="279" t="s">
+        <v>317</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>312</v>
-      </c>
-      <c r="C69" s="273" t="str">
+        <v>308</v>
+      </c>
+      <c r="C69" s="271" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>N</v>
       </c>
@@ -17449,38 +17566,38 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>300</v>
-      </c>
-      <c r="C70" s="273" t="str">
+        <v>296</v>
+      </c>
+      <c r="C70" s="271" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="281" t="s">
-        <v>301</v>
+      <c r="E70" s="278" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>299</v>
-      </c>
-      <c r="C71" s="273" t="str">
+        <v>295</v>
+      </c>
+      <c r="C71" s="271" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="281"/>
+      <c r="E71" s="278"/>
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>291</v>
-      </c>
-      <c r="C72" s="272" t="str">
+        <v>287</v>
+      </c>
+      <c r="C72" s="270" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>354</v>
-      </c>
-      <c r="F72" s="329">
+        <v>349</v>
+      </c>
+      <c r="F72" s="325">
         <f>BS!D89/C60</f>
         <v>-8.7950215386604794E-4</v>
       </c>
@@ -17500,10 +17617,10 @@
       </c>
     </row>
     <row r="76" spans="2:6">
-      <c r="B76" s="275" t="s">
-        <v>304</v>
-      </c>
-      <c r="C76" s="274">
+      <c r="B76" s="273" t="s">
+        <v>300</v>
+      </c>
+      <c r="C76" s="272">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -17524,15 +17641,15 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C80" s="168">
-        <f>Thesis!C132</f>
+        <f>Thesis!F29</f>
         <v>0.4</v>
       </c>
     </row>
@@ -17573,7 +17690,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="329">
+      <c r="F83" s="325">
         <f>(1-C83/C60)</f>
         <v>0.57830345555145946</v>
       </c>
@@ -17583,14 +17700,14 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>307</v>
-      </c>
-      <c r="C86" s="266">
+        <v>303</v>
+      </c>
+      <c r="C86" s="264">
         <f>Market_Price</f>
         <v>56.86</v>
       </c>
@@ -17601,9 +17718,9 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>305</v>
-      </c>
-      <c r="C87" s="265">
+        <v>301</v>
+      </c>
+      <c r="C87" s="263">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>9.4210132770872423E-2</v>
       </c>
@@ -17613,15 +17730,15 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="C90" s="168">
-        <f>Thesis!E24</f>
+        <f>Thesis!F30</f>
         <v>0.2</v>
       </c>
     </row>
@@ -17662,28 +17779,28 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="329">
+      <c r="F93" s="325">
         <f>(1-C93/C60)</f>
         <v>0.345378260199104</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="316"/>
+      <c r="H95" s="312"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="C96" s="135">
-        <f>Thesis!C72</f>
+        <f>Thesis!F31</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="316"/>
+      <c r="H96" s="312"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17695,7 +17812,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="316"/>
+      <c r="H97" s="312"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17707,23 +17824,23 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="316"/>
+      <c r="H98" s="312"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>59.048136223898794</v>
       </c>
       <c r="D99" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="329">
+      <c r="F99" s="325">
         <f>(1-C99/C60)</f>
         <v>0.1132886409700905</v>
       </c>
@@ -17733,15 +17850,15 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="C102" s="135">
-        <f>Thesis!E26</f>
+        <f>Thesis!F32</f>
         <v>0.1174</v>
       </c>
     </row>
@@ -17767,19 +17884,19 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
         <v>53.520960428876833</v>
       </c>
       <c r="D105" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="329">
+      <c r="F105" s="325">
         <f>(1-C105/C66)</f>
         <v>0.19636122353473784</v>
       </c>
@@ -17788,33 +17905,33 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="320" t="s">
-        <v>332</v>
-      </c>
-      <c r="F107" s="317"/>
+      <c r="E107" s="316" t="s">
+        <v>327</v>
+      </c>
+      <c r="F107" s="313"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="313" t="s">
-        <v>333</v>
-      </c>
-      <c r="F108" s="318" t="s">
-        <v>334</v>
+      <c r="E108" s="309" t="s">
+        <v>328</v>
+      </c>
+      <c r="F108" s="314" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="314" t="s">
-        <v>333</v>
-      </c>
-      <c r="F109" s="318" t="s">
-        <v>335</v>
+      <c r="E109" s="310" t="s">
+        <v>328</v>
+      </c>
+      <c r="F109" s="314" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="315" t="s">
-        <v>333</v>
-      </c>
-      <c r="F110" s="319" t="s">
-        <v>336</v>
+      <c r="E110" s="311" t="s">
+        <v>328</v>
+      </c>
+      <c r="F110" s="315" t="s">
+        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D5BB88E-4386-4200-8868-5BA3E78E159D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB47F686-16B4-4C2A-B1EC-6CAF0A43D9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3830,29 +3830,29 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4312,13 +4312,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="346" t="s">
+      <c r="B18" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C18" s="346"/>
-      <c r="D18" s="346"/>
-      <c r="E18" s="346"/>
-      <c r="F18" s="346"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="C30" s="148">
         <f>C152</f>
-        <v>43.592757973888887</v>
+        <v>41.829260960684138</v>
       </c>
       <c r="D30" s="148" t="str">
         <f>D152</f>
@@ -4458,7 +4458,7 @@
         <v>441</v>
       </c>
       <c r="F30" s="307">
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4514,22 +4514,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="346" t="s">
+      <c r="B36" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C36" s="346"/>
-      <c r="D36" s="346"/>
-      <c r="E36" s="346"/>
-      <c r="F36" s="346"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="348" t="s">
+      <c r="B37" s="351" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="348"/>
-      <c r="D37" s="348"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="C37" s="351"/>
+      <c r="D37" s="351"/>
+      <c r="E37" s="351"/>
+      <c r="F37" s="351"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4541,13 +4541,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="347" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="347"/>
-      <c r="D40" s="347"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4567,13 +4567,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="347" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="347"/>
-      <c r="D43" s="347"/>
-      <c r="E43" s="347"/>
-      <c r="F43" s="347"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4602,13 +4602,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="347" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="347"/>
-      <c r="D47" s="347"/>
-      <c r="E47" s="347"/>
-      <c r="F47" s="347"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4624,13 +4624,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="347" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="347"/>
-      <c r="D50" s="347"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4694,13 +4694,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="347" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="347"/>
-      <c r="D58" s="347"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4716,7 +4716,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="347" t="s">
+      <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
       <c r="C61" s="350"/>
@@ -4738,22 +4738,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="348" t="s">
         <v>346</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="346" t="s">
+      <c r="B65" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C65" s="346"/>
-      <c r="D65" s="346"/>
-      <c r="E65" s="346"/>
-      <c r="F65" s="346"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4814,22 +4814,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="346" t="s">
+      <c r="B74" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C74" s="346"/>
-      <c r="D74" s="346"/>
-      <c r="E74" s="346"/>
-      <c r="F74" s="346"/>
+      <c r="C74" s="348"/>
+      <c r="D74" s="348"/>
+      <c r="E74" s="348"/>
+      <c r="F74" s="348"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="348" t="s">
+      <c r="B75" s="351" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="348"/>
-      <c r="D75" s="348"/>
-      <c r="E75" s="348"/>
-      <c r="F75" s="348"/>
+      <c r="C75" s="351"/>
+      <c r="D75" s="351"/>
+      <c r="E75" s="351"/>
+      <c r="F75" s="351"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4873,22 +4873,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="346" t="s">
+      <c r="B83" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C83" s="346"/>
-      <c r="D83" s="346"/>
-      <c r="E83" s="346"/>
-      <c r="F83" s="346"/>
+      <c r="C83" s="348"/>
+      <c r="D83" s="348"/>
+      <c r="E83" s="348"/>
+      <c r="F83" s="348"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="346" t="s">
+      <c r="B84" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C84" s="346"/>
-      <c r="D84" s="346"/>
-      <c r="E84" s="346"/>
-      <c r="F84" s="346"/>
+      <c r="C84" s="348"/>
+      <c r="D84" s="348"/>
+      <c r="E84" s="348"/>
+      <c r="F84" s="348"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4925,13 +4925,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="346" t="s">
+      <c r="B91" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C91" s="346"/>
-      <c r="D91" s="346"/>
-      <c r="E91" s="346"/>
-      <c r="F91" s="346"/>
+      <c r="C91" s="348"/>
+      <c r="D91" s="348"/>
+      <c r="E91" s="348"/>
+      <c r="F91" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4944,13 +4944,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="346" t="s">
+      <c r="B95" s="348" t="s">
         <v>347</v>
       </c>
-      <c r="C95" s="346"/>
-      <c r="D95" s="346"/>
-      <c r="E95" s="346"/>
-      <c r="F95" s="346"/>
+      <c r="C95" s="348"/>
+      <c r="D95" s="348"/>
+      <c r="E95" s="348"/>
+      <c r="F95" s="348"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5081,13 +5081,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="348" t="s">
         <v>369</v>
       </c>
-      <c r="C111" s="346"/>
-      <c r="D111" s="346"/>
-      <c r="E111" s="346"/>
-      <c r="F111" s="346"/>
+      <c r="C111" s="348"/>
+      <c r="D111" s="348"/>
+      <c r="E111" s="348"/>
+      <c r="F111" s="348"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5126,13 +5126,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="347" t="s">
+      <c r="B118" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C118" s="347"/>
-      <c r="D118" s="347"/>
-      <c r="E118" s="347"/>
-      <c r="F118" s="347"/>
+      <c r="C118" s="349"/>
+      <c r="D118" s="349"/>
+      <c r="E118" s="349"/>
+      <c r="F118" s="349"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="258" t="s">
@@ -5275,13 +5275,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="351" t="s">
+      <c r="B129" s="352" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="351"/>
-      <c r="D129" s="351"/>
-      <c r="E129" s="351"/>
-      <c r="F129" s="351"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5294,22 +5294,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="349" t="s">
+      <c r="B133" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="349"/>
-      <c r="D133" s="349"/>
-      <c r="E133" s="349"/>
-      <c r="F133" s="349"/>
+      <c r="C133" s="353"/>
+      <c r="D133" s="353"/>
+      <c r="E133" s="353"/>
+      <c r="F133" s="353"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="348" t="s">
         <v>372</v>
       </c>
-      <c r="C134" s="346"/>
-      <c r="D134" s="346"/>
-      <c r="E134" s="346"/>
-      <c r="F134" s="346"/>
+      <c r="C134" s="348"/>
+      <c r="D134" s="348"/>
+      <c r="E134" s="348"/>
+      <c r="F134" s="348"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="C149" s="332">
         <f>Scenarios!C90</f>
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="150" spans="2:4">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="C150" s="240">
         <f>Scenarios!C91</f>
-        <v>5.0555555555555554</v>
+        <v>4.9209619772758479</v>
       </c>
     </row>
     <row r="151" spans="2:4">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="C151" s="240">
         <f>Scenarios!C92</f>
-        <v>38.537202418333329</v>
+        <v>36.908298983408294</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="C152" s="239">
         <f>Scenarios!C93</f>
-        <v>43.592757973888887</v>
+        <v>41.829260960684138</v>
       </c>
       <c r="D152" s="336" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.345378260199104</v>
+        <v>0.37186026171892639</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5642,13 +5642,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="353" t="s">
+      <c r="B174" s="347" t="s">
         <v>379</v>
       </c>
-      <c r="C174" s="346"/>
-      <c r="D174" s="346"/>
-      <c r="E174" s="346"/>
-      <c r="F174" s="346"/>
+      <c r="C174" s="348"/>
+      <c r="D174" s="348"/>
+      <c r="E174" s="348"/>
+      <c r="F174" s="348"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
@@ -5685,13 +5685,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="347" t="s">
+      <c r="B183" s="349" t="s">
         <v>384</v>
       </c>
-      <c r="C183" s="347"/>
-      <c r="D183" s="347"/>
-      <c r="E183" s="347"/>
-      <c r="F183" s="347"/>
+      <c r="C183" s="349"/>
+      <c r="D183" s="349"/>
+      <c r="E183" s="349"/>
+      <c r="F183" s="349"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5699,22 +5699,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="352" t="s">
+      <c r="B186" s="346" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="352"/>
-      <c r="D186" s="352"/>
-      <c r="E186" s="352"/>
-      <c r="F186" s="352"/>
+      <c r="C186" s="346"/>
+      <c r="D186" s="346"/>
+      <c r="E186" s="346"/>
+      <c r="F186" s="346"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="352" t="s">
+      <c r="B187" s="346" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="352"/>
-      <c r="D187" s="352"/>
-      <c r="E187" s="352"/>
-      <c r="F187" s="352"/>
+      <c r="C187" s="346"/>
+      <c r="D187" s="346"/>
+      <c r="E187" s="346"/>
+      <c r="F187" s="346"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5738,17 +5738,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5765,6 +5754,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -17739,7 +17739,7 @@
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.2</v>
+        <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -17748,7 +17748,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>5.0555555555555554</v>
+        <v>4.9209619772758479</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -17760,7 +17760,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>38.537202418333329</v>
+        <v>36.908298983408294</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -17770,7 +17770,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>43.592757973888887</v>
+        <v>41.829260960684138</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -17781,7 +17781,7 @@
       </c>
       <c r="F93" s="325">
         <f>(1-C93/C60)</f>
-        <v>0.345378260199104</v>
+        <v>0.37186026171892639</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB47F686-16B4-4C2A-B1EC-6CAF0A43D9C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB8584B-9B07-472F-8517-43CCB6DEEC23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3111,7 +3111,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="358">
+  <cellXfs count="360">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3745,7 +3745,6 @@
     <xf numFmtId="37" fontId="48" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="10" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="175" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -3809,9 +3808,6 @@
     <xf numFmtId="9" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="175" fontId="46" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3830,29 +3826,39 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="174" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4160,7 +4166,7 @@
         <v>45780</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="326" t="s">
+      <c r="E1" s="325" t="s">
         <v>356</v>
       </c>
       <c r="F1" s="281" t="s">
@@ -4194,7 +4200,7 @@
       <c r="B5" s="4" t="s">
         <v>318</v>
       </c>
-      <c r="C5" s="328" t="s">
+      <c r="C5" s="327" t="s">
         <v>446</v>
       </c>
     </row>
@@ -4347,7 +4353,7 @@
       <c r="D22" s="1" t="s">
         <v>444</v>
       </c>
-      <c r="E22" s="345" t="s">
+      <c r="E22" s="343" t="s">
         <v>443</v>
       </c>
     </row>
@@ -4378,7 +4384,7 @@
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E25" s="335" t="str">
+      <c r="E25" s="334" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
@@ -4388,14 +4394,14 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
       </c>
-      <c r="C26" s="341">
+      <c r="C26" s="339">
         <f>C127</f>
         <v>66.592285778879997</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="E26" s="337">
+      <c r="E26" s="336">
         <f ca="1">Scenarios!C87</f>
         <v>9.4210132770872423E-2</v>
       </c>
@@ -4408,18 +4414,18 @@
       <c r="B28" s="45" t="s">
         <v>437</v>
       </c>
-      <c r="C28" s="268" t="str">
+      <c r="C28" s="344" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>600132.SS (CNY)</v>
       </c>
-      <c r="D28" s="268" t="str">
+      <c r="D28" s="344" t="str">
         <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
         <v/>
       </c>
-      <c r="E28" s="342" t="s">
+      <c r="E28" s="340" t="s">
         <v>433</v>
       </c>
-      <c r="F28" s="340">
+      <c r="F28" s="338">
         <v>3</v>
       </c>
     </row>
@@ -4427,18 +4433,18 @@
       <c r="B29" s="1" t="s">
         <v>429</v>
       </c>
-      <c r="C29" s="339">
+      <c r="C29" s="345">
         <f>C144</f>
         <v>28.081736799883384</v>
       </c>
-      <c r="D29" s="339" t="str">
+      <c r="D29" s="345" t="str">
         <f>D144</f>
         <v/>
       </c>
-      <c r="E29" s="343" t="s">
+      <c r="E29" s="341" t="s">
         <v>428</v>
       </c>
-      <c r="F29" s="338">
+      <c r="F29" s="337">
         <v>0.4</v>
       </c>
     </row>
@@ -4446,18 +4452,18 @@
       <c r="B30" s="1" t="s">
         <v>430</v>
       </c>
-      <c r="C30" s="148">
+      <c r="C30" s="346">
         <f>C152</f>
         <v>41.829260960684138</v>
       </c>
-      <c r="D30" s="148" t="str">
+      <c r="D30" s="346" t="str">
         <f>D152</f>
         <v/>
       </c>
-      <c r="E30" s="344" t="s">
+      <c r="E30" s="342" t="s">
         <v>441</v>
       </c>
-      <c r="F30" s="307">
+      <c r="F30" s="347">
         <v>0.21740000000000001</v>
       </c>
     </row>
@@ -4465,18 +4471,18 @@
       <c r="B31" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="C31" s="148">
+      <c r="C31" s="346">
         <f>C160</f>
         <v>59.048136223898794</v>
       </c>
-      <c r="D31" s="148" t="str">
+      <c r="D31" s="346" t="str">
         <f>D160</f>
         <v/>
       </c>
-      <c r="E31" s="344" t="s">
+      <c r="E31" s="342" t="s">
         <v>440</v>
       </c>
-      <c r="F31" s="307">
+      <c r="F31" s="347">
         <v>0.08</v>
       </c>
     </row>
@@ -4484,18 +4490,18 @@
       <c r="B32" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="C32" s="148">
+      <c r="C32" s="346">
         <f>C168</f>
         <v>53.520960428876833</v>
       </c>
-      <c r="D32" s="148" t="str">
+      <c r="D32" s="346" t="str">
         <f>D168</f>
         <v/>
       </c>
-      <c r="E32" s="344" t="s">
+      <c r="E32" s="342" t="s">
         <v>442</v>
       </c>
-      <c r="F32" s="307">
+      <c r="F32" s="347">
         <v>0.1174</v>
       </c>
     </row>
@@ -4523,13 +4529,13 @@
       <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="351" t="s">
+      <c r="B37" s="350" t="s">
         <v>342</v>
       </c>
-      <c r="C37" s="351"/>
-      <c r="D37" s="351"/>
-      <c r="E37" s="351"/>
-      <c r="F37" s="351"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4636,7 +4642,7 @@
       <c r="B51" s="47" t="s">
         <v>343</v>
       </c>
-      <c r="C51" s="318">
+      <c r="C51" s="317">
         <f>Normalized_FCF!C48</f>
         <v>38554805.997018404</v>
       </c>
@@ -4644,14 +4650,14 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="317"/>
-      <c r="F51" s="317"/>
+      <c r="E51" s="316"/>
+      <c r="F51" s="316"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>344</v>
       </c>
-      <c r="C52" s="318">
+      <c r="C52" s="317">
         <f>Normalized_FCF!C47</f>
         <v>-7672861</v>
       </c>
@@ -4659,8 +4665,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E52" s="317"/>
-      <c r="F52" s="317"/>
+      <c r="E52" s="316"/>
+      <c r="F52" s="316"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4719,10 +4725,10 @@
       <c r="B61" s="349" t="s">
         <v>341</v>
       </c>
-      <c r="C61" s="350"/>
-      <c r="D61" s="350"/>
-      <c r="E61" s="350"/>
-      <c r="F61" s="350"/>
+      <c r="C61" s="352"/>
+      <c r="D61" s="352"/>
+      <c r="E61" s="352"/>
+      <c r="F61" s="352"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4823,13 +4829,13 @@
       <c r="F74" s="348"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="351" t="s">
+      <c r="B75" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="351"/>
-      <c r="D75" s="351"/>
-      <c r="E75" s="351"/>
-      <c r="F75" s="351"/>
+      <c r="C75" s="350"/>
+      <c r="D75" s="350"/>
+      <c r="E75" s="350"/>
+      <c r="F75" s="350"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4867,7 +4873,7 @@
       <c r="C81" s="122"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="B82" s="327" t="s">
+      <c r="B82" s="326" t="s">
         <v>359</v>
       </c>
       <c r="C82" s="122"/>
@@ -4979,28 +4985,28 @@
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="331" t="s">
+      <c r="B98" s="330" t="s">
         <v>407</v>
       </c>
-      <c r="C98" s="332">
+      <c r="C98" s="331">
         <f>BS!G30/BS!G27</f>
         <v>3.4701988818540461</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="331" t="s">
+      <c r="B99" s="330" t="s">
         <v>408</v>
       </c>
-      <c r="C99" s="332">
+      <c r="C99" s="331">
         <f>BS!G31/BS!G27</f>
         <v>5.0341856510546588E-2</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="331" t="s">
+      <c r="B100" s="330" t="s">
         <v>410</v>
       </c>
-      <c r="C100" s="333">
+      <c r="C100" s="332">
         <f>BS!C50</f>
         <v>3.9546057100127742E-2</v>
       </c>
@@ -5103,7 +5109,7 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="331" t="s">
+      <c r="B114" s="330" t="s">
         <v>409</v>
       </c>
       <c r="C114" s="248">
@@ -5275,13 +5281,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="352" t="s">
+      <c r="B129" s="353" t="s">
         <v>373</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="247" t="s">
@@ -5294,13 +5300,13 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="353" t="s">
+      <c r="B133" s="351" t="s">
         <v>371</v>
       </c>
-      <c r="C133" s="353"/>
-      <c r="D133" s="353"/>
-      <c r="E133" s="353"/>
-      <c r="F133" s="353"/>
+      <c r="C133" s="351"/>
+      <c r="D133" s="351"/>
+      <c r="E133" s="351"/>
+      <c r="F133" s="351"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
       <c r="B134" s="348" t="s">
@@ -5364,7 +5370,7 @@
       <c r="B141" s="1" t="s">
         <v>411</v>
       </c>
-      <c r="C141" s="332">
+      <c r="C141" s="331">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5397,7 +5403,7 @@
         <f>Scenarios!C83</f>
         <v>28.081736799883384</v>
       </c>
-      <c r="D144" s="336" t="str">
+      <c r="D144" s="335" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
@@ -5406,11 +5412,11 @@
       <c r="B145" s="286" t="s">
         <v>420</v>
       </c>
-      <c r="C145" s="334" t="str">
+      <c r="C145" s="333" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D145" s="334" t="str">
+      <c r="D145" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5433,7 +5439,7 @@
       <c r="B149" s="1" t="s">
         <v>414</v>
       </c>
-      <c r="C149" s="332">
+      <c r="C149" s="331">
         <f>Scenarios!C90</f>
         <v>0.21740000000000001</v>
       </c>
@@ -5466,7 +5472,7 @@
         <f>Scenarios!C93</f>
         <v>41.829260960684138</v>
       </c>
-      <c r="D152" s="336" t="str">
+      <c r="D152" s="335" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
@@ -5475,11 +5481,11 @@
       <c r="B153" s="286" t="s">
         <v>420</v>
       </c>
-      <c r="C153" s="334" t="str">
+      <c r="C153" s="333" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D153" s="334" t="str">
+      <c r="D153" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5535,7 +5541,7 @@
         <f>Scenarios!C99</f>
         <v>59.048136223898794</v>
       </c>
-      <c r="D160" s="336" t="str">
+      <c r="D160" s="335" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
@@ -5544,11 +5550,11 @@
       <c r="B161" s="286" t="s">
         <v>420</v>
       </c>
-      <c r="C161" s="334" t="str">
+      <c r="C161" s="333" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D161" s="334" t="str">
+      <c r="D161" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5604,7 +5610,7 @@
         <f>Scenarios!C105</f>
         <v>53.520960428876833</v>
       </c>
-      <c r="D168" s="336" t="str">
+      <c r="D168" s="335" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
@@ -5613,11 +5619,11 @@
       <c r="B169" s="286" t="s">
         <v>420</v>
       </c>
-      <c r="C169" s="334" t="str">
+      <c r="C169" s="333" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D169" s="334" t="str">
+      <c r="D169" s="333" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5642,7 +5648,7 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="347" t="s">
+      <c r="B174" s="355" t="s">
         <v>379</v>
       </c>
       <c r="C174" s="348"/>
@@ -5656,13 +5662,13 @@
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="350" t="s">
+      <c r="B177" s="352" t="s">
         <v>383</v>
       </c>
-      <c r="C177" s="350"/>
-      <c r="D177" s="350"/>
-      <c r="E177" s="350"/>
-      <c r="F177" s="350"/>
+      <c r="C177" s="352"/>
+      <c r="D177" s="352"/>
+      <c r="E177" s="352"/>
+      <c r="F177" s="352"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
@@ -5699,22 +5705,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="346" t="s">
+      <c r="B186" s="354" t="s">
         <v>385</v>
       </c>
-      <c r="C186" s="346"/>
-      <c r="D186" s="346"/>
-      <c r="E186" s="346"/>
-      <c r="F186" s="346"/>
+      <c r="C186" s="354"/>
+      <c r="D186" s="354"/>
+      <c r="E186" s="354"/>
+      <c r="F186" s="354"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="346" t="s">
+      <c r="B187" s="354" t="s">
         <v>386</v>
       </c>
-      <c r="C187" s="346"/>
-      <c r="D187" s="346"/>
-      <c r="E187" s="346"/>
-      <c r="F187" s="346"/>
+      <c r="C187" s="354"/>
+      <c r="D187" s="354"/>
+      <c r="E187" s="354"/>
+      <c r="F187" s="354"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5738,6 +5744,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5754,17 +5771,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -8209,11 +8215,11 @@
         <f t="shared" si="40"/>
         <v>58261577</v>
       </c>
-      <c r="I77" s="330"/>
-      <c r="J77" s="330"/>
-      <c r="K77" s="330"/>
-      <c r="L77" s="330"/>
-      <c r="M77" s="330"/>
+      <c r="I77" s="329"/>
+      <c r="J77" s="329"/>
+      <c r="K77" s="329"/>
+      <c r="L77" s="329"/>
+      <c r="M77" s="329"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8243,11 +8249,11 @@
         <f t="shared" si="40"/>
         <v>364381375</v>
       </c>
-      <c r="I78" s="330"/>
-      <c r="J78" s="330"/>
-      <c r="K78" s="330"/>
-      <c r="L78" s="330"/>
-      <c r="M78" s="330"/>
+      <c r="I78" s="329"/>
+      <c r="J78" s="329"/>
+      <c r="K78" s="329"/>
+      <c r="L78" s="329"/>
+      <c r="M78" s="329"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -9472,7 +9478,7 @@
         <v>325</v>
       </c>
       <c r="C76" s="287"/>
-      <c r="D76" s="323">
+      <c r="D76" s="322">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>1</v>
       </c>
@@ -11543,104 +11549,104 @@
         <v>38554805.997018404</v>
       </c>
       <c r="E48" s="298"/>
-      <c r="G48" s="324">
+      <c r="G48" s="323">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>38554805.997018404</v>
       </c>
-      <c r="H48" s="324">
+      <c r="H48" s="323">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>66982141.426252395</v>
       </c>
-      <c r="I48" s="324">
+      <c r="I48" s="323">
         <f t="shared" si="19"/>
         <v>61731794.960215338</v>
       </c>
-      <c r="J48" s="324">
+      <c r="J48" s="323">
         <f t="shared" si="19"/>
         <v>33863778.321634412</v>
       </c>
-      <c r="K48" s="324">
+      <c r="K48" s="323">
         <f t="shared" si="19"/>
         <v>41746958.77028092</v>
       </c>
-      <c r="L48" s="324">
+      <c r="L48" s="323">
         <f t="shared" si="19"/>
         <v>8061746.2233673697</v>
       </c>
-      <c r="M48" s="324">
+      <c r="M48" s="323">
         <f t="shared" si="19"/>
         <v>6208975.7821457442</v>
       </c>
-      <c r="N48" s="324">
+      <c r="N48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="324">
+      <c r="O48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="324">
+      <c r="P48" s="323">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="324" t="str">
+      <c r="Q48" s="323" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="319" t="s">
+      <c r="B49" s="318" t="s">
         <v>345</v>
       </c>
-      <c r="C49" s="320">
+      <c r="C49" s="319">
         <f>BS!$C$66*C53</f>
         <v>41044772</v>
       </c>
-      <c r="D49" s="321"/>
-      <c r="E49" s="322"/>
-      <c r="F49" s="321"/>
-      <c r="G49" s="320">
+      <c r="D49" s="320"/>
+      <c r="E49" s="321"/>
+      <c r="F49" s="320"/>
+      <c r="G49" s="319">
         <f>Data!C52</f>
         <v>41044772</v>
       </c>
-      <c r="H49" s="320">
+      <c r="H49" s="319">
         <f>Data!D52</f>
         <v>71308016</v>
       </c>
-      <c r="I49" s="320">
+      <c r="I49" s="319">
         <f>Data!E52</f>
         <v>65718589</v>
       </c>
-      <c r="J49" s="320">
+      <c r="J49" s="319">
         <f>Data!F52</f>
         <v>36050786</v>
       </c>
-      <c r="K49" s="320">
+      <c r="K49" s="319">
         <f>Data!G52</f>
         <v>44443082</v>
       </c>
-      <c r="L49" s="320">
+      <c r="L49" s="319">
         <f>Data!H52</f>
         <v>8582394</v>
       </c>
-      <c r="M49" s="320">
+      <c r="M49" s="319">
         <f>Data!I52</f>
         <v>6609967</v>
       </c>
-      <c r="N49" s="320">
+      <c r="N49" s="319">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="320">
+      <c r="O49" s="319">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="320">
+      <c r="P49" s="319">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="320" t="str">
+      <c r="Q49" s="319" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -14004,47 +14010,47 @@
       </c>
       <c r="C113" s="170"/>
       <c r="E113" s="298"/>
-      <c r="G113" s="329">
+      <c r="G113" s="328">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>1.1301097053348144</v>
       </c>
-      <c r="H113" s="329">
+      <c r="H113" s="328">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>1.1421244767311443</v>
       </c>
-      <c r="I113" s="329">
+      <c r="I113" s="328">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>1.4506354245537583</v>
       </c>
-      <c r="J113" s="329">
+      <c r="J113" s="328">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>1.4858503664510887</v>
       </c>
-      <c r="K113" s="329">
+      <c r="K113" s="328">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>2.1056296742310616</v>
       </c>
-      <c r="L113" s="329">
+      <c r="L113" s="328">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>0.96876332816786648</v>
       </c>
-      <c r="M113" s="329">
+      <c r="M113" s="328">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>1.767034158859303</v>
       </c>
-      <c r="N113" s="329">
+      <c r="N113" s="328">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>2.5144917688633623</v>
       </c>
-      <c r="O113" s="329">
+      <c r="O113" s="328">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>4.0690767846879998</v>
       </c>
-      <c r="P113" s="329">
+      <c r="P113" s="328">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v>-2.9196128327089879</v>
       </c>
-      <c r="Q113" s="329" t="str">
+      <c r="Q113" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -14056,47 +14062,47 @@
       </c>
       <c r="C114" s="170"/>
       <c r="E114" s="298"/>
-      <c r="G114" s="329">
+      <c r="G114" s="328">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.0944103829432141</v>
       </c>
-      <c r="H114" s="329">
+      <c r="H114" s="328">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.1613302966984029</v>
       </c>
-      <c r="I114" s="329">
+      <c r="I114" s="328">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>1.477203347027797</v>
       </c>
-      <c r="J114" s="329">
+      <c r="J114" s="328">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>1.5005063764384885</v>
       </c>
-      <c r="K114" s="329">
+      <c r="K114" s="328">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>2.773447584133756</v>
       </c>
-      <c r="L114" s="329">
+      <c r="L114" s="328">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>1.5109716987792317</v>
       </c>
-      <c r="M114" s="329">
+      <c r="M114" s="328">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>1.7382339197122179</v>
       </c>
-      <c r="N114" s="329">
+      <c r="N114" s="328">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>2.378364555476101</v>
       </c>
-      <c r="O114" s="329">
+      <c r="O114" s="328">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>1.6724741518288628</v>
       </c>
-      <c r="P114" s="329">
+      <c r="P114" s="328">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>2.3783234522476708</v>
       </c>
-      <c r="Q114" s="329" t="str">
+      <c r="Q114" s="328" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
@@ -15390,10 +15396,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="356" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="354"/>
+      <c r="F6" s="356"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15408,8 +15414,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
+      <c r="E7" s="356"/>
+      <c r="F7" s="356"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15424,8 +15430,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="354"/>
-      <c r="F8" s="354"/>
+      <c r="E8" s="356"/>
+      <c r="F8" s="356"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15440,8 +15446,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="354"/>
-      <c r="F9" s="354"/>
+      <c r="E9" s="356"/>
+      <c r="F9" s="356"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -16935,11 +16941,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356" t="str">
+      <c r="E7" s="358" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 重庆啤酒(600132.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="356"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="274">
         <v>4</v>
       </c>
@@ -16960,8 +16966,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="274">
         <v>5</v>
       </c>
@@ -16982,8 +16988,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="274">
         <v>6</v>
       </c>
@@ -16993,8 +16999,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="356"/>
-      <c r="F10" s="356"/>
+      <c r="E10" s="358"/>
+      <c r="F10" s="358"/>
       <c r="H10" s="274">
         <v>7</v>
       </c>
@@ -17007,8 +17013,8 @@
       <c r="B11" s="160" t="s">
         <v>278</v>
       </c>
-      <c r="E11" s="356"/>
-      <c r="F11" s="356"/>
+      <c r="E11" s="358"/>
+      <c r="F11" s="358"/>
       <c r="H11" s="274">
         <v>8</v>
       </c>
@@ -17026,8 +17032,8 @@
         <v>3.7342435425912202E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
+      <c r="E12" s="358"/>
+      <c r="F12" s="358"/>
       <c r="H12" s="274">
         <v>9</v>
       </c>
@@ -17044,8 +17050,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>2.3730241339145586E-2</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="356"/>
+      <c r="E13" s="358"/>
+      <c r="F13" s="358"/>
       <c r="H13" s="274">
         <v>10</v>
       </c>
@@ -17062,8 +17068,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-7.4877931429291333E-3</v>
       </c>
-      <c r="E14" s="356"/>
-      <c r="F14" s="356"/>
+      <c r="E14" s="358"/>
+      <c r="F14" s="358"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -17089,21 +17095,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="356" t="s">
+      <c r="E18" s="358" t="s">
         <v>333</v>
       </c>
-      <c r="F18" s="357"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="357"/>
-      <c r="F19" s="357"/>
+      <c r="E19" s="359"/>
+      <c r="F19" s="359"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>306</v>
       </c>
-      <c r="E20" s="357"/>
-      <c r="F20" s="357"/>
+      <c r="E20" s="359"/>
+      <c r="F20" s="359"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -17117,8 +17123,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="357"/>
-      <c r="F21" s="357"/>
+      <c r="E21" s="359"/>
+      <c r="F21" s="359"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -17132,8 +17138,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="357"/>
-      <c r="F22" s="357"/>
+      <c r="E22" s="359"/>
+      <c r="F22" s="359"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17153,8 +17159,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="355"/>
+      <c r="E25" s="357"/>
+      <c r="F25" s="357"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17164,8 +17170,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
+      <c r="E26" s="357"/>
+      <c r="F26" s="357"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -17179,8 +17185,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="355"/>
-      <c r="F27" s="355"/>
+      <c r="E27" s="357"/>
+      <c r="F27" s="357"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17190,8 +17196,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="355"/>
-      <c r="F28" s="355"/>
+      <c r="E28" s="357"/>
+      <c r="F28" s="357"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17211,8 +17217,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="355"/>
-      <c r="F31" s="355"/>
+      <c r="E31" s="357"/>
+      <c r="F31" s="357"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17222,8 +17228,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="355"/>
-      <c r="F32" s="355"/>
+      <c r="E32" s="357"/>
+      <c r="F32" s="357"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -17237,8 +17243,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="355"/>
-      <c r="F33" s="355"/>
+      <c r="E33" s="357"/>
+      <c r="F33" s="357"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17248,8 +17254,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="355"/>
-      <c r="F34" s="355"/>
+      <c r="E34" s="357"/>
+      <c r="F34" s="357"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17269,8 +17275,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="355"/>
-      <c r="F37" s="355"/>
+      <c r="E37" s="357"/>
+      <c r="F37" s="357"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17280,8 +17286,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="355"/>
-      <c r="F38" s="355"/>
+      <c r="E38" s="357"/>
+      <c r="F38" s="357"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -17295,8 +17301,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="355"/>
-      <c r="F39" s="355"/>
+      <c r="E39" s="357"/>
+      <c r="F39" s="357"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17307,8 +17313,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="355"/>
-      <c r="F40" s="355"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17370,8 +17376,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="355"/>
-      <c r="F49" s="355"/>
+      <c r="E49" s="357"/>
+      <c r="F49" s="357"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17381,8 +17387,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="355"/>
-      <c r="F50" s="355"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -17396,8 +17402,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="355"/>
-      <c r="F51" s="355"/>
+      <c r="E51" s="357"/>
+      <c r="F51" s="357"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17407,8 +17413,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="355"/>
-      <c r="F52" s="355"/>
+      <c r="E52" s="357"/>
+      <c r="F52" s="357"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
@@ -17428,8 +17434,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="355"/>
-      <c r="F55" s="355"/>
+      <c r="E55" s="357"/>
+      <c r="F55" s="357"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17439,8 +17445,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="355"/>
-      <c r="F56" s="355"/>
+      <c r="E56" s="357"/>
+      <c r="F56" s="357"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -17454,8 +17460,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="355"/>
-      <c r="F57" s="355"/>
+      <c r="E57" s="357"/>
+      <c r="F57" s="357"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17465,8 +17471,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="355"/>
-      <c r="F58" s="355"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17483,7 +17489,7 @@
       <c r="E60" s="100" t="s">
         <v>299</v>
       </c>
-      <c r="F60" s="308">
+      <c r="F60" s="307">
         <f>Thesis!F28</f>
         <v>3</v>
       </c>
@@ -17597,7 +17603,7 @@
       <c r="E72" s="135" t="s">
         <v>349</v>
       </c>
-      <c r="F72" s="325">
+      <c r="F72" s="324">
         <f>BS!D89/C60</f>
         <v>-8.7950215386604794E-4</v>
       </c>
@@ -17690,7 +17696,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="325">
+      <c r="F83" s="324">
         <f>(1-C83/C60)</f>
         <v>0.57830345555145946</v>
       </c>
@@ -17779,7 +17785,7 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="325">
+      <c r="F93" s="324">
         <f>(1-C93/C60)</f>
         <v>0.37186026171892639</v>
       </c>
@@ -17789,7 +17795,7 @@
         <v>400</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="312"/>
+      <c r="H95" s="311"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
@@ -17800,7 +17806,7 @@
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="312"/>
+      <c r="H96" s="311"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17812,7 +17818,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="312"/>
+      <c r="H97" s="311"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17824,7 +17830,7 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="312"/>
+      <c r="H98" s="311"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
@@ -17840,7 +17846,7 @@
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="325">
+      <c r="F99" s="324">
         <f>(1-C99/C60)</f>
         <v>0.1132886409700905</v>
       </c>
@@ -17896,7 +17902,7 @@
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="325">
+      <c r="F105" s="324">
         <f>(1-C105/C66)</f>
         <v>0.19636122353473784</v>
       </c>
@@ -17905,32 +17911,32 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="316" t="s">
+      <c r="E107" s="315" t="s">
         <v>327</v>
       </c>
-      <c r="F107" s="313"/>
+      <c r="F107" s="312"/>
     </row>
     <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="309" t="s">
+      <c r="E108" s="308" t="s">
         <v>328</v>
       </c>
-      <c r="F108" s="314" t="s">
+      <c r="F108" s="313" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="310" t="s">
+      <c r="E109" s="309" t="s">
         <v>328</v>
       </c>
-      <c r="F109" s="314" t="s">
+      <c r="F109" s="313" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="311" t="s">
+      <c r="E110" s="310" t="s">
         <v>328</v>
       </c>
-      <c r="F110" s="315" t="s">
+      <c r="F110" s="314" t="s">
         <v>331</v>
       </c>
     </row>

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,28 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB8584B-9B07-472F-8517-43CCB6DEEC23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F89B6DE-2979-4A3C-A4F7-D7D96D8E5CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
     <sheet name="Data" sheetId="4" r:id="rId2"/>
     <sheet name="BS" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
-    <sheet name="Valuation_Model" sheetId="8" r:id="rId5"/>
+    <sheet name="DCF" sheetId="8" r:id="rId5"/>
     <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Valuation_Model!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">Valuation_Model!$C$5</definedName>
+    <definedName name="Equity_Cost">DCF!$C$5</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">Valuation_Model!$F$4</definedName>
+    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4909,7 +4909,7 @@
         <v>283</v>
       </c>
       <c r="C87" s="248">
-        <f>Valuation_Model!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
+        <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>57.438828001604072</v>
       </c>
       <c r="D87" s="1" t="str">
@@ -4963,7 +4963,7 @@
         <v>256</v>
       </c>
       <c r="C96" s="188">
-        <f>Valuation_Model!C7</f>
+        <f>DCF!C7</f>
         <v>123521704.27</v>
       </c>
       <c r="D96" s="1" t="str">
@@ -5034,7 +5034,7 @@
         <v>267</v>
       </c>
       <c r="C104" s="188">
-        <f>Valuation_Model!C8</f>
+        <f>DCF!C8</f>
         <v>65618450.04890883</v>
       </c>
       <c r="D104" s="1" t="str">
@@ -5065,7 +5065,7 @@
         <v>258</v>
       </c>
       <c r="C108" s="188">
-        <f>Valuation_Model!C9</f>
+        <f>DCF!C9</f>
         <v>29558000.651999995</v>
       </c>
       <c r="D108" s="1" t="str">
@@ -5100,7 +5100,7 @@
         <v>282</v>
       </c>
       <c r="C113" s="248">
-        <f>Valuation_Model!C12</f>
+        <f>DCF!C12</f>
         <v>57.380259942830683</v>
       </c>
       <c r="D113" s="1" t="str">
@@ -5159,111 +5159,111 @@
     </row>
     <row r="121" spans="1:6">
       <c r="B121" s="253" t="str">
-        <f>Valuation_Model!B74</f>
+        <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
       <c r="C121" s="254">
-        <f>Valuation_Model!C74</f>
+        <f>DCF!C74</f>
         <v>0.1</v>
       </c>
       <c r="D121" s="255">
-        <f>Valuation_Model!D74</f>
+        <f>DCF!D74</f>
         <v>15</v>
       </c>
       <c r="E121" s="256" t="str">
-        <f>ROUND(Valuation_Model!E74,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
         <v>99.94 CNY</v>
       </c>
       <c r="F121" s="257">
-        <f>Valuation_Model!F74</f>
+        <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
     <row r="122" spans="1:6">
       <c r="B122" s="242" t="str">
-        <f>Valuation_Model!B75</f>
+        <f>DCF!B75</f>
         <v>Optimistic</v>
       </c>
       <c r="C122" s="243">
-        <f>Valuation_Model!C75</f>
+        <f>DCF!C75</f>
         <v>0.06</v>
       </c>
       <c r="D122" s="244">
-        <f>Valuation_Model!D75</f>
+        <f>DCF!D75</f>
         <v>10</v>
       </c>
       <c r="E122" s="245" t="str">
-        <f>ROUND(Valuation_Model!E75,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
         <v>69.66 CNY</v>
       </c>
       <c r="F122" s="246">
-        <f>Valuation_Model!F75</f>
+        <f>DCF!F75</f>
         <v>0.18</v>
       </c>
     </row>
     <row r="123" spans="1:6">
       <c r="B123" s="242" t="str">
-        <f>Valuation_Model!B76</f>
+        <f>DCF!B76</f>
         <v>Base</v>
       </c>
       <c r="C123" s="243">
-        <f>Valuation_Model!C76</f>
+        <f>DCF!C76</f>
         <v>0.04</v>
       </c>
       <c r="D123" s="244">
-        <f>Valuation_Model!D76</f>
+        <f>DCF!D76</f>
         <v>10</v>
       </c>
       <c r="E123" s="245" t="str">
-        <f>ROUND(Valuation_Model!E76,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
         <v>65.17 CNY</v>
       </c>
       <c r="F123" s="246">
-        <f>Valuation_Model!F76</f>
+        <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
     <row r="124" spans="1:6">
       <c r="B124" s="242" t="str">
-        <f>Valuation_Model!B77</f>
+        <f>DCF!B77</f>
         <v>Pessimistic</v>
       </c>
       <c r="C124" s="243">
-        <f>Valuation_Model!C77</f>
+        <f>DCF!C77</f>
         <v>0.02</v>
       </c>
       <c r="D124" s="244">
-        <f>Valuation_Model!D77</f>
+        <f>DCF!D77</f>
         <v>10</v>
       </c>
       <c r="E124" s="245" t="str">
-        <f>ROUND(Valuation_Model!E77,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
         <v>61.09 CNY</v>
       </c>
       <c r="F124" s="246">
-        <f>Valuation_Model!F77</f>
+        <f>DCF!F77</f>
         <v>0.18</v>
       </c>
     </row>
     <row r="125" spans="1:6">
       <c r="B125" s="242" t="str">
-        <f>Valuation_Model!B78</f>
+        <f>DCF!B78</f>
         <v>Devil's advocate</v>
       </c>
       <c r="C125" s="243">
-        <f>Valuation_Model!C78</f>
+        <f>DCF!C78</f>
         <v>0</v>
       </c>
       <c r="D125" s="244">
-        <f>Valuation_Model!D78</f>
+        <f>DCF!D78</f>
         <v>15</v>
       </c>
       <c r="E125" s="245" t="str">
-        <f>ROUND(Valuation_Model!E78,2)&amp;" "&amp;Market_currency</f>
+        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
         <v>57.38 CNY</v>
       </c>
       <c r="F125" s="246">
-        <f>Valuation_Model!F78</f>
+        <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
@@ -9581,7 +9581,7 @@
         <v>289</v>
       </c>
       <c r="C86" s="188">
-        <f>-Valuation_Model!C7*Exchange_Rate</f>
+        <f>-DCF!C7*Exchange_Rate</f>
         <v>-123521704.27</v>
       </c>
       <c r="D86" s="248">
@@ -9598,7 +9598,7 @@
         <v>290</v>
       </c>
       <c r="C87" s="188">
-        <f>Valuation_Model!C8*Exchange_Rate</f>
+        <f>DCF!C8*Exchange_Rate</f>
         <v>65618450.04890883</v>
       </c>
       <c r="D87" s="248">
@@ -9615,7 +9615,7 @@
         <v>190</v>
       </c>
       <c r="C88" s="188">
-        <f>Valuation_Model!C9*Exchange_Rate</f>
+        <f>DCF!C9*Exchange_Rate</f>
         <v>29558000.651999995</v>
       </c>
       <c r="D88" s="248">
@@ -15575,7 +15575,7 @@
         <v>2327476884.1218534</v>
       </c>
       <c r="D21" s="139">
-        <f>IF($C$17&lt;B21,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E21" s="125">
@@ -15597,7 +15597,7 @@
         <v>2435878819.4994731</v>
       </c>
       <c r="D22" s="139">
-        <f>IF($C$17&lt;B22,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E22" s="125">
@@ -15619,7 +15619,7 @@
         <v>2549329561.0215406</v>
       </c>
       <c r="D23" s="139">
-        <f>IF($C$17&lt;B23,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E23" s="125">
@@ -15641,7 +15641,7 @@
         <v>2668064256.1823821</v>
       </c>
       <c r="D24" s="139">
-        <f>IF($C$17&lt;B24,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E24" s="125">
@@ -15663,7 +15663,7 @@
         <v>2792329004.4405127</v>
       </c>
       <c r="D25" s="139">
-        <f>IF($C$17&lt;B25,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E25" s="125">
@@ -15685,7 +15685,7 @@
         <v>2922381367.3049536</v>
       </c>
       <c r="D26" s="139">
-        <f>IF($C$17&lt;B26,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E26" s="125">
@@ -15707,7 +15707,7 @@
         <v>3058490902.1787567</v>
       </c>
       <c r="D27" s="139">
-        <f>IF($C$17&lt;B27,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E27" s="125">
@@ -15729,7 +15729,7 @@
         <v>3200939721.066215</v>
       </c>
       <c r="D28" s="139">
-        <f>IF($C$17&lt;B28,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E28" s="125">
@@ -15751,7 +15751,7 @@
         <v>3350023075.3018012</v>
       </c>
       <c r="D29" s="139">
-        <f>IF($C$17&lt;B29,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E29" s="125">
@@ -15773,7 +15773,7 @@
         <v>3506049967.5127697</v>
       </c>
       <c r="D30" s="139">
-        <f>IF($C$17&lt;B30,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="E30" s="125">
@@ -15795,7 +15795,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="139">
-        <f>IF($C$17&lt;B31,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B31,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E31" s="125">
@@ -15817,7 +15817,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="139">
-        <f>IF($C$17&lt;B32,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B32,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E32" s="125">
@@ -15839,7 +15839,7 @@
         <v>0</v>
       </c>
       <c r="D33" s="139">
-        <f>IF($C$17&lt;B33,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B33,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E33" s="125">
@@ -15861,7 +15861,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="139">
-        <f>IF($C$17&lt;B34,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B34,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E34" s="125">
@@ -15883,7 +15883,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="139">
-        <f>IF($C$17&lt;B35,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B35,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E35" s="125">
@@ -15905,7 +15905,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="139">
-        <f>IF($C$17&lt;B36,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B36,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E36" s="125">
@@ -15927,7 +15927,7 @@
         <v>0</v>
       </c>
       <c r="D37" s="139">
-        <f>IF($C$17&lt;B37,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B37,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E37" s="125">
@@ -15949,7 +15949,7 @@
         <v>0</v>
       </c>
       <c r="D38" s="139">
-        <f>IF($C$17&lt;B38,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B38,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E38" s="125">
@@ -15971,7 +15971,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="139">
-        <f>IF($C$17&lt;B39,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B39,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E39" s="125">
@@ -15993,7 +15993,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="139">
-        <f>IF($C$17&lt;B40,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B40,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E40" s="125">
@@ -16015,7 +16015,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="139">
-        <f>IF($C$17&lt;B41,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B41,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E41" s="125">
@@ -16037,7 +16037,7 @@
         <v>0</v>
       </c>
       <c r="D42" s="139">
-        <f>IF($C$17&lt;B42,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B42,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E42" s="125">
@@ -16059,7 +16059,7 @@
         <v>0</v>
       </c>
       <c r="D43" s="139">
-        <f>IF($C$17&lt;B43,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B43,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E43" s="125">
@@ -16081,7 +16081,7 @@
         <v>0</v>
       </c>
       <c r="D44" s="139">
-        <f>IF($C$17&lt;B44,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B44,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E44" s="125">
@@ -16103,7 +16103,7 @@
         <v>0</v>
       </c>
       <c r="D45" s="139">
-        <f>IF($C$17&lt;B45,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B45,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E45" s="125">
@@ -16125,7 +16125,7 @@
         <v>0</v>
       </c>
       <c r="D46" s="139">
-        <f>IF($C$17&lt;B46,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B46,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E46" s="125">
@@ -16147,7 +16147,7 @@
         <v>0</v>
       </c>
       <c r="D47" s="139">
-        <f>IF($C$17&lt;B47,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B47,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E47" s="125">
@@ -16169,7 +16169,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="139">
-        <f>IF($C$17&lt;B48,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B48,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E48" s="125">
@@ -16191,7 +16191,7 @@
         <v>0</v>
       </c>
       <c r="D49" s="139">
-        <f>IF($C$17&lt;B49,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B49,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E49" s="125">
@@ -16213,7 +16213,7 @@
         <v>0</v>
       </c>
       <c r="D50" s="139">
-        <f>IF($C$17&lt;B50,0,Valuation_Model!$C$16)</f>
+        <f>IF($C$17&lt;B50,0,DCF!$C$16)</f>
         <v>0</v>
       </c>
       <c r="E50" s="125">
@@ -16914,7 +16914,7 @@
         <v>96</v>
       </c>
       <c r="C6" s="107">
-        <f>Valuation_Model!C3</f>
+        <f>DCF!C3</f>
         <v>1</v>
       </c>
       <c r="E6" s="100" t="s">
@@ -17131,7 +17131,7 @@
         <v>280</v>
       </c>
       <c r="C22" s="161">
-        <f>Valuation_Model!C12</f>
+        <f>DCF!C12</f>
         <v>57.380259942830683</v>
       </c>
       <c r="D22" t="str">
@@ -17178,7 +17178,7 @@
         <v>114</v>
       </c>
       <c r="C27" s="161">
-        <f>Valuation_Model!E76</f>
+        <f>DCF!E76</f>
         <v>65.168450335018306</v>
       </c>
       <c r="D27" s="161" t="str">
@@ -17236,7 +17236,7 @@
         <v>114</v>
       </c>
       <c r="C33" s="161">
-        <f>Valuation_Model!E77</f>
+        <f>DCF!E77</f>
         <v>61.088521054715052</v>
       </c>
       <c r="D33" t="str">
@@ -17294,7 +17294,7 @@
         <v>114</v>
       </c>
       <c r="C39" s="161">
-        <f>Valuation_Model!E75</f>
+        <f>DCF!E75</f>
         <v>69.664528319209367</v>
       </c>
       <c r="D39" t="str">
@@ -17395,7 +17395,7 @@
         <v>114</v>
       </c>
       <c r="C51" s="161">
-        <f>Valuation_Model!E78</f>
+        <f>DCF!E78</f>
         <v>57.380259942830648</v>
       </c>
       <c r="D51" t="str">
@@ -17453,7 +17453,7 @@
         <v>114</v>
       </c>
       <c r="C57" s="161">
-        <f>Valuation_Model!E74</f>
+        <f>DCF!E74</f>
         <v>99.935214270443552</v>
       </c>
       <c r="D57" t="str">
@@ -17541,7 +17541,7 @@
         <v>103</v>
       </c>
       <c r="C66" s="161">
-        <f>Valuation_Model!C18</f>
+        <f>DCF!C18</f>
         <v>66.598280217741973</v>
       </c>
       <c r="D66" s="161" t="str">

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F89B6DE-2979-4A3C-A4F7-D7D96D8E5CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CA0C0A-8F30-40C9-87B8-A6A7EA64FD9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc_v4\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64CA0C0A-8F30-40C9-87B8-A6A7EA64FD9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93311569-3698-49A7-AF86-745D9FC6BF54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -18,18 +18,21 @@
     <sheet name="BS" sheetId="3" r:id="rId3"/>
     <sheet name="Normalized_FCF" sheetId="2" r:id="rId4"/>
     <sheet name="DCF" sheetId="8" r:id="rId5"/>
-    <sheet name="Scenarios" sheetId="9" r:id="rId6"/>
+    <sheet name="DDM" sheetId="10" r:id="rId6"/>
+    <sheet name="Scenarios" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">DCF!$B$73:$H$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">DDM!$B$68:$H$68</definedName>
     <definedName name="Common_Shares">Thesis!$C$6</definedName>
-    <definedName name="Equity_Cost">DCF!$C$5</definedName>
+    <definedName name="Equity_Cost">Thesis!$C$80</definedName>
     <definedName name="Exchange_Rate">Thesis!$C$16</definedName>
     <definedName name="Market_currency">Thesis!$C$13</definedName>
     <definedName name="Market_Price">Thesis!$C$12</definedName>
     <definedName name="Reporting_currency">Thesis!$C$25</definedName>
     <definedName name="scaling_factor">Data!$C$3</definedName>
-    <definedName name="Terminal_Growth">DCF!$F$4</definedName>
+    <definedName name="Terminal_Growth">Thesis!$C$86</definedName>
+    <definedName name="valuation_method">Thesis!$E$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="461">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -1374,10 +1377,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>CAGR</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Market Price</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1387,10 +1386,6 @@
   </si>
   <si>
     <t>Prompt for fundamental Analysis</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>No Growth Equity Value per share =</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2410,25 +2405,55 @@
     <t>Benchmark yield</t>
   </si>
   <si>
+    <t>Valuation Method</t>
+  </si>
+  <si>
+    <t>Dividend</t>
+  </si>
+  <si>
+    <t>Dividend Value</t>
+  </si>
+  <si>
+    <t>No-Growth DDM</t>
+  </si>
+  <si>
+    <t>No-Growth DDM Valuation</t>
+  </si>
+  <si>
+    <t>Dividend Value per share</t>
+  </si>
+  <si>
+    <t>PV of Dividends</t>
+  </si>
+  <si>
+    <t>Dividends</t>
+  </si>
+  <si>
+    <t>YoY CAGR</t>
+  </si>
+  <si>
+    <t>Payout Ratio:</t>
+  </si>
+  <si>
+    <t>No Growth Equity Value per share =</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>重庆啤酒</t>
+  </si>
+  <si>
+    <t>600132.SS</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>CNS_03</t>
+  </si>
+  <si>
     <t>DCF</t>
-  </si>
-  <si>
-    <t>Valuation Method</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>重庆啤酒</t>
-  </si>
-  <si>
-    <t>600132.SS</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>CNS_03</t>
   </si>
   <si>
     <t>Latest Asset Value</t>
@@ -2444,7 +2469,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="18">
+  <numFmts count="19">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2463,6 +2488,7 @@
     <numFmt numFmtId="179" formatCode="&quot;every&quot;\ 0\ &quot;Months&quot;"/>
     <numFmt numFmtId="180" formatCode="0.0\x"/>
     <numFmt numFmtId="181" formatCode="0\x"/>
+    <numFmt numFmtId="182" formatCode="0.000000000000000%"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3111,7 +3137,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="362">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3617,9 +3643,6 @@
     <xf numFmtId="175" fontId="43" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="39" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="10" fontId="42" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3836,29 +3859,36 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="47" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3877,7 +3907,21 @@
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="8">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -3924,8 +3968,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFF0000"/>
       <color rgb="FF0000FF"/>
-      <color rgb="FFFF0000"/>
       <color rgb="FF003871"/>
       <color rgb="FF005078"/>
       <color rgb="FF002850"/>
@@ -4166,15 +4210,15 @@
         <v>45780</v>
       </c>
       <c r="D1" s="52"/>
-      <c r="E1" s="325" t="s">
-        <v>356</v>
-      </c>
-      <c r="F1" s="281" t="s">
-        <v>445</v>
+      <c r="E1" s="324" t="s">
+        <v>354</v>
+      </c>
+      <c r="F1" s="280" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
-      <c r="A2" s="247" t="s">
+      <c r="A2" s="246" t="s">
         <v>268</v>
       </c>
       <c r="B2" s="36"/>
@@ -4189,7 +4233,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C4" s="46"/>
       <c r="D4" s="5"/>
@@ -4198,10 +4242,10 @@
     </row>
     <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="C5" s="327" t="s">
-        <v>446</v>
+        <v>316</v>
+      </c>
+      <c r="C5" s="326" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -4215,9 +4259,9 @@
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="C7" s="277">
+        <v>308</v>
+      </c>
+      <c r="C7" s="276">
         <v>6</v>
       </c>
       <c r="D7" s="48"/>
@@ -4238,20 +4282,20 @@
     </row>
     <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
     <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="E11" s="34"/>
     </row>
@@ -4267,17 +4311,17 @@
     </row>
     <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C13" s="48" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
@@ -4291,7 +4335,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C15" s="32" t="str">
         <f>IF(C25=C13,C13,C25&amp;"/"&amp;C13)</f>
@@ -4318,73 +4362,77 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B18" s="348" t="s">
-        <v>362</v>
-      </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="B18" s="352" t="s">
+        <v>360</v>
+      </c>
+      <c r="C18" s="352"/>
+      <c r="D18" s="352"/>
+      <c r="E18" s="352"/>
+      <c r="F18" s="352"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C21" s="32" t="str">
         <f>IF(Scenarios!C69="Y",Scenarios!B69,"")&amp;IF(Scenarios!C70="Y",Scenarios!B70,"")&amp;IF(Scenarios!C71="Y",Scenarios!B71,"")&amp;" "&amp;IF(Scenarios!C72="Y",Scenarios!B72,"")</f>
         <v xml:space="preserve">Low Growth </v>
       </c>
-      <c r="E21" s="5"/>
+      <c r="D21" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="E21" s="342" t="s">
+        <v>457</v>
+      </c>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
       <c r="C22" s="48" t="s">
-        <v>449</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="E22" s="343" t="s">
-        <v>443</v>
-      </c>
+        <v>456</v>
+      </c>
+      <c r="D22" s="1" t="str">
+        <f>IF(valuation_method="DDM","DDM Terminal Value","")</f>
+        <v/>
+      </c>
+      <c r="E22" s="347"/>
     </row>
     <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="C23" s="291" t="s">
-        <v>445</v>
+        <v>436</v>
+      </c>
+      <c r="C23" s="290" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="C24" s="291" t="s">
-        <v>445</v>
+        <v>437</v>
+      </c>
+      <c r="C24" s="290" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="D25" s="32" t="str">
         <f>IF(D11="","",Market_currency&amp;"/"&amp;D13&amp;":")</f>
         <v/>
       </c>
-      <c r="E25" s="334" t="str">
+      <c r="E25" s="333" t="str">
         <f>IF(D11="","",1/Exchange_Rate*D16)</f>
         <v/>
       </c>
@@ -4394,14 +4442,14 @@
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
       </c>
-      <c r="C26" s="339">
+      <c r="C26" s="338">
         <f>C127</f>
         <v>66.592285778879997</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="E26" s="336">
+        <v>400</v>
+      </c>
+      <c r="E26" s="335">
         <f ca="1">Scenarios!C87</f>
         <v>9.4210132770872423E-2</v>
       </c>
@@ -4412,96 +4460,96 @@
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
-        <v>437</v>
-      </c>
-      <c r="C28" s="344" t="str">
+        <v>435</v>
+      </c>
+      <c r="C28" s="343" t="str">
         <f>C140&amp;" ("&amp;Market_currency&amp;")"</f>
         <v>600132.SS (CNY)</v>
       </c>
-      <c r="D28" s="344" t="str">
+      <c r="D28" s="343" t="str">
         <f>IF(D11="","",D140&amp;" ("&amp;D13&amp;")")</f>
         <v/>
       </c>
-      <c r="E28" s="340" t="s">
-        <v>433</v>
-      </c>
-      <c r="F28" s="338">
+      <c r="E28" s="339" t="s">
+        <v>431</v>
+      </c>
+      <c r="F28" s="337">
         <v>3</v>
       </c>
     </row>
     <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
-        <v>429</v>
-      </c>
-      <c r="C29" s="345">
+        <v>427</v>
+      </c>
+      <c r="C29" s="344">
         <f>C144</f>
         <v>28.081736799883384</v>
       </c>
-      <c r="D29" s="345" t="str">
+      <c r="D29" s="344" t="str">
         <f>D144</f>
         <v/>
       </c>
-      <c r="E29" s="341" t="s">
-        <v>428</v>
-      </c>
-      <c r="F29" s="337">
+      <c r="E29" s="340" t="s">
+        <v>426</v>
+      </c>
+      <c r="F29" s="336">
         <v>0.4</v>
       </c>
     </row>
     <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
-        <v>430</v>
-      </c>
-      <c r="C30" s="346">
+        <v>428</v>
+      </c>
+      <c r="C30" s="345">
         <f>C152</f>
         <v>41.829260960684138</v>
       </c>
-      <c r="D30" s="346" t="str">
+      <c r="D30" s="345" t="str">
         <f>D152</f>
         <v/>
       </c>
-      <c r="E30" s="342" t="s">
-        <v>441</v>
-      </c>
-      <c r="F30" s="347">
+      <c r="E30" s="341" t="s">
+        <v>439</v>
+      </c>
+      <c r="F30" s="346">
         <v>0.21740000000000001</v>
       </c>
     </row>
     <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="C31" s="346">
+        <v>429</v>
+      </c>
+      <c r="C31" s="345">
         <f>C160</f>
         <v>59.048136223898794</v>
       </c>
-      <c r="D31" s="346" t="str">
+      <c r="D31" s="345" t="str">
         <f>D160</f>
         <v/>
       </c>
-      <c r="E31" s="342" t="s">
-        <v>440</v>
-      </c>
-      <c r="F31" s="347">
+      <c r="E31" s="341" t="s">
+        <v>438</v>
+      </c>
+      <c r="F31" s="346">
         <v>0.08</v>
       </c>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="C32" s="346">
+        <v>430</v>
+      </c>
+      <c r="C32" s="345">
         <f>C168</f>
         <v>53.520960428876833</v>
       </c>
-      <c r="D32" s="346" t="str">
+      <c r="D32" s="345" t="str">
         <f>D168</f>
         <v/>
       </c>
-      <c r="E32" s="342" t="s">
-        <v>442</v>
-      </c>
-      <c r="F32" s="347">
+      <c r="E32" s="341" t="s">
+        <v>440</v>
+      </c>
+      <c r="F32" s="346">
         <v>0.1174</v>
       </c>
     </row>
@@ -4510,8 +4558,8 @@
       <c r="E33" s="5"/>
     </row>
     <row r="34" spans="1:6" ht="13.9">
-      <c r="A34" s="247" t="s">
-        <v>357</v>
+      <c r="A34" s="246" t="s">
+        <v>355</v>
       </c>
       <c r="B34" s="36"/>
       <c r="C34" s="36"/>
@@ -4520,22 +4568,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B36" s="348" t="s">
-        <v>363</v>
-      </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="B36" s="352" t="s">
+        <v>361</v>
+      </c>
+      <c r="C36" s="352"/>
+      <c r="D36" s="352"/>
+      <c r="E36" s="352"/>
+      <c r="F36" s="352"/>
     </row>
     <row r="37" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B37" s="350" t="s">
-        <v>342</v>
-      </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="B37" s="355" t="s">
+        <v>340</v>
+      </c>
+      <c r="C37" s="355"/>
+      <c r="D37" s="355"/>
+      <c r="E37" s="355"/>
+      <c r="F37" s="355"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="234" t="s">
@@ -4547,13 +4595,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="353" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="353"/>
+      <c r="D40" s="353"/>
+      <c r="E40" s="353"/>
+      <c r="F40" s="353"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4573,13 +4621,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="353" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="353"/>
+      <c r="D43" s="353"/>
+      <c r="E43" s="353"/>
+      <c r="F43" s="353"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4608,13 +4656,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="353" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="353"/>
+      <c r="D47" s="353"/>
+      <c r="E47" s="353"/>
+      <c r="F47" s="353"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4630,19 +4678,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="353" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="353"/>
+      <c r="D50" s="353"/>
+      <c r="E50" s="353"/>
+      <c r="F50" s="353"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
-        <v>343</v>
-      </c>
-      <c r="C51" s="317">
+        <v>341</v>
+      </c>
+      <c r="C51" s="316">
         <f>Normalized_FCF!C48</f>
         <v>38554805.997018404</v>
       </c>
@@ -4650,14 +4698,14 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="316"/>
-      <c r="F51" s="316"/>
+      <c r="E51" s="315"/>
+      <c r="F51" s="315"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
-        <v>344</v>
-      </c>
-      <c r="C52" s="317">
+        <v>342</v>
+      </c>
+      <c r="C52" s="316">
         <f>Normalized_FCF!C47</f>
         <v>-7672861</v>
       </c>
@@ -4665,8 +4713,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E52" s="316"/>
-      <c r="F52" s="316"/>
+      <c r="E52" s="315"/>
+      <c r="F52" s="315"/>
     </row>
     <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
@@ -4700,13 +4748,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="353" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="353"/>
+      <c r="D58" s="353"/>
+      <c r="E58" s="353"/>
+      <c r="F58" s="353"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4722,13 +4770,13 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
-        <v>341</v>
-      </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="B61" s="353" t="s">
+        <v>339</v>
+      </c>
+      <c r="C61" s="354"/>
+      <c r="D61" s="354"/>
+      <c r="E61" s="354"/>
+      <c r="F61" s="354"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
@@ -4744,22 +4792,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B64" s="348" t="s">
-        <v>346</v>
-      </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="B64" s="352" t="s">
+        <v>344</v>
+      </c>
+      <c r="C64" s="352"/>
+      <c r="D64" s="352"/>
+      <c r="E64" s="352"/>
+      <c r="F64" s="352"/>
     </row>
     <row r="65" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B65" s="348" t="s">
-        <v>364</v>
-      </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="B65" s="352" t="s">
+        <v>362</v>
+      </c>
+      <c r="C65" s="352"/>
+      <c r="D65" s="352"/>
+      <c r="E65" s="352"/>
+      <c r="F65" s="352"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4788,26 +4836,34 @@
       </c>
     </row>
     <row r="69" spans="1:6">
-      <c r="B69" s="252" t="s">
-        <v>393</v>
+      <c r="B69" s="251" t="s">
+        <v>391</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
         <v>8.081439043489845E-2</v>
       </c>
+      <c r="F69" s="348"/>
     </row>
     <row r="70" spans="1:6">
-      <c r="B70" s="252" t="s">
-        <v>311</v>
+      <c r="B70" s="251" t="s">
+        <v>309</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
         <v>4.2208934224410834E-2</v>
       </c>
+      <c r="E70" s="47" t="s">
+        <v>450</v>
+      </c>
+      <c r="F70" s="349">
+        <f>Normalized_FCF!C92</f>
+        <v>0.52229477939839231</v>
+      </c>
     </row>
     <row r="72" spans="1:6" ht="13.9">
-      <c r="A72" s="247" t="s">
-        <v>358</v>
+      <c r="A72" s="246" t="s">
+        <v>356</v>
       </c>
       <c r="B72" s="36"/>
       <c r="C72" s="36"/>
@@ -4820,22 +4876,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.4" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="348" t="s">
-        <v>365</v>
-      </c>
-      <c r="C74" s="348"/>
-      <c r="D74" s="348"/>
-      <c r="E74" s="348"/>
-      <c r="F74" s="348"/>
+      <c r="B74" s="352" t="s">
+        <v>363</v>
+      </c>
+      <c r="C74" s="352"/>
+      <c r="D74" s="352"/>
+      <c r="E74" s="352"/>
+      <c r="F74" s="352"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="350" t="s">
+      <c r="B75" s="355" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="350"/>
-      <c r="D75" s="350"/>
-      <c r="E75" s="350"/>
-      <c r="F75" s="350"/>
+      <c r="C75" s="355"/>
+      <c r="D75" s="355"/>
+      <c r="E75" s="355"/>
+      <c r="F75" s="355"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="234" t="s">
@@ -4844,7 +4900,7 @@
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
@@ -4853,7 +4909,7 @@
     </row>
     <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C79" s="92">
         <f>IF(C23="Y",1%,0)+IF(C24="Y",1%,0)</f>
@@ -4864,7 +4920,7 @@
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
-      <c r="C80" s="261">
+      <c r="C80" s="260">
         <f>F31+C79</f>
         <v>0.08</v>
       </c>
@@ -4873,42 +4929,42 @@
       <c r="C81" s="122"/>
     </row>
     <row r="82" spans="1:6">
-      <c r="B82" s="326" t="s">
-        <v>359</v>
+      <c r="B82" s="325" t="s">
+        <v>357</v>
       </c>
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B83" s="348" t="s">
-        <v>366</v>
-      </c>
-      <c r="C83" s="348"/>
-      <c r="D83" s="348"/>
-      <c r="E83" s="348"/>
-      <c r="F83" s="348"/>
+      <c r="B83" s="352" t="s">
+        <v>364</v>
+      </c>
+      <c r="C83" s="352"/>
+      <c r="D83" s="352"/>
+      <c r="E83" s="352"/>
+      <c r="F83" s="352"/>
     </row>
     <row r="84" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B84" s="348" t="s">
-        <v>367</v>
-      </c>
-      <c r="C84" s="348"/>
-      <c r="D84" s="348"/>
-      <c r="E84" s="348"/>
-      <c r="F84" s="348"/>
+      <c r="B84" s="352" t="s">
+        <v>365</v>
+      </c>
+      <c r="C84" s="352"/>
+      <c r="D84" s="352"/>
+      <c r="E84" s="352"/>
+      <c r="F84" s="352"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
-      <c r="C86" s="261">
+      <c r="C86" s="260">
         <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
-        <v>283</v>
-      </c>
-      <c r="C87" s="248">
+        <v>281</v>
+      </c>
+      <c r="C87" s="247">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>57.438828001604072</v>
       </c>
@@ -4918,8 +4974,8 @@
       </c>
     </row>
     <row r="89" spans="1:6" ht="13.9">
-      <c r="A89" s="247" t="s">
-        <v>360</v>
+      <c r="A89" s="246" t="s">
+        <v>358</v>
       </c>
       <c r="B89" s="36"/>
       <c r="C89" s="36"/>
@@ -4931,13 +4987,13 @@
       <c r="A90" s="233"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="348" t="s">
-        <v>368</v>
-      </c>
-      <c r="C91" s="348"/>
-      <c r="D91" s="348"/>
-      <c r="E91" s="348"/>
-      <c r="F91" s="348"/>
+      <c r="B91" s="352" t="s">
+        <v>366</v>
+      </c>
+      <c r="C91" s="352"/>
+      <c r="D91" s="352"/>
+      <c r="E91" s="352"/>
+      <c r="F91" s="352"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -4950,13 +5006,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B95" s="348" t="s">
-        <v>347</v>
-      </c>
-      <c r="C95" s="348"/>
-      <c r="D95" s="348"/>
-      <c r="E95" s="348"/>
-      <c r="F95" s="348"/>
+      <c r="B95" s="352" t="s">
+        <v>345</v>
+      </c>
+      <c r="C95" s="352"/>
+      <c r="D95" s="352"/>
+      <c r="E95" s="352"/>
+      <c r="F95" s="352"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -4973,9 +5029,9 @@
     </row>
     <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
-        <v>284</v>
-      </c>
-      <c r="C97" s="248">
+        <v>282</v>
+      </c>
+      <c r="C97" s="247">
         <f>C96*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0.25522532080514426</v>
       </c>
@@ -4985,28 +5041,28 @@
       </c>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="330" t="s">
-        <v>407</v>
-      </c>
-      <c r="C98" s="331">
+      <c r="B98" s="329" t="s">
+        <v>405</v>
+      </c>
+      <c r="C98" s="330">
         <f>BS!G30/BS!G27</f>
         <v>3.4701988818540461</v>
       </c>
     </row>
     <row r="99" spans="2:6">
-      <c r="B99" s="330" t="s">
-        <v>408</v>
-      </c>
-      <c r="C99" s="331">
+      <c r="B99" s="329" t="s">
+        <v>406</v>
+      </c>
+      <c r="C99" s="330">
         <f>BS!G31/BS!G27</f>
         <v>5.0341856510546588E-2</v>
       </c>
     </row>
     <row r="100" spans="2:6">
-      <c r="B100" s="330" t="s">
-        <v>410</v>
-      </c>
-      <c r="C100" s="332">
+      <c r="B100" s="329" t="s">
+        <v>408</v>
+      </c>
+      <c r="C100" s="331">
         <f>BS!C50</f>
         <v>3.9546057100127742E-2</v>
       </c>
@@ -5044,9 +5100,9 @@
     </row>
     <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
-        <v>285</v>
-      </c>
-      <c r="C105" s="248">
+        <v>283</v>
+      </c>
+      <c r="C105" s="247">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>0.13558337834994227</v>
       </c>
@@ -5075,9 +5131,9 @@
     </row>
     <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
-        <v>286</v>
-      </c>
-      <c r="C109" s="248">
+        <v>284</v>
+      </c>
+      <c r="C109" s="247">
         <f>C108*scaling_factor*Exchange_Rate/Common_Shares</f>
         <v>6.1073883681813636E-2</v>
       </c>
@@ -5087,20 +5143,20 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B111" s="348" t="s">
-        <v>369</v>
-      </c>
-      <c r="C111" s="348"/>
-      <c r="D111" s="348"/>
-      <c r="E111" s="348"/>
-      <c r="F111" s="348"/>
+      <c r="B111" s="352" t="s">
+        <v>367</v>
+      </c>
+      <c r="C111" s="352"/>
+      <c r="D111" s="352"/>
+      <c r="E111" s="352"/>
+      <c r="F111" s="352"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
-        <v>282</v>
-      </c>
-      <c r="C113" s="248">
-        <f>DCF!C12</f>
+        <v>451</v>
+      </c>
+      <c r="C113" s="247">
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
         <v>57.380259942830683</v>
       </c>
       <c r="D113" s="1" t="str">
@@ -5109,10 +5165,10 @@
       </c>
     </row>
     <row r="114" spans="1:6">
-      <c r="B114" s="330" t="s">
-        <v>409</v>
-      </c>
-      <c r="C114" s="248">
+      <c r="B114" s="329" t="s">
+        <v>407</v>
+      </c>
+      <c r="C114" s="247">
         <f>BS!D47</f>
         <v>-13.312996389940134</v>
       </c>
@@ -5122,8 +5178,8 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="13.9">
-      <c r="A116" s="247" t="s">
-        <v>361</v>
+      <c r="A116" s="246" t="s">
+        <v>359</v>
       </c>
       <c r="B116" s="36"/>
       <c r="C116" s="36"/>
@@ -5132,49 +5188,49 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B118" s="349" t="s">
-        <v>370</v>
-      </c>
-      <c r="C118" s="349"/>
-      <c r="D118" s="349"/>
-      <c r="E118" s="349"/>
-      <c r="F118" s="349"/>
+      <c r="B118" s="353" t="s">
+        <v>368</v>
+      </c>
+      <c r="C118" s="353"/>
+      <c r="D118" s="353"/>
+      <c r="E118" s="353"/>
+      <c r="F118" s="353"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
-      <c r="B120" s="258" t="s">
+      <c r="B120" s="257" t="s">
         <v>118</v>
       </c>
-      <c r="C120" s="258" t="s">
+      <c r="C120" s="257" t="s">
         <v>133</v>
       </c>
-      <c r="D120" s="258" t="s">
+      <c r="D120" s="257" t="s">
         <v>113</v>
       </c>
-      <c r="E120" s="258" t="s">
+      <c r="E120" s="257" t="s">
         <v>260</v>
       </c>
-      <c r="F120" s="258" t="s">
+      <c r="F120" s="257" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="121" spans="1:6">
-      <c r="B121" s="253" t="str">
+      <c r="B121" s="252" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
       </c>
-      <c r="C121" s="254">
+      <c r="C121" s="253">
         <f>DCF!C74</f>
         <v>0.1</v>
       </c>
-      <c r="D121" s="255">
+      <c r="D121" s="254">
         <f>DCF!D74</f>
         <v>15</v>
       </c>
-      <c r="E121" s="256" t="str">
-        <f>ROUND(DCF!E74,2)&amp;" "&amp;Market_currency</f>
+      <c r="E121" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
         <v>99.94 CNY</v>
       </c>
-      <c r="F121" s="257">
+      <c r="F121" s="256">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
@@ -5192,11 +5248,11 @@
         <f>DCF!D75</f>
         <v>10</v>
       </c>
-      <c r="E122" s="245" t="str">
-        <f>ROUND(DCF!E75,2)&amp;" "&amp;Market_currency</f>
+      <c r="E122" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
         <v>69.66 CNY</v>
       </c>
-      <c r="F122" s="246">
+      <c r="F122" s="245">
         <f>DCF!F75</f>
         <v>0.18</v>
       </c>
@@ -5214,11 +5270,11 @@
         <f>DCF!D76</f>
         <v>10</v>
       </c>
-      <c r="E123" s="245" t="str">
-        <f>ROUND(DCF!E76,2)&amp;" "&amp;Market_currency</f>
+      <c r="E123" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
         <v>65.17 CNY</v>
       </c>
-      <c r="F123" s="246">
+      <c r="F123" s="245">
         <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
@@ -5236,11 +5292,11 @@
         <f>DCF!D77</f>
         <v>10</v>
       </c>
-      <c r="E124" s="245" t="str">
-        <f>ROUND(DCF!E77,2)&amp;" "&amp;Market_currency</f>
+      <c r="E124" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
         <v>61.09 CNY</v>
       </c>
-      <c r="F124" s="246">
+      <c r="F124" s="245">
         <f>DCF!F77</f>
         <v>0.18</v>
       </c>
@@ -5258,11 +5314,11 @@
         <f>DCF!D78</f>
         <v>15</v>
       </c>
-      <c r="E125" s="245" t="str">
-        <f>ROUND(DCF!E78,2)&amp;" "&amp;Market_currency</f>
+      <c r="E125" s="255" t="str">
+        <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
         <v>57.38 CNY</v>
       </c>
-      <c r="F125" s="246">
+      <c r="F125" s="245">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
@@ -5281,17 +5337,17 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B129" s="353" t="s">
-        <v>373</v>
-      </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="B129" s="356" t="s">
+        <v>371</v>
+      </c>
+      <c r="C129" s="356"/>
+      <c r="D129" s="356"/>
+      <c r="E129" s="356"/>
+      <c r="F129" s="356"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
-      <c r="A131" s="247" t="s">
-        <v>405</v>
+      <c r="A131" s="246" t="s">
+        <v>403</v>
       </c>
       <c r="B131" s="36"/>
       <c r="C131" s="36"/>
@@ -5300,22 +5356,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="351" t="s">
-        <v>371</v>
-      </c>
-      <c r="C133" s="351"/>
-      <c r="D133" s="351"/>
-      <c r="E133" s="351"/>
-      <c r="F133" s="351"/>
+      <c r="B133" s="357" t="s">
+        <v>369</v>
+      </c>
+      <c r="C133" s="357"/>
+      <c r="D133" s="357"/>
+      <c r="E133" s="357"/>
+      <c r="F133" s="357"/>
     </row>
     <row r="134" spans="1:6" ht="24.4" customHeight="1">
-      <c r="B134" s="348" t="s">
-        <v>372</v>
-      </c>
-      <c r="C134" s="348"/>
-      <c r="D134" s="348"/>
-      <c r="E134" s="348"/>
-      <c r="F134" s="348"/>
+      <c r="B134" s="352" t="s">
+        <v>370</v>
+      </c>
+      <c r="C134" s="352"/>
+      <c r="D134" s="352"/>
+      <c r="E134" s="352"/>
+      <c r="F134" s="352"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="234" t="s">
@@ -5326,7 +5382,7 @@
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="C136" s="250">
+      <c r="C136" s="249">
         <f>F28</f>
         <v>3</v>
       </c>
@@ -5335,7 +5391,7 @@
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C137" s="249">
+      <c r="C137" s="248">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5355,22 +5411,22 @@
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="234" t="s">
-        <v>412</v>
-      </c>
-      <c r="C140" s="268" t="str">
+        <v>410</v>
+      </c>
+      <c r="C140" s="267" t="str">
         <f>C11</f>
         <v>600132.SS</v>
       </c>
-      <c r="D140" s="268" t="str">
+      <c r="D140" s="267" t="str">
         <f>IF(D11="","",D11)</f>
         <v/>
       </c>
     </row>
     <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
-        <v>411</v>
-      </c>
-      <c r="C141" s="331">
+        <v>409</v>
+      </c>
+      <c r="C141" s="330">
         <f>F29</f>
         <v>0.4</v>
       </c>
@@ -5403,20 +5459,20 @@
         <f>Scenarios!C83</f>
         <v>28.081736799883384</v>
       </c>
-      <c r="D144" s="335" t="str">
+      <c r="D144" s="334" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="145" spans="2:4">
-      <c r="B145" s="286" t="s">
-        <v>420</v>
-      </c>
-      <c r="C145" s="333" t="str">
+      <c r="B145" s="285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C145" s="332" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D145" s="333" t="str">
+      <c r="D145" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5432,14 +5488,14 @@
     </row>
     <row r="148" spans="2:4">
       <c r="B148" s="234" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="C149" s="331">
+        <v>412</v>
+      </c>
+      <c r="C149" s="330">
         <f>Scenarios!C90</f>
         <v>0.21740000000000001</v>
       </c>
@@ -5472,20 +5528,20 @@
         <f>Scenarios!C93</f>
         <v>41.829260960684138</v>
       </c>
-      <c r="D152" s="335" t="str">
+      <c r="D152" s="334" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="153" spans="2:4">
-      <c r="B153" s="286" t="s">
-        <v>420</v>
-      </c>
-      <c r="C153" s="333" t="str">
+      <c r="B153" s="285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C153" s="332" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D153" s="333" t="str">
+      <c r="D153" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5501,12 +5557,12 @@
     </row>
     <row r="156" spans="2:4">
       <c r="B156" s="234" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
@@ -5535,26 +5591,26 @@
     </row>
     <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C160" s="239">
         <f>Scenarios!C99</f>
         <v>59.048136223898794</v>
       </c>
-      <c r="D160" s="335" t="str">
+      <c r="D160" s="334" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="161" spans="1:6">
-      <c r="B161" s="286" t="s">
-        <v>420</v>
-      </c>
-      <c r="C161" s="333" t="str">
+      <c r="B161" s="285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C161" s="332" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D161" s="333" t="str">
+      <c r="D161" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5570,12 +5626,12 @@
     </row>
     <row r="164" spans="1:6">
       <c r="B164" s="234" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C165" s="92">
         <f>F32</f>
@@ -5604,26 +5660,26 @@
     </row>
     <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C168" s="239">
         <f>Scenarios!C105</f>
         <v>53.520960428876833</v>
       </c>
-      <c r="D168" s="335" t="str">
+      <c r="D168" s="334" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
     <row r="169" spans="1:6">
-      <c r="B169" s="286" t="s">
-        <v>420</v>
-      </c>
-      <c r="C169" s="333" t="str">
+      <c r="B169" s="285" t="s">
+        <v>418</v>
+      </c>
+      <c r="C169" s="332" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="D169" s="333" t="str">
+      <c r="D169" s="332" t="str">
         <f>IF($D$11="","",D$13)</f>
         <v/>
       </c>
@@ -5638,8 +5694,8 @@
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
-      <c r="A172" s="247" t="s">
-        <v>377</v>
+      <c r="A172" s="246" t="s">
+        <v>375</v>
       </c>
       <c r="B172" s="36"/>
       <c r="C172" s="36"/>
@@ -5648,113 +5704,102 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="355" t="s">
-        <v>379</v>
-      </c>
-      <c r="C174" s="348"/>
-      <c r="D174" s="348"/>
-      <c r="E174" s="348"/>
-      <c r="F174" s="348"/>
+      <c r="B174" s="351" t="s">
+        <v>377</v>
+      </c>
+      <c r="C174" s="352"/>
+      <c r="D174" s="352"/>
+      <c r="E174" s="352"/>
+      <c r="F174" s="352"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="234" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="177" spans="2:6">
-      <c r="B177" s="352" t="s">
-        <v>383</v>
-      </c>
-      <c r="C177" s="352"/>
-      <c r="D177" s="352"/>
-      <c r="E177" s="352"/>
-      <c r="F177" s="352"/>
+      <c r="B177" s="354" t="s">
+        <v>381</v>
+      </c>
+      <c r="C177" s="354"/>
+      <c r="D177" s="354"/>
+      <c r="E177" s="354"/>
+      <c r="F177" s="354"/>
     </row>
     <row r="178" spans="2:6">
       <c r="B178" s="238" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="179" spans="2:6">
       <c r="B179" s="238" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="180" spans="2:6">
       <c r="B180" s="238" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="349" t="s">
-        <v>384</v>
-      </c>
-      <c r="C183" s="349"/>
-      <c r="D183" s="349"/>
-      <c r="E183" s="349"/>
-      <c r="F183" s="349"/>
+      <c r="B183" s="353" t="s">
+        <v>382</v>
+      </c>
+      <c r="C183" s="353"/>
+      <c r="D183" s="353"/>
+      <c r="E183" s="353"/>
+      <c r="F183" s="353"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B186" s="354" t="s">
-        <v>385</v>
-      </c>
-      <c r="C186" s="354"/>
-      <c r="D186" s="354"/>
-      <c r="E186" s="354"/>
-      <c r="F186" s="354"/>
+      <c r="B186" s="350" t="s">
+        <v>383</v>
+      </c>
+      <c r="C186" s="350"/>
+      <c r="D186" s="350"/>
+      <c r="E186" s="350"/>
+      <c r="F186" s="350"/>
     </row>
     <row r="187" spans="2:6" ht="24.4" customHeight="1">
-      <c r="B187" s="354" t="s">
-        <v>386</v>
-      </c>
-      <c r="C187" s="354"/>
-      <c r="D187" s="354"/>
-      <c r="E187" s="354"/>
-      <c r="F187" s="354"/>
+      <c r="B187" s="350" t="s">
+        <v>384</v>
+      </c>
+      <c r="C187" s="350"/>
+      <c r="D187" s="350"/>
+      <c r="E187" s="350"/>
+      <c r="F187" s="350"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
     </row>
     <row r="190" spans="2:6">
       <c r="B190" s="238" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="191" spans="2:6">
       <c r="B191" s="238" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="192" spans="2:6">
       <c r="B192" s="238" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5771,6 +5816,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -5783,7 +5839,7 @@
     <dataValidation type="list" allowBlank="1" sqref="C25:D25" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"HKD,USD,CNY,EUR"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E22 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E21 E25" xr:uid="{788B6937-776F-41CC-B9B1-7986DB35B57D}">
       <formula1>"DCF,DDM"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6331,7 +6387,7 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C22" s="181">
         <v>2542046725</v>
@@ -6367,7 +6423,7 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C23" s="181">
         <v>-633430356</v>
@@ -6403,7 +6459,7 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C24" s="181">
         <v>-3527746522</v>
@@ -6462,7 +6518,7 @@
         <v>28</v>
       </c>
       <c r="C27" s="97" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
     </row>
     <row r="28" spans="2:13">
@@ -7767,7 +7823,7 @@
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C64" s="183">
         <f>IF(C$4="","",C22+C23+C24)</f>
@@ -8215,11 +8271,11 @@
         <f t="shared" si="40"/>
         <v>58261577</v>
       </c>
-      <c r="I77" s="329"/>
-      <c r="J77" s="329"/>
-      <c r="K77" s="329"/>
-      <c r="L77" s="329"/>
-      <c r="M77" s="329"/>
+      <c r="I77" s="328"/>
+      <c r="J77" s="328"/>
+      <c r="K77" s="328"/>
+      <c r="L77" s="328"/>
+      <c r="M77" s="328"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
@@ -8249,11 +8305,11 @@
         <f t="shared" si="40"/>
         <v>364381375</v>
       </c>
-      <c r="I78" s="329"/>
-      <c r="J78" s="329"/>
-      <c r="K78" s="329"/>
-      <c r="L78" s="329"/>
-      <c r="M78" s="329"/>
+      <c r="I78" s="328"/>
+      <c r="J78" s="328"/>
+      <c r="K78" s="328"/>
+      <c r="L78" s="328"/>
+      <c r="M78" s="328"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
@@ -8356,17 +8412,17 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C4:M16 C19:M25 C39:M43 C45:M48 C51:M52 C55:M58 C77:H78 C79:M80">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="7" priority="4">
       <formula>ISBLANK(C4)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C28:M32">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="6" priority="1">
       <formula>ISBLANK(C28)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C36:M37 C61:M65">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>ISBLANK(C36)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8451,7 +8507,7 @@
         <f>63423634.85+27585675</f>
         <v>91009309.849999994</v>
       </c>
-      <c r="D4" s="290">
+      <c r="D4" s="289">
         <v>0.6</v>
       </c>
       <c r="E4" s="25"/>
@@ -8461,7 +8517,7 @@
       <c r="G4" s="19">
         <v>1081659074.0699999</v>
       </c>
-      <c r="H4" s="290">
+      <c r="H4" s="289">
         <v>0.9</v>
       </c>
     </row>
@@ -8472,7 +8528,7 @@
       <c r="C5" s="19">
         <v>0</v>
       </c>
-      <c r="D5" s="290">
+      <c r="D5" s="289">
         <v>0.6</v>
       </c>
       <c r="E5" s="25"/>
@@ -8482,7 +8538,7 @@
       <c r="G5" s="19">
         <v>0</v>
       </c>
-      <c r="H5" s="290">
+      <c r="H5" s="289">
         <v>0.7</v>
       </c>
     </row>
@@ -8493,7 +8549,7 @@
       <c r="C6" s="19">
         <v>2185835620.7199998</v>
       </c>
-      <c r="D6" s="290">
+      <c r="D6" s="289">
         <v>0.5</v>
       </c>
       <c r="E6" s="25"/>
@@ -8503,7 +8559,7 @@
       <c r="G6" s="19">
         <v>0</v>
       </c>
-      <c r="H6" s="290">
+      <c r="H6" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8514,7 +8570,7 @@
       <c r="C7" s="19">
         <v>0</v>
       </c>
-      <c r="D7" s="290">
+      <c r="D7" s="289">
         <v>0.6</v>
       </c>
       <c r="E7" s="25"/>
@@ -8524,7 +8580,7 @@
       <c r="G7" s="19">
         <v>22482125.719999999</v>
       </c>
-      <c r="H7" s="290">
+      <c r="H7" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8535,7 +8591,7 @@
       <c r="C8" s="19">
         <v>0</v>
       </c>
-      <c r="D8" s="290">
+      <c r="D8" s="289">
         <v>0.6</v>
       </c>
       <c r="E8" s="25"/>
@@ -8545,7 +8601,7 @@
       <c r="G8" s="19">
         <v>0</v>
       </c>
-      <c r="H8" s="290">
+      <c r="H8" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8556,7 +8612,7 @@
       <c r="C9" s="19">
         <v>28012999.57</v>
       </c>
-      <c r="D9" s="290">
+      <c r="D9" s="289">
         <v>0.1</v>
       </c>
       <c r="E9" s="25"/>
@@ -8566,7 +8622,7 @@
       <c r="G9" s="19">
         <v>0</v>
       </c>
-      <c r="H9" s="290">
+      <c r="H9" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8577,10 +8633,10 @@
       <c r="C10" s="19">
         <v>0</v>
       </c>
-      <c r="D10" s="290">
+      <c r="D10" s="289">
         <v>0.9</v>
       </c>
-      <c r="H10" s="291"/>
+      <c r="H10" s="290"/>
     </row>
     <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
@@ -8589,10 +8645,10 @@
       <c r="C11" s="19">
         <v>270038356.50999999</v>
       </c>
-      <c r="D11" s="290">
+      <c r="D11" s="289">
         <v>0.05</v>
       </c>
-      <c r="H11" s="291"/>
+      <c r="H11" s="290"/>
     </row>
     <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
@@ -8650,7 +8706,7 @@
       <c r="C15" s="19">
         <v>0</v>
       </c>
-      <c r="D15" s="290">
+      <c r="D15" s="289">
         <v>0.4</v>
       </c>
       <c r="F15" s="4" t="s">
@@ -8659,7 +8715,7 @@
       <c r="G15" s="19">
         <v>0</v>
       </c>
-      <c r="H15" s="290">
+      <c r="H15" s="289">
         <v>0.8</v>
       </c>
     </row>
@@ -8670,7 +8726,7 @@
       <c r="C16" s="19">
         <v>0</v>
       </c>
-      <c r="D16" s="290">
+      <c r="D16" s="289">
         <v>0.5</v>
       </c>
       <c r="F16" s="4" t="s">
@@ -8679,7 +8735,7 @@
       <c r="G16" s="19">
         <v>0</v>
       </c>
-      <c r="H16" s="290">
+      <c r="H16" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8690,7 +8746,7 @@
       <c r="C17" s="19">
         <v>0</v>
       </c>
-      <c r="D17" s="290">
+      <c r="D17" s="289">
         <v>0.6</v>
       </c>
       <c r="F17" s="4" t="s">
@@ -8699,7 +8755,7 @@
       <c r="G17" s="19">
         <v>0</v>
       </c>
-      <c r="H17" s="290">
+      <c r="H17" s="289">
         <v>0.6</v>
       </c>
     </row>
@@ -8710,7 +8766,7 @@
       <c r="C18" s="19">
         <v>0</v>
       </c>
-      <c r="D18" s="290">
+      <c r="D18" s="289">
         <v>0.6</v>
       </c>
       <c r="F18" s="4" t="s">
@@ -8719,7 +8775,7 @@
       <c r="G18" s="19">
         <v>0</v>
       </c>
-      <c r="H18" s="290">
+      <c r="H18" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8731,7 +8787,7 @@
         <f>4755026247.47+159772560.73+160044048.75</f>
         <v>5074842856.9499998</v>
       </c>
-      <c r="D19" s="290">
+      <c r="D19" s="289">
         <v>0.1</v>
       </c>
       <c r="F19" s="4" t="s">
@@ -8741,7 +8797,7 @@
         <f>142861296.29+17825955.91</f>
         <v>160687252.19999999</v>
       </c>
-      <c r="H19" s="290">
+      <c r="H19" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8752,7 +8808,7 @@
       <c r="C20" s="19">
         <v>0</v>
       </c>
-      <c r="D20" s="290">
+      <c r="D20" s="289">
         <v>0.05</v>
       </c>
       <c r="F20" s="4" t="s">
@@ -8761,7 +8817,7 @@
       <c r="G20" s="19">
         <v>0</v>
       </c>
-      <c r="H20" s="290">
+      <c r="H20" s="289">
         <v>0.2</v>
       </c>
     </row>
@@ -8772,7 +8828,7 @@
       <c r="C21" s="19">
         <v>650634797.63</v>
       </c>
-      <c r="D21" s="290">
+      <c r="D21" s="289">
         <v>0.05</v>
       </c>
       <c r="F21" s="1" t="s">
@@ -8781,7 +8837,7 @@
       <c r="G21" s="19">
         <v>0</v>
       </c>
-      <c r="H21" s="290">
+      <c r="H21" s="289">
         <v>0.1</v>
       </c>
     </row>
@@ -8792,10 +8848,10 @@
       <c r="C22" s="19">
         <v>703465374.02999997</v>
       </c>
-      <c r="D22" s="290">
+      <c r="D22" s="289">
         <v>0.9</v>
       </c>
-      <c r="H22" s="291"/>
+      <c r="H22" s="290"/>
     </row>
     <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
@@ -8805,10 +8861,10 @@
         <f>699192456.06+479496.08</f>
         <v>699671952.13999999</v>
       </c>
-      <c r="D23" s="290">
-        <v>0</v>
-      </c>
-      <c r="H23" s="291"/>
+      <c r="D23" s="289">
+        <v>0</v>
+      </c>
+      <c r="H23" s="290"/>
     </row>
     <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
@@ -9141,13 +9197,13 @@
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
-      <c r="C45" s="259" t="s">
+      <c r="C45" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D45" s="203" t="s">
-        <v>409</v>
-      </c>
-      <c r="F45" s="283" t="s">
+        <v>407</v>
+      </c>
+      <c r="F45" s="282" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9163,7 +9219,7 @@
         <f>H29</f>
         <v>-6443106811.8090019</v>
       </c>
-      <c r="F46" s="280"/>
+      <c r="F46" s="279"/>
     </row>
     <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
@@ -9178,23 +9234,23 @@
         <f>D46*H1/Common_Shares*Exchange_Rate</f>
         <v>-13.312996389940134</v>
       </c>
-      <c r="F47" s="280"/>
+      <c r="F47" s="279"/>
     </row>
     <row r="48" spans="2:8" ht="15" customHeight="1">
-      <c r="F48" s="280"/>
+      <c r="F48" s="279"/>
     </row>
     <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
-      <c r="C49" s="260" t="s">
+      <c r="C49" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D49" s="218" t="s">
         <v>96</v>
       </c>
       <c r="E49" s="2"/>
-      <c r="F49" s="280"/>
+      <c r="F49" s="279"/>
     </row>
     <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
@@ -9208,7 +9264,7 @@
         <f>G31/Normalized_FCF!G8</f>
         <v>3.9727648442014103E-2</v>
       </c>
-      <c r="F50" s="280"/>
+      <c r="F50" s="279"/>
     </row>
     <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
@@ -9219,22 +9275,22 @@
         <f>G29/G32</f>
         <v>0.10805831095063075</v>
       </c>
-      <c r="F51" s="280"/>
+      <c r="F51" s="279"/>
     </row>
     <row r="52" spans="2:8" ht="15" customHeight="1">
-      <c r="F52" s="280"/>
+      <c r="F52" s="279"/>
     </row>
     <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
-      <c r="C53" s="260" t="s">
+      <c r="C53" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D53" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F53" s="280"/>
+      <c r="F53" s="279"/>
     </row>
     <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
@@ -9248,7 +9304,7 @@
         <f>Normalized_FCF!G8/G35</f>
         <v>0.32042139111496037</v>
       </c>
-      <c r="F54" s="280"/>
+      <c r="F54" s="279"/>
     </row>
     <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
@@ -9262,22 +9318,22 @@
         <f>Normalized_FCF!G11/G40</f>
         <v>0</v>
       </c>
-      <c r="F55" s="280"/>
+      <c r="F55" s="279"/>
     </row>
     <row r="56" spans="2:8" ht="15" customHeight="1">
-      <c r="F56" s="280"/>
+      <c r="F56" s="279"/>
     </row>
     <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
-      <c r="C57" s="260" t="s">
+      <c r="C57" s="259" t="s">
         <v>57</v>
       </c>
       <c r="D57" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F57" s="280"/>
+      <c r="F57" s="279"/>
     </row>
     <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
@@ -9299,22 +9355,22 @@
         <f>G39/G32</f>
         <v>0.46268104259923815</v>
       </c>
-      <c r="F59" s="280"/>
+      <c r="F59" s="279"/>
     </row>
     <row r="60" spans="2:8" ht="15" customHeight="1">
-      <c r="F60" s="280"/>
+      <c r="F60" s="279"/>
     </row>
     <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
-      <c r="C61" s="260" t="s">
+      <c r="C61" s="259" t="s">
         <v>138</v>
       </c>
       <c r="D61" s="218" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="280"/>
+      <c r="F61" s="279"/>
     </row>
     <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
@@ -9328,7 +9384,7 @@
         <f>G28/G29</f>
         <v>1.0702127528080294</v>
       </c>
-      <c r="F62" s="280" t="s">
+      <c r="F62" s="279" t="s">
         <v>273</v>
       </c>
     </row>
@@ -9347,13 +9403,13 @@
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="C65" s="259" t="s">
+      <c r="C65" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D65" s="204" t="s">
-        <v>288</v>
-      </c>
-      <c r="F65" s="283" t="s">
+        <v>286</v>
+      </c>
+      <c r="F65" s="282" t="s">
         <v>59</v>
       </c>
     </row>
@@ -9381,7 +9437,7 @@
         <f>G6+G16</f>
         <v>0</v>
       </c>
-      <c r="F67" s="280"/>
+      <c r="F67" s="279"/>
     </row>
     <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
@@ -9391,7 +9447,7 @@
         <f>G18</f>
         <v>0</v>
       </c>
-      <c r="F68" s="280"/>
+      <c r="F68" s="279"/>
     </row>
     <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
@@ -9401,7 +9457,7 @@
         <f>G8+G20</f>
         <v>0</v>
       </c>
-      <c r="F69" s="280"/>
+      <c r="F69" s="279"/>
     </row>
     <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
@@ -9411,26 +9467,26 @@
         <f>SUM(C66:C69)</f>
         <v>1081659074.0699999</v>
       </c>
-      <c r="F70" s="280"/>
+      <c r="F70" s="279"/>
     </row>
     <row r="71" spans="2:6" ht="15" customHeight="1">
-      <c r="F71" s="280"/>
+      <c r="F71" s="279"/>
     </row>
     <row r="72" spans="2:6" ht="15" customHeight="1">
-      <c r="B72" s="282" t="s">
-        <v>321</v>
-      </c>
-      <c r="C72" s="259" t="s">
+      <c r="B72" s="281" t="s">
+        <v>319</v>
+      </c>
+      <c r="C72" s="258" t="s">
         <v>96</v>
       </c>
       <c r="D72" s="203" t="s">
         <v>57</v>
       </c>
-      <c r="F72" s="280"/>
+      <c r="F72" s="279"/>
     </row>
     <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C73" s="188">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
@@ -9441,65 +9497,65 @@
         <v>-1016040624.0210911</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="15" customHeight="1">
-      <c r="B74" s="284" t="s">
-        <v>324</v>
-      </c>
-      <c r="C74" s="285">
+      <c r="B74" s="283" t="s">
+        <v>322</v>
+      </c>
+      <c r="C74" s="284">
         <f>-$C$66/C73</f>
         <v>1.0222883058815033</v>
       </c>
-      <c r="D74" s="285">
+      <c r="D74" s="284">
         <f>-$C$66/D73</f>
         <v>1.0645825063462686</v>
       </c>
-      <c r="F74" s="280" t="s">
-        <v>322</v>
+      <c r="F74" s="279" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
-        <v>323</v>
-      </c>
-      <c r="C75" s="289"/>
-      <c r="D75" s="288">
+        <v>321</v>
+      </c>
+      <c r="C75" s="288"/>
+      <c r="D75" s="287">
         <f>MAX(-D73*D76,G5)</f>
         <v>1016040624.0210911</v>
       </c>
-      <c r="F75" s="280" t="s">
-        <v>355</v>
+      <c r="F75" s="279" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="76" spans="2:6" ht="15" customHeight="1">
-      <c r="B76" s="286" t="s">
-        <v>325</v>
-      </c>
-      <c r="C76" s="287"/>
-      <c r="D76" s="322">
+      <c r="B76" s="285" t="s">
+        <v>323</v>
+      </c>
+      <c r="C76" s="286"/>
+      <c r="D76" s="321">
         <f>IF(D74&lt;=3,1,IF(D74&gt;18,6,2))</f>
         <v>1</v>
       </c>
-      <c r="F76" s="280" t="s">
-        <v>326</v>
+      <c r="F76" s="279" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="77" spans="2:6" ht="15" customHeight="1">
-      <c r="F77" s="280"/>
+      <c r="F77" s="279"/>
     </row>
     <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="C78" s="259" t="s">
+      <c r="C78" s="258" t="s">
         <v>137</v>
       </c>
       <c r="D78" s="204" t="s">
         <v>35</v>
       </c>
-      <c r="F78" s="280"/>
+      <c r="F78" s="279"/>
     </row>
     <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
@@ -9513,7 +9569,7 @@
         <f>G7*H7+G17*H17</f>
         <v>13489275.431999998</v>
       </c>
-      <c r="F79" s="280"/>
+      <c r="F79" s="279"/>
     </row>
     <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
@@ -9527,7 +9583,7 @@
         <f>G19*H19</f>
         <v>16068725.219999999</v>
       </c>
-      <c r="F80" s="280"/>
+      <c r="F80" s="279"/>
     </row>
     <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
@@ -9541,7 +9597,7 @@
         <f>G9*H9+G21*H21</f>
         <v>0</v>
       </c>
-      <c r="F81" s="280"/>
+      <c r="F81" s="279"/>
     </row>
     <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
@@ -9555,11 +9611,11 @@
         <f>SUM(D79:D81)</f>
         <v>29558000.651999995</v>
       </c>
-      <c r="F82" s="280"/>
+      <c r="F82" s="279"/>
     </row>
     <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
@@ -9570,76 +9626,76 @@
     </row>
     <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
-        <v>292</v>
-      </c>
-      <c r="D85" s="268" t="s">
-        <v>293</v>
+        <v>290</v>
+      </c>
+      <c r="D85" s="267" t="s">
+        <v>291</v>
       </c>
     </row>
     <row r="86" spans="2:8" ht="15" customHeight="1">
-      <c r="B86" s="265" t="s">
-        <v>289</v>
+      <c r="B86" s="264" t="s">
+        <v>287</v>
       </c>
       <c r="C86" s="188">
         <f>-DCF!C7*Exchange_Rate</f>
         <v>-123521704.27</v>
       </c>
-      <c r="D86" s="248">
+      <c r="D86" s="247">
         <f>C86*scaling_factor/Common_Shares</f>
         <v>-0.25522532080514426</v>
       </c>
-      <c r="E86" s="267" t="str">
+      <c r="E86" s="266" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="87" spans="2:8" ht="15" customHeight="1">
-      <c r="B87" s="265" t="s">
-        <v>290</v>
+      <c r="B87" s="264" t="s">
+        <v>288</v>
       </c>
       <c r="C87" s="188">
         <f>DCF!C8*Exchange_Rate</f>
         <v>65618450.04890883</v>
       </c>
-      <c r="D87" s="248">
+      <c r="D87" s="247">
         <f>C87*scaling_factor/Common_Shares</f>
         <v>0.13558337834994227</v>
       </c>
-      <c r="E87" s="267" t="str">
+      <c r="E87" s="266" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="88" spans="2:8" ht="15" customHeight="1">
-      <c r="B88" s="266" t="s">
+      <c r="B88" s="265" t="s">
         <v>190</v>
       </c>
       <c r="C88" s="188">
         <f>DCF!C9*Exchange_Rate</f>
         <v>29558000.651999995</v>
       </c>
-      <c r="D88" s="248">
+      <c r="D88" s="247">
         <f>C88*scaling_factor/Common_Shares</f>
         <v>6.1073883681813636E-2</v>
       </c>
-      <c r="E88" s="267" t="str">
+      <c r="E88" s="266" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
     <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C89" s="187">
         <f>SUM(C86:C88)</f>
         <v>-28345253.569091171</v>
       </c>
-      <c r="D89" s="269">
+      <c r="D89" s="268">
         <f>SUM(D86:D88)</f>
         <v>-5.8568058773388353E-2</v>
       </c>
-      <c r="E89" s="267" t="str">
+      <c r="E89" s="266" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
@@ -9760,7 +9816,7 @@
         <v>1</v>
       </c>
       <c r="D3" s="9"/>
-      <c r="E3" s="298"/>
+      <c r="E3" s="297"/>
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
@@ -9774,7 +9830,7 @@
         <v>14154446369.75</v>
       </c>
       <c r="D4" s="57"/>
-      <c r="E4" s="296"/>
+      <c r="E4" s="295"/>
       <c r="F4" s="57"/>
       <c r="G4" s="183">
         <f>Data!C36</f>
@@ -9830,7 +9886,7 @@
         <f>C25</f>
         <v>-10434492185.803093</v>
       </c>
-      <c r="E5" s="298"/>
+      <c r="E5" s="297"/>
       <c r="G5" s="183">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-10995777063</v>
@@ -9885,7 +9941,7 @@
         <f>C4+C5</f>
         <v>3719954183.946907</v>
       </c>
-      <c r="E6" s="298"/>
+      <c r="E6" s="297"/>
       <c r="G6" s="184">
         <f>IF(G4="","",G4+G5)</f>
         <v>3648820779</v>
@@ -9940,7 +9996,7 @@
         <f>C35</f>
         <v>-596464427.25</v>
       </c>
-      <c r="E7" s="298"/>
+      <c r="E7" s="297"/>
       <c r="G7" s="191">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-539608200</v>
@@ -9996,7 +10052,7 @@
         <v>3123489756.696907</v>
       </c>
       <c r="D8" s="59"/>
-      <c r="E8" s="304"/>
+      <c r="E8" s="303"/>
       <c r="F8" s="59"/>
       <c r="G8" s="184">
         <f>IF(G$4="","",G6+G7)</f>
@@ -10052,7 +10108,7 @@
         <f>BS!$G$39*BS!D58</f>
         <v>575917865</v>
       </c>
-      <c r="E9" s="298"/>
+      <c r="E9" s="297"/>
       <c r="G9" s="191">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>575917865</v>
@@ -10107,7 +10163,7 @@
         <f>-C4*C78</f>
         <v>-575917865</v>
       </c>
-      <c r="E10" s="298"/>
+      <c r="E10" s="297"/>
       <c r="G10" s="191">
         <f>Data!C62</f>
         <v>-575917865</v>
@@ -10163,7 +10219,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="169"/>
-      <c r="E11" s="297"/>
+      <c r="E11" s="296"/>
       <c r="F11" s="169"/>
       <c r="G11" s="186">
         <f>G61</f>
@@ -10219,7 +10275,7 @@
         <f>C50</f>
         <v>30881944.997018404</v>
       </c>
-      <c r="E12" s="298"/>
+      <c r="E12" s="297"/>
       <c r="G12" s="191">
         <f>G50</f>
         <v>30881944.997018404</v>
@@ -10274,7 +10330,7 @@
         <f>SUM(C8:C12)</f>
         <v>3154371701.6939254</v>
       </c>
-      <c r="E13" s="298"/>
+      <c r="E13" s="297"/>
       <c r="G13" s="184">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>3140094523.9970183</v>
@@ -10329,7 +10385,7 @@
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-788592925.42348135</v>
       </c>
-      <c r="E14" s="298"/>
+      <c r="E14" s="297"/>
       <c r="G14" s="191">
         <f>Data!C46</f>
         <v>-670547120</v>
@@ -10385,7 +10441,7 @@
         <v>-141879704.29826272</v>
       </c>
       <c r="D15" s="60"/>
-      <c r="E15" s="305"/>
+      <c r="E15" s="304"/>
       <c r="F15" s="60"/>
       <c r="G15" s="183">
         <f>Data!C48</f>
@@ -10442,7 +10498,7 @@
         <v>2223899071.9721813</v>
       </c>
       <c r="D16" s="61"/>
-      <c r="E16" s="306"/>
+      <c r="E16" s="305"/>
       <c r="F16" s="61"/>
       <c r="G16" s="184">
         <f>IF(G$4="","",SUM(G13:G15))</f>
@@ -10499,8 +10555,8 @@
         <v>0</v>
       </c>
       <c r="D17" s="58"/>
-      <c r="E17" s="297" t="s">
-        <v>334</v>
+      <c r="E17" s="296" t="s">
+        <v>332</v>
       </c>
       <c r="F17" s="58"/>
       <c r="G17" s="195"/>
@@ -10524,8 +10580,8 @@
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
-      <c r="E18" s="297" t="s">
-        <v>335</v>
+      <c r="E18" s="296" t="s">
+        <v>333</v>
       </c>
       <c r="F18" s="58"/>
       <c r="G18" s="196"/>
@@ -10550,7 +10606,7 @@
         <v>2223899071.9721813</v>
       </c>
       <c r="D19" s="27"/>
-      <c r="E19" s="295"/>
+      <c r="E19" s="294"/>
       <c r="F19" s="27"/>
       <c r="G19" s="186">
         <f>IF(G$4="","",G16+G17)</f>
@@ -10646,7 +10702,7 @@
       </c>
       <c r="C22" s="62"/>
       <c r="D22" s="27"/>
-      <c r="E22" s="295"/>
+      <c r="E22" s="294"/>
       <c r="F22" s="27"/>
       <c r="G22" s="12"/>
       <c r="H22" s="12"/>
@@ -10670,7 +10726,7 @@
         <v>-8039212664.4388895</v>
       </c>
       <c r="D23" s="58"/>
-      <c r="E23" s="297"/>
+      <c r="E23" s="296"/>
       <c r="F23" s="58"/>
       <c r="G23" s="183">
         <f>Data!C37</f>
@@ -10727,7 +10783,7 @@
         <v>-2395279521.3642035</v>
       </c>
       <c r="D24" s="27"/>
-      <c r="E24" s="295"/>
+      <c r="E24" s="294"/>
       <c r="F24" s="27"/>
       <c r="G24" s="183">
         <f>Data!C40</f>
@@ -10784,7 +10840,7 @@
         <v>-10434492185.803093</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="303"/>
+      <c r="E25" s="302"/>
       <c r="F25" s="9"/>
       <c r="G25" s="184">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
@@ -10833,14 +10889,14 @@
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
-      <c r="E26" s="298"/>
+      <c r="E26" s="297"/>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
-      <c r="E27" s="298"/>
+      <c r="E27" s="297"/>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
@@ -10852,8 +10908,8 @@
         <v>0.56796376590325659</v>
       </c>
       <c r="D28" s="26"/>
-      <c r="E28" s="296" t="s">
-        <v>336</v>
+      <c r="E28" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F28" s="26"/>
       <c r="G28" s="13">
@@ -10912,8 +10968,8 @@
         <v>0.1692245290838959</v>
       </c>
       <c r="D29" s="26"/>
-      <c r="E29" s="296" t="s">
-        <v>336</v>
+      <c r="E29" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F29" s="26"/>
       <c r="G29" s="13">
@@ -10970,7 +11026,7 @@
         <f>ABS(C25/$C$4)</f>
         <v>0.73718829498715255</v>
       </c>
-      <c r="E30" s="298"/>
+      <c r="E30" s="297"/>
       <c r="G30" s="30">
         <f t="shared" ref="G30:Q30" si="13">IF(G$4="","",ABS(G25/G$4))</f>
         <v>0.75084185865894126</v>
@@ -11018,14 +11074,14 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
-      <c r="E31" s="298"/>
+      <c r="E31" s="297"/>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
-      <c r="E32" s="298"/>
+      <c r="E32" s="297"/>
     </row>
     <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
@@ -11036,8 +11092,8 @@
         <f>AVERAGE(G33:J33)</f>
         <v>-515765096.5</v>
       </c>
-      <c r="E33" s="296" t="s">
-        <v>336</v>
+      <c r="E33" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="G33" s="191">
         <f>Data!C41</f>
@@ -11094,8 +11150,8 @@
         <v>-80699330.75</v>
       </c>
       <c r="D34" s="58"/>
-      <c r="E34" s="296" t="s">
-        <v>336</v>
+      <c r="E34" s="295" t="s">
+        <v>334</v>
       </c>
       <c r="F34" s="58"/>
       <c r="G34" s="183">
@@ -11153,7 +11209,7 @@
         <v>-596464427.25</v>
       </c>
       <c r="D35" s="58"/>
-      <c r="E35" s="297"/>
+      <c r="E35" s="296"/>
       <c r="F35" s="58"/>
       <c r="G35" s="184">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
@@ -11202,14 +11258,14 @@
     </row>
     <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
-      <c r="E36" s="298"/>
+      <c r="E36" s="297"/>
     </row>
     <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="298"/>
+      <c r="E37" s="297"/>
     </row>
     <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
@@ -11222,7 +11278,7 @@
         <v>3.6438380069902347E-2</v>
       </c>
       <c r="D38" s="27"/>
-      <c r="E38" s="295"/>
+      <c r="E38" s="294"/>
       <c r="F38" s="27"/>
       <c r="G38" s="13">
         <f t="shared" ref="G38:Q38" si="15">IF(G$4="","",ABS(G33/G$4))</f>
@@ -11280,7 +11336,7 @@
         <v>5.701341376549038E-3</v>
       </c>
       <c r="D39" s="27"/>
-      <c r="E39" s="295"/>
+      <c r="E39" s="294"/>
       <c r="F39" s="27"/>
       <c r="G39" s="13">
         <f t="shared" ref="G39:Q39" si="16">IF(G$4="","",ABS(G34/G$4))</f>
@@ -11336,7 +11392,7 @@
         <f>ABS(C35/$C$4)</f>
         <v>4.2139721446451381E-2</v>
       </c>
-      <c r="E40" s="298"/>
+      <c r="E40" s="297"/>
       <c r="G40" s="30">
         <f t="shared" ref="G40:Q40" si="17">IF(G$4="","",ABS(G35/G$4))</f>
         <v>3.6846911456484638E-2</v>
@@ -11384,26 +11440,26 @@
     </row>
     <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
-      <c r="E41" s="298"/>
+      <c r="E41" s="297"/>
     </row>
     <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
-      <c r="E42" s="298"/>
+      <c r="E42" s="297"/>
     </row>
     <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
       </c>
-      <c r="C43" s="292">
+      <c r="C43" s="291">
         <v>0.25</v>
       </c>
       <c r="D43" s="27"/>
-      <c r="E43" s="295" t="s">
-        <v>337</v>
+      <c r="E43" s="294" t="s">
+        <v>335</v>
       </c>
       <c r="F43" s="27"/>
       <c r="G43" s="6">
@@ -11482,7 +11538,7 @@
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="E46" s="298"/>
+      <c r="E46" s="297"/>
     </row>
     <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
@@ -11493,7 +11549,7 @@
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-7672861</v>
       </c>
-      <c r="E47" s="298"/>
+      <c r="E47" s="297"/>
       <c r="G47" s="191">
         <f>Data!C51</f>
         <v>-7672861</v>
@@ -11542,111 +11598,111 @@
     <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C48" s="191">
         <f>BS!D75*C53</f>
         <v>38554805.997018404</v>
       </c>
-      <c r="E48" s="298"/>
-      <c r="G48" s="323">
+      <c r="E48" s="297"/>
+      <c r="G48" s="322">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>38554805.997018404</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="322">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>66982141.426252395</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="322">
         <f t="shared" si="19"/>
         <v>61731794.960215338</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="322">
         <f t="shared" si="19"/>
         <v>33863778.321634412</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="322">
         <f t="shared" si="19"/>
         <v>41746958.77028092</v>
       </c>
-      <c r="L48" s="323">
+      <c r="L48" s="322">
         <f t="shared" si="19"/>
         <v>8061746.2233673697</v>
       </c>
-      <c r="M48" s="323">
+      <c r="M48" s="322">
         <f t="shared" si="19"/>
         <v>6208975.7821457442</v>
       </c>
-      <c r="N48" s="323">
+      <c r="N48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="323">
+      <c r="O48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="323">
+      <c r="P48" s="322">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="323" t="str">
+      <c r="Q48" s="322" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
-      <c r="B49" s="318" t="s">
-        <v>345</v>
-      </c>
-      <c r="C49" s="319">
+      <c r="B49" s="317" t="s">
+        <v>343</v>
+      </c>
+      <c r="C49" s="318">
         <f>BS!$C$66*C53</f>
         <v>41044772</v>
       </c>
-      <c r="D49" s="320"/>
-      <c r="E49" s="321"/>
-      <c r="F49" s="320"/>
-      <c r="G49" s="319">
+      <c r="D49" s="319"/>
+      <c r="E49" s="320"/>
+      <c r="F49" s="319"/>
+      <c r="G49" s="318">
         <f>Data!C52</f>
         <v>41044772</v>
       </c>
-      <c r="H49" s="319">
+      <c r="H49" s="318">
         <f>Data!D52</f>
         <v>71308016</v>
       </c>
-      <c r="I49" s="319">
+      <c r="I49" s="318">
         <f>Data!E52</f>
         <v>65718589</v>
       </c>
-      <c r="J49" s="319">
+      <c r="J49" s="318">
         <f>Data!F52</f>
         <v>36050786</v>
       </c>
-      <c r="K49" s="319">
+      <c r="K49" s="318">
         <f>Data!G52</f>
         <v>44443082</v>
       </c>
-      <c r="L49" s="319">
+      <c r="L49" s="318">
         <f>Data!H52</f>
         <v>8582394</v>
       </c>
-      <c r="M49" s="319">
+      <c r="M49" s="318">
         <f>Data!I52</f>
         <v>6609967</v>
       </c>
-      <c r="N49" s="319">
+      <c r="N49" s="318">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="319">
+      <c r="O49" s="318">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="319">
+      <c r="P49" s="318">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="319" t="str">
+      <c r="Q49" s="318" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11660,7 +11716,7 @@
         <f>C47+C48</f>
         <v>30881944.997018404</v>
       </c>
-      <c r="E50" s="298"/>
+      <c r="E50" s="297"/>
       <c r="G50" s="184">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>30881944.997018404</v>
@@ -11708,14 +11764,14 @@
     </row>
     <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
-      <c r="E51" s="298"/>
+      <c r="E51" s="297"/>
     </row>
     <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="E52" s="298"/>
+      <c r="E52" s="297"/>
       <c r="G52" s="97" t="s">
         <v>220</v>
       </c>
@@ -11729,8 +11785,8 @@
         <f>G53</f>
         <v>3.7946126449583846E-2</v>
       </c>
-      <c r="E53" s="295" t="s">
-        <v>338</v>
+      <c r="E53" s="294" t="s">
+        <v>336</v>
       </c>
       <c r="G53" s="6">
         <f>IF(Normalized_FCF!G4="","",Normalized_FCF!G49/BS!$C$66)</f>
@@ -11756,8 +11812,8 @@
         <f>G54</f>
         <v>6.2117512427032839E-2</v>
       </c>
-      <c r="E54" s="295" t="s">
-        <v>339</v>
+      <c r="E54" s="294" t="s">
+        <v>337</v>
       </c>
       <c r="G54" s="23">
         <f>IFERROR(ABS(Normalized_FCF!G47/BS!$G$31),0)</f>
@@ -11783,7 +11839,7 @@
         <f>-C8/C47</f>
         <v>407.08280219033122</v>
       </c>
-      <c r="E55" s="298"/>
+      <c r="E55" s="297"/>
       <c r="G55" s="42">
         <f t="shared" ref="G55:Q55" si="21">IF(G4="","",-G8/G47)</f>
         <v>405.22206501590478</v>
@@ -11831,14 +11887,14 @@
     </row>
     <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
-      <c r="E56" s="298"/>
+      <c r="E56" s="297"/>
     </row>
     <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="298"/>
+      <c r="E57" s="297"/>
       <c r="G57" s="97" t="s">
         <v>220</v>
       </c>
@@ -11852,7 +11908,7 @@
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
-      <c r="E58" s="298"/>
+      <c r="E58" s="297"/>
       <c r="G58" s="191">
         <f>Data!C56</f>
         <v>0</v>
@@ -11907,7 +11963,7 @@
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
-      <c r="E59" s="298"/>
+      <c r="E59" s="297"/>
       <c r="G59" s="191">
         <f>Data!C55</f>
         <v>0</v>
@@ -11962,7 +12018,7 @@
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
-      <c r="E60" s="298"/>
+      <c r="E60" s="297"/>
       <c r="G60" s="191">
         <f>Data!C57</f>
         <v>0</v>
@@ -12017,7 +12073,7 @@
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
-      <c r="E61" s="298"/>
+      <c r="E61" s="297"/>
       <c r="G61" s="184">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
@@ -12068,11 +12124,11 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="293">
-        <v>0</v>
-      </c>
-      <c r="E62" s="296" t="s">
-        <v>340</v>
+      <c r="C62" s="292">
+        <v>0</v>
+      </c>
+      <c r="E62" s="295" t="s">
+        <v>338</v>
       </c>
       <c r="G62" s="191">
         <f>Data!C58</f>
@@ -12128,7 +12184,7 @@
         <f>C61+C62</f>
         <v>0</v>
       </c>
-      <c r="E63" s="298"/>
+      <c r="E63" s="297"/>
       <c r="G63" s="184">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>-222656878</v>
@@ -12176,14 +12232,14 @@
     </row>
     <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
-      <c r="E64" s="298"/>
+      <c r="E64" s="297"/>
     </row>
     <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
       </c>
-      <c r="E65" s="298"/>
+      <c r="E65" s="297"/>
       <c r="G65" s="97" t="s">
         <v>220</v>
       </c>
@@ -12197,7 +12253,7 @@
         <f>G66</f>
         <v>0</v>
       </c>
-      <c r="E66" s="298"/>
+      <c r="E66" s="297"/>
       <c r="G66" s="23">
         <f>IFERROR(G58/BS!$C$67,0)</f>
         <v>0</v>
@@ -12222,7 +12278,7 @@
         <f>G67</f>
         <v>0</v>
       </c>
-      <c r="E67" s="298"/>
+      <c r="E67" s="297"/>
       <c r="G67" s="23">
         <f>IFERROR(G59/BS!$C$68,0)</f>
         <v>0</v>
@@ -12247,7 +12303,7 @@
         <f>G68</f>
         <v>0</v>
       </c>
-      <c r="E68" s="298"/>
+      <c r="E68" s="297"/>
       <c r="G68" s="23">
         <f>IFERROR(G60/BS!$C$69,0)</f>
         <v>0</v>
@@ -12273,7 +12329,7 @@
         <v>0</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="303"/>
+      <c r="E69" s="302"/>
       <c r="F69" s="9"/>
       <c r="G69" s="71">
         <f>G61/BS!C70</f>
@@ -12301,7 +12357,7 @@
       <c r="C71" s="54"/>
       <c r="D71" s="56"/>
       <c r="E71" s="66" t="s">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="F71" s="56"/>
       <c r="G71" s="37"/>
@@ -12323,7 +12379,7 @@
       </c>
       <c r="C72" s="62"/>
       <c r="D72" s="27"/>
-      <c r="E72" s="295"/>
+      <c r="E72" s="294"/>
       <c r="F72" s="27"/>
       <c r="G72" s="97"/>
       <c r="H72" s="12"/>
@@ -12347,7 +12403,7 @@
         <v>0.73718829498715255</v>
       </c>
       <c r="D73" s="27"/>
-      <c r="E73" s="295"/>
+      <c r="E73" s="294"/>
       <c r="F73" s="27"/>
       <c r="G73" s="6">
         <f t="shared" ref="G73:Q73" si="24">IF(G$4="","",ABS(G5/G$4))</f>
@@ -12404,7 +12460,7 @@
         <v>0.26281170501284751</v>
       </c>
       <c r="D74" s="27"/>
-      <c r="E74" s="295"/>
+      <c r="E74" s="294"/>
       <c r="F74" s="27"/>
       <c r="G74" s="65">
         <f t="shared" ref="G74:Q74" si="25">IF(G$4="","",ABS(G6/G$4))</f>
@@ -12461,7 +12517,7 @@
         <v>4.2139721446451381E-2</v>
       </c>
       <c r="D75" s="27"/>
-      <c r="E75" s="295"/>
+      <c r="E75" s="294"/>
       <c r="F75" s="27"/>
       <c r="G75" s="6">
         <f t="shared" ref="G75:Q75" si="26">IF(G$4="","",ABS(G7/G$4))</f>
@@ -12518,7 +12574,7 @@
         <v>0.22067198356639611</v>
       </c>
       <c r="D76" s="27"/>
-      <c r="E76" s="295"/>
+      <c r="E76" s="294"/>
       <c r="F76" s="27"/>
       <c r="G76" s="65">
         <f t="shared" ref="G76:Q76" si="27">IF(G$4="","",ABS(G8/G$4))</f>
@@ -12575,7 +12631,7 @@
         <v>4.0688123714313247E-2</v>
       </c>
       <c r="D77" s="27"/>
-      <c r="E77" s="295"/>
+      <c r="E77" s="294"/>
       <c r="F77" s="27"/>
       <c r="G77" s="6">
         <f t="shared" ref="G77:Q77" si="28">IF(G$4="","",G9/G$4)</f>
@@ -12632,8 +12688,8 @@
         <v>4.0688123714313247E-2</v>
       </c>
       <c r="D78" s="27"/>
-      <c r="E78" s="296" t="s">
-        <v>452</v>
+      <c r="E78" s="295" t="s">
+        <v>460</v>
       </c>
       <c r="F78" s="27"/>
       <c r="G78" s="6">
@@ -12691,7 +12747,7 @@
         <v>0</v>
       </c>
       <c r="D79" s="27"/>
-      <c r="E79" s="295"/>
+      <c r="E79" s="294"/>
       <c r="F79" s="27"/>
       <c r="G79" s="65">
         <f t="shared" ref="G79:Q79" si="30">IF(G$4="","",G11/G$4)</f>
@@ -12748,7 +12804,7 @@
         <v>2.1817840267505887E-3</v>
       </c>
       <c r="D80" s="27"/>
-      <c r="E80" s="295"/>
+      <c r="E80" s="294"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
@@ -12805,7 +12861,7 @@
         <v>0.22285376759314668</v>
       </c>
       <c r="D81" s="27"/>
-      <c r="E81" s="295"/>
+      <c r="E81" s="294"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
@@ -12862,7 +12918,7 @@
         <v>5.571344189828667E-2</v>
       </c>
       <c r="D82" s="27"/>
-      <c r="E82" s="295"/>
+      <c r="E82" s="294"/>
       <c r="F82" s="27"/>
       <c r="G82" s="6">
         <f t="shared" ref="G82:Q82" si="33">IF(G$4="","",ABS(G14/G$4))</f>
@@ -12915,12 +12971,12 @@
         <f>B15</f>
         <v>NCI’s Share of Profits</v>
       </c>
-      <c r="C83" s="294">
+      <c r="C83" s="293">
         <f>MIN(BS!C62,MAX(G83:K83))</f>
         <v>1.0023684472850819E-2</v>
       </c>
       <c r="D83" s="27"/>
-      <c r="E83" s="295"/>
+      <c r="E83" s="294"/>
       <c r="F83" s="27"/>
       <c r="G83" s="6">
         <f t="shared" ref="G83:Q83" si="34">IF(G$4="","",-G15/G$4)</f>
@@ -12977,7 +13033,7 @@
         <v>0.15711664122200919</v>
       </c>
       <c r="D84" s="27"/>
-      <c r="E84" s="295"/>
+      <c r="E84" s="294"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
@@ -13029,26 +13085,26 @@
       <c r="B85" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C85" s="294">
+      <c r="C85" s="293">
         <v>0</v>
       </c>
       <c r="D85" s="27"/>
-      <c r="E85" s="297" t="str">
+      <c r="E85" s="296" t="str">
         <f>E17</f>
         <v>WCInv is by default excluded</v>
       </c>
       <c r="F85" s="27"/>
-      <c r="G85" s="251"/>
-      <c r="H85" s="251"/>
-      <c r="I85" s="251"/>
-      <c r="J85" s="251"/>
-      <c r="K85" s="251"/>
-      <c r="L85" s="251"/>
-      <c r="M85" s="251"/>
-      <c r="N85" s="251"/>
-      <c r="O85" s="251"/>
-      <c r="P85" s="251"/>
-      <c r="Q85" s="251"/>
+      <c r="G85" s="250"/>
+      <c r="H85" s="250"/>
+      <c r="I85" s="250"/>
+      <c r="J85" s="250"/>
+      <c r="K85" s="250"/>
+      <c r="L85" s="250"/>
+      <c r="M85" s="250"/>
+      <c r="N85" s="250"/>
+      <c r="O85" s="250"/>
+      <c r="P85" s="250"/>
+      <c r="Q85" s="250"/>
     </row>
     <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
@@ -13058,7 +13114,7 @@
       <c r="C86" s="77">
         <v>0</v>
       </c>
-      <c r="E86" s="297" t="str">
+      <c r="E86" s="296" t="str">
         <f>E18</f>
         <v>Net borrowing is excluded</v>
       </c>
@@ -13084,7 +13140,7 @@
         <v>0.15711664122200919</v>
       </c>
       <c r="D87" s="75"/>
-      <c r="E87" s="295"/>
+      <c r="E87" s="294"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
@@ -13133,14 +13189,14 @@
     </row>
     <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
-      <c r="E88" s="298"/>
+      <c r="E88" s="297"/>
     </row>
     <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
-      <c r="E89" s="298"/>
+      <c r="E89" s="297"/>
     </row>
     <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
@@ -13152,7 +13208,7 @@
         <f>G90</f>
         <v>2.4</v>
       </c>
-      <c r="E90" s="298"/>
+      <c r="E90" s="297"/>
       <c r="G90" s="113">
         <f>Data!C65</f>
         <v>2.4</v>
@@ -13208,7 +13264,7 @@
         <f>C90*Common_Shares/scaling_factor</f>
         <v>1161530875.2</v>
       </c>
-      <c r="E91" s="298"/>
+      <c r="E91" s="297"/>
       <c r="G91" s="74">
         <f t="shared" ref="G91:Q91" si="37">IF(G$4="","",G90*Common_Shares/scaling_factor)</f>
         <v>1161530875.2</v>
@@ -13263,7 +13319,7 @@
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
         <v>0.52229477939839231</v>
       </c>
-      <c r="E92" s="298"/>
+      <c r="E92" s="297"/>
       <c r="G92" s="171">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
         <v>0.50006612287112806</v>
@@ -13312,13 +13368,13 @@
     <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
         <v>4.2208934224410834E-2</v>
       </c>
-      <c r="E93" s="298"/>
+      <c r="E93" s="297"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
         <v>4.2208934224410834E-2</v>
@@ -13366,7 +13422,7 @@
     </row>
     <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
-      <c r="E94" s="298"/>
+      <c r="E94" s="297"/>
     </row>
     <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
@@ -13375,7 +13431,7 @@
       </c>
       <c r="C95" s="62"/>
       <c r="D95" s="27"/>
-      <c r="E95" s="295"/>
+      <c r="E95" s="294"/>
       <c r="F95" s="27"/>
       <c r="G95" s="12"/>
       <c r="H95" s="12"/>
@@ -13399,7 +13455,7 @@
         <v>-3.3469780292926132E-2</v>
       </c>
       <c r="D96" s="27"/>
-      <c r="E96" s="295"/>
+      <c r="E96" s="294"/>
       <c r="F96" s="27"/>
       <c r="G96" s="6">
         <f t="shared" ref="G96:Q96" si="40">IF(H4="","",G4/H4-1)</f>
@@ -13456,7 +13512,7 @@
         <v>4.5467350067964762E-3</v>
       </c>
       <c r="D97" s="27"/>
-      <c r="E97" s="295"/>
+      <c r="E97" s="294"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
@@ -13534,7 +13590,7 @@
       <c r="B100" s="64" t="s">
         <v>28</v>
       </c>
-      <c r="E100" s="298"/>
+      <c r="E100" s="297"/>
       <c r="G100" s="97" t="s">
         <v>220</v>
       </c>
@@ -13549,7 +13605,7 @@
         <v>10968339719.389999</v>
       </c>
       <c r="D101" s="26"/>
-      <c r="E101" s="299"/>
+      <c r="E101" s="298"/>
       <c r="F101" s="26"/>
       <c r="G101" s="183">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
@@ -13606,7 +13662,7 @@
         <v>91009309.849999994</v>
       </c>
       <c r="D102" s="89"/>
-      <c r="E102" s="300"/>
+      <c r="E102" s="299"/>
       <c r="F102" s="89"/>
       <c r="G102" s="185">
         <f>IF(G$4="","",Data!D77)</f>
@@ -13663,7 +13719,7 @@
         <v>2185835620.7199998</v>
       </c>
       <c r="D103" s="89"/>
-      <c r="E103" s="300"/>
+      <c r="E103" s="299"/>
       <c r="F103" s="89"/>
       <c r="G103" s="185">
         <f>IF(G$4="","",Data!D78)</f>
@@ -13720,7 +13776,7 @@
         <v>8514681613.9500008</v>
       </c>
       <c r="D104" s="26"/>
-      <c r="E104" s="299"/>
+      <c r="E104" s="298"/>
       <c r="F104" s="26"/>
       <c r="G104" s="183">
         <f>Data!C79</f>
@@ -13777,7 +13833,7 @@
         <v>2453658105.4399986</v>
       </c>
       <c r="D105" s="26"/>
-      <c r="E105" s="299"/>
+      <c r="E105" s="298"/>
       <c r="F105" s="26"/>
       <c r="G105" s="183">
         <f>Data!C80</f>
@@ -13826,7 +13882,7 @@
     </row>
     <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
-      <c r="E106" s="298"/>
+      <c r="E106" s="297"/>
     </row>
     <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
@@ -13835,7 +13891,7 @@
       </c>
       <c r="C107" s="26"/>
       <c r="D107" s="26"/>
-      <c r="E107" s="299"/>
+      <c r="E107" s="298"/>
       <c r="F107" s="26"/>
       <c r="G107" s="97" t="s">
         <v>220</v>
@@ -13861,7 +13917,7 @@
         <v>6.4297329243833525E-3</v>
       </c>
       <c r="D108" s="26"/>
-      <c r="E108" s="299"/>
+      <c r="E108" s="298"/>
       <c r="F108" s="26"/>
       <c r="G108" s="94">
         <f t="shared" ref="G108:Q108" si="43">IF(G$4="","",G102/G$4)</f>
@@ -13918,7 +13974,7 @@
         <v>0.15442748968207132</v>
       </c>
       <c r="D109" s="26"/>
-      <c r="E109" s="299"/>
+      <c r="E109" s="298"/>
       <c r="F109" s="26"/>
       <c r="G109" s="94">
         <f t="shared" ref="G109:Q109" si="44">IF(G$4="","",G103/G$4)</f>
@@ -13975,7 +14031,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="26"/>
-      <c r="E110" s="299"/>
+      <c r="E110" s="298"/>
       <c r="F110" s="26"/>
       <c r="G110" s="94">
         <f>BS!$G$38/G$4</f>
@@ -13994,63 +14050,63 @@
     </row>
     <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
-      <c r="E111" s="298"/>
+      <c r="E111" s="297"/>
     </row>
     <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
-      <c r="E112" s="298"/>
+      <c r="E112" s="297"/>
     </row>
     <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="C113" s="170"/>
-      <c r="E113" s="298"/>
-      <c r="G113" s="328">
+      <c r="E113" s="297"/>
+      <c r="G113" s="327">
         <f>IF(G$4="","",Data!C$22/Data!C15)</f>
         <v>1.1301097053348144</v>
       </c>
-      <c r="H113" s="328">
+      <c r="H113" s="327">
         <f>IF(H$4="","",Data!D$22/Data!D15)</f>
         <v>1.1421244767311443</v>
       </c>
-      <c r="I113" s="328">
+      <c r="I113" s="327">
         <f>IF(I$4="","",Data!E$22/Data!E15)</f>
         <v>1.4506354245537583</v>
       </c>
-      <c r="J113" s="328">
+      <c r="J113" s="327">
         <f>IF(J$4="","",Data!F$22/Data!F15)</f>
         <v>1.4858503664510887</v>
       </c>
-      <c r="K113" s="328">
+      <c r="K113" s="327">
         <f>IF(K$4="","",Data!G$22/Data!G15)</f>
         <v>2.1056296742310616</v>
       </c>
-      <c r="L113" s="328">
+      <c r="L113" s="327">
         <f>IF(L$4="","",Data!H$22/Data!H15)</f>
         <v>0.96876332816786648</v>
       </c>
-      <c r="M113" s="328">
+      <c r="M113" s="327">
         <f>IF(M$4="","",Data!I$22/Data!I15)</f>
         <v>1.767034158859303</v>
       </c>
-      <c r="N113" s="328">
+      <c r="N113" s="327">
         <f>IF(N$4="","",Data!J$22/Data!J15)</f>
         <v>2.5144917688633623</v>
       </c>
-      <c r="O113" s="328">
+      <c r="O113" s="327">
         <f>IF(O$4="","",Data!K$22/Data!K15)</f>
         <v>4.0690767846879998</v>
       </c>
-      <c r="P113" s="328">
+      <c r="P113" s="327">
         <f>IF(P$4="","",Data!L$22/Data!L15)</f>
         <v>-2.9196128327089879</v>
       </c>
-      <c r="Q113" s="328" t="str">
+      <c r="Q113" s="327" t="str">
         <f>IF(Q$4="","",Data!M$22/Data!M15)</f>
         <v/>
       </c>
@@ -14058,58 +14114,58 @@
     <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C114" s="170"/>
-      <c r="E114" s="298"/>
-      <c r="G114" s="328">
+      <c r="E114" s="297"/>
+      <c r="G114" s="327">
         <f>IF(G$4="","",Data!C$22/G19)</f>
         <v>1.0944103829432141</v>
       </c>
-      <c r="H114" s="328">
+      <c r="H114" s="327">
         <f>IF(H$4="","",Data!D$22/H19)</f>
         <v>1.1613302966984029</v>
       </c>
-      <c r="I114" s="328">
+      <c r="I114" s="327">
         <f>IF(I$4="","",Data!E$22/I19)</f>
         <v>1.477203347027797</v>
       </c>
-      <c r="J114" s="328">
+      <c r="J114" s="327">
         <f>IF(J$4="","",Data!F$22/J19)</f>
         <v>1.5005063764384885</v>
       </c>
-      <c r="K114" s="328">
+      <c r="K114" s="327">
         <f>IF(K$4="","",Data!G$22/K19)</f>
         <v>2.773447584133756</v>
       </c>
-      <c r="L114" s="328">
+      <c r="L114" s="327">
         <f>IF(L$4="","",Data!H$22/L19)</f>
         <v>1.5109716987792317</v>
       </c>
-      <c r="M114" s="328">
+      <c r="M114" s="327">
         <f>IF(M$4="","",Data!I$22/M19)</f>
         <v>1.7382339197122179</v>
       </c>
-      <c r="N114" s="328">
+      <c r="N114" s="327">
         <f>IF(N$4="","",Data!J$22/N19)</f>
         <v>2.378364555476101</v>
       </c>
-      <c r="O114" s="328">
+      <c r="O114" s="327">
         <f>IF(O$4="","",Data!K$22/O19)</f>
         <v>1.6724741518288628</v>
       </c>
-      <c r="P114" s="328">
+      <c r="P114" s="327">
         <f>IF(P$4="","",Data!L$22/P19)</f>
         <v>2.3783234522476708</v>
       </c>
-      <c r="Q114" s="328" t="str">
+      <c r="Q114" s="327" t="str">
         <f>IF(Q$4="","",Data!M$22/Q19)</f>
         <v/>
       </c>
     </row>
     <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
-      <c r="E115" s="298"/>
+      <c r="E115" s="297"/>
     </row>
     <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
@@ -14118,7 +14174,7 @@
       </c>
       <c r="C116" s="55"/>
       <c r="D116" s="55"/>
-      <c r="E116" s="301"/>
+      <c r="E116" s="300"/>
       <c r="F116" s="55"/>
       <c r="G116" s="23" t="str">
         <f>IFERROR(IF(#REF!*G118*(1/#REF!)=G120,"","Error"),"")</f>
@@ -14174,7 +14230,7 @@
         <f>C81</f>
         <v>0.22285376759314668</v>
       </c>
-      <c r="E117" s="298"/>
+      <c r="E117" s="297"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
         <v>0.21441999007930274</v>
@@ -14228,7 +14284,7 @@
         <f>C4/C101</f>
         <v>1.2904821269100146</v>
       </c>
-      <c r="E118" s="298"/>
+      <c r="E118" s="297"/>
       <c r="G118" s="42">
         <f t="shared" ref="G118:Q118" si="46">IF(G4="","",G4/G101)</f>
         <v>1.3351699725448014</v>
@@ -14283,7 +14339,7 @@
         <v>4.4701988818540466</v>
       </c>
       <c r="D119" s="11"/>
-      <c r="E119" s="302"/>
+      <c r="E119" s="301"/>
       <c r="F119" s="11"/>
       <c r="G119" s="15">
         <f t="shared" ref="G119:Q119" si="47">IF(G$4="","",G101/G105)</f>
@@ -14340,7 +14396,7 @@
         <v>1.2729930668709819</v>
       </c>
       <c r="D120" s="103"/>
-      <c r="E120" s="301"/>
+      <c r="E120" s="300"/>
       <c r="F120" s="103"/>
       <c r="G120" s="102">
         <f t="shared" ref="G120:Q120" si="48">IF(G$4="","",G8/G105)</f>
@@ -14436,7 +14492,7 @@
       </c>
       <c r="C123" s="180"/>
       <c r="D123" s="27"/>
-      <c r="E123" s="295"/>
+      <c r="E123" s="294"/>
       <c r="F123" s="27"/>
       <c r="G123" s="12"/>
       <c r="H123" s="12"/>
@@ -14461,7 +14517,7 @@
         <v>4.5951062401283256</v>
       </c>
       <c r="D124" s="27"/>
-      <c r="E124" s="295"/>
+      <c r="E124" s="294"/>
       <c r="F124" s="27"/>
       <c r="G124" s="178">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
@@ -14518,7 +14574,7 @@
         <v>8.081439043489845E-2</v>
       </c>
       <c r="D125" s="27"/>
-      <c r="E125" s="295"/>
+      <c r="E125" s="294"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
@@ -14567,7 +14623,7 @@
     </row>
     <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C126" s="170"/>
       <c r="G126" s="23">
@@ -15300,7 +15356,7 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>ISBLANK(G4)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -15368,7 +15424,7 @@
         <v>251</v>
       </c>
       <c r="F4" s="135">
-        <f>Thesis!C86</f>
+        <f>Terminal_Growth</f>
         <v>0</v>
       </c>
       <c r="H4" s="121"/>
@@ -15378,7 +15434,7 @@
         <v>124</v>
       </c>
       <c r="C5" s="228">
-        <f>Thesis!C80</f>
+        <f>Equity_Cost</f>
         <v>0.08</v>
       </c>
       <c r="E5" s="149"/>
@@ -15396,10 +15452,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="358" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="358"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8">
@@ -15414,8 +15470,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="358"/>
+      <c r="F7" s="358"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8">
@@ -15430,8 +15486,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="358"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8">
@@ -15446,8 +15502,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="358"/>
+      <c r="F9" s="358"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
@@ -16792,7 +16848,7 @@
     </row>
     <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C80" s="156" t="s">
         <v>106</v>
@@ -16823,12 +16879,12 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="C21:F50">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E65 B66:F71">
-    <cfRule type="expression" dxfId="0" priority="14">
+    <cfRule type="expression" dxfId="2" priority="14">
       <formula>ISNUMBER(MATCH(B65, $E$75:$E$78, 0))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -16843,6 +16899,1457 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27DB9BF-8D77-49A8-A09B-23E6CA7BEA90}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A2:H89"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <cols>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="6" width="20.73046875" customWidth="1"/>
+    <col min="7" max="7" width="5.73046875" customWidth="1"/>
+    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" ht="13.9">
+      <c r="B2" s="36" t="s">
+        <v>445</v>
+      </c>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="H2" s="131" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" ht="13.15">
+      <c r="B3" s="109" t="s">
+        <v>444</v>
+      </c>
+      <c r="C3" s="107">
+        <f>scaling_factor</f>
+        <v>1</v>
+      </c>
+      <c r="E3" s="109" t="s">
+        <v>125</v>
+      </c>
+      <c r="H3" s="121"/>
+    </row>
+    <row r="4" spans="2:8">
+      <c r="B4" s="100" t="s">
+        <v>442</v>
+      </c>
+      <c r="C4" s="110">
+        <f>Normalized_FCF!C91</f>
+        <v>1161530875.2</v>
+      </c>
+      <c r="D4" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E4" s="100" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="135">
+        <f>Thesis!E22</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="121"/>
+    </row>
+    <row r="5" spans="2:8">
+      <c r="B5" s="227" t="s">
+        <v>124</v>
+      </c>
+      <c r="C5" s="228">
+        <f>Equity_Cost</f>
+        <v>0.08</v>
+      </c>
+      <c r="E5" s="149"/>
+      <c r="H5" s="121"/>
+    </row>
+    <row r="6" spans="2:8" ht="13.15" customHeight="1">
+      <c r="B6" s="150" t="s">
+        <v>443</v>
+      </c>
+      <c r="C6" s="232">
+        <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
+        <v>14519135940</v>
+      </c>
+      <c r="D6" t="str">
+        <f>Reporting_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="E6" s="358"/>
+      <c r="F6" s="358"/>
+      <c r="H6" s="121"/>
+    </row>
+    <row r="7" spans="2:8" ht="13.15">
+      <c r="B7" s="150" t="s">
+        <v>446</v>
+      </c>
+      <c r="C7" s="112">
+        <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
+        <v>30</v>
+      </c>
+      <c r="D7" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="H7" s="121"/>
+    </row>
+    <row r="8" spans="2:8">
+      <c r="H8" s="121"/>
+    </row>
+    <row r="9" spans="2:8" ht="13.9">
+      <c r="B9" s="36" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="H9" s="121"/>
+    </row>
+    <row r="10" spans="2:8" ht="13.15">
+      <c r="B10" s="120" t="s">
+        <v>136</v>
+      </c>
+      <c r="H10" s="121"/>
+    </row>
+    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B11" s="153" t="s">
+        <v>134</v>
+      </c>
+      <c r="C11" s="162">
+        <f>Scenarios!C65</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="H11" s="121"/>
+    </row>
+    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B12" s="119" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="163">
+        <f>Scenarios!C64</f>
+        <v>10</v>
+      </c>
+      <c r="H12" s="121"/>
+    </row>
+    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+      <c r="B13" s="154" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="141">
+        <f>F47/Common_Shares*scaling_factor</f>
+        <v>34.814523865974699</v>
+      </c>
+      <c r="D13" t="str">
+        <f>Market_currency</f>
+        <v>CNY</v>
+      </c>
+      <c r="H13" s="121"/>
+    </row>
+    <row r="14" spans="2:8">
+      <c r="H14" s="121"/>
+    </row>
+    <row r="15" spans="2:8" ht="13.15">
+      <c r="B15" s="129" t="s">
+        <v>108</v>
+      </c>
+      <c r="C15" s="129" t="s">
+        <v>448</v>
+      </c>
+      <c r="D15" s="129" t="s">
+        <v>119</v>
+      </c>
+      <c r="E15" s="129" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="130" t="s">
+        <v>447</v>
+      </c>
+      <c r="H15" s="121"/>
+    </row>
+    <row r="16" spans="2:8">
+      <c r="B16" s="123">
+        <v>1</v>
+      </c>
+      <c r="C16" s="124">
+        <f>C4*(1+D16)</f>
+        <v>1215629025.7472811</v>
+      </c>
+      <c r="D16" s="139">
+        <f>IF($C$12&lt;B16,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E16" s="125">
+        <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
+        <v>0.92592592592592582</v>
+      </c>
+      <c r="F16" s="126">
+        <f t="shared" ref="F16:F46" si="1">C16*E16</f>
+        <v>1125582431.2474823</v>
+      </c>
+      <c r="H16" s="121"/>
+    </row>
+    <row r="17" spans="2:8">
+      <c r="B17" s="123">
+        <v>2</v>
+      </c>
+      <c r="C17" s="124">
+        <f t="shared" ref="C17:C45" si="2">IF(ROW()-ROW($C$16)&lt;$C$12, $C$16*(1+D17)^(ROW()-ROW($C$16)), 0)</f>
+        <v>1272246790.6716938</v>
+      </c>
+      <c r="D17" s="139">
+        <f>IF($C$12&lt;B17,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E17" s="125">
+        <f t="shared" si="0"/>
+        <v>0.85733882030178321</v>
+      </c>
+      <c r="F17" s="126">
+        <f t="shared" si="1"/>
+        <v>1090746562.6471996</v>
+      </c>
+      <c r="H17" s="121"/>
+    </row>
+    <row r="18" spans="2:8">
+      <c r="B18" s="123">
+        <v>3</v>
+      </c>
+      <c r="C18" s="124">
+        <f t="shared" si="2"/>
+        <v>1331501520.687546</v>
+      </c>
+      <c r="D18" s="139">
+        <f>IF($C$12&lt;B18,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E18" s="125">
+        <f t="shared" si="0"/>
+        <v>0.79383224102016958</v>
+      </c>
+      <c r="F18" s="126">
+        <f t="shared" si="1"/>
+        <v>1056988836.0891583</v>
+      </c>
+      <c r="H18" s="121"/>
+    </row>
+    <row r="19" spans="2:8">
+      <c r="B19" s="123">
+        <v>4</v>
+      </c>
+      <c r="C19" s="124">
+        <f t="shared" si="2"/>
+        <v>1393516032.1035132</v>
+      </c>
+      <c r="D19" s="139">
+        <f>IF($C$12&lt;B19,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E19" s="125">
+        <f t="shared" si="0"/>
+        <v>0.73502985279645328</v>
+      </c>
+      <c r="F19" s="126">
+        <f t="shared" si="1"/>
+        <v>1024275883.946543</v>
+      </c>
+      <c r="H19" s="121"/>
+    </row>
+    <row r="20" spans="2:8">
+      <c r="B20" s="123">
+        <v>5</v>
+      </c>
+      <c r="C20" s="124">
+        <f t="shared" si="2"/>
+        <v>1458418861.3819902</v>
+      </c>
+      <c r="D20" s="139">
+        <f>IF($C$12&lt;B20,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E20" s="125">
+        <f t="shared" si="0"/>
+        <v>0.68058319703375303</v>
+      </c>
+      <c r="F20" s="126">
+        <f t="shared" si="1"/>
+        <v>992575371.29368079</v>
+      </c>
+      <c r="H20" s="121"/>
+    </row>
+    <row r="21" spans="2:8">
+      <c r="B21" s="123">
+        <v>6</v>
+      </c>
+      <c r="C21" s="124">
+        <f t="shared" si="2"/>
+        <v>1526344531.5545132</v>
+      </c>
+      <c r="D21" s="139">
+        <f>IF($C$12&lt;B21,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E21" s="125">
+        <f t="shared" si="0"/>
+        <v>0.63016962688310452</v>
+      </c>
+      <c r="F21" s="126">
+        <f t="shared" si="1"/>
+        <v>961855963.94477451</v>
+      </c>
+      <c r="H21" s="121"/>
+    </row>
+    <row r="22" spans="2:8">
+      <c r="B22" s="123">
+        <v>7</v>
+      </c>
+      <c r="C22" s="124">
+        <f t="shared" si="2"/>
+        <v>1597433831.0454438</v>
+      </c>
+      <c r="D22" s="139">
+        <f>IF($C$12&lt;B22,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E22" s="125">
+        <f t="shared" si="0"/>
+        <v>0.58349039526213387</v>
+      </c>
+      <c r="F22" s="126">
+        <f t="shared" si="1"/>
+        <v>932087297.48181081</v>
+      </c>
+      <c r="H22" s="121"/>
+    </row>
+    <row r="23" spans="2:8">
+      <c r="B23" s="123">
+        <v>8</v>
+      </c>
+      <c r="C23" s="124">
+        <f t="shared" si="2"/>
+        <v>1671834105.4818304</v>
+      </c>
+      <c r="D23" s="139">
+        <f>IF($C$12&lt;B23,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E23" s="125">
+        <f t="shared" si="0"/>
+        <v>0.54026888450197574</v>
+      </c>
+      <c r="F23" s="126">
+        <f t="shared" si="1"/>
+        <v>903239947.241027</v>
+      </c>
+      <c r="H23" s="121"/>
+    </row>
+    <row r="24" spans="2:8">
+      <c r="B24" s="123">
+        <v>9</v>
+      </c>
+      <c r="C24" s="124">
+        <f t="shared" si="2"/>
+        <v>1749699563.0942783</v>
+      </c>
+      <c r="D24" s="139">
+        <f>IF($C$12&lt;B24,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E24" s="125">
+        <f t="shared" si="0"/>
+        <v>0.50024896713145905</v>
+      </c>
+      <c r="F24" s="126">
+        <f t="shared" si="1"/>
+        <v>875285399.22827792</v>
+      </c>
+      <c r="H24" s="121"/>
+    </row>
+    <row r="25" spans="2:8">
+      <c r="B25" s="123">
+        <v>10</v>
+      </c>
+      <c r="C25" s="124">
+        <f t="shared" si="2"/>
+        <v>1831191594.3418229</v>
+      </c>
+      <c r="D25" s="139">
+        <f>IF($C$12&lt;B25,0,DDM!$C$11)</f>
+        <v>4.6574870890079501E-2</v>
+      </c>
+      <c r="E25" s="125">
+        <f t="shared" si="0"/>
+        <v>0.46319348808468425</v>
+      </c>
+      <c r="F25" s="126">
+        <f t="shared" si="1"/>
+        <v>848196021.93454313</v>
+      </c>
+      <c r="H25" s="121"/>
+    </row>
+    <row r="26" spans="2:8">
+      <c r="B26" s="123">
+        <v>11</v>
+      </c>
+      <c r="C26" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D26" s="139">
+        <f>IF($C$12&lt;B26,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E26" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F26" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="121"/>
+    </row>
+    <row r="27" spans="2:8">
+      <c r="B27" s="123">
+        <v>12</v>
+      </c>
+      <c r="C27" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D27" s="139">
+        <f>IF($C$12&lt;B27,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E27" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F27" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="121"/>
+    </row>
+    <row r="28" spans="2:8">
+      <c r="B28" s="123">
+        <v>13</v>
+      </c>
+      <c r="C28" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D28" s="139">
+        <f>IF($C$12&lt;B28,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F28" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="121"/>
+    </row>
+    <row r="29" spans="2:8">
+      <c r="B29" s="123">
+        <v>14</v>
+      </c>
+      <c r="C29" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D29" s="139">
+        <f>IF($C$12&lt;B29,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E29" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F29" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H29" s="121"/>
+    </row>
+    <row r="30" spans="2:8">
+      <c r="B30" s="123">
+        <v>15</v>
+      </c>
+      <c r="C30" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D30" s="139">
+        <f>IF($C$12&lt;B30,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F30" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="121"/>
+    </row>
+    <row r="31" spans="2:8">
+      <c r="B31" s="123">
+        <v>16</v>
+      </c>
+      <c r="C31" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D31" s="139">
+        <f>IF($C$12&lt;B31,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E31" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F31" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="121"/>
+    </row>
+    <row r="32" spans="2:8">
+      <c r="B32" s="123">
+        <v>17</v>
+      </c>
+      <c r="C32" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D32" s="139">
+        <f>IF($C$12&lt;B32,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E32" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F32" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="121"/>
+    </row>
+    <row r="33" spans="2:8">
+      <c r="B33" s="123">
+        <v>18</v>
+      </c>
+      <c r="C33" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D33" s="139">
+        <f>IF($C$12&lt;B33,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E33" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F33" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H33" s="121"/>
+    </row>
+    <row r="34" spans="2:8">
+      <c r="B34" s="123">
+        <v>19</v>
+      </c>
+      <c r="C34" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D34" s="139">
+        <f>IF($C$12&lt;B34,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E34" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F34" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="121"/>
+    </row>
+    <row r="35" spans="2:8">
+      <c r="B35" s="123">
+        <v>20</v>
+      </c>
+      <c r="C35" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D35" s="139">
+        <f>IF($C$12&lt;B35,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E35" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F35" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="121"/>
+    </row>
+    <row r="36" spans="2:8">
+      <c r="B36" s="123">
+        <v>21</v>
+      </c>
+      <c r="C36" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D36" s="139">
+        <f>IF($C$12&lt;B36,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E36" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F36" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="121"/>
+    </row>
+    <row r="37" spans="2:8">
+      <c r="B37" s="123">
+        <v>22</v>
+      </c>
+      <c r="C37" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D37" s="139">
+        <f>IF($C$12&lt;B37,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E37" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F37" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H37" s="121"/>
+    </row>
+    <row r="38" spans="2:8">
+      <c r="B38" s="123">
+        <v>23</v>
+      </c>
+      <c r="C38" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D38" s="139">
+        <f>IF($C$12&lt;B38,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F38" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H38" s="121"/>
+    </row>
+    <row r="39" spans="2:8">
+      <c r="B39" s="123">
+        <v>24</v>
+      </c>
+      <c r="C39" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D39" s="139">
+        <f>IF($C$12&lt;B39,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E39" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F39" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H39" s="121"/>
+    </row>
+    <row r="40" spans="2:8">
+      <c r="B40" s="123">
+        <v>25</v>
+      </c>
+      <c r="C40" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D40" s="139">
+        <f>IF($C$12&lt;B40,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E40" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F40" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H40" s="121"/>
+    </row>
+    <row r="41" spans="2:8">
+      <c r="B41" s="123">
+        <v>26</v>
+      </c>
+      <c r="C41" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D41" s="139">
+        <f>IF($C$12&lt;B41,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E41" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F41" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H41" s="121"/>
+    </row>
+    <row r="42" spans="2:8">
+      <c r="B42" s="123">
+        <v>27</v>
+      </c>
+      <c r="C42" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D42" s="139">
+        <f>IF($C$12&lt;B42,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F42" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H42" s="121"/>
+    </row>
+    <row r="43" spans="2:8">
+      <c r="B43" s="123">
+        <v>28</v>
+      </c>
+      <c r="C43" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D43" s="139">
+        <f>IF($C$12&lt;B43,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E43" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F43" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H43" s="121"/>
+    </row>
+    <row r="44" spans="2:8">
+      <c r="B44" s="123">
+        <v>29</v>
+      </c>
+      <c r="C44" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D44" s="139">
+        <f>IF($C$12&lt;B44,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E44" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F44" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H44" s="121"/>
+    </row>
+    <row r="45" spans="2:8">
+      <c r="B45" s="123">
+        <v>30</v>
+      </c>
+      <c r="C45" s="124">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="D45" s="139">
+        <f>IF($C$12&lt;B45,0,DDM!$C$11)</f>
+        <v>0</v>
+      </c>
+      <c r="E45" s="125">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F45" s="126">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="H45" s="121"/>
+    </row>
+    <row r="46" spans="2:8">
+      <c r="B46" s="127" t="s">
+        <v>132</v>
+      </c>
+      <c r="C46" s="124">
+        <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
+        <v>15195362821.841013</v>
+      </c>
+      <c r="D46" s="140">
+        <f>Terminal_Growth</f>
+        <v>0</v>
+      </c>
+      <c r="E46" s="125">
+        <f>1/(1+Equity_Cost)^C12</f>
+        <v>0.46319348808468425</v>
+      </c>
+      <c r="F46" s="126">
+        <f t="shared" si="1"/>
+        <v>7038393108.1608696</v>
+      </c>
+      <c r="H46" s="121"/>
+    </row>
+    <row r="47" spans="2:8">
+      <c r="C47" s="115"/>
+      <c r="E47" s="128" t="s">
+        <v>101</v>
+      </c>
+      <c r="F47" s="138">
+        <f>SUM(F16:F46)</f>
+        <v>16849226823.215366</v>
+      </c>
+      <c r="H47" s="121"/>
+    </row>
+    <row r="48" spans="2:8">
+      <c r="C48" s="115"/>
+      <c r="H48" s="121"/>
+    </row>
+    <row r="49" spans="1:8" ht="13.15">
+      <c r="B49" s="120" t="s">
+        <v>130</v>
+      </c>
+      <c r="C49" s="137"/>
+      <c r="D49" s="137"/>
+      <c r="E49" s="118"/>
+      <c r="F49" s="118"/>
+      <c r="H49" s="121"/>
+    </row>
+    <row r="50" spans="1:8" ht="13.15">
+      <c r="A50" s="134">
+        <f>F47</f>
+        <v>16849226823.215366</v>
+      </c>
+      <c r="B50" s="132">
+        <f>C73</f>
+        <v>0</v>
+      </c>
+      <c r="C50" s="132">
+        <f>C72</f>
+        <v>0.02</v>
+      </c>
+      <c r="D50" s="132">
+        <f>C71</f>
+        <v>0.04</v>
+      </c>
+      <c r="E50" s="132">
+        <f>C70</f>
+        <v>0.06</v>
+      </c>
+      <c r="F50" s="132">
+        <f>C69</f>
+        <v>0.1</v>
+      </c>
+      <c r="H50" s="121"/>
+    </row>
+    <row r="51" spans="1:8" ht="13.15">
+      <c r="A51" s="144">
+        <v>5</v>
+      </c>
+      <c r="B51" s="124">
+        <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
+        <v>14519135939.999998</v>
+      </c>
+      <c r="C51" s="124">
+        <v>14987599269.207245</v>
+      </c>
+      <c r="D51" s="124">
+        <v>15470092870.695057</v>
+      </c>
+      <c r="E51" s="124">
+        <v>15967232438.135504</v>
+      </c>
+      <c r="F51" s="124">
+        <v>17008007866.667847</v>
+      </c>
+      <c r="H51" s="121"/>
+    </row>
+    <row r="52" spans="1:8" ht="13.15">
+      <c r="A52" s="144">
+        <v>10</v>
+      </c>
+      <c r="B52" s="124">
+        <v>14519135939.999992</v>
+      </c>
+      <c r="C52" s="124">
+        <v>15456493979.11182</v>
+      </c>
+      <c r="D52" s="124">
+        <v>16487800673.681828</v>
+      </c>
+      <c r="E52" s="124">
+        <v>17624299619.090118</v>
+      </c>
+      <c r="F52" s="124">
+        <v>20264258618.299137</v>
+      </c>
+      <c r="H52" s="121"/>
+    </row>
+    <row r="53" spans="1:8" ht="13.15">
+      <c r="A53" s="144">
+        <v>15</v>
+      </c>
+      <c r="B53" s="124">
+        <v>14519135939.999992</v>
+      </c>
+      <c r="C53" s="124">
+        <v>16036881194.938818</v>
+      </c>
+      <c r="D53" s="124">
+        <v>17814511855.633007</v>
+      </c>
+      <c r="E53" s="124">
+        <v>19903659458.038651</v>
+      </c>
+      <c r="F53" s="124">
+        <v>25275991333.808659</v>
+      </c>
+      <c r="H53" s="121"/>
+    </row>
+    <row r="54" spans="1:8" ht="13.15">
+      <c r="A54" s="145">
+        <v>20</v>
+      </c>
+      <c r="B54" s="124">
+        <v>14519135939.99999</v>
+      </c>
+      <c r="C54" s="124">
+        <v>16628202692.594425</v>
+      </c>
+      <c r="D54" s="124">
+        <v>19242485668.138107</v>
+      </c>
+      <c r="E54" s="124">
+        <v>22503789472.247555</v>
+      </c>
+      <c r="F54" s="124">
+        <v>31751092105.805897</v>
+      </c>
+      <c r="H54" s="121"/>
+    </row>
+    <row r="55" spans="1:8" ht="13.15">
+      <c r="A55" s="145">
+        <v>25</v>
+      </c>
+      <c r="B55" s="124">
+        <v>14519135939.999989</v>
+      </c>
+      <c r="C55" s="124">
+        <v>17178164497.849728</v>
+      </c>
+      <c r="D55" s="124">
+        <v>20649088452.098736</v>
+      </c>
+      <c r="E55" s="124">
+        <v>25228646670.450939</v>
+      </c>
+      <c r="F55" s="124">
+        <v>39516563417.118462</v>
+      </c>
+      <c r="H55" s="121"/>
+    </row>
+    <row r="56" spans="1:8" ht="13.15">
+      <c r="A56" s="145">
+        <v>30</v>
+      </c>
+      <c r="B56" s="124">
+        <v>14519135939.99999</v>
+      </c>
+      <c r="C56" s="124">
+        <v>17663307314.270393</v>
+      </c>
+      <c r="D56" s="124">
+        <v>21966384424.907784</v>
+      </c>
+      <c r="E56" s="124">
+        <v>27953157592.641045</v>
+      </c>
+      <c r="F56" s="124">
+        <v>48482956373.868553</v>
+      </c>
+      <c r="H56" s="121"/>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="C57" s="115"/>
+      <c r="D57" s="115"/>
+      <c r="E57" s="115"/>
+      <c r="F57" s="115"/>
+      <c r="H57" s="121"/>
+    </row>
+    <row r="58" spans="1:8" ht="13.15">
+      <c r="B58" s="120" t="s">
+        <v>131</v>
+      </c>
+      <c r="C58" s="115"/>
+      <c r="D58" s="115"/>
+      <c r="E58" s="115"/>
+      <c r="F58" s="115"/>
+      <c r="H58" s="121"/>
+    </row>
+    <row r="59" spans="1:8" ht="13.15">
+      <c r="B59" s="133">
+        <f>B50</f>
+        <v>0</v>
+      </c>
+      <c r="C59" s="133">
+        <f>C50</f>
+        <v>0.02</v>
+      </c>
+      <c r="D59" s="133">
+        <f>D50</f>
+        <v>0.04</v>
+      </c>
+      <c r="E59" s="133">
+        <f>E50</f>
+        <v>0.06</v>
+      </c>
+      <c r="F59" s="133">
+        <f>F50</f>
+        <v>0.1</v>
+      </c>
+      <c r="H59" s="121"/>
+    </row>
+    <row r="60" spans="1:8" ht="13.15">
+      <c r="A60" s="144">
+        <v>0</v>
+      </c>
+      <c r="B60" s="125">
+        <f>C7</f>
+        <v>30</v>
+      </c>
+      <c r="C60" s="125">
+        <f>C7</f>
+        <v>30</v>
+      </c>
+      <c r="D60" s="125">
+        <f>C7</f>
+        <v>30</v>
+      </c>
+      <c r="E60" s="142">
+        <f>C7</f>
+        <v>30</v>
+      </c>
+      <c r="F60" s="125">
+        <f>C7</f>
+        <v>30</v>
+      </c>
+      <c r="H60" s="121"/>
+    </row>
+    <row r="61" spans="1:8" ht="13.15">
+      <c r="A61" s="144">
+        <f t="shared" ref="A61:A66" si="3">A51</f>
+        <v>5</v>
+      </c>
+      <c r="B61" s="125">
+        <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
+        <v>29.999999999999996</v>
+      </c>
+      <c r="C61" s="125">
+        <f t="shared" si="4"/>
+        <v>30.967957041954477</v>
+      </c>
+      <c r="D61" s="125">
+        <f t="shared" si="4"/>
+        <v>31.964903974915998</v>
+      </c>
+      <c r="E61" s="125">
+        <f t="shared" si="4"/>
+        <v>32.992112968952966</v>
+      </c>
+      <c r="F61" s="125">
+        <f t="shared" si="4"/>
+        <v>35.142603396551394</v>
+      </c>
+      <c r="H61" s="121"/>
+    </row>
+    <row r="62" spans="1:8" ht="13.15">
+      <c r="A62" s="144">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="B62" s="125">
+        <f t="shared" si="4"/>
+        <v>29.999999999999986</v>
+      </c>
+      <c r="C62" s="125">
+        <f t="shared" si="4"/>
+        <v>31.936805419383283</v>
+      </c>
+      <c r="D62" s="125">
+        <f t="shared" si="4"/>
+        <v>34.067731182800323</v>
+      </c>
+      <c r="E62" s="125">
+        <f t="shared" si="4"/>
+        <v>36.416009241711357</v>
+      </c>
+      <c r="F62" s="125">
+        <f t="shared" si="4"/>
+        <v>41.870794588687772</v>
+      </c>
+      <c r="H62" s="121"/>
+    </row>
+    <row r="63" spans="1:8" ht="13.15">
+      <c r="A63" s="144">
+        <f t="shared" si="3"/>
+        <v>15</v>
+      </c>
+      <c r="B63" s="125">
+        <f t="shared" si="4"/>
+        <v>29.999999999999986</v>
+      </c>
+      <c r="C63" s="125">
+        <f t="shared" si="4"/>
+        <v>33.136023922933568</v>
+      </c>
+      <c r="D63" s="125">
+        <f t="shared" si="4"/>
+        <v>36.809033118605143</v>
+      </c>
+      <c r="E63" s="125">
+        <f t="shared" si="4"/>
+        <v>41.125710662721403</v>
+      </c>
+      <c r="F63" s="125">
+        <f t="shared" si="4"/>
+        <v>52.226230482849225</v>
+      </c>
+      <c r="H63" s="121"/>
+    </row>
+    <row r="64" spans="1:8" ht="13.15">
+      <c r="A64" s="145">
+        <f t="shared" si="3"/>
+        <v>20</v>
+      </c>
+      <c r="B64" s="125">
+        <f t="shared" si="4"/>
+        <v>29.999999999999979</v>
+      </c>
+      <c r="C64" s="125">
+        <f t="shared" si="4"/>
+        <v>34.357835262325722</v>
+      </c>
+      <c r="D64" s="125">
+        <f t="shared" si="4"/>
+        <v>39.75956781655033</v>
+      </c>
+      <c r="E64" s="125">
+        <f t="shared" si="4"/>
+        <v>46.498199821071907</v>
+      </c>
+      <c r="F64" s="125">
+        <f t="shared" si="4"/>
+        <v>65.605334030240982</v>
+      </c>
+      <c r="H64" s="121"/>
+    </row>
+    <row r="65" spans="1:8" ht="13.15">
+      <c r="A65" s="145">
+        <f t="shared" si="3"/>
+        <v>25</v>
+      </c>
+      <c r="B65" s="125">
+        <f t="shared" si="4"/>
+        <v>29.999999999999975</v>
+      </c>
+      <c r="C65" s="125">
+        <f t="shared" si="4"/>
+        <v>35.494187606283397</v>
+      </c>
+      <c r="D65" s="125">
+        <f t="shared" si="4"/>
+        <v>42.665944869096812</v>
+      </c>
+      <c r="E65" s="125">
+        <f t="shared" si="4"/>
+        <v>52.128405109039029</v>
+      </c>
+      <c r="F65" s="125">
+        <f t="shared" si="4"/>
+        <v>81.650651072666648</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="13.15">
+      <c r="A66" s="145">
+        <f t="shared" si="3"/>
+        <v>30</v>
+      </c>
+      <c r="B66" s="125">
+        <f t="shared" si="4"/>
+        <v>29.999999999999979</v>
+      </c>
+      <c r="C66" s="125">
+        <f t="shared" si="4"/>
+        <v>36.49660844955983</v>
+      </c>
+      <c r="D66" s="125">
+        <f t="shared" si="4"/>
+        <v>45.387792735773054</v>
+      </c>
+      <c r="E66" s="125">
+        <f t="shared" si="4"/>
+        <v>57.757894908120221</v>
+      </c>
+      <c r="F66" s="125">
+        <f t="shared" si="4"/>
+        <v>100.17735884743405</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="13.15">
+      <c r="B68" s="172" t="s">
+        <v>118</v>
+      </c>
+      <c r="C68" s="172" t="s">
+        <v>133</v>
+      </c>
+      <c r="D68" s="172" t="s">
+        <v>113</v>
+      </c>
+      <c r="E68" s="173" t="s">
+        <v>114</v>
+      </c>
+      <c r="F68" s="173" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="B69" s="128" t="str">
+        <f>Scenarios!B54</f>
+        <v>Snowball Scenario</v>
+      </c>
+      <c r="C69" s="143">
+        <f>Scenarios!C56</f>
+        <v>0.1</v>
+      </c>
+      <c r="D69" s="146">
+        <f>Scenarios!C55</f>
+        <v>15</v>
+      </c>
+      <c r="E69" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
+        <v>52.226230482849225</v>
+      </c>
+      <c r="F69" s="143">
+        <f>Scenarios!C58</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="B70" s="128" t="str">
+        <f>Scenarios!B36</f>
+        <v>Optimistic</v>
+      </c>
+      <c r="C70" s="143">
+        <f>Scenarios!C38</f>
+        <v>0.06</v>
+      </c>
+      <c r="D70" s="146">
+        <f>Scenarios!C37</f>
+        <v>10</v>
+      </c>
+      <c r="E70" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
+        <v>36.416009241711357</v>
+      </c>
+      <c r="F70" s="143">
+        <f>Scenarios!C40*(1-F$69-F$73)</f>
+        <v>0.18</v>
+      </c>
+      <c r="H70" s="121"/>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="B71" s="128" t="str">
+        <f>Scenarios!B24</f>
+        <v>Base</v>
+      </c>
+      <c r="C71" s="143">
+        <f>Scenarios!C26</f>
+        <v>0.04</v>
+      </c>
+      <c r="D71" s="146">
+        <f>Scenarios!C25</f>
+        <v>10</v>
+      </c>
+      <c r="E71" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
+        <v>34.067731182800323</v>
+      </c>
+      <c r="F71" s="143">
+        <f>Scenarios!C28*(1-F$69-F$73)</f>
+        <v>0.53999999999999992</v>
+      </c>
+      <c r="H71" s="121"/>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="B72" s="128" t="str">
+        <f>Scenarios!B30</f>
+        <v>Pessimistic</v>
+      </c>
+      <c r="C72" s="143">
+        <f>Scenarios!C32</f>
+        <v>0.02</v>
+      </c>
+      <c r="D72" s="146">
+        <f>Scenarios!C31</f>
+        <v>10</v>
+      </c>
+      <c r="E72" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
+        <v>31.936805419383283</v>
+      </c>
+      <c r="F72" s="143">
+        <f>Scenarios!C34*(1-F$69-F$73)</f>
+        <v>0.18</v>
+      </c>
+      <c r="H72" s="121"/>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="B73" s="128" t="str">
+        <f>Scenarios!B48</f>
+        <v>Devil's advocate</v>
+      </c>
+      <c r="C73" s="143">
+        <f>Scenarios!C50</f>
+        <v>0</v>
+      </c>
+      <c r="D73" s="146">
+        <f>Scenarios!C49</f>
+        <v>15</v>
+      </c>
+      <c r="E73" s="136">
+        <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
+        <v>29.999999999999986</v>
+      </c>
+      <c r="F73" s="143">
+        <f>Scenarios!C52</f>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="B74" s="156"/>
+      <c r="C74" s="156"/>
+      <c r="D74" s="156"/>
+      <c r="E74" s="156"/>
+      <c r="F74" s="157"/>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="B75" s="156" t="s">
+        <v>311</v>
+      </c>
+      <c r="C75" s="156" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="C76" s="156" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="C77" s="156" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="87" spans="3:3">
+      <c r="C87" s="116"/>
+    </row>
+    <row r="88" spans="3:3">
+      <c r="C88" s="116"/>
+    </row>
+    <row r="89" spans="3:3">
+      <c r="C89" s="116"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E6:F6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C16:F45">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E60 B61:F66">
+    <cfRule type="expression" dxfId="0" priority="2">
+      <formula>ISNUMBER(MATCH(B60, $E$70:$E$73, 0))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C12" xr:uid="{0679E683-700B-4E49-B936-C44C7B75B2A2}">
+      <formula1>$A$51:$A$56</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="59" fitToHeight="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
@@ -16863,19 +18370,19 @@
       <c r="D2" s="37"/>
       <c r="E2" s="37"/>
       <c r="F2" s="37"/>
-      <c r="H2" s="275" t="s">
-        <v>298</v>
-      </c>
-      <c r="I2" s="276"/>
+      <c r="H2" s="274" t="s">
+        <v>296</v>
+      </c>
+      <c r="I2" s="275"/>
     </row>
     <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="H3" s="274">
-        <v>0</v>
-      </c>
-      <c r="I3" s="262">
+      <c r="H3" s="273">
+        <v>0</v>
+      </c>
+      <c r="I3" s="261">
         <f>-Market_Price</f>
         <v>-56.86</v>
       </c>
@@ -16892,19 +18399,19 @@
         <v>151</v>
       </c>
       <c r="F4" s="156"/>
-      <c r="H4" s="274">
+      <c r="H4" s="273">
         <v>1</v>
       </c>
-      <c r="I4" s="262">
+      <c r="I4" s="261">
         <f t="shared" ref="I4:I13" si="0">IF(ROW()-3 &lt; $C$76, $C$77, IF(ROW()-3 = $C$76, $C$77 + $C$60, ""))</f>
         <v>2.4</v>
       </c>
     </row>
     <row r="5" spans="2:9">
-      <c r="H5" s="274">
+      <c r="H5" s="273">
         <v>2</v>
       </c>
-      <c r="I5" s="262">
+      <c r="I5" s="261">
         <f t="shared" si="0"/>
         <v>2.4</v>
       </c>
@@ -16918,13 +18425,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="100" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F6" s="100"/>
-      <c r="H6" s="274">
+      <c r="H6" s="273">
         <v>3</v>
       </c>
-      <c r="I6" s="262">
+      <c r="I6" s="261">
         <f t="shared" si="0"/>
         <v>68.992285778880003</v>
       </c>
@@ -16941,15 +18448,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="360" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 重庆啤酒(600132.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
-      <c r="H7" s="274">
+      <c r="F7" s="360"/>
+      <c r="H7" s="273">
         <v>4</v>
       </c>
-      <c r="I7" s="262" t="str">
+      <c r="I7" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16966,12 +18473,12 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
-      <c r="H8" s="274">
+      <c r="E8" s="360"/>
+      <c r="F8" s="360"/>
+      <c r="H8" s="273">
         <v>5</v>
       </c>
-      <c r="I8" s="262" t="str">
+      <c r="I8" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -16988,37 +18495,37 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
-      <c r="H9" s="274">
+      <c r="E9" s="360"/>
+      <c r="F9" s="360"/>
+      <c r="H9" s="273">
         <v>6</v>
       </c>
-      <c r="I9" s="262" t="str">
+      <c r="I9" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
-      <c r="H10" s="274">
+      <c r="E10" s="360"/>
+      <c r="F10" s="360"/>
+      <c r="H10" s="273">
         <v>7</v>
       </c>
-      <c r="I10" s="262" t="str">
+      <c r="I10" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
-        <v>278</v>
-      </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
-      <c r="H11" s="274">
+        <v>449</v>
+      </c>
+      <c r="E11" s="360"/>
+      <c r="F11" s="360"/>
+      <c r="H11" s="273">
         <v>8</v>
       </c>
-      <c r="I11" s="262" t="str">
+      <c r="I11" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17032,12 +18539,12 @@
         <v>3.7342435425912202E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
-      <c r="H12" s="274">
+      <c r="E12" s="360"/>
+      <c r="F12" s="360"/>
+      <c r="H12" s="273">
         <v>9</v>
       </c>
-      <c r="I12" s="262" t="str">
+      <c r="I12" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17050,12 +18557,12 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>2.3730241339145586E-2</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
-      <c r="H13" s="274">
+      <c r="E13" s="360"/>
+      <c r="F13" s="360"/>
+      <c r="H13" s="273">
         <v>10</v>
       </c>
-      <c r="I13" s="262" t="str">
+      <c r="I13" s="261" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
@@ -17068,8 +18575,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-7.4877931429291333E-3</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="360"/>
+      <c r="F14" s="360"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -17085,7 +18592,7 @@
         <v>152</v>
       </c>
       <c r="E17" s="160" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
     </row>
     <row r="18" spans="2:6">
@@ -17095,25 +18602,25 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="358" t="s">
-        <v>333</v>
-      </c>
-      <c r="F18" s="359"/>
+      <c r="E18" s="360" t="s">
+        <v>331</v>
+      </c>
+      <c r="F18" s="361"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="361"/>
+      <c r="F19" s="361"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
-        <v>306</v>
-      </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+        <v>304</v>
+      </c>
+      <c r="E20" s="361"/>
+      <c r="F20" s="361"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
@@ -17123,23 +18630,23 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="361"/>
+      <c r="F21" s="361"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C22" s="161">
-        <f>DCF!C12</f>
+        <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
         <v>57.380259942830683</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="361"/>
+      <c r="F22" s="361"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
@@ -17159,8 +18666,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="359"/>
+      <c r="F25" s="359"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
@@ -17170,23 +18677,23 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="359"/>
+      <c r="F26" s="359"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C27" s="161">
-        <f>DCF!E76</f>
+        <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
         <v>65.168450335018306</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="359"/>
+      <c r="F27" s="359"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -17196,8 +18703,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="359"/>
+      <c r="F28" s="359"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
@@ -17217,8 +18724,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="359"/>
+      <c r="F31" s="359"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
@@ -17228,23 +18735,23 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="359"/>
+      <c r="F32" s="359"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C33" s="161">
-        <f>DCF!E77</f>
+        <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
         <v>61.088521054715052</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="359"/>
+      <c r="F33" s="359"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -17254,8 +18761,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="359"/>
+      <c r="F34" s="359"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
@@ -17275,8 +18782,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
@@ -17286,23 +18793,23 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="359"/>
+      <c r="F38" s="359"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C39" s="161">
-        <f>DCF!E75</f>
+        <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
         <v>69.664528319209367</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="359"/>
+      <c r="F39" s="359"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -17313,8 +18820,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -17376,8 +18883,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="359"/>
+      <c r="F49" s="359"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
@@ -17387,23 +18894,23 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C51" s="161">
-        <f>DCF!E78</f>
+        <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
         <v>57.380259942830648</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="359"/>
+      <c r="F51" s="359"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -17413,12 +18920,12 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="359"/>
+      <c r="F52" s="359"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E54" s="160" t="s">
         <v>150</v>
@@ -17434,8 +18941,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="359"/>
+      <c r="F55" s="359"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
@@ -17445,23 +18952,23 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="359"/>
+      <c r="F56" s="359"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C57" s="161">
-        <f>DCF!E74</f>
+        <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
         <v>99.935214270443552</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="359"/>
+      <c r="F57" s="359"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -17471,8 +18978,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -17487,16 +18994,16 @@
         <v>CNY</v>
       </c>
       <c r="E60" s="100" t="s">
-        <v>299</v>
-      </c>
-      <c r="F60" s="307">
+        <v>297</v>
+      </c>
+      <c r="F60" s="306">
         <f>Thesis!F28</f>
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
@@ -17505,10 +19012,10 @@
     </row>
     <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
-        <v>307</v>
-      </c>
-      <c r="E63" s="279" t="s">
-        <v>314</v>
+        <v>305</v>
+      </c>
+      <c r="E63" s="278" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="64" spans="2:6">
@@ -17520,8 +19027,8 @@
         <v>10</v>
       </c>
       <c r="D64" s="151"/>
-      <c r="E64" s="278" t="s">
-        <v>398</v>
+      <c r="E64" s="277" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="65" spans="2:6">
@@ -17532,8 +19039,8 @@
         <v>4.6574870890079501E-2</v>
       </c>
       <c r="D65" s="152"/>
-      <c r="E65" s="278" t="s">
-        <v>315</v>
+      <c r="E65" s="277" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="66" spans="2:6">
@@ -17541,30 +19048,30 @@
         <v>103</v>
       </c>
       <c r="C66" s="161">
-        <f>DCF!C18</f>
+        <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
         <v>66.598280217741973</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E66" s="278" t="s">
-        <v>316</v>
+      <c r="E66" s="277" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
-        <v>353</v>
-      </c>
-      <c r="E68" s="279" t="s">
-        <v>317</v>
+        <v>351</v>
+      </c>
+      <c r="E68" s="278" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
-        <v>308</v>
-      </c>
-      <c r="C69" s="271" t="str">
+        <v>306</v>
+      </c>
+      <c r="C69" s="270" t="str">
         <f>IF(C60&lt;C22,"Y","N")</f>
         <v>N</v>
       </c>
@@ -17572,38 +19079,38 @@
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
-        <v>296</v>
-      </c>
-      <c r="C70" s="271" t="str">
+        <v>294</v>
+      </c>
+      <c r="C70" s="270" t="str">
         <f>IF(C69="Y","N",IF(C65&gt;8%,"N","Y"))</f>
         <v>Y</v>
       </c>
-      <c r="E70" s="278" t="s">
-        <v>297</v>
+      <c r="E70" s="277" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
-        <v>295</v>
-      </c>
-      <c r="C71" s="271" t="str">
+        <v>293</v>
+      </c>
+      <c r="C71" s="270" t="str">
         <f>IF(C65&gt;8%,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="E71" s="278"/>
+      <c r="E71" s="277"/>
     </row>
     <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
-        <v>287</v>
-      </c>
-      <c r="C72" s="270" t="str">
+        <v>285</v>
+      </c>
+      <c r="C72" s="269" t="str">
         <f>IF(F72&gt;50%,"Y","N")</f>
         <v>N</v>
       </c>
       <c r="E72" s="135" t="s">
-        <v>349</v>
-      </c>
-      <c r="F72" s="324">
+        <v>347</v>
+      </c>
+      <c r="F72" s="323">
         <f>BS!D89/C60</f>
         <v>-8.7950215386604794E-4</v>
       </c>
@@ -17623,10 +19130,10 @@
       </c>
     </row>
     <row r="76" spans="2:6">
-      <c r="B76" s="273" t="s">
-        <v>300</v>
-      </c>
-      <c r="C76" s="272">
+      <c r="B76" s="272" t="s">
+        <v>298</v>
+      </c>
+      <c r="C76" s="271">
         <f>F60</f>
         <v>3</v>
       </c>
@@ -17647,12 +19154,12 @@
     </row>
     <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
@@ -17696,7 +19203,7 @@
       <c r="E83" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F83" s="324">
+      <c r="F83" s="323">
         <f>(1-C83/C60)</f>
         <v>0.57830345555145946</v>
       </c>
@@ -17706,14 +19213,14 @@
     </row>
     <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
     </row>
     <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
-        <v>303</v>
-      </c>
-      <c r="C86" s="264">
+        <v>301</v>
+      </c>
+      <c r="C86" s="263">
         <f>Market_Price</f>
         <v>56.86</v>
       </c>
@@ -17724,9 +19231,9 @@
     </row>
     <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
-        <v>301</v>
-      </c>
-      <c r="C87" s="263">
+        <v>299</v>
+      </c>
+      <c r="C87" s="262">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
         <v>9.4210132770872423E-2</v>
       </c>
@@ -17736,12 +19243,12 @@
     </row>
     <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
@@ -17785,28 +19292,28 @@
       <c r="E93" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F93" s="324">
+      <c r="F93" s="323">
         <f>(1-C93/C60)</f>
         <v>0.37186026171892639</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="G95" s="2"/>
-      <c r="H95" s="311"/>
+      <c r="H95" s="310"/>
     </row>
     <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!F31</f>
         <v>0.08</v>
       </c>
       <c r="G96" s="2"/>
-      <c r="H96" s="311"/>
+      <c r="H96" s="310"/>
     </row>
     <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
@@ -17818,7 +19325,7 @@
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
-      <c r="H97" s="311"/>
+      <c r="H97" s="310"/>
     </row>
     <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
@@ -17830,23 +19337,23 @@
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
-      <c r="H98" s="311"/>
+      <c r="H98" s="310"/>
     </row>
     <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
         <v>59.048136223898794</v>
       </c>
       <c r="D99" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E99" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F99" s="324">
+      <c r="F99" s="323">
         <f>(1-C99/C60)</f>
         <v>0.1132886409700905</v>
       </c>
@@ -17856,12 +19363,12 @@
     </row>
     <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C102" s="135">
         <f>Thesis!F32</f>
@@ -17890,19 +19397,19 @@
     </row>
     <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
         <v>53.520960428876833</v>
       </c>
       <c r="D105" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="E105" s="147" t="s">
         <v>127</v>
       </c>
-      <c r="F105" s="324">
+      <c r="F105" s="323">
         <f>(1-C105/C66)</f>
         <v>0.19636122353473784</v>
       </c>
@@ -17911,33 +19418,33 @@
       <c r="B106" s="100"/>
     </row>
     <row r="107" spans="2:8" ht="14.65">
-      <c r="E107" s="315" t="s">
+      <c r="E107" s="314" t="s">
+        <v>325</v>
+      </c>
+      <c r="F107" s="311"/>
+    </row>
+    <row r="108" spans="2:8" ht="13.9">
+      <c r="E108" s="307" t="s">
+        <v>326</v>
+      </c>
+      <c r="F108" s="312" t="s">
         <v>327</v>
       </c>
-      <c r="F107" s="312"/>
-    </row>
-    <row r="108" spans="2:8" ht="13.9">
-      <c r="E108" s="308" t="s">
+    </row>
+    <row r="109" spans="2:8" ht="13.9">
+      <c r="E109" s="308" t="s">
+        <v>326</v>
+      </c>
+      <c r="F109" s="312" t="s">
         <v>328</v>
       </c>
-      <c r="F108" s="313" t="s">
+    </row>
+    <row r="110" spans="2:8" ht="13.9">
+      <c r="E110" s="309" t="s">
+        <v>326</v>
+      </c>
+      <c r="F110" s="313" t="s">
         <v>329</v>
-      </c>
-    </row>
-    <row r="109" spans="2:8" ht="13.9">
-      <c r="E109" s="309" t="s">
-        <v>328</v>
-      </c>
-      <c r="F109" s="313" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="110" spans="2:8" ht="13.9">
-      <c r="E110" s="310" t="s">
-        <v>328</v>
-      </c>
-      <c r="F110" s="314" t="s">
-        <v>331</v>
       </c>
     </row>
   </sheetData>

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77C42068-37A5-8946-801F-973F027DEE59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31BDE6B8-E1E5-5542-9142-64BFA99AB868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1160" yWindow="4420" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3874,6 +3874,9 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3909,9 +3912,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4220,7 +4220,7 @@
       <c r="C1" s="44">
         <v>45780</v>
       </c>
-      <c r="D1" s="358" t="s">
+      <c r="D1" s="346" t="s">
         <v>461</v>
       </c>
       <c r="E1" s="320" t="s">
@@ -4375,13 +4375,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="346" t="s">
+      <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="346"/>
-      <c r="D18" s="346"/>
-      <c r="E18" s="346"/>
-      <c r="F18" s="346"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>28.081736799883384</v>
+        <v>34.669224296258527</v>
       </c>
       <c r="D29" s="340" t="str">
         <f>D144</f>
@@ -4506,7 +4506,7 @@
         <v>426</v>
       </c>
       <c r="F29" s="332">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.15">
@@ -4515,7 +4515,7 @@
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>41.829260960684138</v>
+        <v>47.182112624483075</v>
       </c>
       <c r="D30" s="341" t="str">
         <f>D152</f>
@@ -4525,7 +4525,7 @@
         <v>439</v>
       </c>
       <c r="F30" s="342">
-        <v>0.21740000000000001</v>
+        <v>0.16739999999999999</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.15">
@@ -4581,22 +4581,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="346" t="s">
+      <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="346"/>
-      <c r="D36" s="346"/>
-      <c r="E36" s="346"/>
-      <c r="F36" s="346"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="348" t="s">
+      <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="348"/>
-      <c r="D37" s="348"/>
-      <c r="E37" s="348"/>
-      <c r="F37" s="348"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="232" t="s">
@@ -4608,13 +4608,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="347" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="347"/>
-      <c r="D40" s="347"/>
-      <c r="E40" s="347"/>
-      <c r="F40" s="347"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
@@ -4634,13 +4634,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="347" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="347"/>
-      <c r="D43" s="347"/>
-      <c r="E43" s="347"/>
-      <c r="F43" s="347"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
@@ -4669,13 +4669,13 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="347" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="347"/>
-      <c r="D47" s="347"/>
-      <c r="E47" s="347"/>
-      <c r="F47" s="347"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
@@ -4691,13 +4691,13 @@
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="347" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="347"/>
-      <c r="D50" s="347"/>
-      <c r="E50" s="347"/>
-      <c r="F50" s="347"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
@@ -4761,13 +4761,13 @@
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="347" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="347"/>
-      <c r="D58" s="347"/>
-      <c r="E58" s="347"/>
-      <c r="F58" s="347"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
@@ -4783,13 +4783,13 @@
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="347" t="s">
+      <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="350"/>
-      <c r="D61" s="350"/>
-      <c r="E61" s="350"/>
-      <c r="F61" s="350"/>
+      <c r="C61" s="351"/>
+      <c r="D61" s="351"/>
+      <c r="E61" s="351"/>
+      <c r="F61" s="351"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
@@ -4805,22 +4805,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="346" t="s">
+      <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="346"/>
-      <c r="D64" s="346"/>
-      <c r="E64" s="346"/>
-      <c r="F64" s="346"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="346" t="s">
+      <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="346"/>
-      <c r="D65" s="346"/>
-      <c r="E65" s="346"/>
-      <c r="F65" s="346"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
@@ -4889,22 +4889,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="17"/>
-      <c r="B74" s="346" t="s">
+      <c r="B74" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="346"/>
-      <c r="D74" s="346"/>
-      <c r="E74" s="346"/>
-      <c r="F74" s="346"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B75" s="348" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="348"/>
-      <c r="D75" s="348"/>
-      <c r="E75" s="348"/>
-      <c r="F75" s="348"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B77" s="232" t="s">
@@ -4948,22 +4948,22 @@
       <c r="C82" s="122"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B83" s="346" t="s">
+      <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="346"/>
-      <c r="D83" s="346"/>
-      <c r="E83" s="346"/>
-      <c r="F83" s="346"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B84" s="346" t="s">
+      <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="346"/>
-      <c r="D84" s="346"/>
-      <c r="E84" s="346"/>
-      <c r="F84" s="346"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="47" t="s">
@@ -5000,13 +5000,13 @@
       <c r="A90" s="231"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B91" s="346" t="s">
+      <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="346"/>
-      <c r="D91" s="346"/>
-      <c r="E91" s="346"/>
-      <c r="F91" s="346"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="1" t="s">
@@ -5019,13 +5019,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B95" s="346" t="s">
+      <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="346"/>
-      <c r="D95" s="346"/>
-      <c r="E95" s="346"/>
-      <c r="F95" s="346"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B96" s="47" t="s">
@@ -5156,13 +5156,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B111" s="346" t="s">
+      <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="346"/>
-      <c r="D111" s="346"/>
-      <c r="E111" s="346"/>
-      <c r="F111" s="346"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
@@ -5201,13 +5201,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B118" s="347" t="s">
+      <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="347"/>
-      <c r="D118" s="347"/>
-      <c r="E118" s="347"/>
-      <c r="F118" s="347"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B120" s="255" t="s">
@@ -5350,13 +5350,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B129" s="351" t="s">
+      <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="351"/>
-      <c r="D129" s="351"/>
-      <c r="E129" s="351"/>
-      <c r="F129" s="351"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A131" s="244" t="s">
@@ -5369,22 +5369,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B133" s="349" t="s">
+      <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="349"/>
-      <c r="D133" s="349"/>
-      <c r="E133" s="349"/>
-      <c r="F133" s="349"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="346" t="s">
+      <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="346"/>
-      <c r="D134" s="346"/>
-      <c r="E134" s="346"/>
-      <c r="F134" s="346"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B135" s="232" t="s">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="C137" s="246">
         <f>F29</f>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.15">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="C141" s="326">
         <f>F29</f>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.15">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="C142" s="238">
         <f>Scenarios!C81</f>
-        <v>3.8134110787171998</v>
+        <v>4.3586709148839331</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.15">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>24.268325721166185</v>
+        <v>30.310553381374593</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.15">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>28.081736799883384</v>
+        <v>34.669224296258527</v>
       </c>
       <c r="D144" s="330" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
@@ -5496,7 +5496,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.57830345555145946</v>
+        <v>0.4793807737524155</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.15">
@@ -5510,7 +5510,7 @@
       </c>
       <c r="C149" s="326">
         <f>Scenarios!C90</f>
-        <v>0.21740000000000001</v>
+        <v>0.16739999999999999</v>
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.15">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="C150" s="238">
         <f>Scenarios!C91</f>
-        <v>4.9209619772758479</v>
+        <v>5.3254251552044352</v>
       </c>
     </row>
     <row r="151" spans="2:4" x14ac:dyDescent="0.15">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>36.908298983408294</v>
+        <v>41.85668746927864</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.15">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>41.829260960684138</v>
+        <v>47.182112624483075</v>
       </c>
       <c r="D152" s="330" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5565,7 +5565,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.37186026171892639</v>
+        <v>0.29147780298229276</v>
       </c>
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.15">
@@ -5717,13 +5717,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B174" s="353" t="s">
+      <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="346"/>
-      <c r="D174" s="346"/>
-      <c r="E174" s="346"/>
-      <c r="F174" s="346"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B176" s="232" t="s">
@@ -5731,13 +5731,13 @@
       </c>
     </row>
     <row r="177" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B177" s="350" t="s">
+      <c r="B177" s="351" t="s">
         <v>381</v>
       </c>
-      <c r="C177" s="350"/>
-      <c r="D177" s="350"/>
-      <c r="E177" s="350"/>
-      <c r="F177" s="350"/>
+      <c r="C177" s="351"/>
+      <c r="D177" s="351"/>
+      <c r="E177" s="351"/>
+      <c r="F177" s="351"/>
     </row>
     <row r="178" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B178" s="236" t="s">
@@ -5760,13 +5760,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B183" s="347" t="s">
+      <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="347"/>
-      <c r="D183" s="347"/>
-      <c r="E183" s="347"/>
-      <c r="F183" s="347"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B185" s="1" t="s">
@@ -5774,22 +5774,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B186" s="352" t="s">
+      <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="352"/>
-      <c r="D186" s="352"/>
-      <c r="E186" s="352"/>
-      <c r="F186" s="352"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B187" s="352" t="s">
+      <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="352"/>
-      <c r="D187" s="352"/>
-      <c r="E187" s="352"/>
-      <c r="F187" s="352"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B189" s="1" t="s">
@@ -15465,10 +15465,10 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="354" t="s">
+      <c r="E6" s="355" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="354"/>
+      <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.15">
@@ -15483,8 +15483,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="354"/>
-      <c r="F7" s="354"/>
+      <c r="E7" s="355"/>
+      <c r="F7" s="355"/>
       <c r="H7" s="121"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.15">
@@ -15499,8 +15499,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="354"/>
-      <c r="F8" s="354"/>
+      <c r="E8" s="355"/>
+      <c r="F8" s="355"/>
       <c r="H8" s="121"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.15">
@@ -15515,8 +15515,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="354"/>
-      <c r="F9" s="354"/>
+      <c r="E9" s="355"/>
+      <c r="F9" s="355"/>
       <c r="H9" s="121"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.15">
@@ -16995,8 +16995,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="354"/>
-      <c r="F6" s="354"/>
+      <c r="E6" s="355"/>
+      <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.15">
@@ -18461,11 +18461,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356" t="str">
+      <c r="E7" s="357" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 重庆啤酒(600132.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="356"/>
+      <c r="F7" s="357"/>
       <c r="H7" s="269">
         <v>4</v>
       </c>
@@ -18486,8 +18486,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="357"/>
+      <c r="F8" s="357"/>
       <c r="H8" s="269">
         <v>5</v>
       </c>
@@ -18508,8 +18508,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="357"/>
+      <c r="F9" s="357"/>
       <c r="H9" s="269">
         <v>6</v>
       </c>
@@ -18519,8 +18519,8 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.15">
-      <c r="E10" s="356"/>
-      <c r="F10" s="356"/>
+      <c r="E10" s="357"/>
+      <c r="F10" s="357"/>
       <c r="H10" s="269">
         <v>7</v>
       </c>
@@ -18533,8 +18533,8 @@
       <c r="B11" s="160" t="s">
         <v>449</v>
       </c>
-      <c r="E11" s="356"/>
-      <c r="F11" s="356"/>
+      <c r="E11" s="357"/>
+      <c r="F11" s="357"/>
       <c r="H11" s="269">
         <v>8</v>
       </c>
@@ -18552,8 +18552,8 @@
         <v>3.7342435425912202E-2</v>
       </c>
       <c r="D12" s="159"/>
-      <c r="E12" s="356"/>
-      <c r="F12" s="356"/>
+      <c r="E12" s="357"/>
+      <c r="F12" s="357"/>
       <c r="H12" s="269">
         <v>9</v>
       </c>
@@ -18570,8 +18570,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>2.3730241339145586E-2</v>
       </c>
-      <c r="E13" s="356"/>
-      <c r="F13" s="356"/>
+      <c r="E13" s="357"/>
+      <c r="F13" s="357"/>
       <c r="H13" s="269">
         <v>10</v>
       </c>
@@ -18588,8 +18588,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-7.4877931429291333E-3</v>
       </c>
-      <c r="E14" s="356"/>
-      <c r="F14" s="356"/>
+      <c r="E14" s="357"/>
+      <c r="F14" s="357"/>
     </row>
     <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
@@ -18615,21 +18615,21 @@
       <c r="C18" s="151">
         <v>10</v>
       </c>
-      <c r="E18" s="356" t="s">
+      <c r="E18" s="357" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="357"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="E19" s="357"/>
-      <c r="F19" s="357"/>
+      <c r="E19" s="358"/>
+      <c r="F19" s="358"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="160" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="357"/>
-      <c r="F20" s="357"/>
+      <c r="E20" s="358"/>
+      <c r="F20" s="358"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
@@ -18643,8 +18643,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="357"/>
-      <c r="F21" s="357"/>
+      <c r="E21" s="358"/>
+      <c r="F21" s="358"/>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
@@ -18658,8 +18658,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="357"/>
-      <c r="F22" s="357"/>
+      <c r="E22" s="358"/>
+      <c r="F22" s="358"/>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="160" t="s">
@@ -18679,8 +18679,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="164"/>
-      <c r="E25" s="355"/>
-      <c r="F25" s="355"/>
+      <c r="E25" s="356"/>
+      <c r="F25" s="356"/>
     </row>
     <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="119" t="s">
@@ -18690,8 +18690,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="165"/>
-      <c r="E26" s="355"/>
-      <c r="F26" s="355"/>
+      <c r="E26" s="356"/>
+      <c r="F26" s="356"/>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
@@ -18705,8 +18705,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="355"/>
-      <c r="F27" s="355"/>
+      <c r="E27" s="356"/>
+      <c r="F27" s="356"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
@@ -18716,8 +18716,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="166"/>
-      <c r="E28" s="355"/>
-      <c r="F28" s="355"/>
+      <c r="E28" s="356"/>
+      <c r="F28" s="356"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="160" t="s">
@@ -18737,8 +18737,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="164"/>
-      <c r="E31" s="355"/>
-      <c r="F31" s="355"/>
+      <c r="E31" s="356"/>
+      <c r="F31" s="356"/>
     </row>
     <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="119" t="s">
@@ -18748,8 +18748,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="165"/>
-      <c r="E32" s="355"/>
-      <c r="F32" s="355"/>
+      <c r="E32" s="356"/>
+      <c r="F32" s="356"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
@@ -18763,8 +18763,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="355"/>
-      <c r="F33" s="355"/>
+      <c r="E33" s="356"/>
+      <c r="F33" s="356"/>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
@@ -18774,8 +18774,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="166"/>
-      <c r="E34" s="355"/>
-      <c r="F34" s="355"/>
+      <c r="E34" s="356"/>
+      <c r="F34" s="356"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="160" t="s">
@@ -18795,8 +18795,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="164"/>
-      <c r="E37" s="355"/>
-      <c r="F37" s="355"/>
+      <c r="E37" s="356"/>
+      <c r="F37" s="356"/>
     </row>
     <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="119" t="s">
@@ -18806,8 +18806,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="165"/>
-      <c r="E38" s="355"/>
-      <c r="F38" s="355"/>
+      <c r="E38" s="356"/>
+      <c r="F38" s="356"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
@@ -18821,8 +18821,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="355"/>
-      <c r="F39" s="355"/>
+      <c r="E39" s="356"/>
+      <c r="F39" s="356"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
@@ -18833,8 +18833,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="166"/>
-      <c r="E40" s="355"/>
-      <c r="F40" s="355"/>
+      <c r="E40" s="356"/>
+      <c r="F40" s="356"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
@@ -18896,8 +18896,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="164"/>
-      <c r="E49" s="355"/>
-      <c r="F49" s="355"/>
+      <c r="E49" s="356"/>
+      <c r="F49" s="356"/>
     </row>
     <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="119" t="s">
@@ -18907,8 +18907,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="165"/>
-      <c r="E50" s="355"/>
-      <c r="F50" s="355"/>
+      <c r="E50" s="356"/>
+      <c r="F50" s="356"/>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
@@ -18922,8 +18922,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="355"/>
-      <c r="F51" s="355"/>
+      <c r="E51" s="356"/>
+      <c r="F51" s="356"/>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
@@ -18933,8 +18933,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="166"/>
-      <c r="E52" s="355"/>
-      <c r="F52" s="355"/>
+      <c r="E52" s="356"/>
+      <c r="F52" s="356"/>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="160" t="s">
@@ -18954,8 +18954,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="164"/>
-      <c r="E55" s="355"/>
-      <c r="F55" s="355"/>
+      <c r="E55" s="356"/>
+      <c r="F55" s="356"/>
     </row>
     <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="119" t="s">
@@ -18965,8 +18965,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="165"/>
-      <c r="E56" s="355"/>
-      <c r="F56" s="355"/>
+      <c r="E56" s="356"/>
+      <c r="F56" s="356"/>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
@@ -18980,8 +18980,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="355"/>
-      <c r="F57" s="355"/>
+      <c r="E57" s="356"/>
+      <c r="F57" s="356"/>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
@@ -18991,8 +18991,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="166"/>
-      <c r="E58" s="355"/>
-      <c r="F58" s="355"/>
+      <c r="E58" s="356"/>
+      <c r="F58" s="356"/>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">
@@ -19176,7 +19176,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.15">
@@ -19185,7 +19185,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>3.8134110787171998</v>
+        <v>4.3586709148839331</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -19197,7 +19197,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>24.268325721166185</v>
+        <v>30.310553381374593</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -19207,7 +19207,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>28.081736799883384</v>
+        <v>34.669224296258527</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19218,7 +19218,7 @@
       </c>
       <c r="F83" s="319">
         <f>(1-C83/C60)</f>
-        <v>0.57830345555145946</v>
+        <v>0.4793807737524155</v>
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.15">
@@ -19265,7 +19265,7 @@
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.21740000000000001</v>
+        <v>0.16739999999999999</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.15">
@@ -19274,7 +19274,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>4.9209619772758479</v>
+        <v>5.3254251552044352</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -19286,7 +19286,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>36.908298983408294</v>
+        <v>41.85668746927864</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -19296,7 +19296,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>41.829260960684138</v>
+        <v>47.182112624483075</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19307,7 +19307,7 @@
       </c>
       <c r="F93" s="319">
         <f>(1-C93/C60)</f>
-        <v>0.37186026171892639</v>
+        <v>0.29147780298229276</v>
       </c>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.15">

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31BDE6B8-E1E5-5542-9142-64BFA99AB868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F7F9FF-EC91-48F0-8730-16254D9D314C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1160" yWindow="4420" windowWidth="17120" windowHeight="10760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2502,7 +2491,7 @@
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3915,7 +3904,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4204,7 +4193,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J192"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4213,7 +4202,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4230,7 +4219,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="244" t="s">
         <v>268</v>
       </c>
@@ -4244,7 +4233,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>417</v>
       </c>
@@ -4253,7 +4242,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>316</v>
       </c>
@@ -4261,7 +4250,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4270,7 +4259,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>308</v>
       </c>
@@ -4280,7 +4269,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>269</v>
       </c>
@@ -4290,17 +4279,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>420</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>419</v>
       </c>
@@ -4312,7 +4301,7 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>95</v>
       </c>
@@ -4322,7 +4311,7 @@
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>418</v>
       </c>
@@ -4332,7 +4321,7 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>422</v>
       </c>
@@ -4346,7 +4335,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>421</v>
       </c>
@@ -4360,7 +4349,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4370,11 +4359,11 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
       <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
@@ -4383,14 +4372,14 @@
       <c r="E18" s="347"/>
       <c r="F18" s="347"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>307</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>349</v>
       </c>
@@ -4405,7 +4394,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4418,7 +4407,7 @@
       </c>
       <c r="E22" s="343"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>436</v>
       </c>
@@ -4426,7 +4415,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>437</v>
       </c>
@@ -4434,7 +4423,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>348</v>
       </c>
@@ -4450,28 +4439,28 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
       </c>
       <c r="C26" s="334">
         <f>C127</f>
-        <v>66.592285778879997</v>
+        <v>87.635778317517335</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>9.4210132770872423E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.19201956038874379</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>435</v>
       </c>
@@ -4490,13 +4479,13 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>427</v>
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>34.669224296258527</v>
+        <v>51.075660805659325</v>
       </c>
       <c r="D29" s="340" t="str">
         <f>D144</f>
@@ -4506,16 +4495,16 @@
         <v>426</v>
       </c>
       <c r="F29" s="332">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.23700000000000002</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>47.182112624483075</v>
+        <v>65.221195836957349</v>
       </c>
       <c r="D30" s="341" t="str">
         <f>D152</f>
@@ -4525,16 +4514,16 @@
         <v>439</v>
       </c>
       <c r="F30" s="342">
-        <v>0.16739999999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.13700000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>429</v>
       </c>
       <c r="C31" s="341">
         <f>C160</f>
-        <v>59.048136223898794</v>
+        <v>79.995918037639569</v>
       </c>
       <c r="D31" s="341" t="str">
         <f>D160</f>
@@ -4544,16 +4533,16 @@
         <v>438</v>
       </c>
       <c r="F31" s="342">
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>430</v>
       </c>
       <c r="C32" s="341">
         <f>C168</f>
-        <v>53.520960428876833</v>
+        <v>74.340476830385043</v>
       </c>
       <c r="D32" s="341" t="str">
         <f>D168</f>
@@ -4563,14 +4552,14 @@
         <v>440</v>
       </c>
       <c r="F32" s="342">
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="244" t="s">
         <v>355</v>
       </c>
@@ -4580,7 +4569,7 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
       <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
@@ -4589,7 +4578,7 @@
       <c r="E36" s="347"/>
       <c r="F36" s="347"/>
     </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
       <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
@@ -4598,7 +4587,7 @@
       <c r="E37" s="349"/>
       <c r="F37" s="349"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:6">
       <c r="B39" s="232" t="s">
         <v>231</v>
       </c>
@@ -4607,7 +4596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
       <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
@@ -4616,7 +4605,7 @@
       <c r="E40" s="348"/>
       <c r="F40" s="348"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
@@ -4629,11 +4618,11 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
       <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
@@ -4642,7 +4631,7 @@
       <c r="E43" s="348"/>
       <c r="F43" s="348"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
@@ -4655,7 +4644,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
@@ -4668,7 +4657,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:6">
       <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
@@ -4677,7 +4666,7 @@
       <c r="E47" s="348"/>
       <c r="F47" s="348"/>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
@@ -4690,7 +4679,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
@@ -4699,7 +4688,7 @@
       <c r="E50" s="348"/>
       <c r="F50" s="348"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
@@ -4714,7 +4703,7 @@
       <c r="E51" s="311"/>
       <c r="F51" s="311"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
@@ -4729,7 +4718,7 @@
       <c r="E52" s="311"/>
       <c r="F52" s="311"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
@@ -4742,12 +4731,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
@@ -4760,7 +4749,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
@@ -4769,7 +4758,7 @@
       <c r="E58" s="348"/>
       <c r="F58" s="348"/>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
@@ -4782,7 +4771,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:6">
       <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
@@ -4791,7 +4780,7 @@
       <c r="E61" s="351"/>
       <c r="F61" s="351"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
@@ -4804,7 +4793,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
       <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
@@ -4813,7 +4802,7 @@
       <c r="E64" s="347"/>
       <c r="F64" s="347"/>
     </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
       <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
@@ -4822,7 +4811,7 @@
       <c r="E65" s="347"/>
       <c r="F65" s="347"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
@@ -4835,7 +4824,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
@@ -4848,7 +4837,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="249" t="s">
         <v>391</v>
       </c>
@@ -4858,7 +4847,7 @@
       </c>
       <c r="F69" s="344"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="249" t="s">
         <v>309</v>
       </c>
@@ -4874,7 +4863,7 @@
         <v>0.52229477939839231</v>
       </c>
     </row>
-    <row r="72" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" ht="13.9">
       <c r="A72" s="244" t="s">
         <v>356</v>
       </c>
@@ -4884,10 +4873,10 @@
       <c r="E72" s="36"/>
       <c r="F72" s="36"/>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="A73" s="231"/>
     </row>
-    <row r="74" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
       <c r="B74" s="347" t="s">
         <v>363</v>
@@ -4897,7 +4886,7 @@
       <c r="E74" s="347"/>
       <c r="F74" s="347"/>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
@@ -4906,21 +4895,21 @@
       <c r="E75" s="349"/>
       <c r="F75" s="349"/>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:6">
       <c r="B77" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:6">
       <c r="B78" s="1" t="s">
         <v>433</v>
       </c>
       <c r="C78" s="92">
         <f>F31</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="B79" s="1" t="s">
         <v>432</v>
       </c>
@@ -4929,25 +4918,25 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6">
       <c r="B80" s="80" t="s">
         <v>248</v>
       </c>
       <c r="C80" s="258">
         <f>F31+C79</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="C81" s="122"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:6">
       <c r="B82" s="321" t="s">
         <v>357</v>
       </c>
       <c r="C82" s="122"/>
     </row>
-    <row r="83" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:6" ht="24.5" customHeight="1">
       <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
@@ -4956,7 +4945,7 @@
       <c r="E83" s="347"/>
       <c r="F83" s="347"/>
     </row>
-    <row r="84" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6" ht="24.5" customHeight="1">
       <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
@@ -4965,7 +4954,7 @@
       <c r="E84" s="347"/>
       <c r="F84" s="347"/>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
         <v>252</v>
       </c>
@@ -4973,20 +4962,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="B87" s="47" t="s">
         <v>281</v>
       </c>
       <c r="C87" s="245">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>57.438828001604072</v>
+        <v>76.585104002138763</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" ht="13.9">
       <c r="A89" s="244" t="s">
         <v>358</v>
       </c>
@@ -4996,10 +4985,10 @@
       <c r="E89" s="36"/>
       <c r="F89" s="36"/>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:6">
       <c r="A90" s="231"/>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:6">
       <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
@@ -5008,17 +4997,17 @@
       <c r="E91" s="347"/>
       <c r="F91" s="347"/>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:6">
       <c r="B94" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:6" ht="24.5" customHeight="1">
       <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
@@ -5027,7 +5016,7 @@
       <c r="E95" s="347"/>
       <c r="F95" s="347"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
         <v>256</v>
       </c>
@@ -5040,7 +5029,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:6">
       <c r="B97" s="47" t="s">
         <v>282</v>
       </c>
@@ -5053,7 +5042,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:6">
       <c r="B98" s="325" t="s">
         <v>405</v>
       </c>
@@ -5062,7 +5051,7 @@
         <v>3.4701988818540461</v>
       </c>
     </row>
-    <row r="99" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:6">
       <c r="B99" s="325" t="s">
         <v>406</v>
       </c>
@@ -5071,7 +5060,7 @@
         <v>5.0341856510546588E-2</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="325" t="s">
         <v>408</v>
       </c>
@@ -5080,12 +5069,12 @@
         <v>3.9546057100127742E-2</v>
       </c>
     </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:6">
       <c r="B102" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>265</v>
       </c>
@@ -5098,7 +5087,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="47" t="s">
         <v>267</v>
       </c>
@@ -5111,7 +5100,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="47" t="s">
         <v>283</v>
       </c>
@@ -5124,12 +5113,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>258</v>
       </c>
@@ -5142,7 +5131,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>284</v>
       </c>
@@ -5155,7 +5144,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="111" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:6" ht="24.5" customHeight="1">
       <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
@@ -5164,20 +5153,20 @@
       <c r="E111" s="347"/>
       <c r="F111" s="347"/>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>451</v>
       </c>
       <c r="C113" s="245">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>57.380259942830683</v>
+        <v>76.526535943365388</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="325" t="s">
         <v>407</v>
       </c>
@@ -5190,7 +5179,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" ht="13.9">
       <c r="A116" s="244" t="s">
         <v>359</v>
       </c>
@@ -5200,7 +5189,7 @@
       <c r="E116" s="36"/>
       <c r="F116" s="36"/>
     </row>
-    <row r="118" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:6" ht="24.5" customHeight="1">
       <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
@@ -5209,7 +5198,7 @@
       <c r="E118" s="348"/>
       <c r="F118" s="348"/>
     </row>
-    <row r="120" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="255" t="s">
         <v>118</v>
       </c>
@@ -5226,7 +5215,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:6">
       <c r="B121" s="250" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5241,14 +5230,14 @@
       </c>
       <c r="E121" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>99.94 CNY</v>
+        <v>128.99 CNY</v>
       </c>
       <c r="F121" s="254">
         <f>DCF!F74</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:6">
       <c r="B122" s="240" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5263,14 +5252,14 @@
       </c>
       <c r="E122" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>69.66 CNY</v>
+        <v>91.22 CNY</v>
       </c>
       <c r="F122" s="243">
         <f>DCF!F75</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:6">
       <c r="B123" s="240" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5285,14 +5274,14 @@
       </c>
       <c r="E123" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>65.17 CNY</v>
+        <v>85.86 CNY</v>
       </c>
       <c r="F123" s="243">
         <f>DCF!F76</f>
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:6">
       <c r="B124" s="240" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5307,14 +5296,14 @@
       </c>
       <c r="E124" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>61.09 CNY</v>
+        <v>80.98 CNY</v>
       </c>
       <c r="F124" s="243">
         <f>DCF!F77</f>
         <v>0.18</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:6">
       <c r="B125" s="240" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5329,27 +5318,27 @@
       </c>
       <c r="E125" s="253" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>57.38 CNY</v>
+        <v>76.53 CNY</v>
       </c>
       <c r="F125" s="243">
         <f>DCF!F78</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="233" t="s">
         <v>259</v>
       </c>
       <c r="C127" s="239">
         <f>Scenarios!C60</f>
-        <v>66.592285778879997</v>
+        <v>87.635778317517335</v>
       </c>
       <c r="D127" s="234" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="129" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6" ht="24.5" customHeight="1">
       <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
@@ -5358,7 +5347,7 @@
       <c r="E129" s="352"/>
       <c r="F129" s="352"/>
     </row>
-    <row r="131" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="244" t="s">
         <v>403</v>
       </c>
@@ -5368,7 +5357,7 @@
       <c r="E131" s="36"/>
       <c r="F131" s="36"/>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:6">
       <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
@@ -5377,7 +5366,7 @@
       <c r="E133" s="350"/>
       <c r="F133" s="350"/>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
       <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
@@ -5386,12 +5375,12 @@
       <c r="E134" s="347"/>
       <c r="F134" s="347"/>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:6">
       <c r="B135" s="232" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:6">
       <c r="B136" s="1" t="s">
         <v>264</v>
       </c>
@@ -5400,16 +5389,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:6">
       <c r="B137" s="1" t="s">
         <v>277</v>
       </c>
       <c r="C137" s="246">
         <f>F29</f>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.23700000000000002</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="B138" s="234" t="s">
         <v>262</v>
       </c>
@@ -5422,7 +5411,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:6">
       <c r="B140" s="232" t="s">
         <v>410</v>
       </c>
@@ -5435,49 +5424,49 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>409</v>
       </c>
       <c r="C141" s="326">
         <f>F29</f>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+        <v>0.23700000000000002</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="B142" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C142" s="238">
         <f>Scenarios!C81</f>
-        <v>4.3586709148839331</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+        <v>4.7765820962496424</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="B143" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>30.310553381374593</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.15">
+        <v>46.299078709409685</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
       <c r="B144" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>34.669224296258527</v>
+        <v>51.075660805659325</v>
       </c>
       <c r="D144" s="330" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="281" t="s">
         <v>418</v>
       </c>
@@ -5490,63 +5479,63 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.4793807737524155</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.41718255048064179</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4">
       <c r="B148" s="232" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="1" t="s">
         <v>412</v>
       </c>
       <c r="C149" s="326">
         <f>Scenarios!C90</f>
-        <v>0.16739999999999999</v>
-      </c>
-    </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.13700000000000001</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4">
       <c r="B150" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C150" s="238">
         <f>Scenarios!C91</f>
-        <v>5.3254251552044352</v>
-      </c>
-    </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+        <v>5.6000862814257664</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4">
       <c r="B151" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>41.85668746927864</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4" x14ac:dyDescent="0.15">
+        <v>59.621109555531582</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4">
       <c r="B152" s="80" t="s">
         <v>261</v>
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>47.182112624483075</v>
+        <v>65.221195836957349</v>
       </c>
       <c r="D152" s="330" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4">
       <c r="B153" s="281" t="s">
         <v>418</v>
       </c>
@@ -5559,63 +5548,63 @@
         <v/>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.29147780298229276</v>
-      </c>
-    </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.25576976562413412</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4">
       <c r="B156" s="232" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="1" t="s">
         <v>411</v>
       </c>
       <c r="C157" s="92">
         <f>Scenarios!C96</f>
-        <v>0.08</v>
-      </c>
-    </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4">
       <c r="B158" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C158" s="238">
         <f>Scenarios!C97</f>
-        <v>6.1850327693949119</v>
-      </c>
-    </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+        <v>6.4152286787079351</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4">
       <c r="B159" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C159" s="238">
         <f>Scenarios!C98</f>
-        <v>52.863103454503879</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4" x14ac:dyDescent="0.15">
+        <v>73.580689358931636</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4">
       <c r="B160" s="80" t="s">
         <v>402</v>
       </c>
       <c r="C160" s="237">
         <f>Scenarios!C99</f>
-        <v>59.048136223898794</v>
+        <v>79.995918037639569</v>
       </c>
       <c r="D160" s="330" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:6">
       <c r="B161" s="281" t="s">
         <v>418</v>
       </c>
@@ -5628,63 +5617,63 @@
         <v/>
       </c>
     </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:6">
       <c r="B162" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>0.1132886409700905</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.15">
+        <v>8.7177411173293029E-2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
       <c r="B164" s="232" t="s">
         <v>434</v>
       </c>
     </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:6">
       <c r="B165" s="1" t="s">
         <v>425</v>
       </c>
       <c r="C165" s="92">
         <f>F32</f>
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.15">
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
       <c r="B166" s="234" t="str">
         <f>"PV("&amp;C136&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C166" s="238">
         <f>Scenarios!C103</f>
-        <v>5.7902475022527575</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.15">
+        <v>6.1077361402784396</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
       <c r="B167" s="234" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C136&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
       </c>
       <c r="C167" s="238">
         <f>Scenarios!C104</f>
-        <v>47.730712926624079</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.15">
+        <v>68.23274069010661</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
       <c r="B168" s="80" t="s">
         <v>402</v>
       </c>
       <c r="C168" s="237">
         <f>Scenarios!C105</f>
-        <v>53.520960428876833</v>
+        <v>74.340476830385043</v>
       </c>
       <c r="D168" s="330" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
         <v/>
       </c>
     </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:6">
       <c r="B169" s="281" t="s">
         <v>418</v>
       </c>
@@ -5697,16 +5686,16 @@
         <v/>
       </c>
     </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:6">
       <c r="B170" s="236" t="s">
         <v>263</v>
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.19636122353473784</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+        <v>0.15104150766667601</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" ht="13.9">
       <c r="A172" s="244" t="s">
         <v>375</v>
       </c>
@@ -5716,7 +5705,7 @@
       <c r="E172" s="36"/>
       <c r="F172" s="36"/>
     </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:6">
       <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
@@ -5725,12 +5714,12 @@
       <c r="E174" s="347"/>
       <c r="F174" s="347"/>
     </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:6">
       <c r="B176" s="232" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="177" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="177" spans="2:6">
       <c r="B177" s="351" t="s">
         <v>381</v>
       </c>
@@ -5739,27 +5728,27 @@
       <c r="E177" s="351"/>
       <c r="F177" s="351"/>
     </row>
-    <row r="178" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="178" spans="2:6">
       <c r="B178" s="236" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="179" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="179" spans="2:6">
       <c r="B179" s="236" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="180" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="180" spans="2:6">
       <c r="B180" s="236" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="182" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="2:6">
       <c r="B182" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="183" spans="2:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="2:6" ht="46.5" customHeight="1">
       <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
@@ -5768,12 +5757,12 @@
       <c r="E183" s="348"/>
       <c r="F183" s="348"/>
     </row>
-    <row r="185" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="186" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="2:6" ht="24.5" customHeight="1">
       <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
@@ -5782,7 +5771,7 @@
       <c r="E186" s="353"/>
       <c r="F186" s="353"/>
     </row>
-    <row r="187" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="2:6" ht="24.5" customHeight="1">
       <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
@@ -5791,22 +5780,22 @@
       <c r="E187" s="353"/>
       <c r="F187" s="353"/>
     </row>
-    <row r="189" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="190" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="190" spans="2:6">
       <c r="B190" s="236" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="191" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="191" spans="2:6">
       <c r="B191" s="236" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="192" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="192" spans="2:6">
       <c r="B192" s="236" t="s">
         <v>389</v>
       </c>
@@ -5867,15 +5856,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -5924,7 +5913,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>98</v>
       </c>
@@ -5940,7 +5929,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -5948,7 +5937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -5984,7 +5973,7 @@
       </c>
       <c r="M4" s="181"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6020,7 +6009,7 @@
       </c>
       <c r="M5" s="181"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6066,7 +6055,7 @@
       </c>
       <c r="M6" s="181"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6102,7 +6091,7 @@
       </c>
       <c r="M7" s="188"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6132,7 +6121,7 @@
       <c r="L8" s="181"/>
       <c r="M8" s="181"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
@@ -6148,7 +6137,7 @@
       <c r="L9" s="181"/>
       <c r="M9" s="181"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
@@ -6164,7 +6153,7 @@
       <c r="L10" s="181"/>
       <c r="M10" s="181"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
@@ -6180,7 +6169,7 @@
       <c r="L11" s="181"/>
       <c r="M11" s="181"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6210,7 +6199,7 @@
       <c r="L12" s="181"/>
       <c r="M12" s="181"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6240,7 +6229,7 @@
       <c r="L13" s="181"/>
       <c r="M13" s="181"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6276,7 +6265,7 @@
       </c>
       <c r="M14" s="181"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6312,7 +6301,7 @@
       </c>
       <c r="M15" s="182"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6330,13 +6319,13 @@
       <c r="L16" s="181"/>
       <c r="M16" s="181"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6366,7 +6355,7 @@
       <c r="L19" s="181"/>
       <c r="M19" s="181"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6382,7 +6371,7 @@
       <c r="L20" s="181"/>
       <c r="M20" s="181"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6398,7 +6387,7 @@
       <c r="L21" s="181"/>
       <c r="M21" s="181"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
@@ -6434,7 +6423,7 @@
       </c>
       <c r="M22" s="181"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
@@ -6470,7 +6459,7 @@
       </c>
       <c r="M23" s="181"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
@@ -6506,7 +6495,7 @@
       </c>
       <c r="M24" s="181"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6526,7 +6515,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6534,7 +6523,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6571,7 +6560,7 @@
       </c>
       <c r="M28" s="181"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6608,7 +6597,7 @@
       </c>
       <c r="M29" s="181"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6645,7 +6634,7 @@
       </c>
       <c r="M30" s="182"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6682,7 +6671,7 @@
       </c>
       <c r="M31" s="182"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
@@ -6719,7 +6708,7 @@
       </c>
       <c r="M32" s="182"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>82</v>
       </c>
@@ -6735,12 +6724,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6789,7 +6778,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6838,7 +6827,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6887,7 +6876,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -6936,7 +6925,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -6985,7 +6974,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7034,7 +7023,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7083,7 +7072,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
@@ -7132,7 +7121,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>169</v>
       </c>
@@ -7181,7 +7170,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7230,7 +7219,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7279,7 +7268,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7328,7 +7317,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7377,12 +7366,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7431,7 +7420,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7480,12 +7469,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="175" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>160</v>
       </c>
@@ -7534,7 +7523,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>168</v>
       </c>
@@ -7583,7 +7572,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>159</v>
       </c>
@@ -7632,7 +7621,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>161</v>
       </c>
@@ -7681,13 +7670,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7736,7 +7725,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7785,7 +7774,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7834,7 +7823,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
@@ -7883,7 +7872,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -7932,12 +7921,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -7987,7 +7976,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8036,7 +8025,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8086,7 +8075,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>169</v>
       </c>
@@ -8135,7 +8124,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8185,7 +8174,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>83</v>
       </c>
@@ -8201,13 +8190,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8256,7 +8245,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
@@ -8290,7 +8279,7 @@
       <c r="L77" s="324"/>
       <c r="M77" s="324"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
@@ -8324,7 +8313,7 @@
       <c r="L78" s="324"/>
       <c r="M78" s="324"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8373,7 +8362,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8454,7 +8443,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8465,7 +8454,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8481,7 +8470,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>157</v>
       </c>
@@ -8492,7 +8481,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>185</v>
       </c>
@@ -8512,7 +8501,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8534,7 +8523,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8555,7 +8544,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8576,7 +8565,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8597,7 +8586,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>174</v>
       </c>
@@ -8618,7 +8607,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8639,7 +8628,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8651,7 +8640,7 @@
       </c>
       <c r="H10" s="286"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8663,7 +8652,7 @@
       </c>
       <c r="H11" s="286"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8687,12 +8676,12 @@
         <v>986982442.09500003</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>184</v>
       </c>
@@ -8712,7 +8701,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>73</v>
       </c>
@@ -8732,7 +8721,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8752,7 +8741,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8772,7 +8761,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>174</v>
       </c>
@@ -8792,7 +8781,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8814,7 +8803,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8834,7 +8823,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8854,7 +8843,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8866,7 +8855,7 @@
       </c>
       <c r="H22" s="286"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8879,7 +8868,7 @@
       </c>
       <c r="H23" s="286"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>74</v>
       </c>
@@ -8903,7 +8892,7 @@
         <v>16068725.219999999</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>201</v>
       </c>
@@ -8920,7 +8909,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -8939,7 +8928,7 @@
         <v>-5174668970.3790016</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -8954,7 +8943,7 @@
       </c>
       <c r="H28" s="207"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -8973,7 +8962,7 @@
         <v>-6443106811.8090019</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -8989,7 +8978,7 @@
       </c>
       <c r="H30" s="207"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>204</v>
       </c>
@@ -9006,7 +8995,7 @@
       </c>
       <c r="H31" s="207"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9026,7 +9015,7 @@
         <v>3340012643.5709996</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9037,7 +9026,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="214"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="215" t="s">
@@ -9050,7 +9039,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>202</v>
       </c>
@@ -9069,7 +9058,7 @@
         <v>2336961476.2559996</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9085,7 +9074,7 @@
       </c>
       <c r="H36" s="214"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9101,7 +9090,7 @@
       </c>
       <c r="H37" s="214"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9117,7 +9106,7 @@
       </c>
       <c r="H38" s="214"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9136,7 +9125,7 @@
         <v>507484285.69499999</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>205</v>
       </c>
@@ -9156,7 +9145,7 @@
         <v>1003051167.3150001</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9176,7 +9165,7 @@
         <v>973493166.66300011</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9195,7 +9184,7 @@
         <v>29558000.651999995</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>97</v>
       </c>
@@ -9206,7 +9195,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>272</v>
       </c>
@@ -9220,7 +9209,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>274</v>
       </c>
@@ -9234,7 +9223,7 @@
       </c>
       <c r="F46" s="275"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9249,10 +9238,10 @@
       </c>
       <c r="F47" s="275"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="275"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="158" t="s">
         <v>144</v>
       </c>
@@ -9265,7 +9254,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="275"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>94</v>
       </c>
@@ -9279,7 +9268,7 @@
       </c>
       <c r="F50" s="275"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>177</v>
       </c>
@@ -9290,10 +9279,10 @@
       </c>
       <c r="F51" s="275"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="275"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="158" t="s">
         <v>143</v>
       </c>
@@ -9305,7 +9294,7 @@
       </c>
       <c r="F53" s="275"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>140</v>
       </c>
@@ -9319,7 +9308,7 @@
       </c>
       <c r="F54" s="275"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>142</v>
       </c>
@@ -9333,10 +9322,10 @@
       </c>
       <c r="F55" s="275"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="275"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="158" t="s">
         <v>176</v>
       </c>
@@ -9348,7 +9337,7 @@
       </c>
       <c r="F57" s="275"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>90</v>
       </c>
@@ -9359,7 +9348,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>93</v>
       </c>
@@ -9370,10 +9359,10 @@
       </c>
       <c r="F59" s="275"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="275"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="158" t="s">
         <v>275</v>
       </c>
@@ -9385,7 +9374,7 @@
       </c>
       <c r="F61" s="275"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>246</v>
       </c>
@@ -9401,7 +9390,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>194</v>
       </c>
@@ -9412,7 +9401,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>189</v>
       </c>
@@ -9426,7 +9415,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>188</v>
       </c>
@@ -9442,7 +9431,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>178</v>
       </c>
@@ -9452,7 +9441,7 @@
       </c>
       <c r="F67" s="275"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>182</v>
       </c>
@@ -9462,7 +9451,7 @@
       </c>
       <c r="F68" s="275"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>180</v>
       </c>
@@ -9472,7 +9461,7 @@
       </c>
       <c r="F69" s="275"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>189</v>
       </c>
@@ -9482,10 +9471,10 @@
       </c>
       <c r="F70" s="275"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="275"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="277" t="s">
         <v>319</v>
       </c>
@@ -9497,7 +9486,7 @@
       </c>
       <c r="F72" s="275"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
@@ -9513,7 +9502,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="279" t="s">
         <v>322</v>
       </c>
@@ -9529,7 +9518,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
@@ -9542,7 +9531,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="281" t="s">
         <v>323</v>
       </c>
@@ -9555,10 +9544,10 @@
         <v>324</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="275"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>190</v>
       </c>
@@ -9570,7 +9559,7 @@
       </c>
       <c r="F78" s="275"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>179</v>
       </c>
@@ -9584,7 +9573,7 @@
       </c>
       <c r="F79" s="275"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>183</v>
       </c>
@@ -9598,7 +9587,7 @@
       </c>
       <c r="F80" s="275"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>181</v>
       </c>
@@ -9612,7 +9601,7 @@
       </c>
       <c r="F81" s="275"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>190</v>
       </c>
@@ -9626,7 +9615,7 @@
       </c>
       <c r="F82" s="275"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>289</v>
       </c>
@@ -9637,7 +9626,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>290</v>
       </c>
@@ -9645,7 +9634,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="260" t="s">
         <v>287</v>
       </c>
@@ -9662,7 +9651,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="260" t="s">
         <v>288</v>
       </c>
@@ -9679,7 +9668,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="261" t="s">
         <v>190</v>
       </c>
@@ -9696,7 +9685,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>292</v>
       </c>
@@ -9727,19 +9716,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9796,7 +9785,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>100</v>
@@ -9819,7 +9808,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9833,7 +9822,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9890,7 +9879,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -9945,7 +9934,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10000,7 +9989,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10055,7 +10044,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>153</v>
@@ -10112,7 +10101,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10167,7 +10156,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>81</v>
@@ -10222,7 +10211,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>195</v>
@@ -10279,7 +10268,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10334,7 +10323,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>165</v>
@@ -10389,7 +10378,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10444,7 +10433,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>244</v>
@@ -10501,7 +10490,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>155</v>
@@ -10558,7 +10547,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10584,7 +10573,7 @@
       <c r="P17" s="194"/>
       <c r="Q17" s="194"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
@@ -10609,7 +10598,7 @@
       <c r="P18" s="195"/>
       <c r="Q18" s="195"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10666,7 +10655,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10685,7 +10674,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>206</v>
@@ -10708,7 +10697,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10729,7 +10718,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10786,7 +10775,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10843,7 +10832,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10900,18 +10889,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="293"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E27" s="293"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -10970,7 +10959,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11030,7 +11019,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11085,18 +11074,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="293"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="293"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>175</v>
@@ -11153,7 +11142,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11212,7 +11201,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11269,18 +11258,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="293"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E37" s="293"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11338,7 +11327,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11396,7 +11385,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11451,18 +11440,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="293"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>209</v>
       </c>
       <c r="E42" s="293"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>172</v>
@@ -11520,10 +11509,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>210</v>
@@ -11546,14 +11535,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="293"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11608,7 +11597,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>346</v>
@@ -11663,7 +11652,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="313" t="s">
         <v>343</v>
@@ -11720,7 +11709,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11775,11 +11764,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="293"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>156</v>
@@ -11789,7 +11778,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>89</v>
@@ -11816,7 +11805,7 @@
       <c r="P53" s="170"/>
       <c r="Q53" s="170"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>88</v>
@@ -11843,7 +11832,7 @@
       <c r="P54" s="170"/>
       <c r="Q54" s="170"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>91</v>
@@ -11898,11 +11887,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="293"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>169</v>
@@ -11912,7 +11901,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>168</v>
@@ -11967,7 +11956,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>160</v>
@@ -12022,7 +12011,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>159</v>
@@ -12077,7 +12066,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>195</v>
@@ -12132,7 +12121,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>161</v>
@@ -12188,7 +12177,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>196</v>
@@ -12243,11 +12232,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="293"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>170</v>
@@ -12257,7 +12246,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>168</v>
@@ -12282,7 +12271,7 @@
       <c r="P66" s="176"/>
       <c r="Q66" s="176"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>158</v>
@@ -12307,7 +12296,7 @@
       <c r="P67" s="176"/>
       <c r="Q67" s="176"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>159</v>
@@ -12332,7 +12321,7 @@
       <c r="P68" s="176"/>
       <c r="Q68" s="176"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>195</v>
@@ -12359,10 +12348,10 @@
       <c r="P69" s="176"/>
       <c r="Q69" s="176"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>213</v>
@@ -12385,7 +12374,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>217</v>
@@ -12406,7 +12395,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12463,7 +12452,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12520,7 +12509,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12577,7 +12566,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>153</v>
@@ -12634,7 +12623,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12691,7 +12680,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>81</v>
@@ -12750,7 +12739,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>154</v>
@@ -12807,7 +12796,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12864,7 +12853,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>165</v>
@@ -12921,7 +12910,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -12978,7 +12967,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13036,7 +13025,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>155</v>
@@ -13093,7 +13082,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13119,7 +13108,7 @@
       <c r="P85" s="248"/>
       <c r="Q85" s="248"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>99</v>
@@ -13143,7 +13132,7 @@
       <c r="P86" s="170"/>
       <c r="Q86" s="170"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>141</v>
@@ -13200,18 +13189,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="293"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>215</v>
       </c>
       <c r="E89" s="293"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13267,7 +13256,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13323,7 +13312,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>214</v>
@@ -13378,7 +13367,7 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>310</v>
@@ -13433,11 +13422,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="293"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="158" t="s">
         <v>85</v>
@@ -13458,7 +13447,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>145</v>
@@ -13515,7 +13504,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>165</v>
@@ -13572,10 +13561,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>216</v>
@@ -13598,7 +13587,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13608,7 +13597,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13665,7 +13654,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>211</v>
@@ -13722,7 +13711,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>212</v>
@@ -13779,7 +13768,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13836,7 +13825,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13893,11 +13882,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="293"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>221</v>
@@ -13920,7 +13909,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>218</v>
@@ -13977,7 +13966,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>219</v>
@@ -14034,7 +14023,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14061,18 +14050,18 @@
       <c r="P110" s="223"/>
       <c r="Q110" s="223"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="293"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="293"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>392</v>
@@ -14124,7 +14113,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>393</v>
@@ -14176,11 +14165,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="293"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14234,7 +14223,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>222</v>
@@ -14289,7 +14278,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>84</v>
       </c>
@@ -14343,7 +14332,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>92</v>
       </c>
@@ -14399,7 +14388,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>223</v>
@@ -14456,7 +14445,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14475,7 +14464,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>224</v>
@@ -14498,7 +14487,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="179" t="s">
         <v>171</v>
@@ -14519,7 +14508,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14577,7 +14566,7 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>270</v>
@@ -14634,7 +14623,7 @@
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>395</v>
       </c>
@@ -14684,688 +14673,688 @@
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15387,16 +15376,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H94"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15408,7 +15397,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>164</v>
       </c>
@@ -15421,7 +15410,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
@@ -15442,24 +15431,24 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="225" t="s">
         <v>124</v>
       </c>
       <c r="C5" s="226">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>229</v>
       </c>
       <c r="C6" s="230">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>27798738399.652267</v>
+        <v>37064984532.86969</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15471,7 +15460,7 @@
       <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="149" t="s">
         <v>225</v>
       </c>
@@ -15487,7 +15476,7 @@
       <c r="F7" s="355"/>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="149" t="s">
         <v>226</v>
       </c>
@@ -15503,7 +15492,7 @@
       <c r="F8" s="355"/>
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="225" t="s">
         <v>191</v>
       </c>
@@ -15519,13 +15508,13 @@
       <c r="F9" s="355"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="150" t="s">
         <v>228</v>
       </c>
       <c r="C10" s="230">
         <f>C6-C7+C8+C9</f>
-        <v>27770393146.083176</v>
+        <v>37036639279.300606</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15533,7 +15522,7 @@
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="228" t="s">
         <v>167</v>
       </c>
@@ -15547,13 +15536,13 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="150" t="s">
         <v>103</v>
       </c>
       <c r="C12" s="112">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>57.380259942830683</v>
+        <v>76.526535943365388</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15561,10 +15550,10 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>230</v>
       </c>
@@ -15574,13 +15563,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="153" t="s">
         <v>134</v>
       </c>
@@ -15590,7 +15579,7 @@
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="13.25" customHeight="1">
       <c r="B17" s="119" t="s">
         <v>135</v>
       </c>
@@ -15600,13 +15589,13 @@
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="13.25" customHeight="1">
       <c r="B18" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="141">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>66.598280217741973</v>
+        <v>87.56668023434645</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15614,10 +15603,10 @@
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:8" ht="13.15">
       <c r="B20" s="129" t="s">
         <v>108</v>
       </c>
@@ -15635,7 +15624,7 @@
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>1</v>
       </c>
@@ -15649,15 +15638,15 @@
       </c>
       <c r="E21" s="125">
         <f t="shared" ref="E21:E50" si="0">IF($C$17&lt;B21,0,1/(1+Equity_Cost)^B21)</f>
-        <v>0.92592592592592582</v>
+        <v>0.94339622641509424</v>
       </c>
       <c r="F21" s="126">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2155071189.0017157</v>
+        <v>2195732909.5489182</v>
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>2</v>
       </c>
@@ -15671,15 +15660,15 @@
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.88999644001423983</v>
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>2088373473.5077786</v>
+        <v>2167923477.6606202</v>
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>3</v>
       </c>
@@ -15693,15 +15682,15 @@
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.8396192830323016</v>
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>2023739998.5246947</v>
+        <v>2140466258.2379582</v>
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>4</v>
       </c>
@@ -15715,15 +15704,15 @@
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.79209366323802044</v>
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>1961106877.4732149</v>
+        <v>2113356790.4339273</v>
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>5</v>
       </c>
@@ -15737,15 +15726,15 @@
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.74725817286605689</v>
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>1900412201.0122008</v>
+        <v>2086590669.8991132</v>
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>6</v>
       </c>
@@ -15759,15 +15748,15 @@
       </c>
       <c r="E26" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0.70496054043967626</v>
       </c>
       <c r="F26" s="126">
         <f t="shared" si="1"/>
-        <v>1841595975.8446994</v>
+        <v>2060163548.0661402</v>
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>7</v>
       </c>
@@ -15781,15 +15770,15 @@
       </c>
       <c r="E27" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0.66505711362233599</v>
       </c>
       <c r="F27" s="126">
         <f t="shared" si="1"/>
-        <v>1784600065.4179232</v>
+        <v>2034071131.4431784</v>
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>8</v>
       </c>
@@ -15803,15 +15792,15 @@
       </c>
       <c r="E28" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0.62741237134182648</v>
       </c>
       <c r="F28" s="126">
         <f t="shared" si="1"/>
-        <v>1729368132.4585094</v>
+        <v>2008309180.9163985</v>
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>9</v>
       </c>
@@ -15825,15 +15814,15 @@
       </c>
       <c r="E29" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0.59189846353002495</v>
       </c>
       <c r="F29" s="126">
         <f t="shared" si="1"/>
-        <v>1675845583.2862802</v>
+        <v>1982873511.0612652</v>
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>10</v>
       </c>
@@ -15847,15 +15836,15 @@
       </c>
       <c r="E30" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0.55839477691511785</v>
       </c>
       <c r="F30" s="126">
         <f t="shared" si="1"/>
-        <v>1623979513.8514338</v>
+        <v>1957759989.4625492</v>
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>11</v>
       </c>
@@ -15877,7 +15866,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>12</v>
       </c>
@@ -15899,7 +15888,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>13</v>
       </c>
@@ -15921,7 +15910,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>14</v>
       </c>
@@ -15943,7 +15932,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>15</v>
       </c>
@@ -15965,7 +15954,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>16</v>
       </c>
@@ -15987,7 +15976,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>17</v>
       </c>
@@ -16009,7 +15998,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>18</v>
       </c>
@@ -16031,7 +16020,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>19</v>
       </c>
@@ -16053,7 +16042,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>20</v>
       </c>
@@ -16075,7 +16064,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>21</v>
       </c>
@@ -16097,7 +16086,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>22</v>
       </c>
@@ -16119,7 +16108,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>23</v>
       </c>
@@ -16141,7 +16130,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>24</v>
       </c>
@@ -16163,7 +16152,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>25</v>
       </c>
@@ -16185,7 +16174,7 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="123">
         <v>26</v>
       </c>
@@ -16207,7 +16196,7 @@
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="B47" s="123">
         <v>27</v>
       </c>
@@ -16229,7 +16218,7 @@
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="B48" s="123">
         <v>28</v>
       </c>
@@ -16251,7 +16240,7 @@
       </c>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8">
       <c r="B49" s="123">
         <v>29</v>
       </c>
@@ -16273,7 +16262,7 @@
       </c>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8">
       <c r="B50" s="123">
         <v>30</v>
       </c>
@@ -16295,13 +16284,13 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8">
       <c r="B51" s="127" t="s">
         <v>132</v>
       </c>
       <c r="C51" s="124">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>29093461051.523167</v>
+        <v>38791281402.030891</v>
       </c>
       <c r="D51" s="140">
         <f>Terminal_Growth</f>
@@ -16309,30 +16298,30 @@
       </c>
       <c r="E51" s="125">
         <f>1/(1+Equity_Cost)^C17</f>
-        <v>0.46319348808468425</v>
+        <v>0.55839477691511785</v>
       </c>
       <c r="F51" s="126">
         <f t="shared" si="1"/>
-        <v>13475901704.910921</v>
+        <v>21660848924.738598</v>
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8">
       <c r="C52" s="115"/>
       <c r="E52" s="128" t="s">
         <v>101</v>
       </c>
       <c r="F52" s="138">
         <f>SUM(F21:F51)</f>
-        <v>32259994715.289375</v>
+        <v>42408096391.468658</v>
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8">
       <c r="C53" s="115"/>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="B54" s="120" t="s">
         <v>130</v>
       </c>
@@ -16342,10 +16331,10 @@
       <c r="F54" s="118"/>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="134">
         <f>F52</f>
-        <v>32259994715.289375</v>
+        <v>42408096391.468658</v>
       </c>
       <c r="B55" s="132">
         <f>C78</f>
@@ -16369,141 +16358,141 @@
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>5</v>
       </c>
       <c r="B56" s="124">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>27798738399.65226</v>
+        <v>37064984532.869675</v>
       </c>
       <c r="C56" s="124">
-        <v>28695671219.365395</v>
+        <v>38173310175.981728</v>
       </c>
       <c r="D56" s="124">
-        <v>29619466785.62315</v>
+        <v>39310698802.635216</v>
       </c>
       <c r="E56" s="124">
-        <v>30571303922.523273</v>
+        <v>40478434736.362221</v>
       </c>
       <c r="F56" s="124">
-        <v>32564001283.448776</v>
+        <v>42910286195.588173</v>
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8" ht="13.15">
       <c r="A57" s="144">
         <v>10</v>
       </c>
       <c r="B57" s="124">
-        <v>27798738399.65226</v>
+        <v>37064984532.869675</v>
       </c>
       <c r="C57" s="124">
-        <v>29593429972.467758</v>
+        <v>39219279015.246628</v>
       </c>
       <c r="D57" s="124">
-        <v>31567998234.011402</v>
+        <v>41581770062.759674</v>
       </c>
       <c r="E57" s="124">
-        <v>33743970482.321777</v>
+        <v>44177698115.491516</v>
       </c>
       <c r="F57" s="124">
-        <v>38798508845.216896</v>
+        <v>50185338735.237732</v>
       </c>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="A58" s="144">
         <v>15</v>
       </c>
       <c r="B58" s="124">
-        <v>27798738399.652252</v>
+        <v>37064984532.869667</v>
       </c>
       <c r="C58" s="124">
-        <v>30704655354.608322</v>
+        <v>40637570756.500168</v>
       </c>
       <c r="D58" s="124">
-        <v>34108156080.274689</v>
+        <v>44825160379.998962</v>
       </c>
       <c r="E58" s="124">
-        <v>38108095740.426071</v>
+        <v>49752364483.188637</v>
       </c>
       <c r="F58" s="124">
-        <v>48394110626.422348</v>
+        <v>62453538589.876228</v>
       </c>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="A59" s="145">
         <v>20</v>
       </c>
       <c r="B59" s="124">
-        <v>27798738399.652252</v>
+        <v>37064984532.869675</v>
       </c>
       <c r="C59" s="124">
-        <v>31836815814.524704</v>
+        <v>42222685575.703217</v>
       </c>
       <c r="D59" s="124">
-        <v>36842194153.850533</v>
+        <v>48654647368.914856</v>
       </c>
       <c r="E59" s="124">
-        <v>43086376429.357841</v>
+        <v>56728441061.510498</v>
       </c>
       <c r="F59" s="124">
-        <v>60791517277.615776</v>
+        <v>79842964471.028748</v>
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="145">
         <v>25</v>
       </c>
       <c r="B60" s="124">
-        <v>27798738399.652248</v>
+        <v>37064984532.869667</v>
       </c>
       <c r="C60" s="124">
-        <v>32889787865.84174</v>
+        <v>43840553023.070267</v>
       </c>
       <c r="D60" s="124">
-        <v>39535314666.333603</v>
+        <v>52794384965.462723</v>
       </c>
       <c r="E60" s="124">
-        <v>48303463227.242409</v>
+        <v>64751732873.259644</v>
       </c>
       <c r="F60" s="124">
-        <v>75659502977.678207</v>
+        <v>102732154410.18817</v>
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="145">
         <v>30</v>
       </c>
       <c r="B61" s="124">
-        <v>27798738399.652245</v>
+        <v>37064984532.869667</v>
       </c>
       <c r="C61" s="124">
-        <v>33818655692.128422</v>
+        <v>45407068563.261345</v>
       </c>
       <c r="D61" s="124">
-        <v>42057445893.31308</v>
+        <v>57049847355.856087</v>
       </c>
       <c r="E61" s="124">
-        <v>53519887035.514709</v>
+        <v>73557564826.937149</v>
       </c>
       <c r="F61" s="124">
-        <v>92826806405.596954</v>
+        <v>131744350750.47754</v>
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8">
       <c r="C62" s="115"/>
       <c r="D62" s="115"/>
       <c r="E62" s="115"/>
       <c r="F62" s="115"/>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="B63" s="120" t="s">
         <v>131</v>
       </c>
@@ -16513,7 +16502,7 @@
       <c r="F63" s="115"/>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="B64" s="133">
         <f>B55</f>
         <v>0</v>
@@ -16536,193 +16525,193 @@
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <v>0</v>
       </c>
       <c r="B65" s="125">
         <f>C12</f>
-        <v>57.380259942830683</v>
+        <v>76.526535943365388</v>
       </c>
       <c r="C65" s="125">
         <f>C12</f>
-        <v>57.380259942830683</v>
+        <v>76.526535943365388</v>
       </c>
       <c r="D65" s="125">
         <f>C12</f>
-        <v>57.380259942830683</v>
+        <v>76.526535943365388</v>
       </c>
       <c r="E65" s="142">
         <f>C12</f>
-        <v>57.380259942830683</v>
+        <v>76.526535943365388</v>
       </c>
       <c r="F65" s="125">
         <f>C12</f>
-        <v>57.380259942830683</v>
+        <v>76.526535943365388</v>
       </c>
       <c r="H65" s="121"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
       </c>
       <c r="B66" s="125">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>57.380259942830662</v>
+        <v>76.52653594336536</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>59.233537211022842</v>
+        <v>78.816601235870735</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>61.142319324659603</v>
+        <v>81.166717588566357</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>63.109042015665942</v>
+        <v>83.579538720387106</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>67.226430341996689</v>
+        <v>88.604324222655677</v>
       </c>
       <c r="H66" s="121"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B67" s="125">
         <f t="shared" si="4"/>
-        <v>57.380259942830662</v>
+        <v>76.52653594336536</v>
       </c>
       <c r="C67" s="125">
         <f t="shared" si="4"/>
-        <v>61.088521054715052</v>
+        <v>80.977822489505968</v>
       </c>
       <c r="D67" s="125">
         <f t="shared" si="4"/>
-        <v>65.168450335018306</v>
+        <v>85.859292827567373</v>
       </c>
       <c r="E67" s="125">
         <f t="shared" si="4"/>
-        <v>69.664528319209367</v>
+        <v>91.223099730662966</v>
       </c>
       <c r="F67" s="125">
         <f t="shared" si="4"/>
-        <v>80.108410896897652</v>
+        <v>103.63631903911077</v>
       </c>
       <c r="H67" s="121"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B68" s="125">
         <f t="shared" si="4"/>
-        <v>57.380259942830648</v>
+        <v>76.526535943365332</v>
       </c>
       <c r="C68" s="125">
         <f t="shared" si="4"/>
-        <v>63.384577900107253</v>
+        <v>83.908351717514989</v>
       </c>
       <c r="D68" s="125">
         <f t="shared" si="4"/>
-        <v>70.417022681390222</v>
+        <v>92.560911292968882</v>
       </c>
       <c r="E68" s="125">
         <f t="shared" si="4"/>
-        <v>78.681852647886259</v>
+        <v>102.74169090041501</v>
       </c>
       <c r="F68" s="125">
         <f t="shared" si="4"/>
-        <v>99.935214270443552</v>
+        <v>128.98534787664605</v>
       </c>
       <c r="H68" s="121"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B69" s="125">
         <f t="shared" si="4"/>
-        <v>57.380259942830648</v>
+        <v>76.52653594336536</v>
       </c>
       <c r="C69" s="125">
         <f t="shared" si="4"/>
-        <v>65.723891612565779</v>
+        <v>87.183577238689594</v>
       </c>
       <c r="D69" s="125">
         <f t="shared" si="4"/>
-        <v>76.066197848991521</v>
+        <v>100.47354536032901</v>
       </c>
       <c r="E69" s="125">
         <f t="shared" si="4"/>
-        <v>88.968168671452133</v>
+        <v>117.15593002693812</v>
       </c>
       <c r="F69" s="125">
         <f t="shared" si="4"/>
-        <v>125.55121518625307</v>
+        <v>164.91605192063443</v>
       </c>
       <c r="H69" s="121"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B70" s="125">
         <f t="shared" si="4"/>
-        <v>57.380259942830641</v>
+        <v>76.526535943365332</v>
       </c>
       <c r="C70" s="125">
         <f t="shared" si="4"/>
-        <v>67.899583173692591</v>
+        <v>90.526477506418018</v>
       </c>
       <c r="D70" s="125">
         <f t="shared" si="4"/>
-        <v>81.630827569959067</v>
+        <v>109.02723122770136</v>
       </c>
       <c r="E70" s="125">
         <f t="shared" si="4"/>
-        <v>99.747915109760982</v>
+        <v>133.73396575490131</v>
       </c>
       <c r="F70" s="125">
         <f t="shared" si="4"/>
-        <v>156.27202204728948</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+        <v>212.21058108631306</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B71" s="125">
         <f t="shared" si="4"/>
-        <v>57.380259942830634</v>
+        <v>76.526535943365332</v>
       </c>
       <c r="C71" s="125">
         <f t="shared" si="4"/>
-        <v>69.818845787098539</v>
+        <v>93.763272478235905</v>
       </c>
       <c r="D71" s="125">
         <f t="shared" si="4"/>
-        <v>86.84215261864405</v>
+        <v>117.8200321381253</v>
       </c>
       <c r="E71" s="125">
         <f t="shared" si="4"/>
-        <v>110.52629165330129</v>
+        <v>151.92891617771031</v>
       </c>
       <c r="F71" s="125">
         <f t="shared" si="4"/>
-        <v>191.7437680909843</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+        <v>272.15670279806284</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="172" t="s">
         <v>118</v>
       </c>
@@ -16739,7 +16728,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16754,14 +16743,14 @@
       </c>
       <c r="E74" s="136">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>99.935214270443552</v>
+        <v>128.98534787664605</v>
       </c>
       <c r="F74" s="143">
         <f>Scenarios!C58</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -16776,7 +16765,7 @@
       </c>
       <c r="E75" s="136">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>69.664528319209367</v>
+        <v>91.223099730662966</v>
       </c>
       <c r="F75" s="143">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16784,7 +16773,7 @@
       </c>
       <c r="H75" s="121"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="B76" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -16799,7 +16788,7 @@
       </c>
       <c r="E76" s="136">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>65.168450335018306</v>
+        <v>85.859292827567373</v>
       </c>
       <c r="F76" s="143">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16807,7 +16796,7 @@
       </c>
       <c r="H76" s="121"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="B77" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -16822,7 +16811,7 @@
       </c>
       <c r="E77" s="136">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>61.088521054715052</v>
+        <v>80.977822489505968</v>
       </c>
       <c r="F77" s="143">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16830,7 +16819,7 @@
       </c>
       <c r="H77" s="121"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8">
       <c r="B78" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -16845,21 +16834,21 @@
       </c>
       <c r="E78" s="136">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>57.380259942830648</v>
+        <v>76.526535943365332</v>
       </c>
       <c r="F78" s="143">
         <f>Scenarios!C52</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8">
       <c r="B79" s="156"/>
       <c r="C79" s="156"/>
       <c r="D79" s="156"/>
       <c r="E79" s="156"/>
       <c r="F79" s="157"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8">
       <c r="B80" s="156" t="s">
         <v>311</v>
       </c>
@@ -16867,23 +16856,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:3">
       <c r="C81" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:3">
       <c r="C82" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:3">
       <c r="C92" s="116"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:3">
       <c r="C93" s="116"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:3">
       <c r="C94" s="116"/>
     </row>
   </sheetData>
@@ -16917,16 +16906,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>445</v>
       </c>
@@ -16938,7 +16927,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>444</v>
       </c>
@@ -16951,7 +16940,7 @@
       </c>
       <c r="H3" s="121"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>442</v>
       </c>
@@ -16972,24 +16961,24 @@
       </c>
       <c r="H4" s="121"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="225" t="s">
         <v>124</v>
       </c>
       <c r="C5" s="226">
         <f>Equity_Cost</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="E5" s="149"/>
       <c r="H5" s="121"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="150" t="s">
         <v>443</v>
       </c>
       <c r="C6" s="230">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>14519135940</v>
+        <v>19358847920</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -16999,13 +16988,13 @@
       <c r="F6" s="355"/>
       <c r="H6" s="121"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="150" t="s">
         <v>446</v>
       </c>
       <c r="C7" s="112">
         <f>(C6*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D7" t="str">
         <f>Market_currency</f>
@@ -17013,10 +17002,10 @@
       </c>
       <c r="H7" s="121"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="H8" s="121"/>
     </row>
-    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
         <v>230</v>
       </c>
@@ -17026,13 +17015,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="121"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="120" t="s">
         <v>136</v>
       </c>
       <c r="H10" s="121"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1">
       <c r="B11" s="153" t="s">
         <v>134</v>
       </c>
@@ -17042,7 +17031,7 @@
       </c>
       <c r="H11" s="121"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1">
       <c r="B12" s="119" t="s">
         <v>135</v>
       </c>
@@ -17052,13 +17041,13 @@
       </c>
       <c r="H12" s="121"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1">
       <c r="B13" s="154" t="s">
         <v>107</v>
       </c>
       <c r="C13" s="141">
         <f>F47/Common_Shares*scaling_factor</f>
-        <v>34.814523865974699</v>
+        <v>45.766209726984385</v>
       </c>
       <c r="D13" t="str">
         <f>Market_currency</f>
@@ -17066,10 +17055,10 @@
       </c>
       <c r="H13" s="121"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8">
       <c r="H14" s="121"/>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="129" t="s">
         <v>108</v>
       </c>
@@ -17087,7 +17076,7 @@
       </c>
       <c r="H15" s="121"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8">
       <c r="B16" s="123">
         <v>1</v>
       </c>
@@ -17101,15 +17090,15 @@
       </c>
       <c r="E16" s="125">
         <f t="shared" ref="E16:E45" si="0">IF($C$12&lt;B16,0,1/(1+Equity_Cost)^B16)</f>
-        <v>0.92592592592592582</v>
+        <v>0.94339622641509424</v>
       </c>
       <c r="F16" s="126">
         <f t="shared" ref="F16:F46" si="1">C16*E16</f>
-        <v>1125582431.2474823</v>
+        <v>1146819835.6106424</v>
       </c>
       <c r="H16" s="121"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17" s="123">
         <v>2</v>
       </c>
@@ -17123,15 +17112,15 @@
       </c>
       <c r="E17" s="125">
         <f t="shared" si="0"/>
-        <v>0.85733882030178321</v>
+        <v>0.88999644001423983</v>
       </c>
       <c r="F17" s="126">
         <f t="shared" si="1"/>
-        <v>1090746562.6471996</v>
+        <v>1132295114.5173492</v>
       </c>
       <c r="H17" s="121"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8">
       <c r="B18" s="123">
         <v>3</v>
       </c>
@@ -17145,15 +17134,15 @@
       </c>
       <c r="E18" s="125">
         <f t="shared" si="0"/>
-        <v>0.79383224102016958</v>
+        <v>0.8396192830323016</v>
       </c>
       <c r="F18" s="126">
         <f t="shared" si="1"/>
-        <v>1056988836.0891583</v>
+        <v>1117954352.1560967</v>
       </c>
       <c r="H18" s="121"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="B19" s="123">
         <v>4</v>
       </c>
@@ -17167,15 +17156,15 @@
       </c>
       <c r="E19" s="125">
         <f t="shared" si="0"/>
-        <v>0.73502985279645328</v>
+        <v>0.79209366323802044</v>
       </c>
       <c r="F19" s="126">
         <f t="shared" si="1"/>
-        <v>1024275883.946543</v>
+        <v>1103795218.6497827</v>
       </c>
       <c r="H19" s="121"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8">
       <c r="B20" s="123">
         <v>5</v>
       </c>
@@ -17189,15 +17178,15 @@
       </c>
       <c r="E20" s="125">
         <f t="shared" si="0"/>
-        <v>0.68058319703375303</v>
+        <v>0.74725817286605689</v>
       </c>
       <c r="F20" s="126">
         <f t="shared" si="1"/>
-        <v>992575371.29368079</v>
+        <v>1089815413.6297011</v>
       </c>
       <c r="H20" s="121"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="123">
         <v>6</v>
       </c>
@@ -17211,15 +17200,15 @@
       </c>
       <c r="E21" s="125">
         <f t="shared" si="0"/>
-        <v>0.63016962688310452</v>
+        <v>0.70496054043967626</v>
       </c>
       <c r="F21" s="126">
         <f t="shared" si="1"/>
-        <v>961855963.94477451</v>
+        <v>1076012665.861814</v>
       </c>
       <c r="H21" s="121"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="123">
         <v>7</v>
       </c>
@@ -17233,15 +17222,15 @@
       </c>
       <c r="E22" s="125">
         <f t="shared" si="0"/>
-        <v>0.58349039526213387</v>
+        <v>0.66505711362233599</v>
       </c>
       <c r="F22" s="126">
         <f t="shared" si="1"/>
-        <v>932087297.48181081</v>
+        <v>1062384732.8777531</v>
       </c>
       <c r="H22" s="121"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="123">
         <v>8</v>
       </c>
@@ -17255,15 +17244,15 @@
       </c>
       <c r="E23" s="125">
         <f t="shared" si="0"/>
-        <v>0.54026888450197574</v>
+        <v>0.62741237134182648</v>
       </c>
       <c r="F23" s="126">
         <f t="shared" si="1"/>
-        <v>903239947.241027</v>
+        <v>1048929400.6104964</v>
       </c>
       <c r="H23" s="121"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="123">
         <v>9</v>
       </c>
@@ -17277,15 +17266,15 @@
       </c>
       <c r="E24" s="125">
         <f t="shared" si="0"/>
-        <v>0.50024896713145905</v>
+        <v>0.59189846353002495</v>
       </c>
       <c r="F24" s="126">
         <f t="shared" si="1"/>
-        <v>875285399.22827792</v>
+        <v>1035644483.0346593</v>
       </c>
       <c r="H24" s="121"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="123">
         <v>10</v>
       </c>
@@ -17299,15 +17288,15 @@
       </c>
       <c r="E25" s="125">
         <f t="shared" si="0"/>
-        <v>0.46319348808468425</v>
+        <v>0.55839477691511785</v>
       </c>
       <c r="F25" s="126">
         <f t="shared" si="1"/>
-        <v>848196021.93454313</v>
+        <v>1022527821.8113412</v>
       </c>
       <c r="H25" s="121"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="123">
         <v>11</v>
       </c>
@@ -17329,7 +17318,7 @@
       </c>
       <c r="H26" s="121"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="123">
         <v>12</v>
       </c>
@@ -17351,7 +17340,7 @@
       </c>
       <c r="H27" s="121"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="123">
         <v>13</v>
       </c>
@@ -17373,7 +17362,7 @@
       </c>
       <c r="H28" s="121"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="123">
         <v>14</v>
       </c>
@@ -17395,7 +17384,7 @@
       </c>
       <c r="H29" s="121"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="123">
         <v>15</v>
       </c>
@@ -17417,7 +17406,7 @@
       </c>
       <c r="H30" s="121"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="123">
         <v>16</v>
       </c>
@@ -17439,7 +17428,7 @@
       </c>
       <c r="H31" s="121"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="123">
         <v>17</v>
       </c>
@@ -17461,7 +17450,7 @@
       </c>
       <c r="H32" s="121"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="123">
         <v>18</v>
       </c>
@@ -17483,7 +17472,7 @@
       </c>
       <c r="H33" s="121"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="123">
         <v>19</v>
       </c>
@@ -17505,7 +17494,7 @@
       </c>
       <c r="H34" s="121"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="123">
         <v>20</v>
       </c>
@@ -17527,7 +17516,7 @@
       </c>
       <c r="H35" s="121"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="123">
         <v>21</v>
       </c>
@@ -17549,7 +17538,7 @@
       </c>
       <c r="H36" s="121"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="123">
         <v>22</v>
       </c>
@@ -17571,7 +17560,7 @@
       </c>
       <c r="H37" s="121"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="123">
         <v>23</v>
       </c>
@@ -17593,7 +17582,7 @@
       </c>
       <c r="H38" s="121"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="123">
         <v>24</v>
       </c>
@@ -17615,7 +17604,7 @@
       </c>
       <c r="H39" s="121"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="123">
         <v>25</v>
       </c>
@@ -17637,7 +17626,7 @@
       </c>
       <c r="H40" s="121"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="123">
         <v>26</v>
       </c>
@@ -17659,7 +17648,7 @@
       </c>
       <c r="H41" s="121"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="123">
         <v>27</v>
       </c>
@@ -17681,7 +17670,7 @@
       </c>
       <c r="H42" s="121"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="123">
         <v>28</v>
       </c>
@@ -17703,7 +17692,7 @@
       </c>
       <c r="H43" s="121"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="123">
         <v>29</v>
       </c>
@@ -17725,7 +17714,7 @@
       </c>
       <c r="H44" s="121"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="123">
         <v>30</v>
       </c>
@@ -17747,13 +17736,13 @@
       </c>
       <c r="H45" s="121"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="127" t="s">
         <v>132</v>
       </c>
       <c r="C46" s="124">
         <f>C$16*(1+F4)^$C$12/Equity_Cost</f>
-        <v>15195362821.841013</v>
+        <v>20260483762.454685</v>
       </c>
       <c r="D46" s="140">
         <f>Terminal_Growth</f>
@@ -17761,30 +17750,30 @@
       </c>
       <c r="E46" s="125">
         <f>1/(1+Equity_Cost)^C12</f>
-        <v>0.46319348808468425</v>
+        <v>0.55839477691511785</v>
       </c>
       <c r="F46" s="126">
         <f t="shared" si="1"/>
-        <v>7038393108.1608696</v>
+        <v>11313348310.728252</v>
       </c>
       <c r="H46" s="121"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="C47" s="115"/>
       <c r="E47" s="128" t="s">
         <v>101</v>
       </c>
       <c r="F47" s="138">
         <f>SUM(F16:F46)</f>
-        <v>16849226823.215366</v>
+        <v>22149527349.487885</v>
       </c>
       <c r="H47" s="121"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="C48" s="115"/>
       <c r="H48" s="121"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="120" t="s">
         <v>130</v>
       </c>
@@ -17794,10 +17783,10 @@
       <c r="F49" s="118"/>
       <c r="H49" s="121"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="134">
         <f>F47</f>
-        <v>16849226823.215366</v>
+        <v>22149527349.487885</v>
       </c>
       <c r="B50" s="132">
         <f>C73</f>
@@ -17821,141 +17810,141 @@
       </c>
       <c r="H50" s="121"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="13.15">
       <c r="A51" s="144">
         <v>5</v>
       </c>
       <c r="B51" s="124">
         <f t="dataTable" ref="B51:F56" dt2D="1" dtr="1" r1="C11" r2="C12"/>
-        <v>14519135939.999998</v>
+        <v>19358847919.999992</v>
       </c>
       <c r="C51" s="124">
-        <v>14987599269.207245</v>
+        <v>19937720617.270786</v>
       </c>
       <c r="D51" s="124">
-        <v>15470092870.695057</v>
+        <v>20531772759.119011</v>
       </c>
       <c r="E51" s="124">
-        <v>15967232438.135504</v>
+        <v>21141675141.020531</v>
       </c>
       <c r="F51" s="124">
-        <v>17008007866.667847</v>
+        <v>22411818462.446606</v>
       </c>
       <c r="H51" s="121"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="13.15">
       <c r="A52" s="144">
         <v>10</v>
       </c>
       <c r="B52" s="124">
-        <v>14519135939.999992</v>
+        <v>19358847919.999992</v>
       </c>
       <c r="C52" s="124">
-        <v>15456493979.11182</v>
+        <v>20484024681.432236</v>
       </c>
       <c r="D52" s="124">
-        <v>16487800673.681828</v>
+        <v>21717941421.923744</v>
       </c>
       <c r="E52" s="124">
-        <v>17624299619.090118</v>
+        <v>23073781091.559425</v>
       </c>
       <c r="F52" s="124">
-        <v>20264258618.299137</v>
+        <v>26211540423.754593</v>
       </c>
       <c r="H52" s="121"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="13.15">
       <c r="A53" s="144">
         <v>15</v>
       </c>
       <c r="B53" s="124">
-        <v>14519135939.999992</v>
+        <v>19358847919.999989</v>
       </c>
       <c r="C53" s="124">
-        <v>16036881194.938818</v>
+        <v>21224791053.552818</v>
       </c>
       <c r="D53" s="124">
-        <v>17814511855.633007</v>
+        <v>23411947252.169121</v>
       </c>
       <c r="E53" s="124">
-        <v>19903659458.038651</v>
+        <v>25985400232.295429</v>
       </c>
       <c r="F53" s="124">
-        <v>25275991333.808659</v>
+        <v>32619157160.448387</v>
       </c>
       <c r="H53" s="121"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="A54" s="145">
         <v>20</v>
       </c>
       <c r="B54" s="124">
-        <v>14519135939.99999</v>
+        <v>19358847919.999989</v>
       </c>
       <c r="C54" s="124">
-        <v>16628202692.594425</v>
+        <v>22052688248.369595</v>
       </c>
       <c r="D54" s="124">
-        <v>19242485668.138107</v>
+        <v>25412068314.253967</v>
       </c>
       <c r="E54" s="124">
-        <v>22503789472.247555</v>
+        <v>29628968609.836342</v>
       </c>
       <c r="F54" s="124">
-        <v>31751092105.805897</v>
+        <v>41701563514.909637</v>
       </c>
       <c r="H54" s="121"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="145">
         <v>25</v>
       </c>
       <c r="B55" s="124">
-        <v>14519135939.999989</v>
+        <v>19358847919.999989</v>
       </c>
       <c r="C55" s="124">
-        <v>17178164497.849728</v>
+        <v>22897691969.888008</v>
       </c>
       <c r="D55" s="124">
-        <v>20649088452.098736</v>
+        <v>27574231649.010162</v>
       </c>
       <c r="E55" s="124">
-        <v>25228646670.450939</v>
+        <v>33819492036.702785</v>
       </c>
       <c r="F55" s="124">
-        <v>39516563417.118462</v>
+        <v>53656467924.790802</v>
       </c>
       <c r="H55" s="121"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="145">
         <v>30</v>
       </c>
       <c r="B56" s="124">
-        <v>14519135939.99999</v>
+        <v>19358847919.999985</v>
       </c>
       <c r="C56" s="124">
-        <v>17663307314.270393</v>
+        <v>23715874858.376266</v>
       </c>
       <c r="D56" s="124">
-        <v>21966384424.907784</v>
+        <v>29796837439.438824</v>
       </c>
       <c r="E56" s="124">
-        <v>27953157592.641045</v>
+        <v>38418732094.368088</v>
       </c>
       <c r="F56" s="124">
-        <v>48482956373.868553</v>
+        <v>68809386612.205093</v>
       </c>
       <c r="H56" s="121"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8">
       <c r="C57" s="115"/>
       <c r="D57" s="115"/>
       <c r="E57" s="115"/>
       <c r="F57" s="115"/>
       <c r="H57" s="121"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="120" t="s">
         <v>131</v>
       </c>
@@ -17965,7 +17954,7 @@
       <c r="F58" s="115"/>
       <c r="H58" s="121"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="133">
         <f>B50</f>
         <v>0</v>
@@ -17988,193 +17977,193 @@
       </c>
       <c r="H59" s="121"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="144">
         <v>0</v>
       </c>
       <c r="B60" s="125">
         <f>C7</f>
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C60" s="125">
         <f>C7</f>
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D60" s="125">
         <f>C7</f>
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E60" s="142">
         <f>C7</f>
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="F60" s="125">
         <f>C7</f>
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H60" s="121"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="144">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
       </c>
       <c r="B61" s="125">
         <f t="shared" ref="B61:F66" si="4">B51/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>29.999999999999996</v>
+        <v>39.999999999999986</v>
       </c>
       <c r="C61" s="125">
         <f t="shared" si="4"/>
-        <v>30.967957041954477</v>
+        <v>41.196089146757004</v>
       </c>
       <c r="D61" s="125">
         <f t="shared" si="4"/>
-        <v>31.964903974915998</v>
+        <v>42.423542648748722</v>
       </c>
       <c r="E61" s="125">
         <f t="shared" si="4"/>
-        <v>32.992112968952966</v>
+        <v>43.68374652952081</v>
       </c>
       <c r="F61" s="125">
         <f t="shared" si="4"/>
-        <v>35.142603396551394</v>
+        <v>46.308165764952413</v>
       </c>
       <c r="H61" s="121"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="13.15">
       <c r="A62" s="144">
         <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="B62" s="125">
         <f t="shared" si="4"/>
-        <v>29.999999999999986</v>
+        <v>39.999999999999986</v>
       </c>
       <c r="C62" s="125">
         <f t="shared" si="4"/>
-        <v>31.936805419383283</v>
+        <v>42.324883724655521</v>
       </c>
       <c r="D62" s="125">
         <f t="shared" si="4"/>
-        <v>34.067731182800323</v>
+        <v>44.874450198013115</v>
       </c>
       <c r="E62" s="125">
         <f t="shared" si="4"/>
-        <v>36.416009241711357</v>
+        <v>47.675938541201013</v>
       </c>
       <c r="F62" s="125">
         <f t="shared" si="4"/>
-        <v>41.870794588687772</v>
+        <v>54.159298181530616</v>
       </c>
       <c r="H62" s="121"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="A63" s="144">
         <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="B63" s="125">
         <f t="shared" si="4"/>
-        <v>29.999999999999986</v>
+        <v>39.999999999999979</v>
       </c>
       <c r="C63" s="125">
         <f t="shared" si="4"/>
-        <v>33.136023922933568</v>
+        <v>43.855483841319042</v>
       </c>
       <c r="D63" s="125">
         <f t="shared" si="4"/>
-        <v>36.809033118605143</v>
+        <v>48.374670536012189</v>
       </c>
       <c r="E63" s="125">
         <f t="shared" si="4"/>
-        <v>41.125710662721403</v>
+        <v>53.692038575186928</v>
       </c>
       <c r="F63" s="125">
         <f t="shared" si="4"/>
-        <v>52.226230482849225</v>
+        <v>67.39896360619457</v>
       </c>
       <c r="H63" s="121"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="A64" s="145">
         <f t="shared" si="3"/>
         <v>20</v>
       </c>
       <c r="B64" s="125">
         <f t="shared" si="4"/>
-        <v>29.999999999999979</v>
+        <v>39.999999999999979</v>
       </c>
       <c r="C64" s="125">
         <f t="shared" si="4"/>
-        <v>34.357835262325722</v>
+        <v>45.566117032380909</v>
       </c>
       <c r="D64" s="125">
         <f t="shared" si="4"/>
-        <v>39.75956781655033</v>
+        <v>52.507398000684262</v>
       </c>
       <c r="E64" s="125">
         <f t="shared" si="4"/>
-        <v>46.498199821071907</v>
+        <v>61.220520419969993</v>
       </c>
       <c r="F64" s="125">
         <f t="shared" si="4"/>
-        <v>65.605334030240982</v>
+        <v>86.165382748478422</v>
       </c>
       <c r="H64" s="121"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="145">
         <f t="shared" si="3"/>
         <v>25</v>
       </c>
       <c r="B65" s="125">
         <f t="shared" si="4"/>
-        <v>29.999999999999975</v>
+        <v>39.999999999999979</v>
       </c>
       <c r="C65" s="125">
         <f t="shared" si="4"/>
-        <v>35.494187606283397</v>
+        <v>47.312096390264962</v>
       </c>
       <c r="D65" s="125">
         <f t="shared" si="4"/>
-        <v>42.665944869096812</v>
+        <v>56.974943473826642</v>
       </c>
       <c r="E65" s="125">
         <f t="shared" si="4"/>
-        <v>52.128405109039029</v>
+        <v>69.87914193336519</v>
       </c>
       <c r="F65" s="125">
         <f t="shared" si="4"/>
-        <v>81.650651072666648</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+        <v>110.86706842581737</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="145">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
       <c r="B66" s="125">
         <f t="shared" si="4"/>
-        <v>29.999999999999979</v>
+        <v>39.999999999999972</v>
       </c>
       <c r="C66" s="125">
         <f t="shared" si="4"/>
-        <v>36.49660844955983</v>
+        <v>49.00265750602842</v>
       </c>
       <c r="D66" s="125">
         <f t="shared" si="4"/>
-        <v>45.387792735773054</v>
+        <v>61.567377485630509</v>
       </c>
       <c r="E66" s="125">
         <f t="shared" si="4"/>
-        <v>57.757894908120221</v>
+        <v>79.382269550610914</v>
       </c>
       <c r="F66" s="125">
         <f t="shared" si="4"/>
-        <v>100.17735884743405</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+        <v>142.17661484104494</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="172" t="s">
         <v>118</v>
       </c>
@@ -18191,7 +18180,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8">
       <c r="B69" s="128" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18206,14 +18195,14 @@
       </c>
       <c r="E69" s="136">
         <f>INDEX(B$60:F$66, MATCH(D69, A$60:A$66, 0), MATCH(C69, B$59:F$59, 0))</f>
-        <v>52.226230482849225</v>
+        <v>67.39896360619457</v>
       </c>
       <c r="F69" s="143">
         <f>Scenarios!C58</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8">
       <c r="B70" s="128" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18228,7 +18217,7 @@
       </c>
       <c r="E70" s="136">
         <f>INDEX(B$60:F$66, MATCH(D70, A$60:A$66, 0), MATCH(C70, B$59:F$59, 0))</f>
-        <v>36.416009241711357</v>
+        <v>47.675938541201013</v>
       </c>
       <c r="F70" s="143">
         <f>Scenarios!C40*(1-F$69-F$73)</f>
@@ -18236,7 +18225,7 @@
       </c>
       <c r="H70" s="121"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8">
       <c r="B71" s="128" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18251,7 +18240,7 @@
       </c>
       <c r="E71" s="136">
         <f>INDEX(B$60:F$66, MATCH(D71, A$60:A$66, 0), MATCH(C71, B$59:F$59, 0))</f>
-        <v>34.067731182800323</v>
+        <v>44.874450198013115</v>
       </c>
       <c r="F71" s="143">
         <f>Scenarios!C28*(1-F$69-F$73)</f>
@@ -18259,7 +18248,7 @@
       </c>
       <c r="H71" s="121"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8">
       <c r="B72" s="128" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18274,7 +18263,7 @@
       </c>
       <c r="E72" s="136">
         <f>INDEX(B$60:F$66, MATCH(D72, A$60:A$66, 0), MATCH(C72, B$59:F$59, 0))</f>
-        <v>31.936805419383283</v>
+        <v>42.324883724655521</v>
       </c>
       <c r="F72" s="143">
         <f>Scenarios!C34*(1-F$69-F$73)</f>
@@ -18282,7 +18271,7 @@
       </c>
       <c r="H72" s="121"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8">
       <c r="B73" s="128" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18297,21 +18286,21 @@
       </c>
       <c r="E73" s="136">
         <f>INDEX(B$60:F$66, MATCH(D73, A$60:A$66, 0), MATCH(C73, B$59:F$59, 0))</f>
-        <v>29.999999999999986</v>
+        <v>39.999999999999979</v>
       </c>
       <c r="F73" s="143">
         <f>Scenarios!C52</f>
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="156"/>
       <c r="C74" s="156"/>
       <c r="D74" s="156"/>
       <c r="E74" s="156"/>
       <c r="F74" s="157"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="156" t="s">
         <v>311</v>
       </c>
@@ -18319,23 +18308,23 @@
         <v>106</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="C76" s="156" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="C77" s="156" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:3">
       <c r="C87" s="116"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:3">
       <c r="C88" s="116"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:3">
       <c r="C89" s="116"/>
     </row>
   </sheetData>
@@ -18365,7 +18354,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -18375,7 +18364,7 @@
     <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>146</v>
       </c>
@@ -18388,7 +18377,7 @@
       </c>
       <c r="I2" s="271"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="160" t="s">
         <v>149</v>
       </c>
@@ -18400,7 +18389,7 @@
         <v>-56.86</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:9">
       <c r="B4" s="153" t="s">
         <v>147</v>
       </c>
@@ -18420,7 +18409,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9">
       <c r="H5" s="269">
         <v>2</v>
       </c>
@@ -18429,7 +18418,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="160" t="s">
         <v>96</v>
       </c>
@@ -18446,10 +18435,10 @@
       </c>
       <c r="I6" s="125">
         <f t="shared" si="0"/>
-        <v>68.992285778880003</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>90.035778317517341</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
@@ -18474,7 +18463,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18496,7 +18485,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18518,7 +18507,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9">
       <c r="E10" s="357"/>
       <c r="F10" s="357"/>
       <c r="H10" s="269">
@@ -18529,7 +18518,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="160" t="s">
         <v>449</v>
       </c>
@@ -18543,7 +18532,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9">
       <c r="B12" s="119" t="s">
         <v>145</v>
       </c>
@@ -18562,7 +18551,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9">
       <c r="B13" s="149" t="s">
         <v>153</v>
       </c>
@@ -18580,7 +18569,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18591,7 +18580,7 @@
       <c r="E14" s="357"/>
       <c r="F14" s="357"/>
     </row>
-    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>163</v>
       </c>
@@ -18600,7 +18589,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>152</v>
       </c>
@@ -18608,7 +18597,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="153" t="s">
         <v>134</v>
       </c>
@@ -18620,18 +18609,18 @@
       </c>
       <c r="F18" s="358"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="E19" s="358"/>
       <c r="F19" s="358"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="160" t="s">
         <v>304</v>
       </c>
       <c r="E20" s="358"/>
       <c r="F20" s="358"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>278</v>
       </c>
@@ -18646,13 +18635,13 @@
       <c r="E21" s="358"/>
       <c r="F21" s="358"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>279</v>
       </c>
       <c r="C22" s="161">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>57.380259942830683</v>
+        <v>76.526535943365388</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18661,7 +18650,7 @@
       <c r="E22" s="358"/>
       <c r="F22" s="358"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="160" t="s">
         <v>116</v>
       </c>
@@ -18670,7 +18659,7 @@
       </c>
       <c r="F24" s="160"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="153" t="s">
         <v>134</v>
       </c>
@@ -18682,7 +18671,7 @@
       <c r="E25" s="356"/>
       <c r="F25" s="356"/>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="119" t="s">
         <v>135</v>
       </c>
@@ -18693,13 +18682,13 @@
       <c r="E26" s="356"/>
       <c r="F26" s="356"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C27" s="161">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>65.168450335018306</v>
+        <v>85.859292827567373</v>
       </c>
       <c r="D27" s="161" t="str">
         <f>Market_currency</f>
@@ -18708,7 +18697,7 @@
       <c r="E27" s="356"/>
       <c r="F27" s="356"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>148</v>
       </c>
@@ -18719,7 +18708,7 @@
       <c r="E28" s="356"/>
       <c r="F28" s="356"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="160" t="s">
         <v>117</v>
       </c>
@@ -18728,7 +18717,7 @@
       </c>
       <c r="F30" s="160"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="153" t="s">
         <v>134</v>
       </c>
@@ -18740,7 +18729,7 @@
       <c r="E31" s="356"/>
       <c r="F31" s="356"/>
     </row>
-    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="119" t="s">
         <v>135</v>
       </c>
@@ -18751,13 +18740,13 @@
       <c r="E32" s="356"/>
       <c r="F32" s="356"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C33" s="161">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>61.088521054715052</v>
+        <v>80.977822489505968</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -18766,7 +18755,7 @@
       <c r="E33" s="356"/>
       <c r="F33" s="356"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>148</v>
       </c>
@@ -18777,7 +18766,7 @@
       <c r="E34" s="356"/>
       <c r="F34" s="356"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="160" t="s">
         <v>115</v>
       </c>
@@ -18786,7 +18775,7 @@
       </c>
       <c r="F36" s="160"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6">
       <c r="B37" s="153" t="s">
         <v>134</v>
       </c>
@@ -18798,7 +18787,7 @@
       <c r="E37" s="356"/>
       <c r="F37" s="356"/>
     </row>
-    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="119" t="s">
         <v>135</v>
       </c>
@@ -18809,13 +18798,13 @@
       <c r="E38" s="356"/>
       <c r="F38" s="356"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C39" s="161">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>69.664528319209367</v>
+        <v>91.223099730662966</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -18824,7 +18813,7 @@
       <c r="E39" s="356"/>
       <c r="F39" s="356"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>148</v>
       </c>
@@ -18836,20 +18825,20 @@
       <c r="E40" s="356"/>
       <c r="F40" s="356"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C42" s="155">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>65.251680075795875</v>
+        <v>85.955760140574199</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>162</v>
       </c>
@@ -18858,12 +18847,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="153" t="s">
         <v>134</v>
       </c>
@@ -18873,12 +18862,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="160"/>
       <c r="E47" s="160"/>
       <c r="F47" s="160"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="160" t="s">
         <v>166</v>
       </c>
@@ -18887,7 +18876,7 @@
       </c>
       <c r="F48" s="160"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="153" t="s">
         <v>134</v>
       </c>
@@ -18899,7 +18888,7 @@
       <c r="E49" s="356"/>
       <c r="F49" s="356"/>
     </row>
-    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="119" t="s">
         <v>135</v>
       </c>
@@ -18910,13 +18899,13 @@
       <c r="E50" s="356"/>
       <c r="F50" s="356"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C51" s="161">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>57.380259942830648</v>
+        <v>76.526535943365332</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -18925,7 +18914,7 @@
       <c r="E51" s="356"/>
       <c r="F51" s="356"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>148</v>
       </c>
@@ -18936,7 +18925,7 @@
       <c r="E52" s="356"/>
       <c r="F52" s="356"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="160" t="s">
         <v>317</v>
       </c>
@@ -18945,7 +18934,7 @@
       </c>
       <c r="F54" s="160"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="153" t="s">
         <v>134</v>
       </c>
@@ -18957,7 +18946,7 @@
       <c r="E55" s="356"/>
       <c r="F55" s="356"/>
     </row>
-    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="119" t="s">
         <v>135</v>
       </c>
@@ -18968,13 +18957,13 @@
       <c r="E56" s="356"/>
       <c r="F56" s="356"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>114</v>
       </c>
       <c r="C57" s="161">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>99.935214270443552</v>
+        <v>128.98534787664605</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -18983,7 +18972,7 @@
       <c r="E57" s="356"/>
       <c r="F57" s="356"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>148</v>
       </c>
@@ -18994,13 +18983,13 @@
       <c r="E58" s="356"/>
       <c r="F58" s="356"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C60" s="155">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>66.592285778879997</v>
+        <v>87.635778317517335</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19014,7 +19003,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
         <v>350</v>
       </c>
@@ -19023,7 +19012,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>305</v>
       </c>
@@ -19031,7 +19020,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6">
       <c r="B64" s="153" t="s">
         <v>134</v>
       </c>
@@ -19044,7 +19033,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6">
       <c r="B65" s="119" t="s">
         <v>135</v>
       </c>
@@ -19056,13 +19045,13 @@
         <v>313</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>103</v>
       </c>
       <c r="C66" s="161">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>66.598280217741973</v>
+        <v>87.56668023434645</v>
       </c>
       <c r="D66" s="161" t="str">
         <f>Market_currency</f>
@@ -19072,7 +19061,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
         <v>351</v>
       </c>
@@ -19080,7 +19069,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>306</v>
       </c>
@@ -19090,7 +19079,7 @@
       </c>
       <c r="E69" s="135"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>294</v>
       </c>
@@ -19102,7 +19091,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>293</v>
       </c>
@@ -19112,7 +19101,7 @@
       </c>
       <c r="E71" s="273"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>285</v>
       </c>
@@ -19125,10 +19114,10 @@
       </c>
       <c r="F72" s="319">
         <f>BS!D89/C60</f>
-        <v>-8.7950215386604794E-4</v>
-      </c>
-    </row>
-    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+        <v>-6.6831218821595498E-4</v>
+      </c>
+    </row>
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>128</v>
       </c>
@@ -19137,12 +19126,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6">
       <c r="B76" s="268" t="s">
         <v>298</v>
       </c>
@@ -19152,7 +19141,7 @@
       </c>
       <c r="D76" s="135"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>112</v>
       </c>
@@ -19165,49 +19154,49 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6">
       <c r="B80" s="149" t="s">
         <v>300</v>
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.23700000000000002</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>4.3586709148839331</v>
+        <v>4.7765820962496424</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>30.310553381374593</v>
+        <v>46.299078709409685</v>
       </c>
       <c r="D82" s="117"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="111" t="s">
         <v>102</v>
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>34.669224296258527</v>
+        <v>51.075660805659325</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19218,18 +19207,18 @@
       </c>
       <c r="F83" s="319">
         <f>(1-C83/C60)</f>
-        <v>0.4793807737524155</v>
-      </c>
-    </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.41718255048064179</v>
+      </c>
+    </row>
+    <row r="84" spans="2:8">
       <c r="E84" s="121"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8">
       <c r="B86" s="149" t="s">
         <v>301</v>
       </c>
@@ -19242,61 +19231,61 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>299</v>
       </c>
       <c r="C87" s="259">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>9.4210132770872423E-2</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.19201956038874379</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8">
       <c r="B90" s="149" t="s">
         <v>415</v>
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.16739999999999999</v>
-      </c>
-    </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.13700000000000001</v>
+      </c>
+    </row>
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>5.3254251552044352</v>
+        <v>5.6000862814257664</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>41.85668746927864</v>
+        <v>59.621109555531582</v>
       </c>
       <c r="D92" s="117"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="111" t="s">
         <v>102</v>
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>47.182112624483075</v>
+        <v>65.221195836957349</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19307,58 +19296,58 @@
       </c>
       <c r="F93" s="319">
         <f>(1-C93/C60)</f>
-        <v>0.29147780298229276</v>
-      </c>
-    </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.25576976562413412</v>
+      </c>
+    </row>
+    <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
         <v>398</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="306"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8">
       <c r="B96" s="149" t="s">
         <v>404</v>
       </c>
       <c r="C96" s="135">
         <f>Thesis!F31</f>
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="G96" s="2"/>
       <c r="H96" s="306"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C97" s="117">
         <f>PV(C96, C76, -C77, 0)</f>
-        <v>6.1850327693949119</v>
+        <v>6.4152286787079351</v>
       </c>
       <c r="D97" s="117"/>
       <c r="G97" s="2"/>
       <c r="H97" s="306"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C98" s="117">
         <f>C60/(1+C96)^C76</f>
-        <v>52.863103454503879</v>
+        <v>73.580689358931636</v>
       </c>
       <c r="D98" s="117"/>
       <c r="G98" s="2"/>
       <c r="H98" s="306"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="111" t="s">
         <v>399</v>
       </c>
       <c r="C99" s="112">
         <f>C97+C98</f>
-        <v>59.048136223898794</v>
+        <v>79.995918037639569</v>
       </c>
       <c r="D99" t="s">
         <v>397</v>
@@ -19368,53 +19357,53 @@
       </c>
       <c r="F99" s="319">
         <f>(1-C99/C60)</f>
-        <v>0.1132886409700905</v>
-      </c>
-    </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
+        <v>8.7177411173293029E-2</v>
+      </c>
+    </row>
+    <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
         <v>424</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8">
       <c r="B102" s="149" t="s">
         <v>423</v>
       </c>
       <c r="C102" s="135">
         <f>Thesis!F32</f>
-        <v>0.1174</v>
-      </c>
-    </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
         <v>122</v>
       </c>
       <c r="C103" s="117">
         <f>PV(C102, C76, -C77, 0)</f>
-        <v>5.7902475022527575</v>
+        <v>6.1077361402784396</v>
       </c>
       <c r="D103" s="117"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
         <v>123</v>
       </c>
       <c r="C104" s="117">
         <f>C60/(1+C102)^C76</f>
-        <v>47.730712926624079</v>
+        <v>68.23274069010661</v>
       </c>
       <c r="D104" s="117"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="111" t="s">
         <v>399</v>
       </c>
       <c r="C105" s="112">
         <f>C103+C104</f>
-        <v>53.520960428876833</v>
+        <v>74.340476830385043</v>
       </c>
       <c r="D105" t="s">
         <v>397</v>
@@ -19424,19 +19413,19 @@
       </c>
       <c r="F105" s="319">
         <f>(1-C105/C66)</f>
-        <v>0.19636122353473784</v>
-      </c>
-    </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.15104150766667601</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="310" t="s">
         <v>325</v>
       </c>
       <c r="F107" s="307"/>
     </row>
-    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="303" t="s">
         <v>326</v>
       </c>
@@ -19444,7 +19433,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="304" t="s">
         <v>326</v>
       </c>
@@ -19452,7 +19441,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="305" t="s">
         <v>326</v>
       </c>

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52F7F9FF-EC91-48F0-8730-16254D9D314C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B95251-15D5-4E01-9104-95A8A3EA0406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="463">
   <si>
     <t>Number of Shares:</t>
   </si>
@@ -2466,6 +2466,9 @@
   </si>
   <si>
     <t>CN</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
 </sst>
 </file>
@@ -4216,7 +4219,7 @@
         <v>354</v>
       </c>
       <c r="F1" s="276" t="s">
-        <v>452</v>
+        <v>462</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="13.9">
@@ -4306,7 +4309,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>56.86</v>
+        <v>57.9</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4327,7 +4330,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>27518.602318279998</v>
+        <v>28021.932364200002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4453,7 +4456,7 @@
       </c>
       <c r="E26" s="331">
         <f ca="1">Scenarios!C87</f>
-        <v>0.19201956038874379</v>
+        <v>0.18459249999780813</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4485,7 +4488,7 @@
       </c>
       <c r="C29" s="340">
         <f>C144</f>
-        <v>51.075660805659325</v>
+        <v>40.809862006189697</v>
       </c>
       <c r="D29" s="340" t="str">
         <f>D144</f>
@@ -4495,7 +4498,7 @@
         <v>426</v>
       </c>
       <c r="F29" s="332">
-        <v>0.23700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4504,7 +4507,7 @@
       </c>
       <c r="C30" s="341">
         <f>C152</f>
-        <v>65.221195836957349</v>
+        <v>57.560060075377699</v>
       </c>
       <c r="D30" s="341" t="str">
         <f>D152</f>
@@ -4514,7 +4517,7 @@
         <v>439</v>
       </c>
       <c r="F30" s="342">
-        <v>0.13700000000000001</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="31" spans="2:6">
@@ -4843,7 +4846,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>8.081439043489845E-2</v>
+        <v>7.9362802074755184E-2</v>
       </c>
       <c r="F69" s="344"/>
     </row>
@@ -4853,7 +4856,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.2208934224410834E-2</v>
+        <v>4.145077720207254E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -5395,7 +5398,7 @@
       </c>
       <c r="C137" s="246">
         <f>F29</f>
-        <v>0.23700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5430,7 +5433,7 @@
       </c>
       <c r="C141" s="326">
         <f>F29</f>
-        <v>0.23700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -5440,7 +5443,7 @@
       </c>
       <c r="C142" s="238">
         <f>Scenarios!C81</f>
-        <v>4.7765820962496424</v>
+        <v>4.141861698859338</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5450,7 +5453,7 @@
       </c>
       <c r="C143" s="238">
         <f>Scenarios!C82</f>
-        <v>46.299078709409685</v>
+        <v>36.66800030733036</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5459,7 +5462,7 @@
       </c>
       <c r="C144" s="237">
         <f>Scenarios!C83</f>
-        <v>51.075660805659325</v>
+        <v>40.809862006189697</v>
       </c>
       <c r="D144" s="330" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
@@ -5485,7 +5488,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.41718255048064179</v>
+        <v>0.53432419053403568</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5499,7 +5502,7 @@
       </c>
       <c r="C149" s="326">
         <f>Scenarios!C90</f>
-        <v>0.13700000000000001</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="150" spans="2:4">
@@ -5509,7 +5512,7 @@
       </c>
       <c r="C150" s="238">
         <f>Scenarios!C91</f>
-        <v>5.6000862814257664</v>
+        <v>5.160300872171014</v>
       </c>
     </row>
     <row r="151" spans="2:4">
@@ -5519,7 +5522,7 @@
       </c>
       <c r="C151" s="238">
         <f>Scenarios!C92</f>
-        <v>59.621109555531582</v>
+        <v>52.399759203206685</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5528,7 +5531,7 @@
       </c>
       <c r="C152" s="237">
         <f>Scenarios!C93</f>
-        <v>65.221195836957349</v>
+        <v>57.560060075377699</v>
       </c>
       <c r="D152" s="330" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5554,7 +5557,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.25576976562413412</v>
+        <v>0.34318994843830652</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -13374,12 +13377,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.2208934224410834E-2</v>
+        <v>4.145077720207254E-2</v>
       </c>
       <c r="E93" s="293"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.2208934224410834E-2</v>
+        <v>4.145077720207254E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14573,50 +14576,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>8.081439043489845E-2</v>
+        <v>7.9362802074755184E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="290"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>8.4406706021332489E-2</v>
+        <v>8.2890592476217009E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>9.6906274947503632E-2</v>
+        <v>9.5165644102159871E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.2314772588312069E-2</v>
+        <v>9.0656614324204216E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>8.633151887018238E-2</v>
+        <v>8.4780831830027117E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.8344642812274692E-2</v>
+        <v>4.7476276171087024E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6974092318383514E-2</v>
+        <v>1.6669203613528267E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.5561807203328634E-2</v>
+        <v>1.5282285968588362E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2529275688212001E-2</v>
+        <v>1.2304224795021319E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.2372446829315589E-2</v>
+        <v>1.2150212896630128E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>6.8498886251495425E-3</v>
+        <v>6.7268509020035061E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14630,43 +14633,43 @@
       <c r="C126" s="170"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1740361155834801E-2</v>
+        <v>8.0272140506403564E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.8535838544342239E-2</v>
+        <v>9.6765937472043165E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4005488036054061E-2</v>
+        <v>9.2316961135233744E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7183068683916898E-2</v>
+        <v>8.5617086103065884E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.3677547127310843E-2</v>
+        <v>6.2533770805853095E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.647434348495414E-2</v>
+        <v>2.5998811235828884E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.530817103745733E-2</v>
+        <v>1.5033205616404555E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1850977430760143E-2</v>
+        <v>1.1638110133212809E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0853298209495249E-3</v>
+        <v>4.9939871091397225E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.579935318807917E-3</v>
+        <v>-5.479708501337101E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18386,7 +18389,7 @@
       </c>
       <c r="I3" s="125">
         <f>-Market_Price</f>
-        <v>-56.86</v>
+        <v>-57.9</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18626,7 +18629,7 @@
       </c>
       <c r="C21" s="161">
         <f>Market_Price</f>
-        <v>56.86</v>
+        <v>57.9</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19165,7 +19168,7 @@
       </c>
       <c r="C80" s="168">
         <f>Thesis!F29</f>
-        <v>0.23700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19174,7 +19177,7 @@
       </c>
       <c r="C81" s="117">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>4.7765820962496424</v>
+        <v>4.141861698859338</v>
       </c>
       <c r="D81" s="117"/>
       <c r="E81" s="100"/>
@@ -19186,7 +19189,7 @@
       </c>
       <c r="C82" s="117">
         <f>C60/(1+C80)^C76</f>
-        <v>46.299078709409685</v>
+        <v>36.66800030733036</v>
       </c>
       <c r="D82" s="117"/>
     </row>
@@ -19196,7 +19199,7 @@
       </c>
       <c r="C83" s="112">
         <f>C81+C82</f>
-        <v>51.075660805659325</v>
+        <v>40.809862006189697</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19207,7 +19210,7 @@
       </c>
       <c r="F83" s="319">
         <f>(1-C83/C60)</f>
-        <v>0.41718255048064179</v>
+        <v>0.53432419053403568</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19224,7 +19227,7 @@
       </c>
       <c r="C86" s="117">
         <f>Market_Price</f>
-        <v>56.86</v>
+        <v>57.9</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19237,7 +19240,7 @@
       </c>
       <c r="C87" s="259">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.19201956038874379</v>
+        <v>0.18459249999780813</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19254,7 +19257,7 @@
       </c>
       <c r="C90" s="168">
         <f>Thesis!F30</f>
-        <v>0.13700000000000001</v>
+        <v>0.187</v>
       </c>
     </row>
     <row r="91" spans="2:8">
@@ -19263,7 +19266,7 @@
       </c>
       <c r="C91" s="117">
         <f>PV(C90, C76, -C77, 0)</f>
-        <v>5.6000862814257664</v>
+        <v>5.160300872171014</v>
       </c>
       <c r="D91" s="117"/>
       <c r="E91" s="100"/>
@@ -19275,7 +19278,7 @@
       </c>
       <c r="C92" s="117">
         <f>C60/(1+C90)^C76</f>
-        <v>59.621109555531582</v>
+        <v>52.399759203206685</v>
       </c>
       <c r="D92" s="117"/>
     </row>
@@ -19285,7 +19288,7 @@
       </c>
       <c r="C93" s="112">
         <f>C91+C92</f>
-        <v>65.221195836957349</v>
+        <v>57.560060075377699</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19296,7 +19299,7 @@
       </c>
       <c r="F93" s="319">
         <f>(1-C93/C60)</f>
-        <v>0.25576976562413412</v>
+        <v>0.34318994843830652</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932FD22C-A6EB-4557-8E8B-1299C4FB2EC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9734F704-4F77-46AE-87E2-9EC5CF8EA2FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3868,29 +3868,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4366,13 +4366,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="349" t="s">
+      <c r="B18" s="347" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="349"/>
-      <c r="D18" s="349"/>
-      <c r="E18" s="349"/>
-      <c r="F18" s="349"/>
+      <c r="C18" s="347"/>
+      <c r="D18" s="347"/>
+      <c r="E18" s="347"/>
+      <c r="F18" s="347"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4448,14 +4448,14 @@
       </c>
       <c r="C26" s="307">
         <f>C127</f>
-        <v>87.635778317517335</v>
+        <v>82.72003076740333</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>400</v>
       </c>
       <c r="E26" s="304">
         <f ca="1">Scenarios!C87</f>
-        <v>0.18459249999780813</v>
+        <v>0.16334582016407428</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="C29" s="313">
         <f>C144</f>
-        <v>40.809862006189697</v>
+        <v>38.753046443654675</v>
       </c>
       <c r="D29" s="313" t="str">
         <f>D144</f>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="C30" s="314">
         <f>C152</f>
-        <v>57.560060075377699</v>
+        <v>54.620804067443785</v>
       </c>
       <c r="D30" s="314" t="str">
         <f>D152</f>
@@ -4525,7 +4525,7 @@
       </c>
       <c r="C31" s="314">
         <f>C160</f>
-        <v>79.995918037639569</v>
+        <v>75.868561604045041</v>
       </c>
       <c r="D31" s="314" t="str">
         <f>D160</f>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="C32" s="314">
         <f>C168</f>
-        <v>74.340476830385043</v>
+        <v>70.513102505372515</v>
       </c>
       <c r="D32" s="314" t="str">
         <f>D168</f>
@@ -4572,22 +4572,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="349" t="s">
+      <c r="B36" s="347" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="349"/>
-      <c r="D36" s="349"/>
-      <c r="E36" s="349"/>
-      <c r="F36" s="349"/>
+      <c r="C36" s="347"/>
+      <c r="D36" s="347"/>
+      <c r="E36" s="347"/>
+      <c r="F36" s="347"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="352" t="s">
+      <c r="B37" s="349" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="352"/>
-      <c r="D37" s="352"/>
-      <c r="E37" s="352"/>
-      <c r="F37" s="352"/>
+      <c r="C37" s="349"/>
+      <c r="D37" s="349"/>
+      <c r="E37" s="349"/>
+      <c r="F37" s="349"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4599,13 +4599,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="350" t="s">
+      <c r="B40" s="348" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="350"/>
-      <c r="D40" s="350"/>
-      <c r="E40" s="350"/>
-      <c r="F40" s="350"/>
+      <c r="C40" s="348"/>
+      <c r="D40" s="348"/>
+      <c r="E40" s="348"/>
+      <c r="F40" s="348"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4613,7 +4613,7 @@
       </c>
       <c r="C41" s="341">
         <f>Normalized_FCF!C8</f>
-        <v>3123489756.696907</v>
+        <v>2957715106.6986084</v>
       </c>
       <c r="D41" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4625,13 +4625,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="350" t="s">
+      <c r="B43" s="348" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="350"/>
-      <c r="D43" s="350"/>
-      <c r="E43" s="350"/>
-      <c r="F43" s="350"/>
+      <c r="C43" s="348"/>
+      <c r="D43" s="348"/>
+      <c r="E43" s="348"/>
+      <c r="F43" s="348"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4660,13 +4660,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="350" t="s">
+      <c r="B47" s="348" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="350"/>
-      <c r="D47" s="350"/>
-      <c r="E47" s="350"/>
-      <c r="F47" s="350"/>
+      <c r="C47" s="348"/>
+      <c r="D47" s="348"/>
+      <c r="E47" s="348"/>
+      <c r="F47" s="348"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4682,13 +4682,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="350" t="s">
+      <c r="B50" s="348" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="350"/>
-      <c r="D50" s="350"/>
-      <c r="E50" s="350"/>
-      <c r="F50" s="350"/>
+      <c r="C50" s="348"/>
+      <c r="D50" s="348"/>
+      <c r="E50" s="348"/>
+      <c r="F50" s="348"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="C51" s="346">
         <f>Normalized_FCF!C48</f>
-        <v>38554805.997018404</v>
+        <v>39079014.816265978</v>
       </c>
       <c r="D51" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="C53" s="341">
         <f>Normalized_FCF!C12</f>
-        <v>30881944.997018404</v>
+        <v>31406153.816265978</v>
       </c>
       <c r="D53" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4752,13 +4752,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="350" t="s">
+      <c r="B58" s="348" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="350"/>
-      <c r="D58" s="350"/>
-      <c r="E58" s="350"/>
-      <c r="F58" s="350"/>
+      <c r="C58" s="348"/>
+      <c r="D58" s="348"/>
+      <c r="E58" s="348"/>
+      <c r="F58" s="348"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="C59" s="341">
         <f>Normalized_FCF!C14</f>
-        <v>-788592925.42348135</v>
+        <v>-747280315.12871861</v>
       </c>
       <c r="D59" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4774,7 +4774,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="350" t="s">
+      <c r="B61" s="348" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4796,22 +4796,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="349" t="s">
+      <c r="B64" s="347" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="349"/>
-      <c r="D64" s="349"/>
-      <c r="E64" s="349"/>
-      <c r="F64" s="349"/>
+      <c r="C64" s="347"/>
+      <c r="D64" s="347"/>
+      <c r="E64" s="347"/>
+      <c r="F64" s="347"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="349" t="s">
+      <c r="B65" s="347" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="349"/>
-      <c r="D65" s="349"/>
-      <c r="E65" s="349"/>
-      <c r="F65" s="349"/>
+      <c r="C65" s="347"/>
+      <c r="D65" s="347"/>
+      <c r="E65" s="347"/>
+      <c r="F65" s="347"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="C67" s="341">
         <f>Normalized_FCF!G19</f>
-        <v>2322754575.9970183</v>
+        <v>2323278784.8162661</v>
       </c>
       <c r="D67" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4832,7 +4832,7 @@
       </c>
       <c r="C68" s="341">
         <f>Normalized_FCF!C19</f>
-        <v>2223899071.9721813</v>
+        <v>2099961241.0878935</v>
       </c>
       <c r="D68" s="1" t="str">
         <f>Reporting_currency</f>
@@ -4845,7 +4845,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.9362802074755184E-2</v>
+        <v>7.4939915413211919E-2</v>
       </c>
       <c r="F69" s="317"/>
     </row>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="F70" s="318">
         <f>Normalized_FCF!C92</f>
-        <v>0.52229477939839231</v>
+        <v>0.55312014930250053</v>
       </c>
     </row>
     <row r="72" spans="1:6" ht="13.9">
@@ -4880,22 +4880,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="349" t="s">
+      <c r="B74" s="347" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="349"/>
-      <c r="D74" s="349"/>
-      <c r="E74" s="349"/>
-      <c r="F74" s="349"/>
+      <c r="C74" s="347"/>
+      <c r="D74" s="347"/>
+      <c r="E74" s="347"/>
+      <c r="F74" s="347"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="352" t="s">
+      <c r="B75" s="349" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="352"/>
-      <c r="D75" s="352"/>
-      <c r="E75" s="352"/>
-      <c r="F75" s="352"/>
+      <c r="C75" s="349"/>
+      <c r="D75" s="349"/>
+      <c r="E75" s="349"/>
+      <c r="F75" s="349"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="210" t="s">
@@ -4939,22 +4939,22 @@
       <c r="C82" s="121"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="349" t="s">
+      <c r="B83" s="347" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="349"/>
-      <c r="D83" s="349"/>
-      <c r="E83" s="349"/>
-      <c r="F83" s="349"/>
+      <c r="C83" s="347"/>
+      <c r="D83" s="347"/>
+      <c r="E83" s="347"/>
+      <c r="F83" s="347"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="349" t="s">
+      <c r="B84" s="347" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="349"/>
-      <c r="D84" s="349"/>
-      <c r="E84" s="349"/>
-      <c r="F84" s="349"/>
+      <c r="C84" s="347"/>
+      <c r="D84" s="347"/>
+      <c r="E84" s="347"/>
+      <c r="F84" s="347"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4970,7 +4970,7 @@
       </c>
       <c r="C87" s="223">
         <f>DCF!C6*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>76.585104002138763</v>
+        <v>72.317018373749505</v>
       </c>
       <c r="D87" s="1" t="str">
         <f>Market_currency</f>
@@ -4991,13 +4991,13 @@
       <c r="A90" s="209"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="349" t="s">
+      <c r="B91" s="347" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="349"/>
-      <c r="D91" s="349"/>
-      <c r="E91" s="349"/>
-      <c r="F91" s="349"/>
+      <c r="C91" s="347"/>
+      <c r="D91" s="347"/>
+      <c r="E91" s="347"/>
+      <c r="F91" s="347"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5010,13 +5010,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="349" t="s">
+      <c r="B95" s="347" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="349"/>
-      <c r="D95" s="349"/>
-      <c r="E95" s="349"/>
-      <c r="F95" s="349"/>
+      <c r="C95" s="347"/>
+      <c r="D95" s="347"/>
+      <c r="E95" s="347"/>
+      <c r="F95" s="347"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="C100" s="300">
         <f>BS!C50</f>
-        <v>3.9546057100127742E-2</v>
+        <v>4.1762542981319963E-2</v>
       </c>
     </row>
     <row r="102" spans="2:6">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="C104" s="341">
         <f>DCF!C8</f>
-        <v>65618450.04890883</v>
+        <v>51803895.882383943</v>
       </c>
       <c r="D104" s="1" t="str">
         <f>Reporting_currency</f>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="C105" s="223">
         <f>C104*scaling_factor*Exchange_Rate/Common_Shares</f>
-        <v>0.13558337834994227</v>
+        <v>0.10703921244996059</v>
       </c>
       <c r="D105" s="1" t="str">
         <f>Market_currency</f>
@@ -5147,13 +5147,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="349" t="s">
+      <c r="B111" s="347" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="349"/>
-      <c r="D111" s="349"/>
-      <c r="E111" s="349"/>
-      <c r="F111" s="349"/>
+      <c r="C111" s="347"/>
+      <c r="D111" s="347"/>
+      <c r="E111" s="347"/>
+      <c r="F111" s="347"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="C113" s="223">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>76.526535943365388</v>
+        <v>72.229906149076143</v>
       </c>
       <c r="D113" s="1" t="str">
         <f>Market_currency</f>
@@ -5192,13 +5192,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="350" t="s">
+      <c r="B118" s="348" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="350"/>
-      <c r="D118" s="350"/>
-      <c r="E118" s="350"/>
-      <c r="F118" s="350"/>
+      <c r="C118" s="348"/>
+      <c r="D118" s="348"/>
+      <c r="E118" s="348"/>
+      <c r="F118" s="348"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="233" t="s">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="E121" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E74,DDM!E69),2)&amp;" "&amp;Market_currency</f>
-        <v>128.99 CNY</v>
+        <v>121.77 CNY</v>
       </c>
       <c r="F121" s="232">
         <f>DCF!F74</f>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="E122" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E75,DDM!E70),2)&amp;" "&amp;Market_currency</f>
-        <v>91.22 CNY</v>
+        <v>86.11 CNY</v>
       </c>
       <c r="F122" s="221">
         <f>DCF!F75</f>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="E123" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E76,DDM!E71),2)&amp;" "&amp;Market_currency</f>
-        <v>85.86 CNY</v>
+        <v>81.04 CNY</v>
       </c>
       <c r="F123" s="221">
         <f>DCF!F76</f>
@@ -5298,7 +5298,7 @@
       </c>
       <c r="E124" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E77,DDM!E72),2)&amp;" "&amp;Market_currency</f>
-        <v>80.98 CNY</v>
+        <v>76.43 CNY</v>
       </c>
       <c r="F124" s="221">
         <f>DCF!F77</f>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="E125" s="231" t="str">
         <f>ROUND(IF(valuation_method="DCF",DCF!E78,DDM!E73),2)&amp;" "&amp;Market_currency</f>
-        <v>76.53 CNY</v>
+        <v>72.23 CNY</v>
       </c>
       <c r="F125" s="221">
         <f>DCF!F78</f>
@@ -5333,7 +5333,7 @@
       </c>
       <c r="C127" s="217">
         <f>Scenarios!C60</f>
-        <v>87.635778317517335</v>
+        <v>82.72003076740333</v>
       </c>
       <c r="D127" s="212" t="str">
         <f>Market_currency</f>
@@ -5341,13 +5341,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="353" t="s">
+      <c r="B129" s="352" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="353"/>
-      <c r="D129" s="353"/>
-      <c r="E129" s="353"/>
-      <c r="F129" s="353"/>
+      <c r="C129" s="352"/>
+      <c r="D129" s="352"/>
+      <c r="E129" s="352"/>
+      <c r="F129" s="352"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="222" t="s">
@@ -5360,22 +5360,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="354" t="s">
+      <c r="B133" s="350" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="354"/>
-      <c r="D133" s="354"/>
-      <c r="E133" s="354"/>
-      <c r="F133" s="354"/>
+      <c r="C133" s="350"/>
+      <c r="D133" s="350"/>
+      <c r="E133" s="350"/>
+      <c r="F133" s="350"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="349" t="s">
+      <c r="B134" s="347" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="349"/>
-      <c r="D134" s="349"/>
-      <c r="E134" s="349"/>
-      <c r="F134" s="349"/>
+      <c r="C134" s="347"/>
+      <c r="D134" s="347"/>
+      <c r="E134" s="347"/>
+      <c r="F134" s="347"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="210" t="s">
@@ -5452,7 +5452,7 @@
       </c>
       <c r="C143" s="216">
         <f>Scenarios!C82</f>
-        <v>36.66800030733036</v>
+        <v>34.611184744795338</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="C144" s="215">
         <f>Scenarios!C83</f>
-        <v>40.809862006189697</v>
+        <v>38.753046443654675</v>
       </c>
       <c r="D144" s="303" t="str">
         <f>IF($D$11="","",C144*$E$25)</f>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="C146" s="92">
         <f>Scenarios!F83</f>
-        <v>0.53432419053403568</v>
+        <v>0.53151557024171581</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="C151" s="216">
         <f>Scenarios!C92</f>
-        <v>52.399759203206685</v>
+        <v>49.460503195272771</v>
       </c>
     </row>
     <row r="152" spans="2:4">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="C152" s="215">
         <f>Scenarios!C93</f>
-        <v>57.560060075377699</v>
+        <v>54.620804067443785</v>
       </c>
       <c r="D152" s="303" t="str">
         <f>IF($D$11="","",C152*$E$25)</f>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="C154" s="92">
         <f>Scenarios!F93</f>
-        <v>0.34318994843830652</v>
+        <v>0.33969071867212519</v>
       </c>
     </row>
     <row r="156" spans="2:4">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="C159" s="216">
         <f>Scenarios!C98</f>
-        <v>73.580689358931636</v>
+        <v>69.453332925337108</v>
       </c>
     </row>
     <row r="160" spans="2:4">
@@ -5599,7 +5599,7 @@
       </c>
       <c r="C160" s="215">
         <f>Scenarios!C99</f>
-        <v>79.995918037639569</v>
+        <v>75.868561604045041</v>
       </c>
       <c r="D160" s="303" t="str">
         <f>IF($D$11="","",C160*$E$25)</f>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="C162" s="92">
         <f>Scenarios!F99</f>
-        <v>8.7177411173293029E-2</v>
+        <v>8.2827207627903632E-2</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="C167" s="216">
         <f>Scenarios!C104</f>
-        <v>68.23274069010661</v>
+        <v>64.405366365094082</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="C168" s="215">
         <f>Scenarios!C105</f>
-        <v>74.340476830385043</v>
+        <v>70.513102505372515</v>
       </c>
       <c r="D168" s="303" t="str">
         <f>IF($D$11="","",C168*$E$25)</f>
@@ -5694,7 +5694,7 @@
       </c>
       <c r="C170" s="92">
         <f>Scenarios!F105</f>
-        <v>0.15104150766667601</v>
+        <v>0.14689628955752243</v>
       </c>
     </row>
     <row r="172" spans="1:6" ht="13.9">
@@ -5708,13 +5708,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="348" t="s">
+      <c r="B174" s="354" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="349"/>
-      <c r="D174" s="349"/>
-      <c r="E174" s="349"/>
-      <c r="F174" s="349"/>
+      <c r="C174" s="347"/>
+      <c r="D174" s="347"/>
+      <c r="E174" s="347"/>
+      <c r="F174" s="347"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="210" t="s">
@@ -5751,13 +5751,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="350" t="s">
+      <c r="B183" s="348" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="350"/>
-      <c r="D183" s="350"/>
-      <c r="E183" s="350"/>
-      <c r="F183" s="350"/>
+      <c r="C183" s="348"/>
+      <c r="D183" s="348"/>
+      <c r="E183" s="348"/>
+      <c r="F183" s="348"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5765,22 +5765,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="347" t="s">
+      <c r="B186" s="353" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="347"/>
-      <c r="D186" s="347"/>
-      <c r="E186" s="347"/>
-      <c r="F186" s="347"/>
+      <c r="C186" s="353"/>
+      <c r="D186" s="353"/>
+      <c r="E186" s="353"/>
+      <c r="F186" s="353"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="347" t="s">
+      <c r="B187" s="353" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="347"/>
-      <c r="D187" s="347"/>
-      <c r="E187" s="347"/>
-      <c r="F187" s="347"/>
+      <c r="C187" s="353"/>
+      <c r="D187" s="353"/>
+      <c r="E187" s="353"/>
+      <c r="F187" s="353"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5804,6 +5804,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5820,17 +5831,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -9265,7 +9265,7 @@
       </c>
       <c r="C50" s="95">
         <f>G31/Normalized_FCF!C8</f>
-        <v>3.9546057100127742E-2</v>
+        <v>4.1762542981319963E-2</v>
       </c>
       <c r="D50" s="95">
         <f>G31/Normalized_FCF!G8</f>
@@ -9305,7 +9305,7 @@
       </c>
       <c r="C54" s="92">
         <f>Normalized_FCF!C8/G35</f>
-        <v>0.32189273249886463</v>
+        <v>0.30480874656531537</v>
       </c>
       <c r="D54" s="92">
         <f>Normalized_FCF!G8/G35</f>
@@ -9430,7 +9430,7 @@
       </c>
       <c r="D66" s="76">
         <f>C66-D75</f>
-        <v>65618450.04890883</v>
+        <v>51803895.882383943</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>227</v>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="D73" s="76">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
-        <v>-1016040624.0210911</v>
+        <v>-1029855178.187616</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>352</v>
@@ -9517,7 +9517,7 @@
       </c>
       <c r="D74" s="258">
         <f>-$C$66/D73</f>
-        <v>1.0645825063462686</v>
+        <v>1.050302117209869</v>
       </c>
       <c r="F74" s="253" t="s">
         <v>320</v>
@@ -9530,7 +9530,7 @@
       <c r="C75" s="262"/>
       <c r="D75" s="261">
         <f>MAX(-D73*D76,G5)</f>
-        <v>1016040624.0210911</v>
+        <v>1029855178.187616</v>
       </c>
       <c r="F75" s="253" t="s">
         <v>353</v>
@@ -9662,11 +9662,11 @@
       </c>
       <c r="C87" s="76">
         <f>DCF!C8*Exchange_Rate</f>
-        <v>65618450.04890883</v>
+        <v>51803895.882383943</v>
       </c>
       <c r="D87" s="223">
         <f>C87*scaling_factor/Common_Shares</f>
-        <v>0.13558337834994227</v>
+        <v>0.10703921244996059</v>
       </c>
       <c r="E87" s="240" t="str">
         <f>Market_currency</f>
@@ -9696,11 +9696,11 @@
       </c>
       <c r="C89" s="180">
         <f>SUM(C86:C88)</f>
-        <v>-28345253.569091171</v>
+        <v>-42159807.735616058</v>
       </c>
       <c r="D89" s="242">
         <f>SUM(D86:D88)</f>
-        <v>-5.8568058773388353E-2</v>
+        <v>-8.7112224673370042E-2</v>
       </c>
       <c r="E89" s="240" t="str">
         <f>Market_currency</f>
@@ -9891,7 +9891,7 @@
       </c>
       <c r="C5" s="321">
         <f>C25</f>
-        <v>-10434492185.803093</v>
+        <v>-10627750820.551392</v>
       </c>
       <c r="E5" s="270"/>
       <c r="G5" s="326">
@@ -9946,7 +9946,7 @@
       </c>
       <c r="C6" s="322">
         <f>C4+C5</f>
-        <v>3719954183.946907</v>
+        <v>3526695549.1986084</v>
       </c>
       <c r="E6" s="270"/>
       <c r="G6" s="322">
@@ -10001,7 +10001,7 @@
       </c>
       <c r="C7" s="321">
         <f>C35</f>
-        <v>-596464427.25</v>
+        <v>-568980442.5</v>
       </c>
       <c r="E7" s="270"/>
       <c r="G7" s="321">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="C8" s="323">
         <f>C6+C7</f>
-        <v>3123489756.696907</v>
+        <v>2957715106.6986084</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="276"/>
@@ -10280,36 +10280,36 @@
       </c>
       <c r="C12" s="321">
         <f>C50</f>
-        <v>30881944.997018404</v>
+        <v>31406153.816265978</v>
       </c>
       <c r="E12" s="270"/>
       <c r="G12" s="321">
         <f>G50</f>
-        <v>30881944.997018404</v>
+        <v>31406153.816265978</v>
       </c>
       <c r="H12" s="321">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
-        <v>61060472.426252395</v>
+        <v>61971192.331585214</v>
       </c>
       <c r="I12" s="321">
         <f t="shared" si="6"/>
-        <v>58034950.960215338</v>
+        <v>58874284.747775584</v>
       </c>
       <c r="J12" s="321">
         <f t="shared" si="6"/>
-        <v>19677003.321634412</v>
+        <v>20137430.77782803</v>
       </c>
       <c r="K12" s="321">
         <f t="shared" si="6"/>
-        <v>5923283.77028092</v>
+        <v>6490894.562197201</v>
       </c>
       <c r="L12" s="321">
         <f t="shared" si="6"/>
-        <v>-2708899.7766326303</v>
+        <v>-2599288.5787666151</v>
       </c>
       <c r="M12" s="321">
         <f t="shared" si="6"/>
-        <v>-6124799.2178542558</v>
+        <v>-6040379.1363799218</v>
       </c>
       <c r="N12" s="321">
         <f t="shared" si="6"/>
@@ -10335,36 +10335,36 @@
       </c>
       <c r="C13" s="322">
         <f>SUM(C8:C12)</f>
-        <v>3154371701.6939254</v>
+        <v>2989121260.5148745</v>
       </c>
       <c r="E13" s="270"/>
       <c r="G13" s="322">
         <f>IF(G$4="","",SUM(G8:G12))</f>
-        <v>3140094523.9970183</v>
+        <v>3140618732.8162661</v>
       </c>
       <c r="H13" s="322">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
-        <v>3330847239.4262524</v>
+        <v>3331757959.3315854</v>
       </c>
       <c r="I13" s="322">
         <f t="shared" si="7"/>
-        <v>3252252693.9602156</v>
+        <v>3253092027.7477756</v>
       </c>
       <c r="J13" s="322">
         <f t="shared" si="7"/>
-        <v>2917646554.3216343</v>
+        <v>2918106981.7778282</v>
       </c>
       <c r="K13" s="322">
         <f t="shared" si="7"/>
-        <v>1708844715.7702808</v>
+        <v>1709412326.5621972</v>
       </c>
       <c r="L13" s="322">
         <f t="shared" si="7"/>
-        <v>565883983.22336733</v>
+        <v>565993594.42123342</v>
       </c>
       <c r="M13" s="322">
         <f t="shared" si="7"/>
-        <v>489257189.78214574</v>
+        <v>489341609.8636201</v>
       </c>
       <c r="N13" s="322">
         <f t="shared" si="7"/>
@@ -10390,7 +10390,7 @@
       </c>
       <c r="C14" s="321">
         <f>-SUM(C8+C11,C12)*C43</f>
-        <v>-788592925.42348135</v>
+        <v>-747280315.12871861</v>
       </c>
       <c r="E14" s="270"/>
       <c r="G14" s="321">
@@ -10502,38 +10502,38 @@
       </c>
       <c r="C16" s="325">
         <f>SUM(C13:C15)</f>
-        <v>2223899071.9721813</v>
+        <v>2099961241.0878935</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="278"/>
       <c r="F16" s="61"/>
       <c r="G16" s="322">
         <f>IF(G$4="","",SUM(G13:G15))</f>
-        <v>2322754575.9970183</v>
+        <v>2323278784.8162661</v>
       </c>
       <c r="H16" s="322">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
-        <v>2666725242.4262524</v>
+        <v>2667635962.3315854</v>
       </c>
       <c r="I16" s="322">
         <f t="shared" si="8"/>
-        <v>2540373514.9602156</v>
+        <v>2541212848.7477756</v>
       </c>
       <c r="J16" s="322">
         <f t="shared" si="8"/>
-        <v>2375722735.3216343</v>
+        <v>2376183162.7778282</v>
       </c>
       <c r="K16" s="322">
         <f t="shared" si="8"/>
-        <v>1330376999.7702808</v>
+        <v>1330944610.5621972</v>
       </c>
       <c r="L16" s="322">
         <f t="shared" si="8"/>
-        <v>467103296.22336733</v>
+        <v>467212907.42123342</v>
       </c>
       <c r="M16" s="322">
         <f t="shared" si="8"/>
-        <v>428239183.78214574</v>
+        <v>428323603.8636201</v>
       </c>
       <c r="N16" s="322">
         <f t="shared" si="8"/>
@@ -10610,38 +10610,38 @@
       </c>
       <c r="C19" s="322">
         <f>C16+C17</f>
-        <v>2223899071.9721813</v>
+        <v>2099961241.0878935</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="267"/>
       <c r="F19" s="27"/>
       <c r="G19" s="327">
         <f>IF(G$4="","",G16+G17)</f>
-        <v>2322754575.9970183</v>
+        <v>2323278784.8162661</v>
       </c>
       <c r="H19" s="327">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
-        <v>2666725242.4262524</v>
+        <v>2667635962.3315854</v>
       </c>
       <c r="I19" s="327">
         <f t="shared" si="9"/>
-        <v>2540373514.9602156</v>
+        <v>2541212848.7477756</v>
       </c>
       <c r="J19" s="327">
         <f t="shared" si="9"/>
-        <v>2375722735.3216343</v>
+        <v>2376183162.7778282</v>
       </c>
       <c r="K19" s="327">
         <f t="shared" si="9"/>
-        <v>1330376999.7702808</v>
+        <v>1330944610.5621972</v>
       </c>
       <c r="L19" s="327">
         <f t="shared" si="9"/>
-        <v>467103296.22336733</v>
+        <v>467212907.42123342</v>
       </c>
       <c r="M19" s="327">
         <f t="shared" si="9"/>
-        <v>428239183.78214574</v>
+        <v>428323603.8636201</v>
       </c>
       <c r="N19" s="327">
         <f t="shared" si="9"/>
@@ -10730,7 +10730,7 @@
       </c>
       <c r="C23" s="330">
         <f>-C4*C28</f>
-        <v>-8039212664.4388895</v>
+        <v>-8199195071.4115868</v>
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="269"/>
@@ -10787,7 +10787,7 @@
       </c>
       <c r="C24" s="321">
         <f>-C4*C29</f>
-        <v>-2395279521.3642035</v>
+        <v>-2428555749.1398058</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="267"/>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="C25" s="322">
         <f>C23+C24</f>
-        <v>-10434492185.803093</v>
+        <v>-10627750820.551392</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="275"/>
@@ -10911,8 +10911,8 @@
         <v>43</v>
       </c>
       <c r="C28" s="63">
-        <f>AVERAGE(G28:J28)</f>
-        <v>0.56796376590325659</v>
+        <f>G28</f>
+        <v>0.57926639143826886</v>
       </c>
       <c r="D28" s="26"/>
       <c r="E28" s="268" t="s">
@@ -10971,8 +10971,8 @@
         <v>Selling Expenses</v>
       </c>
       <c r="C29" s="63">
-        <f>AVERAGE(G29:J29)</f>
-        <v>0.1692245290838959</v>
+        <f>G29</f>
+        <v>0.17157546722067235</v>
       </c>
       <c r="D29" s="26"/>
       <c r="E29" s="268" t="s">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="C30" s="71">
         <f>ABS(C25/$C$4)</f>
-        <v>0.73718829498715255</v>
+        <v>0.75084185865894115</v>
       </c>
       <c r="E30" s="270"/>
       <c r="G30" s="30">
@@ -11153,8 +11153,8 @@
         <v>49</v>
       </c>
       <c r="C34" s="331">
-        <f>AVERAGE(G34:J34)</f>
-        <v>-80699330.75</v>
+        <f>AVERAGE(G34:I34)</f>
+        <v>-53215346</v>
       </c>
       <c r="D34" s="58"/>
       <c r="E34" s="268" t="s">
@@ -11213,7 +11213,7 @@
       </c>
       <c r="C35" s="322">
         <f>C33+C34</f>
-        <v>-596464427.25</v>
+        <v>-568980442.5</v>
       </c>
       <c r="D35" s="58"/>
       <c r="E35" s="269"/>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C39" s="23">
         <f>ABS(C34/$C$4)</f>
-        <v>5.701341376549038E-3</v>
+        <v>3.7596204478706082E-3</v>
       </c>
       <c r="D39" s="27"/>
       <c r="E39" s="267"/>
@@ -11397,7 +11397,7 @@
       </c>
       <c r="C40" s="71">
         <f>ABS(C35/$C$4)</f>
-        <v>4.2139721446451381E-2</v>
+        <v>4.0198000517772954E-2</v>
       </c>
       <c r="E40" s="270"/>
       <c r="G40" s="30">
@@ -11471,31 +11471,31 @@
       <c r="F43" s="27"/>
       <c r="G43" s="6">
         <f t="shared" ref="G43:Q43" si="18">IF(G$4="","",-G14/SUM(G8+G11,G12))</f>
-        <v>0.2135436098740309</v>
+        <v>0.21350796675618908</v>
       </c>
       <c r="H43" s="6">
         <f t="shared" si="18"/>
-        <v>0.19938530627853016</v>
+        <v>0.1993308052705112</v>
       </c>
       <c r="I43" s="6">
         <f t="shared" si="18"/>
-        <v>0.21888802808036303</v>
+        <v>0.21883155254382944</v>
       </c>
       <c r="J43" s="6">
         <f t="shared" si="18"/>
-        <v>0.18574005072591793</v>
+        <v>0.18571074411735178</v>
       </c>
       <c r="K43" s="6">
         <f t="shared" si="18"/>
-        <v>0.22147577981033897</v>
+        <v>0.221402238722086</v>
       </c>
       <c r="L43" s="6">
         <f t="shared" si="18"/>
-        <v>0.1745599626929342</v>
+        <v>0.17452615713965794</v>
       </c>
       <c r="M43" s="6">
         <f t="shared" si="18"/>
-        <v>0.12471560413280758</v>
+        <v>0.12469408848555873</v>
       </c>
       <c r="N43" s="6">
         <f t="shared" si="18"/>
@@ -11609,36 +11609,36 @@
       </c>
       <c r="C48" s="321">
         <f>BS!D75*C53</f>
-        <v>38554805.997018404</v>
+        <v>39079014.816265978</v>
       </c>
       <c r="E48" s="270"/>
       <c r="G48" s="330">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
-        <v>38554805.997018404</v>
+        <v>39079014.816265978</v>
       </c>
       <c r="H48" s="330">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
-        <v>66982141.426252395</v>
+        <v>67892861.331585214</v>
       </c>
       <c r="I48" s="330">
         <f t="shared" si="19"/>
-        <v>61731794.960215338</v>
+        <v>62571128.747775584</v>
       </c>
       <c r="J48" s="330">
         <f t="shared" si="19"/>
-        <v>33863778.321634412</v>
+        <v>34324205.77782803</v>
       </c>
       <c r="K48" s="330">
         <f t="shared" si="19"/>
-        <v>41746958.77028092</v>
+        <v>42314569.562197201</v>
       </c>
       <c r="L48" s="330">
         <f t="shared" si="19"/>
-        <v>8061746.2233673697</v>
+        <v>8171357.4212333849</v>
       </c>
       <c r="M48" s="330">
         <f t="shared" si="19"/>
-        <v>6208975.7821457442</v>
+        <v>6293395.8636200782</v>
       </c>
       <c r="N48" s="330">
         <f t="shared" si="19"/>
@@ -11721,36 +11721,36 @@
       </c>
       <c r="C50" s="322">
         <f>C47+C48</f>
-        <v>30881944.997018404</v>
+        <v>31406153.816265978</v>
       </c>
       <c r="E50" s="270"/>
       <c r="G50" s="322">
         <f>IF(G$4="","",(G47+G48))</f>
-        <v>30881944.997018404</v>
+        <v>31406153.816265978</v>
       </c>
       <c r="H50" s="322">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
-        <v>61060472.426252395</v>
+        <v>61971192.331585214</v>
       </c>
       <c r="I50" s="322">
         <f t="shared" si="20"/>
-        <v>58034950.960215338</v>
+        <v>58874284.747775584</v>
       </c>
       <c r="J50" s="322">
         <f t="shared" si="20"/>
-        <v>19677003.321634412</v>
+        <v>20137430.77782803</v>
       </c>
       <c r="K50" s="322">
         <f t="shared" si="20"/>
-        <v>5923283.77028092</v>
+        <v>6490894.562197201</v>
       </c>
       <c r="L50" s="322">
         <f t="shared" si="20"/>
-        <v>-2708899.7766326303</v>
+        <v>-2599288.5787666151</v>
       </c>
       <c r="M50" s="322">
         <f t="shared" si="20"/>
-        <v>-6124799.2178542558</v>
+        <v>-6040379.1363799218</v>
       </c>
       <c r="N50" s="322">
         <f t="shared" si="20"/>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="C55" s="42">
         <f>-C8/C47</f>
-        <v>407.08280219033122</v>
+        <v>385.47747791842033</v>
       </c>
       <c r="E55" s="270"/>
       <c r="G55" s="42">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="C73" s="77">
         <f>ABS(C5/C$4)</f>
-        <v>0.73718829498715255</v>
+        <v>0.75084185865894115</v>
       </c>
       <c r="D73" s="27"/>
       <c r="E73" s="267"/>
@@ -12464,7 +12464,7 @@
       </c>
       <c r="C74" s="78">
         <f>ABS(C6/C$4)</f>
-        <v>0.26281170501284751</v>
+        <v>0.2491581413410589</v>
       </c>
       <c r="D74" s="27"/>
       <c r="E74" s="267"/>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="C75" s="77">
         <f>ABS(C7/C$4)</f>
-        <v>4.2139721446451381E-2</v>
+        <v>4.0198000517772954E-2</v>
       </c>
       <c r="D75" s="27"/>
       <c r="E75" s="267"/>
@@ -12578,7 +12578,7 @@
       </c>
       <c r="C76" s="78">
         <f>ABS(C8/C$4)</f>
-        <v>0.22067198356639611</v>
+        <v>0.20896014082328593</v>
       </c>
       <c r="D76" s="27"/>
       <c r="E76" s="267"/>
@@ -12808,38 +12808,38 @@
       </c>
       <c r="C80" s="77">
         <f>ABS(C12/C$4)</f>
-        <v>2.1817840267505887E-3</v>
+        <v>2.2188189488912299E-3</v>
       </c>
       <c r="D80" s="27"/>
       <c r="E80" s="267"/>
       <c r="F80" s="27"/>
       <c r="G80" s="6">
         <f t="shared" ref="G80:Q80" si="31">IF(G$4="","",ABS(G12/G$4))</f>
-        <v>2.1087601947286307E-3</v>
+        <v>2.1445555661620589E-3</v>
       </c>
       <c r="H80" s="6">
         <f t="shared" si="31"/>
-        <v>4.1215758808539147E-3</v>
+        <v>4.1830493848554898E-3</v>
       </c>
       <c r="I80" s="6">
         <f t="shared" si="31"/>
-        <v>4.1338260117560113E-3</v>
+        <v>4.1936117061721371E-3</v>
       </c>
       <c r="J80" s="6">
         <f t="shared" si="31"/>
-        <v>1.4998503953132702E-3</v>
+        <v>1.5349457953036647E-3</v>
       </c>
       <c r="K80" s="6">
         <f t="shared" si="31"/>
-        <v>5.4135290086463315E-4</v>
+        <v>5.9322915070896193E-4</v>
       </c>
       <c r="L80" s="6">
         <f t="shared" si="31"/>
-        <v>7.5626952918153914E-4</v>
+        <v>7.2566831989420212E-4</v>
       </c>
       <c r="M80" s="6">
         <f t="shared" si="31"/>
-        <v>1.7664279843384704E-3</v>
+        <v>1.7420807381590862E-3</v>
       </c>
       <c r="N80" s="6">
         <f t="shared" si="31"/>
@@ -12865,38 +12865,38 @@
       </c>
       <c r="C81" s="78">
         <f>C13/C4</f>
-        <v>0.22285376759314668</v>
+        <v>0.21117895977217718</v>
       </c>
       <c r="D81" s="27"/>
       <c r="E81" s="267"/>
       <c r="F81" s="27"/>
       <c r="G81" s="65">
         <f t="shared" ref="G81:Q81" si="32">IF(G$4="","",G13/G$4)</f>
-        <v>0.21441999007930274</v>
+        <v>0.21445578545073618</v>
       </c>
       <c r="H81" s="65">
         <f t="shared" si="32"/>
-        <v>0.22483186092948915</v>
+        <v>0.22489333443349074</v>
       </c>
       <c r="I81" s="65">
         <f t="shared" si="32"/>
-        <v>0.23165776072271912</v>
+        <v>0.23171754641713521</v>
       </c>
       <c r="J81" s="65">
         <f t="shared" si="32"/>
-        <v>0.22239328145421189</v>
+        <v>0.2224283768542023</v>
       </c>
       <c r="K81" s="65">
         <f t="shared" si="32"/>
-        <v>0.15617824164543909</v>
+        <v>0.15623011789528343</v>
       </c>
       <c r="L81" s="65">
         <f t="shared" si="32"/>
-        <v>0.15798325846358852</v>
+        <v>0.15801385967287587</v>
       </c>
       <c r="M81" s="65">
         <f t="shared" si="32"/>
-        <v>0.14110464046734167</v>
+        <v>0.14112898771352106</v>
       </c>
       <c r="N81" s="65">
         <f t="shared" si="32"/>
@@ -12922,7 +12922,7 @@
       </c>
       <c r="C82" s="77">
         <f>ABS(C14/C$4)</f>
-        <v>5.571344189828667E-2</v>
+        <v>5.2794739943044296E-2</v>
       </c>
       <c r="D82" s="27"/>
       <c r="E82" s="267"/>
@@ -13037,38 +13037,38 @@
       </c>
       <c r="C84" s="78">
         <f>ABS(C16/C$4)</f>
-        <v>0.15711664122200919</v>
+        <v>0.14836053535628208</v>
       </c>
       <c r="D84" s="27"/>
       <c r="E84" s="267"/>
       <c r="F84" s="27"/>
       <c r="G84" s="65">
         <f t="shared" ref="G84:Q84" si="35">IF(G$4="","",ABS(G16/G$4))</f>
-        <v>0.15860828689576373</v>
+        <v>0.15864408226719717</v>
       </c>
       <c r="H84" s="65">
         <f t="shared" si="35"/>
-        <v>0.18000369147689105</v>
+        <v>0.18006516498089264</v>
       </c>
       <c r="I84" s="65">
         <f t="shared" si="35"/>
-        <v>0.18095065028861054</v>
+        <v>0.18101043598302666</v>
       </c>
       <c r="J84" s="65">
         <f t="shared" si="35"/>
-        <v>0.18108594207580322</v>
+        <v>0.18112103747579367</v>
       </c>
       <c r="K84" s="65">
         <f t="shared" si="35"/>
-        <v>0.12158854378760792</v>
+        <v>0.12164042003745225</v>
       </c>
       <c r="L84" s="65">
         <f t="shared" si="35"/>
-        <v>0.13040570676007632</v>
+        <v>0.13043630796936367</v>
       </c>
       <c r="M84" s="65">
         <f t="shared" si="35"/>
-        <v>0.12350668998551453</v>
+        <v>0.12353103723169394</v>
       </c>
       <c r="N84" s="65">
         <f t="shared" si="35"/>
@@ -13144,38 +13144,38 @@
       </c>
       <c r="C87" s="78">
         <f>ABS(C19/C$4)</f>
-        <v>0.15711664122200919</v>
+        <v>0.14836053535628208</v>
       </c>
       <c r="D87" s="75"/>
       <c r="E87" s="267"/>
       <c r="F87" s="75"/>
       <c r="G87" s="65">
         <f t="shared" ref="G87:Q87" si="36">IF(G$4="","",ABS(G19/G$4))</f>
-        <v>0.15860828689576373</v>
+        <v>0.15864408226719717</v>
       </c>
       <c r="H87" s="65">
         <f t="shared" si="36"/>
-        <v>0.18000369147689105</v>
+        <v>0.18006516498089264</v>
       </c>
       <c r="I87" s="65">
         <f t="shared" si="36"/>
-        <v>0.18095065028861054</v>
+        <v>0.18101043598302666</v>
       </c>
       <c r="J87" s="65">
         <f t="shared" si="36"/>
-        <v>0.18108594207580322</v>
+        <v>0.18112103747579367</v>
       </c>
       <c r="K87" s="65">
         <f t="shared" si="36"/>
-        <v>0.12158854378760792</v>
+        <v>0.12164042003745225</v>
       </c>
       <c r="L87" s="65">
         <f t="shared" si="36"/>
-        <v>0.13040570676007632</v>
+        <v>0.13043630796936367</v>
       </c>
       <c r="M87" s="65">
         <f t="shared" si="36"/>
-        <v>0.12350668998551453</v>
+        <v>0.12353103723169394</v>
       </c>
       <c r="N87" s="65">
         <f t="shared" si="36"/>
@@ -13324,12 +13324,12 @@
       </c>
       <c r="C92" s="23">
         <f>C90/(C19*scaling_factor/Common_Shares)</f>
-        <v>0.52229477939839231</v>
+        <v>0.55312014930250053</v>
       </c>
       <c r="E92" s="270"/>
       <c r="G92" s="170">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",G90/(G19*scaling_factor/Common_Shares))</f>
-        <v>0.50006612287112806</v>
+        <v>0.49995329135321925</v>
       </c>
       <c r="H92" s="170">
         <f t="shared" si="38"/>
@@ -13516,38 +13516,38 @@
       </c>
       <c r="C97" s="77">
         <f>C13/G13-1</f>
-        <v>4.5467350067964762E-3</v>
+        <v>-4.8238097390936763E-2</v>
       </c>
       <c r="D97" s="27"/>
       <c r="E97" s="267"/>
       <c r="F97" s="27"/>
       <c r="G97" s="6">
         <f t="shared" ref="G97:Q97" si="41">IF(H5="","",G13/H13-1)</f>
-        <v>-5.726852710966468E-2</v>
+        <v>-5.7368881187775611E-2</v>
       </c>
       <c r="H97" s="6">
         <f t="shared" si="41"/>
-        <v>2.4166186597983419E-2</v>
+        <v>2.4181895535944298E-2</v>
       </c>
       <c r="I97" s="6">
         <f t="shared" si="41"/>
-        <v>0.11468357575490451</v>
+        <v>0.11479532726584996</v>
       </c>
       <c r="J97" s="6">
         <f t="shared" si="41"/>
-        <v>0.70737956901278332</v>
+        <v>0.70708198158746138</v>
       </c>
       <c r="K97" s="6">
         <f t="shared" si="41"/>
-        <v>2.0197792594100701</v>
+        <v>2.0201973015439978</v>
       </c>
       <c r="L97" s="6">
         <f t="shared" si="41"/>
-        <v>0.15661863543659238</v>
+        <v>0.15664309556462253</v>
       </c>
       <c r="M97" s="6">
         <f t="shared" si="41"/>
-        <v>0.3453621204922479</v>
+        <v>0.34559425929816934</v>
       </c>
       <c r="N97" s="6">
         <f t="shared" si="41"/>
@@ -14127,31 +14127,31 @@
       <c r="E114" s="270"/>
       <c r="G114" s="297">
         <f>IF(G$4="","",Data!C$22/G19)</f>
-        <v>1.0944103829432141</v>
+        <v>1.0941634476299129</v>
       </c>
       <c r="H114" s="297">
         <f>IF(H$4="","",Data!D$22/H19)</f>
-        <v>1.1613302966984029</v>
+        <v>1.1609338233291711</v>
       </c>
       <c r="I114" s="297">
         <f>IF(I$4="","",Data!E$22/I19)</f>
-        <v>1.477203347027797</v>
+        <v>1.4767154435131946</v>
       </c>
       <c r="J114" s="297">
         <f>IF(J$4="","",Data!F$22/J19)</f>
-        <v>1.5005063764384885</v>
+        <v>1.5002156268259466</v>
       </c>
       <c r="K114" s="297">
         <f>IF(K$4="","",Data!G$22/K19)</f>
-        <v>2.773447584133756</v>
+        <v>2.7722647860164824</v>
       </c>
       <c r="L114" s="297">
         <f>IF(L$4="","",Data!H$22/L19)</f>
-        <v>1.5109716987792317</v>
+        <v>1.5106172149556596</v>
       </c>
       <c r="M114" s="297">
         <f>IF(M$4="","",Data!I$22/M19)</f>
-        <v>1.7382339197122179</v>
+        <v>1.7378913239556451</v>
       </c>
       <c r="N114" s="297">
         <f>IF(N$4="","",Data!J$22/N19)</f>
@@ -14235,36 +14235,36 @@
       </c>
       <c r="C117" s="23">
         <f>C81</f>
-        <v>0.22285376759314668</v>
+        <v>0.21117895977217718</v>
       </c>
       <c r="E117" s="270"/>
       <c r="G117" s="23">
         <f t="shared" ref="G117:Q117" si="45">G81</f>
-        <v>0.21441999007930274</v>
+        <v>0.21445578545073618</v>
       </c>
       <c r="H117" s="23">
         <f t="shared" si="45"/>
-        <v>0.22483186092948915</v>
+        <v>0.22489333443349074</v>
       </c>
       <c r="I117" s="23">
         <f t="shared" si="45"/>
-        <v>0.23165776072271912</v>
+        <v>0.23171754641713521</v>
       </c>
       <c r="J117" s="23">
         <f t="shared" si="45"/>
-        <v>0.22239328145421189</v>
+        <v>0.2224283768542023</v>
       </c>
       <c r="K117" s="23">
         <f t="shared" si="45"/>
-        <v>0.15617824164543909</v>
+        <v>0.15623011789528343</v>
       </c>
       <c r="L117" s="23">
         <f t="shared" si="45"/>
-        <v>0.15798325846358852</v>
+        <v>0.15801385967287587</v>
       </c>
       <c r="M117" s="23">
         <f t="shared" si="45"/>
-        <v>0.14110464046734167</v>
+        <v>0.14112898771352106</v>
       </c>
       <c r="N117" s="23">
         <f t="shared" si="45"/>
@@ -14400,7 +14400,7 @@
       </c>
       <c r="C120" s="102">
         <f>C8/C105</f>
-        <v>1.2729930668709819</v>
+        <v>1.205430821898563</v>
       </c>
       <c r="D120" s="103"/>
       <c r="E120" s="273"/>
@@ -14521,38 +14521,38 @@
       </c>
       <c r="C124" s="177">
         <f>C16*$C$3/Common_Shares*Exchange_Rate</f>
-        <v>4.5951062401283256</v>
+        <v>4.3390211024249705</v>
       </c>
       <c r="D124" s="27"/>
       <c r="E124" s="267"/>
       <c r="F124" s="27"/>
       <c r="G124" s="177">
         <f t="shared" ref="G124:Q124" si="49">IF(G$4="","",G16*$C$3/Common_Shares*Exchange_Rate)</f>
-        <v>4.7993653043729649</v>
+        <v>4.8004484449016038</v>
       </c>
       <c r="H124" s="177">
         <f t="shared" si="49"/>
-        <v>5.5100907935150563</v>
+        <v>5.5119725581925749</v>
       </c>
       <c r="I124" s="177">
         <f t="shared" si="49"/>
-        <v>5.2490179693714243</v>
+        <v>5.2507522332925598</v>
       </c>
       <c r="J124" s="177">
         <f t="shared" si="49"/>
-        <v>4.9088101629585701</v>
+        <v>4.9097615159690315</v>
       </c>
       <c r="K124" s="177">
         <f t="shared" si="49"/>
-        <v>2.7488763903059388</v>
+        <v>2.7500492096684588</v>
       </c>
       <c r="L124" s="177">
         <f t="shared" si="49"/>
-        <v>0.96514688922328662</v>
+        <v>0.96537337211796936</v>
       </c>
       <c r="M124" s="177">
         <f t="shared" si="49"/>
-        <v>0.88484435758126612</v>
+        <v>0.88501878961735259</v>
       </c>
       <c r="N124" s="177">
         <f t="shared" si="49"/>
@@ -14578,38 +14578,38 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.9362802074755184E-2</v>
+        <v>7.4939915413211919E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="267"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>8.2890592476217009E-2</v>
+        <v>8.2909299566521655E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>9.5165644102159871E-2</v>
+        <v>9.5198144355657599E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.0656614324204216E-2</v>
+        <v>9.0686567068956128E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>8.4780831830027117E-2</v>
+        <v>8.4797262797392609E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.7476276171087024E-2</v>
+        <v>4.7496532118626235E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6669203613528267E-2</v>
+        <v>1.6673115235198089E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.5282285968588362E-2</v>
+        <v>1.5285298611698663E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
@@ -15421,7 +15421,7 @@
       </c>
       <c r="C4" s="343">
         <f>Normalized_FCF!C19</f>
-        <v>2223899071.9721813</v>
+        <v>2099961241.0878935</v>
       </c>
       <c r="D4" t="str">
         <f>Reporting_currency</f>
@@ -15453,7 +15453,7 @@
       </c>
       <c r="C6" s="344">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
-        <v>37064984532.86969</v>
+        <v>34999354018.131561</v>
       </c>
       <c r="D6" t="str">
         <f>Reporting_currency</f>
@@ -15487,7 +15487,7 @@
       </c>
       <c r="C8" s="343">
         <f>BS!D66</f>
-        <v>65618450.04890883</v>
+        <v>51803895.882383943</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -15519,7 +15519,7 @@
       </c>
       <c r="C10" s="344">
         <f>C6-C7+C8+C9</f>
-        <v>37036639279.300606</v>
+        <v>34957194210.39595</v>
       </c>
       <c r="D10" t="str">
         <f>Reporting_currency</f>
@@ -15547,7 +15547,7 @@
       </c>
       <c r="C12" s="111">
         <f>(C10*scaling_factor)/Common_Shares*Exchange_Rate</f>
-        <v>76.526535943365388</v>
+        <v>72.229906149076143</v>
       </c>
       <c r="D12" t="str">
         <f>Market_currency</f>
@@ -15600,7 +15600,7 @@
       </c>
       <c r="C18" s="140">
         <f>(F52-C7+C8+C9)*Exchange_Rate/Common_Shares*scaling_factor</f>
-        <v>87.56668023434645</v>
+        <v>82.654783518406717</v>
       </c>
       <c r="D18" t="str">
         <f>Market_currency</f>
@@ -15635,7 +15635,7 @@
       </c>
       <c r="C21" s="123">
         <f>C4*(1+D21)</f>
-        <v>2327476884.1218534</v>
+        <v>2197766664.7657332</v>
       </c>
       <c r="D21" s="138">
         <f>IF($C$17&lt;B21,0,DCF!$C$16)</f>
@@ -15647,7 +15647,7 @@
       </c>
       <c r="F21" s="125">
         <f t="shared" ref="F21:F51" si="1">C21*E21</f>
-        <v>2195732909.5489182</v>
+        <v>2073364778.0808802</v>
       </c>
       <c r="H21" s="120"/>
     </row>
@@ -15657,7 +15657,7 @@
       </c>
       <c r="C22" s="123">
         <f t="shared" ref="C22:C50" si="2">IF(ROW()-ROW($C$21)&lt;$C$17, $C$21*(1+D22)^(ROW()-ROW($C$21)), 0)</f>
-        <v>2435878819.4994731</v>
+        <v>2300127363.423718</v>
       </c>
       <c r="D22" s="138">
         <f>IF($C$17&lt;B22,0,DCF!$C$16)</f>
@@ -15669,7 +15669,7 @@
       </c>
       <c r="F22" s="125">
         <f t="shared" si="1"/>
-        <v>2167923477.6606202</v>
+        <v>2047105165.0264487</v>
       </c>
       <c r="H22" s="120"/>
     </row>
@@ -15679,7 +15679,7 @@
       </c>
       <c r="C23" s="123">
         <f t="shared" si="2"/>
-        <v>2549329561.0215406</v>
+        <v>2407255498.4059167</v>
       </c>
       <c r="D23" s="138">
         <f>IF($C$17&lt;B23,0,DCF!$C$16)</f>
@@ -15691,7 +15691,7 @@
       </c>
       <c r="F23" s="125">
         <f t="shared" si="1"/>
-        <v>2140466258.2379582</v>
+        <v>2021178135.6471417</v>
       </c>
       <c r="H23" s="120"/>
     </row>
@@ -15701,7 +15701,7 @@
       </c>
       <c r="C24" s="123">
         <f t="shared" si="2"/>
-        <v>2668064256.1823821</v>
+        <v>2519373112.4436064</v>
       </c>
       <c r="D24" s="138">
         <f>IF($C$17&lt;B24,0,DCF!$C$16)</f>
@@ -15713,7 +15713,7 @@
       </c>
       <c r="F24" s="125">
         <f t="shared" si="1"/>
-        <v>2113356790.4339273</v>
+        <v>1995579477.6988294</v>
       </c>
       <c r="H24" s="120"/>
     </row>
@@ -15723,7 +15723,7 @@
       </c>
       <c r="C25" s="123">
         <f t="shared" si="2"/>
-        <v>2792329004.4405127</v>
+        <v>2636712589.8796053</v>
       </c>
       <c r="D25" s="138">
         <f>IF($C$17&lt;B25,0,DCF!$C$16)</f>
@@ -15735,7 +15735,7 @@
       </c>
       <c r="F25" s="125">
         <f t="shared" si="1"/>
-        <v>2086590669.8991132</v>
+        <v>1970305032.2863626</v>
       </c>
       <c r="H25" s="120"/>
     </row>
@@ -15745,7 +15745,7 @@
       </c>
       <c r="C26" s="123">
         <f t="shared" si="2"/>
-        <v>2922381367.3049536</v>
+        <v>2759517138.3274951</v>
       </c>
       <c r="D26" s="138">
         <f>IF($C$17&lt;B26,0,DCF!$C$16)</f>
@@ -15757,7 +15757,7 @@
       </c>
       <c r="F26" s="125">
         <f t="shared" si="1"/>
-        <v>2060163548.0661402</v>
+        <v>1945350693.1878998</v>
       </c>
       <c r="H26" s="120"/>
     </row>
@@ -15767,7 +15767,7 @@
       </c>
       <c r="C27" s="123">
         <f t="shared" si="2"/>
-        <v>3058490902.1787567</v>
+        <v>2888041292.7640605</v>
       </c>
       <c r="D27" s="138">
         <f>IF($C$17&lt;B27,0,DCF!$C$16)</f>
@@ -15779,7 +15779,7 @@
       </c>
       <c r="F27" s="125">
         <f t="shared" si="1"/>
-        <v>2034071131.4431784</v>
+        <v>1920712406.1877859</v>
       </c>
       <c r="H27" s="120"/>
     </row>
@@ -15789,7 +15789,7 @@
       </c>
       <c r="C28" s="123">
         <f t="shared" si="2"/>
-        <v>3200939721.066215</v>
+        <v>3022551443.0997648</v>
       </c>
       <c r="D28" s="138">
         <f>IF($C$17&lt;B28,0,DCF!$C$16)</f>
@@ -15801,7 +15801,7 @@
       </c>
       <c r="F28" s="125">
         <f t="shared" si="1"/>
-        <v>2008309180.9163985</v>
+        <v>1896386168.4178832</v>
       </c>
       <c r="H28" s="120"/>
     </row>
@@ -15811,7 +15811,7 @@
       </c>
       <c r="C29" s="123">
         <f t="shared" si="2"/>
-        <v>3350023075.3018012</v>
+        <v>3163326386.3207598</v>
       </c>
       <c r="D29" s="138">
         <f>IF($C$17&lt;B29,0,DCF!$C$16)</f>
@@ -15823,7 +15823,7 @@
       </c>
       <c r="F29" s="125">
         <f t="shared" si="1"/>
-        <v>1982873511.0612652</v>
+        <v>1872368027.7072439</v>
       </c>
       <c r="H29" s="120"/>
     </row>
@@ -15833,7 +15833,7 @@
       </c>
       <c r="C30" s="123">
         <f t="shared" si="2"/>
-        <v>3506049967.5127697</v>
+        <v>3310657904.3468313</v>
       </c>
       <c r="D30" s="138">
         <f>IF($C$17&lt;B30,0,DCF!$C$16)</f>
@@ -15845,7 +15845,7 @@
       </c>
       <c r="F30" s="125">
         <f t="shared" si="1"/>
-        <v>1957759989.4625492</v>
+        <v>1848654081.9400206</v>
       </c>
       <c r="H30" s="120"/>
     </row>
@@ -16295,7 +16295,7 @@
       </c>
       <c r="C51" s="123">
         <f>C$21*(1+Terminal_Growth)^$C$17/Equity_Cost</f>
-        <v>38791281402.030891</v>
+        <v>36629444412.762222</v>
       </c>
       <c r="D51" s="139">
         <f>Terminal_Growth</f>
@@ -16307,7 +16307,7 @@
       </c>
       <c r="F51" s="125">
         <f t="shared" si="1"/>
-        <v>21660848924.738598</v>
+        <v>20453690441.389072</v>
       </c>
       <c r="H51" s="120"/>
     </row>
@@ -16318,7 +16318,7 @@
       </c>
       <c r="F52" s="137">
         <f>SUM(F21:F51)</f>
-        <v>42408096391.468658</v>
+        <v>40044694407.569565</v>
       </c>
       <c r="H52" s="120"/>
     </row>
@@ -16339,7 +16339,7 @@
     <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
-        <v>42408096391.468658</v>
+        <v>40044694407.569565</v>
       </c>
       <c r="B55" s="131">
         <f>C78</f>
@@ -16369,19 +16369,19 @@
       </c>
       <c r="B56" s="123">
         <f t="dataTable" ref="B56:F61" dt2D="1" dtr="1" r1="C16" r2="C17"/>
-        <v>37064984532.869675</v>
+        <v>34999354018.131546</v>
       </c>
       <c r="C56" s="123">
-        <v>38173310175.981728</v>
+        <v>36045912705.246384</v>
       </c>
       <c r="D56" s="123">
-        <v>39310698802.635216</v>
+        <v>37119914696.671471</v>
       </c>
       <c r="E56" s="123">
-        <v>40478434736.362221</v>
+        <v>38222572740.625626</v>
       </c>
       <c r="F56" s="123">
-        <v>42910286195.588173</v>
+        <v>40518897188.447235</v>
       </c>
       <c r="H56" s="120"/>
     </row>
@@ -16390,19 +16390,19 @@
         <v>10</v>
       </c>
       <c r="B57" s="123">
-        <v>37064984532.869675</v>
+        <v>34999354018.131546</v>
       </c>
       <c r="C57" s="123">
-        <v>39219279015.246628</v>
+        <v>37033589731.386833</v>
       </c>
       <c r="D57" s="123">
-        <v>41581770062.759674</v>
+        <v>39264419221.231857</v>
       </c>
       <c r="E57" s="123">
-        <v>44177698115.491516</v>
+        <v>41715676278.75441</v>
       </c>
       <c r="F57" s="123">
-        <v>50185338735.237732</v>
+        <v>47388511260.723457</v>
       </c>
       <c r="H57" s="120"/>
     </row>
@@ -16411,19 +16411,19 @@
         <v>15</v>
       </c>
       <c r="B58" s="123">
-        <v>37064984532.869667</v>
+        <v>34999354018.131531</v>
       </c>
       <c r="C58" s="123">
-        <v>40637570756.500168</v>
+        <v>38372840114.96933</v>
       </c>
       <c r="D58" s="123">
-        <v>44825160379.998962</v>
+        <v>42327055490.009201</v>
       </c>
       <c r="E58" s="123">
-        <v>49752364483.188637</v>
+        <v>46979666651.203575</v>
       </c>
       <c r="F58" s="123">
-        <v>62453538589.876228</v>
+        <v>58973004692.709213</v>
       </c>
       <c r="H58" s="120"/>
     </row>
@@ -16432,19 +16432,19 @@
         <v>20</v>
       </c>
       <c r="B59" s="123">
-        <v>37064984532.869675</v>
+        <v>34999354018.131531</v>
       </c>
       <c r="C59" s="123">
-        <v>42222685575.703217</v>
+        <v>39869616531.197845</v>
       </c>
       <c r="D59" s="123">
-        <v>48654647368.914856</v>
+        <v>45943125279.92202</v>
       </c>
       <c r="E59" s="123">
-        <v>56728441061.510498</v>
+        <v>53566966683.819527</v>
       </c>
       <c r="F59" s="123">
-        <v>79842964471.028748</v>
+        <v>75393318373.045044</v>
       </c>
       <c r="H59" s="120"/>
     </row>
@@ -16453,19 +16453,19 @@
         <v>25</v>
       </c>
       <c r="B60" s="123">
-        <v>37064984532.869667</v>
+        <v>34999354018.131531</v>
       </c>
       <c r="C60" s="123">
-        <v>43840553023.070267</v>
+        <v>41397320272.571182</v>
       </c>
       <c r="D60" s="123">
-        <v>52794384965.462723</v>
+        <v>49852155420.087311</v>
       </c>
       <c r="E60" s="123">
-        <v>64751732873.259644</v>
+        <v>61143120675.227715</v>
       </c>
       <c r="F60" s="123">
-        <v>102732154410.18817</v>
+        <v>97006894419.689941</v>
       </c>
       <c r="H60" s="120"/>
     </row>
@@ -16474,19 +16474,19 @@
         <v>30</v>
       </c>
       <c r="B61" s="123">
-        <v>37064984532.869667</v>
+        <v>34999354018.131523</v>
       </c>
       <c r="C61" s="123">
-        <v>45407068563.261345</v>
+        <v>42876533947.068497</v>
       </c>
       <c r="D61" s="123">
-        <v>57049847355.856087</v>
+        <v>53870461014.688095</v>
       </c>
       <c r="E61" s="123">
-        <v>73557564826.937149</v>
+        <v>69458203869.114365</v>
       </c>
       <c r="F61" s="123">
-        <v>131744350750.47754</v>
+        <v>124402241898.03172</v>
       </c>
       <c r="H61" s="120"/>
     </row>
@@ -16536,23 +16536,23 @@
       </c>
       <c r="B65" s="124">
         <f>C12</f>
-        <v>76.526535943365388</v>
+        <v>72.229906149076143</v>
       </c>
       <c r="C65" s="124">
         <f>C12</f>
-        <v>76.526535943365388</v>
+        <v>72.229906149076143</v>
       </c>
       <c r="D65" s="124">
         <f>C12</f>
-        <v>76.526535943365388</v>
+        <v>72.229906149076143</v>
       </c>
       <c r="E65" s="141">
         <f>C12</f>
-        <v>76.526535943365388</v>
+        <v>72.229906149076143</v>
       </c>
       <c r="F65" s="124">
         <f>C12</f>
-        <v>76.526535943365388</v>
+        <v>72.229906149076143</v>
       </c>
       <c r="H65" s="120"/>
     </row>
@@ -16563,23 +16563,23 @@
       </c>
       <c r="B66" s="124">
         <f t="shared" ref="B66:F71" si="4">(B56-$C$7+$C$8+$C$9)/Common_Shares*$C$3*Exchange_Rate</f>
-        <v>76.52653594336536</v>
+        <v>72.229906149076115</v>
       </c>
       <c r="C66" s="124">
         <f t="shared" si="4"/>
-        <v>78.816601235870735</v>
+        <v>74.39234616914284</v>
       </c>
       <c r="D66" s="124">
         <f t="shared" si="4"/>
-        <v>81.166717588566357</v>
+        <v>76.611490605554295</v>
       </c>
       <c r="E66" s="124">
         <f t="shared" si="4"/>
-        <v>83.579538720387106</v>
+        <v>78.889845285565968</v>
       </c>
       <c r="F66" s="124">
         <f t="shared" si="4"/>
-        <v>88.604324222655677</v>
+        <v>83.634599637294173</v>
       </c>
       <c r="H66" s="120"/>
     </row>
@@ -16590,23 +16590,23 @@
       </c>
       <c r="B67" s="124">
         <f t="shared" si="4"/>
-        <v>76.52653594336536</v>
+        <v>72.229906149076115</v>
       </c>
       <c r="C67" s="124">
         <f t="shared" si="4"/>
-        <v>80.977822489505968</v>
+        <v>76.433122624894764</v>
       </c>
       <c r="D67" s="124">
         <f t="shared" si="4"/>
-        <v>85.859292827567373</v>
+        <v>81.042548762367147</v>
       </c>
       <c r="E67" s="124">
         <f t="shared" si="4"/>
-        <v>91.223099730662966</v>
+        <v>86.107430862071254</v>
       </c>
       <c r="F67" s="124">
         <f t="shared" si="4"/>
-        <v>103.63631903911077</v>
+        <v>97.828861817904809</v>
       </c>
       <c r="H67" s="120"/>
     </row>
@@ -16617,23 +16617,23 @@
       </c>
       <c r="B68" s="124">
         <f t="shared" si="4"/>
-        <v>76.526535943365332</v>
+        <v>72.229906149076086</v>
       </c>
       <c r="C68" s="124">
         <f t="shared" si="4"/>
-        <v>83.908351717514989</v>
+        <v>79.200333543885222</v>
       </c>
       <c r="D68" s="124">
         <f t="shared" si="4"/>
-        <v>92.560911292968882</v>
+        <v>87.370686224748425</v>
       </c>
       <c r="E68" s="124">
         <f t="shared" si="4"/>
-        <v>102.74169090041501</v>
+        <v>96.984091279473134</v>
       </c>
       <c r="F68" s="124">
         <f t="shared" si="4"/>
-        <v>128.98534787664605</v>
+        <v>121.7651900123478</v>
       </c>
       <c r="H68" s="120"/>
     </row>
@@ -16644,23 +16644,23 @@
       </c>
       <c r="B69" s="124">
         <f t="shared" si="4"/>
-        <v>76.52653594336536</v>
+        <v>72.229906149076086</v>
       </c>
       <c r="C69" s="124">
         <f t="shared" si="4"/>
-        <v>87.183577238689594</v>
+        <v>82.293030841604406</v>
       </c>
       <c r="D69" s="124">
         <f t="shared" si="4"/>
-        <v>100.47354536032901</v>
+        <v>94.842349424658138</v>
       </c>
       <c r="E69" s="124">
         <f t="shared" si="4"/>
-        <v>117.15593002693812</v>
+        <v>110.59502527686351</v>
       </c>
       <c r="F69" s="124">
         <f t="shared" si="4"/>
-        <v>164.91605192063443</v>
+        <v>155.69347696039841</v>
       </c>
       <c r="H69" s="120"/>
     </row>
@@ -16671,23 +16671,23 @@
       </c>
       <c r="B70" s="124">
         <f t="shared" si="4"/>
-        <v>76.526535943365332</v>
+        <v>72.229906149076086</v>
       </c>
       <c r="C70" s="124">
         <f t="shared" si="4"/>
-        <v>90.526477506418018</v>
+        <v>85.449631374211592</v>
       </c>
       <c r="D70" s="124">
         <f t="shared" si="4"/>
-        <v>109.02723122770136</v>
+        <v>102.91933862632813</v>
       </c>
       <c r="E70" s="124">
         <f t="shared" si="4"/>
-        <v>133.73396575490131</v>
+        <v>126.24916755375205</v>
       </c>
       <c r="F70" s="124">
         <f t="shared" si="4"/>
-        <v>212.21058108631306</v>
+        <v>200.35228338516606</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="13.15">
@@ -16697,23 +16697,23 @@
       </c>
       <c r="B71" s="124">
         <f t="shared" si="4"/>
-        <v>76.526535943365332</v>
+        <v>72.229906149076072</v>
       </c>
       <c r="C71" s="124">
         <f t="shared" si="4"/>
-        <v>93.763272478235905</v>
+        <v>88.506039855976894</v>
       </c>
       <c r="D71" s="124">
         <f t="shared" si="4"/>
-        <v>117.8200321381253</v>
+        <v>111.22211699662442</v>
       </c>
       <c r="E71" s="124">
         <f t="shared" si="4"/>
-        <v>151.92891617771031</v>
+        <v>143.43011391636313</v>
       </c>
       <c r="F71" s="124">
         <f t="shared" si="4"/>
-        <v>272.15670279806284</v>
+        <v>256.95760946976043</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="13.15">
@@ -16748,7 +16748,7 @@
       </c>
       <c r="E74" s="135">
         <f>INDEX(B$65:F$71, MATCH(D74, A$65:A$71, 0), MATCH(C74, B$64:F$64, 0))</f>
-        <v>128.98534787664605</v>
+        <v>121.7651900123478</v>
       </c>
       <c r="F74" s="142">
         <f>Scenarios!C58</f>
@@ -16770,7 +16770,7 @@
       </c>
       <c r="E75" s="135">
         <f>INDEX(B$65:F$71, MATCH(D75, A$65:A$71, 0), MATCH(C75, B$64:F$64, 0))</f>
-        <v>91.223099730662966</v>
+        <v>86.107430862071254</v>
       </c>
       <c r="F75" s="142">
         <f>Scenarios!C40*(1-F$74-F$78)</f>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="E76" s="135">
         <f>INDEX(B$65:F$71, MATCH(D76, A$65:A$71, 0), MATCH(C76, B$64:F$64, 0))</f>
-        <v>85.859292827567373</v>
+        <v>81.042548762367147</v>
       </c>
       <c r="F76" s="142">
         <f>Scenarios!C28*(1-F$74-F$78)</f>
@@ -16816,7 +16816,7 @@
       </c>
       <c r="E77" s="135">
         <f>INDEX(B$65:F$71, MATCH(D77, A$65:A$71, 0), MATCH(C77, B$64:F$64, 0))</f>
-        <v>80.977822489505968</v>
+        <v>76.433122624894764</v>
       </c>
       <c r="F77" s="142">
         <f>Scenarios!C34*(1-F$74-F$78)</f>
@@ -16839,7 +16839,7 @@
       </c>
       <c r="E78" s="135">
         <f>INDEX(B$65:F$71, MATCH(D78, A$65:A$71, 0), MATCH(C78, B$64:F$64, 0))</f>
-        <v>76.526535943365332</v>
+        <v>72.229906149076086</v>
       </c>
       <c r="F78" s="142">
         <f>Scenarios!C52</f>
@@ -18440,7 +18440,7 @@
       </c>
       <c r="I6" s="124">
         <f t="shared" si="0"/>
-        <v>90.035778317517341</v>
+        <v>85.120030767403335</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="12.75" customHeight="1">
@@ -18474,7 +18474,7 @@
       </c>
       <c r="C8" s="343">
         <f>Normalized_FCF!G19</f>
-        <v>2322754575.9970183</v>
+        <v>2323278784.8162661</v>
       </c>
       <c r="D8" t="str">
         <f>Reporting_currency</f>
@@ -18496,7 +18496,7 @@
       </c>
       <c r="C9" s="343">
         <f>Normalized_FCF!C19</f>
-        <v>2223899071.9721813</v>
+        <v>2099961241.0878935</v>
       </c>
       <c r="D9" t="str">
         <f>Reporting_currency</f>
@@ -18580,7 +18580,7 @@
       </c>
       <c r="C14" s="158">
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
-        <v>-7.4877931429291333E-3</v>
+        <v>-7.4772485650086429E-3</v>
       </c>
       <c r="E14" s="357"/>
       <c r="F14" s="357"/>
@@ -18646,7 +18646,7 @@
       </c>
       <c r="C22" s="160">
         <f>IF(valuation_method="DCF",DCF!C12,DDM!C7)</f>
-        <v>76.526535943365388</v>
+        <v>72.229906149076143</v>
       </c>
       <c r="D22" t="str">
         <f>Market_currency</f>
@@ -18693,7 +18693,7 @@
       </c>
       <c r="C27" s="160">
         <f>IF(valuation_method="DCF",DCF!E76,DDM!E71)</f>
-        <v>85.859292827567373</v>
+        <v>81.042548762367147</v>
       </c>
       <c r="D27" s="160" t="str">
         <f>Market_currency</f>
@@ -18751,7 +18751,7 @@
       </c>
       <c r="C33" s="160">
         <f>IF(valuation_method="DCF",DCF!E77,DDM!E72)</f>
-        <v>80.977822489505968</v>
+        <v>76.433122624894764</v>
       </c>
       <c r="D33" t="str">
         <f>Market_currency</f>
@@ -18809,7 +18809,7 @@
       </c>
       <c r="C39" s="160">
         <f>IF(valuation_method="DCF",DCF!E75,DDM!E70)</f>
-        <v>91.223099730662966</v>
+        <v>86.107430862071254</v>
       </c>
       <c r="D39" t="str">
         <f>Market_currency</f>
@@ -18836,7 +18836,7 @@
       </c>
       <c r="C42" s="154">
         <f>C27*C28+C33*C34+C39*C40</f>
-        <v>85.955760140574199</v>
+        <v>81.133639954813503</v>
       </c>
       <c r="D42" t="str">
         <f>Market_currency</f>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="C51" s="160">
         <f>IF(valuation_method="DCF",DCF!E78,DDM!E73)</f>
-        <v>76.526535943365332</v>
+        <v>72.229906149076086</v>
       </c>
       <c r="D51" t="str">
         <f>Market_currency</f>
@@ -18968,7 +18968,7 @@
       </c>
       <c r="C57" s="160">
         <f>IF(valuation_method="DCF",DCF!E74,DDM!E69)</f>
-        <v>128.98534787664605</v>
+        <v>121.7651900123478</v>
       </c>
       <c r="D57" t="str">
         <f>Market_currency</f>
@@ -18994,7 +18994,7 @@
       </c>
       <c r="C60" s="154">
         <f>C51*C52+C57*C58+C42*(1-C52-C58)</f>
-        <v>87.635778317517335</v>
+        <v>82.72003076740333</v>
       </c>
       <c r="D60" t="str">
         <f>Market_currency</f>
@@ -19056,7 +19056,7 @@
       </c>
       <c r="C66" s="160">
         <f>IF(valuation_method="DCF",DCF!C18,DDM!C13)</f>
-        <v>87.56668023434645</v>
+        <v>82.654783518406717</v>
       </c>
       <c r="D66" s="160" t="str">
         <f>Market_currency</f>
@@ -19119,7 +19119,7 @@
       </c>
       <c r="F72" s="293">
         <f>BS!D89/C60</f>
-        <v>-6.6831218821595498E-4</v>
+        <v>-1.0530971019379444E-3</v>
       </c>
     </row>
     <row r="74" spans="2:6" ht="13.9">
@@ -19191,7 +19191,7 @@
       </c>
       <c r="C82" s="116">
         <f>C60/(1+C80)^C76</f>
-        <v>36.66800030733036</v>
+        <v>34.611184744795338</v>
       </c>
       <c r="D82" s="116"/>
     </row>
@@ -19201,7 +19201,7 @@
       </c>
       <c r="C83" s="111">
         <f>C81+C82</f>
-        <v>40.809862006189697</v>
+        <v>38.753046443654675</v>
       </c>
       <c r="D83" t="str">
         <f>Market_currency</f>
@@ -19212,7 +19212,7 @@
       </c>
       <c r="F83" s="293">
         <f>(1-C83/C60)</f>
-        <v>0.53432419053403568</v>
+        <v>0.53151557024171581</v>
       </c>
     </row>
     <row r="84" spans="2:8">
@@ -19242,7 +19242,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.18459249999780813</v>
+        <v>0.16334582016407428</v>
       </c>
     </row>
     <row r="88" spans="2:8">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="C92" s="116">
         <f>C60/(1+C90)^C76</f>
-        <v>52.399759203206685</v>
+        <v>49.460503195272771</v>
       </c>
       <c r="D92" s="116"/>
     </row>
@@ -19290,7 +19290,7 @@
       </c>
       <c r="C93" s="111">
         <f>C91+C92</f>
-        <v>57.560060075377699</v>
+        <v>54.620804067443785</v>
       </c>
       <c r="D93" t="str">
         <f>Market_currency</f>
@@ -19301,7 +19301,7 @@
       </c>
       <c r="F93" s="293">
         <f>(1-C93/C60)</f>
-        <v>0.34318994843830652</v>
+        <v>0.33969071867212519</v>
       </c>
     </row>
     <row r="95" spans="2:8" ht="13.15">
@@ -19340,7 +19340,7 @@
       </c>
       <c r="C98" s="116">
         <f>C60/(1+C96)^C76</f>
-        <v>73.580689358931636</v>
+        <v>69.453332925337108</v>
       </c>
       <c r="D98" s="116"/>
       <c r="G98" s="2"/>
@@ -19352,7 +19352,7 @@
       </c>
       <c r="C99" s="111">
         <f>C97+C98</f>
-        <v>79.995918037639569</v>
+        <v>75.868561604045041</v>
       </c>
       <c r="D99" t="s">
         <v>397</v>
@@ -19362,7 +19362,7 @@
       </c>
       <c r="F99" s="293">
         <f>(1-C99/C60)</f>
-        <v>8.7177411173293029E-2</v>
+        <v>8.2827207627903632E-2</v>
       </c>
     </row>
     <row r="100" spans="2:8">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="C104" s="116">
         <f>C60/(1+C102)^C76</f>
-        <v>68.23274069010661</v>
+        <v>64.405366365094082</v>
       </c>
       <c r="D104" s="116"/>
     </row>
@@ -19408,7 +19408,7 @@
       </c>
       <c r="C105" s="111">
         <f>C103+C104</f>
-        <v>74.340476830385043</v>
+        <v>70.513102505372515</v>
       </c>
       <c r="D105" t="s">
         <v>397</v>
@@ -19418,7 +19418,7 @@
       </c>
       <c r="F105" s="293">
         <f>(1-C105/C66)</f>
-        <v>0.15104150766667601</v>
+        <v>0.14689628955752243</v>
       </c>
     </row>
     <row r="106" spans="2:8">

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9734F704-4F77-46AE-87E2-9EC5CF8EA2FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC3E426-D618-4541-9F19-4BB41723EABA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3868,29 +3868,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4308,7 +4308,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>57.9</v>
+        <v>57.36</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>28021.932364200002</v>
+        <v>27760.587917279998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4366,13 +4366,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="347" t="s">
+      <c r="B18" s="349" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="347"/>
-      <c r="D18" s="347"/>
-      <c r="E18" s="347"/>
-      <c r="F18" s="347"/>
+      <c r="C18" s="349"/>
+      <c r="D18" s="349"/>
+      <c r="E18" s="349"/>
+      <c r="F18" s="349"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="E26" s="304">
         <f ca="1">Scenarios!C87</f>
-        <v>0.16334582016407428</v>
+        <v>0.16711358671554644</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4497,7 +4497,7 @@
         <v>426</v>
       </c>
       <c r="F29" s="305">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4572,22 +4572,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="347" t="s">
+      <c r="B36" s="349" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="347"/>
-      <c r="D36" s="347"/>
-      <c r="E36" s="347"/>
-      <c r="F36" s="347"/>
+      <c r="C36" s="349"/>
+      <c r="D36" s="349"/>
+      <c r="E36" s="349"/>
+      <c r="F36" s="349"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="349" t="s">
+      <c r="B37" s="352" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="349"/>
-      <c r="D37" s="349"/>
-      <c r="E37" s="349"/>
-      <c r="F37" s="349"/>
+      <c r="C37" s="352"/>
+      <c r="D37" s="352"/>
+      <c r="E37" s="352"/>
+      <c r="F37" s="352"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4599,13 +4599,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="348" t="s">
+      <c r="B40" s="350" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="348"/>
-      <c r="D40" s="348"/>
-      <c r="E40" s="348"/>
-      <c r="F40" s="348"/>
+      <c r="C40" s="350"/>
+      <c r="D40" s="350"/>
+      <c r="E40" s="350"/>
+      <c r="F40" s="350"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4625,13 +4625,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="348" t="s">
+      <c r="B43" s="350" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="348"/>
-      <c r="D43" s="348"/>
-      <c r="E43" s="348"/>
-      <c r="F43" s="348"/>
+      <c r="C43" s="350"/>
+      <c r="D43" s="350"/>
+      <c r="E43" s="350"/>
+      <c r="F43" s="350"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4660,13 +4660,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="348" t="s">
+      <c r="B47" s="350" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="348"/>
-      <c r="D47" s="348"/>
-      <c r="E47" s="348"/>
-      <c r="F47" s="348"/>
+      <c r="C47" s="350"/>
+      <c r="D47" s="350"/>
+      <c r="E47" s="350"/>
+      <c r="F47" s="350"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4682,13 +4682,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="348" t="s">
+      <c r="B50" s="350" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="348"/>
-      <c r="D50" s="348"/>
-      <c r="E50" s="348"/>
-      <c r="F50" s="348"/>
+      <c r="C50" s="350"/>
+      <c r="D50" s="350"/>
+      <c r="E50" s="350"/>
+      <c r="F50" s="350"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4752,13 +4752,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="348" t="s">
+      <c r="B58" s="350" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="348"/>
-      <c r="D58" s="348"/>
-      <c r="E58" s="348"/>
-      <c r="F58" s="348"/>
+      <c r="C58" s="350"/>
+      <c r="D58" s="350"/>
+      <c r="E58" s="350"/>
+      <c r="F58" s="350"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4774,7 +4774,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="348" t="s">
+      <c r="B61" s="350" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="351"/>
@@ -4796,22 +4796,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="347" t="s">
+      <c r="B64" s="349" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="347"/>
-      <c r="D64" s="347"/>
-      <c r="E64" s="347"/>
-      <c r="F64" s="347"/>
+      <c r="C64" s="349"/>
+      <c r="D64" s="349"/>
+      <c r="E64" s="349"/>
+      <c r="F64" s="349"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="347" t="s">
+      <c r="B65" s="349" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="347"/>
-      <c r="D65" s="347"/>
-      <c r="E65" s="347"/>
-      <c r="F65" s="347"/>
+      <c r="C65" s="349"/>
+      <c r="D65" s="349"/>
+      <c r="E65" s="349"/>
+      <c r="F65" s="349"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.4939915413211919E-2</v>
+        <v>7.5645416708942995E-2</v>
       </c>
       <c r="F69" s="317"/>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.145077720207254E-2</v>
+        <v>4.1841004184100417E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>450</v>
@@ -4880,22 +4880,22 @@
     </row>
     <row r="74" spans="1:6" ht="24.5" customHeight="1">
       <c r="A74" s="17"/>
-      <c r="B74" s="347" t="s">
+      <c r="B74" s="349" t="s">
         <v>363</v>
       </c>
-      <c r="C74" s="347"/>
-      <c r="D74" s="347"/>
-      <c r="E74" s="347"/>
-      <c r="F74" s="347"/>
+      <c r="C74" s="349"/>
+      <c r="D74" s="349"/>
+      <c r="E74" s="349"/>
+      <c r="F74" s="349"/>
     </row>
     <row r="75" spans="1:6">
-      <c r="B75" s="349" t="s">
+      <c r="B75" s="352" t="s">
         <v>253</v>
       </c>
-      <c r="C75" s="349"/>
-      <c r="D75" s="349"/>
-      <c r="E75" s="349"/>
-      <c r="F75" s="349"/>
+      <c r="C75" s="352"/>
+      <c r="D75" s="352"/>
+      <c r="E75" s="352"/>
+      <c r="F75" s="352"/>
     </row>
     <row r="77" spans="1:6">
       <c r="B77" s="210" t="s">
@@ -4939,22 +4939,22 @@
       <c r="C82" s="121"/>
     </row>
     <row r="83" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B83" s="347" t="s">
+      <c r="B83" s="349" t="s">
         <v>364</v>
       </c>
-      <c r="C83" s="347"/>
-      <c r="D83" s="347"/>
-      <c r="E83" s="347"/>
-      <c r="F83" s="347"/>
+      <c r="C83" s="349"/>
+      <c r="D83" s="349"/>
+      <c r="E83" s="349"/>
+      <c r="F83" s="349"/>
     </row>
     <row r="84" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B84" s="347" t="s">
+      <c r="B84" s="349" t="s">
         <v>365</v>
       </c>
-      <c r="C84" s="347"/>
-      <c r="D84" s="347"/>
-      <c r="E84" s="347"/>
-      <c r="F84" s="347"/>
+      <c r="C84" s="349"/>
+      <c r="D84" s="349"/>
+      <c r="E84" s="349"/>
+      <c r="F84" s="349"/>
     </row>
     <row r="86" spans="1:6">
       <c r="B86" s="47" t="s">
@@ -4991,13 +4991,13 @@
       <c r="A90" s="209"/>
     </row>
     <row r="91" spans="1:6">
-      <c r="B91" s="347" t="s">
+      <c r="B91" s="349" t="s">
         <v>366</v>
       </c>
-      <c r="C91" s="347"/>
-      <c r="D91" s="347"/>
-      <c r="E91" s="347"/>
-      <c r="F91" s="347"/>
+      <c r="C91" s="349"/>
+      <c r="D91" s="349"/>
+      <c r="E91" s="349"/>
+      <c r="F91" s="349"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="1" t="s">
@@ -5010,13 +5010,13 @@
       </c>
     </row>
     <row r="95" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B95" s="347" t="s">
+      <c r="B95" s="349" t="s">
         <v>345</v>
       </c>
-      <c r="C95" s="347"/>
-      <c r="D95" s="347"/>
-      <c r="E95" s="347"/>
-      <c r="F95" s="347"/>
+      <c r="C95" s="349"/>
+      <c r="D95" s="349"/>
+      <c r="E95" s="349"/>
+      <c r="F95" s="349"/>
     </row>
     <row r="96" spans="1:6">
       <c r="B96" s="47" t="s">
@@ -5147,13 +5147,13 @@
       </c>
     </row>
     <row r="111" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B111" s="347" t="s">
+      <c r="B111" s="349" t="s">
         <v>367</v>
       </c>
-      <c r="C111" s="347"/>
-      <c r="D111" s="347"/>
-      <c r="E111" s="347"/>
-      <c r="F111" s="347"/>
+      <c r="C111" s="349"/>
+      <c r="D111" s="349"/>
+      <c r="E111" s="349"/>
+      <c r="F111" s="349"/>
     </row>
     <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
@@ -5192,13 +5192,13 @@
       <c r="F116" s="36"/>
     </row>
     <row r="118" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B118" s="348" t="s">
+      <c r="B118" s="350" t="s">
         <v>368</v>
       </c>
-      <c r="C118" s="348"/>
-      <c r="D118" s="348"/>
-      <c r="E118" s="348"/>
-      <c r="F118" s="348"/>
+      <c r="C118" s="350"/>
+      <c r="D118" s="350"/>
+      <c r="E118" s="350"/>
+      <c r="F118" s="350"/>
     </row>
     <row r="120" spans="1:6" ht="12.4">
       <c r="B120" s="233" t="s">
@@ -5341,13 +5341,13 @@
       </c>
     </row>
     <row r="129" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B129" s="352" t="s">
+      <c r="B129" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C129" s="352"/>
-      <c r="D129" s="352"/>
-      <c r="E129" s="352"/>
-      <c r="F129" s="352"/>
+      <c r="C129" s="353"/>
+      <c r="D129" s="353"/>
+      <c r="E129" s="353"/>
+      <c r="F129" s="353"/>
     </row>
     <row r="131" spans="1:6" ht="13.9">
       <c r="A131" s="222" t="s">
@@ -5360,22 +5360,22 @@
       <c r="F131" s="36"/>
     </row>
     <row r="133" spans="1:6">
-      <c r="B133" s="350" t="s">
+      <c r="B133" s="354" t="s">
         <v>369</v>
       </c>
-      <c r="C133" s="350"/>
-      <c r="D133" s="350"/>
-      <c r="E133" s="350"/>
-      <c r="F133" s="350"/>
+      <c r="C133" s="354"/>
+      <c r="D133" s="354"/>
+      <c r="E133" s="354"/>
+      <c r="F133" s="354"/>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="347" t="s">
+      <c r="B134" s="349" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="347"/>
-      <c r="D134" s="347"/>
-      <c r="E134" s="347"/>
-      <c r="F134" s="347"/>
+      <c r="C134" s="349"/>
+      <c r="D134" s="349"/>
+      <c r="E134" s="349"/>
+      <c r="F134" s="349"/>
     </row>
     <row r="135" spans="1:6">
       <c r="B135" s="210" t="s">
@@ -5397,7 +5397,7 @@
       </c>
       <c r="C137" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="C141" s="299">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="C142" s="216">
         <f>Scenarios!C81</f>
-        <v>4.1418616988593371</v>
+        <v>4.141861698859338</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5708,13 +5708,13 @@
       <c r="F172" s="36"/>
     </row>
     <row r="174" spans="1:6">
-      <c r="B174" s="354" t="s">
+      <c r="B174" s="348" t="s">
         <v>377</v>
       </c>
-      <c r="C174" s="347"/>
-      <c r="D174" s="347"/>
-      <c r="E174" s="347"/>
-      <c r="F174" s="347"/>
+      <c r="C174" s="349"/>
+      <c r="D174" s="349"/>
+      <c r="E174" s="349"/>
+      <c r="F174" s="349"/>
     </row>
     <row r="176" spans="1:6">
       <c r="B176" s="210" t="s">
@@ -5751,13 +5751,13 @@
       </c>
     </row>
     <row r="183" spans="2:6" ht="46.5" customHeight="1">
-      <c r="B183" s="348" t="s">
+      <c r="B183" s="350" t="s">
         <v>382</v>
       </c>
-      <c r="C183" s="348"/>
-      <c r="D183" s="348"/>
-      <c r="E183" s="348"/>
-      <c r="F183" s="348"/>
+      <c r="C183" s="350"/>
+      <c r="D183" s="350"/>
+      <c r="E183" s="350"/>
+      <c r="F183" s="350"/>
     </row>
     <row r="185" spans="2:6">
       <c r="B185" s="1" t="s">
@@ -5765,22 +5765,22 @@
       </c>
     </row>
     <row r="186" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B186" s="353" t="s">
+      <c r="B186" s="347" t="s">
         <v>383</v>
       </c>
-      <c r="C186" s="353"/>
-      <c r="D186" s="353"/>
-      <c r="E186" s="353"/>
-      <c r="F186" s="353"/>
+      <c r="C186" s="347"/>
+      <c r="D186" s="347"/>
+      <c r="E186" s="347"/>
+      <c r="F186" s="347"/>
     </row>
     <row r="187" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B187" s="353" t="s">
+      <c r="B187" s="347" t="s">
         <v>384</v>
       </c>
-      <c r="C187" s="353"/>
-      <c r="D187" s="353"/>
-      <c r="E187" s="353"/>
-      <c r="F187" s="353"/>
+      <c r="C187" s="347"/>
+      <c r="D187" s="347"/>
+      <c r="E187" s="347"/>
+      <c r="F187" s="347"/>
     </row>
     <row r="189" spans="2:6">
       <c r="B189" s="1" t="s">
@@ -5804,17 +5804,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B186:F186"/>
-    <mergeCell ref="B187:F187"/>
-    <mergeCell ref="B174:F174"/>
-    <mergeCell ref="B183:F183"/>
-    <mergeCell ref="B177:F177"/>
-    <mergeCell ref="B75:F75"/>
-    <mergeCell ref="B118:F118"/>
-    <mergeCell ref="B83:F83"/>
-    <mergeCell ref="B129:F129"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B95:F95"/>
     <mergeCell ref="B134:F134"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5831,6 +5820,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B74:F74"/>
+    <mergeCell ref="B75:F75"/>
+    <mergeCell ref="B118:F118"/>
+    <mergeCell ref="B83:F83"/>
+    <mergeCell ref="B129:F129"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B95:F95"/>
+    <mergeCell ref="B186:F186"/>
+    <mergeCell ref="B187:F187"/>
+    <mergeCell ref="B174:F174"/>
+    <mergeCell ref="B183:F183"/>
+    <mergeCell ref="B177:F177"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13379,12 +13379,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.145077720207254E-2</v>
+        <v>4.1841004184100417E-2</v>
       </c>
       <c r="E93" s="270"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.145077720207254E-2</v>
+        <v>4.1841004184100417E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14578,50 +14578,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.4939915413211919E-2</v>
+        <v>7.5645416708942995E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="267"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>8.2909299566521655E-2</v>
+        <v>8.3689826445285984E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>9.5198144355657599E-2</v>
+        <v>9.6094361195825928E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.0686567068956128E-2</v>
+        <v>9.1540310901195257E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>8.4797262797392609E-2</v>
+        <v>8.5595563388581444E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.7496532118626235E-2</v>
+        <v>4.7943675203425011E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6673115235198089E-2</v>
+        <v>1.683007970916962E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.5285298611698663E-2</v>
+        <v>1.5429197866411308E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2304224795021319E-2</v>
+        <v>1.2420059547275705E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.2150212896630128E-2</v>
+        <v>1.2264597746075391E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>6.7268509020035061E-3</v>
+        <v>6.7901789962692295E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14635,43 +14635,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0272140506403564E-2</v>
+        <v>8.1027840573932475E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.6765937472043165E-2</v>
+        <v>9.7676913870838558E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2316961135233744E-2</v>
+        <v>9.3186053865586371E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5617086103065884E-2</v>
+        <v>8.6423104696086384E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2533770805853095E-2</v>
+        <v>6.312247785318853E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.5998811235828884E-2</v>
+        <v>2.6243569919011375E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5033205616404555E-2</v>
+        <v>1.517473161070125E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1638110133212809E-2</v>
+        <v>1.1747673931538034E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9939871091397225E-3</v>
+        <v>5.0410016321337167E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.479708501337101E-3</v>
+        <v>-5.5312957152618232E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18391,7 +18391,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-57.9</v>
+        <v>-57.36</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18631,7 +18631,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>57.9</v>
+        <v>57.36</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19170,7 +19170,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19179,7 +19179,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>4.1418616988593371</v>
+        <v>4.141861698859338</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19229,7 +19229,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>57.9</v>
+        <v>57.36</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19242,7 +19242,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.16334582016407428</v>
+        <v>0.16711358671554644</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B337D9-2A93-4F2E-860B-8EA4D21175A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93339607-B907-4D3D-991E-2D835DCE41FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3882,29 +3882,29 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4380,13 +4380,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="350" t="s">
+      <c r="B18" s="348" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="350"/>
-      <c r="D18" s="350"/>
-      <c r="E18" s="350"/>
-      <c r="F18" s="350"/>
+      <c r="C18" s="348"/>
+      <c r="D18" s="348"/>
+      <c r="E18" s="348"/>
+      <c r="F18" s="348"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4511,7 +4511,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4586,22 +4586,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="350" t="s">
+      <c r="B36" s="348" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="350"/>
-      <c r="D36" s="350"/>
-      <c r="E36" s="350"/>
-      <c r="F36" s="350"/>
+      <c r="C36" s="348"/>
+      <c r="D36" s="348"/>
+      <c r="E36" s="348"/>
+      <c r="F36" s="348"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="353" t="s">
+      <c r="B37" s="350" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="353"/>
-      <c r="D37" s="353"/>
-      <c r="E37" s="353"/>
-      <c r="F37" s="353"/>
+      <c r="C37" s="350"/>
+      <c r="D37" s="350"/>
+      <c r="E37" s="350"/>
+      <c r="F37" s="350"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4613,13 +4613,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="351" t="s">
+      <c r="B40" s="349" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="351"/>
-      <c r="D40" s="351"/>
-      <c r="E40" s="351"/>
-      <c r="F40" s="351"/>
+      <c r="C40" s="349"/>
+      <c r="D40" s="349"/>
+      <c r="E40" s="349"/>
+      <c r="F40" s="349"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4639,13 +4639,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="351" t="s">
+      <c r="B43" s="349" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="351"/>
-      <c r="D43" s="351"/>
-      <c r="E43" s="351"/>
-      <c r="F43" s="351"/>
+      <c r="C43" s="349"/>
+      <c r="D43" s="349"/>
+      <c r="E43" s="349"/>
+      <c r="F43" s="349"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4674,13 +4674,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="351" t="s">
+      <c r="B47" s="349" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="351"/>
-      <c r="D47" s="351"/>
-      <c r="E47" s="351"/>
-      <c r="F47" s="351"/>
+      <c r="C47" s="349"/>
+      <c r="D47" s="349"/>
+      <c r="E47" s="349"/>
+      <c r="F47" s="349"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4696,13 +4696,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="351" t="s">
+      <c r="B50" s="349" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="351"/>
-      <c r="D50" s="351"/>
-      <c r="E50" s="351"/>
-      <c r="F50" s="351"/>
+      <c r="C50" s="349"/>
+      <c r="D50" s="349"/>
+      <c r="E50" s="349"/>
+      <c r="F50" s="349"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4766,13 +4766,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="351" t="s">
+      <c r="B58" s="349" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="351"/>
-      <c r="D58" s="351"/>
-      <c r="E58" s="351"/>
-      <c r="F58" s="351"/>
+      <c r="C58" s="349"/>
+      <c r="D58" s="349"/>
+      <c r="E58" s="349"/>
+      <c r="F58" s="349"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4788,7 +4788,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="351" t="s">
+      <c r="B61" s="349" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="352"/>
@@ -4810,22 +4810,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="350" t="s">
+      <c r="B64" s="348" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="350"/>
-      <c r="D64" s="350"/>
-      <c r="E64" s="350"/>
-      <c r="F64" s="350"/>
+      <c r="C64" s="348"/>
+      <c r="D64" s="348"/>
+      <c r="E64" s="348"/>
+      <c r="F64" s="348"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="350" t="s">
+      <c r="B65" s="348" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="350"/>
-      <c r="D65" s="350"/>
-      <c r="E65" s="350"/>
-      <c r="F65" s="350"/>
+      <c r="C65" s="348"/>
+      <c r="D65" s="348"/>
+      <c r="E65" s="348"/>
+      <c r="F65" s="348"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4960,22 +4960,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="350" t="s">
+      <c r="B80" s="348" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="350"/>
-      <c r="D80" s="350"/>
-      <c r="E80" s="350"/>
-      <c r="F80" s="350"/>
+      <c r="C80" s="348"/>
+      <c r="D80" s="348"/>
+      <c r="E80" s="348"/>
+      <c r="F80" s="348"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="353" t="s">
+      <c r="B81" s="350" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="353"/>
-      <c r="D81" s="353"/>
-      <c r="E81" s="353"/>
-      <c r="F81" s="353"/>
+      <c r="C81" s="350"/>
+      <c r="D81" s="350"/>
+      <c r="E81" s="350"/>
+      <c r="F81" s="350"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5019,22 +5019,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="350" t="s">
+      <c r="B89" s="348" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="350"/>
-      <c r="D89" s="350"/>
-      <c r="E89" s="350"/>
-      <c r="F89" s="350"/>
+      <c r="C89" s="348"/>
+      <c r="D89" s="348"/>
+      <c r="E89" s="348"/>
+      <c r="F89" s="348"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="350" t="s">
+      <c r="B90" s="348" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="350"/>
-      <c r="D90" s="350"/>
-      <c r="E90" s="350"/>
-      <c r="F90" s="350"/>
+      <c r="C90" s="348"/>
+      <c r="D90" s="348"/>
+      <c r="E90" s="348"/>
+      <c r="F90" s="348"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5071,13 +5071,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="350" t="s">
+      <c r="B97" s="348" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="350"/>
-      <c r="D97" s="350"/>
-      <c r="E97" s="350"/>
-      <c r="F97" s="350"/>
+      <c r="C97" s="348"/>
+      <c r="D97" s="348"/>
+      <c r="E97" s="348"/>
+      <c r="F97" s="348"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5090,13 +5090,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="350" t="s">
+      <c r="B101" s="348" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="350"/>
-      <c r="D101" s="350"/>
-      <c r="E101" s="350"/>
-      <c r="F101" s="350"/>
+      <c r="C101" s="348"/>
+      <c r="D101" s="348"/>
+      <c r="E101" s="348"/>
+      <c r="F101" s="348"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5218,13 +5218,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="350" t="s">
+      <c r="B116" s="348" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="350"/>
-      <c r="D116" s="350"/>
-      <c r="E116" s="350"/>
-      <c r="F116" s="350"/>
+      <c r="C116" s="348"/>
+      <c r="D116" s="348"/>
+      <c r="E116" s="348"/>
+      <c r="F116" s="348"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5263,13 +5263,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="351" t="s">
+      <c r="B123" s="349" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="351"/>
-      <c r="D123" s="351"/>
-      <c r="E123" s="351"/>
-      <c r="F123" s="351"/>
+      <c r="C123" s="349"/>
+      <c r="D123" s="349"/>
+      <c r="E123" s="349"/>
+      <c r="F123" s="349"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5412,13 +5412,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="354" t="s">
+      <c r="B134" s="353" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="354"/>
-      <c r="D134" s="354"/>
-      <c r="E134" s="354"/>
-      <c r="F134" s="354"/>
+      <c r="C134" s="353"/>
+      <c r="D134" s="353"/>
+      <c r="E134" s="353"/>
+      <c r="F134" s="353"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5431,22 +5431,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="355" t="s">
+      <c r="B138" s="351" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="355"/>
-      <c r="D138" s="355"/>
-      <c r="E138" s="355"/>
-      <c r="F138" s="355"/>
+      <c r="C138" s="351"/>
+      <c r="D138" s="351"/>
+      <c r="E138" s="351"/>
+      <c r="F138" s="351"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="350" t="s">
+      <c r="B139" s="348" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="350"/>
-      <c r="D139" s="350"/>
-      <c r="E139" s="350"/>
-      <c r="F139" s="350"/>
+      <c r="C139" s="348"/>
+      <c r="D139" s="348"/>
+      <c r="E139" s="348"/>
+      <c r="F139" s="348"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5513,7 +5513,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>4.1418616988593371</v>
+        <v>4.141861698859338</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5779,13 +5779,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="349" t="s">
+      <c r="B179" s="355" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="350"/>
-      <c r="D179" s="350"/>
-      <c r="E179" s="350"/>
-      <c r="F179" s="350"/>
+      <c r="C179" s="348"/>
+      <c r="D179" s="348"/>
+      <c r="E179" s="348"/>
+      <c r="F179" s="348"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5822,13 +5822,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="351" t="s">
+      <c r="B188" s="349" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="351"/>
-      <c r="D188" s="351"/>
-      <c r="E188" s="351"/>
-      <c r="F188" s="351"/>
+      <c r="C188" s="349"/>
+      <c r="D188" s="349"/>
+      <c r="E188" s="349"/>
+      <c r="F188" s="349"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5836,22 +5836,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="348" t="s">
+      <c r="B191" s="354" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="348"/>
-      <c r="D191" s="348"/>
-      <c r="E191" s="348"/>
-      <c r="F191" s="348"/>
+      <c r="C191" s="354"/>
+      <c r="D191" s="354"/>
+      <c r="E191" s="354"/>
+      <c r="F191" s="354"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="348" t="s">
+      <c r="B192" s="354" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="348"/>
-      <c r="D192" s="348"/>
-      <c r="E192" s="348"/>
-      <c r="F192" s="348"/>
+      <c r="C192" s="354"/>
+      <c r="D192" s="354"/>
+      <c r="E192" s="354"/>
+      <c r="F192" s="354"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5875,6 +5875,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5891,17 +5902,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -19241,7 +19241,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19250,7 +19250,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>4.1418616988593371</v>
+        <v>4.141861698859338</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93339607-B907-4D3D-991E-2D835DCE41FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58585259-0B36-4859-BC3E-F92B95F17D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="2205" windowWidth="12690" windowHeight="7642" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -2483,7 +2483,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="17">
+  <numFmts count="18">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;mm&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.00&quot;x&quot;"/>
@@ -2501,6 +2501,7 @@
     <numFmt numFmtId="178" formatCode="0.0\x"/>
     <numFmt numFmtId="179" formatCode="0\x"/>
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
+    <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
   <fonts count="59">
     <font>
@@ -3149,7 +3150,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="52" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="360">
+  <cellXfs count="369">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -3821,36 +3822,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="37" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
     <xf numFmtId="37" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3865,10 +3843,6 @@
     </xf>
     <xf numFmtId="37" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="37" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="37" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="37" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="37" fontId="11" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="37" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3880,6 +3854,48 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="3" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="181" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="47" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="181" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4380,13 +4396,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="348" t="s">
+      <c r="B18" s="357" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="348"/>
-      <c r="D18" s="348"/>
-      <c r="E18" s="348"/>
-      <c r="F18" s="348"/>
+      <c r="C18" s="357"/>
+      <c r="D18" s="357"/>
+      <c r="E18" s="357"/>
+      <c r="F18" s="357"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4511,7 +4527,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4586,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="348" t="s">
+      <c r="B36" s="357" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="348"/>
-      <c r="D36" s="348"/>
-      <c r="E36" s="348"/>
-      <c r="F36" s="348"/>
+      <c r="C36" s="357"/>
+      <c r="D36" s="357"/>
+      <c r="E36" s="357"/>
+      <c r="F36" s="357"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="350" t="s">
+      <c r="B37" s="359" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="350"/>
-      <c r="D37" s="350"/>
-      <c r="E37" s="350"/>
-      <c r="F37" s="350"/>
+      <c r="C37" s="359"/>
+      <c r="D37" s="359"/>
+      <c r="E37" s="359"/>
+      <c r="F37" s="359"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4613,19 +4629,19 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="349" t="s">
+      <c r="B40" s="358" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="349"/>
-      <c r="D40" s="349"/>
-      <c r="E40" s="349"/>
-      <c r="F40" s="349"/>
+      <c r="C40" s="358"/>
+      <c r="D40" s="358"/>
+      <c r="E40" s="358"/>
+      <c r="F40" s="358"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="C41" s="76">
+      <c r="C41" s="355">
         <f>Normalized_FCF!C8</f>
         <v>2957715106.6986084</v>
       </c>
@@ -4639,19 +4655,19 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="349" t="s">
+      <c r="B43" s="358" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="349"/>
-      <c r="D43" s="349"/>
-      <c r="E43" s="349"/>
-      <c r="F43" s="349"/>
+      <c r="C43" s="358"/>
+      <c r="D43" s="358"/>
+      <c r="E43" s="358"/>
+      <c r="F43" s="358"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="C44" s="76">
+      <c r="C44" s="355">
         <f>Normalized_FCF!C9</f>
         <v>575917865</v>
       </c>
@@ -4664,7 +4680,7 @@
       <c r="B45" s="52" t="s">
         <v>236</v>
       </c>
-      <c r="C45" s="76">
+      <c r="C45" s="355">
         <f>Normalized_FCF!C10</f>
         <v>-575917865</v>
       </c>
@@ -4674,19 +4690,19 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="349" t="s">
+      <c r="B47" s="358" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="349"/>
-      <c r="D47" s="349"/>
-      <c r="E47" s="349"/>
-      <c r="F47" s="349"/>
+      <c r="C47" s="358"/>
+      <c r="D47" s="358"/>
+      <c r="E47" s="358"/>
+      <c r="F47" s="358"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="C48" s="76">
+      <c r="C48" s="355">
         <f>Normalized_FCF!C11</f>
         <v>0</v>
       </c>
@@ -4696,19 +4712,19 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="349" t="s">
+      <c r="B50" s="358" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="349"/>
-      <c r="D50" s="349"/>
-      <c r="E50" s="349"/>
-      <c r="F50" s="349"/>
+      <c r="C50" s="358"/>
+      <c r="D50" s="358"/>
+      <c r="E50" s="358"/>
+      <c r="F50" s="358"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>341</v>
       </c>
-      <c r="C51" s="340">
+      <c r="C51" s="356">
         <f>Normalized_FCF!C48</f>
         <v>39079014.816265978</v>
       </c>
@@ -4723,7 +4739,7 @@
       <c r="B52" s="47" t="s">
         <v>342</v>
       </c>
-      <c r="C52" s="340">
+      <c r="C52" s="356">
         <f>Normalized_FCF!C47</f>
         <v>-7672861</v>
       </c>
@@ -4738,7 +4754,7 @@
       <c r="B53" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="C53" s="76">
+      <c r="C53" s="355">
         <f>Normalized_FCF!C12</f>
         <v>31406153.816265978</v>
       </c>
@@ -4756,7 +4772,7 @@
       <c r="B56" s="47" t="s">
         <v>266</v>
       </c>
-      <c r="C56" s="76">
+      <c r="C56" s="355">
         <f>Normalized_FCF!C15</f>
         <v>-141879704.29826272</v>
       </c>
@@ -4766,19 +4782,19 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="349" t="s">
+      <c r="B58" s="358" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="349"/>
-      <c r="D58" s="349"/>
-      <c r="E58" s="349"/>
-      <c r="F58" s="349"/>
+      <c r="C58" s="358"/>
+      <c r="D58" s="358"/>
+      <c r="E58" s="358"/>
+      <c r="F58" s="358"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="C59" s="76">
+      <c r="C59" s="355">
         <f>Normalized_FCF!C14</f>
         <v>-747280315.12871861</v>
       </c>
@@ -4788,19 +4804,19 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="349" t="s">
+      <c r="B61" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C61" s="352"/>
-      <c r="D61" s="352"/>
-      <c r="E61" s="352"/>
-      <c r="F61" s="352"/>
+      <c r="C61" s="361"/>
+      <c r="D61" s="361"/>
+      <c r="E61" s="361"/>
+      <c r="F61" s="361"/>
     </row>
     <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>243</v>
       </c>
-      <c r="C62" s="76">
+      <c r="C62" s="355">
         <f>Normalized_FCF!C17</f>
         <v>0</v>
       </c>
@@ -4810,28 +4826,28 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="348" t="s">
+      <c r="B64" s="357" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="348"/>
-      <c r="D64" s="348"/>
-      <c r="E64" s="348"/>
-      <c r="F64" s="348"/>
+      <c r="C64" s="357"/>
+      <c r="D64" s="357"/>
+      <c r="E64" s="357"/>
+      <c r="F64" s="357"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="348" t="s">
+      <c r="B65" s="357" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="348"/>
-      <c r="D65" s="348"/>
-      <c r="E65" s="348"/>
-      <c r="F65" s="348"/>
+      <c r="C65" s="357"/>
+      <c r="D65" s="357"/>
+      <c r="E65" s="357"/>
+      <c r="F65" s="357"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>271</v>
       </c>
-      <c r="C67" s="76">
+      <c r="C67" s="355">
         <f>Normalized_FCF!G19</f>
         <v>2323278784.8162661</v>
       </c>
@@ -4844,7 +4860,7 @@
       <c r="B68" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="C68" s="76">
+      <c r="C68" s="355">
         <f>Normalized_FCF!C19</f>
         <v>2099961241.0878935</v>
       </c>
@@ -4883,10 +4899,10 @@
       <c r="B72" s="210" t="s">
         <v>451</v>
       </c>
-      <c r="C72" s="344" t="s">
+      <c r="C72" s="329" t="s">
         <v>453</v>
       </c>
-      <c r="D72" s="344" t="s">
+      <c r="D72" s="329" t="s">
         <v>454</v>
       </c>
     </row>
@@ -4908,11 +4924,11 @@
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
       </c>
-      <c r="C74" s="343">
+      <c r="C74" s="328">
         <f>Normalized_FCF!C117</f>
         <v>0.21117895977217718</v>
       </c>
-      <c r="D74" s="343">
+      <c r="D74" s="328">
         <f>Normalized_FCF!G117</f>
         <v>0.21445578545073618</v>
       </c>
@@ -4922,11 +4938,11 @@
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
       </c>
-      <c r="C75" s="345">
+      <c r="C75" s="330">
         <f>Normalized_FCF!C118</f>
         <v>1.2904821269100146</v>
       </c>
-      <c r="D75" s="345">
+      <c r="D75" s="330">
         <f>Normalized_FCF!G118</f>
         <v>1.3351699725448014</v>
       </c>
@@ -4936,11 +4952,11 @@
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
       </c>
-      <c r="C76" s="345">
+      <c r="C76" s="330">
         <f>Normalized_FCF!C119</f>
         <v>4.4701988818540466</v>
       </c>
-      <c r="D76" s="345">
+      <c r="D76" s="330">
         <f>Normalized_FCF!G119</f>
         <v>4.4701988818540466</v>
       </c>
@@ -4960,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="348" t="s">
+      <c r="B80" s="357" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="348"/>
-      <c r="D80" s="348"/>
-      <c r="E80" s="348"/>
-      <c r="F80" s="348"/>
+      <c r="C80" s="357"/>
+      <c r="D80" s="357"/>
+      <c r="E80" s="357"/>
+      <c r="F80" s="357"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="350" t="s">
+      <c r="B81" s="359" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="350"/>
-      <c r="D81" s="350"/>
-      <c r="E81" s="350"/>
-      <c r="F81" s="350"/>
+      <c r="C81" s="359"/>
+      <c r="D81" s="359"/>
+      <c r="E81" s="359"/>
+      <c r="F81" s="359"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5019,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="348" t="s">
+      <c r="B89" s="357" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="348"/>
-      <c r="D89" s="348"/>
-      <c r="E89" s="348"/>
-      <c r="F89" s="348"/>
+      <c r="C89" s="357"/>
+      <c r="D89" s="357"/>
+      <c r="E89" s="357"/>
+      <c r="F89" s="357"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="348" t="s">
+      <c r="B90" s="357" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="348"/>
-      <c r="D90" s="348"/>
-      <c r="E90" s="348"/>
-      <c r="F90" s="348"/>
+      <c r="C90" s="357"/>
+      <c r="D90" s="357"/>
+      <c r="E90" s="357"/>
+      <c r="F90" s="357"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5071,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="348" t="s">
+      <c r="B97" s="357" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="348"/>
-      <c r="D97" s="348"/>
-      <c r="E97" s="348"/>
-      <c r="F97" s="348"/>
+      <c r="C97" s="357"/>
+      <c r="D97" s="357"/>
+      <c r="E97" s="357"/>
+      <c r="F97" s="357"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5090,19 +5106,19 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="348" t="s">
+      <c r="B101" s="357" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="348"/>
-      <c r="D101" s="348"/>
-      <c r="E101" s="348"/>
-      <c r="F101" s="348"/>
+      <c r="C101" s="357"/>
+      <c r="D101" s="357"/>
+      <c r="E101" s="357"/>
+      <c r="F101" s="357"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>256</v>
       </c>
-      <c r="C102" s="76">
+      <c r="C102" s="355">
         <f>DCF!C7</f>
         <v>123521704.27</v>
       </c>
@@ -5128,7 +5144,7 @@
       <c r="B104" s="296" t="s">
         <v>405</v>
       </c>
-      <c r="C104" s="346">
+      <c r="C104" s="331">
         <f>IF(BS!G31/BS!G27&gt;300%,"nm",BS!G31/BS!G27)</f>
         <v>5.0341856510546588E-2</v>
       </c>
@@ -5137,7 +5153,7 @@
       <c r="B105" s="296" t="s">
         <v>407</v>
       </c>
-      <c r="C105" s="347">
+      <c r="C105" s="332">
         <f>IF(BS!C50&gt;30,"nm",BS!C50)</f>
         <v>4.1762542981319963E-2</v>
       </c>
@@ -5151,7 +5167,7 @@
       <c r="B108" s="47" t="s">
         <v>265</v>
       </c>
-      <c r="C108" s="76">
+      <c r="C108" s="355">
         <f>BS!C66</f>
         <v>1081659074.0699999</v>
       </c>
@@ -5164,7 +5180,7 @@
       <c r="B109" s="47" t="s">
         <v>267</v>
       </c>
-      <c r="C109" s="76">
+      <c r="C109" s="355">
         <f>DCF!C8</f>
         <v>51803895.882383943</v>
       </c>
@@ -5195,7 +5211,7 @@
       <c r="B113" s="47" t="s">
         <v>258</v>
       </c>
-      <c r="C113" s="76">
+      <c r="C113" s="355">
         <f>DCF!C9</f>
         <v>29558000.651999995</v>
       </c>
@@ -5218,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="348" t="s">
+      <c r="B116" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="348"/>
-      <c r="D116" s="348"/>
-      <c r="E116" s="348"/>
-      <c r="F116" s="348"/>
+      <c r="C116" s="357"/>
+      <c r="D116" s="357"/>
+      <c r="E116" s="357"/>
+      <c r="F116" s="357"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5263,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="349" t="s">
+      <c r="B123" s="358" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="349"/>
-      <c r="D123" s="349"/>
-      <c r="E123" s="349"/>
-      <c r="F123" s="349"/>
+      <c r="C123" s="358"/>
+      <c r="D123" s="358"/>
+      <c r="E123" s="358"/>
+      <c r="F123" s="358"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5412,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="353" t="s">
+      <c r="B134" s="362" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="353"/>
-      <c r="D134" s="353"/>
-      <c r="E134" s="353"/>
-      <c r="F134" s="353"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5431,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="351" t="s">
+      <c r="B138" s="360" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="351"/>
-      <c r="D138" s="351"/>
-      <c r="E138" s="351"/>
-      <c r="F138" s="351"/>
+      <c r="C138" s="360"/>
+      <c r="D138" s="360"/>
+      <c r="E138" s="360"/>
+      <c r="F138" s="360"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="348" t="s">
+      <c r="B139" s="357" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="348"/>
-      <c r="D139" s="348"/>
-      <c r="E139" s="348"/>
-      <c r="F139" s="348"/>
+      <c r="C139" s="357"/>
+      <c r="D139" s="357"/>
+      <c r="E139" s="357"/>
+      <c r="F139" s="357"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5468,7 +5484,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5503,7 +5519,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5513,7 +5529,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>4.141861698859338</v>
+        <v>4.1418616988593371</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5779,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="355" t="s">
+      <c r="B179" s="364" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="348"/>
-      <c r="D179" s="348"/>
-      <c r="E179" s="348"/>
-      <c r="F179" s="348"/>
+      <c r="C179" s="357"/>
+      <c r="D179" s="357"/>
+      <c r="E179" s="357"/>
+      <c r="F179" s="357"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5793,13 +5809,13 @@
       </c>
     </row>
     <row r="182" spans="1:6">
-      <c r="B182" s="352" t="s">
+      <c r="B182" s="361" t="s">
         <v>381</v>
       </c>
-      <c r="C182" s="352"/>
-      <c r="D182" s="352"/>
-      <c r="E182" s="352"/>
-      <c r="F182" s="352"/>
+      <c r="C182" s="361"/>
+      <c r="D182" s="361"/>
+      <c r="E182" s="361"/>
+      <c r="F182" s="361"/>
     </row>
     <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
@@ -5822,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="349" t="s">
+      <c r="B188" s="358" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="349"/>
-      <c r="D188" s="349"/>
-      <c r="E188" s="349"/>
-      <c r="F188" s="349"/>
+      <c r="C188" s="358"/>
+      <c r="D188" s="358"/>
+      <c r="E188" s="358"/>
+      <c r="F188" s="358"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5836,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="354" t="s">
+      <c r="B191" s="363" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="354"/>
-      <c r="D191" s="354"/>
-      <c r="E191" s="354"/>
-      <c r="F191" s="354"/>
+      <c r="C191" s="363"/>
+      <c r="D191" s="363"/>
+      <c r="E191" s="363"/>
+      <c r="F191" s="363"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="354" t="s">
+      <c r="B192" s="363" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="354"/>
-      <c r="D192" s="354"/>
-      <c r="E192" s="354"/>
-      <c r="F192" s="354"/>
+      <c r="C192" s="363"/>
+      <c r="D192" s="363"/>
+      <c r="E192" s="363"/>
+      <c r="F192" s="363"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -6017,383 +6033,383 @@
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="334">
+      <c r="C4" s="321">
         <v>14644597842</v>
       </c>
-      <c r="D4" s="334">
+      <c r="D4" s="321">
         <v>14814836410</v>
       </c>
-      <c r="E4" s="334">
+      <c r="E4" s="321">
         <v>14039040539</v>
       </c>
-      <c r="F4" s="334">
+      <c r="F4" s="321">
         <v>13119310688</v>
       </c>
-      <c r="G4" s="334">
+      <c r="G4" s="321">
         <v>10941631163</v>
       </c>
-      <c r="H4" s="334">
+      <c r="H4" s="321">
         <v>3581923735</v>
       </c>
-      <c r="I4" s="334">
+      <c r="I4" s="321">
         <v>3467335930</v>
       </c>
-      <c r="J4" s="334">
+      <c r="J4" s="321">
         <v>3175519522</v>
       </c>
-      <c r="K4" s="334">
+      <c r="K4" s="321">
         <v>3195921516</v>
       </c>
-      <c r="L4" s="334">
+      <c r="L4" s="321">
         <v>3323745278</v>
       </c>
-      <c r="M4" s="334"/>
+      <c r="M4" s="321"/>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="334">
+      <c r="C5" s="321">
         <v>8483123346</v>
       </c>
-      <c r="D5" s="334">
+      <c r="D5" s="321">
         <v>8491525016</v>
       </c>
-      <c r="E5" s="334">
+      <c r="E5" s="321">
         <v>7873287284</v>
       </c>
-      <c r="F5" s="334">
+      <c r="F5" s="321">
         <v>7328418046</v>
       </c>
-      <c r="G5" s="334">
+      <c r="G5" s="321">
         <v>6166079008</v>
       </c>
-      <c r="H5" s="334">
+      <c r="H5" s="321">
         <v>2359127300</v>
       </c>
-      <c r="I5" s="334">
+      <c r="I5" s="321">
         <v>2362728713</v>
       </c>
-      <c r="J5" s="334">
+      <c r="J5" s="321">
         <v>2190920673</v>
       </c>
-      <c r="K5" s="334">
+      <c r="K5" s="321">
         <v>2209433704</v>
       </c>
-      <c r="L5" s="334">
+      <c r="L5" s="321">
         <v>2369740058</v>
       </c>
-      <c r="M5" s="334"/>
+      <c r="M5" s="321"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="334">
+      <c r="C6" s="321">
         <f>516942154+C7</f>
         <v>3029595871</v>
       </c>
-      <c r="D6" s="334">
+      <c r="D6" s="321">
         <f>494670738+D7</f>
         <v>3027292571</v>
       </c>
-      <c r="E6" s="334">
+      <c r="E6" s="321">
         <f>534570349+E7</f>
         <v>2860787576</v>
       </c>
-      <c r="F6" s="334">
+      <c r="F6" s="321">
         <f>516877145+F7</f>
         <v>2729771806</v>
       </c>
-      <c r="G6" s="334">
+      <c r="G6" s="321">
         <f>684104925+G7</f>
         <v>2988418106</v>
       </c>
-      <c r="H6" s="334">
+      <c r="H6" s="321">
         <f>161996928+H7</f>
         <v>654203552</v>
       </c>
-      <c r="I6" s="334">
+      <c r="I6" s="321">
         <f>153940810+I7</f>
         <v>609225228</v>
       </c>
-      <c r="J6" s="334">
+      <c r="J6" s="321">
         <f>155718230+J7</f>
         <v>620936767</v>
       </c>
-      <c r="K6" s="334">
+      <c r="K6" s="321">
         <f>183628555+K7</f>
         <v>629182097</v>
       </c>
-      <c r="L6" s="334">
+      <c r="L6" s="321">
         <f>232657686+L7</f>
         <v>722526234</v>
       </c>
-      <c r="M6" s="334"/>
+      <c r="M6" s="321"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="335">
+      <c r="C7" s="322">
         <v>2512653717</v>
       </c>
-      <c r="D7" s="335">
+      <c r="D7" s="322">
         <v>2532621833</v>
       </c>
-      <c r="E7" s="335">
+      <c r="E7" s="322">
         <v>2326217227</v>
       </c>
-      <c r="F7" s="335">
+      <c r="F7" s="322">
         <v>2212894661</v>
       </c>
-      <c r="G7" s="335">
+      <c r="G7" s="322">
         <v>2304313181</v>
       </c>
-      <c r="H7" s="335">
+      <c r="H7" s="322">
         <v>492206624</v>
       </c>
-      <c r="I7" s="335">
+      <c r="I7" s="322">
         <v>455284418</v>
       </c>
-      <c r="J7" s="335">
+      <c r="J7" s="322">
         <v>465218537</v>
       </c>
-      <c r="K7" s="335">
+      <c r="K7" s="322">
         <v>445553542</v>
       </c>
-      <c r="L7" s="335">
+      <c r="L7" s="322">
         <v>489868548</v>
       </c>
-      <c r="M7" s="335"/>
+      <c r="M7" s="322"/>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C8" s="334">
+      <c r="C8" s="321">
         <v>22666046</v>
       </c>
-      <c r="D8" s="334">
+      <c r="D8" s="321">
         <v>26232056</v>
       </c>
-      <c r="E8" s="334">
+      <c r="E8" s="321">
         <v>110747936</v>
       </c>
-      <c r="F8" s="334">
+      <c r="F8" s="321">
         <v>163151285</v>
       </c>
-      <c r="G8" s="334">
+      <c r="G8" s="321">
         <v>84212617</v>
       </c>
-      <c r="H8" s="334">
-        <v>0</v>
-      </c>
-      <c r="I8" s="334">
-        <v>0</v>
-      </c>
-      <c r="J8" s="334"/>
-      <c r="K8" s="334"/>
-      <c r="L8" s="334"/>
-      <c r="M8" s="334"/>
+      <c r="H8" s="321">
+        <v>0</v>
+      </c>
+      <c r="I8" s="321">
+        <v>0</v>
+      </c>
+      <c r="J8" s="321"/>
+      <c r="K8" s="321"/>
+      <c r="L8" s="321"/>
+      <c r="M8" s="321"/>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C9" s="334"/>
-      <c r="D9" s="334"/>
-      <c r="E9" s="334"/>
-      <c r="F9" s="334"/>
-      <c r="G9" s="334"/>
-      <c r="H9" s="334"/>
-      <c r="I9" s="334"/>
-      <c r="J9" s="334"/>
-      <c r="K9" s="334"/>
-      <c r="L9" s="334"/>
-      <c r="M9" s="334"/>
+      <c r="C9" s="321"/>
+      <c r="D9" s="321"/>
+      <c r="E9" s="321"/>
+      <c r="F9" s="321"/>
+      <c r="G9" s="321"/>
+      <c r="H9" s="321"/>
+      <c r="I9" s="321"/>
+      <c r="J9" s="321"/>
+      <c r="K9" s="321"/>
+      <c r="L9" s="321"/>
+      <c r="M9" s="321"/>
     </row>
     <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C10" s="334"/>
-      <c r="D10" s="334"/>
-      <c r="E10" s="334"/>
-      <c r="F10" s="334"/>
-      <c r="G10" s="334"/>
-      <c r="H10" s="334"/>
-      <c r="I10" s="334"/>
-      <c r="J10" s="334"/>
-      <c r="K10" s="334"/>
-      <c r="L10" s="334"/>
-      <c r="M10" s="334"/>
+      <c r="C10" s="321"/>
+      <c r="D10" s="321"/>
+      <c r="E10" s="321"/>
+      <c r="F10" s="321"/>
+      <c r="G10" s="321"/>
+      <c r="H10" s="321"/>
+      <c r="I10" s="321"/>
+      <c r="J10" s="321"/>
+      <c r="K10" s="321"/>
+      <c r="L10" s="321"/>
+      <c r="M10" s="321"/>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C11" s="334"/>
-      <c r="D11" s="334"/>
-      <c r="E11" s="334"/>
-      <c r="F11" s="334"/>
-      <c r="G11" s="334"/>
-      <c r="H11" s="334"/>
-      <c r="I11" s="334"/>
-      <c r="J11" s="334"/>
-      <c r="K11" s="334"/>
-      <c r="L11" s="334"/>
-      <c r="M11" s="334"/>
+      <c r="C11" s="321"/>
+      <c r="D11" s="321"/>
+      <c r="E11" s="321"/>
+      <c r="F11" s="321"/>
+      <c r="G11" s="321"/>
+      <c r="H11" s="321"/>
+      <c r="I11" s="321"/>
+      <c r="J11" s="321"/>
+      <c r="K11" s="321"/>
+      <c r="L11" s="321"/>
+      <c r="M11" s="321"/>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="334">
+      <c r="C12" s="321">
         <v>7672861</v>
       </c>
-      <c r="D12" s="334">
+      <c r="D12" s="321">
         <v>5921669</v>
       </c>
-      <c r="E12" s="334">
+      <c r="E12" s="321">
         <v>3696844</v>
       </c>
-      <c r="F12" s="334">
+      <c r="F12" s="321">
         <v>14186775</v>
       </c>
-      <c r="G12" s="334">
+      <c r="G12" s="321">
         <v>35823675</v>
       </c>
-      <c r="H12" s="334">
+      <c r="H12" s="321">
         <v>10770646</v>
       </c>
-      <c r="I12" s="334">
+      <c r="I12" s="321">
         <v>12333775</v>
       </c>
-      <c r="J12" s="334"/>
-      <c r="K12" s="334"/>
-      <c r="L12" s="334"/>
-      <c r="M12" s="334"/>
+      <c r="J12" s="321"/>
+      <c r="K12" s="321"/>
+      <c r="L12" s="321"/>
+      <c r="M12" s="321"/>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="334">
+      <c r="C13" s="321">
         <v>41044772</v>
       </c>
-      <c r="D13" s="334">
+      <c r="D13" s="321">
         <v>71308016</v>
       </c>
-      <c r="E13" s="334">
+      <c r="E13" s="321">
         <v>65718589</v>
       </c>
-      <c r="F13" s="334">
+      <c r="F13" s="321">
         <v>36050786</v>
       </c>
-      <c r="G13" s="334">
+      <c r="G13" s="321">
         <v>44443082</v>
       </c>
-      <c r="H13" s="334">
+      <c r="H13" s="321">
         <v>8582394</v>
       </c>
-      <c r="I13" s="334">
+      <c r="I13" s="321">
         <v>6609967</v>
       </c>
-      <c r="J13" s="334"/>
-      <c r="K13" s="334"/>
-      <c r="L13" s="334"/>
-      <c r="M13" s="334"/>
+      <c r="J13" s="321"/>
+      <c r="K13" s="321"/>
+      <c r="L13" s="321"/>
+      <c r="M13" s="321"/>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="334">
+      <c r="C14" s="321">
         <v>670547120</v>
       </c>
-      <c r="D14" s="334">
+      <c r="D14" s="321">
         <v>664121997</v>
       </c>
-      <c r="E14" s="334">
+      <c r="E14" s="321">
         <v>711879179</v>
       </c>
-      <c r="F14" s="334">
+      <c r="F14" s="321">
         <v>541923819</v>
       </c>
-      <c r="G14" s="334">
+      <c r="G14" s="321">
         <v>378467716</v>
       </c>
-      <c r="H14" s="334">
+      <c r="H14" s="321">
         <v>98780687</v>
       </c>
-      <c r="I14" s="334">
+      <c r="I14" s="321">
         <v>61018006</v>
       </c>
-      <c r="J14" s="334">
+      <c r="J14" s="321">
         <v>18873927</v>
       </c>
-      <c r="K14" s="334">
+      <c r="K14" s="321">
         <v>16833271</v>
       </c>
-      <c r="L14" s="334">
+      <c r="L14" s="321">
         <v>42979625</v>
       </c>
-      <c r="M14" s="334"/>
+      <c r="M14" s="321"/>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="336">
+      <c r="C15" s="323">
         <v>2249380492</v>
       </c>
-      <c r="D15" s="336">
+      <c r="D15" s="323">
         <v>2711568555</v>
       </c>
-      <c r="E15" s="336">
+      <c r="E15" s="323">
         <v>2586899641</v>
       </c>
-      <c r="F15" s="336">
+      <c r="F15" s="323">
         <v>2399156196</v>
       </c>
-      <c r="G15" s="336">
+      <c r="G15" s="323">
         <v>1752317096</v>
       </c>
-      <c r="H15" s="336">
+      <c r="H15" s="323">
         <v>728536930</v>
       </c>
-      <c r="I15" s="336">
+      <c r="I15" s="323">
         <v>421259471</v>
       </c>
-      <c r="J15" s="336">
+      <c r="J15" s="323">
         <v>326122335</v>
       </c>
-      <c r="K15" s="336">
+      <c r="K15" s="323">
         <v>139941169</v>
       </c>
-      <c r="L15" s="336">
+      <c r="L15" s="323">
         <v>-153552021</v>
       </c>
-      <c r="M15" s="336"/>
+      <c r="M15" s="323"/>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="334">
+      <c r="C16" s="321">
         <v>146792828</v>
       </c>
-      <c r="D16" s="334"/>
-      <c r="E16" s="334"/>
-      <c r="F16" s="334"/>
-      <c r="G16" s="334"/>
-      <c r="H16" s="334"/>
-      <c r="I16" s="334"/>
-      <c r="J16" s="334"/>
-      <c r="K16" s="334"/>
-      <c r="L16" s="334"/>
-      <c r="M16" s="334"/>
+      <c r="D16" s="321"/>
+      <c r="E16" s="321"/>
+      <c r="F16" s="321"/>
+      <c r="G16" s="321"/>
+      <c r="H16" s="321"/>
+      <c r="I16" s="321"/>
+      <c r="J16" s="321"/>
+      <c r="K16" s="321"/>
+      <c r="L16" s="321"/>
+      <c r="M16" s="321"/>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
@@ -6405,171 +6421,171 @@
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C19" s="334">
+      <c r="C19" s="321">
         <v>575917865</v>
       </c>
-      <c r="D19" s="334">
+      <c r="D19" s="321">
         <v>514817738</v>
       </c>
-      <c r="E19" s="334">
+      <c r="E19" s="321">
         <v>504410326</v>
       </c>
-      <c r="F19" s="334">
+      <c r="F19" s="321">
         <v>451827434</v>
       </c>
-      <c r="G19" s="334">
+      <c r="G19" s="321">
         <v>413794059</v>
       </c>
-      <c r="H19" s="334">
+      <c r="H19" s="321">
         <v>174070610</v>
       </c>
-      <c r="I19" s="334">
+      <c r="I19" s="321">
         <v>173632673</v>
       </c>
-      <c r="J19" s="334"/>
-      <c r="K19" s="334"/>
-      <c r="L19" s="334"/>
-      <c r="M19" s="334"/>
+      <c r="J19" s="321"/>
+      <c r="K19" s="321"/>
+      <c r="L19" s="321"/>
+      <c r="M19" s="321"/>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="334"/>
-      <c r="D20" s="334"/>
-      <c r="E20" s="334"/>
-      <c r="F20" s="334"/>
-      <c r="G20" s="334"/>
-      <c r="H20" s="334"/>
-      <c r="I20" s="334"/>
-      <c r="J20" s="334"/>
-      <c r="K20" s="334"/>
-      <c r="L20" s="334"/>
-      <c r="M20" s="334"/>
+      <c r="C20" s="321"/>
+      <c r="D20" s="321"/>
+      <c r="E20" s="321"/>
+      <c r="F20" s="321"/>
+      <c r="G20" s="321"/>
+      <c r="H20" s="321"/>
+      <c r="I20" s="321"/>
+      <c r="J20" s="321"/>
+      <c r="K20" s="321"/>
+      <c r="L20" s="321"/>
+      <c r="M20" s="321"/>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="334"/>
-      <c r="D21" s="334"/>
-      <c r="E21" s="334"/>
-      <c r="F21" s="334"/>
-      <c r="G21" s="334"/>
-      <c r="H21" s="334"/>
-      <c r="I21" s="334"/>
-      <c r="J21" s="334"/>
-      <c r="K21" s="334"/>
-      <c r="L21" s="334"/>
-      <c r="M21" s="334"/>
+      <c r="C21" s="321"/>
+      <c r="D21" s="321"/>
+      <c r="E21" s="321"/>
+      <c r="F21" s="321"/>
+      <c r="G21" s="321"/>
+      <c r="H21" s="321"/>
+      <c r="I21" s="321"/>
+      <c r="J21" s="321"/>
+      <c r="K21" s="321"/>
+      <c r="L21" s="321"/>
+      <c r="M21" s="321"/>
     </row>
     <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>372</v>
       </c>
-      <c r="C22" s="334">
+      <c r="C22" s="321">
         <v>2542046725</v>
       </c>
-      <c r="D22" s="334">
+      <c r="D22" s="321">
         <v>3096948817</v>
       </c>
-      <c r="E22" s="334">
+      <c r="E22" s="321">
         <v>3752648259</v>
       </c>
-      <c r="F22" s="334">
+      <c r="F22" s="321">
         <v>3564787113</v>
       </c>
-      <c r="G22" s="334">
+      <c r="G22" s="321">
         <v>3689730876</v>
       </c>
-      <c r="H22" s="334">
+      <c r="H22" s="321">
         <v>705779861</v>
       </c>
-      <c r="I22" s="334">
+      <c r="I22" s="321">
         <v>744379875</v>
       </c>
-      <c r="J22" s="334">
+      <c r="J22" s="321">
         <v>820031927</v>
       </c>
-      <c r="K22" s="334">
+      <c r="K22" s="321">
         <v>569431362</v>
       </c>
-      <c r="L22" s="334">
+      <c r="L22" s="321">
         <v>448312451</v>
       </c>
-      <c r="M22" s="334"/>
+      <c r="M22" s="321"/>
     </row>
     <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>374</v>
       </c>
-      <c r="C23" s="334">
+      <c r="C23" s="321">
         <v>-633430356</v>
       </c>
-      <c r="D23" s="334">
+      <c r="D23" s="321">
         <v>-1050978857</v>
       </c>
-      <c r="E23" s="334">
+      <c r="E23" s="321">
         <v>-388086486</v>
       </c>
-      <c r="F23" s="334">
+      <c r="F23" s="321">
         <v>-1151748524</v>
       </c>
-      <c r="G23" s="334">
+      <c r="G23" s="321">
         <v>-2804885087</v>
       </c>
-      <c r="H23" s="334">
+      <c r="H23" s="321">
         <v>-22429423</v>
       </c>
-      <c r="I23" s="334">
+      <c r="I23" s="321">
         <v>-17918687</v>
       </c>
-      <c r="J23" s="334">
+      <c r="J23" s="321">
         <v>6460189</v>
       </c>
-      <c r="K23" s="334">
+      <c r="K23" s="321">
         <v>-71411814</v>
       </c>
-      <c r="L23" s="334">
+      <c r="L23" s="321">
         <v>-100881139</v>
       </c>
-      <c r="M23" s="334"/>
+      <c r="M23" s="321"/>
     </row>
     <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>373</v>
       </c>
-      <c r="C24" s="334">
+      <c r="C24" s="321">
         <v>-3527746522</v>
       </c>
-      <c r="D24" s="334">
+      <c r="D24" s="321">
         <v>-2742702995</v>
       </c>
-      <c r="E24" s="334">
+      <c r="E24" s="321">
         <v>-2133485949</v>
       </c>
-      <c r="F24" s="334">
+      <c r="F24" s="321">
         <v>-2013680615</v>
       </c>
-      <c r="G24" s="334">
+      <c r="G24" s="321">
         <v>-587625771</v>
       </c>
-      <c r="H24" s="334">
+      <c r="H24" s="321">
         <v>-398002277</v>
       </c>
-      <c r="I24" s="334">
+      <c r="I24" s="321">
         <v>-448634809</v>
       </c>
-      <c r="J24" s="334">
+      <c r="J24" s="321">
         <v>-405497889</v>
       </c>
-      <c r="K24" s="334">
+      <c r="K24" s="321">
         <v>-449187720</v>
       </c>
-      <c r="L24" s="334">
+      <c r="L24" s="321">
         <v>-252880739</v>
       </c>
-      <c r="M24" s="334"/>
+      <c r="M24" s="321"/>
     </row>
     <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
@@ -6603,186 +6619,186 @@
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="323">
+      <c r="C28" s="318">
         <f>BS!C4</f>
         <v>91009309.849999994</v>
       </c>
-      <c r="D28" s="334">
+      <c r="D28" s="321">
         <v>64628136</v>
       </c>
-      <c r="E28" s="334">
+      <c r="E28" s="321">
         <v>65511539</v>
       </c>
-      <c r="F28" s="334">
+      <c r="F28" s="321">
         <v>109244674</v>
       </c>
-      <c r="G28" s="334">
+      <c r="G28" s="321">
         <v>114510542</v>
       </c>
-      <c r="H28" s="334">
+      <c r="H28" s="321">
         <v>58261577</v>
       </c>
-      <c r="I28" s="334">
+      <c r="I28" s="321">
         <v>67050347</v>
       </c>
-      <c r="J28" s="334">
+      <c r="J28" s="321">
         <v>26764864</v>
       </c>
-      <c r="K28" s="334">
+      <c r="K28" s="321">
         <v>51244805</v>
       </c>
-      <c r="L28" s="334">
+      <c r="L28" s="321">
         <v>61946543</v>
       </c>
-      <c r="M28" s="334"/>
+      <c r="M28" s="321"/>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="323">
+      <c r="C29" s="318">
         <f>BS!C6</f>
         <v>2185835620.7199998</v>
       </c>
-      <c r="D29" s="334">
+      <c r="D29" s="321">
         <v>2100354952</v>
       </c>
-      <c r="E29" s="334">
+      <c r="E29" s="321">
         <v>2166477563</v>
       </c>
-      <c r="F29" s="334">
+      <c r="F29" s="321">
         <v>1886751987</v>
       </c>
-      <c r="G29" s="334">
+      <c r="G29" s="321">
         <v>1420570476</v>
       </c>
-      <c r="H29" s="334">
+      <c r="H29" s="321">
         <v>364381375</v>
       </c>
-      <c r="I29" s="334">
+      <c r="I29" s="321">
         <v>336913911</v>
       </c>
-      <c r="J29" s="334">
+      <c r="J29" s="321">
         <v>631313453</v>
       </c>
-      <c r="K29" s="334">
+      <c r="K29" s="321">
         <v>825981328</v>
       </c>
-      <c r="L29" s="334">
+      <c r="L29" s="321">
         <v>1074501976</v>
       </c>
-      <c r="M29" s="334"/>
+      <c r="M29" s="321"/>
     </row>
     <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="C30" s="324">
+      <c r="C30" s="319">
         <f>BS!C33+BS!C42</f>
         <v>8514681613.9500008</v>
       </c>
-      <c r="D30" s="336">
+      <c r="D30" s="323">
         <v>8734763046</v>
       </c>
-      <c r="E30" s="336">
+      <c r="E30" s="323">
         <v>8874519390</v>
       </c>
-      <c r="F30" s="336">
+      <c r="F30" s="323">
         <v>8404513904</v>
       </c>
-      <c r="G30" s="336">
+      <c r="G30" s="323">
         <v>8026536570</v>
       </c>
-      <c r="H30" s="336">
+      <c r="H30" s="323">
         <v>2003002194</v>
       </c>
-      <c r="I30" s="336">
+      <c r="I30" s="323">
         <v>2135750535</v>
       </c>
-      <c r="J30" s="336">
+      <c r="J30" s="323">
         <v>2340923121</v>
       </c>
-      <c r="K30" s="336">
+      <c r="K30" s="323">
         <v>2123382866</v>
       </c>
-      <c r="L30" s="336">
+      <c r="L30" s="323">
         <v>2502070463</v>
       </c>
-      <c r="M30" s="336"/>
+      <c r="M30" s="323"/>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="324">
+      <c r="C31" s="319">
         <f>BS!G27</f>
         <v>2453658105.4399986</v>
       </c>
-      <c r="D31" s="336">
+      <c r="D31" s="323">
         <v>3652148548</v>
       </c>
-      <c r="E31" s="336">
+      <c r="E31" s="323">
         <v>3623022779</v>
       </c>
-      <c r="F31" s="336">
+      <c r="F31" s="323">
         <v>3128295240</v>
       </c>
-      <c r="G31" s="336">
+      <c r="G31" s="323">
         <v>1568836504</v>
       </c>
-      <c r="H31" s="336">
+      <c r="H31" s="323">
         <v>1511351330</v>
       </c>
-      <c r="I31" s="336">
+      <c r="I31" s="323">
         <v>1161882585</v>
       </c>
-      <c r="J31" s="336">
+      <c r="J31" s="323">
         <v>1165260073</v>
       </c>
-      <c r="K31" s="336">
+      <c r="K31" s="323">
         <v>1242276954</v>
       </c>
-      <c r="L31" s="336">
+      <c r="L31" s="323">
         <v>1219123567</v>
       </c>
-      <c r="M31" s="336"/>
+      <c r="M31" s="323"/>
     </row>
     <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C32" s="323">
+      <c r="C32" s="318">
         <f>BS!G28</f>
         <v>1268437841.4300001</v>
       </c>
-      <c r="D32" s="334">
+      <c r="D32" s="321">
         <v>1511947928</v>
       </c>
-      <c r="E32" s="334">
+      <c r="E32" s="321">
         <v>1566866997</v>
       </c>
-      <c r="F32" s="334">
+      <c r="F32" s="321">
         <v>1373750136</v>
       </c>
-      <c r="G32" s="334">
+      <c r="G32" s="321">
         <v>983547315</v>
       </c>
-      <c r="H32" s="334">
+      <c r="H32" s="321">
         <v>92634421</v>
       </c>
-      <c r="I32" s="334">
+      <c r="I32" s="321">
         <v>16868025</v>
       </c>
-      <c r="J32" s="334">
+      <c r="J32" s="321">
         <v>1596604</v>
       </c>
-      <c r="K32" s="334">
+      <c r="K32" s="321">
         <v>12325253</v>
       </c>
-      <c r="L32" s="334">
+      <c r="L32" s="321">
         <v>77762305</v>
       </c>
-      <c r="M32" s="334"/>
+      <c r="M32" s="321"/>
     </row>
     <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
@@ -6809,47 +6825,47 @@
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="323">
+      <c r="C36" s="318">
         <f t="shared" ref="C36:M36" si="1">IF(C$4="","",C4)</f>
         <v>14644597842</v>
       </c>
-      <c r="D36" s="323">
+      <c r="D36" s="318">
         <f t="shared" si="1"/>
         <v>14814836410</v>
       </c>
-      <c r="E36" s="323">
+      <c r="E36" s="318">
         <f t="shared" si="1"/>
         <v>14039040539</v>
       </c>
-      <c r="F36" s="323">
+      <c r="F36" s="318">
         <f t="shared" si="1"/>
         <v>13119310688</v>
       </c>
-      <c r="G36" s="323">
+      <c r="G36" s="318">
         <f t="shared" si="1"/>
         <v>10941631163</v>
       </c>
-      <c r="H36" s="323">
+      <c r="H36" s="318">
         <f t="shared" si="1"/>
         <v>3581923735</v>
       </c>
-      <c r="I36" s="323">
+      <c r="I36" s="318">
         <f t="shared" si="1"/>
         <v>3467335930</v>
       </c>
-      <c r="J36" s="323">
+      <c r="J36" s="318">
         <f t="shared" si="1"/>
         <v>3175519522</v>
       </c>
-      <c r="K36" s="323">
+      <c r="K36" s="318">
         <f t="shared" si="1"/>
         <v>3195921516</v>
       </c>
-      <c r="L36" s="323">
+      <c r="L36" s="318">
         <f t="shared" si="1"/>
         <v>3323745278</v>
       </c>
-      <c r="M36" s="323" t="str">
+      <c r="M36" s="318" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6858,47 +6874,47 @@
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="C37" s="323">
+      <c r="C37" s="318">
         <f t="shared" ref="C37:M37" si="2">IF(C$4="","",-C5)</f>
         <v>-8483123346</v>
       </c>
-      <c r="D37" s="323">
+      <c r="D37" s="318">
         <f t="shared" si="2"/>
         <v>-8491525016</v>
       </c>
-      <c r="E37" s="323">
+      <c r="E37" s="318">
         <f t="shared" si="2"/>
         <v>-7873287284</v>
       </c>
-      <c r="F37" s="323">
+      <c r="F37" s="318">
         <f t="shared" si="2"/>
         <v>-7328418046</v>
       </c>
-      <c r="G37" s="323">
+      <c r="G37" s="318">
         <f t="shared" si="2"/>
         <v>-6166079008</v>
       </c>
-      <c r="H37" s="323">
+      <c r="H37" s="318">
         <f t="shared" si="2"/>
         <v>-2359127300</v>
       </c>
-      <c r="I37" s="323">
+      <c r="I37" s="318">
         <f t="shared" si="2"/>
         <v>-2362728713</v>
       </c>
-      <c r="J37" s="323">
+      <c r="J37" s="318">
         <f t="shared" si="2"/>
         <v>-2190920673</v>
       </c>
-      <c r="K37" s="323">
+      <c r="K37" s="318">
         <f t="shared" si="2"/>
         <v>-2209433704</v>
       </c>
-      <c r="L37" s="323">
+      <c r="L37" s="318">
         <f t="shared" si="2"/>
         <v>-2369740058</v>
       </c>
-      <c r="M37" s="323" t="str">
+      <c r="M37" s="318" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -6907,47 +6923,47 @@
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="C38" s="319">
+      <c r="C38" s="317">
         <f>IF(C36="","",C36+C37)</f>
         <v>6161474496</v>
       </c>
-      <c r="D38" s="319">
+      <c r="D38" s="317">
         <f t="shared" ref="D38" si="3">IF(D36="","",D36+D37)</f>
         <v>6323311394</v>
       </c>
-      <c r="E38" s="319">
+      <c r="E38" s="317">
         <f t="shared" ref="E38" si="4">IF(E36="","",E36+E37)</f>
         <v>6165753255</v>
       </c>
-      <c r="F38" s="319">
+      <c r="F38" s="317">
         <f t="shared" ref="F38" si="5">IF(F36="","",F36+F37)</f>
         <v>5790892642</v>
       </c>
-      <c r="G38" s="319">
+      <c r="G38" s="317">
         <f t="shared" ref="G38" si="6">IF(G36="","",G36+G37)</f>
         <v>4775552155</v>
       </c>
-      <c r="H38" s="319">
+      <c r="H38" s="317">
         <f t="shared" ref="H38" si="7">IF(H36="","",H36+H37)</f>
         <v>1222796435</v>
       </c>
-      <c r="I38" s="319">
+      <c r="I38" s="317">
         <f t="shared" ref="I38" si="8">IF(I36="","",I36+I37)</f>
         <v>1104607217</v>
       </c>
-      <c r="J38" s="319">
+      <c r="J38" s="317">
         <f t="shared" ref="J38" si="9">IF(J36="","",J36+J37)</f>
         <v>984598849</v>
       </c>
-      <c r="K38" s="319">
+      <c r="K38" s="317">
         <f t="shared" ref="K38" si="10">IF(K36="","",K36+K37)</f>
         <v>986487812</v>
       </c>
-      <c r="L38" s="319">
+      <c r="L38" s="317">
         <f t="shared" ref="L38" si="11">IF(L36="","",L36+L37)</f>
         <v>954005220</v>
       </c>
-      <c r="M38" s="319" t="str">
+      <c r="M38" s="317" t="str">
         <f t="shared" ref="M38" si="12">IF(M36="","",M36+M37)</f>
         <v/>
       </c>
@@ -6956,47 +6972,47 @@
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="C39" s="323">
+      <c r="C39" s="318">
         <f t="shared" ref="C39:M39" si="13">IF(C$4="","",-C6)</f>
         <v>-3029595871</v>
       </c>
-      <c r="D39" s="323">
+      <c r="D39" s="318">
         <f t="shared" si="13"/>
         <v>-3027292571</v>
       </c>
-      <c r="E39" s="323">
+      <c r="E39" s="318">
         <f t="shared" si="13"/>
         <v>-2860787576</v>
       </c>
-      <c r="F39" s="323">
+      <c r="F39" s="318">
         <f t="shared" si="13"/>
         <v>-2729771806</v>
       </c>
-      <c r="G39" s="323">
+      <c r="G39" s="318">
         <f t="shared" si="13"/>
         <v>-2988418106</v>
       </c>
-      <c r="H39" s="323">
+      <c r="H39" s="318">
         <f t="shared" si="13"/>
         <v>-654203552</v>
       </c>
-      <c r="I39" s="323">
+      <c r="I39" s="318">
         <f t="shared" si="13"/>
         <v>-609225228</v>
       </c>
-      <c r="J39" s="323">
+      <c r="J39" s="318">
         <f t="shared" si="13"/>
         <v>-620936767</v>
       </c>
-      <c r="K39" s="323">
+      <c r="K39" s="318">
         <f t="shared" si="13"/>
         <v>-629182097</v>
       </c>
-      <c r="L39" s="323">
+      <c r="L39" s="318">
         <f t="shared" si="13"/>
         <v>-722526234</v>
       </c>
-      <c r="M39" s="323" t="str">
+      <c r="M39" s="318" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
@@ -7005,47 +7021,47 @@
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="C40" s="333">
+      <c r="C40" s="320">
         <f t="shared" ref="C40:M40" si="14">IF(C$4="","",-C7)</f>
         <v>-2512653717</v>
       </c>
-      <c r="D40" s="333">
+      <c r="D40" s="320">
         <f t="shared" si="14"/>
         <v>-2532621833</v>
       </c>
-      <c r="E40" s="333">
+      <c r="E40" s="320">
         <f t="shared" si="14"/>
         <v>-2326217227</v>
       </c>
-      <c r="F40" s="333">
+      <c r="F40" s="320">
         <f t="shared" si="14"/>
         <v>-2212894661</v>
       </c>
-      <c r="G40" s="333">
+      <c r="G40" s="320">
         <f t="shared" si="14"/>
         <v>-2304313181</v>
       </c>
-      <c r="H40" s="333">
+      <c r="H40" s="320">
         <f t="shared" si="14"/>
         <v>-492206624</v>
       </c>
-      <c r="I40" s="333">
+      <c r="I40" s="320">
         <f t="shared" si="14"/>
         <v>-455284418</v>
       </c>
-      <c r="J40" s="333">
+      <c r="J40" s="320">
         <f t="shared" si="14"/>
         <v>-465218537</v>
       </c>
-      <c r="K40" s="333">
+      <c r="K40" s="320">
         <f t="shared" si="14"/>
         <v>-445553542</v>
       </c>
-      <c r="L40" s="333">
+      <c r="L40" s="320">
         <f t="shared" si="14"/>
         <v>-489868548</v>
       </c>
-      <c r="M40" s="333" t="str">
+      <c r="M40" s="320" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -7054,47 +7070,47 @@
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="333">
+      <c r="C41" s="320">
         <f>IF(C$4="","",C39-C40)</f>
         <v>-516942154</v>
       </c>
-      <c r="D41" s="333">
+      <c r="D41" s="320">
         <f t="shared" ref="D41:M41" si="15">IF(D$4="","",D39-D40)</f>
         <v>-494670738</v>
       </c>
-      <c r="E41" s="333">
+      <c r="E41" s="320">
         <f t="shared" si="15"/>
         <v>-534570349</v>
       </c>
-      <c r="F41" s="333">
+      <c r="F41" s="320">
         <f t="shared" si="15"/>
         <v>-516877145</v>
       </c>
-      <c r="G41" s="333">
+      <c r="G41" s="320">
         <f t="shared" si="15"/>
         <v>-684104925</v>
       </c>
-      <c r="H41" s="333">
+      <c r="H41" s="320">
         <f t="shared" si="15"/>
         <v>-161996928</v>
       </c>
-      <c r="I41" s="333">
+      <c r="I41" s="320">
         <f t="shared" si="15"/>
         <v>-153940810</v>
       </c>
-      <c r="J41" s="333">
+      <c r="J41" s="320">
         <f t="shared" si="15"/>
         <v>-155718230</v>
       </c>
-      <c r="K41" s="333">
+      <c r="K41" s="320">
         <f t="shared" si="15"/>
         <v>-183628555</v>
       </c>
-      <c r="L41" s="333">
+      <c r="L41" s="320">
         <f t="shared" si="15"/>
         <v>-232657686</v>
       </c>
-      <c r="M41" s="333" t="str">
+      <c r="M41" s="320" t="str">
         <f t="shared" si="15"/>
         <v/>
       </c>
@@ -7103,47 +7119,47 @@
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
-      <c r="C42" s="323">
+      <c r="C42" s="318">
         <f t="shared" ref="C42:M42" si="16">IF(C$4="","",-C8)</f>
         <v>-22666046</v>
       </c>
-      <c r="D42" s="323">
+      <c r="D42" s="318">
         <f t="shared" si="16"/>
         <v>-26232056</v>
       </c>
-      <c r="E42" s="323">
+      <c r="E42" s="318">
         <f t="shared" si="16"/>
         <v>-110747936</v>
       </c>
-      <c r="F42" s="323">
+      <c r="F42" s="318">
         <f t="shared" si="16"/>
         <v>-163151285</v>
       </c>
-      <c r="G42" s="323">
+      <c r="G42" s="318">
         <f t="shared" si="16"/>
         <v>-84212617</v>
       </c>
-      <c r="H42" s="323">
+      <c r="H42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I42" s="323">
+      <c r="I42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="J42" s="323">
+      <c r="J42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K42" s="323">
+      <c r="K42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="L42" s="323">
+      <c r="L42" s="318">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="M42" s="323" t="str">
+      <c r="M42" s="318" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
@@ -7152,47 +7168,47 @@
       <c r="B43" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="C43" s="324">
+      <c r="C43" s="319">
         <f>IF(C$4="","",C38+C39+C42)</f>
         <v>3109212579</v>
       </c>
-      <c r="D43" s="324">
+      <c r="D43" s="319">
         <f t="shared" ref="D43:M43" si="17">IF(D$4="","",D38+D39+D42)</f>
         <v>3269786767</v>
       </c>
-      <c r="E43" s="324">
+      <c r="E43" s="319">
         <f t="shared" si="17"/>
         <v>3194217743</v>
       </c>
-      <c r="F43" s="324">
+      <c r="F43" s="319">
         <f t="shared" si="17"/>
         <v>2897969551</v>
       </c>
-      <c r="G43" s="324">
+      <c r="G43" s="319">
         <f t="shared" si="17"/>
         <v>1702921432</v>
       </c>
-      <c r="H43" s="324">
+      <c r="H43" s="319">
         <f t="shared" si="17"/>
         <v>568592883</v>
       </c>
-      <c r="I43" s="324">
+      <c r="I43" s="319">
         <f t="shared" si="17"/>
         <v>495381989</v>
       </c>
-      <c r="J43" s="324">
+      <c r="J43" s="319">
         <f t="shared" si="17"/>
         <v>363662082</v>
       </c>
-      <c r="K43" s="324">
+      <c r="K43" s="319">
         <f t="shared" si="17"/>
         <v>357305715</v>
       </c>
-      <c r="L43" s="324">
+      <c r="L43" s="319">
         <f t="shared" si="17"/>
         <v>231478986</v>
       </c>
-      <c r="M43" s="324" t="str">
+      <c r="M43" s="319" t="str">
         <f t="shared" si="17"/>
         <v/>
       </c>
@@ -7299,47 +7315,47 @@
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="C46" s="323">
+      <c r="C46" s="318">
         <f t="shared" ref="C46:M46" si="20">IF(C$4="","",-C14)</f>
         <v>-670547120</v>
       </c>
-      <c r="D46" s="323">
+      <c r="D46" s="318">
         <f t="shared" si="20"/>
         <v>-664121997</v>
       </c>
-      <c r="E46" s="323">
+      <c r="E46" s="318">
         <f t="shared" si="20"/>
         <v>-711879179</v>
       </c>
-      <c r="F46" s="323">
+      <c r="F46" s="318">
         <f t="shared" si="20"/>
         <v>-541923819</v>
       </c>
-      <c r="G46" s="323">
+      <c r="G46" s="318">
         <f t="shared" si="20"/>
         <v>-378467716</v>
       </c>
-      <c r="H46" s="323">
+      <c r="H46" s="318">
         <f t="shared" si="20"/>
         <v>-98780687</v>
       </c>
-      <c r="I46" s="323">
+      <c r="I46" s="318">
         <f t="shared" si="20"/>
         <v>-61018006</v>
       </c>
-      <c r="J46" s="323">
+      <c r="J46" s="318">
         <f t="shared" si="20"/>
         <v>-18873927</v>
       </c>
-      <c r="K46" s="323">
+      <c r="K46" s="318">
         <f t="shared" si="20"/>
         <v>-16833271</v>
       </c>
-      <c r="L46" s="323">
+      <c r="L46" s="318">
         <f t="shared" si="20"/>
         <v>-42979625</v>
       </c>
-      <c r="M46" s="323" t="str">
+      <c r="M46" s="318" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -7348,47 +7364,47 @@
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="324">
+      <c r="C47" s="319">
         <f t="shared" ref="C47:M47" si="21">IF(C$4="","",C15)</f>
         <v>2249380492</v>
       </c>
-      <c r="D47" s="324">
+      <c r="D47" s="319">
         <f t="shared" si="21"/>
         <v>2711568555</v>
       </c>
-      <c r="E47" s="324">
+      <c r="E47" s="319">
         <f t="shared" si="21"/>
         <v>2586899641</v>
       </c>
-      <c r="F47" s="324">
+      <c r="F47" s="319">
         <f t="shared" si="21"/>
         <v>2399156196</v>
       </c>
-      <c r="G47" s="324">
+      <c r="G47" s="319">
         <f t="shared" si="21"/>
         <v>1752317096</v>
       </c>
-      <c r="H47" s="324">
+      <c r="H47" s="319">
         <f t="shared" si="21"/>
         <v>728536930</v>
       </c>
-      <c r="I47" s="324">
+      <c r="I47" s="319">
         <f t="shared" si="21"/>
         <v>421259471</v>
       </c>
-      <c r="J47" s="324">
+      <c r="J47" s="319">
         <f t="shared" si="21"/>
         <v>326122335</v>
       </c>
-      <c r="K47" s="324">
+      <c r="K47" s="319">
         <f t="shared" si="21"/>
         <v>139941169</v>
       </c>
-      <c r="L47" s="324">
+      <c r="L47" s="319">
         <f t="shared" si="21"/>
         <v>-153552021</v>
       </c>
-      <c r="M47" s="324" t="str">
+      <c r="M47" s="319" t="str">
         <f t="shared" si="21"/>
         <v/>
       </c>
@@ -7397,47 +7413,47 @@
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="323">
+      <c r="C48" s="318">
         <f t="shared" ref="C48:M48" si="22">IF(C$4="","",MIN(-C16,0))</f>
         <v>-146792828</v>
       </c>
-      <c r="D48" s="323">
+      <c r="D48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="E48" s="323">
+      <c r="E48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="F48" s="323">
+      <c r="F48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="G48" s="323">
+      <c r="G48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="H48" s="323">
+      <c r="H48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I48" s="323">
+      <c r="I48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J48" s="323">
+      <c r="J48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K48" s="323">
+      <c r="K48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L48" s="323">
+      <c r="L48" s="318">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="M48" s="323" t="str">
+      <c r="M48" s="318" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -7451,47 +7467,47 @@
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
-      <c r="C51" s="323">
+      <c r="C51" s="318">
         <f t="shared" ref="C51:M51" si="23">IF(C$4="","",-C12)</f>
         <v>-7672861</v>
       </c>
-      <c r="D51" s="323">
+      <c r="D51" s="318">
         <f t="shared" si="23"/>
         <v>-5921669</v>
       </c>
-      <c r="E51" s="323">
+      <c r="E51" s="318">
         <f t="shared" si="23"/>
         <v>-3696844</v>
       </c>
-      <c r="F51" s="323">
+      <c r="F51" s="318">
         <f t="shared" si="23"/>
         <v>-14186775</v>
       </c>
-      <c r="G51" s="323">
+      <c r="G51" s="318">
         <f t="shared" si="23"/>
         <v>-35823675</v>
       </c>
-      <c r="H51" s="323">
+      <c r="H51" s="318">
         <f t="shared" si="23"/>
         <v>-10770646</v>
       </c>
-      <c r="I51" s="323">
+      <c r="I51" s="318">
         <f t="shared" si="23"/>
         <v>-12333775</v>
       </c>
-      <c r="J51" s="323">
+      <c r="J51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="K51" s="323">
+      <c r="K51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="L51" s="323">
+      <c r="L51" s="318">
         <f t="shared" si="23"/>
         <v>0</v>
       </c>
-      <c r="M51" s="323" t="str">
+      <c r="M51" s="318" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -7500,47 +7516,47 @@
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C52" s="323">
+      <c r="C52" s="318">
         <f t="shared" ref="C52:M52" si="24">IF(C$4="","",C13)</f>
         <v>41044772</v>
       </c>
-      <c r="D52" s="323">
+      <c r="D52" s="318">
         <f t="shared" si="24"/>
         <v>71308016</v>
       </c>
-      <c r="E52" s="323">
+      <c r="E52" s="318">
         <f t="shared" si="24"/>
         <v>65718589</v>
       </c>
-      <c r="F52" s="323">
+      <c r="F52" s="318">
         <f t="shared" si="24"/>
         <v>36050786</v>
       </c>
-      <c r="G52" s="323">
+      <c r="G52" s="318">
         <f t="shared" si="24"/>
         <v>44443082</v>
       </c>
-      <c r="H52" s="323">
+      <c r="H52" s="318">
         <f t="shared" si="24"/>
         <v>8582394</v>
       </c>
-      <c r="I52" s="323">
+      <c r="I52" s="318">
         <f t="shared" si="24"/>
         <v>6609967</v>
       </c>
-      <c r="J52" s="323">
+      <c r="J52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="K52" s="323">
+      <c r="K52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="L52" s="323">
+      <c r="L52" s="318">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="M52" s="323" t="str">
+      <c r="M52" s="318" t="str">
         <f t="shared" si="24"/>
         <v/>
       </c>
@@ -7756,47 +7772,47 @@
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C61" s="323">
+      <c r="C61" s="318">
         <f>IF(C$4="","",-C19)</f>
         <v>-575917865</v>
       </c>
-      <c r="D61" s="323">
+      <c r="D61" s="318">
         <f t="shared" ref="D61:M61" si="29">IF(D$4="","",-D19)</f>
         <v>-514817738</v>
       </c>
-      <c r="E61" s="323">
+      <c r="E61" s="318">
         <f t="shared" si="29"/>
         <v>-504410326</v>
       </c>
-      <c r="F61" s="323">
+      <c r="F61" s="318">
         <f t="shared" si="29"/>
         <v>-451827434</v>
       </c>
-      <c r="G61" s="323">
+      <c r="G61" s="318">
         <f t="shared" si="29"/>
         <v>-413794059</v>
       </c>
-      <c r="H61" s="323">
+      <c r="H61" s="318">
         <f t="shared" si="29"/>
         <v>-174070610</v>
       </c>
-      <c r="I61" s="323">
+      <c r="I61" s="318">
         <f t="shared" si="29"/>
         <v>-173632673</v>
       </c>
-      <c r="J61" s="323">
+      <c r="J61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="K61" s="323">
+      <c r="K61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="L61" s="323">
+      <c r="L61" s="318">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="M61" s="323" t="str">
+      <c r="M61" s="318" t="str">
         <f t="shared" si="29"/>
         <v/>
       </c>
@@ -7805,47 +7821,47 @@
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C62" s="323">
+      <c r="C62" s="318">
         <f>IF(C$4="","",IF(C20=0,C61,-C20))</f>
         <v>-575917865</v>
       </c>
-      <c r="D62" s="323">
+      <c r="D62" s="318">
         <f t="shared" ref="D62:M62" si="30">IF(D$4="","",IF(D20=0,D61,-D20))</f>
         <v>-514817738</v>
       </c>
-      <c r="E62" s="323">
+      <c r="E62" s="318">
         <f t="shared" si="30"/>
         <v>-504410326</v>
       </c>
-      <c r="F62" s="323">
+      <c r="F62" s="318">
         <f t="shared" si="30"/>
         <v>-451827434</v>
       </c>
-      <c r="G62" s="323">
+      <c r="G62" s="318">
         <f t="shared" si="30"/>
         <v>-413794059</v>
       </c>
-      <c r="H62" s="323">
+      <c r="H62" s="318">
         <f t="shared" si="30"/>
         <v>-174070610</v>
       </c>
-      <c r="I62" s="323">
+      <c r="I62" s="318">
         <f t="shared" si="30"/>
         <v>-173632673</v>
       </c>
-      <c r="J62" s="323">
+      <c r="J62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="K62" s="323">
+      <c r="K62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="L62" s="323">
+      <c r="L62" s="318">
         <f t="shared" si="30"/>
         <v>0</v>
       </c>
-      <c r="M62" s="323" t="str">
+      <c r="M62" s="318" t="str">
         <f t="shared" si="30"/>
         <v/>
       </c>
@@ -7854,47 +7870,47 @@
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C63" s="323">
+      <c r="C63" s="318">
         <f>IF(C$4="","",-C21)</f>
         <v>0</v>
       </c>
-      <c r="D63" s="323">
+      <c r="D63" s="318">
         <f t="shared" ref="D63:M63" si="31">IF(D$4="","",-D21)</f>
         <v>0</v>
       </c>
-      <c r="E63" s="323">
+      <c r="E63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="F63" s="323">
+      <c r="F63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="G63" s="323">
+      <c r="G63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="H63" s="323">
+      <c r="H63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="I63" s="323">
+      <c r="I63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="J63" s="323">
+      <c r="J63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="K63" s="323">
+      <c r="K63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="L63" s="323">
+      <c r="L63" s="318">
         <f t="shared" si="31"/>
         <v>0</v>
       </c>
-      <c r="M63" s="323" t="str">
+      <c r="M63" s="318" t="str">
         <f t="shared" si="31"/>
         <v/>
       </c>
@@ -7903,47 +7919,47 @@
       <c r="B64" s="27" t="s">
         <v>394</v>
       </c>
-      <c r="C64" s="323">
+      <c r="C64" s="318">
         <f>IF(C$4="","",C22+C23+C24)</f>
         <v>-1619130153</v>
       </c>
-      <c r="D64" s="323">
+      <c r="D64" s="318">
         <f t="shared" ref="D64:M64" si="32">IF(D$4="","",D22+D23+D24)</f>
         <v>-696733035</v>
       </c>
-      <c r="E64" s="323">
+      <c r="E64" s="318">
         <f t="shared" si="32"/>
         <v>1231075824</v>
       </c>
-      <c r="F64" s="323">
+      <c r="F64" s="318">
         <f t="shared" si="32"/>
         <v>399357974</v>
       </c>
-      <c r="G64" s="323">
+      <c r="G64" s="318">
         <f t="shared" si="32"/>
         <v>297220018</v>
       </c>
-      <c r="H64" s="323">
+      <c r="H64" s="318">
         <f t="shared" si="32"/>
         <v>285348161</v>
       </c>
-      <c r="I64" s="323">
+      <c r="I64" s="318">
         <f t="shared" si="32"/>
         <v>277826379</v>
       </c>
-      <c r="J64" s="323">
+      <c r="J64" s="318">
         <f t="shared" si="32"/>
         <v>420994227</v>
       </c>
-      <c r="K64" s="323">
+      <c r="K64" s="318">
         <f t="shared" si="32"/>
         <v>48831828</v>
       </c>
-      <c r="L64" s="323">
+      <c r="L64" s="318">
         <f t="shared" si="32"/>
         <v>94550573</v>
       </c>
-      <c r="M64" s="323" t="str">
+      <c r="M64" s="318" t="str">
         <f t="shared" si="32"/>
         <v/>
       </c>
@@ -8325,115 +8341,115 @@
       <c r="B77" s="93" t="s">
         <v>86</v>
       </c>
-      <c r="C77" s="333">
+      <c r="C77" s="320">
         <f t="shared" ref="C77:H78" si="40">IF(C$4="","",C28)</f>
         <v>91009309.849999994</v>
       </c>
-      <c r="D77" s="333">
+      <c r="D77" s="320">
         <f t="shared" si="40"/>
         <v>64628136</v>
       </c>
-      <c r="E77" s="333">
+      <c r="E77" s="320">
         <f t="shared" si="40"/>
         <v>65511539</v>
       </c>
-      <c r="F77" s="333">
+      <c r="F77" s="320">
         <f t="shared" si="40"/>
         <v>109244674</v>
       </c>
-      <c r="G77" s="333">
+      <c r="G77" s="320">
         <f t="shared" si="40"/>
         <v>114510542</v>
       </c>
-      <c r="H77" s="333">
+      <c r="H77" s="320">
         <f t="shared" si="40"/>
         <v>58261577</v>
       </c>
-      <c r="I77" s="337"/>
-      <c r="J77" s="337"/>
-      <c r="K77" s="337"/>
-      <c r="L77" s="337"/>
-      <c r="M77" s="337"/>
+      <c r="I77" s="324"/>
+      <c r="J77" s="324"/>
+      <c r="K77" s="324"/>
+      <c r="L77" s="324"/>
+      <c r="M77" s="324"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>87</v>
       </c>
-      <c r="C78" s="333">
+      <c r="C78" s="320">
         <f t="shared" si="40"/>
         <v>2185835620.7199998</v>
       </c>
-      <c r="D78" s="333">
+      <c r="D78" s="320">
         <f t="shared" si="40"/>
         <v>2100354952</v>
       </c>
-      <c r="E78" s="333">
+      <c r="E78" s="320">
         <f t="shared" si="40"/>
         <v>2166477563</v>
       </c>
-      <c r="F78" s="333">
+      <c r="F78" s="320">
         <f t="shared" si="40"/>
         <v>1886751987</v>
       </c>
-      <c r="G78" s="333">
+      <c r="G78" s="320">
         <f t="shared" si="40"/>
         <v>1420570476</v>
       </c>
-      <c r="H78" s="333">
+      <c r="H78" s="320">
         <f t="shared" si="40"/>
         <v>364381375</v>
       </c>
-      <c r="I78" s="337"/>
-      <c r="J78" s="337"/>
-      <c r="K78" s="337"/>
-      <c r="L78" s="337"/>
-      <c r="M78" s="337"/>
+      <c r="I78" s="324"/>
+      <c r="J78" s="324"/>
+      <c r="K78" s="324"/>
+      <c r="L78" s="324"/>
+      <c r="M78" s="324"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C79" s="323">
+      <c r="C79" s="318">
         <f t="shared" ref="C79:M79" si="41">IF(C$4="","",C30)</f>
         <v>8514681613.9500008</v>
       </c>
-      <c r="D79" s="323">
+      <c r="D79" s="318">
         <f t="shared" si="41"/>
         <v>8734763046</v>
       </c>
-      <c r="E79" s="323">
+      <c r="E79" s="318">
         <f t="shared" si="41"/>
         <v>8874519390</v>
       </c>
-      <c r="F79" s="323">
+      <c r="F79" s="318">
         <f t="shared" si="41"/>
         <v>8404513904</v>
       </c>
-      <c r="G79" s="323">
+      <c r="G79" s="318">
         <f t="shared" si="41"/>
         <v>8026536570</v>
       </c>
-      <c r="H79" s="323">
+      <c r="H79" s="318">
         <f t="shared" si="41"/>
         <v>2003002194</v>
       </c>
-      <c r="I79" s="323">
+      <c r="I79" s="318">
         <f t="shared" si="41"/>
         <v>2135750535</v>
       </c>
-      <c r="J79" s="323">
+      <c r="J79" s="318">
         <f t="shared" si="41"/>
         <v>2340923121</v>
       </c>
-      <c r="K79" s="323">
+      <c r="K79" s="318">
         <f t="shared" si="41"/>
         <v>2123382866</v>
       </c>
-      <c r="L79" s="323">
+      <c r="L79" s="318">
         <f t="shared" si="41"/>
         <v>2502070463</v>
       </c>
-      <c r="M79" s="323" t="str">
+      <c r="M79" s="318" t="str">
         <f t="shared" si="41"/>
         <v/>
       </c>
@@ -8442,47 +8458,47 @@
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C80" s="323">
+      <c r="C80" s="318">
         <f t="shared" ref="C80:M80" si="42">IF(C$4="","",C31)</f>
         <v>2453658105.4399986</v>
       </c>
-      <c r="D80" s="323">
+      <c r="D80" s="318">
         <f t="shared" si="42"/>
         <v>3652148548</v>
       </c>
-      <c r="E80" s="323">
+      <c r="E80" s="318">
         <f t="shared" si="42"/>
         <v>3623022779</v>
       </c>
-      <c r="F80" s="323">
+      <c r="F80" s="318">
         <f t="shared" si="42"/>
         <v>3128295240</v>
       </c>
-      <c r="G80" s="323">
+      <c r="G80" s="318">
         <f t="shared" si="42"/>
         <v>1568836504</v>
       </c>
-      <c r="H80" s="323">
+      <c r="H80" s="318">
         <f t="shared" si="42"/>
         <v>1511351330</v>
       </c>
-      <c r="I80" s="323">
+      <c r="I80" s="318">
         <f t="shared" si="42"/>
         <v>1161882585</v>
       </c>
-      <c r="J80" s="323">
+      <c r="J80" s="318">
         <f t="shared" si="42"/>
         <v>1165260073</v>
       </c>
-      <c r="K80" s="323">
+      <c r="K80" s="318">
         <f t="shared" si="42"/>
         <v>1242276954</v>
       </c>
-      <c r="L80" s="323">
+      <c r="L80" s="318">
         <f t="shared" si="42"/>
         <v>1219123567</v>
       </c>
-      <c r="M80" s="323" t="str">
+      <c r="M80" s="318" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -9566,11 +9582,11 @@
       <c r="B73" s="105" t="s">
         <v>318</v>
       </c>
-      <c r="C73" s="76">
+      <c r="C73" s="355">
         <f>(Normalized_FCF!G25+Normalized_FCF!G35-Normalized_FCF!G91)/12</f>
         <v>-1058076344.85</v>
       </c>
-      <c r="D73" s="76">
+      <c r="D73" s="355">
         <f>(Normalized_FCF!C25+Normalized_FCF!C35-Normalized_FCF!C91)/12</f>
         <v>-1029855178.187616</v>
       </c>
@@ -9598,8 +9614,8 @@
       <c r="B75" s="80" t="s">
         <v>321</v>
       </c>
-      <c r="C75" s="341"/>
-      <c r="D75" s="342">
+      <c r="C75" s="326"/>
+      <c r="D75" s="327">
         <f>MAX(-D73*D76,G5)</f>
         <v>1029855178.187616</v>
       </c>
@@ -9903,54 +9919,54 @@
       <c r="B4" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="317">
+      <c r="C4" s="333">
         <f>AVERAGE(G4:J4)</f>
         <v>14154446369.75</v>
       </c>
       <c r="D4" s="57"/>
       <c r="E4" s="266"/>
       <c r="F4" s="57"/>
-      <c r="G4" s="323">
+      <c r="G4" s="339">
         <f>Data!C36</f>
         <v>14644597842</v>
       </c>
-      <c r="H4" s="323">
+      <c r="H4" s="339">
         <f>Data!D36</f>
         <v>14814836410</v>
       </c>
-      <c r="I4" s="323">
+      <c r="I4" s="339">
         <f>Data!E36</f>
         <v>14039040539</v>
       </c>
-      <c r="J4" s="323">
+      <c r="J4" s="339">
         <f>Data!F36</f>
         <v>13119310688</v>
       </c>
-      <c r="K4" s="323">
+      <c r="K4" s="339">
         <f>Data!G36</f>
         <v>10941631163</v>
       </c>
-      <c r="L4" s="323">
+      <c r="L4" s="339">
         <f>Data!H36</f>
         <v>3581923735</v>
       </c>
-      <c r="M4" s="323">
+      <c r="M4" s="339">
         <f>Data!I36</f>
         <v>3467335930</v>
       </c>
-      <c r="N4" s="323">
+      <c r="N4" s="339">
         <f>Data!J36</f>
         <v>3175519522</v>
       </c>
-      <c r="O4" s="323">
+      <c r="O4" s="339">
         <f>Data!K36</f>
         <v>3195921516</v>
       </c>
-      <c r="P4" s="323">
+      <c r="P4" s="339">
         <f>Data!L36</f>
         <v>3323745278</v>
       </c>
-      <c r="Q4" s="323" t="str">
+      <c r="Q4" s="339" t="str">
         <f>Data!M36</f>
         <v/>
       </c>
@@ -9960,52 +9976,52 @@
       <c r="B5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="318">
+      <c r="C5" s="334">
         <f>C25</f>
         <v>-10627750820.551392</v>
       </c>
       <c r="E5" s="268"/>
-      <c r="G5" s="323">
+      <c r="G5" s="339">
         <f t="shared" ref="G5:Q5" si="1">G25</f>
         <v>-10995777063</v>
       </c>
-      <c r="H5" s="323">
+      <c r="H5" s="339">
         <f t="shared" si="1"/>
         <v>-11024146849</v>
       </c>
-      <c r="I5" s="323">
+      <c r="I5" s="339">
         <f t="shared" si="1"/>
         <v>-10199504511</v>
       </c>
-      <c r="J5" s="323">
+      <c r="J5" s="339">
         <f t="shared" si="1"/>
         <v>-9541312707</v>
       </c>
-      <c r="K5" s="323">
+      <c r="K5" s="339">
         <f t="shared" si="1"/>
         <v>-8470392189</v>
       </c>
-      <c r="L5" s="323">
+      <c r="L5" s="339">
         <f t="shared" si="1"/>
         <v>-2851333924</v>
       </c>
-      <c r="M5" s="323">
+      <c r="M5" s="339">
         <f t="shared" si="1"/>
         <v>-2818013131</v>
       </c>
-      <c r="N5" s="323">
+      <c r="N5" s="339">
         <f t="shared" si="1"/>
         <v>-2656139210</v>
       </c>
-      <c r="O5" s="323">
+      <c r="O5" s="339">
         <f t="shared" si="1"/>
         <v>-2654987246</v>
       </c>
-      <c r="P5" s="323">
+      <c r="P5" s="339">
         <f t="shared" si="1"/>
         <v>-2859608606</v>
       </c>
-      <c r="Q5" s="323" t="str">
+      <c r="Q5" s="339" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10015,52 +10031,52 @@
       <c r="B6" s="31" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="319">
+      <c r="C6" s="335">
         <f>C4+C5</f>
         <v>3526695549.1986084</v>
       </c>
       <c r="E6" s="268"/>
-      <c r="G6" s="319">
+      <c r="G6" s="335">
         <f>IF(G4="","",G4+G5)</f>
         <v>3648820779</v>
       </c>
-      <c r="H6" s="319">
+      <c r="H6" s="335">
         <f t="shared" ref="H6:Q6" si="2">IF(H4="","",H4+H5)</f>
         <v>3790689561</v>
       </c>
-      <c r="I6" s="319">
+      <c r="I6" s="335">
         <f t="shared" si="2"/>
         <v>3839536028</v>
       </c>
-      <c r="J6" s="319">
+      <c r="J6" s="335">
         <f t="shared" si="2"/>
         <v>3577997981</v>
       </c>
-      <c r="K6" s="319">
+      <c r="K6" s="335">
         <f t="shared" si="2"/>
         <v>2471238974</v>
       </c>
-      <c r="L6" s="319">
+      <c r="L6" s="335">
         <f t="shared" si="2"/>
         <v>730589811</v>
       </c>
-      <c r="M6" s="319">
+      <c r="M6" s="335">
         <f t="shared" si="2"/>
         <v>649322799</v>
       </c>
-      <c r="N6" s="319">
+      <c r="N6" s="335">
         <f t="shared" si="2"/>
         <v>519380312</v>
       </c>
-      <c r="O6" s="319">
+      <c r="O6" s="335">
         <f t="shared" si="2"/>
         <v>540934270</v>
       </c>
-      <c r="P6" s="319">
+      <c r="P6" s="335">
         <f t="shared" si="2"/>
         <v>464136672</v>
       </c>
-      <c r="Q6" s="319" t="str">
+      <c r="Q6" s="335" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -10070,52 +10086,52 @@
       <c r="B7" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="318">
+      <c r="C7" s="334">
         <f>C35</f>
         <v>-568980442.5</v>
       </c>
       <c r="E7" s="268"/>
-      <c r="G7" s="318">
+      <c r="G7" s="334">
         <f t="shared" ref="G7:Q7" si="3">G35</f>
         <v>-539608200</v>
       </c>
-      <c r="H7" s="318">
+      <c r="H7" s="334">
         <f t="shared" si="3"/>
         <v>-520902794</v>
       </c>
-      <c r="I7" s="318">
+      <c r="I7" s="334">
         <f t="shared" si="3"/>
         <v>-645318285</v>
       </c>
-      <c r="J7" s="318">
+      <c r="J7" s="334">
         <f t="shared" si="3"/>
         <v>-680028430</v>
       </c>
-      <c r="K7" s="318">
+      <c r="K7" s="334">
         <f t="shared" si="3"/>
         <v>-768317542</v>
       </c>
-      <c r="L7" s="318">
+      <c r="L7" s="334">
         <f t="shared" si="3"/>
         <v>-161996928</v>
       </c>
-      <c r="M7" s="318">
+      <c r="M7" s="334">
         <f t="shared" si="3"/>
         <v>-153940810</v>
       </c>
-      <c r="N7" s="318">
+      <c r="N7" s="334">
         <f t="shared" si="3"/>
         <v>-155718230</v>
       </c>
-      <c r="O7" s="318">
+      <c r="O7" s="334">
         <f t="shared" si="3"/>
         <v>-183628555</v>
       </c>
-      <c r="P7" s="318">
+      <c r="P7" s="334">
         <f t="shared" si="3"/>
         <v>-232657686</v>
       </c>
-      <c r="Q7" s="318" t="str">
+      <c r="Q7" s="334" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
@@ -10125,54 +10141,54 @@
       <c r="B8" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="C8" s="320">
+      <c r="C8" s="336">
         <f>C6+C7</f>
         <v>2957715106.6986084</v>
       </c>
       <c r="D8" s="59"/>
       <c r="E8" s="274"/>
       <c r="F8" s="59"/>
-      <c r="G8" s="319">
+      <c r="G8" s="335">
         <f>IF(G$4="","",G6+G7)</f>
         <v>3109212579</v>
       </c>
-      <c r="H8" s="319">
+      <c r="H8" s="335">
         <f t="shared" ref="H8:Q8" si="4">IF(H$4="","",H6+H7)</f>
         <v>3269786767</v>
       </c>
-      <c r="I8" s="319">
+      <c r="I8" s="335">
         <f t="shared" si="4"/>
         <v>3194217743</v>
       </c>
-      <c r="J8" s="319">
+      <c r="J8" s="335">
         <f t="shared" si="4"/>
         <v>2897969551</v>
       </c>
-      <c r="K8" s="319">
+      <c r="K8" s="335">
         <f t="shared" si="4"/>
         <v>1702921432</v>
       </c>
-      <c r="L8" s="319">
+      <c r="L8" s="335">
         <f t="shared" si="4"/>
         <v>568592883</v>
       </c>
-      <c r="M8" s="319">
+      <c r="M8" s="335">
         <f t="shared" si="4"/>
         <v>495381989</v>
       </c>
-      <c r="N8" s="319">
+      <c r="N8" s="335">
         <f t="shared" si="4"/>
         <v>363662082</v>
       </c>
-      <c r="O8" s="319">
+      <c r="O8" s="335">
         <f t="shared" si="4"/>
         <v>357305715</v>
       </c>
-      <c r="P8" s="319">
+      <c r="P8" s="335">
         <f t="shared" si="4"/>
         <v>231478986</v>
       </c>
-      <c r="Q8" s="319" t="str">
+      <c r="Q8" s="335" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
@@ -10182,52 +10198,52 @@
       <c r="B9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C9" s="318">
+      <c r="C9" s="334">
         <f>BS!$G$39*BS!D58</f>
         <v>575917865</v>
       </c>
       <c r="E9" s="268"/>
-      <c r="G9" s="318">
+      <c r="G9" s="334">
         <f>IF(Data!C61="","",-Data!C61)</f>
         <v>575917865</v>
       </c>
-      <c r="H9" s="318">
+      <c r="H9" s="334">
         <f>IF(Data!D61="","",-Data!D61)</f>
         <v>514817738</v>
       </c>
-      <c r="I9" s="318">
+      <c r="I9" s="334">
         <f>IF(Data!E61="","",-Data!E61)</f>
         <v>504410326</v>
       </c>
-      <c r="J9" s="318">
+      <c r="J9" s="334">
         <f>IF(Data!F61="","",-Data!F61)</f>
         <v>451827434</v>
       </c>
-      <c r="K9" s="318">
+      <c r="K9" s="334">
         <f>IF(Data!G61="","",-Data!G61)</f>
         <v>413794059</v>
       </c>
-      <c r="L9" s="318">
+      <c r="L9" s="334">
         <f>IF(Data!H61="","",-Data!H61)</f>
         <v>174070610</v>
       </c>
-      <c r="M9" s="318">
+      <c r="M9" s="334">
         <f>IF(Data!I61="","",-Data!I61)</f>
         <v>173632673</v>
       </c>
-      <c r="N9" s="318">
+      <c r="N9" s="334">
         <f>IF(Data!J61="","",-Data!J61)</f>
         <v>0</v>
       </c>
-      <c r="O9" s="318">
+      <c r="O9" s="334">
         <f>IF(Data!K61="","",-Data!K61)</f>
         <v>0</v>
       </c>
-      <c r="P9" s="318">
+      <c r="P9" s="334">
         <f>IF(Data!L61="","",-Data!L61)</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="318" t="str">
+      <c r="Q9" s="334" t="str">
         <f>IF(Data!M61="","",-Data!M61)</f>
         <v/>
       </c>
@@ -10237,52 +10253,52 @@
       <c r="B10" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="318">
+      <c r="C10" s="334">
         <f>-C4*C78</f>
         <v>-575917865</v>
       </c>
       <c r="E10" s="268"/>
-      <c r="G10" s="318">
+      <c r="G10" s="334">
         <f>Data!C62</f>
         <v>-575917865</v>
       </c>
-      <c r="H10" s="318">
+      <c r="H10" s="334">
         <f>Data!D62</f>
         <v>-514817738</v>
       </c>
-      <c r="I10" s="318">
+      <c r="I10" s="334">
         <f>Data!E62</f>
         <v>-504410326</v>
       </c>
-      <c r="J10" s="318">
+      <c r="J10" s="334">
         <f>Data!F62</f>
         <v>-451827434</v>
       </c>
-      <c r="K10" s="318">
+      <c r="K10" s="334">
         <f>Data!G62</f>
         <v>-413794059</v>
       </c>
-      <c r="L10" s="318">
+      <c r="L10" s="334">
         <f>Data!H62</f>
         <v>-174070610</v>
       </c>
-      <c r="M10" s="318">
+      <c r="M10" s="334">
         <f>Data!I62</f>
         <v>-173632673</v>
       </c>
-      <c r="N10" s="318">
+      <c r="N10" s="334">
         <f>Data!J62</f>
         <v>0</v>
       </c>
-      <c r="O10" s="318">
+      <c r="O10" s="334">
         <f>Data!K62</f>
         <v>0</v>
       </c>
-      <c r="P10" s="318">
+      <c r="P10" s="334">
         <f>Data!L62</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="318" t="str">
+      <c r="Q10" s="334" t="str">
         <f>Data!M62</f>
         <v/>
       </c>
@@ -10292,54 +10308,54 @@
       <c r="B11" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C11" s="321">
+      <c r="C11" s="337">
         <f>C63</f>
         <v>0</v>
       </c>
       <c r="D11" s="168"/>
       <c r="E11" s="267"/>
       <c r="F11" s="168"/>
-      <c r="G11" s="324">
+      <c r="G11" s="340">
         <f>G61</f>
         <v>0</v>
       </c>
-      <c r="H11" s="324">
+      <c r="H11" s="340">
         <f t="shared" ref="H11:Q11" si="5">H61</f>
         <v>0</v>
       </c>
-      <c r="I11" s="324">
+      <c r="I11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="J11" s="324">
+      <c r="J11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="K11" s="324">
+      <c r="K11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="L11" s="324">
+      <c r="L11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="M11" s="324">
+      <c r="M11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N11" s="324">
+      <c r="N11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="O11" s="324">
+      <c r="O11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="P11" s="324">
+      <c r="P11" s="340">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="Q11" s="324" t="str">
+      <c r="Q11" s="340" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
@@ -10349,52 +10365,52 @@
       <c r="B12" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C12" s="318">
+      <c r="C12" s="334">
         <f>C50</f>
         <v>31406153.816265978</v>
       </c>
       <c r="E12" s="268"/>
-      <c r="G12" s="318">
+      <c r="G12" s="334">
         <f>G50</f>
         <v>31406153.816265978</v>
       </c>
-      <c r="H12" s="318">
+      <c r="H12" s="334">
         <f t="shared" ref="H12:Q12" si="6">H50</f>
         <v>61971192.331585214</v>
       </c>
-      <c r="I12" s="318">
+      <c r="I12" s="334">
         <f t="shared" si="6"/>
         <v>58874284.747775584</v>
       </c>
-      <c r="J12" s="318">
+      <c r="J12" s="334">
         <f t="shared" si="6"/>
         <v>20137430.77782803</v>
       </c>
-      <c r="K12" s="318">
+      <c r="K12" s="334">
         <f t="shared" si="6"/>
         <v>6490894.562197201</v>
       </c>
-      <c r="L12" s="318">
+      <c r="L12" s="334">
         <f t="shared" si="6"/>
         <v>-2599288.5787666151</v>
       </c>
-      <c r="M12" s="318">
+      <c r="M12" s="334">
         <f t="shared" si="6"/>
         <v>-6040379.1363799218</v>
       </c>
-      <c r="N12" s="318">
+      <c r="N12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="O12" s="318">
+      <c r="O12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="P12" s="318">
+      <c r="P12" s="334">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q12" s="318" t="str">
+      <c r="Q12" s="334" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
@@ -10404,52 +10420,52 @@
       <c r="B13" s="70" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="319">
+      <c r="C13" s="335">
         <f>SUM(C8:C12)</f>
         <v>2989121260.5148745</v>
       </c>
       <c r="E13" s="268"/>
-      <c r="G13" s="319">
+      <c r="G13" s="335">
         <f>IF(G$4="","",SUM(G8:G12))</f>
         <v>3140618732.8162661</v>
       </c>
-      <c r="H13" s="319">
+      <c r="H13" s="335">
         <f t="shared" ref="H13:Q13" si="7">IF(H$4="","",SUM(H8:H12))</f>
         <v>3331757959.3315854</v>
       </c>
-      <c r="I13" s="319">
+      <c r="I13" s="335">
         <f t="shared" si="7"/>
         <v>3253092027.7477756</v>
       </c>
-      <c r="J13" s="319">
+      <c r="J13" s="335">
         <f t="shared" si="7"/>
         <v>2918106981.7778282</v>
       </c>
-      <c r="K13" s="319">
+      <c r="K13" s="335">
         <f t="shared" si="7"/>
         <v>1709412326.5621972</v>
       </c>
-      <c r="L13" s="319">
+      <c r="L13" s="335">
         <f t="shared" si="7"/>
         <v>565993594.42123342</v>
       </c>
-      <c r="M13" s="319">
+      <c r="M13" s="335">
         <f t="shared" si="7"/>
         <v>489341609.8636201</v>
       </c>
-      <c r="N13" s="319">
+      <c r="N13" s="335">
         <f t="shared" si="7"/>
         <v>363662082</v>
       </c>
-      <c r="O13" s="319">
+      <c r="O13" s="335">
         <f t="shared" si="7"/>
         <v>357305715</v>
       </c>
-      <c r="P13" s="319">
+      <c r="P13" s="335">
         <f t="shared" si="7"/>
         <v>231478986</v>
       </c>
-      <c r="Q13" s="319" t="str">
+      <c r="Q13" s="335" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10459,52 +10475,52 @@
       <c r="B14" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="318">
+      <c r="C14" s="334">
         <f>-SUM(C8+C11,C12)*C43</f>
         <v>-747280315.12871861</v>
       </c>
       <c r="E14" s="268"/>
-      <c r="G14" s="318">
+      <c r="G14" s="334">
         <f>Data!C46</f>
         <v>-670547120</v>
       </c>
-      <c r="H14" s="318">
+      <c r="H14" s="334">
         <f>Data!D46</f>
         <v>-664121997</v>
       </c>
-      <c r="I14" s="318">
+      <c r="I14" s="334">
         <f>Data!E46</f>
         <v>-711879179</v>
       </c>
-      <c r="J14" s="318">
+      <c r="J14" s="334">
         <f>Data!F46</f>
         <v>-541923819</v>
       </c>
-      <c r="K14" s="318">
+      <c r="K14" s="334">
         <f>Data!G46</f>
         <v>-378467716</v>
       </c>
-      <c r="L14" s="318">
+      <c r="L14" s="334">
         <f>Data!H46</f>
         <v>-98780687</v>
       </c>
-      <c r="M14" s="318">
+      <c r="M14" s="334">
         <f>Data!I46</f>
         <v>-61018006</v>
       </c>
-      <c r="N14" s="318">
+      <c r="N14" s="334">
         <f>Data!J46</f>
         <v>-18873927</v>
       </c>
-      <c r="O14" s="318">
+      <c r="O14" s="334">
         <f>Data!K46</f>
         <v>-16833271</v>
       </c>
-      <c r="P14" s="318">
+      <c r="P14" s="334">
         <f>Data!L46</f>
         <v>-42979625</v>
       </c>
-      <c r="Q14" s="318" t="str">
+      <c r="Q14" s="334" t="str">
         <f>Data!M46</f>
         <v/>
       </c>
@@ -10514,54 +10530,54 @@
       <c r="B15" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="C15" s="318">
+      <c r="C15" s="334">
         <f>-C4*C83</f>
         <v>-141879704.29826272</v>
       </c>
       <c r="D15" s="60"/>
       <c r="E15" s="275"/>
       <c r="F15" s="60"/>
-      <c r="G15" s="323">
+      <c r="G15" s="339">
         <f>Data!C48</f>
         <v>-146792828</v>
       </c>
-      <c r="H15" s="323">
+      <c r="H15" s="339">
         <f>Data!D48</f>
         <v>0</v>
       </c>
-      <c r="I15" s="323">
+      <c r="I15" s="339">
         <f>Data!E48</f>
         <v>0</v>
       </c>
-      <c r="J15" s="323">
+      <c r="J15" s="339">
         <f>Data!F48</f>
         <v>0</v>
       </c>
-      <c r="K15" s="323">
+      <c r="K15" s="339">
         <f>Data!G48</f>
         <v>0</v>
       </c>
-      <c r="L15" s="323">
+      <c r="L15" s="339">
         <f>Data!H48</f>
         <v>0</v>
       </c>
-      <c r="M15" s="323">
+      <c r="M15" s="339">
         <f>Data!I48</f>
         <v>0</v>
       </c>
-      <c r="N15" s="323">
+      <c r="N15" s="339">
         <f>Data!J48</f>
         <v>0</v>
       </c>
-      <c r="O15" s="323">
+      <c r="O15" s="339">
         <f>Data!K48</f>
         <v>0</v>
       </c>
-      <c r="P15" s="323">
+      <c r="P15" s="339">
         <f>Data!L48</f>
         <v>0</v>
       </c>
-      <c r="Q15" s="323" t="str">
+      <c r="Q15" s="339" t="str">
         <f>Data!M48</f>
         <v/>
       </c>
@@ -10571,54 +10587,54 @@
       <c r="B16" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="C16" s="322">
+      <c r="C16" s="338">
         <f>SUM(C13:C15)</f>
         <v>2099961241.0878935</v>
       </c>
       <c r="D16" s="61"/>
       <c r="E16" s="276"/>
       <c r="F16" s="61"/>
-      <c r="G16" s="319">
+      <c r="G16" s="335">
         <f>IF(G$4="","",SUM(G13:G15))</f>
         <v>2323278784.8162661</v>
       </c>
-      <c r="H16" s="319">
+      <c r="H16" s="335">
         <f t="shared" ref="H16:Q16" si="8">IF(H$4="","",SUM(H13:H15))</f>
         <v>2667635962.3315854</v>
       </c>
-      <c r="I16" s="319">
+      <c r="I16" s="335">
         <f t="shared" si="8"/>
         <v>2541212848.7477756</v>
       </c>
-      <c r="J16" s="319">
+      <c r="J16" s="335">
         <f t="shared" si="8"/>
         <v>2376183162.7778282</v>
       </c>
-      <c r="K16" s="319">
+      <c r="K16" s="335">
         <f t="shared" si="8"/>
         <v>1330944610.5621972</v>
       </c>
-      <c r="L16" s="319">
+      <c r="L16" s="335">
         <f t="shared" si="8"/>
         <v>467212907.42123342</v>
       </c>
-      <c r="M16" s="319">
+      <c r="M16" s="335">
         <f t="shared" si="8"/>
         <v>428323603.8636201</v>
       </c>
-      <c r="N16" s="319">
+      <c r="N16" s="335">
         <f t="shared" si="8"/>
         <v>344788155</v>
       </c>
-      <c r="O16" s="319">
+      <c r="O16" s="335">
         <f t="shared" si="8"/>
         <v>340472444</v>
       </c>
-      <c r="P16" s="319">
+      <c r="P16" s="335">
         <f t="shared" si="8"/>
         <v>188499361</v>
       </c>
-      <c r="Q16" s="319" t="str">
+      <c r="Q16" s="335" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
@@ -10628,7 +10644,7 @@
       <c r="B17" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="318">
+      <c r="C17" s="334">
         <f>-C4*C85</f>
         <v>0</v>
       </c>
@@ -10637,24 +10653,24 @@
         <v>332</v>
       </c>
       <c r="F17" s="58"/>
-      <c r="G17" s="325"/>
-      <c r="H17" s="325"/>
-      <c r="I17" s="325"/>
-      <c r="J17" s="325"/>
-      <c r="K17" s="325"/>
-      <c r="L17" s="325"/>
-      <c r="M17" s="325"/>
-      <c r="N17" s="325"/>
-      <c r="O17" s="325"/>
-      <c r="P17" s="325"/>
-      <c r="Q17" s="325"/>
+      <c r="G17" s="341"/>
+      <c r="H17" s="341"/>
+      <c r="I17" s="341"/>
+      <c r="J17" s="341"/>
+      <c r="K17" s="341"/>
+      <c r="L17" s="341"/>
+      <c r="M17" s="341"/>
+      <c r="N17" s="341"/>
+      <c r="O17" s="341"/>
+      <c r="P17" s="341"/>
+      <c r="Q17" s="341"/>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="318">
+      <c r="C18" s="334">
         <v>0</v>
       </c>
       <c r="D18" s="58"/>
@@ -10662,71 +10678,71 @@
         <v>333</v>
       </c>
       <c r="F18" s="58"/>
-      <c r="G18" s="326"/>
-      <c r="H18" s="326"/>
-      <c r="I18" s="326"/>
-      <c r="J18" s="326"/>
-      <c r="K18" s="326"/>
-      <c r="L18" s="326"/>
-      <c r="M18" s="326"/>
-      <c r="N18" s="326"/>
-      <c r="O18" s="326"/>
-      <c r="P18" s="326"/>
-      <c r="Q18" s="326"/>
+      <c r="G18" s="342"/>
+      <c r="H18" s="342"/>
+      <c r="I18" s="342"/>
+      <c r="J18" s="342"/>
+      <c r="K18" s="342"/>
+      <c r="L18" s="342"/>
+      <c r="M18" s="342"/>
+      <c r="N18" s="342"/>
+      <c r="O18" s="342"/>
+      <c r="P18" s="342"/>
+      <c r="Q18" s="342"/>
     </row>
     <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C19" s="319">
+      <c r="C19" s="335">
         <f>C16+C17</f>
         <v>2099961241.0878935</v>
       </c>
       <c r="D19" s="27"/>
       <c r="E19" s="265"/>
       <c r="F19" s="27"/>
-      <c r="G19" s="324">
+      <c r="G19" s="340">
         <f>IF(G$4="","",G16+G17)</f>
         <v>2323278784.8162661</v>
       </c>
-      <c r="H19" s="324">
+      <c r="H19" s="340">
         <f t="shared" ref="H19:Q19" si="9">IF(H$4="","",H16+H17)</f>
         <v>2667635962.3315854</v>
       </c>
-      <c r="I19" s="324">
+      <c r="I19" s="340">
         <f t="shared" si="9"/>
         <v>2541212848.7477756</v>
       </c>
-      <c r="J19" s="324">
+      <c r="J19" s="340">
         <f t="shared" si="9"/>
         <v>2376183162.7778282</v>
       </c>
-      <c r="K19" s="324">
+      <c r="K19" s="340">
         <f t="shared" si="9"/>
         <v>1330944610.5621972</v>
       </c>
-      <c r="L19" s="324">
+      <c r="L19" s="340">
         <f t="shared" si="9"/>
         <v>467212907.42123342</v>
       </c>
-      <c r="M19" s="324">
+      <c r="M19" s="340">
         <f t="shared" si="9"/>
         <v>428323603.8636201</v>
       </c>
-      <c r="N19" s="324">
+      <c r="N19" s="340">
         <f t="shared" si="9"/>
         <v>344788155</v>
       </c>
-      <c r="O19" s="324">
+      <c r="O19" s="340">
         <f t="shared" si="9"/>
         <v>340472444</v>
       </c>
-      <c r="P19" s="324">
+      <c r="P19" s="340">
         <f t="shared" si="9"/>
         <v>188499361</v>
       </c>
-      <c r="Q19" s="324" t="str">
+      <c r="Q19" s="340" t="str">
         <f t="shared" si="9"/>
         <v/>
       </c>
@@ -10799,54 +10815,54 @@
       <c r="B23" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="327">
+      <c r="C23" s="343">
         <f>-C4*C28</f>
         <v>-8199195071.4115868</v>
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="267"/>
       <c r="F23" s="58"/>
-      <c r="G23" s="323">
+      <c r="G23" s="339">
         <f>Data!C37</f>
         <v>-8483123346</v>
       </c>
-      <c r="H23" s="323">
+      <c r="H23" s="339">
         <f>Data!D37</f>
         <v>-8491525016</v>
       </c>
-      <c r="I23" s="323">
+      <c r="I23" s="339">
         <f>Data!E37</f>
         <v>-7873287284</v>
       </c>
-      <c r="J23" s="323">
+      <c r="J23" s="339">
         <f>Data!F37</f>
         <v>-7328418046</v>
       </c>
-      <c r="K23" s="323">
+      <c r="K23" s="339">
         <f>Data!G37</f>
         <v>-6166079008</v>
       </c>
-      <c r="L23" s="323">
+      <c r="L23" s="339">
         <f>Data!H37</f>
         <v>-2359127300</v>
       </c>
-      <c r="M23" s="323">
+      <c r="M23" s="339">
         <f>Data!I37</f>
         <v>-2362728713</v>
       </c>
-      <c r="N23" s="323">
+      <c r="N23" s="339">
         <f>Data!J37</f>
         <v>-2190920673</v>
       </c>
-      <c r="O23" s="323">
+      <c r="O23" s="339">
         <f>Data!K37</f>
         <v>-2209433704</v>
       </c>
-      <c r="P23" s="323">
+      <c r="P23" s="339">
         <f>Data!L37</f>
         <v>-2369740058</v>
       </c>
-      <c r="Q23" s="323" t="str">
+      <c r="Q23" s="339" t="str">
         <f>Data!M37</f>
         <v/>
       </c>
@@ -10856,54 +10872,54 @@
       <c r="B24" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="C24" s="318">
+      <c r="C24" s="334">
         <f>-C4*C29</f>
         <v>-2428555749.1398058</v>
       </c>
       <c r="D24" s="27"/>
       <c r="E24" s="265"/>
       <c r="F24" s="27"/>
-      <c r="G24" s="323">
+      <c r="G24" s="339">
         <f>Data!C40</f>
         <v>-2512653717</v>
       </c>
-      <c r="H24" s="323">
+      <c r="H24" s="339">
         <f>Data!D40</f>
         <v>-2532621833</v>
       </c>
-      <c r="I24" s="323">
+      <c r="I24" s="339">
         <f>Data!E40</f>
         <v>-2326217227</v>
       </c>
-      <c r="J24" s="323">
+      <c r="J24" s="339">
         <f>Data!F40</f>
         <v>-2212894661</v>
       </c>
-      <c r="K24" s="323">
+      <c r="K24" s="339">
         <f>Data!G40</f>
         <v>-2304313181</v>
       </c>
-      <c r="L24" s="323">
+      <c r="L24" s="339">
         <f>Data!H40</f>
         <v>-492206624</v>
       </c>
-      <c r="M24" s="323">
+      <c r="M24" s="339">
         <f>Data!I40</f>
         <v>-455284418</v>
       </c>
-      <c r="N24" s="323">
+      <c r="N24" s="339">
         <f>Data!J40</f>
         <v>-465218537</v>
       </c>
-      <c r="O24" s="323">
+      <c r="O24" s="339">
         <f>Data!K40</f>
         <v>-445553542</v>
       </c>
-      <c r="P24" s="323">
+      <c r="P24" s="339">
         <f>Data!L40</f>
         <v>-489868548</v>
       </c>
-      <c r="Q24" s="323" t="str">
+      <c r="Q24" s="339" t="str">
         <f>Data!M40</f>
         <v/>
       </c>
@@ -10913,54 +10929,54 @@
       <c r="B25" s="70" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="319">
+      <c r="C25" s="335">
         <f>C23+C24</f>
         <v>-10627750820.551392</v>
       </c>
       <c r="D25" s="9"/>
       <c r="E25" s="273"/>
       <c r="F25" s="9"/>
-      <c r="G25" s="319">
+      <c r="G25" s="335">
         <f t="shared" ref="G25:Q25" si="10">IF(G$4="","",G23+G24)</f>
         <v>-10995777063</v>
       </c>
-      <c r="H25" s="319">
+      <c r="H25" s="335">
         <f t="shared" si="10"/>
         <v>-11024146849</v>
       </c>
-      <c r="I25" s="319">
+      <c r="I25" s="335">
         <f t="shared" si="10"/>
         <v>-10199504511</v>
       </c>
-      <c r="J25" s="319">
+      <c r="J25" s="335">
         <f t="shared" si="10"/>
         <v>-9541312707</v>
       </c>
-      <c r="K25" s="319">
+      <c r="K25" s="335">
         <f t="shared" si="10"/>
         <v>-8470392189</v>
       </c>
-      <c r="L25" s="319">
+      <c r="L25" s="335">
         <f t="shared" si="10"/>
         <v>-2851333924</v>
       </c>
-      <c r="M25" s="319">
+      <c r="M25" s="335">
         <f t="shared" si="10"/>
         <v>-2818013131</v>
       </c>
-      <c r="N25" s="319">
+      <c r="N25" s="335">
         <f t="shared" si="10"/>
         <v>-2656139210</v>
       </c>
-      <c r="O25" s="319">
+      <c r="O25" s="335">
         <f t="shared" si="10"/>
         <v>-2654987246</v>
       </c>
-      <c r="P25" s="319">
+      <c r="P25" s="335">
         <f t="shared" si="10"/>
         <v>-2859608606</v>
       </c>
-      <c r="Q25" s="319" t="str">
+      <c r="Q25" s="335" t="str">
         <f t="shared" si="10"/>
         <v/>
       </c>
@@ -11166,54 +11182,54 @@
       <c r="B33" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="C33" s="328">
+      <c r="C33" s="346">
         <f>AVERAGE(G33:J33)</f>
         <v>-515765096.5</v>
       </c>
       <c r="E33" s="266" t="s">
         <v>334</v>
       </c>
-      <c r="G33" s="318">
+      <c r="G33" s="334">
         <f>Data!C41</f>
         <v>-516942154</v>
       </c>
-      <c r="H33" s="318">
+      <c r="H33" s="334">
         <f>Data!D41</f>
         <v>-494670738</v>
       </c>
-      <c r="I33" s="318">
+      <c r="I33" s="334">
         <f>Data!E41</f>
         <v>-534570349</v>
       </c>
-      <c r="J33" s="318">
+      <c r="J33" s="334">
         <f>Data!F41</f>
         <v>-516877145</v>
       </c>
-      <c r="K33" s="318">
+      <c r="K33" s="334">
         <f>Data!G41</f>
         <v>-684104925</v>
       </c>
-      <c r="L33" s="318">
+      <c r="L33" s="334">
         <f>Data!H41</f>
         <v>-161996928</v>
       </c>
-      <c r="M33" s="318">
+      <c r="M33" s="334">
         <f>Data!I41</f>
         <v>-153940810</v>
       </c>
-      <c r="N33" s="318">
+      <c r="N33" s="334">
         <f>Data!J41</f>
         <v>-155718230</v>
       </c>
-      <c r="O33" s="318">
+      <c r="O33" s="334">
         <f>Data!K41</f>
         <v>-183628555</v>
       </c>
-      <c r="P33" s="318">
+      <c r="P33" s="334">
         <f>Data!L41</f>
         <v>-232657686</v>
       </c>
-      <c r="Q33" s="318" t="str">
+      <c r="Q33" s="334" t="str">
         <f>Data!M41</f>
         <v/>
       </c>
@@ -11223,7 +11239,7 @@
       <c r="B34" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="C34" s="328">
+      <c r="C34" s="346">
         <f>AVERAGE(G34:I34)</f>
         <v>-53215346</v>
       </c>
@@ -11232,47 +11248,47 @@
         <v>334</v>
       </c>
       <c r="F34" s="58"/>
-      <c r="G34" s="323">
+      <c r="G34" s="339">
         <f>Data!C42</f>
         <v>-22666046</v>
       </c>
-      <c r="H34" s="323">
+      <c r="H34" s="339">
         <f>Data!D42</f>
         <v>-26232056</v>
       </c>
-      <c r="I34" s="323">
+      <c r="I34" s="339">
         <f>Data!E42</f>
         <v>-110747936</v>
       </c>
-      <c r="J34" s="323">
+      <c r="J34" s="339">
         <f>Data!F42</f>
         <v>-163151285</v>
       </c>
-      <c r="K34" s="323">
+      <c r="K34" s="339">
         <f>Data!G42</f>
         <v>-84212617</v>
       </c>
-      <c r="L34" s="323">
+      <c r="L34" s="339">
         <f>Data!H42</f>
         <v>0</v>
       </c>
-      <c r="M34" s="323">
+      <c r="M34" s="339">
         <f>Data!I42</f>
         <v>0</v>
       </c>
-      <c r="N34" s="323">
+      <c r="N34" s="339">
         <f>Data!J42</f>
         <v>0</v>
       </c>
-      <c r="O34" s="323">
+      <c r="O34" s="339">
         <f>Data!K42</f>
         <v>0</v>
       </c>
-      <c r="P34" s="323">
+      <c r="P34" s="339">
         <f>Data!L42</f>
         <v>0</v>
       </c>
-      <c r="Q34" s="323" t="str">
+      <c r="Q34" s="339" t="str">
         <f>Data!M42</f>
         <v/>
       </c>
@@ -11282,54 +11298,54 @@
       <c r="B35" s="70" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="319">
+      <c r="C35" s="335">
         <f>C33+C34</f>
         <v>-568980442.5</v>
       </c>
       <c r="D35" s="58"/>
       <c r="E35" s="267"/>
       <c r="F35" s="58"/>
-      <c r="G35" s="319">
+      <c r="G35" s="335">
         <f t="shared" ref="G35:Q35" si="14">IF(G4="","",G33+G34)</f>
         <v>-539608200</v>
       </c>
-      <c r="H35" s="319">
+      <c r="H35" s="335">
         <f t="shared" si="14"/>
         <v>-520902794</v>
       </c>
-      <c r="I35" s="319">
+      <c r="I35" s="335">
         <f t="shared" si="14"/>
         <v>-645318285</v>
       </c>
-      <c r="J35" s="319">
+      <c r="J35" s="335">
         <f t="shared" si="14"/>
         <v>-680028430</v>
       </c>
-      <c r="K35" s="319">
+      <c r="K35" s="335">
         <f t="shared" si="14"/>
         <v>-768317542</v>
       </c>
-      <c r="L35" s="319">
+      <c r="L35" s="335">
         <f t="shared" si="14"/>
         <v>-161996928</v>
       </c>
-      <c r="M35" s="319">
+      <c r="M35" s="335">
         <f t="shared" si="14"/>
         <v>-153940810</v>
       </c>
-      <c r="N35" s="319">
+      <c r="N35" s="335">
         <f t="shared" si="14"/>
         <v>-155718230</v>
       </c>
-      <c r="O35" s="319">
+      <c r="O35" s="335">
         <f t="shared" si="14"/>
         <v>-183628555</v>
       </c>
-      <c r="P35" s="319">
+      <c r="P35" s="335">
         <f t="shared" si="14"/>
         <v>-232657686</v>
       </c>
-      <c r="Q35" s="319" t="str">
+      <c r="Q35" s="335" t="str">
         <f t="shared" si="14"/>
         <v/>
       </c>
@@ -11623,52 +11639,52 @@
       <c r="B47" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C47" s="318">
+      <c r="C47" s="334">
         <f>-BS!G31*Normalized_FCF!C54</f>
         <v>-7672861</v>
       </c>
       <c r="E47" s="268"/>
-      <c r="G47" s="318">
+      <c r="G47" s="334">
         <f>Data!C51</f>
         <v>-7672861</v>
       </c>
-      <c r="H47" s="318">
+      <c r="H47" s="334">
         <f>Data!D51</f>
         <v>-5921669</v>
       </c>
-      <c r="I47" s="318">
+      <c r="I47" s="334">
         <f>Data!E51</f>
         <v>-3696844</v>
       </c>
-      <c r="J47" s="318">
+      <c r="J47" s="334">
         <f>Data!F51</f>
         <v>-14186775</v>
       </c>
-      <c r="K47" s="318">
+      <c r="K47" s="334">
         <f>Data!G51</f>
         <v>-35823675</v>
       </c>
-      <c r="L47" s="318">
+      <c r="L47" s="334">
         <f>Data!H51</f>
         <v>-10770646</v>
       </c>
-      <c r="M47" s="318">
+      <c r="M47" s="334">
         <f>Data!I51</f>
         <v>-12333775</v>
       </c>
-      <c r="N47" s="318">
+      <c r="N47" s="334">
         <f>Data!J51</f>
         <v>0</v>
       </c>
-      <c r="O47" s="318">
+      <c r="O47" s="334">
         <f>Data!K51</f>
         <v>0</v>
       </c>
-      <c r="P47" s="318">
+      <c r="P47" s="334">
         <f>Data!L51</f>
         <v>0</v>
       </c>
-      <c r="Q47" s="318" t="str">
+      <c r="Q47" s="334" t="str">
         <f>Data!M51</f>
         <v/>
       </c>
@@ -11678,52 +11694,52 @@
       <c r="B48" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="C48" s="318">
+      <c r="C48" s="334">
         <f>BS!D75*C53</f>
         <v>39079014.816265978</v>
       </c>
       <c r="E48" s="268"/>
-      <c r="G48" s="327">
+      <c r="G48" s="343">
         <f>IFERROR(IF(G$4="","",($C$48/$C$49)*G49),0)</f>
         <v>39079014.816265978</v>
       </c>
-      <c r="H48" s="327">
+      <c r="H48" s="343">
         <f t="shared" ref="H48:Q48" si="19">IFERROR(IF(H$4="","",($C$48/$C$49)*H49),0)</f>
         <v>67892861.331585214</v>
       </c>
-      <c r="I48" s="327">
+      <c r="I48" s="343">
         <f t="shared" si="19"/>
         <v>62571128.747775584</v>
       </c>
-      <c r="J48" s="327">
+      <c r="J48" s="343">
         <f t="shared" si="19"/>
         <v>34324205.77782803</v>
       </c>
-      <c r="K48" s="327">
+      <c r="K48" s="343">
         <f t="shared" si="19"/>
         <v>42314569.562197201</v>
       </c>
-      <c r="L48" s="327">
+      <c r="L48" s="343">
         <f t="shared" si="19"/>
         <v>8171357.4212333849</v>
       </c>
-      <c r="M48" s="327">
+      <c r="M48" s="343">
         <f t="shared" si="19"/>
         <v>6293395.8636200782</v>
       </c>
-      <c r="N48" s="327">
+      <c r="N48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="O48" s="327">
+      <c r="O48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="P48" s="327">
+      <c r="P48" s="343">
         <f t="shared" si="19"/>
         <v>0</v>
       </c>
-      <c r="Q48" s="327" t="str">
+      <c r="Q48" s="343" t="str">
         <f t="shared" si="19"/>
         <v/>
       </c>
@@ -11733,54 +11749,54 @@
       <c r="B49" s="287" t="s">
         <v>343</v>
       </c>
-      <c r="C49" s="329">
+      <c r="C49" s="348">
         <f>BS!$C$66*C53</f>
         <v>41044772</v>
       </c>
       <c r="D49" s="288"/>
       <c r="E49" s="289"/>
       <c r="F49" s="288"/>
-      <c r="G49" s="329">
+      <c r="G49" s="348">
         <f>Data!C52</f>
         <v>41044772</v>
       </c>
-      <c r="H49" s="329">
+      <c r="H49" s="348">
         <f>Data!D52</f>
         <v>71308016</v>
       </c>
-      <c r="I49" s="329">
+      <c r="I49" s="348">
         <f>Data!E52</f>
         <v>65718589</v>
       </c>
-      <c r="J49" s="329">
+      <c r="J49" s="348">
         <f>Data!F52</f>
         <v>36050786</v>
       </c>
-      <c r="K49" s="329">
+      <c r="K49" s="348">
         <f>Data!G52</f>
         <v>44443082</v>
       </c>
-      <c r="L49" s="329">
+      <c r="L49" s="348">
         <f>Data!H52</f>
         <v>8582394</v>
       </c>
-      <c r="M49" s="329">
+      <c r="M49" s="348">
         <f>Data!I52</f>
         <v>6609967</v>
       </c>
-      <c r="N49" s="329">
+      <c r="N49" s="348">
         <f>Data!J52</f>
         <v>0</v>
       </c>
-      <c r="O49" s="329">
+      <c r="O49" s="348">
         <f>Data!K52</f>
         <v>0</v>
       </c>
-      <c r="P49" s="329">
+      <c r="P49" s="348">
         <f>Data!L52</f>
         <v>0</v>
       </c>
-      <c r="Q49" s="329" t="str">
+      <c r="Q49" s="348" t="str">
         <f>Data!M52</f>
         <v/>
       </c>
@@ -11790,52 +11806,52 @@
       <c r="B50" s="70" t="s">
         <v>68</v>
       </c>
-      <c r="C50" s="319">
+      <c r="C50" s="335">
         <f>C47+C48</f>
         <v>31406153.816265978</v>
       </c>
       <c r="E50" s="268"/>
-      <c r="G50" s="319">
+      <c r="G50" s="335">
         <f>IF(G$4="","",(G47+G48))</f>
         <v>31406153.816265978</v>
       </c>
-      <c r="H50" s="319">
+      <c r="H50" s="335">
         <f t="shared" ref="H50:Q50" si="20">IF(H$4="","",(H47+H48))</f>
         <v>61971192.331585214</v>
       </c>
-      <c r="I50" s="319">
+      <c r="I50" s="335">
         <f t="shared" si="20"/>
         <v>58874284.747775584</v>
       </c>
-      <c r="J50" s="319">
+      <c r="J50" s="335">
         <f t="shared" si="20"/>
         <v>20137430.77782803</v>
       </c>
-      <c r="K50" s="319">
+      <c r="K50" s="335">
         <f t="shared" si="20"/>
         <v>6490894.562197201</v>
       </c>
-      <c r="L50" s="319">
+      <c r="L50" s="335">
         <f t="shared" si="20"/>
         <v>-2599288.5787666151</v>
       </c>
-      <c r="M50" s="319">
+      <c r="M50" s="335">
         <f t="shared" si="20"/>
         <v>-6040379.1363799218</v>
       </c>
-      <c r="N50" s="319">
+      <c r="N50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="O50" s="319">
+      <c r="O50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="P50" s="319">
+      <c r="P50" s="335">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="Q50" s="319" t="str">
+      <c r="Q50" s="335" t="str">
         <f t="shared" si="20"/>
         <v/>
       </c>
@@ -11982,52 +11998,52 @@
       <c r="B58" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="318">
+      <c r="C58" s="334">
         <f>BS!$C67*C66</f>
         <v>0</v>
       </c>
       <c r="E58" s="268"/>
-      <c r="G58" s="318">
+      <c r="G58" s="334">
         <f>Data!C56</f>
         <v>0</v>
       </c>
-      <c r="H58" s="318">
+      <c r="H58" s="334">
         <f>Data!D56</f>
         <v>0</v>
       </c>
-      <c r="I58" s="318">
+      <c r="I58" s="334">
         <f>Data!E56</f>
         <v>0</v>
       </c>
-      <c r="J58" s="318">
+      <c r="J58" s="334">
         <f>Data!F56</f>
         <v>0</v>
       </c>
-      <c r="K58" s="318">
+      <c r="K58" s="334">
         <f>Data!G56</f>
         <v>0</v>
       </c>
-      <c r="L58" s="318">
+      <c r="L58" s="334">
         <f>Data!H56</f>
         <v>0</v>
       </c>
-      <c r="M58" s="318">
+      <c r="M58" s="334">
         <f>Data!I56</f>
         <v>0</v>
       </c>
-      <c r="N58" s="318">
+      <c r="N58" s="334">
         <f>Data!J56</f>
         <v>0</v>
       </c>
-      <c r="O58" s="318">
+      <c r="O58" s="334">
         <f>Data!K56</f>
         <v>0</v>
       </c>
-      <c r="P58" s="318">
+      <c r="P58" s="334">
         <f>Data!L56</f>
         <v>0</v>
       </c>
-      <c r="Q58" s="318" t="str">
+      <c r="Q58" s="334" t="str">
         <f>Data!M56</f>
         <v/>
       </c>
@@ -12037,52 +12053,52 @@
       <c r="B59" s="40" t="s">
         <v>160</v>
       </c>
-      <c r="C59" s="318">
+      <c r="C59" s="334">
         <f>BS!$C68*C67</f>
         <v>0</v>
       </c>
       <c r="E59" s="268"/>
-      <c r="G59" s="318">
+      <c r="G59" s="334">
         <f>Data!C55</f>
         <v>0</v>
       </c>
-      <c r="H59" s="318">
+      <c r="H59" s="334">
         <f>Data!D55</f>
         <v>0</v>
       </c>
-      <c r="I59" s="318">
+      <c r="I59" s="334">
         <f>Data!E55</f>
         <v>0</v>
       </c>
-      <c r="J59" s="318">
+      <c r="J59" s="334">
         <f>Data!F55</f>
         <v>0</v>
       </c>
-      <c r="K59" s="318">
+      <c r="K59" s="334">
         <f>Data!G55</f>
         <v>0</v>
       </c>
-      <c r="L59" s="318">
+      <c r="L59" s="334">
         <f>Data!H55</f>
         <v>0</v>
       </c>
-      <c r="M59" s="318">
+      <c r="M59" s="334">
         <f>Data!I55</f>
         <v>0</v>
       </c>
-      <c r="N59" s="318">
+      <c r="N59" s="334">
         <f>Data!J55</f>
         <v>0</v>
       </c>
-      <c r="O59" s="318">
+      <c r="O59" s="334">
         <f>Data!K55</f>
         <v>0</v>
       </c>
-      <c r="P59" s="318">
+      <c r="P59" s="334">
         <f>Data!L55</f>
         <v>0</v>
       </c>
-      <c r="Q59" s="318" t="str">
+      <c r="Q59" s="334" t="str">
         <f>Data!M55</f>
         <v/>
       </c>
@@ -12092,52 +12108,52 @@
       <c r="B60" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="C60" s="318">
+      <c r="C60" s="334">
         <f>BS!$C69*C68</f>
         <v>0</v>
       </c>
       <c r="E60" s="268"/>
-      <c r="G60" s="318">
+      <c r="G60" s="334">
         <f>Data!C57</f>
         <v>0</v>
       </c>
-      <c r="H60" s="318">
+      <c r="H60" s="334">
         <f>Data!D57</f>
         <v>0</v>
       </c>
-      <c r="I60" s="318">
+      <c r="I60" s="334">
         <f>Data!E57</f>
         <v>0</v>
       </c>
-      <c r="J60" s="318">
+      <c r="J60" s="334">
         <f>Data!F57</f>
         <v>0</v>
       </c>
-      <c r="K60" s="318">
+      <c r="K60" s="334">
         <f>Data!G57</f>
         <v>0</v>
       </c>
-      <c r="L60" s="318">
+      <c r="L60" s="334">
         <f>Data!H57</f>
         <v>0</v>
       </c>
-      <c r="M60" s="318">
+      <c r="M60" s="334">
         <f>Data!I57</f>
         <v>0</v>
       </c>
-      <c r="N60" s="318">
+      <c r="N60" s="334">
         <f>Data!J57</f>
         <v>0</v>
       </c>
-      <c r="O60" s="318">
+      <c r="O60" s="334">
         <f>Data!K57</f>
         <v>0</v>
       </c>
-      <c r="P60" s="318">
+      <c r="P60" s="334">
         <f>Data!L57</f>
         <v>0</v>
       </c>
-      <c r="Q60" s="318" t="str">
+      <c r="Q60" s="334" t="str">
         <f>Data!M57</f>
         <v/>
       </c>
@@ -12147,52 +12163,52 @@
       <c r="B61" s="31" t="s">
         <v>195</v>
       </c>
-      <c r="C61" s="319">
+      <c r="C61" s="335">
         <f>SUM(C58:C60)</f>
         <v>0</v>
       </c>
       <c r="E61" s="268"/>
-      <c r="G61" s="319">
+      <c r="G61" s="335">
         <f t="shared" ref="G61:Q61" si="22">IF(G4="","",SUM(G58:G60))</f>
         <v>0</v>
       </c>
-      <c r="H61" s="319">
+      <c r="H61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="I61" s="319">
+      <c r="I61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="J61" s="319">
+      <c r="J61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="K61" s="319">
+      <c r="K61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="L61" s="319">
+      <c r="L61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="M61" s="319">
+      <c r="M61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="N61" s="319">
+      <c r="N61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="O61" s="319">
+      <c r="O61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="P61" s="319">
+      <c r="P61" s="335">
         <f t="shared" si="22"/>
         <v>0</v>
       </c>
-      <c r="Q61" s="319" t="str">
+      <c r="Q61" s="335" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
@@ -12202,53 +12218,53 @@
       <c r="B62" s="40" t="s">
         <v>161</v>
       </c>
-      <c r="C62" s="330">
+      <c r="C62" s="349">
         <v>0</v>
       </c>
       <c r="E62" s="266" t="s">
         <v>338</v>
       </c>
-      <c r="G62" s="318">
+      <c r="G62" s="334">
         <f>Data!C58</f>
         <v>-222656878</v>
       </c>
-      <c r="H62" s="318">
+      <c r="H62" s="334">
         <f>Data!D58</f>
         <v>40517438</v>
       </c>
-      <c r="I62" s="318">
+      <c r="I62" s="334">
         <f>Data!E58</f>
         <v>42539332</v>
       </c>
-      <c r="J62" s="318">
+      <c r="J62" s="334">
         <f>Data!F58</f>
         <v>21246453</v>
       </c>
-      <c r="K62" s="318">
+      <c r="K62" s="334">
         <f>Data!G58</f>
         <v>419243973</v>
       </c>
-      <c r="L62" s="318">
+      <c r="L62" s="334">
         <f>Data!H58</f>
         <v>260912986</v>
       </c>
-      <c r="M62" s="318">
+      <c r="M62" s="334">
         <f>Data!I58</f>
         <v>-7380704</v>
       </c>
-      <c r="N62" s="318">
+      <c r="N62" s="334">
         <f>Data!J58</f>
         <v>-18665820</v>
       </c>
-      <c r="O62" s="318">
+      <c r="O62" s="334">
         <f>Data!K58</f>
         <v>-200531275</v>
       </c>
-      <c r="P62" s="318">
+      <c r="P62" s="334">
         <f>Data!L58</f>
         <v>-342051382</v>
       </c>
-      <c r="Q62" s="318" t="str">
+      <c r="Q62" s="334" t="str">
         <f>Data!M58</f>
         <v/>
       </c>
@@ -12258,52 +12274,52 @@
       <c r="B63" s="31" t="s">
         <v>196</v>
       </c>
-      <c r="C63" s="319">
+      <c r="C63" s="335">
         <f>C61+C62</f>
         <v>0</v>
       </c>
       <c r="E63" s="268"/>
-      <c r="G63" s="319">
+      <c r="G63" s="335">
         <f t="shared" ref="G63:Q63" si="23">IF(G4="","",G61+G62)</f>
         <v>-222656878</v>
       </c>
-      <c r="H63" s="319">
+      <c r="H63" s="335">
         <f t="shared" si="23"/>
         <v>40517438</v>
       </c>
-      <c r="I63" s="319">
+      <c r="I63" s="335">
         <f t="shared" si="23"/>
         <v>42539332</v>
       </c>
-      <c r="J63" s="319">
+      <c r="J63" s="335">
         <f t="shared" si="23"/>
         <v>21246453</v>
       </c>
-      <c r="K63" s="319">
+      <c r="K63" s="335">
         <f t="shared" si="23"/>
         <v>419243973</v>
       </c>
-      <c r="L63" s="319">
+      <c r="L63" s="335">
         <f t="shared" si="23"/>
         <v>260912986</v>
       </c>
-      <c r="M63" s="319">
+      <c r="M63" s="335">
         <f t="shared" si="23"/>
         <v>-7380704</v>
       </c>
-      <c r="N63" s="319">
+      <c r="N63" s="335">
         <f t="shared" si="23"/>
         <v>-18665820</v>
       </c>
-      <c r="O63" s="319">
+      <c r="O63" s="335">
         <f t="shared" si="23"/>
         <v>-200531275</v>
       </c>
-      <c r="P63" s="319">
+      <c r="P63" s="335">
         <f t="shared" si="23"/>
         <v>-342051382</v>
       </c>
-      <c r="Q63" s="319" t="str">
+      <c r="Q63" s="335" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
@@ -13678,54 +13694,54 @@
       <c r="B101" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="C101" s="331">
+      <c r="C101" s="350">
         <f>BS!G32</f>
         <v>10968339719.389999</v>
       </c>
       <c r="D101" s="26"/>
       <c r="E101" s="269"/>
       <c r="F101" s="26"/>
-      <c r="G101" s="323">
+      <c r="G101" s="339">
         <f t="shared" ref="G101:Q101" si="42">IF(G$4="","",G105+G104)</f>
         <v>10968339719.389999</v>
       </c>
-      <c r="H101" s="323">
+      <c r="H101" s="339">
         <f t="shared" si="42"/>
         <v>12386911594</v>
       </c>
-      <c r="I101" s="323">
+      <c r="I101" s="339">
         <f t="shared" si="42"/>
         <v>12497542169</v>
       </c>
-      <c r="J101" s="323">
+      <c r="J101" s="339">
         <f t="shared" si="42"/>
         <v>11532809144</v>
       </c>
-      <c r="K101" s="323">
+      <c r="K101" s="339">
         <f t="shared" si="42"/>
         <v>9595373074</v>
       </c>
-      <c r="L101" s="323">
+      <c r="L101" s="339">
         <f t="shared" si="42"/>
         <v>3514353524</v>
       </c>
-      <c r="M101" s="323">
+      <c r="M101" s="339">
         <f t="shared" si="42"/>
         <v>3297633120</v>
       </c>
-      <c r="N101" s="323">
+      <c r="N101" s="339">
         <f t="shared" si="42"/>
         <v>3506183194</v>
       </c>
-      <c r="O101" s="323">
+      <c r="O101" s="339">
         <f t="shared" si="42"/>
         <v>3365659820</v>
       </c>
-      <c r="P101" s="323">
+      <c r="P101" s="339">
         <f t="shared" si="42"/>
         <v>3721194030</v>
       </c>
-      <c r="Q101" s="323" t="str">
+      <c r="Q101" s="339" t="str">
         <f t="shared" si="42"/>
         <v/>
       </c>
@@ -13735,54 +13751,54 @@
       <c r="B102" s="93" t="s">
         <v>211</v>
       </c>
-      <c r="C102" s="332">
+      <c r="C102" s="351">
         <f>BS!C4</f>
         <v>91009309.849999994</v>
       </c>
       <c r="D102" s="89"/>
       <c r="E102" s="270"/>
       <c r="F102" s="89"/>
-      <c r="G102" s="333">
+      <c r="G102" s="352">
         <f>IF(G$4="","",Data!D77)</f>
         <v>64628136</v>
       </c>
-      <c r="H102" s="333">
+      <c r="H102" s="352">
         <f>IF(H$4="","",Data!E77)</f>
         <v>65511539</v>
       </c>
-      <c r="I102" s="333">
+      <c r="I102" s="352">
         <f>IF(I$4="","",Data!F77)</f>
         <v>109244674</v>
       </c>
-      <c r="J102" s="333">
+      <c r="J102" s="352">
         <f>IF(J$4="","",Data!G77)</f>
         <v>114510542</v>
       </c>
-      <c r="K102" s="333">
+      <c r="K102" s="352">
         <f>IF(K$4="","",Data!H77)</f>
         <v>58261577</v>
       </c>
-      <c r="L102" s="333">
+      <c r="L102" s="352">
         <f>IF(L$4="","",Data!I77)</f>
         <v>0</v>
       </c>
-      <c r="M102" s="333">
+      <c r="M102" s="352">
         <f>IF(M$4="","",Data!J77)</f>
         <v>0</v>
       </c>
-      <c r="N102" s="333">
+      <c r="N102" s="352">
         <f>IF(N$4="","",Data!K77)</f>
         <v>0</v>
       </c>
-      <c r="O102" s="333">
+      <c r="O102" s="352">
         <f>IF(O$4="","",Data!L77)</f>
         <v>0</v>
       </c>
-      <c r="P102" s="333">
+      <c r="P102" s="352">
         <f>IF(P$4="","",Data!M77)</f>
         <v>0</v>
       </c>
-      <c r="Q102" s="333" t="str">
+      <c r="Q102" s="352" t="str">
         <f>IF(Q$4="","",Data!N77)</f>
         <v/>
       </c>
@@ -13792,54 +13808,54 @@
       <c r="B103" s="93" t="s">
         <v>212</v>
       </c>
-      <c r="C103" s="332">
+      <c r="C103" s="351">
         <f>BS!C6+BS!C7</f>
         <v>2185835620.7199998</v>
       </c>
       <c r="D103" s="89"/>
       <c r="E103" s="270"/>
       <c r="F103" s="89"/>
-      <c r="G103" s="333">
+      <c r="G103" s="352">
         <f>IF(G$4="","",Data!D78)</f>
         <v>2100354952</v>
       </c>
-      <c r="H103" s="333">
+      <c r="H103" s="352">
         <f>IF(H$4="","",Data!E78)</f>
         <v>2166477563</v>
       </c>
-      <c r="I103" s="333">
+      <c r="I103" s="352">
         <f>IF(I$4="","",Data!F78)</f>
         <v>1886751987</v>
       </c>
-      <c r="J103" s="333">
+      <c r="J103" s="352">
         <f>IF(J$4="","",Data!G78)</f>
         <v>1420570476</v>
       </c>
-      <c r="K103" s="333">
+      <c r="K103" s="352">
         <f>IF(K$4="","",Data!H78)</f>
         <v>364381375</v>
       </c>
-      <c r="L103" s="333">
+      <c r="L103" s="352">
         <f>IF(L$4="","",Data!I78)</f>
         <v>0</v>
       </c>
-      <c r="M103" s="333">
+      <c r="M103" s="352">
         <f>IF(M$4="","",Data!J78)</f>
         <v>0</v>
       </c>
-      <c r="N103" s="333">
+      <c r="N103" s="352">
         <f>IF(N$4="","",Data!K78)</f>
         <v>0</v>
       </c>
-      <c r="O103" s="333">
+      <c r="O103" s="352">
         <f>IF(O$4="","",Data!L78)</f>
         <v>0</v>
       </c>
-      <c r="P103" s="333">
+      <c r="P103" s="352">
         <f>IF(P$4="","",Data!M78)</f>
         <v>0</v>
       </c>
-      <c r="Q103" s="333" t="str">
+      <c r="Q103" s="352" t="str">
         <f>IF(Q$4="","",Data!N78)</f>
         <v/>
       </c>
@@ -13849,54 +13865,54 @@
       <c r="B104" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="C104" s="331">
+      <c r="C104" s="350">
         <f>BS!G30</f>
         <v>8514681613.9500008</v>
       </c>
       <c r="D104" s="26"/>
       <c r="E104" s="269"/>
       <c r="F104" s="26"/>
-      <c r="G104" s="323">
+      <c r="G104" s="339">
         <f>Data!C79</f>
         <v>8514681613.9500008</v>
       </c>
-      <c r="H104" s="323">
+      <c r="H104" s="339">
         <f>Data!D79</f>
         <v>8734763046</v>
       </c>
-      <c r="I104" s="323">
+      <c r="I104" s="339">
         <f>Data!E79</f>
         <v>8874519390</v>
       </c>
-      <c r="J104" s="323">
+      <c r="J104" s="339">
         <f>Data!F79</f>
         <v>8404513904</v>
       </c>
-      <c r="K104" s="323">
+      <c r="K104" s="339">
         <f>Data!G79</f>
         <v>8026536570</v>
       </c>
-      <c r="L104" s="323">
+      <c r="L104" s="339">
         <f>Data!H79</f>
         <v>2003002194</v>
       </c>
-      <c r="M104" s="323">
+      <c r="M104" s="339">
         <f>Data!I79</f>
         <v>2135750535</v>
       </c>
-      <c r="N104" s="323">
+      <c r="N104" s="339">
         <f>Data!J79</f>
         <v>2340923121</v>
       </c>
-      <c r="O104" s="323">
+      <c r="O104" s="339">
         <f>Data!K79</f>
         <v>2123382866</v>
       </c>
-      <c r="P104" s="323">
+      <c r="P104" s="339">
         <f>Data!L79</f>
         <v>2502070463</v>
       </c>
-      <c r="Q104" s="323" t="str">
+      <c r="Q104" s="339" t="str">
         <f>Data!M79</f>
         <v/>
       </c>
@@ -13906,54 +13922,54 @@
       <c r="B105" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="C105" s="331">
+      <c r="C105" s="350">
         <f>BS!G27</f>
         <v>2453658105.4399986</v>
       </c>
       <c r="D105" s="26"/>
       <c r="E105" s="269"/>
       <c r="F105" s="26"/>
-      <c r="G105" s="323">
+      <c r="G105" s="339">
         <f>Data!C80</f>
         <v>2453658105.4399986</v>
       </c>
-      <c r="H105" s="323">
+      <c r="H105" s="339">
         <f>Data!D80</f>
         <v>3652148548</v>
       </c>
-      <c r="I105" s="323">
+      <c r="I105" s="339">
         <f>Data!E80</f>
         <v>3623022779</v>
       </c>
-      <c r="J105" s="323">
+      <c r="J105" s="339">
         <f>Data!F80</f>
         <v>3128295240</v>
       </c>
-      <c r="K105" s="323">
+      <c r="K105" s="339">
         <f>Data!G80</f>
         <v>1568836504</v>
       </c>
-      <c r="L105" s="323">
+      <c r="L105" s="339">
         <f>Data!H80</f>
         <v>1511351330</v>
       </c>
-      <c r="M105" s="323">
+      <c r="M105" s="339">
         <f>Data!I80</f>
         <v>1161882585</v>
       </c>
-      <c r="N105" s="323">
+      <c r="N105" s="339">
         <f>Data!J80</f>
         <v>1165260073</v>
       </c>
-      <c r="O105" s="323">
+      <c r="O105" s="339">
         <f>Data!K80</f>
         <v>1242276954</v>
       </c>
-      <c r="P105" s="323">
+      <c r="P105" s="339">
         <f>Data!L80</f>
         <v>1219123567</v>
       </c>
-      <c r="Q105" s="323" t="str">
+      <c r="Q105" s="339" t="str">
         <f>Data!M80</f>
         <v/>
       </c>
@@ -15451,7 +15467,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:H94"/>
+  <dimension ref="A2:Q105"/>
   <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="6.1328125" customWidth="1"/>
@@ -15490,7 +15506,7 @@
       <c r="B4" s="100" t="s">
         <v>129</v>
       </c>
-      <c r="C4" s="114">
+      <c r="C4" s="344">
         <f>Normalized_FCF!C19</f>
         <v>2099961241.0878935</v>
       </c>
@@ -15522,7 +15538,7 @@
       <c r="B6" s="149" t="s">
         <v>229</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="353">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>34999354018.131561</v>
       </c>
@@ -15530,17 +15546,17 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356" t="s">
+      <c r="E6" s="365" t="s">
         <v>250</v>
       </c>
-      <c r="F6" s="356"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>225</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>BS!G31</f>
         <v>123521704.27</v>
       </c>
@@ -15548,15 +15564,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="356"/>
-      <c r="F7" s="356"/>
+      <c r="E7" s="365"/>
+      <c r="F7" s="365"/>
       <c r="H7" s="120"/>
     </row>
     <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>226</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>BS!D66</f>
         <v>51803895.882383943</v>
       </c>
@@ -15564,15 +15580,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="356"/>
-      <c r="F8" s="356"/>
+      <c r="E8" s="365"/>
+      <c r="F8" s="365"/>
       <c r="H8" s="120"/>
     </row>
     <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>191</v>
       </c>
-      <c r="C9" s="339">
+      <c r="C9" s="354">
         <f>BS!H42</f>
         <v>29558000.651999995</v>
       </c>
@@ -15580,15 +15596,15 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="356"/>
-      <c r="F9" s="356"/>
+      <c r="E9" s="365"/>
+      <c r="F9" s="365"/>
       <c r="H9" s="120"/>
     </row>
     <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="338">
+      <c r="C10" s="353">
         <f>C6-C7+C8+C9</f>
         <v>34957194210.39595</v>
       </c>
@@ -15655,7 +15671,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" ht="13.25" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>135</v>
       </c>
@@ -15665,7 +15681,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" ht="13.25" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>107</v>
       </c>
@@ -15679,10 +15695,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" ht="13.15">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>108</v>
       </c>
@@ -15700,7 +15716,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15722,7 +15738,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15744,7 +15760,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15764,9 +15780,19 @@
         <f t="shared" si="1"/>
         <v>2021178135.6471417</v>
       </c>
-      <c r="H23" s="120"/>
-    </row>
-    <row r="24" spans="2:8">
+      <c r="G23" s="344"/>
+      <c r="H23" s="345"/>
+      <c r="I23" s="344"/>
+      <c r="J23" s="344"/>
+      <c r="K23" s="344"/>
+      <c r="L23" s="344"/>
+      <c r="M23" s="344"/>
+      <c r="N23" s="344"/>
+      <c r="O23" s="344"/>
+      <c r="P23" s="344"/>
+      <c r="Q23" s="344"/>
+    </row>
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15786,9 +15812,19 @@
         <f t="shared" si="1"/>
         <v>1995579477.6988294</v>
       </c>
-      <c r="H24" s="120"/>
-    </row>
-    <row r="25" spans="2:8">
+      <c r="G24" s="344"/>
+      <c r="H24" s="345"/>
+      <c r="I24" s="344"/>
+      <c r="J24" s="344"/>
+      <c r="K24" s="344"/>
+      <c r="L24" s="344"/>
+      <c r="M24" s="344"/>
+      <c r="N24" s="344"/>
+      <c r="O24" s="344"/>
+      <c r="P24" s="344"/>
+      <c r="Q24" s="344"/>
+    </row>
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15808,9 +15844,19 @@
         <f t="shared" si="1"/>
         <v>1970305032.2863626</v>
       </c>
-      <c r="H25" s="120"/>
-    </row>
-    <row r="26" spans="2:8">
+      <c r="G25" s="344"/>
+      <c r="H25" s="345"/>
+      <c r="I25" s="344"/>
+      <c r="J25" s="344"/>
+      <c r="K25" s="344"/>
+      <c r="L25" s="344"/>
+      <c r="M25" s="344"/>
+      <c r="N25" s="344"/>
+      <c r="O25" s="344"/>
+      <c r="P25" s="344"/>
+      <c r="Q25" s="344"/>
+    </row>
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15832,7 +15878,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15854,7 +15900,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15876,7 +15922,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15898,7 +15944,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15920,7 +15966,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15942,7 +15988,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -15964,11 +16010,11 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
-      <c r="C33" s="123">
+      <c r="C33" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -15984,13 +16030,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H33" s="120"/>
-    </row>
-    <row r="34" spans="2:8">
+      <c r="G33" s="344"/>
+      <c r="H33" s="345"/>
+      <c r="I33" s="344"/>
+      <c r="J33" s="344"/>
+      <c r="K33" s="344"/>
+      <c r="L33" s="344"/>
+      <c r="M33" s="344"/>
+      <c r="N33" s="344"/>
+      <c r="O33" s="344"/>
+      <c r="P33" s="344"/>
+      <c r="Q33" s="344"/>
+    </row>
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
-      <c r="C34" s="123">
+      <c r="C34" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16006,13 +16062,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H34" s="120"/>
-    </row>
-    <row r="35" spans="2:8">
+      <c r="G34" s="344"/>
+      <c r="H34" s="345"/>
+      <c r="I34" s="344"/>
+      <c r="J34" s="344"/>
+      <c r="K34" s="344"/>
+      <c r="L34" s="344"/>
+      <c r="M34" s="344"/>
+      <c r="N34" s="344"/>
+      <c r="O34" s="344"/>
+      <c r="P34" s="344"/>
+      <c r="Q34" s="344"/>
+    </row>
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
-      <c r="C35" s="123">
+      <c r="C35" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16028,9 +16094,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H35" s="120"/>
-    </row>
-    <row r="36" spans="2:8">
+      <c r="G35" s="344"/>
+      <c r="H35" s="345"/>
+      <c r="I35" s="344"/>
+      <c r="J35" s="344"/>
+      <c r="K35" s="344"/>
+      <c r="L35" s="344"/>
+      <c r="M35" s="344"/>
+      <c r="N35" s="344"/>
+      <c r="O35" s="344"/>
+      <c r="P35" s="344"/>
+      <c r="Q35" s="344"/>
+    </row>
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16052,7 +16128,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16074,7 +16150,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16096,7 +16172,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16118,7 +16194,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16140,7 +16216,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16162,7 +16238,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16184,7 +16260,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16206,7 +16282,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16228,7 +16304,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16250,7 +16326,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16272,11 +16348,11 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
-      <c r="C47" s="123">
+      <c r="C47" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16292,13 +16368,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H47" s="120"/>
-    </row>
-    <row r="48" spans="2:8">
+      <c r="G47" s="344"/>
+      <c r="H47" s="345"/>
+      <c r="I47" s="344"/>
+      <c r="J47" s="344"/>
+      <c r="K47" s="344"/>
+      <c r="L47" s="344"/>
+      <c r="M47" s="344"/>
+      <c r="N47" s="344"/>
+      <c r="O47" s="344"/>
+      <c r="P47" s="344"/>
+      <c r="Q47" s="344"/>
+    </row>
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
-      <c r="C48" s="123">
+      <c r="C48" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16314,13 +16400,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H48" s="120"/>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="G48" s="344"/>
+      <c r="H48" s="345"/>
+      <c r="I48" s="344"/>
+      <c r="J48" s="344"/>
+      <c r="K48" s="344"/>
+      <c r="L48" s="344"/>
+      <c r="M48" s="344"/>
+      <c r="N48" s="344"/>
+      <c r="O48" s="344"/>
+      <c r="P48" s="344"/>
+      <c r="Q48" s="344"/>
+    </row>
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
-      <c r="C49" s="123">
+      <c r="C49" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16336,13 +16432,23 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H49" s="120"/>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="G49" s="344"/>
+      <c r="H49" s="345"/>
+      <c r="I49" s="344"/>
+      <c r="J49" s="344"/>
+      <c r="K49" s="344"/>
+      <c r="L49" s="344"/>
+      <c r="M49" s="344"/>
+      <c r="N49" s="344"/>
+      <c r="O49" s="344"/>
+      <c r="P49" s="344"/>
+      <c r="Q49" s="344"/>
+    </row>
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
-      <c r="C50" s="123">
+      <c r="C50" s="347">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -16358,9 +16464,19 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="H50" s="120"/>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="G50" s="344"/>
+      <c r="H50" s="345"/>
+      <c r="I50" s="344"/>
+      <c r="J50" s="344"/>
+      <c r="K50" s="344"/>
+      <c r="L50" s="344"/>
+      <c r="M50" s="344"/>
+      <c r="N50" s="344"/>
+      <c r="O50" s="344"/>
+      <c r="P50" s="344"/>
+      <c r="Q50" s="344"/>
+    </row>
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>132</v>
       </c>
@@ -16382,7 +16498,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>101</v>
@@ -16393,11 +16509,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>130</v>
       </c>
@@ -16407,7 +16523,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>40044694407.569565</v>
@@ -16434,7 +16550,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16456,7 +16572,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" ht="13.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16477,14 +16593,14 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
       <c r="B58" s="123">
         <v>34999354018.131531</v>
       </c>
-      <c r="C58" s="123">
+      <c r="C58" s="347">
         <v>38372840114.96933</v>
       </c>
       <c r="D58" s="123">
@@ -16496,16 +16612,26 @@
       <c r="F58" s="123">
         <v>58973004692.709213</v>
       </c>
-      <c r="H58" s="120"/>
-    </row>
-    <row r="59" spans="1:8" ht="13.15">
+      <c r="G58" s="344"/>
+      <c r="H58" s="345"/>
+      <c r="I58" s="344"/>
+      <c r="J58" s="344"/>
+      <c r="K58" s="344"/>
+      <c r="L58" s="344"/>
+      <c r="M58" s="344"/>
+      <c r="N58" s="344"/>
+      <c r="O58" s="344"/>
+      <c r="P58" s="344"/>
+      <c r="Q58" s="344"/>
+    </row>
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
       <c r="B59" s="123">
         <v>34999354018.131531</v>
       </c>
-      <c r="C59" s="123">
+      <c r="C59" s="347">
         <v>39869616531.197845</v>
       </c>
       <c r="D59" s="123">
@@ -16517,16 +16643,26 @@
       <c r="F59" s="123">
         <v>75393318373.045044</v>
       </c>
-      <c r="H59" s="120"/>
-    </row>
-    <row r="60" spans="1:8" ht="13.15">
+      <c r="G59" s="344"/>
+      <c r="H59" s="345"/>
+      <c r="I59" s="344"/>
+      <c r="J59" s="344"/>
+      <c r="K59" s="344"/>
+      <c r="L59" s="344"/>
+      <c r="M59" s="344"/>
+      <c r="N59" s="344"/>
+      <c r="O59" s="344"/>
+      <c r="P59" s="344"/>
+      <c r="Q59" s="344"/>
+    </row>
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
       <c r="B60" s="123">
         <v>34999354018.131531</v>
       </c>
-      <c r="C60" s="123">
+      <c r="C60" s="347">
         <v>41397320272.571182</v>
       </c>
       <c r="D60" s="123">
@@ -16538,16 +16674,26 @@
       <c r="F60" s="123">
         <v>97006894419.689941</v>
       </c>
-      <c r="H60" s="120"/>
-    </row>
-    <row r="61" spans="1:8" ht="13.15">
+      <c r="G60" s="344"/>
+      <c r="H60" s="345"/>
+      <c r="I60" s="344"/>
+      <c r="J60" s="344"/>
+      <c r="K60" s="344"/>
+      <c r="L60" s="344"/>
+      <c r="M60" s="344"/>
+      <c r="N60" s="344"/>
+      <c r="O60" s="344"/>
+      <c r="P60" s="344"/>
+      <c r="Q60" s="344"/>
+    </row>
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
       <c r="B61" s="123">
         <v>34999354018.131523</v>
       </c>
-      <c r="C61" s="123">
+      <c r="C61" s="347">
         <v>42876533947.068497</v>
       </c>
       <c r="D61" s="123">
@@ -16559,26 +16705,56 @@
       <c r="F61" s="123">
         <v>124402241898.03172</v>
       </c>
-      <c r="H61" s="120"/>
-    </row>
-    <row r="62" spans="1:8">
-      <c r="C62" s="114"/>
+      <c r="G61" s="344"/>
+      <c r="H61" s="345"/>
+      <c r="I61" s="344"/>
+      <c r="J61" s="344"/>
+      <c r="K61" s="344"/>
+      <c r="L61" s="344"/>
+      <c r="M61" s="344"/>
+      <c r="N61" s="344"/>
+      <c r="O61" s="344"/>
+      <c r="P61" s="344"/>
+      <c r="Q61" s="344"/>
+    </row>
+    <row r="62" spans="1:17">
+      <c r="C62" s="344"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
       <c r="F62" s="114"/>
-      <c r="H62" s="120"/>
-    </row>
-    <row r="63" spans="1:8" ht="13.15">
+      <c r="G62" s="344"/>
+      <c r="H62" s="345"/>
+      <c r="I62" s="344"/>
+      <c r="J62" s="344"/>
+      <c r="K62" s="344"/>
+      <c r="L62" s="344"/>
+      <c r="M62" s="344"/>
+      <c r="N62" s="344"/>
+      <c r="O62" s="344"/>
+      <c r="P62" s="344"/>
+      <c r="Q62" s="344"/>
+    </row>
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>131</v>
       </c>
-      <c r="C63" s="114"/>
+      <c r="C63" s="344"/>
       <c r="D63" s="114"/>
       <c r="E63" s="114"/>
       <c r="F63" s="114"/>
-      <c r="H63" s="120"/>
-    </row>
-    <row r="64" spans="1:8" ht="13.15">
+      <c r="G63" s="344"/>
+      <c r="H63" s="345"/>
+      <c r="I63" s="344"/>
+      <c r="J63" s="344"/>
+      <c r="K63" s="344"/>
+      <c r="L63" s="344"/>
+      <c r="M63" s="344"/>
+      <c r="N63" s="344"/>
+      <c r="O63" s="344"/>
+      <c r="P63" s="344"/>
+      <c r="Q63" s="344"/>
+    </row>
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16950,6 +17126,76 @@
     </row>
     <row r="94" spans="3:3">
       <c r="C94" s="115"/>
+    </row>
+    <row r="101" spans="3:17">
+      <c r="C101" s="344"/>
+      <c r="G101" s="344"/>
+      <c r="H101" s="344"/>
+      <c r="I101" s="344"/>
+      <c r="J101" s="344"/>
+      <c r="K101" s="344"/>
+      <c r="L101" s="344"/>
+      <c r="M101" s="344"/>
+      <c r="N101" s="344"/>
+      <c r="O101" s="344"/>
+      <c r="P101" s="344"/>
+      <c r="Q101" s="344"/>
+    </row>
+    <row r="102" spans="3:17">
+      <c r="C102" s="344"/>
+      <c r="G102" s="344"/>
+      <c r="H102" s="344"/>
+      <c r="I102" s="344"/>
+      <c r="J102" s="344"/>
+      <c r="K102" s="344"/>
+      <c r="L102" s="344"/>
+      <c r="M102" s="344"/>
+      <c r="N102" s="344"/>
+      <c r="O102" s="344"/>
+      <c r="P102" s="344"/>
+      <c r="Q102" s="344"/>
+    </row>
+    <row r="103" spans="3:17">
+      <c r="C103" s="344"/>
+      <c r="G103" s="344"/>
+      <c r="H103" s="344"/>
+      <c r="I103" s="344"/>
+      <c r="J103" s="344"/>
+      <c r="K103" s="344"/>
+      <c r="L103" s="344"/>
+      <c r="M103" s="344"/>
+      <c r="N103" s="344"/>
+      <c r="O103" s="344"/>
+      <c r="P103" s="344"/>
+      <c r="Q103" s="344"/>
+    </row>
+    <row r="104" spans="3:17">
+      <c r="C104" s="344"/>
+      <c r="G104" s="344"/>
+      <c r="H104" s="344"/>
+      <c r="I104" s="344"/>
+      <c r="J104" s="344"/>
+      <c r="K104" s="344"/>
+      <c r="L104" s="344"/>
+      <c r="M104" s="344"/>
+      <c r="N104" s="344"/>
+      <c r="O104" s="344"/>
+      <c r="P104" s="344"/>
+      <c r="Q104" s="344"/>
+    </row>
+    <row r="105" spans="3:17">
+      <c r="C105" s="344"/>
+      <c r="G105" s="344"/>
+      <c r="H105" s="344"/>
+      <c r="I105" s="344"/>
+      <c r="J105" s="344"/>
+      <c r="K105" s="344"/>
+      <c r="L105" s="344"/>
+      <c r="M105" s="344"/>
+      <c r="N105" s="344"/>
+      <c r="O105" s="344"/>
+      <c r="P105" s="344"/>
+      <c r="Q105" s="344"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -17052,7 +17298,7 @@
       <c r="B6" s="149" t="s">
         <v>442</v>
       </c>
-      <c r="C6" s="338">
+      <c r="C6" s="325">
         <f>(C4*(1+Terminal_Growth))/(Equity_Cost-Terminal_Growth)</f>
         <v>19358847920</v>
       </c>
@@ -17060,8 +17306,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E6" s="356"/>
-      <c r="F6" s="356"/>
+      <c r="E6" s="365"/>
+      <c r="F6" s="365"/>
       <c r="H6" s="120"/>
     </row>
     <row r="7" spans="2:8" ht="13.15">
@@ -18518,7 +18764,7 @@
       <c r="B7" s="100" t="s">
         <v>276</v>
       </c>
-      <c r="C7" s="114">
+      <c r="C7" s="344">
         <f>Normalized_FCF!G8</f>
         <v>3109212579</v>
       </c>
@@ -18526,11 +18772,11 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E7" s="358" t="str">
+      <c r="E7" s="367" t="str">
         <f>"Please develop three logical "&amp;C18&amp;"-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme "&amp;C46&amp;"-year scenarios (Success Scenario, Devil’s Advocate Scenario) for "&amp;Thesis!C5&amp;"("&amp;Thesis!C11&amp;"). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative."</f>
         <v>Please develop three logical 10-year scenarios (Base Case, Pessimistic Case, Optimistic Case) and two extreme 15-year scenarios (Success Scenario, Devil’s Advocate Scenario) for 重庆啤酒(600132.SS). Each scenario should include the Compound Growth Rate, the Probability Assessment, and the Business Narrative.</v>
       </c>
-      <c r="F7" s="358"/>
+      <c r="F7" s="367"/>
       <c r="H7" s="247">
         <v>4</v>
       </c>
@@ -18543,7 +18789,7 @@
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="114">
+      <c r="C8" s="344">
         <f>Normalized_FCF!G19</f>
         <v>2323278784.8162661</v>
       </c>
@@ -18551,8 +18797,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E8" s="358"/>
-      <c r="F8" s="358"/>
+      <c r="E8" s="367"/>
+      <c r="F8" s="367"/>
       <c r="H8" s="247">
         <v>5</v>
       </c>
@@ -18565,7 +18811,7 @@
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="C9" s="114">
+      <c r="C9" s="344">
         <f>Normalized_FCF!C19</f>
         <v>2099961241.0878935</v>
       </c>
@@ -18573,8 +18819,8 @@
         <f>Reporting_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E9" s="358"/>
-      <c r="F9" s="358"/>
+      <c r="E9" s="367"/>
+      <c r="F9" s="367"/>
       <c r="H9" s="247">
         <v>6</v>
       </c>
@@ -18584,8 +18830,8 @@
       </c>
     </row>
     <row r="10" spans="2:9">
-      <c r="E10" s="358"/>
-      <c r="F10" s="358"/>
+      <c r="E10" s="367"/>
+      <c r="F10" s="367"/>
       <c r="H10" s="247">
         <v>7</v>
       </c>
@@ -18598,8 +18844,8 @@
       <c r="B11" s="159" t="s">
         <v>448</v>
       </c>
-      <c r="E11" s="358"/>
-      <c r="F11" s="358"/>
+      <c r="E11" s="367"/>
+      <c r="F11" s="367"/>
       <c r="H11" s="247">
         <v>8</v>
       </c>
@@ -18617,8 +18863,8 @@
         <v>3.7342435425912202E-2</v>
       </c>
       <c r="D12" s="158"/>
-      <c r="E12" s="358"/>
-      <c r="F12" s="358"/>
+      <c r="E12" s="367"/>
+      <c r="F12" s="367"/>
       <c r="H12" s="247">
         <v>9</v>
       </c>
@@ -18635,8 +18881,8 @@
         <f ca="1">(Normalized_FCF!G8/OFFSET(Normalized_FCF!G8, 0, $C$4))^(1/$C$4) - 1</f>
         <v>2.3730241339145586E-2</v>
       </c>
-      <c r="E13" s="358"/>
-      <c r="F13" s="358"/>
+      <c r="E13" s="367"/>
+      <c r="F13" s="367"/>
       <c r="H13" s="247">
         <v>10</v>
       </c>
@@ -18653,8 +18899,8 @@
         <f ca="1">(Normalized_FCF!G19/OFFSET(Normalized_FCF!G19, 0, $C$4))^(1/$C$4) - 1</f>
         <v>-7.4772485650086429E-3</v>
       </c>
-      <c r="E14" s="358"/>
-      <c r="F14" s="358"/>
+      <c r="E14" s="367"/>
+      <c r="F14" s="367"/>
     </row>
     <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
@@ -18680,21 +18926,21 @@
       <c r="C18" s="150">
         <v>10</v>
       </c>
-      <c r="E18" s="358" t="s">
+      <c r="E18" s="367" t="s">
         <v>331</v>
       </c>
-      <c r="F18" s="359"/>
+      <c r="F18" s="368"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="E19" s="359"/>
-      <c r="F19" s="359"/>
+      <c r="E19" s="368"/>
+      <c r="F19" s="368"/>
     </row>
     <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>304</v>
       </c>
-      <c r="E20" s="359"/>
-      <c r="F20" s="359"/>
+      <c r="E20" s="368"/>
+      <c r="F20" s="368"/>
     </row>
     <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
@@ -18708,8 +18954,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E21" s="359"/>
-      <c r="F21" s="359"/>
+      <c r="E21" s="368"/>
+      <c r="F21" s="368"/>
     </row>
     <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
@@ -18723,8 +18969,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E22" s="359"/>
-      <c r="F22" s="359"/>
+      <c r="E22" s="368"/>
+      <c r="F22" s="368"/>
     </row>
     <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
@@ -18744,8 +18990,8 @@
         <v>10</v>
       </c>
       <c r="D25" s="163"/>
-      <c r="E25" s="357"/>
-      <c r="F25" s="357"/>
+      <c r="E25" s="366"/>
+      <c r="F25" s="366"/>
     </row>
     <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
@@ -18755,8 +19001,8 @@
         <v>0.04</v>
       </c>
       <c r="D26" s="164"/>
-      <c r="E26" s="357"/>
-      <c r="F26" s="357"/>
+      <c r="E26" s="366"/>
+      <c r="F26" s="366"/>
     </row>
     <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
@@ -18770,8 +19016,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E27" s="357"/>
-      <c r="F27" s="357"/>
+      <c r="E27" s="366"/>
+      <c r="F27" s="366"/>
     </row>
     <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
@@ -18781,8 +19027,8 @@
         <v>0.6</v>
       </c>
       <c r="D28" s="165"/>
-      <c r="E28" s="357"/>
-      <c r="F28" s="357"/>
+      <c r="E28" s="366"/>
+      <c r="F28" s="366"/>
     </row>
     <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
@@ -18802,8 +19048,8 @@
         <v>10</v>
       </c>
       <c r="D31" s="163"/>
-      <c r="E31" s="357"/>
-      <c r="F31" s="357"/>
+      <c r="E31" s="366"/>
+      <c r="F31" s="366"/>
     </row>
     <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
@@ -18813,8 +19059,8 @@
         <v>0.02</v>
       </c>
       <c r="D32" s="164"/>
-      <c r="E32" s="357"/>
-      <c r="F32" s="357"/>
+      <c r="E32" s="366"/>
+      <c r="F32" s="366"/>
     </row>
     <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
@@ -18828,8 +19074,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E33" s="357"/>
-      <c r="F33" s="357"/>
+      <c r="E33" s="366"/>
+      <c r="F33" s="366"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
@@ -18839,8 +19085,8 @@
         <v>0.2</v>
       </c>
       <c r="D34" s="165"/>
-      <c r="E34" s="357"/>
-      <c r="F34" s="357"/>
+      <c r="E34" s="366"/>
+      <c r="F34" s="366"/>
     </row>
     <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
@@ -18860,8 +19106,8 @@
         <v>10</v>
       </c>
       <c r="D37" s="163"/>
-      <c r="E37" s="357"/>
-      <c r="F37" s="357"/>
+      <c r="E37" s="366"/>
+      <c r="F37" s="366"/>
     </row>
     <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
@@ -18871,8 +19117,8 @@
         <v>0.06</v>
       </c>
       <c r="D38" s="164"/>
-      <c r="E38" s="357"/>
-      <c r="F38" s="357"/>
+      <c r="E38" s="366"/>
+      <c r="F38" s="366"/>
     </row>
     <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
@@ -18886,8 +19132,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E39" s="357"/>
-      <c r="F39" s="357"/>
+      <c r="E39" s="366"/>
+      <c r="F39" s="366"/>
     </row>
     <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
@@ -18898,8 +19144,8 @@
         <v>0.2</v>
       </c>
       <c r="D40" s="165"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="E40" s="366"/>
+      <c r="F40" s="366"/>
     </row>
     <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
@@ -18961,8 +19207,8 @@
         <v>15</v>
       </c>
       <c r="D49" s="163"/>
-      <c r="E49" s="357"/>
-      <c r="F49" s="357"/>
+      <c r="E49" s="366"/>
+      <c r="F49" s="366"/>
     </row>
     <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
@@ -18972,8 +19218,8 @@
         <v>0</v>
       </c>
       <c r="D50" s="164"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="E50" s="366"/>
+      <c r="F50" s="366"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
@@ -18987,8 +19233,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E51" s="357"/>
-      <c r="F51" s="357"/>
+      <c r="E51" s="366"/>
+      <c r="F51" s="366"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
@@ -18998,8 +19244,8 @@
         <v>0.05</v>
       </c>
       <c r="D52" s="165"/>
-      <c r="E52" s="357"/>
-      <c r="F52" s="357"/>
+      <c r="E52" s="366"/>
+      <c r="F52" s="366"/>
     </row>
     <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
@@ -19019,8 +19265,8 @@
         <v>15</v>
       </c>
       <c r="D55" s="163"/>
-      <c r="E55" s="357"/>
-      <c r="F55" s="357"/>
+      <c r="E55" s="366"/>
+      <c r="F55" s="366"/>
     </row>
     <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
@@ -19030,8 +19276,8 @@
         <v>0.1</v>
       </c>
       <c r="D56" s="164"/>
-      <c r="E56" s="357"/>
-      <c r="F56" s="357"/>
+      <c r="E56" s="366"/>
+      <c r="F56" s="366"/>
     </row>
     <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
@@ -19045,8 +19291,8 @@
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
-      <c r="E57" s="357"/>
-      <c r="F57" s="357"/>
+      <c r="E57" s="366"/>
+      <c r="F57" s="366"/>
     </row>
     <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
@@ -19056,8 +19302,8 @@
         <v>0.05</v>
       </c>
       <c r="D58" s="165"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="E58" s="366"/>
+      <c r="F58" s="366"/>
     </row>
     <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
@@ -19241,7 +19487,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33699999999999997</v>
+        <v>0.33700000000000002</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19250,7 +19496,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>4.141861698859338</v>
+        <v>4.1418616988593371</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58585259-0B36-4859-BC3E-F92B95F17D7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE94E276-C146-4DD7-B915-A8DC5EB02995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3898,29 +3898,29 @@
     <xf numFmtId="181" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4338,7 +4338,7 @@
         <v>95</v>
       </c>
       <c r="C12" s="50">
-        <v>57.36</v>
+        <v>56.7</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4359,7 +4359,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>27760.587917279998</v>
+        <v>27441.166926600003</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4396,13 +4396,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="357" t="s">
+      <c r="B18" s="359" t="s">
         <v>360</v>
       </c>
-      <c r="C18" s="357"/>
-      <c r="D18" s="357"/>
-      <c r="E18" s="357"/>
-      <c r="F18" s="357"/>
+      <c r="C18" s="359"/>
+      <c r="D18" s="359"/>
+      <c r="E18" s="359"/>
+      <c r="F18" s="359"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4485,7 +4485,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.16711358671554644</v>
+        <v>0.17178490416300884</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4527,7 +4527,7 @@
         <v>425</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="30" spans="2:6">
@@ -4602,22 +4602,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="357" t="s">
+      <c r="B36" s="359" t="s">
         <v>361</v>
       </c>
-      <c r="C36" s="357"/>
-      <c r="D36" s="357"/>
-      <c r="E36" s="357"/>
-      <c r="F36" s="357"/>
+      <c r="C36" s="359"/>
+      <c r="D36" s="359"/>
+      <c r="E36" s="359"/>
+      <c r="F36" s="359"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="359" t="s">
+      <c r="B37" s="362" t="s">
         <v>340</v>
       </c>
-      <c r="C37" s="359"/>
-      <c r="D37" s="359"/>
-      <c r="E37" s="359"/>
-      <c r="F37" s="359"/>
+      <c r="C37" s="362"/>
+      <c r="D37" s="362"/>
+      <c r="E37" s="362"/>
+      <c r="F37" s="362"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4629,13 +4629,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="358" t="s">
+      <c r="B40" s="360" t="s">
         <v>232</v>
       </c>
-      <c r="C40" s="358"/>
-      <c r="D40" s="358"/>
-      <c r="E40" s="358"/>
-      <c r="F40" s="358"/>
+      <c r="C40" s="360"/>
+      <c r="D40" s="360"/>
+      <c r="E40" s="360"/>
+      <c r="F40" s="360"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4655,13 +4655,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="358" t="s">
+      <c r="B43" s="360" t="s">
         <v>234</v>
       </c>
-      <c r="C43" s="358"/>
-      <c r="D43" s="358"/>
-      <c r="E43" s="358"/>
-      <c r="F43" s="358"/>
+      <c r="C43" s="360"/>
+      <c r="D43" s="360"/>
+      <c r="E43" s="360"/>
+      <c r="F43" s="360"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4690,13 +4690,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="358" t="s">
+      <c r="B47" s="360" t="s">
         <v>237</v>
       </c>
-      <c r="C47" s="358"/>
-      <c r="D47" s="358"/>
-      <c r="E47" s="358"/>
-      <c r="F47" s="358"/>
+      <c r="C47" s="360"/>
+      <c r="D47" s="360"/>
+      <c r="E47" s="360"/>
+      <c r="F47" s="360"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4712,13 +4712,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="358" t="s">
+      <c r="B50" s="360" t="s">
         <v>241</v>
       </c>
-      <c r="C50" s="358"/>
-      <c r="D50" s="358"/>
-      <c r="E50" s="358"/>
-      <c r="F50" s="358"/>
+      <c r="C50" s="360"/>
+      <c r="D50" s="360"/>
+      <c r="E50" s="360"/>
+      <c r="F50" s="360"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4782,13 +4782,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="358" t="s">
+      <c r="B58" s="360" t="s">
         <v>242</v>
       </c>
-      <c r="C58" s="358"/>
-      <c r="D58" s="358"/>
-      <c r="E58" s="358"/>
-      <c r="F58" s="358"/>
+      <c r="C58" s="360"/>
+      <c r="D58" s="360"/>
+      <c r="E58" s="360"/>
+      <c r="F58" s="360"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4804,7 +4804,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="358" t="s">
+      <c r="B61" s="360" t="s">
         <v>339</v>
       </c>
       <c r="C61" s="361"/>
@@ -4826,22 +4826,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="357" t="s">
+      <c r="B64" s="359" t="s">
         <v>344</v>
       </c>
-      <c r="C64" s="357"/>
-      <c r="D64" s="357"/>
-      <c r="E64" s="357"/>
-      <c r="F64" s="357"/>
+      <c r="C64" s="359"/>
+      <c r="D64" s="359"/>
+      <c r="E64" s="359"/>
+      <c r="F64" s="359"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="357" t="s">
+      <c r="B65" s="359" t="s">
         <v>362</v>
       </c>
-      <c r="C65" s="357"/>
-      <c r="D65" s="357"/>
-      <c r="E65" s="357"/>
-      <c r="F65" s="357"/>
+      <c r="C65" s="359"/>
+      <c r="D65" s="359"/>
+      <c r="E65" s="359"/>
+      <c r="F65" s="359"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.5645416708942995E-2</v>
+        <v>7.6525945369047083E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.1841004184100417E-2</v>
+        <v>4.2328042328042326E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>449</v>
@@ -4976,22 +4976,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="357" t="s">
+      <c r="B80" s="359" t="s">
         <v>363</v>
       </c>
-      <c r="C80" s="357"/>
-      <c r="D80" s="357"/>
-      <c r="E80" s="357"/>
-      <c r="F80" s="357"/>
+      <c r="C80" s="359"/>
+      <c r="D80" s="359"/>
+      <c r="E80" s="359"/>
+      <c r="F80" s="359"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="359" t="s">
+      <c r="B81" s="362" t="s">
         <v>253</v>
       </c>
-      <c r="C81" s="359"/>
-      <c r="D81" s="359"/>
-      <c r="E81" s="359"/>
-      <c r="F81" s="359"/>
+      <c r="C81" s="362"/>
+      <c r="D81" s="362"/>
+      <c r="E81" s="362"/>
+      <c r="F81" s="362"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5035,22 +5035,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="357" t="s">
+      <c r="B89" s="359" t="s">
         <v>364</v>
       </c>
-      <c r="C89" s="357"/>
-      <c r="D89" s="357"/>
-      <c r="E89" s="357"/>
-      <c r="F89" s="357"/>
+      <c r="C89" s="359"/>
+      <c r="D89" s="359"/>
+      <c r="E89" s="359"/>
+      <c r="F89" s="359"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="357" t="s">
+      <c r="B90" s="359" t="s">
         <v>365</v>
       </c>
-      <c r="C90" s="357"/>
-      <c r="D90" s="357"/>
-      <c r="E90" s="357"/>
-      <c r="F90" s="357"/>
+      <c r="C90" s="359"/>
+      <c r="D90" s="359"/>
+      <c r="E90" s="359"/>
+      <c r="F90" s="359"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5087,13 +5087,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="357" t="s">
+      <c r="B97" s="359" t="s">
         <v>366</v>
       </c>
-      <c r="C97" s="357"/>
-      <c r="D97" s="357"/>
-      <c r="E97" s="357"/>
-      <c r="F97" s="357"/>
+      <c r="C97" s="359"/>
+      <c r="D97" s="359"/>
+      <c r="E97" s="359"/>
+      <c r="F97" s="359"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5106,13 +5106,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="357" t="s">
+      <c r="B101" s="359" t="s">
         <v>345</v>
       </c>
-      <c r="C101" s="357"/>
-      <c r="D101" s="357"/>
-      <c r="E101" s="357"/>
-      <c r="F101" s="357"/>
+      <c r="C101" s="359"/>
+      <c r="D101" s="359"/>
+      <c r="E101" s="359"/>
+      <c r="F101" s="359"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5234,13 +5234,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="357" t="s">
+      <c r="B116" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C116" s="357"/>
-      <c r="D116" s="357"/>
-      <c r="E116" s="357"/>
-      <c r="F116" s="357"/>
+      <c r="C116" s="359"/>
+      <c r="D116" s="359"/>
+      <c r="E116" s="359"/>
+      <c r="F116" s="359"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5279,13 +5279,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="358" t="s">
+      <c r="B123" s="360" t="s">
         <v>368</v>
       </c>
-      <c r="C123" s="358"/>
-      <c r="D123" s="358"/>
-      <c r="E123" s="358"/>
-      <c r="F123" s="358"/>
+      <c r="C123" s="360"/>
+      <c r="D123" s="360"/>
+      <c r="E123" s="360"/>
+      <c r="F123" s="360"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5428,13 +5428,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="363" t="s">
         <v>371</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="363"/>
+      <c r="D134" s="363"/>
+      <c r="E134" s="363"/>
+      <c r="F134" s="363"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5447,22 +5447,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="360" t="s">
+      <c r="B138" s="364" t="s">
         <v>369</v>
       </c>
-      <c r="C138" s="360"/>
-      <c r="D138" s="360"/>
-      <c r="E138" s="360"/>
-      <c r="F138" s="360"/>
+      <c r="C138" s="364"/>
+      <c r="D138" s="364"/>
+      <c r="E138" s="364"/>
+      <c r="F138" s="364"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="357" t="s">
+      <c r="B139" s="359" t="s">
         <v>370</v>
       </c>
-      <c r="C139" s="357"/>
-      <c r="D139" s="357"/>
-      <c r="E139" s="357"/>
-      <c r="F139" s="357"/>
+      <c r="C139" s="359"/>
+      <c r="D139" s="359"/>
+      <c r="E139" s="359"/>
+      <c r="F139" s="359"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5484,7 +5484,7 @@
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="147" spans="2:4">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>4.1418616988593371</v>
+        <v>4.141861698859338</v>
       </c>
     </row>
     <row r="148" spans="2:4">
@@ -5795,13 +5795,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="364" t="s">
+      <c r="B179" s="358" t="s">
         <v>377</v>
       </c>
-      <c r="C179" s="357"/>
-      <c r="D179" s="357"/>
-      <c r="E179" s="357"/>
-      <c r="F179" s="357"/>
+      <c r="C179" s="359"/>
+      <c r="D179" s="359"/>
+      <c r="E179" s="359"/>
+      <c r="F179" s="359"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5838,13 +5838,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="358" t="s">
+      <c r="B188" s="360" t="s">
         <v>382</v>
       </c>
-      <c r="C188" s="358"/>
-      <c r="D188" s="358"/>
-      <c r="E188" s="358"/>
-      <c r="F188" s="358"/>
+      <c r="C188" s="360"/>
+      <c r="D188" s="360"/>
+      <c r="E188" s="360"/>
+      <c r="F188" s="360"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5852,22 +5852,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="363" t="s">
+      <c r="B191" s="357" t="s">
         <v>383</v>
       </c>
-      <c r="C191" s="363"/>
-      <c r="D191" s="363"/>
-      <c r="E191" s="363"/>
-      <c r="F191" s="363"/>
+      <c r="C191" s="357"/>
+      <c r="D191" s="357"/>
+      <c r="E191" s="357"/>
+      <c r="F191" s="357"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="363" t="s">
+      <c r="B192" s="357" t="s">
         <v>384</v>
       </c>
-      <c r="C192" s="363"/>
-      <c r="D192" s="363"/>
-      <c r="E192" s="363"/>
-      <c r="F192" s="363"/>
+      <c r="C192" s="357"/>
+      <c r="D192" s="357"/>
+      <c r="E192" s="357"/>
+      <c r="F192" s="357"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5891,17 +5891,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5918,6 +5907,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13466,12 +13466,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.1841004184100417E-2</v>
+        <v>4.2328042328042326E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.1841004184100417E-2</v>
+        <v>4.2328042328042326E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14665,50 +14665,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.5645416708942995E-2</v>
+        <v>7.6525945369047083E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>8.3689826445285984E-2</v>
+        <v>8.4663993737241691E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>9.6094361195825928E-2</v>
+        <v>9.7212919897576272E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.1540310901195257E-2</v>
+        <v>9.260585949369593E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>8.5595563388581444E-2</v>
+        <v>8.6591913861887679E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.7943675203425011E-2</v>
+        <v>4.8501749729602445E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.683007970916962E-2</v>
+        <v>1.7025985398905985E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.5429197866411308E-2</v>
+        <v>1.5608796995015037E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2420059547275705E-2</v>
+        <v>1.2564631668990023E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.2264597746075391E-2</v>
+        <v>1.240736025952177E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>6.7901789962692295E-3</v>
+        <v>6.8692181168607223E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14722,43 +14722,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.1027840573932475E-2</v>
+        <v>8.1971021786962375E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7676913870838558E-2</v>
+        <v>9.8813893820657833E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.3186053865586371E-2</v>
+        <v>9.4270759254497946E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.6423104696086384E-2</v>
+        <v>8.7429087925352991E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.312247785318853E-2</v>
+        <v>6.385723685465422E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6243569919011375E-2</v>
+        <v>2.6549050627063354E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.517473161070125E-2</v>
+        <v>1.5351368698233222E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1747673931538034E-2</v>
+        <v>1.1884419342381334E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0410016321337167E-3</v>
+        <v>5.0996799580104047E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.5312957152618232E-3</v>
+        <v>-5.5956811680320656E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18708,7 +18708,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-57.36</v>
+        <v>-56.7</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18948,7 +18948,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>57.36</v>
+        <v>56.7</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19487,7 +19487,7 @@
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
+        <v>0.33699999999999997</v>
       </c>
     </row>
     <row r="81" spans="2:8">
@@ -19496,7 +19496,7 @@
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>4.1418616988593371</v>
+        <v>4.141861698859338</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
@@ -19546,7 +19546,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>57.36</v>
+        <v>56.7</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.16711358671554644</v>
+        <v>0.17178490416300884</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8525A44C-BE3D-4D09-A4AA-9ABD11512C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D588708D-A269-A749-98DB-F3C0426549CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-100" yWindow="-100" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,6 +38,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2502,7 +2513,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59">
+  <fonts count="59" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3894,30 +3905,30 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -3932,7 +3943,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4221,16 +4232,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="32.73046875" style="1" customWidth="1"/>
-    <col min="3" max="4" width="25.73046875" style="1" customWidth="1"/>
-    <col min="5" max="6" width="15.73046875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
+    <col min="3" max="4" width="25.6640625" style="1" customWidth="1"/>
+    <col min="5" max="6" width="15.6640625" style="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4247,7 +4258,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="13.9">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4261,7 +4272,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B4" s="45" t="s">
         <v>415</v>
       </c>
@@ -4270,7 +4281,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="12.4">
+    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4278,7 +4289,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4287,7 +4298,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4297,7 +4308,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4307,17 +4318,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B10" s="45" t="s">
         <v>418</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B11" s="1" t="s">
         <v>417</v>
       </c>
@@ -4329,17 +4340,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>56.58</v>
+        <v>57.7</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B13" s="1" t="s">
         <v>416</v>
       </c>
@@ -4349,13 +4360,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B14" s="4" t="s">
         <v>420</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>27383.090382840001</v>
+        <v>27925.138124600002</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4363,7 +4374,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>419</v>
       </c>
@@ -4377,7 +4388,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4387,27 +4398,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B18" s="358" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
-    </row>
-    <row r="20" spans="2:6">
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4422,7 +4433,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4435,7 +4446,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B23" s="1" t="s">
         <v>434</v>
       </c>
@@ -4443,7 +4454,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="24" spans="2:6">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="1" t="s">
         <v>435</v>
       </c>
@@ -4451,7 +4462,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4467,7 +4478,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -4481,14 +4492,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.17264221100414634</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6">
+        <v>0.1647356777052329</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="45" t="s">
         <v>433</v>
       </c>
@@ -4507,7 +4518,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B29" s="1" t="s">
         <v>425</v>
       </c>
@@ -4523,10 +4534,10 @@
         <v>424</v>
       </c>
       <c r="F29" s="302">
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="1" t="s">
         <v>426</v>
       </c>
@@ -4545,7 +4556,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="1" t="s">
         <v>427</v>
       </c>
@@ -4564,7 +4575,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
@@ -4583,11 +4594,11 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="13.9">
+    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4597,25 +4608,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B36" s="358" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
-    </row>
-    <row r="39" spans="1:6">
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4624,16 +4635,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B40" s="359" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
-    </row>
-    <row r="41" spans="1:6">
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4646,20 +4657,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B43" s="359" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
-    </row>
-    <row r="44" spans="1:6">
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4672,7 +4683,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4685,16 +4696,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
-    </row>
-    <row r="48" spans="1:6">
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4707,16 +4718,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
-    </row>
-    <row r="51" spans="2:6">
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4731,7 +4742,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4746,7 +4757,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4759,12 +4770,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4777,16 +4788,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
-    </row>
-    <row r="59" spans="2:6">
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4799,8 +4810,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4808,7 +4819,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4821,25 +4832,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B64" s="358" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
-    </row>
-    <row r="67" spans="1:6">
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4852,7 +4863,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4865,23 +4876,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.6688248540561513E-2</v>
+        <v>7.5199672485701377E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.2417815482502653E-2</v>
+        <v>4.1594454072790291E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4891,7 +4902,7 @@
         <v>0.55312014930250053</v>
       </c>
     </row>
-    <row r="72" spans="1:6">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B72" s="210" t="s">
         <v>450</v>
       </c>
@@ -4902,7 +4913,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:6">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B73" s="47" t="s">
         <v>451</v>
       </c>
@@ -4915,7 +4926,7 @@
         <v>1.279974062341126</v>
       </c>
     </row>
-    <row r="74" spans="1:6">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4929,7 +4940,7 @@
         <v>0.21445578545073618</v>
       </c>
     </row>
-    <row r="75" spans="1:6">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4943,7 +4954,7 @@
         <v>1.3351699725448014</v>
       </c>
     </row>
-    <row r="76" spans="1:6">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4957,7 +4968,7 @@
         <v>4.4701988818540466</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="13.9">
+    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4967,34 +4978,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.6" customHeight="1">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
-    </row>
-    <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
-    </row>
-    <row r="83" spans="1:6">
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B84" s="1" t="s">
         <v>431</v>
       </c>
@@ -5003,7 +5014,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="85" spans="1:6">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B85" s="1" t="s">
         <v>430</v>
       </c>
@@ -5012,7 +5023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5021,34 +5032,34 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:6">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B89" s="358" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
-    </row>
-    <row r="92" spans="1:6">
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5056,7 +5067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5069,7 +5080,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="13.9">
+    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5079,38 +5090,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
-    </row>
-    <row r="98" spans="2:6">
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
+    </row>
+    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6">
+    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.6" customHeight="1">
-      <c r="B101" s="358" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
-    </row>
-    <row r="102" spans="2:6">
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
+    </row>
+    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5123,7 +5134,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="103" spans="2:6">
+    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5136,7 +5147,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6">
+    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5145,7 +5156,7 @@
         <v>5.0341856510546588E-2</v>
       </c>
     </row>
-    <row r="105" spans="2:6">
+    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5154,12 +5165,12 @@
         <v>4.1762542981319963E-2</v>
       </c>
     </row>
-    <row r="107" spans="2:6">
+    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6">
+    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5172,7 +5183,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6">
+    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5185,7 +5196,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="110" spans="2:6">
+    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5198,12 +5209,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="2:6">
+    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5216,7 +5227,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5229,16 +5240,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B116" s="358" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
-    </row>
-    <row r="118" spans="1:6">
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B118" s="47" t="s">
         <v>449</v>
       </c>
@@ -5251,7 +5262,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="119" spans="1:6">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5264,7 +5275,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="13.9">
+    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5274,16 +5285,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B123" s="359" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
-    </row>
-    <row r="125" spans="1:6" ht="12.4">
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
+    </row>
+    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5300,7 +5311,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5322,7 +5333,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5344,7 +5355,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="128" spans="1:6">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5366,7 +5377,7 @@
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="129" spans="1:6">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5388,7 +5399,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="130" spans="1:6">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5410,7 +5421,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5423,16 +5434,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B134" s="362" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
-    </row>
-    <row r="136" spans="1:6" ht="13.9">
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
+    </row>
+    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5442,30 +5453,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
-    </row>
-    <row r="140" spans="1:6">
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5474,16 +5485,16 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
       <c r="C142" s="224">
         <f>F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5496,7 +5507,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="145" spans="2:4">
+    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5509,26 +5520,26 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4">
+    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
       <c r="C146" s="297">
         <f>F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="147" spans="2:4">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
       </c>
       <c r="C147" s="216">
         <f>Scenarios!C81</f>
-        <v>4.1418616988593371</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4">
+        <v>4.141861698859338</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5538,7 +5549,7 @@
         <v>34.611184744795338</v>
       </c>
     </row>
-    <row r="149" spans="2:4">
+    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5551,7 +5562,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4">
+    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B150" s="259" t="s">
         <v>416</v>
       </c>
@@ -5564,7 +5575,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4">
+    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5573,12 +5584,12 @@
         <v>0.53151557024171581</v>
       </c>
     </row>
-    <row r="153" spans="2:4">
+    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4">
+    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5587,7 +5598,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="155" spans="2:4">
+    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5597,7 +5608,7 @@
         <v>5.160300872171014</v>
       </c>
     </row>
-    <row r="156" spans="2:4">
+    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5607,7 +5618,7 @@
         <v>49.460503195272771</v>
       </c>
     </row>
-    <row r="157" spans="2:4">
+    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5620,7 +5631,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4">
+    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B158" s="259" t="s">
         <v>416</v>
       </c>
@@ -5633,7 +5644,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4">
+    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5642,12 +5653,12 @@
         <v>0.33969071867212519</v>
       </c>
     </row>
-    <row r="161" spans="2:4">
+    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4">
+    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5656,7 +5667,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="163" spans="2:4">
+    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5666,7 +5677,7 @@
         <v>6.4152286787079351</v>
       </c>
     </row>
-    <row r="164" spans="2:4">
+    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5676,7 +5687,7 @@
         <v>69.453332925337108</v>
       </c>
     </row>
-    <row r="165" spans="2:4">
+    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5689,7 +5700,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4">
+    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B166" s="259" t="s">
         <v>416</v>
       </c>
@@ -5702,7 +5713,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4">
+    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5711,12 +5722,12 @@
         <v>8.2827207627903632E-2</v>
       </c>
     </row>
-    <row r="169" spans="2:4">
+    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B169" s="210" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="170" spans="2:4">
+    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B170" s="1" t="s">
         <v>423</v>
       </c>
@@ -5725,7 +5736,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="171" spans="2:4">
+    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5735,7 +5746,7 @@
         <v>6.1077361402784396</v>
       </c>
     </row>
-    <row r="172" spans="2:4">
+    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5745,7 +5756,7 @@
         <v>64.405366365094082</v>
       </c>
     </row>
-    <row r="173" spans="2:4">
+    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5758,7 +5769,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4">
+    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B174" s="259" t="s">
         <v>416</v>
       </c>
@@ -5771,7 +5782,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4">
+    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5780,7 +5791,7 @@
         <v>0.14689628955752243</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="13.9">
+    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5790,21 +5801,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
-    </row>
-    <row r="181" spans="1:6">
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5813,80 +5824,91 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
-    </row>
-    <row r="190" spans="1:6">
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B191" s="356" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.6" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
-    </row>
-    <row r="194" spans="2:2">
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
+    </row>
+    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2">
+    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2">
+    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2">
+    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5925,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5944,15 +5955,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="11.65"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
-    <col min="2" max="2" width="27.265625" style="1" customWidth="1"/>
-    <col min="3" max="13" width="20.73046875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.86328125" style="1"/>
+    <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
+    <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13">
+    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -6001,7 +6012,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="13.9">
+    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6017,7 +6028,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13">
+    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6025,7 +6036,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6061,7 +6072,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6097,7 +6108,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6143,7 +6154,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13">
+    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6179,7 +6190,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6209,7 +6220,7 @@
       <c r="L8" s="351"/>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6225,7 +6236,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6241,7 +6252,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13">
+    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6257,7 +6268,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6287,7 +6298,7 @@
       <c r="L12" s="351"/>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6317,7 +6328,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6353,7 +6364,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6389,7 +6400,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6407,13 +6418,13 @@
       <c r="L16" s="351"/>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13">
+    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13">
+    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6443,7 +6454,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13">
+    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6459,7 +6470,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13">
+    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6475,7 +6486,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13">
+    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6511,7 +6522,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13">
+    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6547,7 +6558,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13">
+    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6583,7 +6594,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13">
+    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6603,7 +6614,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13">
+    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6611,7 +6622,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="28" spans="2:13">
+    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6648,7 +6659,7 @@
       </c>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13">
+    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6685,7 +6696,7 @@
       </c>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13">
+    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6722,7 +6733,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13">
+    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6759,7 +6770,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13">
+    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6796,7 +6807,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="13.9">
+    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6812,12 +6823,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6866,7 +6877,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6915,7 +6926,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6964,7 +6975,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -7013,7 +7024,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7062,7 +7073,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7111,7 +7122,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7160,7 +7171,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7209,7 +7220,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7258,7 +7269,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7307,7 +7318,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7356,7 +7367,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7405,7 +7416,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13">
+    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7454,12 +7465,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13">
+    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13">
+    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7508,7 +7519,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13">
+    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7557,12 +7568,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13">
+    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13">
+    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7611,7 +7622,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13">
+    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7660,7 +7671,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13">
+    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7709,7 +7720,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13">
+    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7758,13 +7769,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13">
+    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13">
+    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7813,7 +7824,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13">
+    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7862,7 +7873,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13">
+    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7911,7 +7922,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13">
+    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -7960,7 +7971,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13">
+    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -8009,12 +8020,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13">
+    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13">
+    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8064,7 +8075,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13">
+    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8113,7 +8124,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13">
+    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8163,7 +8174,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13">
+    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8212,7 +8223,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13">
+    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8262,7 +8273,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="13.9">
+    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8278,13 +8289,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13">
+    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13">
+    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8333,7 +8344,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13">
+    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8367,7 +8378,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13">
+    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8401,7 +8412,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13">
+    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8450,7 +8461,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13">
+    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8531,18 +8542,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.265625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="18.73046875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="5.73046875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="18.73046875" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="12.265625" style="1"/>
+    <col min="3" max="4" width="18.6640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.6640625" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1">
+    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8558,7 +8569,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1">
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8569,7 +8580,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1">
+    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8589,7 +8600,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1">
+    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8611,7 +8622,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1">
+    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8632,7 +8643,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1">
+    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8653,7 +8664,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1">
+    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8674,7 +8685,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1">
+    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8695,7 +8706,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1">
+    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8716,7 +8727,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1">
+    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8728,7 +8739,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1">
+    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8740,7 +8751,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1">
+    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8764,12 +8775,12 @@
         <v>986982442.09500003</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1">
+    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1">
+    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8789,7 +8800,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1">
+    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="4" t="s">
         <v>454</v>
       </c>
@@ -8809,7 +8820,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1">
+    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8829,7 +8840,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1">
+    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8849,7 +8860,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1">
+    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8869,7 +8880,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1">
+    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8891,7 +8902,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1">
+    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8911,7 +8922,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1">
+    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8931,7 +8942,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1">
+    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8943,7 +8954,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1">
+    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8956,7 +8967,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1">
+    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -8980,7 +8991,7 @@
         <v>16068725.219999999</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1">
+    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -8997,7 +9008,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1">
+    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -9016,7 +9027,7 @@
         <v>-5174668970.3790016</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1">
+    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -9031,7 +9042,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1">
+    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9050,7 +9061,7 @@
         <v>-6443106811.8090019</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1">
+    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9066,7 +9077,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1">
+    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9083,7 +9094,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1">
+    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9103,7 +9114,7 @@
         <v>3340012643.5709996</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1">
+    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9114,7 +9125,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1">
+    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9127,7 +9138,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1">
+    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9146,7 +9157,7 @@
         <v>2336961476.2559996</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1">
+    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9162,7 +9173,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1">
+    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9178,7 +9189,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1">
+    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9194,7 +9205,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1">
+    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9213,7 +9224,7 @@
         <v>507484285.69499999</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1">
+    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9233,7 +9244,7 @@
         <v>1003051167.3150001</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1">
+    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9253,7 +9264,7 @@
         <v>973493166.66300011</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1">
+    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9272,7 +9283,7 @@
         <v>29558000.651999995</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1">
+    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9283,7 +9294,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1">
+    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9297,7 +9308,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1">
+    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9311,7 +9322,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1">
+    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9326,10 +9337,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1">
+    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1">
+    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9342,7 +9353,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1">
+    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9356,7 +9367,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1">
+    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9367,10 +9378,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1">
+    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1">
+    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9382,7 +9393,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1">
+    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9396,7 +9407,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1">
+    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9410,10 +9421,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1">
+    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1">
+    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9425,7 +9436,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1">
+    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9436,7 +9447,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1">
+    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9447,10 +9458,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1">
+    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1">
+    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9462,7 +9473,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1">
+    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9478,7 +9489,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1">
+    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9489,7 +9500,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1">
+    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9503,7 +9514,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1">
+    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9519,7 +9530,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1">
+    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9529,7 +9540,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1">
+    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9539,7 +9550,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1">
+    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9549,7 +9560,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1">
+    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9559,10 +9570,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1">
+    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1">
+    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9574,7 +9585,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1">
+    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9590,7 +9601,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1">
+    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9606,7 +9617,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1">
+    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9619,7 +9630,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1">
+    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9632,10 +9643,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1">
+    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1">
+    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9647,7 +9658,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1">
+    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9661,7 +9672,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1">
+    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9675,7 +9686,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1">
+    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9689,7 +9700,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1">
+    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9703,7 +9714,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1">
+    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9714,7 +9725,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1">
+    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9722,7 +9733,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1">
+    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
@@ -9739,7 +9750,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1">
+    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
@@ -9756,7 +9767,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1">
+    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
@@ -9773,7 +9784,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1">
+    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
@@ -9804,19 +9815,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr defaultColWidth="12.265625" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="1.265625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="26.265625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="20.73046875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="2.73046875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.73046875" style="2" customWidth="1"/>
-    <col min="7" max="17" width="20.73046875" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="12.265625" style="2"/>
+    <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
+    <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9873,7 +9884,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9896,7 +9907,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9910,7 +9921,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9967,7 +9978,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -10022,7 +10033,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10077,7 +10088,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10132,7 +10143,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10189,7 +10200,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10244,7 +10255,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10299,7 +10310,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10356,7 +10367,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10411,7 +10422,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10466,7 +10477,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10521,7 +10532,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10578,7 +10589,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10635,7 +10646,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10661,7 +10672,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10686,7 +10697,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10743,7 +10754,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10762,7 +10773,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10785,7 +10796,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10806,7 +10817,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10863,7 +10874,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10920,7 +10931,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10977,18 +10988,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11047,7 +11058,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11107,7 +11118,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11162,18 +11173,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11230,7 +11241,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11289,7 +11300,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11346,18 +11357,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11415,7 +11426,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11473,7 +11484,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11528,18 +11539,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11597,10 +11608,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11623,14 +11634,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11685,7 +11696,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11740,7 +11751,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11797,7 +11808,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11852,11 +11863,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11866,7 +11877,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11893,7 +11904,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11920,7 +11931,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -11975,11 +11986,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -11989,7 +12000,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -12044,7 +12055,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12099,7 +12110,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12154,7 +12165,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12209,7 +12220,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12265,7 +12276,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12320,11 +12331,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12334,7 +12345,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12359,7 +12370,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12384,7 +12395,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12409,7 +12420,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12436,10 +12447,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12462,7 +12473,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12483,7 +12494,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12540,7 +12551,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12597,7 +12608,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12654,7 +12665,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12711,7 +12722,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12768,7 +12779,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12827,7 +12838,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12884,7 +12895,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12941,7 +12952,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -12998,7 +13009,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13055,7 +13066,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13113,7 +13124,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13170,7 +13181,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13196,7 +13207,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13220,7 +13231,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13277,18 +13288,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13344,7 +13355,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13400,7 +13411,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13455,19 +13466,19 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.2417815482502653E-2</v>
+        <v>4.1594454072790291E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.2417815482502653E-2</v>
+        <v>4.1594454072790291E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -13510,11 +13521,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13535,7 +13546,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13592,7 +13603,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13649,10 +13660,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13675,7 +13686,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13685,7 +13696,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13742,7 +13753,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13799,7 +13810,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13856,7 +13867,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13913,7 +13924,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13970,11 +13981,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -13997,7 +14008,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14054,7 +14065,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14111,7 +14122,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14138,18 +14149,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14201,7 +14212,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14253,11 +14264,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14311,7 +14322,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14366,7 +14377,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14420,7 +14431,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14476,7 +14487,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14533,7 +14544,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14552,7 +14563,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14575,7 +14586,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14596,7 +14607,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14654,795 +14665,795 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.6688248540561513E-2</v>
+        <v>7.5199672485701377E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>8.484355682045959E-2</v>
+        <v>8.3196680154273894E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>9.7419097882512809E-2</v>
+        <v>9.5528120592592275E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.280226640672605E-2</v>
+        <v>9.1000905256370182E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>8.6775565853111206E-2</v>
+        <v>8.5091187451802969E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.860461664313289E-2</v>
+        <v>4.7661164812278313E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.7062095654258914E-2</v>
+        <v>1.6730907662356489E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.5641901548556957E-2</v>
+        <v>1.5338280582623095E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2591279880377065E-2</v>
+        <v>1.2346873754449468E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.2433674915427437E-2</v>
+        <v>1.2192328019322086E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>6.8837869781902261E-3</v>
+        <v>6.7501675429116632E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.2144873370815955E-2</v>
+        <v>8.0550380161538412E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.902346729641745E-2</v>
+        <v>9.7101348000542445E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.4470697238070583E-2</v>
+        <v>9.2636950601906992E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.7614515471324053E-2</v>
+        <v>8.5913852432712559E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.3992671079160374E-2</v>
+        <v>6.2750525644001631E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6605358263600078E-2</v>
+        <v>2.6088928432486867E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5383927274475498E-2</v>
+        <v>1.5085313781452749E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1909624897720425E-2</v>
+        <v>1.1678450202998642E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.1104958221843402E-3</v>
+        <v>5.0112972897606578E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.6075489965962911E-3</v>
+        <v>-5.4987022916363629E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
-    <row r="129" ht="15.75" customHeight="1"/>
-    <row r="130" ht="15.75" customHeight="1"/>
-    <row r="131" ht="15.75" customHeight="1"/>
-    <row r="132" ht="15.75" customHeight="1"/>
-    <row r="133" ht="15.75" customHeight="1"/>
-    <row r="134" ht="15.75" customHeight="1"/>
-    <row r="135" ht="15.75" customHeight="1"/>
-    <row r="136" ht="15.75" customHeight="1"/>
-    <row r="137" ht="15.75" customHeight="1"/>
-    <row r="138" ht="15.75" customHeight="1"/>
-    <row r="139" ht="15.75" customHeight="1"/>
-    <row r="140" ht="15.75" customHeight="1"/>
-    <row r="141" ht="15.75" customHeight="1"/>
-    <row r="142" ht="15.75" customHeight="1"/>
-    <row r="143" ht="15.75" customHeight="1"/>
-    <row r="144" ht="15.75" customHeight="1"/>
-    <row r="145" ht="15.75" customHeight="1"/>
-    <row r="146" ht="15.75" customHeight="1"/>
-    <row r="147" ht="15.75" customHeight="1"/>
-    <row r="148" ht="15.75" customHeight="1"/>
-    <row r="149" ht="15.75" customHeight="1"/>
-    <row r="150" ht="15.75" customHeight="1"/>
-    <row r="151" ht="15.75" customHeight="1"/>
-    <row r="152" ht="15.75" customHeight="1"/>
-    <row r="153" ht="15.75" customHeight="1"/>
-    <row r="154" ht="15.75" customHeight="1"/>
-    <row r="155" ht="15.75" customHeight="1"/>
-    <row r="156" ht="15.75" customHeight="1"/>
-    <row r="157" ht="15.75" customHeight="1"/>
-    <row r="158" ht="15.75" customHeight="1"/>
-    <row r="159" ht="15.75" customHeight="1"/>
-    <row r="160" ht="15.75" customHeight="1"/>
-    <row r="161" ht="15.75" customHeight="1"/>
-    <row r="162" ht="15.75" customHeight="1"/>
-    <row r="163" ht="15.75" customHeight="1"/>
-    <row r="164" ht="15.75" customHeight="1"/>
-    <row r="165" ht="15.75" customHeight="1"/>
-    <row r="166" ht="15.75" customHeight="1"/>
-    <row r="167" ht="15.75" customHeight="1"/>
-    <row r="168" ht="15.75" customHeight="1"/>
-    <row r="169" ht="15.75" customHeight="1"/>
-    <row r="170" ht="15.75" customHeight="1"/>
-    <row r="171" ht="15.75" customHeight="1"/>
-    <row r="172" ht="15.75" customHeight="1"/>
-    <row r="173" ht="15.75" customHeight="1"/>
-    <row r="174" ht="15.75" customHeight="1"/>
-    <row r="175" ht="15.75" customHeight="1"/>
-    <row r="176" ht="15.75" customHeight="1"/>
-    <row r="177" ht="15.75" customHeight="1"/>
-    <row r="178" ht="15.75" customHeight="1"/>
-    <row r="179" ht="15.75" customHeight="1"/>
-    <row r="180" ht="15.75" customHeight="1"/>
-    <row r="181" ht="15.75" customHeight="1"/>
-    <row r="182" ht="15.75" customHeight="1"/>
-    <row r="183" ht="15.75" customHeight="1"/>
-    <row r="184" ht="15.75" customHeight="1"/>
-    <row r="185" ht="15.75" customHeight="1"/>
-    <row r="186" ht="15.75" customHeight="1"/>
-    <row r="187" ht="15.75" customHeight="1"/>
-    <row r="188" ht="15.75" customHeight="1"/>
-    <row r="189" ht="15.75" customHeight="1"/>
-    <row r="190" ht="15.75" customHeight="1"/>
-    <row r="191" ht="15.75" customHeight="1"/>
-    <row r="192" ht="15.75" customHeight="1"/>
-    <row r="193" ht="15.75" customHeight="1"/>
-    <row r="194" ht="15.75" customHeight="1"/>
-    <row r="195" ht="15.75" customHeight="1"/>
-    <row r="196" ht="15.75" customHeight="1"/>
-    <row r="197" ht="15.75" customHeight="1"/>
-    <row r="198" ht="15.75" customHeight="1"/>
-    <row r="199" ht="15.75" customHeight="1"/>
-    <row r="200" ht="15.75" customHeight="1"/>
-    <row r="201" ht="15.75" customHeight="1"/>
-    <row r="202" ht="15.75" customHeight="1"/>
-    <row r="203" ht="15.75" customHeight="1"/>
-    <row r="204" ht="15.75" customHeight="1"/>
-    <row r="205" ht="15.75" customHeight="1"/>
-    <row r="206" ht="15.75" customHeight="1"/>
-    <row r="207" ht="15.75" customHeight="1"/>
-    <row r="208" ht="15.75" customHeight="1"/>
-    <row r="209" ht="15.75" customHeight="1"/>
-    <row r="210" ht="15.75" customHeight="1"/>
-    <row r="211" ht="15.75" customHeight="1"/>
-    <row r="212" ht="15.75" customHeight="1"/>
-    <row r="213" ht="15.75" customHeight="1"/>
-    <row r="214" ht="15.75" customHeight="1"/>
-    <row r="215" ht="15.75" customHeight="1"/>
-    <row r="216" ht="15.75" customHeight="1"/>
-    <row r="217" ht="15.75" customHeight="1"/>
-    <row r="218" ht="15.75" customHeight="1"/>
-    <row r="219" ht="15.75" customHeight="1"/>
-    <row r="220" ht="15.75" customHeight="1"/>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15464,16 +15475,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15485,7 +15496,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15498,7 +15509,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15519,7 +15530,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15530,7 +15541,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15548,7 +15559,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15564,7 +15575,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15580,7 +15591,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15596,7 +15607,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15610,7 +15621,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.15" thickBot="1">
+    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
@@ -15624,7 +15635,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.5" thickTop="1">
+    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
@@ -15638,10 +15649,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="13.9">
+    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15651,13 +15662,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.35" customHeight="1">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15667,7 +15678,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.35" customHeight="1">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15677,7 +15688,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.35" customHeight="1">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15691,10 +15702,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17">
+    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="13.15">
+    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15712,7 +15723,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17">
+    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15734,7 +15745,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17">
+    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15756,7 +15767,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17">
+    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15788,7 +15799,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17">
+    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15820,7 +15831,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17">
+    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15852,7 +15863,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17">
+    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15874,7 +15885,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17">
+    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15896,7 +15907,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17">
+    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15918,7 +15929,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17">
+    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15940,7 +15951,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17">
+    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15962,7 +15973,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17">
+    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15984,7 +15995,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17">
+    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -16006,7 +16017,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17">
+    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -16038,7 +16049,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17">
+    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -16070,7 +16081,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17">
+    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16102,7 +16113,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17">
+    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16124,7 +16135,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17">
+    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16146,7 +16157,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16168,7 +16179,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16190,7 +16201,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17">
+    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16212,7 +16223,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17">
+    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16234,7 +16245,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16256,7 +16267,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17">
+    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16278,7 +16289,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16300,7 +16311,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16322,7 +16333,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16344,7 +16355,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16376,7 +16387,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16408,7 +16419,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16440,7 +16451,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16472,7 +16483,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16494,7 +16505,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16505,11 +16516,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" ht="13.15">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16519,7 +16530,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" ht="13.15">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>40044694407.569565</v>
@@ -16546,7 +16557,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" ht="13.15">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16568,7 +16579,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" ht="13.15">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16589,7 +16600,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" ht="13.15">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16620,7 +16631,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" ht="13.15">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16651,7 +16662,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" ht="13.15">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16682,7 +16693,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" ht="13.15">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16713,7 +16724,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16730,7 +16741,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" ht="13.15">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16750,7 +16761,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" ht="13.15">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16773,7 +16784,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -16799,7 +16810,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16826,7 +16837,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" ht="13.15">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16853,7 +16864,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16880,7 +16891,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" ht="13.15">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16907,7 +16918,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" ht="13.15">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16933,7 +16944,7 @@
         <v>200.35228338516606</v>
       </c>
     </row>
-    <row r="71" spans="1:8" ht="13.15">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16959,7 +16970,7 @@
         <v>256.95760946976043</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="13.15">
+    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -16976,7 +16987,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -16998,7 +17009,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -17021,7 +17032,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -17044,7 +17055,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -17067,7 +17078,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -17089,14 +17100,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17104,26 +17115,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3">
+    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3">
+    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3">
+    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3">
+    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3">
+    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17137,7 +17148,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17">
+    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17151,7 +17162,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17">
+    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17165,7 +17176,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17">
+    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17179,7 +17190,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17">
+    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17224,16 +17235,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="6.1328125" customWidth="1"/>
-    <col min="2" max="2" width="24.73046875" customWidth="1"/>
-    <col min="3" max="6" width="20.73046875" customWidth="1"/>
-    <col min="7" max="7" width="5.73046875" customWidth="1"/>
-    <col min="8" max="8" width="56.86328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" customWidth="1"/>
+    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="13.9">
+    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>443</v>
       </c>
@@ -17245,7 +17256,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="13.15">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B3" s="109" t="s">
         <v>442</v>
       </c>
@@ -17258,7 +17269,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B4" s="100" t="s">
         <v>440</v>
       </c>
@@ -17279,7 +17290,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17290,7 +17301,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.35" customHeight="1">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B6" s="149" t="s">
         <v>441</v>
       </c>
@@ -17306,7 +17317,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" ht="13.15">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B7" s="149" t="s">
         <v>444</v>
       </c>
@@ -17320,10 +17331,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="13.9">
+    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17333,13 +17344,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" ht="13.15">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.35" customHeight="1">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17349,7 +17360,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.35" customHeight="1">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17359,7 +17370,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.35" customHeight="1">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17373,10 +17384,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="13.15">
+    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17394,7 +17405,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17416,7 +17427,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17438,7 +17449,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17460,7 +17471,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17482,7 +17493,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17504,7 +17515,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17526,7 +17537,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17548,7 +17559,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17570,7 +17581,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17592,7 +17603,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17614,7 +17625,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17636,7 +17647,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17658,7 +17669,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17680,7 +17691,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17702,7 +17713,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17724,7 +17735,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17746,7 +17757,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8">
+    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17768,7 +17779,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17790,7 +17801,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17812,7 +17823,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17834,7 +17845,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17856,7 +17867,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17878,7 +17889,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17900,7 +17911,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17922,7 +17933,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17944,7 +17955,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -17966,7 +17977,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -17988,7 +17999,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -18010,7 +18021,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -18032,7 +18043,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -18054,7 +18065,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -18076,7 +18087,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -18087,11 +18098,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" ht="13.15">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18101,7 +18112,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" ht="13.15">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>22149527349.487885</v>
@@ -18128,7 +18139,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" ht="13.15">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18150,7 +18161,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" ht="13.15">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18171,7 +18182,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" ht="13.15">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18192,7 +18203,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" ht="13.15">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18213,7 +18224,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" ht="13.15">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18234,7 +18245,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" ht="13.15">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18255,14 +18266,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" ht="13.15">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18272,7 +18283,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" ht="13.15">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>0</v>
@@ -18295,7 +18306,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" ht="13.15">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -18321,7 +18332,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" ht="13.15">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18348,7 +18359,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" ht="13.15">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18375,7 +18386,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" ht="13.15">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18402,7 +18413,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" ht="13.15">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18429,7 +18440,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" ht="13.15">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18455,7 +18466,7 @@
         <v>110.86706842581737</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="13.15">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18481,7 +18492,7 @@
         <v>142.17661484104494</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="13.15">
+    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18498,7 +18509,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18520,7 +18531,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18543,7 +18554,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18566,7 +18577,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18589,7 +18600,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18611,14 +18622,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18626,23 +18637,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3">
+    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3">
+    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3">
+    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18672,17 +18683,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="12.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.73046875" customWidth="1"/>
-    <col min="2" max="2" width="22.73046875" customWidth="1"/>
+    <col min="1" max="1" width="2.6640625" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
     <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.73046875" customWidth="1"/>
-    <col min="5" max="6" width="42.73046875" customWidth="1"/>
-    <col min="8" max="9" width="15.73046875" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="5" max="6" width="42.6640625" customWidth="1"/>
+    <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="13.9">
+    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18695,7 +18706,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" ht="13.15">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18704,10 +18715,10 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-56.58</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9">
+        <v>-57.7</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18727,7 +18738,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="5" spans="2:9">
+    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18736,7 +18747,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="13.15">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18756,7 +18767,7 @@
         <v>85.120030767403335</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18781,7 +18792,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18803,7 +18814,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18825,7 +18836,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9">
+    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18836,7 +18847,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="13.15">
+    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B11" s="159" t="s">
         <v>447</v>
       </c>
@@ -18850,7 +18861,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9">
+    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18869,7 +18880,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9">
+    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18887,7 +18898,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9">
+    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18898,7 +18909,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="13.9">
+    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18907,7 +18918,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" ht="13.15">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18915,7 +18926,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18927,24 +18938,24 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" ht="13.15">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>56.58</v>
+        <v>57.7</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18953,7 +18964,7 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
@@ -18968,7 +18979,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" ht="13.15">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -18977,7 +18988,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -18989,7 +19000,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6">
+    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -19000,7 +19011,7 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
@@ -19015,7 +19026,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -19026,7 +19037,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" ht="13.15">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -19035,7 +19046,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -19047,7 +19058,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6">
+    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -19058,7 +19069,7 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
@@ -19073,7 +19084,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -19084,7 +19095,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" ht="13.15">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -19093,7 +19104,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19105,7 +19116,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6">
+    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19116,7 +19127,7 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
@@ -19131,7 +19142,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19143,7 +19154,7 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" ht="13.15">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
@@ -19156,7 +19167,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="13.9">
+    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19165,12 +19176,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" ht="13.15">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19180,12 +19191,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" ht="13.15">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" ht="13.15">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19194,7 +19205,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19206,7 +19217,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6">
+    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19217,7 +19228,7 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
@@ -19232,7 +19243,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19243,7 +19254,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" ht="13.15">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19252,7 +19263,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19264,7 +19275,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6">
+    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19275,7 +19286,7 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6">
+    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
@@ -19290,7 +19301,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6">
+    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19301,7 +19312,7 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" ht="13.15">
+    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
@@ -19321,7 +19332,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="13.9">
+    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19330,7 +19341,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" ht="13.15">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19338,7 +19349,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19351,7 +19362,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6">
+    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19363,7 +19374,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6">
+    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
@@ -19379,7 +19390,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" ht="13.15">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19387,7 +19398,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19397,7 +19408,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19409,7 +19420,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19419,7 +19430,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19435,7 +19446,7 @@
         <v>-1.0530971019379444E-3</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="13.9">
+    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19444,12 +19455,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" ht="13.15">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19459,7 +19470,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19472,33 +19483,33 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" ht="13.15">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
       <c r="C80" s="167">
         <f>Thesis!F29</f>
-        <v>0.33700000000000002</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8">
+        <v>0.33699999999999997</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
       <c r="C81" s="116">
         <f>PV(C80, C76, -C77, 0)</f>
-        <v>4.1418616988593371</v>
+        <v>4.141861698859338</v>
       </c>
       <c r="D81" s="116"/>
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
@@ -19508,7 +19519,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" ht="13.15">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
@@ -19528,45 +19539,45 @@
         <v>0.53151557024171581</v>
       </c>
     </row>
-    <row r="84" spans="2:8">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" ht="13.15">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>56.58</v>
+        <v>57.7</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="13.15">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.17264221100414634</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8">
+        <v>0.1647356777052329</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" ht="13.15">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19575,7 +19586,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="91" spans="2:8">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19587,7 +19598,7 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
@@ -19597,7 +19608,7 @@
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" ht="13.15">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
@@ -19617,14 +19628,14 @@
         <v>0.33969071867212519</v>
       </c>
     </row>
-    <row r="95" spans="2:8" ht="13.15">
+    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8">
+    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19635,7 +19646,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19647,7 +19658,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
@@ -19659,7 +19670,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" ht="13.15">
+    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
@@ -19678,15 +19689,15 @@
         <v>8.2827207627903632E-2</v>
       </c>
     </row>
-    <row r="100" spans="2:8">
+    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" ht="13.15">
+    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B101" s="109" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="102" spans="2:8">
+    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B102" s="148" t="s">
         <v>421</v>
       </c>
@@ -19695,7 +19706,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:8">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19705,7 +19716,7 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8">
+    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
@@ -19715,7 +19726,7 @@
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" ht="13.15">
+    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
@@ -19734,16 +19745,16 @@
         <v>0.14689628955752243</v>
       </c>
     </row>
-    <row r="106" spans="2:8">
+    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="14.65">
+    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="13.9">
+    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19751,7 +19762,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="13.9">
+    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19759,7 +19770,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="13.9">
+    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10209"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamanl/PycharmProjects/Invest_Proc/financial_models/opportunities/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D588708D-A269-A749-98DB-F3C0426549CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227A1C9A-AF91-4468-8D67-2AC37D10E0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-100" yWindow="-100" windowWidth="17120" windowHeight="10760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -38,17 +38,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
     <ext uri="GoogleSheetsCustomDataVersion1">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataSignature="AMtx7mi73Cg0ax9bLfpeUuF69nNRn7idDQ=="/>
@@ -2513,7 +2502,7 @@
     <numFmt numFmtId="180" formatCode="0.000000000000000%"/>
     <numFmt numFmtId="181" formatCode="#,##0_);\(#,##0\);0;@"/>
   </numFmts>
-  <fonts count="59" x14ac:knownFonts="1">
+  <fonts count="59">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -3905,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -3943,7 +3932,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2 2" xfId="1" xr:uid="{A35F4541-DCCE-4554-A311-39480A36979A}"/>
   </cellStyles>
   <dxfs count="8">
@@ -4232,7 +4221,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J197"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.6640625" style="1" customWidth="1"/>
@@ -4241,7 +4230,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="B1" s="3" t="s">
         <v>41</v>
       </c>
@@ -4258,7 +4247,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="13.9">
       <c r="A2" s="222" t="s">
         <v>267</v>
       </c>
@@ -4272,7 +4261,7 @@
       <c r="I2" s="22"/>
       <c r="J2" s="22"/>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="B4" s="45" t="s">
         <v>415</v>
       </c>
@@ -4281,7 +4270,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:10" ht="14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="12.4">
       <c r="B5" s="4" t="s">
         <v>315</v>
       </c>
@@ -4289,7 +4278,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="B6" s="4" t="s">
         <v>0</v>
       </c>
@@ -4298,7 +4287,7 @@
       </c>
       <c r="E6" s="48"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="B7" s="2" t="s">
         <v>307</v>
       </c>
@@ -4308,7 +4297,7 @@
       <c r="D7" s="48"/>
       <c r="E7" s="48"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="B8" s="1" t="s">
         <v>268</v>
       </c>
@@ -4318,17 +4307,17 @@
       </c>
       <c r="E8" s="48"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="E9" s="34"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="B10" s="45" t="s">
         <v>418</v>
       </c>
       <c r="C10" s="46"/>
       <c r="E10" s="34"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="B11" s="1" t="s">
         <v>417</v>
       </c>
@@ -4340,17 +4329,17 @@
       </c>
       <c r="E11" s="34"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>57.7</v>
+        <v>58.76</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="B13" s="1" t="s">
         <v>416</v>
       </c>
@@ -4360,13 +4349,13 @@
       <c r="D13" s="48"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>420</v>
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>27925.138124600002</v>
+        <v>28438.14759448</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4374,7 +4363,7 @@
       </c>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="B15" s="4" t="s">
         <v>419</v>
       </c>
@@ -4388,7 +4377,7 @@
       </c>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="B16" s="4" t="s">
         <v>1</v>
       </c>
@@ -4398,27 +4387,27 @@
       <c r="D16" s="50"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B18" s="356" t="s">
+    <row r="18" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
+    </row>
+    <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
         <v>306</v>
       </c>
       <c r="C20" s="46"/>
       <c r="D20" s="5"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="2" t="s">
         <v>348</v>
       </c>
@@ -4433,7 +4422,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -4446,7 +4435,7 @@
       </c>
       <c r="E22" s="313"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="1" t="s">
         <v>434</v>
       </c>
@@ -4454,7 +4443,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="1" t="s">
         <v>435</v>
       </c>
@@ -4462,7 +4451,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="4" t="s">
         <v>347</v>
       </c>
@@ -4478,7 +4467,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="1" t="str">
         <f>"Expected Equity Value ("&amp;C13&amp;") :"</f>
         <v>Expected Equity Value (CNY) :</v>
@@ -4492,14 +4481,14 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.1647356777052329</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+        <v>0.15744323570336882</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6">
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="45" t="s">
         <v>433</v>
       </c>
@@ -4518,7 +4507,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="1" t="s">
         <v>425</v>
       </c>
@@ -4537,7 +4526,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6">
       <c r="B30" s="1" t="s">
         <v>426</v>
       </c>
@@ -4556,7 +4545,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="1" t="s">
         <v>427</v>
       </c>
@@ -4575,7 +4564,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
@@ -4594,11 +4583,11 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:6">
       <c r="D33" s="5"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="13.9">
       <c r="A34" s="222" t="s">
         <v>354</v>
       </c>
@@ -4608,25 +4597,25 @@
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
     </row>
-    <row r="36" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B36" s="356" t="s">
+    <row r="36" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
-    </row>
-    <row r="37" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B37" s="358" t="s">
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
+    </row>
+    <row r="37" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
+    </row>
+    <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
         <v>230</v>
       </c>
@@ -4635,16 +4624,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="357" t="s">
+    <row r="40" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
+    </row>
+    <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
         <v>232</v>
       </c>
@@ -4657,20 +4646,20 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:6">
       <c r="B42" s="47"/>
       <c r="C42" s="76"/>
     </row>
-    <row r="43" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B43" s="357" t="s">
+    <row r="43" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
+    </row>
+    <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
         <v>234</v>
       </c>
@@ -4683,7 +4672,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:6">
       <c r="B45" s="52" t="s">
         <v>235</v>
       </c>
@@ -4696,16 +4685,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B47" s="357" t="s">
+    <row r="47" spans="1:6">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
+    </row>
+    <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
         <v>237</v>
       </c>
@@ -4718,16 +4707,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B50" s="357" t="s">
+    <row r="50" spans="2:6">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
-    </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
+    </row>
+    <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
         <v>340</v>
       </c>
@@ -4742,7 +4731,7 @@
       <c r="E51" s="286"/>
       <c r="F51" s="286"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="47" t="s">
         <v>341</v>
       </c>
@@ -4757,7 +4746,7 @@
       <c r="E52" s="286"/>
       <c r="F52" s="286"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:6">
       <c r="B53" s="47" t="s">
         <v>238</v>
       </c>
@@ -4770,12 +4759,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="1" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="47" t="s">
         <v>265</v>
       </c>
@@ -4788,16 +4777,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B58" s="357" t="s">
+    <row r="58" spans="2:6">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
-    </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
+    </row>
+    <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
         <v>239</v>
       </c>
@@ -4810,8 +4799,8 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B61" s="357" t="s">
+    <row r="61" spans="2:6">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4819,7 +4808,7 @@
       <c r="E61" s="360"/>
       <c r="F61" s="360"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:6">
       <c r="B62" s="47" t="s">
         <v>242</v>
       </c>
@@ -4832,25 +4821,25 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="64" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B64" s="356" t="s">
+    <row r="64" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
-    </row>
-    <row r="65" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B65" s="356" t="s">
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
+    </row>
+    <row r="65" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
+    </row>
+    <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
         <v>270</v>
       </c>
@@ -4863,7 +4852,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:6">
       <c r="B68" s="47" t="s">
         <v>248</v>
       </c>
@@ -4876,23 +4865,23 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:6">
       <c r="B69" s="227" t="s">
         <v>390</v>
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.5199672485701377E-2</v>
+        <v>7.3843109299267698E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:6">
       <c r="B70" s="227" t="s">
         <v>308</v>
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.1594454072790291E-2</v>
+        <v>4.084411164057182E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4902,7 +4891,7 @@
         <v>0.55312014930250053</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:6">
       <c r="B72" s="210" t="s">
         <v>450</v>
       </c>
@@ -4913,7 +4902,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:6">
       <c r="B73" s="47" t="s">
         <v>451</v>
       </c>
@@ -4926,7 +4915,7 @@
         <v>1.279974062341126</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:6">
       <c r="B74" s="259" t="str">
         <f>Normalized_FCF!B117</f>
         <v>Pre-tax Profit/Sales</v>
@@ -4940,7 +4929,7 @@
         <v>0.21445578545073618</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:6">
       <c r="B75" s="259" t="str">
         <f>Normalized_FCF!B118</f>
         <v>Sales/Total Assets</v>
@@ -4954,7 +4943,7 @@
         <v>1.3351699725448014</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:6">
       <c r="B76" s="259" t="str">
         <f>Normalized_FCF!B119</f>
         <v>Total Assets/Equity</v>
@@ -4968,7 +4957,7 @@
         <v>4.4701988818540466</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" ht="13.9">
       <c r="A78" s="222" t="s">
         <v>355</v>
       </c>
@@ -4978,34 +4967,34 @@
       <c r="E78" s="36"/>
       <c r="F78" s="36"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:6">
       <c r="A79" s="209"/>
     </row>
-    <row r="80" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B81" s="358" t="s">
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
+    </row>
+    <row r="81" spans="1:6">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
+    </row>
+    <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:6">
       <c r="B84" s="1" t="s">
         <v>431</v>
       </c>
@@ -5014,7 +5003,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:6">
       <c r="B85" s="1" t="s">
         <v>430</v>
       </c>
@@ -5023,7 +5012,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:6">
       <c r="B86" s="80" t="s">
         <v>247</v>
       </c>
@@ -5032,34 +5021,34 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:6">
       <c r="C87" s="121"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:6">
       <c r="B88" s="293" t="s">
         <v>356</v>
       </c>
       <c r="C88" s="121"/>
     </row>
-    <row r="89" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B89" s="356" t="s">
+    <row r="89" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
-    </row>
-    <row r="90" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B90" s="356" t="s">
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
+    </row>
+    <row r="90" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
+    </row>
+    <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
         <v>251</v>
       </c>
@@ -5067,7 +5056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:6">
       <c r="B93" s="47" t="s">
         <v>280</v>
       </c>
@@ -5080,7 +5069,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="95" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" ht="13.9">
       <c r="A95" s="222" t="s">
         <v>357</v>
       </c>
@@ -5090,38 +5079,38 @@
       <c r="E95" s="36"/>
       <c r="F95" s="36"/>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:6">
       <c r="A96" s="209"/>
     </row>
-    <row r="97" spans="2:6" x14ac:dyDescent="0.15">
-      <c r="B97" s="356" t="s">
+    <row r="97" spans="2:6">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
-    </row>
-    <row r="98" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
+    </row>
+    <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="100" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:6">
       <c r="B100" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="101" spans="2:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B101" s="356" t="s">
+    <row r="101" spans="2:6" ht="24.5" customHeight="1">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
-    </row>
-    <row r="102" spans="2:6" x14ac:dyDescent="0.15">
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
+    </row>
+    <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
         <v>255</v>
       </c>
@@ -5134,7 +5123,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="103" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:6">
       <c r="B103" s="47" t="s">
         <v>281</v>
       </c>
@@ -5147,7 +5136,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="104" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:6">
       <c r="B104" s="296" t="s">
         <v>404</v>
       </c>
@@ -5156,7 +5145,7 @@
         <v>5.0341856510546588E-2</v>
       </c>
     </row>
-    <row r="105" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:6">
       <c r="B105" s="296" t="s">
         <v>406</v>
       </c>
@@ -5165,12 +5154,12 @@
         <v>4.1762542981319963E-2</v>
       </c>
     </row>
-    <row r="107" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:6">
       <c r="B107" s="1" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="108" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:6">
       <c r="B108" s="47" t="s">
         <v>264</v>
       </c>
@@ -5183,7 +5172,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="109" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:6">
       <c r="B109" s="47" t="s">
         <v>266</v>
       </c>
@@ -5196,7 +5185,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="110" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="110" spans="2:6">
       <c r="B110" s="47" t="s">
         <v>282</v>
       </c>
@@ -5209,12 +5198,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="112" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:6">
       <c r="B112" s="1" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:6">
       <c r="B113" s="47" t="s">
         <v>257</v>
       </c>
@@ -5227,7 +5216,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:6">
       <c r="B114" s="47" t="s">
         <v>283</v>
       </c>
@@ -5240,16 +5229,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="116" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B116" s="356" t="s">
+    <row r="116" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
+    </row>
+    <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
         <v>449</v>
       </c>
@@ -5262,7 +5251,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:6">
       <c r="B119" s="296" t="s">
         <v>405</v>
       </c>
@@ -5275,7 +5264,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="121" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" ht="13.9">
       <c r="A121" s="222" t="s">
         <v>358</v>
       </c>
@@ -5285,16 +5274,16 @@
       <c r="E121" s="36"/>
       <c r="F121" s="36"/>
     </row>
-    <row r="123" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B123" s="357" t="s">
+    <row r="123" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
-    </row>
-    <row r="125" spans="1:6" ht="14" x14ac:dyDescent="0.2">
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
+    </row>
+    <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
         <v>117</v>
       </c>
@@ -5311,7 +5300,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:6">
       <c r="B126" s="228" t="str">
         <f>DCF!B74</f>
         <v>Snowball Scenario</v>
@@ -5333,7 +5322,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:6">
       <c r="B127" s="218" t="str">
         <f>DCF!B75</f>
         <v>Optimistic</v>
@@ -5355,7 +5344,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:6">
       <c r="B128" s="218" t="str">
         <f>DCF!B76</f>
         <v>Base</v>
@@ -5377,7 +5366,7 @@
         <v>0.53999999999999992</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:6">
       <c r="B129" s="218" t="str">
         <f>DCF!B77</f>
         <v>Pessimistic</v>
@@ -5399,7 +5388,7 @@
         <v>0.18</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:6">
       <c r="B130" s="218" t="str">
         <f>DCF!B78</f>
         <v>Devil's advocate</v>
@@ -5421,7 +5410,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:6">
       <c r="B132" s="211" t="s">
         <v>258</v>
       </c>
@@ -5434,16 +5423,16 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="134" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B134" s="361" t="s">
+    <row r="134" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
-    </row>
-    <row r="136" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
+    </row>
+    <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
         <v>402</v>
       </c>
@@ -5453,30 +5442,30 @@
       <c r="E136" s="36"/>
       <c r="F136" s="36"/>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B138" s="359" t="s">
+    <row r="138" spans="1:6">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
-    </row>
-    <row r="139" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B139" s="356" t="s">
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
+    </row>
+    <row r="139" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
+    </row>
+    <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:6">
       <c r="B141" s="1" t="s">
         <v>263</v>
       </c>
@@ -5485,7 +5474,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:6">
       <c r="B142" s="1" t="s">
         <v>276</v>
       </c>
@@ -5494,7 +5483,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:6">
       <c r="B143" s="212" t="s">
         <v>261</v>
       </c>
@@ -5507,7 +5496,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:4">
       <c r="B145" s="210" t="s">
         <v>408</v>
       </c>
@@ -5520,7 +5509,7 @@
         <v/>
       </c>
     </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:4">
       <c r="B146" s="1" t="s">
         <v>407</v>
       </c>
@@ -5529,7 +5518,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="147" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="147" spans="2:4">
       <c r="B147" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5539,7 +5528,7 @@
         <v>4.141861698859338</v>
       </c>
     </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="148" spans="2:4">
       <c r="B148" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5549,7 +5538,7 @@
         <v>34.611184744795338</v>
       </c>
     </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:4">
       <c r="B149" s="80" t="s">
         <v>260</v>
       </c>
@@ -5562,7 +5551,7 @@
         <v/>
       </c>
     </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:4">
       <c r="B150" s="259" t="s">
         <v>416</v>
       </c>
@@ -5575,7 +5564,7 @@
         <v/>
       </c>
     </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:4">
       <c r="B151" s="214" t="s">
         <v>262</v>
       </c>
@@ -5584,12 +5573,12 @@
         <v>0.53151557024171581</v>
       </c>
     </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:4">
       <c r="B153" s="210" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:4">
       <c r="B154" s="1" t="s">
         <v>410</v>
       </c>
@@ -5598,7 +5587,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="155" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="155" spans="2:4">
       <c r="B155" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5608,7 +5597,7 @@
         <v>5.160300872171014</v>
       </c>
     </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="156" spans="2:4">
       <c r="B156" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5618,7 +5607,7 @@
         <v>49.460503195272771</v>
       </c>
     </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:4">
       <c r="B157" s="80" t="s">
         <v>260</v>
       </c>
@@ -5631,7 +5620,7 @@
         <v/>
       </c>
     </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="158" spans="2:4">
       <c r="B158" s="259" t="s">
         <v>416</v>
       </c>
@@ -5644,7 +5633,7 @@
         <v/>
       </c>
     </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="159" spans="2:4">
       <c r="B159" s="214" t="s">
         <v>262</v>
       </c>
@@ -5653,12 +5642,12 @@
         <v>0.33969071867212519</v>
       </c>
     </row>
-    <row r="161" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="161" spans="2:4">
       <c r="B161" s="210" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="162" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="162" spans="2:4">
       <c r="B162" s="1" t="s">
         <v>409</v>
       </c>
@@ -5667,7 +5656,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="163" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="163" spans="2:4">
       <c r="B163" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5677,7 +5666,7 @@
         <v>6.4152286787079351</v>
       </c>
     </row>
-    <row r="164" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="164" spans="2:4">
       <c r="B164" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5687,7 +5676,7 @@
         <v>69.453332925337108</v>
       </c>
     </row>
-    <row r="165" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="165" spans="2:4">
       <c r="B165" s="80" t="s">
         <v>401</v>
       </c>
@@ -5700,7 +5689,7 @@
         <v/>
       </c>
     </row>
-    <row r="166" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="166" spans="2:4">
       <c r="B166" s="259" t="s">
         <v>416</v>
       </c>
@@ -5713,7 +5702,7 @@
         <v/>
       </c>
     </row>
-    <row r="167" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:4">
       <c r="B167" s="214" t="s">
         <v>262</v>
       </c>
@@ -5722,12 +5711,12 @@
         <v>8.2827207627903632E-2</v>
       </c>
     </row>
-    <row r="169" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="169" spans="2:4">
       <c r="B169" s="210" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="170" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="170" spans="2:4">
       <c r="B170" s="1" t="s">
         <v>423</v>
       </c>
@@ -5736,7 +5725,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="171" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="171" spans="2:4">
       <c r="B171" s="212" t="str">
         <f>"PV("&amp;C141&amp;" yrs of Dividends)"</f>
         <v>PV(3 yrs of Dividends)</v>
@@ -5746,7 +5735,7 @@
         <v>6.1077361402784396</v>
       </c>
     </row>
-    <row r="172" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="172" spans="2:4">
       <c r="B172" s="212" t="str">
         <f>"+ PV(Equity Value realized at year "&amp;C141&amp;")"</f>
         <v>+ PV(Equity Value realized at year 3)</v>
@@ -5756,7 +5745,7 @@
         <v>64.405366365094082</v>
       </c>
     </row>
-    <row r="173" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="173" spans="2:4">
       <c r="B173" s="80" t="s">
         <v>401</v>
       </c>
@@ -5769,7 +5758,7 @@
         <v/>
       </c>
     </row>
-    <row r="174" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="174" spans="2:4">
       <c r="B174" s="259" t="s">
         <v>416</v>
       </c>
@@ -5782,7 +5771,7 @@
         <v/>
       </c>
     </row>
-    <row r="175" spans="2:4" x14ac:dyDescent="0.15">
+    <row r="175" spans="2:4">
       <c r="B175" s="214" t="s">
         <v>262</v>
       </c>
@@ -5791,7 +5780,7 @@
         <v>0.14689628955752243</v>
       </c>
     </row>
-    <row r="177" spans="1:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" ht="13.9">
       <c r="A177" s="222" t="s">
         <v>374</v>
       </c>
@@ -5801,21 +5790,21 @@
       <c r="E177" s="36"/>
       <c r="F177" s="36"/>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.15">
-      <c r="B179" s="363" t="s">
+    <row r="179" spans="1:6">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
+    </row>
+    <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:6">
       <c r="B182" s="360" t="s">
         <v>380</v>
       </c>
@@ -5824,91 +5813,80 @@
       <c r="E182" s="360"/>
       <c r="F182" s="360"/>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:6">
       <c r="B183" s="214" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:6">
       <c r="B184" s="214" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:6">
       <c r="B185" s="214" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:6">
       <c r="B187" s="1" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="188" spans="1:6" ht="46.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B188" s="357" t="s">
+    <row r="188" spans="1:6" ht="46.5" customHeight="1">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.15">
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
+    </row>
+    <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="191" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B191" s="362" t="s">
+    <row r="191" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
-    </row>
-    <row r="192" spans="1:6" ht="24.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B192" s="362" t="s">
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
+    </row>
+    <row r="192" spans="1:6" ht="24.5" customHeight="1">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
-    </row>
-    <row r="194" spans="2:2" x14ac:dyDescent="0.15">
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
+    </row>
+    <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="195" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="195" spans="2:2">
       <c r="B195" s="214" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="196" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="196" spans="2:2">
       <c r="B196" s="214" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="197" spans="2:2" x14ac:dyDescent="0.15">
+    <row r="197" spans="2:2">
       <c r="B197" s="214" t="s">
         <v>388</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5925,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -5955,15 +5944,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:M80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="11.65"/>
   <cols>
     <col min="1" max="1" width="3" style="1" customWidth="1"/>
     <col min="2" max="2" width="27.33203125" style="1" customWidth="1"/>
     <col min="3" max="13" width="20.6640625" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.83203125" style="1"/>
+    <col min="14" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:13">
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
         <v>CNY</v>
@@ -6012,7 +6001,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:13" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>97</v>
       </c>
@@ -6028,7 +6017,7 @@
       <c r="L2" s="37"/>
       <c r="M2" s="37"/>
     </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:13">
       <c r="B3" s="16" t="s">
         <v>27</v>
       </c>
@@ -6036,7 +6025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:13">
       <c r="B4" s="32" t="s">
         <v>2</v>
       </c>
@@ -6072,7 +6061,7 @@
       </c>
       <c r="M4" s="351"/>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:13">
       <c r="B5" s="40" t="s">
         <v>43</v>
       </c>
@@ -6108,7 +6097,7 @@
       </c>
       <c r="M5" s="351"/>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:13">
       <c r="B6" s="40" t="s">
         <v>54</v>
       </c>
@@ -6154,7 +6143,7 @@
       </c>
       <c r="M6" s="351"/>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:13">
       <c r="B7" s="69" t="s">
         <v>61</v>
       </c>
@@ -6190,7 +6179,7 @@
       </c>
       <c r="M7" s="352"/>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:13">
       <c r="B8" s="40" t="s">
         <v>49</v>
       </c>
@@ -6220,7 +6209,7 @@
       <c r="L8" s="351"/>
       <c r="M8" s="351"/>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:13">
       <c r="B9" s="40" t="s">
         <v>159</v>
       </c>
@@ -6236,7 +6225,7 @@
       <c r="L9" s="351"/>
       <c r="M9" s="351"/>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:13">
       <c r="B10" s="40" t="s">
         <v>167</v>
       </c>
@@ -6252,7 +6241,7 @@
       <c r="L10" s="351"/>
       <c r="M10" s="351"/>
     </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:13">
       <c r="B11" s="40" t="s">
         <v>158</v>
       </c>
@@ -6268,7 +6257,7 @@
       <c r="L11" s="351"/>
       <c r="M11" s="351"/>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:13">
       <c r="B12" s="40" t="s">
         <v>39</v>
       </c>
@@ -6298,7 +6287,7 @@
       <c r="L12" s="351"/>
       <c r="M12" s="351"/>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:13">
       <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
@@ -6328,7 +6317,7 @@
       <c r="L13" s="351"/>
       <c r="M13" s="351"/>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:13">
       <c r="B14" s="40" t="s">
         <v>50</v>
       </c>
@@ -6364,7 +6353,7 @@
       </c>
       <c r="M14" s="351"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:13">
       <c r="B15" s="43" t="s">
         <v>42</v>
       </c>
@@ -6400,7 +6389,7 @@
       </c>
       <c r="M15" s="353"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:13">
       <c r="B16" s="28" t="s">
         <v>44</v>
       </c>
@@ -6418,13 +6407,13 @@
       <c r="L16" s="351"/>
       <c r="M16" s="351"/>
     </row>
-    <row r="18" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:13">
       <c r="B18" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C18" s="9"/>
     </row>
-    <row r="19" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:13">
       <c r="B19" s="27" t="s">
         <v>47</v>
       </c>
@@ -6454,7 +6443,7 @@
       <c r="L19" s="351"/>
       <c r="M19" s="351"/>
     </row>
-    <row r="20" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:13">
       <c r="B20" s="27" t="s">
         <v>53</v>
       </c>
@@ -6470,7 +6459,7 @@
       <c r="L20" s="351"/>
       <c r="M20" s="351"/>
     </row>
-    <row r="21" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:13">
       <c r="B21" s="27" t="s">
         <v>52</v>
       </c>
@@ -6486,7 +6475,7 @@
       <c r="L21" s="351"/>
       <c r="M21" s="351"/>
     </row>
-    <row r="22" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:13">
       <c r="B22" s="27" t="s">
         <v>371</v>
       </c>
@@ -6522,7 +6511,7 @@
       </c>
       <c r="M22" s="351"/>
     </row>
-    <row r="23" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:13">
       <c r="B23" s="27" t="s">
         <v>373</v>
       </c>
@@ -6558,7 +6547,7 @@
       </c>
       <c r="M23" s="351"/>
     </row>
-    <row r="24" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:13">
       <c r="B24" s="27" t="s">
         <v>372</v>
       </c>
@@ -6594,7 +6583,7 @@
       </c>
       <c r="M24" s="351"/>
     </row>
-    <row r="25" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:13">
       <c r="B25" s="24" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
         <v>Dividend per share (CNY)</v>
@@ -6614,7 +6603,7 @@
       <c r="L25" s="39"/>
       <c r="M25" s="39"/>
     </row>
-    <row r="27" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:13">
       <c r="B27" s="16" t="s">
         <v>28</v>
       </c>
@@ -6622,7 +6611,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="28" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:13">
       <c r="B28" s="26" t="s">
         <v>24</v>
       </c>
@@ -6659,7 +6648,7 @@
       </c>
       <c r="M28" s="351"/>
     </row>
-    <row r="29" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:13">
       <c r="B29" s="26" t="s">
         <v>32</v>
       </c>
@@ -6696,7 +6685,7 @@
       </c>
       <c r="M29" s="351"/>
     </row>
-    <row r="30" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:13">
       <c r="B30" s="29" t="s">
         <v>40</v>
       </c>
@@ -6733,7 +6722,7 @@
       </c>
       <c r="M30" s="353"/>
     </row>
-    <row r="31" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:13">
       <c r="B31" s="29" t="s">
         <v>30</v>
       </c>
@@ -6770,7 +6759,7 @@
       </c>
       <c r="M31" s="353"/>
     </row>
-    <row r="32" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:13">
       <c r="B32" s="26" t="s">
         <v>172</v>
       </c>
@@ -6807,7 +6796,7 @@
       </c>
       <c r="M32" s="351"/>
     </row>
-    <row r="34" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:13" ht="13.9">
       <c r="B34" s="36" t="s">
         <v>81</v>
       </c>
@@ -6823,12 +6812,12 @@
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
     </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:13">
       <c r="B35" s="16" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:13">
       <c r="B36" s="32" t="s">
         <v>2</v>
       </c>
@@ -6877,7 +6866,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:13">
       <c r="B37" s="40" t="s">
         <v>43</v>
       </c>
@@ -6926,7 +6915,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:13">
       <c r="B38" s="31" t="s">
         <v>58</v>
       </c>
@@ -6975,7 +6964,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:13">
       <c r="B39" s="40" t="s">
         <v>54</v>
       </c>
@@ -7024,7 +7013,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:13">
       <c r="B40" s="69" t="s">
         <v>61</v>
       </c>
@@ -7073,7 +7062,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:13">
       <c r="B41" s="69" t="s">
         <v>64</v>
       </c>
@@ -7122,7 +7111,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:13">
       <c r="B42" s="40" t="s">
         <v>49</v>
       </c>
@@ -7171,7 +7160,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:13">
       <c r="B43" s="43" t="s">
         <v>152</v>
       </c>
@@ -7220,7 +7209,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:13">
       <c r="B44" s="43" t="s">
         <v>168</v>
       </c>
@@ -7269,7 +7258,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:13">
       <c r="B45" s="40" t="s">
         <v>68</v>
       </c>
@@ -7318,7 +7307,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:13">
       <c r="B46" s="40" t="s">
         <v>50</v>
       </c>
@@ -7367,7 +7356,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:13">
       <c r="B47" s="43" t="s">
         <v>42</v>
       </c>
@@ -7416,7 +7405,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:13">
       <c r="B48" s="28" t="s">
         <v>44</v>
       </c>
@@ -7465,12 +7454,12 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:13">
       <c r="B50" s="16" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="51" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:13">
       <c r="B51" s="40" t="s">
         <v>39</v>
       </c>
@@ -7519,7 +7508,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:13">
       <c r="B52" s="40" t="s">
         <v>67</v>
       </c>
@@ -7568,12 +7557,12 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:13">
       <c r="B54" s="174" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:13">
       <c r="B55" s="40" t="s">
         <v>159</v>
       </c>
@@ -7622,7 +7611,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:13">
       <c r="B56" s="40" t="s">
         <v>167</v>
       </c>
@@ -7671,7 +7660,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:13">
       <c r="B57" s="40" t="s">
         <v>158</v>
       </c>
@@ -7720,7 +7709,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:13">
       <c r="B58" s="40" t="s">
         <v>160</v>
       </c>
@@ -7769,13 +7758,13 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:13">
       <c r="B60" s="16" t="s">
         <v>51</v>
       </c>
       <c r="C60" s="9"/>
     </row>
-    <row r="61" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:13">
       <c r="B61" s="27" t="s">
         <v>47</v>
       </c>
@@ -7824,7 +7813,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:13">
       <c r="B62" s="27" t="s">
         <v>53</v>
       </c>
@@ -7873,7 +7862,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:13">
       <c r="B63" s="27" t="s">
         <v>52</v>
       </c>
@@ -7922,7 +7911,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:13">
       <c r="B64" s="27" t="s">
         <v>393</v>
       </c>
@@ -7971,7 +7960,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:13">
       <c r="B65" s="24" t="s">
         <v>36</v>
       </c>
@@ -8020,12 +8009,12 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:13">
       <c r="B67" s="91" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:13">
       <c r="B68" s="1" t="str">
         <f>B36</f>
         <v>Sales</v>
@@ -8075,7 +8064,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:13">
       <c r="B69" s="31" t="s">
         <v>58</v>
       </c>
@@ -8124,7 +8113,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:13">
       <c r="B70" s="80" t="str">
         <f>B43</f>
         <v>Operating EBIT</v>
@@ -8174,7 +8163,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:13">
       <c r="B71" s="43" t="s">
         <v>168</v>
       </c>
@@ -8223,7 +8212,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:13">
       <c r="B72" s="80" t="str">
         <f>B47</f>
         <v>Reported Net Income</v>
@@ -8273,7 +8262,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:13" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:13" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>82</v>
       </c>
@@ -8289,13 +8278,13 @@
       <c r="L74" s="37"/>
       <c r="M74" s="37"/>
     </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:13">
       <c r="B75" s="16" t="s">
         <v>28</v>
       </c>
       <c r="C75" s="9"/>
     </row>
-    <row r="76" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:13">
       <c r="B76" s="26" t="s">
         <v>3</v>
       </c>
@@ -8344,7 +8333,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:13">
       <c r="B77" s="93" t="s">
         <v>85</v>
       </c>
@@ -8378,7 +8367,7 @@
       <c r="L77" s="355"/>
       <c r="M77" s="355"/>
     </row>
-    <row r="78" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:13">
       <c r="B78" s="93" t="s">
         <v>86</v>
       </c>
@@ -8412,7 +8401,7 @@
       <c r="L78" s="355"/>
       <c r="M78" s="355"/>
     </row>
-    <row r="79" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:13">
       <c r="B79" s="26" t="s">
         <v>40</v>
       </c>
@@ -8461,7 +8450,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="2:13" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:13">
       <c r="B80" s="26" t="s">
         <v>30</v>
       </c>
@@ -8542,7 +8531,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="2.33203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="34" style="1" bestFit="1" customWidth="1"/>
@@ -8553,7 +8542,7 @@
     <col min="9" max="16384" width="12.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:8" ht="15" customHeight="1">
       <c r="B1" s="18" t="s">
         <v>37</v>
       </c>
@@ -8569,7 +8558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="2:8" ht="15" customHeight="1">
       <c r="B2" s="79" t="s">
         <v>156</v>
       </c>
@@ -8580,7 +8569,7 @@
       <c r="G2" s="37"/>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="15" customHeight="1">
       <c r="B3" s="16" t="s">
         <v>184</v>
       </c>
@@ -8600,7 +8589,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8" ht="15" customHeight="1">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -8622,7 +8611,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8" ht="15" customHeight="1">
       <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
@@ -8643,7 +8632,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="15" customHeight="1">
       <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
@@ -8664,7 +8653,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="15" customHeight="1">
       <c r="B7" s="1" t="s">
         <v>69</v>
       </c>
@@ -8685,7 +8674,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8" ht="15" customHeight="1">
       <c r="B8" s="1" t="s">
         <v>173</v>
       </c>
@@ -8706,7 +8695,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8" ht="15" customHeight="1">
       <c r="B9" s="4" t="s">
         <v>25</v>
       </c>
@@ -8727,7 +8716,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="10" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="15" customHeight="1">
       <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
@@ -8739,7 +8728,7 @@
       </c>
       <c r="H10" s="262"/>
     </row>
-    <row r="11" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="15" customHeight="1">
       <c r="B11" s="4" t="s">
         <v>12</v>
       </c>
@@ -8751,7 +8740,7 @@
       </c>
       <c r="H11" s="262"/>
     </row>
-    <row r="12" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="15" customHeight="1">
       <c r="B12" s="80" t="s">
         <v>72</v>
       </c>
@@ -8775,12 +8764,12 @@
         <v>986982442.09500003</v>
       </c>
     </row>
-    <row r="13" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="15" customHeight="1">
       <c r="F13" s="80"/>
       <c r="G13" s="81"/>
       <c r="H13" s="20"/>
     </row>
-    <row r="14" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8" ht="15" customHeight="1">
       <c r="B14" s="16" t="s">
         <v>183</v>
       </c>
@@ -8800,7 +8789,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="15" customHeight="1">
       <c r="B15" s="4" t="s">
         <v>454</v>
       </c>
@@ -8820,7 +8809,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="16" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="15" customHeight="1">
       <c r="B16" s="1" t="s">
         <v>34</v>
       </c>
@@ -8840,7 +8829,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="17" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8" ht="15" customHeight="1">
       <c r="B17" s="1" t="s">
         <v>69</v>
       </c>
@@ -8860,7 +8849,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="18" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8" ht="15" customHeight="1">
       <c r="B18" s="4" t="s">
         <v>173</v>
       </c>
@@ -8880,7 +8869,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="19" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8" ht="15" customHeight="1">
       <c r="B19" s="4" t="s">
         <v>26</v>
       </c>
@@ -8902,7 +8891,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8" ht="15" customHeight="1">
       <c r="B20" s="4" t="s">
         <v>18</v>
       </c>
@@ -8922,7 +8911,7 @@
         <v>0.2</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8" ht="15" customHeight="1">
       <c r="B21" s="4" t="s">
         <v>19</v>
       </c>
@@ -8942,7 +8931,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="22" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8" ht="15" customHeight="1">
       <c r="B22" s="4" t="s">
         <v>20</v>
       </c>
@@ -8954,7 +8943,7 @@
       </c>
       <c r="H22" s="262"/>
     </row>
-    <row r="23" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8" ht="15" customHeight="1">
       <c r="B23" s="4" t="s">
         <v>21</v>
       </c>
@@ -8967,7 +8956,7 @@
       </c>
       <c r="H23" s="262"/>
     </row>
-    <row r="24" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8" ht="15" customHeight="1">
       <c r="B24" s="80" t="s">
         <v>73</v>
       </c>
@@ -8991,7 +8980,7 @@
         <v>16068725.219999999</v>
       </c>
     </row>
-    <row r="26" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8" ht="15" customHeight="1">
       <c r="B26" s="16" t="s">
         <v>200</v>
       </c>
@@ -9008,7 +8997,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8" ht="15" customHeight="1">
       <c r="B27" s="4" t="s">
         <v>5</v>
       </c>
@@ -9027,7 +9016,7 @@
         <v>-5174668970.3790016</v>
       </c>
     </row>
-    <row r="28" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8" ht="15" customHeight="1">
       <c r="B28" s="4" t="s">
         <v>6</v>
       </c>
@@ -9042,7 +9031,7 @@
       </c>
       <c r="H28" s="188"/>
     </row>
-    <row r="29" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8" ht="15" customHeight="1">
       <c r="B29" s="4" t="s">
         <v>7</v>
       </c>
@@ -9061,7 +9050,7 @@
         <v>-6443106811.8090019</v>
       </c>
     </row>
-    <row r="30" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8" ht="15" customHeight="1">
       <c r="B30" s="2" t="s">
         <v>8</v>
       </c>
@@ -9077,7 +9066,7 @@
       </c>
       <c r="H30" s="188"/>
     </row>
-    <row r="31" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8" ht="15" customHeight="1">
       <c r="B31" s="80" t="s">
         <v>203</v>
       </c>
@@ -9094,7 +9083,7 @@
       </c>
       <c r="H31" s="188"/>
     </row>
-    <row r="32" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8" ht="15" customHeight="1">
       <c r="B32" s="4" t="s">
         <v>9</v>
       </c>
@@ -9114,7 +9103,7 @@
         <v>3340012643.5709996</v>
       </c>
     </row>
-    <row r="33" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8" ht="15" customHeight="1">
       <c r="B33" s="83" t="s">
         <v>4</v>
       </c>
@@ -9125,7 +9114,7 @@
       <c r="G33" s="2"/>
       <c r="H33" s="195"/>
     </row>
-    <row r="34" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8" ht="15" customHeight="1">
       <c r="B34" s="83"/>
       <c r="C34" s="84"/>
       <c r="F34" s="196" t="s">
@@ -9138,7 +9127,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8" ht="15" customHeight="1">
       <c r="B35" s="16" t="s">
         <v>201</v>
       </c>
@@ -9157,7 +9146,7 @@
         <v>2336961476.2559996</v>
       </c>
     </row>
-    <row r="36" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8" ht="15" customHeight="1">
       <c r="B36" s="4" t="s">
         <v>13</v>
       </c>
@@ -9173,7 +9162,7 @@
       </c>
       <c r="H36" s="195"/>
     </row>
-    <row r="37" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8" ht="15" customHeight="1">
       <c r="B37" s="4" t="s">
         <v>14</v>
       </c>
@@ -9189,7 +9178,7 @@
       </c>
       <c r="H37" s="195"/>
     </row>
-    <row r="38" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8" ht="15" customHeight="1">
       <c r="B38" s="4" t="s">
         <v>15</v>
       </c>
@@ -9205,7 +9194,7 @@
       </c>
       <c r="H38" s="195"/>
     </row>
-    <row r="39" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8" ht="15" customHeight="1">
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
@@ -9224,7 +9213,7 @@
         <v>507484285.69499999</v>
       </c>
     </row>
-    <row r="40" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8" ht="15" customHeight="1">
       <c r="B40" s="80" t="s">
         <v>204</v>
       </c>
@@ -9244,7 +9233,7 @@
         <v>1003051167.3150001</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8" ht="15" customHeight="1">
       <c r="B41" s="4" t="s">
         <v>17</v>
       </c>
@@ -9264,7 +9253,7 @@
         <v>973493166.66300011</v>
       </c>
     </row>
-    <row r="42" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8" ht="15" customHeight="1">
       <c r="B42" s="83" t="s">
         <v>22</v>
       </c>
@@ -9283,7 +9272,7 @@
         <v>29558000.651999995</v>
       </c>
     </row>
-    <row r="44" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8" ht="15" customHeight="1">
       <c r="B44" s="79" t="s">
         <v>96</v>
       </c>
@@ -9294,7 +9283,7 @@
       <c r="G44" s="37"/>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8" ht="15" customHeight="1">
       <c r="B45" s="16" t="s">
         <v>271</v>
       </c>
@@ -9308,7 +9297,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8" ht="15" customHeight="1">
       <c r="B46" s="1" t="s">
         <v>273</v>
       </c>
@@ -9322,7 +9311,7 @@
       </c>
       <c r="F46" s="253"/>
     </row>
-    <row r="47" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8" ht="15" customHeight="1">
       <c r="B47" s="1" t="str">
         <f>"Equity per share ("&amp;Market_currency&amp;")"</f>
         <v>Equity per share (CNY)</v>
@@ -9337,10 +9326,10 @@
       </c>
       <c r="F47" s="253"/>
     </row>
-    <row r="48" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8" ht="15" customHeight="1">
       <c r="F48" s="253"/>
     </row>
-    <row r="49" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:8" ht="15" customHeight="1">
       <c r="B49" s="157" t="s">
         <v>143</v>
       </c>
@@ -9353,7 +9342,7 @@
       <c r="E49" s="2"/>
       <c r="F49" s="253"/>
     </row>
-    <row r="50" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:8" ht="15" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>93</v>
       </c>
@@ -9367,7 +9356,7 @@
       </c>
       <c r="F50" s="253"/>
     </row>
-    <row r="51" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:8" ht="15" customHeight="1">
       <c r="B51" s="1" t="s">
         <v>176</v>
       </c>
@@ -9378,10 +9367,10 @@
       </c>
       <c r="F51" s="253"/>
     </row>
-    <row r="52" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:8" ht="15" customHeight="1">
       <c r="F52" s="253"/>
     </row>
-    <row r="53" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:8" ht="15" customHeight="1">
       <c r="B53" s="157" t="s">
         <v>142</v>
       </c>
@@ -9393,7 +9382,7 @@
       </c>
       <c r="F53" s="253"/>
     </row>
-    <row r="54" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:8" ht="15" customHeight="1">
       <c r="B54" s="1" t="s">
         <v>139</v>
       </c>
@@ -9407,7 +9396,7 @@
       </c>
       <c r="F54" s="253"/>
     </row>
-    <row r="55" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:8" ht="15" customHeight="1">
       <c r="B55" s="1" t="s">
         <v>141</v>
       </c>
@@ -9421,10 +9410,10 @@
       </c>
       <c r="F55" s="253"/>
     </row>
-    <row r="56" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:8" ht="15" customHeight="1">
       <c r="F56" s="253"/>
     </row>
-    <row r="57" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:8" ht="15" customHeight="1">
       <c r="B57" s="157" t="s">
         <v>175</v>
       </c>
@@ -9436,7 +9425,7 @@
       </c>
       <c r="F57" s="253"/>
     </row>
-    <row r="58" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:8" ht="15" customHeight="1">
       <c r="B58" s="2" t="s">
         <v>89</v>
       </c>
@@ -9447,7 +9436,7 @@
       </c>
       <c r="F58" s="5"/>
     </row>
-    <row r="59" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:8" ht="15" customHeight="1">
       <c r="B59" s="1" t="s">
         <v>92</v>
       </c>
@@ -9458,10 +9447,10 @@
       </c>
       <c r="F59" s="253"/>
     </row>
-    <row r="60" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:8" ht="15" customHeight="1">
       <c r="F60" s="253"/>
     </row>
-    <row r="61" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:8" ht="15" customHeight="1">
       <c r="B61" s="157" t="s">
         <v>274</v>
       </c>
@@ -9473,7 +9462,7 @@
       </c>
       <c r="F61" s="253"/>
     </row>
-    <row r="62" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:8" ht="15" customHeight="1">
       <c r="B62" s="1" t="s">
         <v>245</v>
       </c>
@@ -9489,7 +9478,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:8" ht="15" customHeight="1">
       <c r="B64" s="79" t="s">
         <v>193</v>
       </c>
@@ -9500,7 +9489,7 @@
       <c r="G64" s="37"/>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6" ht="15" customHeight="1">
       <c r="B65" s="16" t="s">
         <v>188</v>
       </c>
@@ -9514,7 +9503,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6" ht="15" customHeight="1">
       <c r="B66" s="105" t="s">
         <v>187</v>
       </c>
@@ -9530,7 +9519,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="67" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:6" ht="15" customHeight="1">
       <c r="B67" s="105" t="s">
         <v>177</v>
       </c>
@@ -9540,7 +9529,7 @@
       </c>
       <c r="F67" s="253"/>
     </row>
-    <row r="68" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="15" customHeight="1">
       <c r="B68" s="105" t="s">
         <v>181</v>
       </c>
@@ -9550,7 +9539,7 @@
       </c>
       <c r="F68" s="253"/>
     </row>
-    <row r="69" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6" ht="15" customHeight="1">
       <c r="B69" s="105" t="s">
         <v>179</v>
       </c>
@@ -9560,7 +9549,7 @@
       </c>
       <c r="F69" s="253"/>
     </row>
-    <row r="70" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6" ht="15" customHeight="1">
       <c r="B70" s="80" t="s">
         <v>188</v>
       </c>
@@ -9570,10 +9559,10 @@
       </c>
       <c r="F70" s="253"/>
     </row>
-    <row r="71" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6" ht="15" customHeight="1">
       <c r="F71" s="253"/>
     </row>
-    <row r="72" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6" ht="15" customHeight="1">
       <c r="B72" s="255" t="s">
         <v>318</v>
       </c>
@@ -9585,7 +9574,7 @@
       </c>
       <c r="F72" s="253"/>
     </row>
-    <row r="73" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:6" ht="15" customHeight="1">
       <c r="B73" s="105" t="s">
         <v>317</v>
       </c>
@@ -9601,7 +9590,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:6" ht="15" customHeight="1">
       <c r="B74" s="257" t="s">
         <v>321</v>
       </c>
@@ -9617,7 +9606,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="75" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="15" customHeight="1">
       <c r="B75" s="80" t="s">
         <v>320</v>
       </c>
@@ -9630,7 +9619,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="76" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6" ht="15" customHeight="1">
       <c r="B76" s="259" t="s">
         <v>322</v>
       </c>
@@ -9643,10 +9632,10 @@
         <v>323</v>
       </c>
     </row>
-    <row r="77" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6" ht="15" customHeight="1">
       <c r="F77" s="253"/>
     </row>
-    <row r="78" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:6" ht="15" customHeight="1">
       <c r="B78" s="16" t="s">
         <v>189</v>
       </c>
@@ -9658,7 +9647,7 @@
       </c>
       <c r="F78" s="253"/>
     </row>
-    <row r="79" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="15" customHeight="1">
       <c r="B79" s="105" t="s">
         <v>178</v>
       </c>
@@ -9672,7 +9661,7 @@
       </c>
       <c r="F79" s="253"/>
     </row>
-    <row r="80" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6" ht="15" customHeight="1">
       <c r="B80" s="105" t="s">
         <v>182</v>
       </c>
@@ -9686,7 +9675,7 @@
       </c>
       <c r="F80" s="253"/>
     </row>
-    <row r="81" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8" ht="15" customHeight="1">
       <c r="B81" s="105" t="s">
         <v>180</v>
       </c>
@@ -9700,7 +9689,7 @@
       </c>
       <c r="F81" s="253"/>
     </row>
-    <row r="82" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8" ht="15" customHeight="1">
       <c r="B82" s="80" t="s">
         <v>189</v>
       </c>
@@ -9714,7 +9703,7 @@
       </c>
       <c r="F82" s="253"/>
     </row>
-    <row r="84" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8" ht="15" customHeight="1">
       <c r="B84" s="79" t="s">
         <v>288</v>
       </c>
@@ -9725,7 +9714,7 @@
       <c r="G84" s="37"/>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="15" customHeight="1">
       <c r="B85" s="16" t="s">
         <v>289</v>
       </c>
@@ -9733,7 +9722,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8" ht="15" customHeight="1">
       <c r="B86" s="238" t="s">
         <v>286</v>
       </c>
@@ -9750,7 +9739,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="15" customHeight="1">
       <c r="B87" s="238" t="s">
         <v>287</v>
       </c>
@@ -9767,7 +9756,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="88" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:8" ht="15" customHeight="1">
       <c r="B88" s="239" t="s">
         <v>189</v>
       </c>
@@ -9784,7 +9773,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="89" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="15" customHeight="1">
       <c r="B89" s="80" t="s">
         <v>291</v>
       </c>
@@ -9815,19 +9804,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q808"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.33203125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.33203125" style="2" customWidth="1"/>
     <col min="2" max="2" width="26.33203125" style="2" customWidth="1"/>
     <col min="3" max="3" width="20.6640625" style="2" customWidth="1"/>
     <col min="4" max="4" width="2.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.1640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="25.1328125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.6640625" style="2" customWidth="1"/>
     <col min="7" max="17" width="20.6640625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="12.33203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" ht="15.75" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="90" t="str">
         <f>Thesis!C25</f>
@@ -9884,7 +9873,7 @@
         <v>42004</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="15.75" customHeight="1">
       <c r="A2" s="3"/>
       <c r="B2" s="54" t="s">
         <v>99</v>
@@ -9907,7 +9896,7 @@
       <c r="P2" s="37"/>
       <c r="Q2" s="37"/>
     </row>
-    <row r="3" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17" ht="15.75" customHeight="1">
       <c r="A3" s="10"/>
       <c r="B3" s="16" t="s">
         <v>66</v>
@@ -9921,7 +9910,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="9"/>
     </row>
-    <row r="4" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" ht="15.75" customHeight="1">
       <c r="A4" s="10"/>
       <c r="B4" s="26" t="s">
         <v>2</v>
@@ -9978,7 +9967,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="10"/>
       <c r="B5" s="2" t="s">
         <v>46</v>
@@ -10033,7 +10022,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="10"/>
       <c r="B6" s="31" t="s">
         <v>48</v>
@@ -10088,7 +10077,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" ht="15.75" customHeight="1">
       <c r="A7" s="10"/>
       <c r="B7" s="8" t="s">
         <v>45</v>
@@ -10143,7 +10132,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17" ht="15.75" customHeight="1">
       <c r="A8" s="10"/>
       <c r="B8" s="29" t="s">
         <v>152</v>
@@ -10200,7 +10189,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" ht="15.75" customHeight="1">
       <c r="A9" s="10"/>
       <c r="B9" s="2" t="s">
         <v>65</v>
@@ -10255,7 +10244,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" ht="15.75" customHeight="1">
       <c r="A10" s="10"/>
       <c r="B10" s="2" t="s">
         <v>80</v>
@@ -10310,7 +10299,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" ht="15.75" customHeight="1">
       <c r="A11" s="10"/>
       <c r="B11" s="31" t="s">
         <v>194</v>
@@ -10367,7 +10356,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" ht="15.75" customHeight="1">
       <c r="A12" s="10"/>
       <c r="B12" s="2" t="s">
         <v>68</v>
@@ -10422,7 +10411,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" ht="15.75" customHeight="1">
       <c r="A13" s="10"/>
       <c r="B13" s="70" t="s">
         <v>164</v>
@@ -10477,7 +10466,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" ht="15.75" customHeight="1">
       <c r="A14" s="10"/>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -10532,7 +10521,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" ht="15.75" customHeight="1">
       <c r="A15" s="10"/>
       <c r="B15" s="40" t="s">
         <v>243</v>
@@ -10589,7 +10578,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" ht="15.75" customHeight="1">
       <c r="A16" s="10"/>
       <c r="B16" s="41" t="s">
         <v>154</v>
@@ -10646,7 +10635,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" ht="15.75" customHeight="1">
       <c r="A17" s="10"/>
       <c r="B17" s="27" t="s">
         <v>52</v>
@@ -10672,7 +10661,7 @@
       <c r="P17" s="335"/>
       <c r="Q17" s="335"/>
     </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:17" ht="15.75" customHeight="1">
       <c r="A18" s="10"/>
       <c r="B18" s="27" t="s">
         <v>98</v>
@@ -10697,7 +10686,7 @@
       <c r="P18" s="336"/>
       <c r="Q18" s="336"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1">
       <c r="A19" s="10"/>
       <c r="B19" s="31" t="s">
         <v>66</v>
@@ -10754,7 +10743,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1">
       <c r="A20" s="10"/>
       <c r="B20" s="27"/>
       <c r="C20" s="62"/>
@@ -10773,7 +10762,7 @@
       <c r="P20" s="12"/>
       <c r="Q20" s="12"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1">
       <c r="A21" s="10"/>
       <c r="B21" s="54" t="s">
         <v>205</v>
@@ -10796,7 +10785,7 @@
       <c r="P21" s="37"/>
       <c r="Q21" s="37"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1">
       <c r="A22" s="10"/>
       <c r="B22" s="64" t="s">
         <v>46</v>
@@ -10817,7 +10806,7 @@
       <c r="P22" s="12"/>
       <c r="Q22" s="12"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1">
       <c r="A23" s="10"/>
       <c r="B23" s="27" t="s">
         <v>43</v>
@@ -10874,7 +10863,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1">
       <c r="A24" s="10"/>
       <c r="B24" s="68" t="s">
         <v>62</v>
@@ -10931,7 +10920,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1">
       <c r="A25" s="10"/>
       <c r="B25" s="70" t="s">
         <v>46</v>
@@ -10988,18 +10977,18 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1">
       <c r="A26" s="10"/>
       <c r="E26" s="268"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1">
       <c r="A27" s="10"/>
       <c r="B27" s="64" t="s">
         <v>206</v>
       </c>
       <c r="E27" s="268"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1">
       <c r="A28" s="10"/>
       <c r="B28" s="26" t="s">
         <v>43</v>
@@ -11058,7 +11047,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1">
       <c r="A29" s="10"/>
       <c r="B29" s="68" t="str">
         <f>B24</f>
@@ -11118,7 +11107,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1">
       <c r="A30" s="10"/>
       <c r="B30" s="70" t="s">
         <v>46</v>
@@ -11173,18 +11162,18 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1">
       <c r="A31" s="10"/>
       <c r="E31" s="268"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1">
       <c r="A32" s="10"/>
       <c r="B32" s="64" t="s">
         <v>45</v>
       </c>
       <c r="E32" s="268"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1">
       <c r="A33" s="10"/>
       <c r="B33" s="8" t="s">
         <v>174</v>
@@ -11241,7 +11230,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1">
       <c r="A34" s="10"/>
       <c r="B34" s="27" t="s">
         <v>49</v>
@@ -11300,7 +11289,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1">
       <c r="A35" s="10"/>
       <c r="B35" s="70" t="s">
         <v>45</v>
@@ -11357,18 +11346,18 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1">
       <c r="A36" s="10"/>
       <c r="E36" s="268"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1">
       <c r="A37" s="10"/>
       <c r="B37" s="64" t="s">
         <v>207</v>
       </c>
       <c r="E37" s="268"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1">
       <c r="A38" s="10"/>
       <c r="B38" s="2" t="str">
         <f>B33</f>
@@ -11426,7 +11415,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1">
       <c r="A39" s="10"/>
       <c r="B39" s="27" t="str">
         <f>B34</f>
@@ -11484,7 +11473,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1">
       <c r="A40" s="10"/>
       <c r="B40" s="70" t="s">
         <v>45</v>
@@ -11539,18 +11528,18 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1">
       <c r="A41" s="10"/>
       <c r="E41" s="268"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1">
       <c r="A42" s="10"/>
       <c r="B42" s="64" t="s">
         <v>208</v>
       </c>
       <c r="E42" s="268"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1">
       <c r="A43" s="10"/>
       <c r="B43" s="27" t="s">
         <v>171</v>
@@ -11608,10 +11597,10 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1">
       <c r="A44" s="10"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1">
       <c r="A45" s="10"/>
       <c r="B45" s="54" t="s">
         <v>209</v>
@@ -11634,14 +11623,14 @@
       <c r="P45" s="37"/>
       <c r="Q45" s="37"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1">
       <c r="A46" s="10"/>
       <c r="B46" s="64" t="s">
         <v>60</v>
       </c>
       <c r="E46" s="268"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1">
       <c r="A47" s="10"/>
       <c r="B47" s="2" t="s">
         <v>39</v>
@@ -11696,7 +11685,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1">
       <c r="A48" s="10"/>
       <c r="B48" s="2" t="s">
         <v>345</v>
@@ -11751,7 +11740,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1">
       <c r="A49" s="10"/>
       <c r="B49" s="287" t="s">
         <v>342</v>
@@ -11808,7 +11797,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1">
       <c r="A50" s="10"/>
       <c r="B50" s="70" t="s">
         <v>68</v>
@@ -11863,11 +11852,11 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1">
       <c r="A51" s="10"/>
       <c r="E51" s="268"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1">
       <c r="A52" s="10"/>
       <c r="B52" s="72" t="s">
         <v>155</v>
@@ -11877,7 +11866,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1">
       <c r="A53" s="10"/>
       <c r="B53" s="8" t="s">
         <v>88</v>
@@ -11904,7 +11893,7 @@
       <c r="P53" s="169"/>
       <c r="Q53" s="169"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1">
       <c r="A54" s="10"/>
       <c r="B54" s="8" t="s">
         <v>87</v>
@@ -11931,7 +11920,7 @@
       <c r="P54" s="169"/>
       <c r="Q54" s="169"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1">
       <c r="A55" s="10"/>
       <c r="B55" s="26" t="s">
         <v>90</v>
@@ -11986,11 +11975,11 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1">
       <c r="A56" s="10"/>
       <c r="E56" s="268"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1">
       <c r="A57" s="10"/>
       <c r="B57" s="64" t="s">
         <v>168</v>
@@ -12000,7 +11989,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1">
       <c r="A58" s="10"/>
       <c r="B58" s="40" t="s">
         <v>167</v>
@@ -12055,7 +12044,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1">
       <c r="A59" s="10"/>
       <c r="B59" s="40" t="s">
         <v>159</v>
@@ -12110,7 +12099,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1">
       <c r="A60" s="10"/>
       <c r="B60" s="40" t="s">
         <v>158</v>
@@ -12165,7 +12154,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1">
       <c r="A61" s="10"/>
       <c r="B61" s="31" t="s">
         <v>194</v>
@@ -12220,7 +12209,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1">
       <c r="A62" s="10"/>
       <c r="B62" s="40" t="s">
         <v>160</v>
@@ -12276,7 +12265,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1">
       <c r="A63" s="10"/>
       <c r="B63" s="31" t="s">
         <v>195</v>
@@ -12331,11 +12320,11 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1">
       <c r="A64" s="10"/>
       <c r="E64" s="268"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1">
       <c r="A65" s="10"/>
       <c r="B65" s="96" t="s">
         <v>169</v>
@@ -12345,7 +12334,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1">
       <c r="A66" s="10"/>
       <c r="B66" s="40" t="s">
         <v>167</v>
@@ -12370,7 +12359,7 @@
       <c r="P66" s="175"/>
       <c r="Q66" s="175"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1">
       <c r="A67" s="10"/>
       <c r="B67" s="105" t="s">
         <v>157</v>
@@ -12395,7 +12384,7 @@
       <c r="P67" s="175"/>
       <c r="Q67" s="175"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1">
       <c r="A68" s="10"/>
       <c r="B68" s="105" t="s">
         <v>158</v>
@@ -12420,7 +12409,7 @@
       <c r="P68" s="175"/>
       <c r="Q68" s="175"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1">
       <c r="A69" s="10"/>
       <c r="B69" s="31" t="s">
         <v>194</v>
@@ -12447,10 +12436,10 @@
       <c r="P69" s="175"/>
       <c r="Q69" s="175"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1">
       <c r="A70" s="10"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1">
       <c r="A71" s="10"/>
       <c r="B71" s="54" t="s">
         <v>212</v>
@@ -12473,7 +12462,7 @@
       <c r="P71" s="37"/>
       <c r="Q71" s="37"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1">
       <c r="A72" s="10"/>
       <c r="B72" s="72" t="s">
         <v>216</v>
@@ -12494,7 +12483,7 @@
       <c r="P72" s="12"/>
       <c r="Q72" s="12"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1">
       <c r="A73" s="10"/>
       <c r="B73" s="2" t="s">
         <v>46</v>
@@ -12551,7 +12540,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1">
       <c r="A74" s="10"/>
       <c r="B74" s="31" t="s">
         <v>48</v>
@@ -12608,7 +12597,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1">
       <c r="A75" s="10"/>
       <c r="B75" s="8" t="s">
         <v>45</v>
@@ -12665,7 +12654,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1">
       <c r="A76" s="10"/>
       <c r="B76" s="29" t="s">
         <v>152</v>
@@ -12722,7 +12711,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1">
       <c r="A77" s="10"/>
       <c r="B77" s="2" t="s">
         <v>65</v>
@@ -12779,7 +12768,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1">
       <c r="A78" s="10"/>
       <c r="B78" s="2" t="s">
         <v>80</v>
@@ -12838,7 +12827,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1">
       <c r="A79" s="10"/>
       <c r="B79" s="31" t="s">
         <v>153</v>
@@ -12895,7 +12884,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1">
       <c r="A80" s="10"/>
       <c r="B80" s="2" t="s">
         <v>68</v>
@@ -12952,7 +12941,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1">
       <c r="A81" s="10"/>
       <c r="B81" s="70" t="s">
         <v>164</v>
@@ -13009,7 +12998,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1">
       <c r="A82" s="10"/>
       <c r="B82" s="2" t="s">
         <v>63</v>
@@ -13066,7 +13055,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1">
       <c r="A83" s="10"/>
       <c r="B83" s="40" t="str">
         <f>B15</f>
@@ -13124,7 +13113,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1">
       <c r="A84" s="10"/>
       <c r="B84" s="41" t="s">
         <v>154</v>
@@ -13181,7 +13170,7 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1">
       <c r="A85" s="10"/>
       <c r="B85" s="27" t="s">
         <v>52</v>
@@ -13207,7 +13196,7 @@
       <c r="P85" s="226"/>
       <c r="Q85" s="226"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1">
       <c r="A86" s="10"/>
       <c r="B86" s="8" t="s">
         <v>98</v>
@@ -13231,7 +13220,7 @@
       <c r="P86" s="169"/>
       <c r="Q86" s="169"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1">
       <c r="A87" s="10"/>
       <c r="B87" s="31" t="s">
         <v>140</v>
@@ -13288,18 +13277,18 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1">
       <c r="A88" s="10"/>
       <c r="E88" s="268"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1">
       <c r="A89" s="10"/>
       <c r="B89" s="64" t="s">
         <v>214</v>
       </c>
       <c r="E89" s="268"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1">
       <c r="A90" s="10"/>
       <c r="B90" s="2" t="str">
         <f>"Dividend per share ("&amp;Market_currency&amp;")"</f>
@@ -13355,7 +13344,7 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1">
       <c r="A91" s="10"/>
       <c r="B91" s="2" t="str">
         <f>"Dividend ("&amp;Market_currency&amp;")"</f>
@@ -13411,7 +13400,7 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1">
       <c r="A92" s="10"/>
       <c r="B92" s="2" t="s">
         <v>213</v>
@@ -13466,19 +13455,19 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1">
       <c r="A93" s="10"/>
       <c r="B93" s="2" t="s">
         <v>309</v>
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.1594454072790291E-2</v>
+        <v>4.084411164057182E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.1594454072790291E-2</v>
+        <v>4.084411164057182E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -13521,11 +13510,11 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1">
       <c r="A94" s="10"/>
       <c r="E94" s="268"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1">
       <c r="A95" s="10"/>
       <c r="B95" s="157" t="s">
         <v>84</v>
@@ -13546,7 +13535,7 @@
       <c r="P95" s="12"/>
       <c r="Q95" s="12"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1">
       <c r="A96" s="10"/>
       <c r="B96" s="27" t="s">
         <v>144</v>
@@ -13603,7 +13592,7 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1">
       <c r="A97" s="10"/>
       <c r="B97" s="70" t="s">
         <v>164</v>
@@ -13660,10 +13649,10 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1">
       <c r="A98" s="10"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="54" t="s">
         <v>215</v>
@@ -13686,7 +13675,7 @@
       <c r="P99" s="37"/>
       <c r="Q99" s="37"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1">
       <c r="A100" s="10"/>
       <c r="B100" s="64" t="s">
         <v>28</v>
@@ -13696,7 +13685,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1">
       <c r="A101" s="10"/>
       <c r="B101" s="26" t="s">
         <v>3</v>
@@ -13753,7 +13742,7 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1">
       <c r="A102" s="10"/>
       <c r="B102" s="93" t="s">
         <v>210</v>
@@ -13810,7 +13799,7 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1">
       <c r="A103" s="10"/>
       <c r="B103" s="93" t="s">
         <v>211</v>
@@ -13867,7 +13856,7 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1">
       <c r="A104" s="10"/>
       <c r="B104" s="26" t="s">
         <v>40</v>
@@ -13924,7 +13913,7 @@
         <v/>
       </c>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1">
       <c r="A105" s="10"/>
       <c r="B105" s="26" t="s">
         <v>30</v>
@@ -13981,11 +13970,11 @@
         <v/>
       </c>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1">
       <c r="A106" s="10"/>
       <c r="E106" s="268"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1">
       <c r="A107" s="10"/>
       <c r="B107" s="91" t="s">
         <v>220</v>
@@ -14008,7 +13997,7 @@
       <c r="P107" s="12"/>
       <c r="Q107" s="12"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1">
       <c r="A108" s="10"/>
       <c r="B108" s="26" t="s">
         <v>217</v>
@@ -14065,7 +14054,7 @@
         <v/>
       </c>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1">
       <c r="A109" s="10"/>
       <c r="B109" s="26" t="s">
         <v>218</v>
@@ -14122,7 +14111,7 @@
         <v/>
       </c>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1">
       <c r="A110" s="10"/>
       <c r="B110" s="26" t="s">
         <v>69</v>
@@ -14149,18 +14138,18 @@
       <c r="P110" s="204"/>
       <c r="Q110" s="204"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1">
       <c r="A111" s="10"/>
       <c r="E111" s="268"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1">
       <c r="A112" s="10"/>
       <c r="B112" s="64" t="s">
         <v>51</v>
       </c>
       <c r="E112" s="268"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1">
       <c r="A113" s="10"/>
       <c r="B113" s="2" t="s">
         <v>391</v>
@@ -14212,7 +14201,7 @@
         <v/>
       </c>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1">
       <c r="A114" s="10"/>
       <c r="B114" s="2" t="s">
         <v>392</v>
@@ -14264,11 +14253,11 @@
         <v/>
       </c>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1">
       <c r="A115" s="10"/>
       <c r="E115" s="268"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1">
       <c r="A116" s="10"/>
       <c r="B116" s="91" t="s">
         <v>38</v>
@@ -14322,7 +14311,7 @@
         <v/>
       </c>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1">
       <c r="A117" s="10"/>
       <c r="B117" s="7" t="s">
         <v>221</v>
@@ -14377,7 +14366,7 @@
         <v/>
       </c>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1">
       <c r="B118" s="7" t="s">
         <v>83</v>
       </c>
@@ -14431,7 +14420,7 @@
         <v/>
       </c>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1">
       <c r="B119" s="7" t="s">
         <v>91</v>
       </c>
@@ -14487,7 +14476,7 @@
         <v/>
       </c>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1">
       <c r="A120" s="10"/>
       <c r="B120" s="70" t="s">
         <v>222</v>
@@ -14544,7 +14533,7 @@
         <v/>
       </c>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1">
       <c r="A121" s="10"/>
       <c r="B121" s="27"/>
       <c r="C121" s="62"/>
@@ -14563,7 +14552,7 @@
       <c r="P121" s="12"/>
       <c r="Q121" s="12"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1">
       <c r="A122" s="10"/>
       <c r="B122" s="54" t="s">
         <v>223</v>
@@ -14586,7 +14575,7 @@
       <c r="P122" s="37"/>
       <c r="Q122" s="37"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1">
       <c r="A123" s="10"/>
       <c r="B123" s="178" t="s">
         <v>170</v>
@@ -14607,7 +14596,7 @@
       <c r="P123" s="12"/>
       <c r="Q123" s="12"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1">
       <c r="A124" s="10"/>
       <c r="B124" s="27" t="str">
         <f>"FCFE per share ("&amp;Market_currency&amp;")"</f>
@@ -14665,795 +14654,795 @@
         <v/>
       </c>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1">
       <c r="A125" s="10"/>
       <c r="B125" s="27" t="s">
         <v>269</v>
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.5199672485701377E-2</v>
+        <v>7.3843109299267698E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>8.3196680154273894E-2</v>
+        <v>8.1695855086821034E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>9.5528120592592275E-2</v>
+        <v>9.3804842719410739E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>9.1000905256370182E-2</v>
+        <v>8.935929600565963E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>8.5091187451802969E-2</v>
+        <v>8.3556186452842615E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.7661164812278313E-2</v>
+        <v>4.6801382056985343E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6730907662356489E-2</v>
+        <v>1.6429090744009011E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.5338280582623095E-2</v>
+        <v>1.5061585936306205E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2346873754449468E-2</v>
+        <v>1.2124142539682341E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.2192328019322086E-2</v>
+        <v>1.1972384729661069E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>6.7501675429116632E-3</v>
+        <v>6.6283980126957626E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
         <v/>
       </c>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1">
       <c r="B126" s="2" t="s">
         <v>394</v>
       </c>
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.0550380161538412E-2</v>
+        <v>7.9097292976868058E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.7101348000542445E-2</v>
+        <v>9.5349689918844446E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.2636950601906992E-2</v>
+        <v>9.0965827939585325E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.5913852432712559E-2</v>
+        <v>8.4364010983109514E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2750525644001631E-2</v>
+        <v>6.1618538625917194E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.6088928432486867E-2</v>
+        <v>2.5618297660900142E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.5085313781452749E-2</v>
+        <v>1.4813182525354386E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1678450202998642E-2</v>
+        <v>1.1467777003284916E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>5.0112972897606578E-3</v>
+        <v>4.9208960792918649E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.4987022916363629E-3</v>
+        <v>-5.3995085470969735E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
         <v/>
       </c>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="128" spans="1:17" ht="15.75" customHeight="1"/>
+    <row r="129" ht="15.75" customHeight="1"/>
+    <row r="130" ht="15.75" customHeight="1"/>
+    <row r="131" ht="15.75" customHeight="1"/>
+    <row r="132" ht="15.75" customHeight="1"/>
+    <row r="133" ht="15.75" customHeight="1"/>
+    <row r="134" ht="15.75" customHeight="1"/>
+    <row r="135" ht="15.75" customHeight="1"/>
+    <row r="136" ht="15.75" customHeight="1"/>
+    <row r="137" ht="15.75" customHeight="1"/>
+    <row r="138" ht="15.75" customHeight="1"/>
+    <row r="139" ht="15.75" customHeight="1"/>
+    <row r="140" ht="15.75" customHeight="1"/>
+    <row r="141" ht="15.75" customHeight="1"/>
+    <row r="142" ht="15.75" customHeight="1"/>
+    <row r="143" ht="15.75" customHeight="1"/>
+    <row r="144" ht="15.75" customHeight="1"/>
+    <row r="145" ht="15.75" customHeight="1"/>
+    <row r="146" ht="15.75" customHeight="1"/>
+    <row r="147" ht="15.75" customHeight="1"/>
+    <row r="148" ht="15.75" customHeight="1"/>
+    <row r="149" ht="15.75" customHeight="1"/>
+    <row r="150" ht="15.75" customHeight="1"/>
+    <row r="151" ht="15.75" customHeight="1"/>
+    <row r="152" ht="15.75" customHeight="1"/>
+    <row r="153" ht="15.75" customHeight="1"/>
+    <row r="154" ht="15.75" customHeight="1"/>
+    <row r="155" ht="15.75" customHeight="1"/>
+    <row r="156" ht="15.75" customHeight="1"/>
+    <row r="157" ht="15.75" customHeight="1"/>
+    <row r="158" ht="15.75" customHeight="1"/>
+    <row r="159" ht="15.75" customHeight="1"/>
+    <row r="160" ht="15.75" customHeight="1"/>
+    <row r="161" ht="15.75" customHeight="1"/>
+    <row r="162" ht="15.75" customHeight="1"/>
+    <row r="163" ht="15.75" customHeight="1"/>
+    <row r="164" ht="15.75" customHeight="1"/>
+    <row r="165" ht="15.75" customHeight="1"/>
+    <row r="166" ht="15.75" customHeight="1"/>
+    <row r="167" ht="15.75" customHeight="1"/>
+    <row r="168" ht="15.75" customHeight="1"/>
+    <row r="169" ht="15.75" customHeight="1"/>
+    <row r="170" ht="15.75" customHeight="1"/>
+    <row r="171" ht="15.75" customHeight="1"/>
+    <row r="172" ht="15.75" customHeight="1"/>
+    <row r="173" ht="15.75" customHeight="1"/>
+    <row r="174" ht="15.75" customHeight="1"/>
+    <row r="175" ht="15.75" customHeight="1"/>
+    <row r="176" ht="15.75" customHeight="1"/>
+    <row r="177" ht="15.75" customHeight="1"/>
+    <row r="178" ht="15.75" customHeight="1"/>
+    <row r="179" ht="15.75" customHeight="1"/>
+    <row r="180" ht="15.75" customHeight="1"/>
+    <row r="181" ht="15.75" customHeight="1"/>
+    <row r="182" ht="15.75" customHeight="1"/>
+    <row r="183" ht="15.75" customHeight="1"/>
+    <row r="184" ht="15.75" customHeight="1"/>
+    <row r="185" ht="15.75" customHeight="1"/>
+    <row r="186" ht="15.75" customHeight="1"/>
+    <row r="187" ht="15.75" customHeight="1"/>
+    <row r="188" ht="15.75" customHeight="1"/>
+    <row r="189" ht="15.75" customHeight="1"/>
+    <row r="190" ht="15.75" customHeight="1"/>
+    <row r="191" ht="15.75" customHeight="1"/>
+    <row r="192" ht="15.75" customHeight="1"/>
+    <row r="193" ht="15.75" customHeight="1"/>
+    <row r="194" ht="15.75" customHeight="1"/>
+    <row r="195" ht="15.75" customHeight="1"/>
+    <row r="196" ht="15.75" customHeight="1"/>
+    <row r="197" ht="15.75" customHeight="1"/>
+    <row r="198" ht="15.75" customHeight="1"/>
+    <row r="199" ht="15.75" customHeight="1"/>
+    <row r="200" ht="15.75" customHeight="1"/>
+    <row r="201" ht="15.75" customHeight="1"/>
+    <row r="202" ht="15.75" customHeight="1"/>
+    <row r="203" ht="15.75" customHeight="1"/>
+    <row r="204" ht="15.75" customHeight="1"/>
+    <row r="205" ht="15.75" customHeight="1"/>
+    <row r="206" ht="15.75" customHeight="1"/>
+    <row r="207" ht="15.75" customHeight="1"/>
+    <row r="208" ht="15.75" customHeight="1"/>
+    <row r="209" ht="15.75" customHeight="1"/>
+    <row r="210" ht="15.75" customHeight="1"/>
+    <row r="211" ht="15.75" customHeight="1"/>
+    <row r="212" ht="15.75" customHeight="1"/>
+    <row r="213" ht="15.75" customHeight="1"/>
+    <row r="214" ht="15.75" customHeight="1"/>
+    <row r="215" ht="15.75" customHeight="1"/>
+    <row r="216" ht="15.75" customHeight="1"/>
+    <row r="217" ht="15.75" customHeight="1"/>
+    <row r="218" ht="15.75" customHeight="1"/>
+    <row r="219" ht="15.75" customHeight="1"/>
+    <row r="220" ht="15.75" customHeight="1"/>
+    <row r="221" ht="15.75" customHeight="1"/>
+    <row r="222" ht="15.75" customHeight="1"/>
+    <row r="223" ht="15.75" customHeight="1"/>
+    <row r="224" ht="15.75" customHeight="1"/>
+    <row r="225" ht="15.75" customHeight="1"/>
+    <row r="226" ht="15.75" customHeight="1"/>
+    <row r="227" ht="15.75" customHeight="1"/>
+    <row r="228" ht="15.75" customHeight="1"/>
+    <row r="229" ht="15.75" customHeight="1"/>
+    <row r="230" ht="15.75" customHeight="1"/>
+    <row r="231" ht="15.75" customHeight="1"/>
+    <row r="232" ht="15.75" customHeight="1"/>
+    <row r="233" ht="15.75" customHeight="1"/>
+    <row r="234" ht="15.75" customHeight="1"/>
+    <row r="235" ht="15.75" customHeight="1"/>
+    <row r="236" ht="15.75" customHeight="1"/>
+    <row r="237" ht="15.75" customHeight="1"/>
+    <row r="238" ht="15.75" customHeight="1"/>
+    <row r="239" ht="15.75" customHeight="1"/>
+    <row r="240" ht="15.75" customHeight="1"/>
+    <row r="241" ht="15.75" customHeight="1"/>
+    <row r="242" ht="15.75" customHeight="1"/>
+    <row r="243" ht="15.75" customHeight="1"/>
+    <row r="244" ht="15.75" customHeight="1"/>
+    <row r="245" ht="15.75" customHeight="1"/>
+    <row r="246" ht="15.75" customHeight="1"/>
+    <row r="247" ht="15.75" customHeight="1"/>
+    <row r="248" ht="15.75" customHeight="1"/>
+    <row r="249" ht="15.75" customHeight="1"/>
+    <row r="250" ht="15.75" customHeight="1"/>
+    <row r="251" ht="15.75" customHeight="1"/>
+    <row r="252" ht="15.75" customHeight="1"/>
+    <row r="253" ht="15.75" customHeight="1"/>
+    <row r="254" ht="15.75" customHeight="1"/>
+    <row r="255" ht="15.75" customHeight="1"/>
+    <row r="256" ht="15.75" customHeight="1"/>
+    <row r="257" ht="15.75" customHeight="1"/>
+    <row r="258" ht="15.75" customHeight="1"/>
+    <row r="259" ht="15.75" customHeight="1"/>
+    <row r="260" ht="15.75" customHeight="1"/>
+    <row r="261" ht="15.75" customHeight="1"/>
+    <row r="262" ht="15.75" customHeight="1"/>
+    <row r="263" ht="15.75" customHeight="1"/>
+    <row r="264" ht="15.75" customHeight="1"/>
+    <row r="265" ht="15.75" customHeight="1"/>
+    <row r="266" ht="15.75" customHeight="1"/>
+    <row r="267" ht="15.75" customHeight="1"/>
+    <row r="268" ht="15.75" customHeight="1"/>
+    <row r="269" ht="15.75" customHeight="1"/>
+    <row r="270" ht="15.75" customHeight="1"/>
+    <row r="271" ht="15.75" customHeight="1"/>
+    <row r="272" ht="15.75" customHeight="1"/>
+    <row r="273" ht="15.75" customHeight="1"/>
+    <row r="274" ht="15.75" customHeight="1"/>
+    <row r="275" ht="15.75" customHeight="1"/>
+    <row r="276" ht="15.75" customHeight="1"/>
+    <row r="277" ht="15.75" customHeight="1"/>
+    <row r="278" ht="15.75" customHeight="1"/>
+    <row r="279" ht="15.75" customHeight="1"/>
+    <row r="280" ht="15.75" customHeight="1"/>
+    <row r="281" ht="15.75" customHeight="1"/>
+    <row r="282" ht="15.75" customHeight="1"/>
+    <row r="283" ht="15.75" customHeight="1"/>
+    <row r="284" ht="15.75" customHeight="1"/>
+    <row r="285" ht="15.75" customHeight="1"/>
+    <row r="286" ht="15.75" customHeight="1"/>
+    <row r="287" ht="15.75" customHeight="1"/>
+    <row r="288" ht="15.75" customHeight="1"/>
+    <row r="289" ht="15.75" customHeight="1"/>
+    <row r="290" ht="15.75" customHeight="1"/>
+    <row r="291" ht="15.75" customHeight="1"/>
+    <row r="292" ht="15.75" customHeight="1"/>
+    <row r="293" ht="15.75" customHeight="1"/>
+    <row r="294" ht="15.75" customHeight="1"/>
+    <row r="295" ht="15.75" customHeight="1"/>
+    <row r="296" ht="15.75" customHeight="1"/>
+    <row r="297" ht="15.75" customHeight="1"/>
+    <row r="298" ht="15.75" customHeight="1"/>
+    <row r="299" ht="15.75" customHeight="1"/>
+    <row r="300" ht="15.75" customHeight="1"/>
+    <row r="301" ht="15.75" customHeight="1"/>
+    <row r="302" ht="15.75" customHeight="1"/>
+    <row r="303" ht="15.75" customHeight="1"/>
+    <row r="304" ht="15.75" customHeight="1"/>
+    <row r="305" ht="15.75" customHeight="1"/>
+    <row r="306" ht="15.75" customHeight="1"/>
+    <row r="307" ht="15.75" customHeight="1"/>
+    <row r="308" ht="15.75" customHeight="1"/>
+    <row r="309" ht="15.75" customHeight="1"/>
+    <row r="310" ht="15.75" customHeight="1"/>
+    <row r="311" ht="15.75" customHeight="1"/>
+    <row r="312" ht="15.75" customHeight="1"/>
+    <row r="313" ht="15.75" customHeight="1"/>
+    <row r="314" ht="15.75" customHeight="1"/>
+    <row r="315" ht="15.75" customHeight="1"/>
+    <row r="316" ht="15.75" customHeight="1"/>
+    <row r="317" ht="15.75" customHeight="1"/>
+    <row r="318" ht="15.75" customHeight="1"/>
+    <row r="319" ht="15.75" customHeight="1"/>
+    <row r="320" ht="15.75" customHeight="1"/>
+    <row r="321" ht="15.75" customHeight="1"/>
+    <row r="322" ht="15.75" customHeight="1"/>
+    <row r="323" ht="15.75" customHeight="1"/>
+    <row r="324" ht="15.75" customHeight="1"/>
+    <row r="325" ht="15.75" customHeight="1"/>
+    <row r="326" ht="15.75" customHeight="1"/>
+    <row r="327" ht="15.75" customHeight="1"/>
+    <row r="328" ht="15.75" customHeight="1"/>
+    <row r="329" ht="15.75" customHeight="1"/>
+    <row r="330" ht="15.75" customHeight="1"/>
+    <row r="331" ht="15.75" customHeight="1"/>
+    <row r="332" ht="15.75" customHeight="1"/>
+    <row r="333" ht="15.75" customHeight="1"/>
+    <row r="334" ht="15.75" customHeight="1"/>
+    <row r="335" ht="15.75" customHeight="1"/>
+    <row r="336" ht="15.75" customHeight="1"/>
+    <row r="337" ht="15.75" customHeight="1"/>
+    <row r="338" ht="15.75" customHeight="1"/>
+    <row r="339" ht="15.75" customHeight="1"/>
+    <row r="340" ht="15.75" customHeight="1"/>
+    <row r="341" ht="15.75" customHeight="1"/>
+    <row r="342" ht="15.75" customHeight="1"/>
+    <row r="343" ht="15.75" customHeight="1"/>
+    <row r="344" ht="15.75" customHeight="1"/>
+    <row r="345" ht="15.75" customHeight="1"/>
+    <row r="346" ht="15.75" customHeight="1"/>
+    <row r="347" ht="15.75" customHeight="1"/>
+    <row r="348" ht="15.75" customHeight="1"/>
+    <row r="349" ht="15.75" customHeight="1"/>
+    <row r="350" ht="15.75" customHeight="1"/>
+    <row r="351" ht="15.75" customHeight="1"/>
+    <row r="352" ht="15.75" customHeight="1"/>
+    <row r="353" ht="15.75" customHeight="1"/>
+    <row r="354" ht="15.75" customHeight="1"/>
+    <row r="355" ht="15.75" customHeight="1"/>
+    <row r="356" ht="15.75" customHeight="1"/>
+    <row r="357" ht="15.75" customHeight="1"/>
+    <row r="358" ht="15.75" customHeight="1"/>
+    <row r="359" ht="15.75" customHeight="1"/>
+    <row r="360" ht="15.75" customHeight="1"/>
+    <row r="361" ht="15.75" customHeight="1"/>
+    <row r="362" ht="15.75" customHeight="1"/>
+    <row r="363" ht="15.75" customHeight="1"/>
+    <row r="364" ht="15.75" customHeight="1"/>
+    <row r="365" ht="15.75" customHeight="1"/>
+    <row r="366" ht="15.75" customHeight="1"/>
+    <row r="367" ht="15.75" customHeight="1"/>
+    <row r="368" ht="15.75" customHeight="1"/>
+    <row r="369" ht="15.75" customHeight="1"/>
+    <row r="370" ht="15.75" customHeight="1"/>
+    <row r="371" ht="15.75" customHeight="1"/>
+    <row r="372" ht="15.75" customHeight="1"/>
+    <row r="373" ht="15.75" customHeight="1"/>
+    <row r="374" ht="15.75" customHeight="1"/>
+    <row r="375" ht="15.75" customHeight="1"/>
+    <row r="376" ht="15.75" customHeight="1"/>
+    <row r="377" ht="15.75" customHeight="1"/>
+    <row r="378" ht="15.75" customHeight="1"/>
+    <row r="379" ht="15.75" customHeight="1"/>
+    <row r="380" ht="15.75" customHeight="1"/>
+    <row r="381" ht="15.75" customHeight="1"/>
+    <row r="382" ht="15.75" customHeight="1"/>
+    <row r="383" ht="15.75" customHeight="1"/>
+    <row r="384" ht="15.75" customHeight="1"/>
+    <row r="385" ht="15.75" customHeight="1"/>
+    <row r="386" ht="15.75" customHeight="1"/>
+    <row r="387" ht="15.75" customHeight="1"/>
+    <row r="388" ht="15.75" customHeight="1"/>
+    <row r="389" ht="15.75" customHeight="1"/>
+    <row r="390" ht="15.75" customHeight="1"/>
+    <row r="391" ht="15.75" customHeight="1"/>
+    <row r="392" ht="15.75" customHeight="1"/>
+    <row r="393" ht="15.75" customHeight="1"/>
+    <row r="394" ht="15.75" customHeight="1"/>
+    <row r="395" ht="15.75" customHeight="1"/>
+    <row r="396" ht="15.75" customHeight="1"/>
+    <row r="397" ht="15.75" customHeight="1"/>
+    <row r="398" ht="15.75" customHeight="1"/>
+    <row r="399" ht="15.75" customHeight="1"/>
+    <row r="400" ht="15.75" customHeight="1"/>
+    <row r="401" ht="15.75" customHeight="1"/>
+    <row r="402" ht="15.75" customHeight="1"/>
+    <row r="403" ht="15.75" customHeight="1"/>
+    <row r="404" ht="15.75" customHeight="1"/>
+    <row r="405" ht="15.75" customHeight="1"/>
+    <row r="406" ht="15.75" customHeight="1"/>
+    <row r="407" ht="15.75" customHeight="1"/>
+    <row r="408" ht="15.75" customHeight="1"/>
+    <row r="409" ht="15.75" customHeight="1"/>
+    <row r="410" ht="15.75" customHeight="1"/>
+    <row r="411" ht="15.75" customHeight="1"/>
+    <row r="412" ht="15.75" customHeight="1"/>
+    <row r="413" ht="15.75" customHeight="1"/>
+    <row r="414" ht="15.75" customHeight="1"/>
+    <row r="415" ht="15.75" customHeight="1"/>
+    <row r="416" ht="15.75" customHeight="1"/>
+    <row r="417" ht="15.75" customHeight="1"/>
+    <row r="418" ht="15.75" customHeight="1"/>
+    <row r="419" ht="15.75" customHeight="1"/>
+    <row r="420" ht="15.75" customHeight="1"/>
+    <row r="421" ht="15.75" customHeight="1"/>
+    <row r="422" ht="15.75" customHeight="1"/>
+    <row r="423" ht="15.75" customHeight="1"/>
+    <row r="424" ht="15.75" customHeight="1"/>
+    <row r="425" ht="15.75" customHeight="1"/>
+    <row r="426" ht="15.75" customHeight="1"/>
+    <row r="427" ht="15.75" customHeight="1"/>
+    <row r="428" ht="15.75" customHeight="1"/>
+    <row r="429" ht="15.75" customHeight="1"/>
+    <row r="430" ht="15.75" customHeight="1"/>
+    <row r="431" ht="15.75" customHeight="1"/>
+    <row r="432" ht="15.75" customHeight="1"/>
+    <row r="433" ht="15.75" customHeight="1"/>
+    <row r="434" ht="15.75" customHeight="1"/>
+    <row r="435" ht="15.75" customHeight="1"/>
+    <row r="436" ht="15.75" customHeight="1"/>
+    <row r="437" ht="15.75" customHeight="1"/>
+    <row r="438" ht="15.75" customHeight="1"/>
+    <row r="439" ht="15.75" customHeight="1"/>
+    <row r="440" ht="15.75" customHeight="1"/>
+    <row r="441" ht="15.75" customHeight="1"/>
+    <row r="442" ht="15.75" customHeight="1"/>
+    <row r="443" ht="15.75" customHeight="1"/>
+    <row r="444" ht="15.75" customHeight="1"/>
+    <row r="445" ht="15.75" customHeight="1"/>
+    <row r="446" ht="15.75" customHeight="1"/>
+    <row r="447" ht="15.75" customHeight="1"/>
+    <row r="448" ht="15.75" customHeight="1"/>
+    <row r="449" ht="15.75" customHeight="1"/>
+    <row r="450" ht="15.75" customHeight="1"/>
+    <row r="451" ht="15.75" customHeight="1"/>
+    <row r="452" ht="15.75" customHeight="1"/>
+    <row r="453" ht="15.75" customHeight="1"/>
+    <row r="454" ht="15.75" customHeight="1"/>
+    <row r="455" ht="15.75" customHeight="1"/>
+    <row r="456" ht="15.75" customHeight="1"/>
+    <row r="457" ht="15.75" customHeight="1"/>
+    <row r="458" ht="15.75" customHeight="1"/>
+    <row r="459" ht="15.75" customHeight="1"/>
+    <row r="460" ht="15.75" customHeight="1"/>
+    <row r="461" ht="15.75" customHeight="1"/>
+    <row r="462" ht="15.75" customHeight="1"/>
+    <row r="463" ht="15.75" customHeight="1"/>
+    <row r="464" ht="15.75" customHeight="1"/>
+    <row r="465" ht="15.75" customHeight="1"/>
+    <row r="466" ht="15.75" customHeight="1"/>
+    <row r="467" ht="15.75" customHeight="1"/>
+    <row r="468" ht="15.75" customHeight="1"/>
+    <row r="469" ht="15.75" customHeight="1"/>
+    <row r="470" ht="15.75" customHeight="1"/>
+    <row r="471" ht="15.75" customHeight="1"/>
+    <row r="472" ht="15.75" customHeight="1"/>
+    <row r="473" ht="15.75" customHeight="1"/>
+    <row r="474" ht="15.75" customHeight="1"/>
+    <row r="475" ht="15.75" customHeight="1"/>
+    <row r="476" ht="15.75" customHeight="1"/>
+    <row r="477" ht="15.75" customHeight="1"/>
+    <row r="478" ht="15.75" customHeight="1"/>
+    <row r="479" ht="15.75" customHeight="1"/>
+    <row r="480" ht="15.75" customHeight="1"/>
+    <row r="481" ht="15.75" customHeight="1"/>
+    <row r="482" ht="15.75" customHeight="1"/>
+    <row r="483" ht="15.75" customHeight="1"/>
+    <row r="484" ht="15.75" customHeight="1"/>
+    <row r="485" ht="15.75" customHeight="1"/>
+    <row r="486" ht="15.75" customHeight="1"/>
+    <row r="487" ht="15.75" customHeight="1"/>
+    <row r="488" ht="15.75" customHeight="1"/>
+    <row r="489" ht="15.75" customHeight="1"/>
+    <row r="490" ht="15.75" customHeight="1"/>
+    <row r="491" ht="15.75" customHeight="1"/>
+    <row r="492" ht="15.75" customHeight="1"/>
+    <row r="493" ht="15.75" customHeight="1"/>
+    <row r="494" ht="15.75" customHeight="1"/>
+    <row r="495" ht="15.75" customHeight="1"/>
+    <row r="496" ht="15.75" customHeight="1"/>
+    <row r="497" ht="15.75" customHeight="1"/>
+    <row r="498" ht="15.75" customHeight="1"/>
+    <row r="499" ht="15.75" customHeight="1"/>
+    <row r="500" ht="15.75" customHeight="1"/>
+    <row r="501" ht="15.75" customHeight="1"/>
+    <row r="502" ht="15.75" customHeight="1"/>
+    <row r="503" ht="15.75" customHeight="1"/>
+    <row r="504" ht="15.75" customHeight="1"/>
+    <row r="505" ht="15.75" customHeight="1"/>
+    <row r="506" ht="15.75" customHeight="1"/>
+    <row r="507" ht="15.75" customHeight="1"/>
+    <row r="508" ht="15.75" customHeight="1"/>
+    <row r="509" ht="15.75" customHeight="1"/>
+    <row r="510" ht="15.75" customHeight="1"/>
+    <row r="511" ht="15.75" customHeight="1"/>
+    <row r="512" ht="15.75" customHeight="1"/>
+    <row r="513" ht="15.75" customHeight="1"/>
+    <row r="514" ht="15.75" customHeight="1"/>
+    <row r="515" ht="15.75" customHeight="1"/>
+    <row r="516" ht="15.75" customHeight="1"/>
+    <row r="517" ht="15.75" customHeight="1"/>
+    <row r="518" ht="15.75" customHeight="1"/>
+    <row r="519" ht="15.75" customHeight="1"/>
+    <row r="520" ht="15.75" customHeight="1"/>
+    <row r="521" ht="15.75" customHeight="1"/>
+    <row r="522" ht="15.75" customHeight="1"/>
+    <row r="523" ht="15.75" customHeight="1"/>
+    <row r="524" ht="15.75" customHeight="1"/>
+    <row r="525" ht="15.75" customHeight="1"/>
+    <row r="526" ht="15.75" customHeight="1"/>
+    <row r="527" ht="15.75" customHeight="1"/>
+    <row r="528" ht="15.75" customHeight="1"/>
+    <row r="529" ht="15.75" customHeight="1"/>
+    <row r="530" ht="15.75" customHeight="1"/>
+    <row r="531" ht="15.75" customHeight="1"/>
+    <row r="532" ht="15.75" customHeight="1"/>
+    <row r="533" ht="15.75" customHeight="1"/>
+    <row r="534" ht="15.75" customHeight="1"/>
+    <row r="535" ht="15.75" customHeight="1"/>
+    <row r="536" ht="15.75" customHeight="1"/>
+    <row r="537" ht="15.75" customHeight="1"/>
+    <row r="538" ht="15.75" customHeight="1"/>
+    <row r="539" ht="15.75" customHeight="1"/>
+    <row r="540" ht="15.75" customHeight="1"/>
+    <row r="541" ht="15.75" customHeight="1"/>
+    <row r="542" ht="15.75" customHeight="1"/>
+    <row r="543" ht="15.75" customHeight="1"/>
+    <row r="544" ht="15.75" customHeight="1"/>
+    <row r="545" ht="15.75" customHeight="1"/>
+    <row r="546" ht="15.75" customHeight="1"/>
+    <row r="547" ht="15.75" customHeight="1"/>
+    <row r="548" ht="15.75" customHeight="1"/>
+    <row r="549" ht="15.75" customHeight="1"/>
+    <row r="550" ht="15.75" customHeight="1"/>
+    <row r="551" ht="15.75" customHeight="1"/>
+    <row r="552" ht="15.75" customHeight="1"/>
+    <row r="553" ht="15.75" customHeight="1"/>
+    <row r="554" ht="15.75" customHeight="1"/>
+    <row r="555" ht="15.75" customHeight="1"/>
+    <row r="556" ht="15.75" customHeight="1"/>
+    <row r="557" ht="15.75" customHeight="1"/>
+    <row r="558" ht="15.75" customHeight="1"/>
+    <row r="559" ht="15.75" customHeight="1"/>
+    <row r="560" ht="15.75" customHeight="1"/>
+    <row r="561" ht="15.75" customHeight="1"/>
+    <row r="562" ht="15.75" customHeight="1"/>
+    <row r="563" ht="15.75" customHeight="1"/>
+    <row r="564" ht="15.75" customHeight="1"/>
+    <row r="565" ht="15.75" customHeight="1"/>
+    <row r="566" ht="15.75" customHeight="1"/>
+    <row r="567" ht="15.75" customHeight="1"/>
+    <row r="568" ht="15.75" customHeight="1"/>
+    <row r="569" ht="15.75" customHeight="1"/>
+    <row r="570" ht="15.75" customHeight="1"/>
+    <row r="571" ht="15.75" customHeight="1"/>
+    <row r="572" ht="15.75" customHeight="1"/>
+    <row r="573" ht="15.75" customHeight="1"/>
+    <row r="574" ht="15.75" customHeight="1"/>
+    <row r="575" ht="15.75" customHeight="1"/>
+    <row r="576" ht="15.75" customHeight="1"/>
+    <row r="577" ht="15.75" customHeight="1"/>
+    <row r="578" ht="15.75" customHeight="1"/>
+    <row r="579" ht="15.75" customHeight="1"/>
+    <row r="580" ht="15.75" customHeight="1"/>
+    <row r="581" ht="15.75" customHeight="1"/>
+    <row r="582" ht="15.75" customHeight="1"/>
+    <row r="583" ht="15.75" customHeight="1"/>
+    <row r="584" ht="15.75" customHeight="1"/>
+    <row r="585" ht="15.75" customHeight="1"/>
+    <row r="586" ht="15.75" customHeight="1"/>
+    <row r="587" ht="15.75" customHeight="1"/>
+    <row r="588" ht="15.75" customHeight="1"/>
+    <row r="589" ht="15.75" customHeight="1"/>
+    <row r="590" ht="15.75" customHeight="1"/>
+    <row r="591" ht="15.75" customHeight="1"/>
+    <row r="592" ht="15.75" customHeight="1"/>
+    <row r="593" ht="15.75" customHeight="1"/>
+    <row r="594" ht="15.75" customHeight="1"/>
+    <row r="595" ht="15.75" customHeight="1"/>
+    <row r="596" ht="15.75" customHeight="1"/>
+    <row r="597" ht="15.75" customHeight="1"/>
+    <row r="598" ht="15.75" customHeight="1"/>
+    <row r="599" ht="15.75" customHeight="1"/>
+    <row r="600" ht="15.75" customHeight="1"/>
+    <row r="601" ht="15.75" customHeight="1"/>
+    <row r="602" ht="15.75" customHeight="1"/>
+    <row r="603" ht="15.75" customHeight="1"/>
+    <row r="604" ht="15.75" customHeight="1"/>
+    <row r="605" ht="15.75" customHeight="1"/>
+    <row r="606" ht="15.75" customHeight="1"/>
+    <row r="607" ht="15.75" customHeight="1"/>
+    <row r="608" ht="15.75" customHeight="1"/>
+    <row r="609" ht="15.75" customHeight="1"/>
+    <row r="610" ht="15.75" customHeight="1"/>
+    <row r="611" ht="15.75" customHeight="1"/>
+    <row r="612" ht="15.75" customHeight="1"/>
+    <row r="613" ht="15.75" customHeight="1"/>
+    <row r="614" ht="15.75" customHeight="1"/>
+    <row r="615" ht="15.75" customHeight="1"/>
+    <row r="616" ht="15.75" customHeight="1"/>
+    <row r="617" ht="15.75" customHeight="1"/>
+    <row r="618" ht="15.75" customHeight="1"/>
+    <row r="619" ht="15.75" customHeight="1"/>
+    <row r="620" ht="15.75" customHeight="1"/>
+    <row r="621" ht="15.75" customHeight="1"/>
+    <row r="622" ht="15.75" customHeight="1"/>
+    <row r="623" ht="15.75" customHeight="1"/>
+    <row r="624" ht="15.75" customHeight="1"/>
+    <row r="625" ht="15.75" customHeight="1"/>
+    <row r="626" ht="15.75" customHeight="1"/>
+    <row r="627" ht="15.75" customHeight="1"/>
+    <row r="628" ht="15.75" customHeight="1"/>
+    <row r="629" ht="15.75" customHeight="1"/>
+    <row r="630" ht="15.75" customHeight="1"/>
+    <row r="631" ht="15.75" customHeight="1"/>
+    <row r="632" ht="15.75" customHeight="1"/>
+    <row r="633" ht="15.75" customHeight="1"/>
+    <row r="634" ht="15.75" customHeight="1"/>
+    <row r="635" ht="15.75" customHeight="1"/>
+    <row r="636" ht="15.75" customHeight="1"/>
+    <row r="637" ht="15.75" customHeight="1"/>
+    <row r="638" ht="15.75" customHeight="1"/>
+    <row r="639" ht="15.75" customHeight="1"/>
+    <row r="640" ht="15.75" customHeight="1"/>
+    <row r="641" ht="15.75" customHeight="1"/>
+    <row r="642" ht="15.75" customHeight="1"/>
+    <row r="643" ht="15.75" customHeight="1"/>
+    <row r="644" ht="15.75" customHeight="1"/>
+    <row r="645" ht="15.75" customHeight="1"/>
+    <row r="646" ht="15.75" customHeight="1"/>
+    <row r="647" ht="15.75" customHeight="1"/>
+    <row r="648" ht="15.75" customHeight="1"/>
+    <row r="649" ht="15.75" customHeight="1"/>
+    <row r="650" ht="15.75" customHeight="1"/>
+    <row r="651" ht="15.75" customHeight="1"/>
+    <row r="652" ht="15.75" customHeight="1"/>
+    <row r="653" ht="15.75" customHeight="1"/>
+    <row r="654" ht="15.75" customHeight="1"/>
+    <row r="655" ht="15.75" customHeight="1"/>
+    <row r="656" ht="15.75" customHeight="1"/>
+    <row r="657" ht="15.75" customHeight="1"/>
+    <row r="658" ht="15.75" customHeight="1"/>
+    <row r="659" ht="15.75" customHeight="1"/>
+    <row r="660" ht="15.75" customHeight="1"/>
+    <row r="661" ht="15.75" customHeight="1"/>
+    <row r="662" ht="15.75" customHeight="1"/>
+    <row r="663" ht="15.75" customHeight="1"/>
+    <row r="664" ht="15.75" customHeight="1"/>
+    <row r="665" ht="15.75" customHeight="1"/>
+    <row r="666" ht="15.75" customHeight="1"/>
+    <row r="667" ht="15.75" customHeight="1"/>
+    <row r="668" ht="15.75" customHeight="1"/>
+    <row r="669" ht="15.75" customHeight="1"/>
+    <row r="670" ht="15.75" customHeight="1"/>
+    <row r="671" ht="15.75" customHeight="1"/>
+    <row r="672" ht="15.75" customHeight="1"/>
+    <row r="673" ht="15.75" customHeight="1"/>
+    <row r="674" ht="15.75" customHeight="1"/>
+    <row r="675" ht="15.75" customHeight="1"/>
+    <row r="676" ht="15.75" customHeight="1"/>
+    <row r="677" ht="15.75" customHeight="1"/>
+    <row r="678" ht="15.75" customHeight="1"/>
+    <row r="679" ht="15.75" customHeight="1"/>
+    <row r="680" ht="15.75" customHeight="1"/>
+    <row r="681" ht="15.75" customHeight="1"/>
+    <row r="682" ht="15.75" customHeight="1"/>
+    <row r="683" ht="15.75" customHeight="1"/>
+    <row r="684" ht="15.75" customHeight="1"/>
+    <row r="685" ht="15.75" customHeight="1"/>
+    <row r="686" ht="15.75" customHeight="1"/>
+    <row r="687" ht="15.75" customHeight="1"/>
+    <row r="688" ht="15.75" customHeight="1"/>
+    <row r="689" ht="15.75" customHeight="1"/>
+    <row r="690" ht="15.75" customHeight="1"/>
+    <row r="691" ht="15.75" customHeight="1"/>
+    <row r="692" ht="15.75" customHeight="1"/>
+    <row r="693" ht="15.75" customHeight="1"/>
+    <row r="694" ht="15.75" customHeight="1"/>
+    <row r="695" ht="15.75" customHeight="1"/>
+    <row r="696" ht="15.75" customHeight="1"/>
+    <row r="697" ht="15.75" customHeight="1"/>
+    <row r="698" ht="15.75" customHeight="1"/>
+    <row r="699" ht="15.75" customHeight="1"/>
+    <row r="700" ht="15.75" customHeight="1"/>
+    <row r="701" ht="15.75" customHeight="1"/>
+    <row r="702" ht="15.75" customHeight="1"/>
+    <row r="703" ht="15.75" customHeight="1"/>
+    <row r="704" ht="15.75" customHeight="1"/>
+    <row r="705" ht="15.75" customHeight="1"/>
+    <row r="706" ht="15.75" customHeight="1"/>
+    <row r="707" ht="15.75" customHeight="1"/>
+    <row r="708" ht="15.75" customHeight="1"/>
+    <row r="709" ht="15.75" customHeight="1"/>
+    <row r="710" ht="15.75" customHeight="1"/>
+    <row r="711" ht="15.75" customHeight="1"/>
+    <row r="712" ht="15.75" customHeight="1"/>
+    <row r="713" ht="15.75" customHeight="1"/>
+    <row r="714" ht="15.75" customHeight="1"/>
+    <row r="715" ht="15.75" customHeight="1"/>
+    <row r="716" ht="15.75" customHeight="1"/>
+    <row r="717" ht="15.75" customHeight="1"/>
+    <row r="718" ht="15.75" customHeight="1"/>
+    <row r="719" ht="15.75" customHeight="1"/>
+    <row r="720" ht="15.75" customHeight="1"/>
+    <row r="721" ht="15.75" customHeight="1"/>
+    <row r="722" ht="15.75" customHeight="1"/>
+    <row r="723" ht="15.75" customHeight="1"/>
+    <row r="724" ht="15.75" customHeight="1"/>
+    <row r="725" ht="15.75" customHeight="1"/>
+    <row r="726" ht="15.75" customHeight="1"/>
+    <row r="727" ht="15.75" customHeight="1"/>
+    <row r="728" ht="15.75" customHeight="1"/>
+    <row r="729" ht="15.75" customHeight="1"/>
+    <row r="730" ht="15.75" customHeight="1"/>
+    <row r="731" ht="15.75" customHeight="1"/>
+    <row r="732" ht="15.75" customHeight="1"/>
+    <row r="733" ht="15.75" customHeight="1"/>
+    <row r="734" ht="15.75" customHeight="1"/>
+    <row r="735" ht="15.75" customHeight="1"/>
+    <row r="736" ht="15.75" customHeight="1"/>
+    <row r="737" ht="15.75" customHeight="1"/>
+    <row r="738" ht="15.75" customHeight="1"/>
+    <row r="739" ht="15.75" customHeight="1"/>
+    <row r="740" ht="15.75" customHeight="1"/>
+    <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
+    <row r="757" ht="15.75" customHeight="1"/>
+    <row r="758" ht="15.75" customHeight="1"/>
+    <row r="759" ht="15.75" customHeight="1"/>
+    <row r="760" ht="15.75" customHeight="1"/>
+    <row r="761" ht="15.75" customHeight="1"/>
+    <row r="762" ht="15.75" customHeight="1"/>
+    <row r="763" ht="15.75" customHeight="1"/>
+    <row r="764" ht="15.75" customHeight="1"/>
+    <row r="765" ht="15.75" customHeight="1"/>
+    <row r="766" ht="15.75" customHeight="1"/>
+    <row r="767" ht="15.75" customHeight="1"/>
+    <row r="768" ht="15.75" customHeight="1"/>
+    <row r="769" ht="15.75" customHeight="1"/>
+    <row r="770" ht="15.75" customHeight="1"/>
+    <row r="771" ht="15.75" customHeight="1"/>
+    <row r="772" ht="15.75" customHeight="1"/>
+    <row r="773" ht="15.75" customHeight="1"/>
+    <row r="774" ht="15.75" customHeight="1"/>
+    <row r="775" ht="15.75" customHeight="1"/>
+    <row r="776" ht="15.75" customHeight="1"/>
+    <row r="777" ht="15.75" customHeight="1"/>
+    <row r="778" ht="15.75" customHeight="1"/>
+    <row r="779" ht="15.75" customHeight="1"/>
+    <row r="780" ht="15.75" customHeight="1"/>
+    <row r="781" ht="15.75" customHeight="1"/>
+    <row r="782" ht="15.75" customHeight="1"/>
+    <row r="783" ht="15.75" customHeight="1"/>
+    <row r="784" ht="15.75" customHeight="1"/>
+    <row r="785" ht="15.75" customHeight="1"/>
+    <row r="786" ht="15.75" customHeight="1"/>
+    <row r="787" ht="15.75" customHeight="1"/>
+    <row r="788" ht="15.75" customHeight="1"/>
+    <row r="789" ht="15.75" customHeight="1"/>
+    <row r="790" ht="15.75" customHeight="1"/>
+    <row r="791" ht="15.75" customHeight="1"/>
+    <row r="792" ht="15.75" customHeight="1"/>
+    <row r="793" ht="15.75" customHeight="1"/>
+    <row r="794" ht="15.75" customHeight="1"/>
+    <row r="795" ht="15.75" customHeight="1"/>
+    <row r="796" ht="15.75" customHeight="1"/>
+    <row r="797" ht="15.75" customHeight="1"/>
+    <row r="798" ht="15.75" customHeight="1"/>
+    <row r="799" ht="15.75" customHeight="1"/>
+    <row r="800" ht="15.75" customHeight="1"/>
+    <row r="801" ht="15.75" customHeight="1"/>
+    <row r="802" ht="15.75" customHeight="1"/>
+    <row r="803" ht="15.75" customHeight="1"/>
+    <row r="804" ht="15.75" customHeight="1"/>
+    <row r="805" ht="15.75" customHeight="1"/>
+    <row r="806" ht="15.75" customHeight="1"/>
+    <row r="807" ht="15.75" customHeight="1"/>
+    <row r="808" ht="15.75" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="G4:Q13 G15:Q16 G23:Q24 G34:Q34">
@@ -15475,16 +15464,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q105"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>55</v>
       </c>
@@ -15496,7 +15485,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>163</v>
       </c>
@@ -15509,7 +15498,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>128</v>
       </c>
@@ -15530,7 +15519,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -15541,7 +15530,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>228</v>
       </c>
@@ -15559,7 +15548,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8">
       <c r="B7" s="148" t="s">
         <v>224</v>
       </c>
@@ -15575,7 +15564,7 @@
       <c r="F7" s="364"/>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="B8" s="148" t="s">
         <v>225</v>
       </c>
@@ -15591,7 +15580,7 @@
       <c r="F8" s="364"/>
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:8">
       <c r="B9" s="205" t="s">
         <v>190</v>
       </c>
@@ -15607,7 +15596,7 @@
       <c r="F9" s="364"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="149" t="s">
         <v>227</v>
       </c>
@@ -15621,7 +15610,7 @@
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="14" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:8" ht="13.15" thickBot="1">
       <c r="B11" s="207" t="s">
         <v>166</v>
       </c>
@@ -15635,7 +15624,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="14" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.5" thickTop="1">
       <c r="B12" s="149" t="s">
         <v>102</v>
       </c>
@@ -15649,10 +15638,10 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8">
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" ht="13.9">
       <c r="B14" s="36" t="s">
         <v>229</v>
       </c>
@@ -15662,13 +15651,13 @@
       <c r="F14" s="37"/>
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8" ht="13.25" customHeight="1">
       <c r="B16" s="152" t="s">
         <v>133</v>
       </c>
@@ -15678,7 +15667,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:17" ht="13.25" customHeight="1">
       <c r="B17" s="118" t="s">
         <v>134</v>
       </c>
@@ -15688,7 +15677,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:17" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:17" ht="13.25" customHeight="1">
       <c r="B18" s="153" t="s">
         <v>106</v>
       </c>
@@ -15702,10 +15691,10 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:17">
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:17" ht="14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:17" ht="13.15">
       <c r="B20" s="128" t="s">
         <v>107</v>
       </c>
@@ -15723,7 +15712,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:17">
       <c r="B21" s="122">
         <v>1</v>
       </c>
@@ -15745,7 +15734,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:17">
       <c r="B22" s="122">
         <v>2</v>
       </c>
@@ -15767,7 +15756,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:17">
       <c r="B23" s="122">
         <v>3</v>
       </c>
@@ -15799,7 +15788,7 @@
       <c r="P23" s="338"/>
       <c r="Q23" s="338"/>
     </row>
-    <row r="24" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:17">
       <c r="B24" s="122">
         <v>4</v>
       </c>
@@ -15831,7 +15820,7 @@
       <c r="P24" s="338"/>
       <c r="Q24" s="338"/>
     </row>
-    <row r="25" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:17">
       <c r="B25" s="122">
         <v>5</v>
       </c>
@@ -15863,7 +15852,7 @@
       <c r="P25" s="338"/>
       <c r="Q25" s="338"/>
     </row>
-    <row r="26" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:17">
       <c r="B26" s="122">
         <v>6</v>
       </c>
@@ -15885,7 +15874,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:17">
       <c r="B27" s="122">
         <v>7</v>
       </c>
@@ -15907,7 +15896,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:17">
       <c r="B28" s="122">
         <v>8</v>
       </c>
@@ -15929,7 +15918,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:17">
       <c r="B29" s="122">
         <v>9</v>
       </c>
@@ -15951,7 +15940,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:17">
       <c r="B30" s="122">
         <v>10</v>
       </c>
@@ -15973,7 +15962,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:17">
       <c r="B31" s="122">
         <v>11</v>
       </c>
@@ -15995,7 +15984,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:17">
       <c r="B32" s="122">
         <v>12</v>
       </c>
@@ -16017,7 +16006,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:17">
       <c r="B33" s="122">
         <v>13</v>
       </c>
@@ -16049,7 +16038,7 @@
       <c r="P33" s="338"/>
       <c r="Q33" s="338"/>
     </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:17">
       <c r="B34" s="122">
         <v>14</v>
       </c>
@@ -16081,7 +16070,7 @@
       <c r="P34" s="338"/>
       <c r="Q34" s="338"/>
     </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:17">
       <c r="B35" s="122">
         <v>15</v>
       </c>
@@ -16113,7 +16102,7 @@
       <c r="P35" s="338"/>
       <c r="Q35" s="338"/>
     </row>
-    <row r="36" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:17">
       <c r="B36" s="122">
         <v>16</v>
       </c>
@@ -16135,7 +16124,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:17">
       <c r="B37" s="122">
         <v>17</v>
       </c>
@@ -16157,7 +16146,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:17">
       <c r="B38" s="122">
         <v>18</v>
       </c>
@@ -16179,7 +16168,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:17">
       <c r="B39" s="122">
         <v>19</v>
       </c>
@@ -16201,7 +16190,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:17">
       <c r="B40" s="122">
         <v>20</v>
       </c>
@@ -16223,7 +16212,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:17">
       <c r="B41" s="122">
         <v>21</v>
       </c>
@@ -16245,7 +16234,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:17">
       <c r="B42" s="122">
         <v>22</v>
       </c>
@@ -16267,7 +16256,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:17">
       <c r="B43" s="122">
         <v>23</v>
       </c>
@@ -16289,7 +16278,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:17">
       <c r="B44" s="122">
         <v>24</v>
       </c>
@@ -16311,7 +16300,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:17">
       <c r="B45" s="122">
         <v>25</v>
       </c>
@@ -16333,7 +16322,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:17">
       <c r="B46" s="122">
         <v>26</v>
       </c>
@@ -16355,7 +16344,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:17">
       <c r="B47" s="122">
         <v>27</v>
       </c>
@@ -16387,7 +16376,7 @@
       <c r="P47" s="338"/>
       <c r="Q47" s="338"/>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:17">
       <c r="B48" s="122">
         <v>28</v>
       </c>
@@ -16419,7 +16408,7 @@
       <c r="P48" s="338"/>
       <c r="Q48" s="338"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:17">
       <c r="B49" s="122">
         <v>29</v>
       </c>
@@ -16451,7 +16440,7 @@
       <c r="P49" s="338"/>
       <c r="Q49" s="338"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:17">
       <c r="B50" s="122">
         <v>30</v>
       </c>
@@ -16483,7 +16472,7 @@
       <c r="P50" s="338"/>
       <c r="Q50" s="338"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:17">
       <c r="B51" s="126" t="s">
         <v>131</v>
       </c>
@@ -16505,7 +16494,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:17">
       <c r="C52" s="114"/>
       <c r="E52" s="127" t="s">
         <v>100</v>
@@ -16516,11 +16505,11 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:17">
       <c r="C53" s="114"/>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:17" ht="13.15">
       <c r="B54" s="119" t="s">
         <v>129</v>
       </c>
@@ -16530,7 +16519,7 @@
       <c r="F54" s="117"/>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:17" ht="13.15">
       <c r="A55" s="133">
         <f>F52</f>
         <v>40044694407.569565</v>
@@ -16557,7 +16546,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:17" ht="13.15">
       <c r="A56" s="143">
         <v>5</v>
       </c>
@@ -16579,7 +16568,7 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:17" ht="13.15">
       <c r="A57" s="143">
         <v>10</v>
       </c>
@@ -16600,7 +16589,7 @@
       </c>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:17" ht="13.15">
       <c r="A58" s="143">
         <v>15</v>
       </c>
@@ -16631,7 +16620,7 @@
       <c r="P58" s="338"/>
       <c r="Q58" s="338"/>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:17" ht="13.15">
       <c r="A59" s="144">
         <v>20</v>
       </c>
@@ -16662,7 +16651,7 @@
       <c r="P59" s="338"/>
       <c r="Q59" s="338"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:17" ht="13.15">
       <c r="A60" s="144">
         <v>25</v>
       </c>
@@ -16693,7 +16682,7 @@
       <c r="P60" s="338"/>
       <c r="Q60" s="338"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:17" ht="13.15">
       <c r="A61" s="144">
         <v>30</v>
       </c>
@@ -16724,7 +16713,7 @@
       <c r="P61" s="338"/>
       <c r="Q61" s="338"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:17">
       <c r="C62" s="338"/>
       <c r="D62" s="114"/>
       <c r="E62" s="114"/>
@@ -16741,7 +16730,7 @@
       <c r="P62" s="338"/>
       <c r="Q62" s="338"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:17" ht="13.15">
       <c r="B63" s="119" t="s">
         <v>130</v>
       </c>
@@ -16761,7 +16750,7 @@
       <c r="P63" s="338"/>
       <c r="Q63" s="338"/>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:17" ht="13.15">
       <c r="B64" s="132">
         <f>B55</f>
         <v>0</v>
@@ -16784,7 +16773,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="143">
         <v>0</v>
       </c>
@@ -16810,7 +16799,7 @@
       </c>
       <c r="H65" s="120"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="143">
         <f t="shared" ref="A66:A71" si="3">A56</f>
         <v>5</v>
@@ -16837,7 +16826,7 @@
       </c>
       <c r="H66" s="120"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:8" ht="13.15">
       <c r="A67" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -16864,7 +16853,7 @@
       </c>
       <c r="H67" s="120"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="A68" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -16891,7 +16880,7 @@
       </c>
       <c r="H68" s="120"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8" ht="13.15">
       <c r="A69" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -16918,7 +16907,7 @@
       </c>
       <c r="H69" s="120"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8" ht="13.15">
       <c r="A70" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -16944,7 +16933,7 @@
         <v>200.35228338516606</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8" ht="13.15">
       <c r="A71" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -16970,7 +16959,7 @@
         <v>256.95760946976043</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" ht="13.15">
       <c r="B73" s="171" t="s">
         <v>117</v>
       </c>
@@ -16987,7 +16976,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -17009,7 +16998,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -17032,7 +17021,7 @@
       </c>
       <c r="H75" s="120"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="B76" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -17055,7 +17044,7 @@
       </c>
       <c r="H76" s="120"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="B77" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -17078,7 +17067,7 @@
       </c>
       <c r="H77" s="120"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:8">
       <c r="B78" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -17100,14 +17089,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:8">
       <c r="B79" s="155"/>
       <c r="C79" s="155"/>
       <c r="D79" s="155"/>
       <c r="E79" s="155"/>
       <c r="F79" s="156"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:8">
       <c r="B80" s="155" t="s">
         <v>310</v>
       </c>
@@ -17115,26 +17104,26 @@
         <v>105</v>
       </c>
     </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:3">
       <c r="C81" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:3">
       <c r="C82" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:3">
       <c r="C92" s="115"/>
     </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:3">
       <c r="C93" s="115"/>
     </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:3">
       <c r="C94" s="115"/>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="101" spans="3:17">
       <c r="C101" s="338"/>
       <c r="G101" s="338"/>
       <c r="H101" s="338"/>
@@ -17148,7 +17137,7 @@
       <c r="P101" s="338"/>
       <c r="Q101" s="338"/>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="102" spans="3:17">
       <c r="C102" s="338"/>
       <c r="G102" s="338"/>
       <c r="H102" s="338"/>
@@ -17162,7 +17151,7 @@
       <c r="P102" s="338"/>
       <c r="Q102" s="338"/>
     </row>
-    <row r="103" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="103" spans="3:17">
       <c r="C103" s="338"/>
       <c r="G103" s="338"/>
       <c r="H103" s="338"/>
@@ -17176,7 +17165,7 @@
       <c r="P103" s="338"/>
       <c r="Q103" s="338"/>
     </row>
-    <row r="104" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="104" spans="3:17">
       <c r="C104" s="338"/>
       <c r="G104" s="338"/>
       <c r="H104" s="338"/>
@@ -17190,7 +17179,7 @@
       <c r="P104" s="338"/>
       <c r="Q104" s="338"/>
     </row>
-    <row r="105" spans="3:17" x14ac:dyDescent="0.15">
+    <row r="105" spans="3:17">
       <c r="C105" s="338"/>
       <c r="G105" s="338"/>
       <c r="H105" s="338"/>
@@ -17235,16 +17224,16 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:H89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="6.1640625" customWidth="1"/>
+    <col min="1" max="1" width="6.1328125" customWidth="1"/>
     <col min="2" max="2" width="24.6640625" customWidth="1"/>
     <col min="3" max="6" width="20.6640625" customWidth="1"/>
     <col min="7" max="7" width="5.6640625" customWidth="1"/>
-    <col min="8" max="8" width="56.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="56.796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:8" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>443</v>
       </c>
@@ -17256,7 +17245,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:8" ht="13.15">
       <c r="B3" s="109" t="s">
         <v>442</v>
       </c>
@@ -17269,7 +17258,7 @@
       </c>
       <c r="H3" s="120"/>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:8">
       <c r="B4" s="100" t="s">
         <v>440</v>
       </c>
@@ -17290,7 +17279,7 @@
       </c>
       <c r="H4" s="120"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:8">
       <c r="B5" s="205" t="s">
         <v>123</v>
       </c>
@@ -17301,7 +17290,7 @@
       <c r="E5" s="148"/>
       <c r="H5" s="120"/>
     </row>
-    <row r="6" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:8" ht="13.25" customHeight="1">
       <c r="B6" s="149" t="s">
         <v>441</v>
       </c>
@@ -17317,7 +17306,7 @@
       <c r="F6" s="364"/>
       <c r="H6" s="120"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:8" ht="13.15">
       <c r="B7" s="149" t="s">
         <v>444</v>
       </c>
@@ -17331,10 +17320,10 @@
       </c>
       <c r="H7" s="120"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:8">
       <c r="H8" s="120"/>
     </row>
-    <row r="9" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="13.9">
       <c r="B9" s="36" t="s">
         <v>229</v>
       </c>
@@ -17344,13 +17333,13 @@
       <c r="F9" s="37"/>
       <c r="H9" s="120"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:8" ht="13.15">
       <c r="B10" s="119" t="s">
         <v>135</v>
       </c>
       <c r="H10" s="120"/>
     </row>
-    <row r="11" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:8" ht="13.25" customHeight="1">
       <c r="B11" s="152" t="s">
         <v>133</v>
       </c>
@@ -17360,7 +17349,7 @@
       </c>
       <c r="H11" s="120"/>
     </row>
-    <row r="12" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:8" ht="13.25" customHeight="1">
       <c r="B12" s="118" t="s">
         <v>134</v>
       </c>
@@ -17370,7 +17359,7 @@
       </c>
       <c r="H12" s="120"/>
     </row>
-    <row r="13" spans="2:8" ht="13.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:8" ht="13.25" customHeight="1">
       <c r="B13" s="153" t="s">
         <v>106</v>
       </c>
@@ -17384,10 +17373,10 @@
       </c>
       <c r="H13" s="120"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:8">
       <c r="H14" s="120"/>
     </row>
-    <row r="15" spans="2:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:8" ht="13.15">
       <c r="B15" s="128" t="s">
         <v>107</v>
       </c>
@@ -17405,7 +17394,7 @@
       </c>
       <c r="H15" s="120"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:8">
       <c r="B16" s="122">
         <v>1</v>
       </c>
@@ -17427,7 +17416,7 @@
       </c>
       <c r="H16" s="120"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:8">
       <c r="B17" s="122">
         <v>2</v>
       </c>
@@ -17449,7 +17438,7 @@
       </c>
       <c r="H17" s="120"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:8">
       <c r="B18" s="122">
         <v>3</v>
       </c>
@@ -17471,7 +17460,7 @@
       </c>
       <c r="H18" s="120"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:8">
       <c r="B19" s="122">
         <v>4</v>
       </c>
@@ -17493,7 +17482,7 @@
       </c>
       <c r="H19" s="120"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:8">
       <c r="B20" s="122">
         <v>5</v>
       </c>
@@ -17515,7 +17504,7 @@
       </c>
       <c r="H20" s="120"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:8">
       <c r="B21" s="122">
         <v>6</v>
       </c>
@@ -17537,7 +17526,7 @@
       </c>
       <c r="H21" s="120"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:8">
       <c r="B22" s="122">
         <v>7</v>
       </c>
@@ -17559,7 +17548,7 @@
       </c>
       <c r="H22" s="120"/>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:8">
       <c r="B23" s="122">
         <v>8</v>
       </c>
@@ -17581,7 +17570,7 @@
       </c>
       <c r="H23" s="120"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:8">
       <c r="B24" s="122">
         <v>9</v>
       </c>
@@ -17603,7 +17592,7 @@
       </c>
       <c r="H24" s="120"/>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:8">
       <c r="B25" s="122">
         <v>10</v>
       </c>
@@ -17625,7 +17614,7 @@
       </c>
       <c r="H25" s="120"/>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:8">
       <c r="B26" s="122">
         <v>11</v>
       </c>
@@ -17647,7 +17636,7 @@
       </c>
       <c r="H26" s="120"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:8">
       <c r="B27" s="122">
         <v>12</v>
       </c>
@@ -17669,7 +17658,7 @@
       </c>
       <c r="H27" s="120"/>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:8">
       <c r="B28" s="122">
         <v>13</v>
       </c>
@@ -17691,7 +17680,7 @@
       </c>
       <c r="H28" s="120"/>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:8">
       <c r="B29" s="122">
         <v>14</v>
       </c>
@@ -17713,7 +17702,7 @@
       </c>
       <c r="H29" s="120"/>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:8">
       <c r="B30" s="122">
         <v>15</v>
       </c>
@@ -17735,7 +17724,7 @@
       </c>
       <c r="H30" s="120"/>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:8">
       <c r="B31" s="122">
         <v>16</v>
       </c>
@@ -17757,7 +17746,7 @@
       </c>
       <c r="H31" s="120"/>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:8">
       <c r="B32" s="122">
         <v>17</v>
       </c>
@@ -17779,7 +17768,7 @@
       </c>
       <c r="H32" s="120"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:8">
       <c r="B33" s="122">
         <v>18</v>
       </c>
@@ -17801,7 +17790,7 @@
       </c>
       <c r="H33" s="120"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:8">
       <c r="B34" s="122">
         <v>19</v>
       </c>
@@ -17823,7 +17812,7 @@
       </c>
       <c r="H34" s="120"/>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:8">
       <c r="B35" s="122">
         <v>20</v>
       </c>
@@ -17845,7 +17834,7 @@
       </c>
       <c r="H35" s="120"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:8">
       <c r="B36" s="122">
         <v>21</v>
       </c>
@@ -17867,7 +17856,7 @@
       </c>
       <c r="H36" s="120"/>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:8">
       <c r="B37" s="122">
         <v>22</v>
       </c>
@@ -17889,7 +17878,7 @@
       </c>
       <c r="H37" s="120"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:8">
       <c r="B38" s="122">
         <v>23</v>
       </c>
@@ -17911,7 +17900,7 @@
       </c>
       <c r="H38" s="120"/>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:8">
       <c r="B39" s="122">
         <v>24</v>
       </c>
@@ -17933,7 +17922,7 @@
       </c>
       <c r="H39" s="120"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:8">
       <c r="B40" s="122">
         <v>25</v>
       </c>
@@ -17955,7 +17944,7 @@
       </c>
       <c r="H40" s="120"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:8">
       <c r="B41" s="122">
         <v>26</v>
       </c>
@@ -17977,7 +17966,7 @@
       </c>
       <c r="H41" s="120"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:8">
       <c r="B42" s="122">
         <v>27</v>
       </c>
@@ -17999,7 +17988,7 @@
       </c>
       <c r="H42" s="120"/>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:8">
       <c r="B43" s="122">
         <v>28</v>
       </c>
@@ -18021,7 +18010,7 @@
       </c>
       <c r="H43" s="120"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:8">
       <c r="B44" s="122">
         <v>29</v>
       </c>
@@ -18043,7 +18032,7 @@
       </c>
       <c r="H44" s="120"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:8">
       <c r="B45" s="122">
         <v>30</v>
       </c>
@@ -18065,7 +18054,7 @@
       </c>
       <c r="H45" s="120"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:8">
       <c r="B46" s="126" t="s">
         <v>131</v>
       </c>
@@ -18087,7 +18076,7 @@
       </c>
       <c r="H46" s="120"/>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:8">
       <c r="C47" s="114"/>
       <c r="E47" s="127" t="s">
         <v>100</v>
@@ -18098,11 +18087,11 @@
       </c>
       <c r="H47" s="120"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:8">
       <c r="C48" s="114"/>
       <c r="H48" s="120"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:8" ht="13.15">
       <c r="B49" s="119" t="s">
         <v>129</v>
       </c>
@@ -18112,7 +18101,7 @@
       <c r="F49" s="117"/>
       <c r="H49" s="120"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:8" ht="13.15">
       <c r="A50" s="133">
         <f>F47</f>
         <v>22149527349.487885</v>
@@ -18139,7 +18128,7 @@
       </c>
       <c r="H50" s="120"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:8" ht="13.15">
       <c r="A51" s="143">
         <v>5</v>
       </c>
@@ -18161,7 +18150,7 @@
       </c>
       <c r="H51" s="120"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:8" ht="13.15">
       <c r="A52" s="143">
         <v>10</v>
       </c>
@@ -18182,7 +18171,7 @@
       </c>
       <c r="H52" s="120"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:8" ht="13.15">
       <c r="A53" s="143">
         <v>15</v>
       </c>
@@ -18203,7 +18192,7 @@
       </c>
       <c r="H53" s="120"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:8" ht="13.15">
       <c r="A54" s="144">
         <v>20</v>
       </c>
@@ -18224,7 +18213,7 @@
       </c>
       <c r="H54" s="120"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:8" ht="13.15">
       <c r="A55" s="144">
         <v>25</v>
       </c>
@@ -18245,7 +18234,7 @@
       </c>
       <c r="H55" s="120"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:8" ht="13.15">
       <c r="A56" s="144">
         <v>30</v>
       </c>
@@ -18266,14 +18255,14 @@
       </c>
       <c r="H56" s="120"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:8">
       <c r="C57" s="114"/>
       <c r="D57" s="114"/>
       <c r="E57" s="114"/>
       <c r="F57" s="114"/>
       <c r="H57" s="120"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:8" ht="13.15">
       <c r="B58" s="119" t="s">
         <v>130</v>
       </c>
@@ -18283,7 +18272,7 @@
       <c r="F58" s="114"/>
       <c r="H58" s="120"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:8" ht="13.15">
       <c r="B59" s="132">
         <f>B50</f>
         <v>0</v>
@@ -18306,7 +18295,7 @@
       </c>
       <c r="H59" s="120"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:8" ht="13.15">
       <c r="A60" s="143">
         <v>0</v>
       </c>
@@ -18332,7 +18321,7 @@
       </c>
       <c r="H60" s="120"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:8" ht="13.15">
       <c r="A61" s="143">
         <f t="shared" ref="A61:A66" si="3">A51</f>
         <v>5</v>
@@ -18359,7 +18348,7 @@
       </c>
       <c r="H61" s="120"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:8" ht="13.15">
       <c r="A62" s="143">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -18386,7 +18375,7 @@
       </c>
       <c r="H62" s="120"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:8" ht="13.15">
       <c r="A63" s="143">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -18413,7 +18402,7 @@
       </c>
       <c r="H63" s="120"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:8" ht="13.15">
       <c r="A64" s="144">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -18440,7 +18429,7 @@
       </c>
       <c r="H64" s="120"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:8" ht="13.15">
       <c r="A65" s="144">
         <f t="shared" si="3"/>
         <v>25</v>
@@ -18466,7 +18455,7 @@
         <v>110.86706842581737</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:8" ht="13.15">
       <c r="A66" s="144">
         <f t="shared" si="3"/>
         <v>30</v>
@@ -18492,7 +18481,7 @@
         <v>142.17661484104494</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="14" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" ht="13.15">
       <c r="B68" s="171" t="s">
         <v>117</v>
       </c>
@@ -18509,7 +18498,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:8">
       <c r="B69" s="127" t="str">
         <f>Scenarios!B54</f>
         <v>Snowball Scenario</v>
@@ -18531,7 +18520,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:8">
       <c r="B70" s="127" t="str">
         <f>Scenarios!B36</f>
         <v>Optimistic</v>
@@ -18554,7 +18543,7 @@
       </c>
       <c r="H70" s="120"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:8">
       <c r="B71" s="127" t="str">
         <f>Scenarios!B24</f>
         <v>Base</v>
@@ -18577,7 +18566,7 @@
       </c>
       <c r="H71" s="120"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:8">
       <c r="B72" s="127" t="str">
         <f>Scenarios!B30</f>
         <v>Pessimistic</v>
@@ -18600,7 +18589,7 @@
       </c>
       <c r="H72" s="120"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:8">
       <c r="B73" s="127" t="str">
         <f>Scenarios!B48</f>
         <v>Devil's advocate</v>
@@ -18622,14 +18611,14 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:8">
       <c r="B74" s="155"/>
       <c r="C74" s="155"/>
       <c r="D74" s="155"/>
       <c r="E74" s="155"/>
       <c r="F74" s="156"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:8">
       <c r="B75" s="155" t="s">
         <v>310</v>
       </c>
@@ -18637,23 +18626,23 @@
         <v>105</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:8">
       <c r="C76" s="155" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:8">
       <c r="C77" s="155" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:3">
       <c r="C87" s="115"/>
     </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:3">
       <c r="C88" s="115"/>
     </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:3">
       <c r="C89" s="115"/>
     </row>
   </sheetData>
@@ -18683,7 +18672,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7DB08D6-06C8-485A-B381-9C0DCA9661D4}">
   <dimension ref="B2:I110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="2.6640625" customWidth="1"/>
     <col min="2" max="2" width="22.6640625" customWidth="1"/>
@@ -18693,7 +18682,7 @@
     <col min="8" max="9" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:9" ht="13.9">
       <c r="B2" s="36" t="s">
         <v>145</v>
       </c>
@@ -18706,7 +18695,7 @@
       </c>
       <c r="I2" s="249"/>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:9" ht="13.15">
       <c r="B3" s="159" t="s">
         <v>148</v>
       </c>
@@ -18715,10 +18704,10 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-57.7</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.15">
+        <v>-58.76</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9">
       <c r="B4" s="152" t="s">
         <v>146</v>
       </c>
@@ -18738,7 +18727,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:9">
       <c r="H5" s="247">
         <v>2</v>
       </c>
@@ -18747,7 +18736,7 @@
         <v>2.4</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:9" ht="13.15">
       <c r="B6" s="159" t="s">
         <v>95</v>
       </c>
@@ -18767,7 +18756,7 @@
         <v>85.120030767403335</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:9" ht="12.75" customHeight="1">
       <c r="B7" s="100" t="s">
         <v>275</v>
       </c>
@@ -18792,7 +18781,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:9">
       <c r="B8" s="100" t="s">
         <v>66</v>
       </c>
@@ -18814,7 +18803,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:9">
       <c r="B9" s="100" t="s">
         <v>57</v>
       </c>
@@ -18836,7 +18825,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:9">
       <c r="E10" s="366"/>
       <c r="F10" s="366"/>
       <c r="H10" s="247">
@@ -18847,7 +18836,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:9" ht="13.15">
       <c r="B11" s="159" t="s">
         <v>447</v>
       </c>
@@ -18861,7 +18850,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:9" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:9">
       <c r="B12" s="118" t="s">
         <v>144</v>
       </c>
@@ -18880,7 +18869,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:9">
       <c r="B13" s="148" t="s">
         <v>152</v>
       </c>
@@ -18898,7 +18887,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:9">
       <c r="B14" s="100" t="s">
         <v>66</v>
       </c>
@@ -18909,7 +18898,7 @@
       <c r="E14" s="366"/>
       <c r="F14" s="366"/>
     </row>
-    <row r="16" spans="2:9" ht="16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:9" ht="13.9">
       <c r="B16" s="36" t="s">
         <v>162</v>
       </c>
@@ -18918,7 +18907,7 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6" ht="13.15">
       <c r="B17" s="109" t="s">
         <v>151</v>
       </c>
@@ -18926,7 +18915,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="152" t="s">
         <v>133</v>
       </c>
@@ -18938,24 +18927,24 @@
       </c>
       <c r="F18" s="367"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="E19" s="367"/>
       <c r="F19" s="367"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6" ht="13.15">
       <c r="B20" s="159" t="s">
         <v>303</v>
       </c>
       <c r="E20" s="367"/>
       <c r="F20" s="367"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="100" t="s">
         <v>277</v>
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>57.7</v>
+        <v>58.76</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -18964,7 +18953,7 @@
       <c r="E21" s="367"/>
       <c r="F21" s="367"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="100" t="s">
         <v>278</v>
       </c>
@@ -18979,7 +18968,7 @@
       <c r="E22" s="367"/>
       <c r="F22" s="367"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6" ht="13.15">
       <c r="B24" s="159" t="s">
         <v>115</v>
       </c>
@@ -18988,7 +18977,7 @@
       </c>
       <c r="F24" s="159"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="152" t="s">
         <v>133</v>
       </c>
@@ -19000,7 +18989,7 @@
       <c r="E25" s="365"/>
       <c r="F25" s="365"/>
     </row>
-    <row r="26" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="118" t="s">
         <v>134</v>
       </c>
@@ -19011,7 +19000,7 @@
       <c r="E26" s="365"/>
       <c r="F26" s="365"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="100" t="s">
         <v>113</v>
       </c>
@@ -19026,7 +19015,7 @@
       <c r="E27" s="365"/>
       <c r="F27" s="365"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="100" t="s">
         <v>147</v>
       </c>
@@ -19037,7 +19026,7 @@
       <c r="E28" s="365"/>
       <c r="F28" s="365"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6" ht="13.15">
       <c r="B30" s="159" t="s">
         <v>116</v>
       </c>
@@ -19046,7 +19035,7 @@
       </c>
       <c r="F30" s="159"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="152" t="s">
         <v>133</v>
       </c>
@@ -19058,7 +19047,7 @@
       <c r="E31" s="365"/>
       <c r="F31" s="365"/>
     </row>
-    <row r="32" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="118" t="s">
         <v>134</v>
       </c>
@@ -19069,7 +19058,7 @@
       <c r="E32" s="365"/>
       <c r="F32" s="365"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:6">
       <c r="B33" s="100" t="s">
         <v>113</v>
       </c>
@@ -19084,7 +19073,7 @@
       <c r="E33" s="365"/>
       <c r="F33" s="365"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:6">
       <c r="B34" s="100" t="s">
         <v>147</v>
       </c>
@@ -19095,7 +19084,7 @@
       <c r="E34" s="365"/>
       <c r="F34" s="365"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:6" ht="13.15">
       <c r="B36" s="159" t="s">
         <v>114</v>
       </c>
@@ -19104,7 +19093,7 @@
       </c>
       <c r="F36" s="159"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:6">
       <c r="B37" s="152" t="s">
         <v>133</v>
       </c>
@@ -19116,7 +19105,7 @@
       <c r="E37" s="365"/>
       <c r="F37" s="365"/>
     </row>
-    <row r="38" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:6">
       <c r="B38" s="118" t="s">
         <v>134</v>
       </c>
@@ -19127,7 +19116,7 @@
       <c r="E38" s="365"/>
       <c r="F38" s="365"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:6">
       <c r="B39" s="100" t="s">
         <v>113</v>
       </c>
@@ -19142,7 +19131,7 @@
       <c r="E39" s="365"/>
       <c r="F39" s="365"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:6">
       <c r="B40" s="100" t="s">
         <v>147</v>
       </c>
@@ -19154,7 +19143,7 @@
       <c r="E40" s="365"/>
       <c r="F40" s="365"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:6" ht="13.15">
       <c r="B42" s="100" t="s">
         <v>120</v>
       </c>
@@ -19167,7 +19156,7 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="44" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" ht="13.9">
       <c r="B44" s="36" t="s">
         <v>161</v>
       </c>
@@ -19176,12 +19165,12 @@
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:6" ht="13.15">
       <c r="B45" s="109" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:6">
       <c r="B46" s="152" t="s">
         <v>133</v>
       </c>
@@ -19191,12 +19180,12 @@
       <c r="E46" s="100"/>
       <c r="F46" s="100"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:6" ht="13.15">
       <c r="B47" s="159"/>
       <c r="E47" s="159"/>
       <c r="F47" s="159"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:6" ht="13.15">
       <c r="B48" s="159" t="s">
         <v>165</v>
       </c>
@@ -19205,7 +19194,7 @@
       </c>
       <c r="F48" s="159"/>
     </row>
-    <row r="49" spans="2:6" ht="12.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:6" ht="12.75" customHeight="1">
       <c r="B49" s="152" t="s">
         <v>133</v>
       </c>
@@ -19217,7 +19206,7 @@
       <c r="E49" s="365"/>
       <c r="F49" s="365"/>
     </row>
-    <row r="50" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:6">
       <c r="B50" s="118" t="s">
         <v>134</v>
       </c>
@@ -19228,7 +19217,7 @@
       <c r="E50" s="365"/>
       <c r="F50" s="365"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:6">
       <c r="B51" s="100" t="s">
         <v>113</v>
       </c>
@@ -19243,7 +19232,7 @@
       <c r="E51" s="365"/>
       <c r="F51" s="365"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:6">
       <c r="B52" s="100" t="s">
         <v>147</v>
       </c>
@@ -19254,7 +19243,7 @@
       <c r="E52" s="365"/>
       <c r="F52" s="365"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:6" ht="13.15">
       <c r="B54" s="159" t="s">
         <v>316</v>
       </c>
@@ -19263,7 +19252,7 @@
       </c>
       <c r="F54" s="159"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:6">
       <c r="B55" s="152" t="s">
         <v>133</v>
       </c>
@@ -19275,7 +19264,7 @@
       <c r="E55" s="365"/>
       <c r="F55" s="365"/>
     </row>
-    <row r="56" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:6">
       <c r="B56" s="118" t="s">
         <v>134</v>
       </c>
@@ -19286,7 +19275,7 @@
       <c r="E56" s="365"/>
       <c r="F56" s="365"/>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:6">
       <c r="B57" s="100" t="s">
         <v>113</v>
       </c>
@@ -19301,7 +19290,7 @@
       <c r="E57" s="365"/>
       <c r="F57" s="365"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:6">
       <c r="B58" s="100" t="s">
         <v>147</v>
       </c>
@@ -19312,7 +19301,7 @@
       <c r="E58" s="365"/>
       <c r="F58" s="365"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:6" ht="13.15">
       <c r="B60" s="100" t="s">
         <v>120</v>
       </c>
@@ -19332,7 +19321,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="62" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:6" ht="13.9">
       <c r="B62" s="36" t="s">
         <v>349</v>
       </c>
@@ -19341,7 +19330,7 @@
       <c r="E62" s="37"/>
       <c r="F62" s="37"/>
     </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:6" ht="13.15">
       <c r="B63" s="109" t="s">
         <v>304</v>
       </c>
@@ -19349,7 +19338,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:6">
       <c r="B64" s="152" t="s">
         <v>133</v>
       </c>
@@ -19362,7 +19351,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="65" spans="2:6" ht="14" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:6">
       <c r="B65" s="118" t="s">
         <v>134</v>
       </c>
@@ -19374,7 +19363,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:6">
       <c r="B66" s="100" t="s">
         <v>102</v>
       </c>
@@ -19390,7 +19379,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:6" ht="13.15">
       <c r="B68" s="109" t="s">
         <v>350</v>
       </c>
@@ -19398,7 +19387,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:6">
       <c r="B69" s="100" t="s">
         <v>305</v>
       </c>
@@ -19408,7 +19397,7 @@
       </c>
       <c r="E69" s="134"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:6">
       <c r="B70" s="100" t="s">
         <v>293</v>
       </c>
@@ -19420,7 +19409,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:6">
       <c r="B71" s="100" t="s">
         <v>292</v>
       </c>
@@ -19430,7 +19419,7 @@
       </c>
       <c r="E71" s="251"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:6">
       <c r="B72" s="100" t="s">
         <v>284</v>
       </c>
@@ -19446,7 +19435,7 @@
         <v>-1.0530971019379444E-3</v>
       </c>
     </row>
-    <row r="74" spans="2:6" ht="16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:6" ht="13.9">
       <c r="B74" s="36" t="s">
         <v>127</v>
       </c>
@@ -19455,12 +19444,12 @@
       <c r="E74" s="37"/>
       <c r="F74" s="37"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:6" ht="13.15">
       <c r="B75" s="109" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:6">
       <c r="B76" s="246" t="s">
         <v>297</v>
       </c>
@@ -19470,7 +19459,7 @@
       </c>
       <c r="D76" s="134"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:6">
       <c r="B77" s="100" t="s">
         <v>111</v>
       </c>
@@ -19483,12 +19472,12 @@
         <v>CNY</v>
       </c>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:6" ht="13.15">
       <c r="B79" s="109" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:6">
       <c r="B80" s="148" t="s">
         <v>299</v>
       </c>
@@ -19497,7 +19486,7 @@
         <v>0.33699999999999997</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:8">
       <c r="B81" s="100" t="s">
         <v>121</v>
       </c>
@@ -19509,7 +19498,7 @@
       <c r="E81" s="100"/>
       <c r="F81" s="100"/>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:8">
       <c r="B82" s="100" t="s">
         <v>122</v>
       </c>
@@ -19519,7 +19508,7 @@
       </c>
       <c r="D82" s="116"/>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:8" ht="13.15">
       <c r="B83" s="110" t="s">
         <v>101</v>
       </c>
@@ -19539,45 +19528,45 @@
         <v>0.53151557024171581</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:8">
       <c r="E84" s="120"/>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:8" ht="13.15">
       <c r="B85" s="109" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:8">
       <c r="B86" s="148" t="s">
         <v>300</v>
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>57.7</v>
+        <v>58.76</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
         <v>CNY</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:8" ht="13.15">
       <c r="B87" s="100" t="s">
         <v>298</v>
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.1647356777052329</v>
-      </c>
-    </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.15">
+        <v>0.15744323570336882</v>
+      </c>
+    </row>
+    <row r="88" spans="2:8">
       <c r="B88" s="100"/>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:8" ht="13.15">
       <c r="B89" s="109" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:8">
       <c r="B90" s="148" t="s">
         <v>413</v>
       </c>
@@ -19586,7 +19575,7 @@
         <v>0.187</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:8">
       <c r="B91" s="100" t="s">
         <v>121</v>
       </c>
@@ -19598,7 +19587,7 @@
       <c r="E91" s="100"/>
       <c r="F91" s="100"/>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:8">
       <c r="B92" s="100" t="s">
         <v>122</v>
       </c>
@@ -19608,7 +19597,7 @@
       </c>
       <c r="D92" s="116"/>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:8" ht="13.15">
       <c r="B93" s="110" t="s">
         <v>101</v>
       </c>
@@ -19628,14 +19617,14 @@
         <v>0.33969071867212519</v>
       </c>
     </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:8" ht="13.15">
       <c r="B95" s="109" t="s">
         <v>397</v>
       </c>
       <c r="G95" s="2"/>
       <c r="H95" s="281"/>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:8">
       <c r="B96" s="148" t="s">
         <v>403</v>
       </c>
@@ -19646,7 +19635,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="281"/>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:8">
       <c r="B97" s="100" t="s">
         <v>121</v>
       </c>
@@ -19658,7 +19647,7 @@
       <c r="G97" s="2"/>
       <c r="H97" s="281"/>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:8">
       <c r="B98" s="100" t="s">
         <v>122</v>
       </c>
@@ -19670,7 +19659,7 @@
       <c r="G98" s="2"/>
       <c r="H98" s="281"/>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:8" ht="13.15">
       <c r="B99" s="110" t="s">
         <v>398</v>
       </c>
@@ -19689,15 +19678,15 @@
         <v>8.2827207627903632E-2</v>
       </c>
     </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:8">
       <c r="B100" s="100"/>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:8" ht="13.15">
       <c r="B101" s="109" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:8">
       <c r="B102" s="148" t="s">
         <v>421</v>
       </c>
@@ -19706,7 +19695,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:8">
       <c r="B103" s="100" t="s">
         <v>121</v>
       </c>
@@ -19716,7 +19705,7 @@
       </c>
       <c r="D103" s="116"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:8">
       <c r="B104" s="100" t="s">
         <v>122</v>
       </c>
@@ -19726,7 +19715,7 @@
       </c>
       <c r="D104" s="116"/>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:8" ht="13.15">
       <c r="B105" s="110" t="s">
         <v>398</v>
       </c>
@@ -19745,16 +19734,16 @@
         <v>0.14689628955752243</v>
       </c>
     </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:8">
       <c r="B106" s="100"/>
     </row>
-    <row r="107" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" ht="14.65">
       <c r="E107" s="285" t="s">
         <v>324</v>
       </c>
       <c r="F107" s="282"/>
     </row>
-    <row r="108" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" ht="13.9">
       <c r="E108" s="278" t="s">
         <v>325</v>
       </c>
@@ -19762,7 +19751,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="109" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" ht="13.9">
       <c r="E109" s="279" t="s">
         <v>325</v>
       </c>
@@ -19770,7 +19759,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="2:8" ht="16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" ht="13.9">
       <c r="E110" s="280" t="s">
         <v>325</v>
       </c>

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{227A1C9A-AF91-4468-8D67-2AC37D10E0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E97BEA4-A8BC-4EF5-97F1-ED23B073AB98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>58.76</v>
+        <v>58.65</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>28438.14759448</v>
+        <v>28384.910762700001</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15744323570336882</v>
+        <v>0.15819162411968435</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.3843109299267698E-2</v>
+        <v>7.3981604474424034E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.084411164057182E-2</v>
+        <v>4.0920716112531966E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13462,12 +13462,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.084411164057182E-2</v>
+        <v>4.0920716112531966E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.084411164057182E-2</v>
+        <v>4.0920716112531966E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14661,50 +14661,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.3843109299267698E-2</v>
+        <v>7.3981604474424034E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>8.1695855086821034E-2</v>
+        <v>8.1849078344443368E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>9.3804842719410739E-2</v>
+        <v>9.398077678077707E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>8.935929600565963E-2</v>
+        <v>8.9526892298253363E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>8.3556186452842615E-2</v>
+        <v>8.3712898823001397E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.6801382056985343E-2</v>
+        <v>4.6889159585139964E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6429090744009011E-2</v>
+        <v>1.6459904042932131E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.5061585936306205E-2</v>
+        <v>1.5089834435078477E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2124142539682341E-2</v>
+        <v>1.2146881766951993E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.1972384729661069E-2</v>
+        <v>1.1994839330177058E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>6.6283980126957626E-3</v>
+        <v>6.6408297907246889E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14718,43 +14718,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9097292976868058E-2</v>
+        <v>7.9245642545963627E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5349689918844446E-2</v>
+        <v>9.5528521391838012E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.0965827939585325E-2</v>
+        <v>9.1136437335550449E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4364010983109514E-2</v>
+        <v>8.4522238454689078E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.1618538625917194E-2</v>
+        <v>6.1734106217542953E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.5618297660900142E-2</v>
+        <v>2.5666345619002426E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4813182525354386E-2</v>
+        <v>1.4840965135376362E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1467777003284916E-2</v>
+        <v>1.1489285195447939E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9208960792918649E-3</v>
+        <v>4.9301253814013632E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.3995085470969735E-3</v>
+        <v>-5.4096355025987754E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18704,7 +18704,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-58.76</v>
+        <v>-58.65</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18944,7 +18944,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>58.76</v>
+        <v>58.65</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19542,7 +19542,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>58.76</v>
+        <v>58.65</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15744323570336882</v>
+        <v>0.15819162411968435</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E97BEA4-A8BC-4EF5-97F1-ED23B073AB98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F1A27F-2D8C-4383-8F94-DA480E6D127F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>58.65</v>
+        <v>57.8</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>28384.910762700001</v>
+        <v>27973.535244399998</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.15819162411968435</v>
+        <v>0.16403992868784401</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.3981604474424034E-2</v>
+        <v>7.5069569246106749E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.0920716112531966E-2</v>
+        <v>4.1522491349480967E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+      <c r="B134" s="362" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="361"/>
-      <c r="D134" s="361"/>
-      <c r="E134" s="361"/>
-      <c r="F134" s="361"/>
+      <c r="C134" s="362"/>
+      <c r="D134" s="362"/>
+      <c r="E134" s="362"/>
+      <c r="F134" s="362"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="359" t="s">
+      <c r="B138" s="363" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="359"/>
-      <c r="D138" s="359"/>
-      <c r="E138" s="359"/>
-      <c r="F138" s="359"/>
+      <c r="C138" s="363"/>
+      <c r="D138" s="363"/>
+      <c r="E138" s="363"/>
+      <c r="F138" s="363"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="356" t="s">
+      <c r="B139" s="358" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="356"/>
-      <c r="D139" s="356"/>
-      <c r="E139" s="356"/>
-      <c r="F139" s="356"/>
+      <c r="C139" s="358"/>
+      <c r="D139" s="358"/>
+      <c r="E139" s="358"/>
+      <c r="F139" s="358"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="363" t="s">
+      <c r="B179" s="357" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="356"/>
-      <c r="D179" s="356"/>
-      <c r="E179" s="356"/>
-      <c r="F179" s="356"/>
+      <c r="C179" s="358"/>
+      <c r="D179" s="358"/>
+      <c r="E179" s="358"/>
+      <c r="F179" s="358"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="357" t="s">
+      <c r="B188" s="359" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="357"/>
-      <c r="D188" s="357"/>
-      <c r="E188" s="357"/>
-      <c r="F188" s="357"/>
+      <c r="C188" s="359"/>
+      <c r="D188" s="359"/>
+      <c r="E188" s="359"/>
+      <c r="F188" s="359"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="362" t="s">
+      <c r="B191" s="356" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="362"/>
-      <c r="D191" s="362"/>
-      <c r="E191" s="362"/>
-      <c r="F191" s="362"/>
+      <c r="C191" s="356"/>
+      <c r="D191" s="356"/>
+      <c r="E191" s="356"/>
+      <c r="F191" s="356"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="362" t="s">
+      <c r="B192" s="356" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="362"/>
-      <c r="D192" s="362"/>
-      <c r="E192" s="362"/>
-      <c r="F192" s="362"/>
+      <c r="C192" s="356"/>
+      <c r="D192" s="356"/>
+      <c r="E192" s="356"/>
+      <c r="F192" s="356"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,17 +5887,6 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5914,6 +5903,17 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">
@@ -13462,12 +13462,12 @@
       </c>
       <c r="C93" s="23">
         <f>C90/Market_Price</f>
-        <v>4.0920716112531966E-2</v>
+        <v>4.1522491349480967E-2</v>
       </c>
       <c r="E93" s="268"/>
       <c r="G93" s="23">
         <f t="shared" ref="G93:Q93" si="39">IF(G$4="","",G90/Market_Price)</f>
-        <v>4.0920716112531966E-2</v>
+        <v>4.1522491349480967E-2</v>
       </c>
       <c r="H93" s="23">
         <f t="shared" si="39"/>
@@ -14661,50 +14661,50 @@
       </c>
       <c r="C125" s="77">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>7.3981604474424034E-2</v>
+        <v>7.5069569246106749E-2</v>
       </c>
       <c r="D125" s="27"/>
       <c r="E125" s="265"/>
       <c r="F125" s="27"/>
       <c r="G125" s="77">
         <f t="shared" ref="G125" si="50">IF(G$4="","",G124/Market_Price)</f>
-        <v>8.1849078344443368E-2</v>
+        <v>8.3052741261273433E-2</v>
       </c>
       <c r="H125" s="77">
         <f t="shared" ref="H125" si="51">IF(H$4="","",H124/Market_Price)</f>
-        <v>9.398077678077707E-2</v>
+        <v>9.536284702755321E-2</v>
       </c>
       <c r="I125" s="77">
         <f t="shared" ref="I125" si="52">IF(I$4="","",I124/Market_Price)</f>
-        <v>8.9526892298253363E-2</v>
+        <v>9.0843464243815925E-2</v>
       </c>
       <c r="J125" s="77">
         <f t="shared" ref="J125" si="53">IF(J$4="","",J124/Market_Price)</f>
-        <v>8.3712898823001397E-2</v>
+        <v>8.4943970864516119E-2</v>
       </c>
       <c r="K125" s="77">
         <f t="shared" ref="K125" si="54">IF(K$4="","",K124/Market_Price)</f>
-        <v>4.6889159585139964E-2</v>
+        <v>4.7578706049627315E-2</v>
       </c>
       <c r="L125" s="77">
         <f t="shared" ref="L125" si="55">IF(L$4="","",L124/Market_Price)</f>
-        <v>1.6459904042932131E-2</v>
+        <v>1.670196145532819E-2</v>
       </c>
       <c r="M125" s="77">
         <f t="shared" ref="M125" si="56">IF(M$4="","",M124/Market_Price)</f>
-        <v>1.5089834435078477E-2</v>
+        <v>1.5311743765006101E-2</v>
       </c>
       <c r="N125" s="77">
         <f t="shared" ref="N125" si="57">IF(N$4="","",N124/Market_Price)</f>
-        <v>1.2146881766951993E-2</v>
+        <v>1.2325512381171876E-2</v>
       </c>
       <c r="O125" s="77">
         <f t="shared" ref="O125" si="58">IF(O$4="","",O124/Market_Price)</f>
-        <v>1.1994839330177058E-2</v>
+        <v>1.2171234026209073E-2</v>
       </c>
       <c r="P125" s="77">
         <f t="shared" ref="P125" si="59">IF(P$4="","",P124/Market_Price)</f>
-        <v>6.6408297907246889E-3</v>
+        <v>6.7384890523529938E-3</v>
       </c>
       <c r="Q125" s="77" t="str">
         <f t="shared" ref="Q125" si="60">IF(Q$4="","",Q124/Market_Price)</f>
@@ -14718,43 +14718,43 @@
       <c r="C126" s="169"/>
       <c r="G126" s="23">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.9245642545963627E-2</v>
+        <v>8.0411019642227799E-2</v>
       </c>
       <c r="H126" s="23">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.5528521391838012E-2</v>
+        <v>9.6933352588776819E-2</v>
       </c>
       <c r="I126" s="23">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>9.1136437335550449E-2</v>
+        <v>9.247667906107325E-2</v>
       </c>
       <c r="J126" s="23">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>8.4522238454689078E-2</v>
+        <v>8.5765212549610989E-2</v>
       </c>
       <c r="K126" s="23">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.1734106217542953E-2</v>
+        <v>6.2641960720742115E-2</v>
       </c>
       <c r="L126" s="23">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.5666345619002426E-2</v>
+        <v>2.6043791878105408E-2</v>
       </c>
       <c r="M126" s="23">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.4840965135376362E-2</v>
+        <v>1.5059214622661311E-2</v>
       </c>
       <c r="N126" s="23">
         <f>IF(N$4="","",(Data!J47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>1.1489285195447939E-2</v>
+        <v>1.1658245271851587E-2</v>
       </c>
       <c r="O126" s="23">
         <f>IF(O$4="","",(Data!K47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.9301253814013632E-3</v>
+        <v>5.002627225245501E-3</v>
       </c>
       <c r="P126" s="23">
         <f>IF(P$4="","",(Data!L47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>-5.4096355025987754E-3</v>
+        <v>-5.4891889658722874E-3</v>
       </c>
       <c r="Q126" s="23" t="str">
         <f>IF(Q$4="","",(Data!M47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -18704,7 +18704,7 @@
       </c>
       <c r="I3" s="124">
         <f>-Market_Price</f>
-        <v>-58.65</v>
+        <v>-57.8</v>
       </c>
     </row>
     <row r="4" spans="2:9">
@@ -18944,7 +18944,7 @@
       </c>
       <c r="C21" s="160">
         <f>Market_Price</f>
-        <v>58.65</v>
+        <v>57.8</v>
       </c>
       <c r="D21" t="str">
         <f>Market_currency</f>
@@ -19542,7 +19542,7 @@
       </c>
       <c r="C86" s="116">
         <f>Market_Price</f>
-        <v>58.65</v>
+        <v>57.8</v>
       </c>
       <c r="D86" t="str">
         <f>Market_currency</f>
@@ -19555,7 +19555,7 @@
       </c>
       <c r="C87" s="237">
         <f ca="1">IRR(OFFSET($I$3, 0, 0, $C$76 + 1, 1))</f>
-        <v>0.15819162411968435</v>
+        <v>0.16403992868784401</v>
       </c>
     </row>
     <row r="88" spans="2:8">

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F1A27F-2D8C-4383-8F94-DA480E6D127F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD29B88B-B7EB-48DA-BAB4-56EBC0CA9B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="358" t="s">
+      <c r="B18" s="356" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="358"/>
-      <c r="D18" s="358"/>
-      <c r="E18" s="358"/>
-      <c r="F18" s="358"/>
+      <c r="C18" s="356"/>
+      <c r="D18" s="356"/>
+      <c r="E18" s="356"/>
+      <c r="F18" s="356"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="358" t="s">
+      <c r="B36" s="356" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="358"/>
-      <c r="D36" s="358"/>
-      <c r="E36" s="358"/>
-      <c r="F36" s="358"/>
+      <c r="C36" s="356"/>
+      <c r="D36" s="356"/>
+      <c r="E36" s="356"/>
+      <c r="F36" s="356"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="361" t="s">
+      <c r="B37" s="358" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="361"/>
-      <c r="D37" s="361"/>
-      <c r="E37" s="361"/>
-      <c r="F37" s="361"/>
+      <c r="C37" s="358"/>
+      <c r="D37" s="358"/>
+      <c r="E37" s="358"/>
+      <c r="F37" s="358"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="359" t="s">
+      <c r="B40" s="357" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="359"/>
-      <c r="D40" s="359"/>
-      <c r="E40" s="359"/>
-      <c r="F40" s="359"/>
+      <c r="C40" s="357"/>
+      <c r="D40" s="357"/>
+      <c r="E40" s="357"/>
+      <c r="F40" s="357"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="359" t="s">
+      <c r="B43" s="357" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="359"/>
-      <c r="D43" s="359"/>
-      <c r="E43" s="359"/>
-      <c r="F43" s="359"/>
+      <c r="C43" s="357"/>
+      <c r="D43" s="357"/>
+      <c r="E43" s="357"/>
+      <c r="F43" s="357"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="359" t="s">
+      <c r="B47" s="357" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="359"/>
-      <c r="D47" s="359"/>
-      <c r="E47" s="359"/>
-      <c r="F47" s="359"/>
+      <c r="C47" s="357"/>
+      <c r="D47" s="357"/>
+      <c r="E47" s="357"/>
+      <c r="F47" s="357"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="359" t="s">
+      <c r="B50" s="357" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="359"/>
-      <c r="D50" s="359"/>
-      <c r="E50" s="359"/>
-      <c r="F50" s="359"/>
+      <c r="C50" s="357"/>
+      <c r="D50" s="357"/>
+      <c r="E50" s="357"/>
+      <c r="F50" s="357"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="359" t="s">
+      <c r="B58" s="357" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="359"/>
-      <c r="D58" s="359"/>
-      <c r="E58" s="359"/>
-      <c r="F58" s="359"/>
+      <c r="C58" s="357"/>
+      <c r="D58" s="357"/>
+      <c r="E58" s="357"/>
+      <c r="F58" s="357"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="359" t="s">
+      <c r="B61" s="357" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="358" t="s">
+      <c r="B64" s="356" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="358"/>
-      <c r="D64" s="358"/>
-      <c r="E64" s="358"/>
-      <c r="F64" s="358"/>
+      <c r="C64" s="356"/>
+      <c r="D64" s="356"/>
+      <c r="E64" s="356"/>
+      <c r="F64" s="356"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="358" t="s">
+      <c r="B65" s="356" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="358"/>
-      <c r="D65" s="358"/>
-      <c r="E65" s="358"/>
-      <c r="F65" s="358"/>
+      <c r="C65" s="356"/>
+      <c r="D65" s="356"/>
+      <c r="E65" s="356"/>
+      <c r="F65" s="356"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="358" t="s">
+      <c r="B80" s="356" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="358"/>
-      <c r="D80" s="358"/>
-      <c r="E80" s="358"/>
-      <c r="F80" s="358"/>
+      <c r="C80" s="356"/>
+      <c r="D80" s="356"/>
+      <c r="E80" s="356"/>
+      <c r="F80" s="356"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="361" t="s">
+      <c r="B81" s="358" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="361"/>
-      <c r="D81" s="361"/>
-      <c r="E81" s="361"/>
-      <c r="F81" s="361"/>
+      <c r="C81" s="358"/>
+      <c r="D81" s="358"/>
+      <c r="E81" s="358"/>
+      <c r="F81" s="358"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="358" t="s">
+      <c r="B89" s="356" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="358"/>
-      <c r="D89" s="358"/>
-      <c r="E89" s="358"/>
-      <c r="F89" s="358"/>
+      <c r="C89" s="356"/>
+      <c r="D89" s="356"/>
+      <c r="E89" s="356"/>
+      <c r="F89" s="356"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="358" t="s">
+      <c r="B90" s="356" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="358"/>
-      <c r="D90" s="358"/>
-      <c r="E90" s="358"/>
-      <c r="F90" s="358"/>
+      <c r="C90" s="356"/>
+      <c r="D90" s="356"/>
+      <c r="E90" s="356"/>
+      <c r="F90" s="356"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="358" t="s">
+      <c r="B97" s="356" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="358"/>
-      <c r="D97" s="358"/>
-      <c r="E97" s="358"/>
-      <c r="F97" s="358"/>
+      <c r="C97" s="356"/>
+      <c r="D97" s="356"/>
+      <c r="E97" s="356"/>
+      <c r="F97" s="356"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="358" t="s">
+      <c r="B101" s="356" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="358"/>
-      <c r="D101" s="358"/>
-      <c r="E101" s="358"/>
-      <c r="F101" s="358"/>
+      <c r="C101" s="356"/>
+      <c r="D101" s="356"/>
+      <c r="E101" s="356"/>
+      <c r="F101" s="356"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="358" t="s">
+      <c r="B116" s="356" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="358"/>
-      <c r="D116" s="358"/>
-      <c r="E116" s="358"/>
-      <c r="F116" s="358"/>
+      <c r="C116" s="356"/>
+      <c r="D116" s="356"/>
+      <c r="E116" s="356"/>
+      <c r="F116" s="356"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="359" t="s">
+      <c r="B123" s="357" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="359"/>
-      <c r="D123" s="359"/>
-      <c r="E123" s="359"/>
-      <c r="F123" s="359"/>
+      <c r="C123" s="357"/>
+      <c r="D123" s="357"/>
+      <c r="E123" s="357"/>
+      <c r="F123" s="357"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="362" t="s">
+      <c r="B134" s="361" t="s">
         <v>370</v>
       </c>
-      <c r="C134" s="362"/>
-      <c r="D134" s="362"/>
-      <c r="E134" s="362"/>
-      <c r="F134" s="362"/>
+      <c r="C134" s="361"/>
+      <c r="D134" s="361"/>
+      <c r="E134" s="361"/>
+      <c r="F134" s="361"/>
     </row>
     <row r="136" spans="1:6" ht="13.9">
       <c r="A136" s="222" t="s">
@@ -5443,22 +5443,22 @@
       <c r="F136" s="36"/>
     </row>
     <row r="138" spans="1:6">
-      <c r="B138" s="363" t="s">
+      <c r="B138" s="359" t="s">
         <v>368</v>
       </c>
-      <c r="C138" s="363"/>
-      <c r="D138" s="363"/>
-      <c r="E138" s="363"/>
-      <c r="F138" s="363"/>
+      <c r="C138" s="359"/>
+      <c r="D138" s="359"/>
+      <c r="E138" s="359"/>
+      <c r="F138" s="359"/>
     </row>
     <row r="139" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B139" s="358" t="s">
+      <c r="B139" s="356" t="s">
         <v>369</v>
       </c>
-      <c r="C139" s="358"/>
-      <c r="D139" s="358"/>
-      <c r="E139" s="358"/>
-      <c r="F139" s="358"/>
+      <c r="C139" s="356"/>
+      <c r="D139" s="356"/>
+      <c r="E139" s="356"/>
+      <c r="F139" s="356"/>
     </row>
     <row r="140" spans="1:6">
       <c r="B140" s="210" t="s">
@@ -5791,13 +5791,13 @@
       <c r="F177" s="36"/>
     </row>
     <row r="179" spans="1:6">
-      <c r="B179" s="357" t="s">
+      <c r="B179" s="363" t="s">
         <v>376</v>
       </c>
-      <c r="C179" s="358"/>
-      <c r="D179" s="358"/>
-      <c r="E179" s="358"/>
-      <c r="F179" s="358"/>
+      <c r="C179" s="356"/>
+      <c r="D179" s="356"/>
+      <c r="E179" s="356"/>
+      <c r="F179" s="356"/>
     </row>
     <row r="181" spans="1:6">
       <c r="B181" s="210" t="s">
@@ -5834,13 +5834,13 @@
       </c>
     </row>
     <row r="188" spans="1:6" ht="46.5" customHeight="1">
-      <c r="B188" s="359" t="s">
+      <c r="B188" s="357" t="s">
         <v>381</v>
       </c>
-      <c r="C188" s="359"/>
-      <c r="D188" s="359"/>
-      <c r="E188" s="359"/>
-      <c r="F188" s="359"/>
+      <c r="C188" s="357"/>
+      <c r="D188" s="357"/>
+      <c r="E188" s="357"/>
+      <c r="F188" s="357"/>
     </row>
     <row r="190" spans="1:6">
       <c r="B190" s="1" t="s">
@@ -5848,22 +5848,22 @@
       </c>
     </row>
     <row r="191" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B191" s="356" t="s">
+      <c r="B191" s="362" t="s">
         <v>382</v>
       </c>
-      <c r="C191" s="356"/>
-      <c r="D191" s="356"/>
-      <c r="E191" s="356"/>
-      <c r="F191" s="356"/>
+      <c r="C191" s="362"/>
+      <c r="D191" s="362"/>
+      <c r="E191" s="362"/>
+      <c r="F191" s="362"/>
     </row>
     <row r="192" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B192" s="356" t="s">
+      <c r="B192" s="362" t="s">
         <v>383</v>
       </c>
-      <c r="C192" s="356"/>
-      <c r="D192" s="356"/>
-      <c r="E192" s="356"/>
-      <c r="F192" s="356"/>
+      <c r="C192" s="362"/>
+      <c r="D192" s="362"/>
+      <c r="E192" s="362"/>
+      <c r="F192" s="362"/>
     </row>
     <row r="194" spans="2:2">
       <c r="B194" s="1" t="s">
@@ -5887,6 +5887,17 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="B191:F191"/>
+    <mergeCell ref="B192:F192"/>
+    <mergeCell ref="B179:F179"/>
+    <mergeCell ref="B188:F188"/>
+    <mergeCell ref="B182:F182"/>
+    <mergeCell ref="B81:F81"/>
+    <mergeCell ref="B123:F123"/>
+    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B134:F134"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B101:F101"/>
     <mergeCell ref="B139:F139"/>
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B18:F18"/>
@@ -5903,17 +5914,6 @@
     <mergeCell ref="B61:F61"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="B80:F80"/>
-    <mergeCell ref="B81:F81"/>
-    <mergeCell ref="B123:F123"/>
-    <mergeCell ref="B89:F89"/>
-    <mergeCell ref="B134:F134"/>
-    <mergeCell ref="B64:F64"/>
-    <mergeCell ref="B101:F101"/>
-    <mergeCell ref="B191:F191"/>
-    <mergeCell ref="B192:F192"/>
-    <mergeCell ref="B179:F179"/>
-    <mergeCell ref="B188:F188"/>
-    <mergeCell ref="B182:F182"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="5">

--- a/financial_models/opportunities/600132.SS_Valuation.xlsx
+++ b/financial_models/opportunities/600132.SS_Valuation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD29B88B-B7EB-48DA-BAB4-56EBC0CA9B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0880C8B7-39F2-4049-91EE-5EBF352B67E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1837" yWindow="1837" windowWidth="12691" windowHeight="7643" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Thesis" sheetId="6" r:id="rId1"/>
@@ -3894,29 +3894,29 @@
     </xf>
     <xf numFmtId="181" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="181" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4334,7 +4334,7 @@
         <v>94</v>
       </c>
       <c r="C12" s="50">
-        <v>57.8</v>
+        <v>58.48</v>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="48"/>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="C14" s="35">
         <f>Thesis!C12*Common_Shares/1000000</f>
-        <v>27973.535244399998</v>
+        <v>28302.635659039996</v>
       </c>
       <c r="D14" s="35" t="str">
         <f>IF(D11="","",Thesis!D12*Common_Shares/1000000)</f>
@@ -4392,13 +4392,13 @@
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B18" s="356" t="s">
+      <c r="B18" s="358" t="s">
         <v>359</v>
       </c>
-      <c r="C18" s="356"/>
-      <c r="D18" s="356"/>
-      <c r="E18" s="356"/>
-      <c r="F18" s="356"/>
+      <c r="C18" s="358"/>
+      <c r="D18" s="358"/>
+      <c r="E18" s="358"/>
+      <c r="F18" s="358"/>
     </row>
     <row r="20" spans="2:6">
       <c r="B20" s="45" t="s">
@@ -4481,7 +4481,7 @@
       </c>
       <c r="E26" s="301">
         <f ca="1">Scenarios!C87</f>
-        <v>0.16403992868784401</v>
+        <v>0.15935199863821548</v>
       </c>
     </row>
     <row r="27" spans="2:6">
@@ -4598,22 +4598,22 @@
       <c r="F34" s="36"/>
     </row>
     <row r="36" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B36" s="356" t="s">
+      <c r="B36" s="358" t="s">
         <v>360</v>
       </c>
-      <c r="C36" s="356"/>
-      <c r="D36" s="356"/>
-      <c r="E36" s="356"/>
-      <c r="F36" s="356"/>
+      <c r="C36" s="358"/>
+      <c r="D36" s="358"/>
+      <c r="E36" s="358"/>
+      <c r="F36" s="358"/>
     </row>
     <row r="37" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B37" s="358" t="s">
+      <c r="B37" s="361" t="s">
         <v>339</v>
       </c>
-      <c r="C37" s="358"/>
-      <c r="D37" s="358"/>
-      <c r="E37" s="358"/>
-      <c r="F37" s="358"/>
+      <c r="C37" s="361"/>
+      <c r="D37" s="361"/>
+      <c r="E37" s="361"/>
+      <c r="F37" s="361"/>
     </row>
     <row r="39" spans="1:6">
       <c r="B39" s="210" t="s">
@@ -4625,13 +4625,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B40" s="357" t="s">
+      <c r="B40" s="359" t="s">
         <v>231</v>
       </c>
-      <c r="C40" s="357"/>
-      <c r="D40" s="357"/>
-      <c r="E40" s="357"/>
-      <c r="F40" s="357"/>
+      <c r="C40" s="359"/>
+      <c r="D40" s="359"/>
+      <c r="E40" s="359"/>
+      <c r="F40" s="359"/>
     </row>
     <row r="41" spans="1:6">
       <c r="B41" s="47" t="s">
@@ -4651,13 +4651,13 @@
       <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B43" s="357" t="s">
+      <c r="B43" s="359" t="s">
         <v>233</v>
       </c>
-      <c r="C43" s="357"/>
-      <c r="D43" s="357"/>
-      <c r="E43" s="357"/>
-      <c r="F43" s="357"/>
+      <c r="C43" s="359"/>
+      <c r="D43" s="359"/>
+      <c r="E43" s="359"/>
+      <c r="F43" s="359"/>
     </row>
     <row r="44" spans="1:6">
       <c r="B44" s="47" t="s">
@@ -4686,13 +4686,13 @@
       </c>
     </row>
     <row r="47" spans="1:6">
-      <c r="B47" s="357" t="s">
+      <c r="B47" s="359" t="s">
         <v>236</v>
       </c>
-      <c r="C47" s="357"/>
-      <c r="D47" s="357"/>
-      <c r="E47" s="357"/>
-      <c r="F47" s="357"/>
+      <c r="C47" s="359"/>
+      <c r="D47" s="359"/>
+      <c r="E47" s="359"/>
+      <c r="F47" s="359"/>
     </row>
     <row r="48" spans="1:6">
       <c r="B48" s="47" t="s">
@@ -4708,13 +4708,13 @@
       </c>
     </row>
     <row r="50" spans="2:6">
-      <c r="B50" s="357" t="s">
+      <c r="B50" s="359" t="s">
         <v>240</v>
       </c>
-      <c r="C50" s="357"/>
-      <c r="D50" s="357"/>
-      <c r="E50" s="357"/>
-      <c r="F50" s="357"/>
+      <c r="C50" s="359"/>
+      <c r="D50" s="359"/>
+      <c r="E50" s="359"/>
+      <c r="F50" s="359"/>
     </row>
     <row r="51" spans="2:6">
       <c r="B51" s="47" t="s">
@@ -4778,13 +4778,13 @@
       </c>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="357" t="s">
+      <c r="B58" s="359" t="s">
         <v>241</v>
       </c>
-      <c r="C58" s="357"/>
-      <c r="D58" s="357"/>
-      <c r="E58" s="357"/>
-      <c r="F58" s="357"/>
+      <c r="C58" s="359"/>
+      <c r="D58" s="359"/>
+      <c r="E58" s="359"/>
+      <c r="F58" s="359"/>
     </row>
     <row r="59" spans="2:6">
       <c r="B59" s="47" t="s">
@@ -4800,7 +4800,7 @@
       </c>
     </row>
     <row r="61" spans="2:6">
-      <c r="B61" s="357" t="s">
+      <c r="B61" s="359" t="s">
         <v>338</v>
       </c>
       <c r="C61" s="360"/>
@@ -4822,22 +4822,22 @@
       </c>
     </row>
     <row r="64" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B64" s="356" t="s">
+      <c r="B64" s="358" t="s">
         <v>343</v>
       </c>
-      <c r="C64" s="356"/>
-      <c r="D64" s="356"/>
-      <c r="E64" s="356"/>
-      <c r="F64" s="356"/>
+      <c r="C64" s="358"/>
+      <c r="D64" s="358"/>
+      <c r="E64" s="358"/>
+      <c r="F64" s="358"/>
     </row>
     <row r="65" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B65" s="356" t="s">
+      <c r="B65" s="358" t="s">
         <v>361</v>
       </c>
-      <c r="C65" s="356"/>
-      <c r="D65" s="356"/>
-      <c r="E65" s="356"/>
-      <c r="F65" s="356"/>
+      <c r="C65" s="358"/>
+      <c r="D65" s="358"/>
+      <c r="E65" s="358"/>
+      <c r="F65" s="358"/>
     </row>
     <row r="67" spans="1:6">
       <c r="B67" s="47" t="s">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C69" s="92">
         <f>Normalized_FCF!C125</f>
-        <v>7.5069569246106749E-2</v>
+        <v>7.4196667278128778E-2</v>
       </c>
       <c r="F69" s="314"/>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="C70" s="92">
         <f>Normalized_FCF!C93</f>
-        <v>4.1522491349480967E-2</v>
+        <v>4.1039671682626538E-2</v>
       </c>
       <c r="E70" s="47" t="s">
         <v>448</v>
@@ -4972,22 +4972,22 @@
     </row>
     <row r="80" spans="1:6" ht="24.5" customHeight="1">
       <c r="A80" s="17"/>
-      <c r="B80" s="356" t="s">
+      <c r="B80" s="358" t="s">
         <v>362</v>
       </c>
-      <c r="C80" s="356"/>
-      <c r="D80" s="356"/>
-      <c r="E80" s="356"/>
-      <c r="F80" s="356"/>
+      <c r="C80" s="358"/>
+      <c r="D80" s="358"/>
+      <c r="E80" s="358"/>
+      <c r="F80" s="358"/>
     </row>
     <row r="81" spans="1:6">
-      <c r="B81" s="358" t="s">
+      <c r="B81" s="361" t="s">
         <v>252</v>
       </c>
-      <c r="C81" s="358"/>
-      <c r="D81" s="358"/>
-      <c r="E81" s="358"/>
-      <c r="F81" s="358"/>
+      <c r="C81" s="361"/>
+      <c r="D81" s="361"/>
+      <c r="E81" s="361"/>
+      <c r="F81" s="361"/>
     </row>
     <row r="83" spans="1:6">
       <c r="B83" s="210" t="s">
@@ -5031,22 +5031,22 @@
       <c r="C88" s="121"/>
     </row>
     <row r="89" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B89" s="356" t="s">
+      <c r="B89" s="358" t="s">
         <v>363</v>
       </c>
-      <c r="C89" s="356"/>
-      <c r="D89" s="356"/>
-      <c r="E89" s="356"/>
-      <c r="F89" s="356"/>
+      <c r="C89" s="358"/>
+      <c r="D89" s="358"/>
+      <c r="E89" s="358"/>
+      <c r="F89" s="358"/>
     </row>
     <row r="90" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B90" s="356" t="s">
+      <c r="B90" s="358" t="s">
         <v>364</v>
       </c>
-      <c r="C90" s="356"/>
-      <c r="D90" s="356"/>
-      <c r="E90" s="356"/>
-      <c r="F90" s="356"/>
+      <c r="C90" s="358"/>
+      <c r="D90" s="358"/>
+      <c r="E90" s="358"/>
+      <c r="F90" s="358"/>
     </row>
     <row r="92" spans="1:6">
       <c r="B92" s="47" t="s">
@@ -5083,13 +5083,13 @@
       <c r="A96" s="209"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="356" t="s">
+      <c r="B97" s="358" t="s">
         <v>365</v>
       </c>
-      <c r="C97" s="356"/>
-      <c r="D97" s="356"/>
-      <c r="E97" s="356"/>
-      <c r="F97" s="356"/>
+      <c r="C97" s="358"/>
+      <c r="D97" s="358"/>
+      <c r="E97" s="358"/>
+      <c r="F97" s="358"/>
     </row>
     <row r="98" spans="2:6">
       <c r="B98" s="1" t="s">
@@ -5102,13 +5102,13 @@
       </c>
     </row>
     <row r="101" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B101" s="356" t="s">
+      <c r="B101" s="358" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="356"/>
-      <c r="D101" s="356"/>
-      <c r="E101" s="356"/>
-      <c r="F101" s="356"/>
+      <c r="C101" s="358"/>
+      <c r="D101" s="358"/>
+      <c r="E101" s="358"/>
+      <c r="F101" s="358"/>
     </row>
     <row r="102" spans="2:6">
       <c r="B102" s="47" t="s">
@@ -5230,13 +5230,13 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B116" s="356" t="s">
+      <c r="B116" s="358" t="s">
         <v>366</v>
       </c>
-      <c r="C116" s="356"/>
-      <c r="D116" s="356"/>
-      <c r="E116" s="356"/>
-      <c r="F116" s="356"/>
+      <c r="C116" s="358"/>
+      <c r="D116" s="358"/>
+      <c r="E116" s="358"/>
+      <c r="F116" s="358"/>
     </row>
     <row r="118" spans="1:6">
       <c r="B118" s="47" t="s">
@@ -5275,13 +5275,13 @@
       <c r="F121" s="36"/>
     </row>
     <row r="123" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B123" s="357" t="s">
+      <c r="B123" s="359" t="s">
         <v>367</v>
       </c>
-      <c r="C123" s="357"/>
-      <c r="D123" s="357"/>
-      <c r="E123" s="357"/>
-      <c r="F123" s="357"/>
+      <c r="C123" s="359"/>
+      <c r="D123" s="359"/>
+      <c r="E123" s="359"/>
+      <c r="F123" s="359"/>
     </row>
     <row r="125" spans="1:6" ht="12.4">
       <c r="B125" s="233" t="s">
@@ -5424,13 +5424,13 @@
       </c>
     </row>
     <row r="134" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B134" s="361" t="s">
+     